--- a/data/ELC.MI.xlsx
+++ b/data/ELC.MI.xlsx
@@ -62886,6 +62886,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2719">
+      <c r="A2719" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2719" t="n">
+        <v>35171</v>
+      </c>
+      <c r="C2719" t="n">
+        <v>1.16499996185303</v>
+      </c>
+      <c r="D2719" t="n">
+        <v>1.10500001907349</v>
+      </c>
+      <c r="E2719" t="n">
+        <v>1.14999997615814</v>
+      </c>
+      <c r="F2719" t="n">
+        <v>1.12000000476837</v>
+      </c>
+      <c r="G2719" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ELC.MI.xlsx
+++ b/data/ELC.MI.xlsx
@@ -62909,6 +62909,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2720">
+      <c r="A2720" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2720" t="n">
+        <v>12330</v>
+      </c>
+      <c r="C2720" t="n">
+        <v>1.13999998569489</v>
+      </c>
+      <c r="D2720" t="n">
+        <v>1.10500001907349</v>
+      </c>
+      <c r="E2720" t="n">
+        <v>1.10500001907349</v>
+      </c>
+      <c r="F2720" t="n">
+        <v>1.12000000476837</v>
+      </c>
+      <c r="G2720" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ELC.MI.xlsx
+++ b/data/ELC.MI.xlsx
@@ -62932,6 +62932,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2721">
+      <c r="A2721" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2721" t="n">
+        <v>16549</v>
+      </c>
+      <c r="C2721" t="n">
+        <v>1.14499998092651</v>
+      </c>
+      <c r="D2721" t="n">
+        <v>1.10500001907349</v>
+      </c>
+      <c r="E2721" t="n">
+        <v>1.13499999046326</v>
+      </c>
+      <c r="F2721" t="n">
+        <v>1.13999998569489</v>
+      </c>
+      <c r="G2721" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ELC.MI.xlsx
+++ b/data/ELC.MI.xlsx
@@ -62955,6 +62955,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2722">
+      <c r="A2722" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2722" t="n">
+        <v>19168</v>
+      </c>
+      <c r="C2722" t="n">
+        <v>1.12999999523163</v>
+      </c>
+      <c r="D2722" t="n">
+        <v>1.12000000476837</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>1.12999999523163</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ELC.MI.xlsx
+++ b/data/ELC.MI.xlsx
@@ -62796,22 +62796,22 @@
     </row>
     <row r="2715">
       <c r="A2715" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2715" t="n">
-        <v>2632</v>
+        <v>100</v>
       </c>
       <c r="C2715" t="n">
-        <v>1.17999994754791</v>
+        <v>1.16999995708466</v>
       </c>
       <c r="D2715" t="n">
-        <v>1.17999994754791</v>
+        <v>1.16999995708466</v>
       </c>
       <c r="E2715" t="n">
-        <v>1.17999994754791</v>
+        <v>1.16999995708466</v>
       </c>
       <c r="F2715" t="n">
-        <v>1.17999994754791</v>
+        <v>1.16999995708466</v>
       </c>
       <c r="G2715" t="s">
         <v>7</v>
@@ -62819,22 +62819,22 @@
     </row>
     <row r="2716">
       <c r="A2716" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2716" t="n">
-        <v>4400</v>
+        <v>2632</v>
       </c>
       <c r="C2716" t="n">
         <v>1.17999994754791</v>
       </c>
       <c r="D2716" t="n">
-        <v>1.14999997615814</v>
+        <v>1.17999994754791</v>
       </c>
       <c r="E2716" t="n">
         <v>1.17999994754791</v>
       </c>
       <c r="F2716" t="n">
-        <v>1.14999997615814</v>
+        <v>1.17999994754791</v>
       </c>
       <c r="G2716" t="s">
         <v>7</v>
@@ -62842,22 +62842,22 @@
     </row>
     <row r="2717">
       <c r="A2717" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2717" t="n">
-        <v>16011</v>
+        <v>4400</v>
       </c>
       <c r="C2717" t="n">
-        <v>1.16499996185303</v>
+        <v>1.17999994754791</v>
       </c>
       <c r="D2717" t="n">
         <v>1.14999997615814</v>
       </c>
       <c r="E2717" t="n">
+        <v>1.17999994754791</v>
+      </c>
+      <c r="F2717" t="n">
         <v>1.14999997615814</v>
-      </c>
-      <c r="F2717" t="n">
-        <v>1.16499996185303</v>
       </c>
       <c r="G2717" t="s">
         <v>7</v>
@@ -62865,22 +62865,22 @@
     </row>
     <row r="2718">
       <c r="A2718" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2718" t="n">
-        <v>31743</v>
+        <v>16011</v>
       </c>
       <c r="C2718" t="n">
-        <v>1.17499995231628</v>
+        <v>1.16499996185303</v>
       </c>
       <c r="D2718" t="n">
         <v>1.14999997615814</v>
       </c>
       <c r="E2718" t="n">
+        <v>1.14999997615814</v>
+      </c>
+      <c r="F2718" t="n">
         <v>1.16499996185303</v>
-      </c>
-      <c r="F2718" t="n">
-        <v>1.14999997615814</v>
       </c>
       <c r="G2718" t="s">
         <v>7</v>
@@ -62888,22 +62888,22 @@
     </row>
     <row r="2719">
       <c r="A2719" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2719" t="n">
-        <v>35171</v>
+        <v>31743</v>
       </c>
       <c r="C2719" t="n">
+        <v>1.17499995231628</v>
+      </c>
+      <c r="D2719" t="n">
+        <v>1.14999997615814</v>
+      </c>
+      <c r="E2719" t="n">
         <v>1.16499996185303</v>
       </c>
-      <c r="D2719" t="n">
-        <v>1.10500001907349</v>
-      </c>
-      <c r="E2719" t="n">
+      <c r="F2719" t="n">
         <v>1.14999997615814</v>
-      </c>
-      <c r="F2719" t="n">
-        <v>1.12000000476837</v>
       </c>
       <c r="G2719" t="s">
         <v>7</v>
@@ -62911,19 +62911,19 @@
     </row>
     <row r="2720">
       <c r="A2720" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2720" t="n">
-        <v>12330</v>
+        <v>35171</v>
       </c>
       <c r="C2720" t="n">
-        <v>1.13999998569489</v>
+        <v>1.16499996185303</v>
       </c>
       <c r="D2720" t="n">
         <v>1.10500001907349</v>
       </c>
       <c r="E2720" t="n">
-        <v>1.10500001907349</v>
+        <v>1.14999997615814</v>
       </c>
       <c r="F2720" t="n">
         <v>1.12000000476837</v>
@@ -62934,22 +62934,22 @@
     </row>
     <row r="2721">
       <c r="A2721" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2721" t="n">
-        <v>16549</v>
+        <v>12330</v>
       </c>
       <c r="C2721" t="n">
-        <v>1.14499998092651</v>
+        <v>1.13999998569489</v>
       </c>
       <c r="D2721" t="n">
         <v>1.10500001907349</v>
       </c>
       <c r="E2721" t="n">
-        <v>1.13499999046326</v>
+        <v>1.10500001907349</v>
       </c>
       <c r="F2721" t="n">
-        <v>1.13999998569489</v>
+        <v>1.12000000476837</v>
       </c>
       <c r="G2721" t="s">
         <v>7</v>
@@ -62957,24 +62957,47 @@
     </row>
     <row r="2722">
       <c r="A2722" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2722" t="n">
-        <v>19168</v>
+        <v>16549</v>
       </c>
       <c r="C2722" t="n">
+        <v>1.14499998092651</v>
+      </c>
+      <c r="D2722" t="n">
+        <v>1.10500001907349</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>1.13499999046326</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>1.13999998569489</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2723">
+      <c r="A2723" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2723" t="n">
+        <v>3396</v>
+      </c>
+      <c r="C2723" t="n">
+        <v>1.1599999666214</v>
+      </c>
+      <c r="D2723" t="n">
         <v>1.12999999523163</v>
       </c>
-      <c r="D2722" t="n">
-        <v>1.12000000476837</v>
-      </c>
-      <c r="E2722" t="n">
-        <v>1.125</v>
-      </c>
-      <c r="F2722" t="n">
-        <v>1.12999999523163</v>
-      </c>
-      <c r="G2722" t="s">
+      <c r="E2723" t="n">
+        <v>1.13999998569489</v>
+      </c>
+      <c r="F2723" t="n">
+        <v>1.14499998092651</v>
+      </c>
+      <c r="G2723" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ELC.MI.xlsx
+++ b/data/ELC.MI.xlsx
@@ -473,7 +473,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G4" t="n">
-        <v>1.72445023059845</v>
+        <v>1.72445011138916</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>1.81900000572205</v>
       </c>
       <c r="G10" t="n">
-        <v>1.62527191638947</v>
+        <v>1.62527179718018</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G11" t="n">
-        <v>1.59936058521271</v>
+        <v>1.59936046600342</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>1.65199995040894</v>
       </c>
       <c r="G12" t="n">
-        <v>1.47605764865875</v>
+        <v>1.47605776786804</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>1.61099994182587</v>
       </c>
       <c r="G14" t="n">
-        <v>1.43942451477051</v>
+        <v>1.43942439556122</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>1.71800005435944</v>
       </c>
       <c r="G15" t="n">
-        <v>1.53502881526947</v>
+        <v>1.53502869606018</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>1.70700001716614</v>
       </c>
       <c r="G16" t="n">
-        <v>1.52520024776459</v>
+        <v>1.52520036697388</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G17" t="n">
-        <v>1.44746601581573</v>
+        <v>1.44746589660645</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>1.625</v>
       </c>
       <c r="G18" t="n">
-        <v>1.45193338394165</v>
+        <v>1.45193326473236</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G19" t="n">
-        <v>1.46533572673798</v>
+        <v>1.46533584594727</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>1.63100004196167</v>
       </c>
       <c r="G20" t="n">
-        <v>1.45729434490204</v>
+        <v>1.45729446411133</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>1.65100002288818</v>
       </c>
       <c r="G21" t="n">
-        <v>1.47516441345215</v>
+        <v>1.47516429424286</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>1.59099996089935</v>
       </c>
       <c r="G22" t="n">
-        <v>1.4215544462204</v>
+        <v>1.42155432701111</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>1.54499995708466</v>
       </c>
       <c r="G24" t="n">
-        <v>1.38045370578766</v>
+        <v>1.38045358657837</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G28" t="n">
-        <v>1.28216898441315</v>
+        <v>1.28216886520386</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G29" t="n">
-        <v>1.31344127655029</v>
+        <v>1.313441157341</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>1.63199996948242</v>
       </c>
       <c r="G32" t="n">
-        <v>1.45818793773651</v>
+        <v>1.45818781852722</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G35" t="n">
-        <v>1.51001071929932</v>
+        <v>1.51001083850861</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>1.75399994850159</v>
       </c>
       <c r="G36" t="n">
-        <v>1.56719470024109</v>
+        <v>1.5671945810318</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>1.75</v>
       </c>
       <c r="G38" t="n">
-        <v>1.56362044811249</v>
+        <v>1.56362056732178</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>1.74699997901917</v>
       </c>
       <c r="G39" t="n">
-        <v>1.56093990802765</v>
+        <v>1.56094002723694</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G40" t="n">
-        <v>1.5770229101181</v>
+        <v>1.57702302932739</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G42" t="n">
-        <v>1.5814905166626</v>
+        <v>1.58149039745331</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G44" t="n">
-        <v>1.51894593238831</v>
+        <v>1.51894581317902</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G45" t="n">
-        <v>1.5814905166626</v>
+        <v>1.58149039745331</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>1.75</v>
       </c>
       <c r="G47" t="n">
-        <v>1.56362044811249</v>
+        <v>1.56362056732178</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>1.75</v>
       </c>
       <c r="G48" t="n">
-        <v>1.56362044811249</v>
+        <v>1.56362056732178</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>1.75</v>
       </c>
       <c r="G49" t="n">
-        <v>1.56362044811249</v>
+        <v>1.56362056732178</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G50" t="n">
-        <v>1.5814905166626</v>
+        <v>1.58149039745331</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>1.76600003242493</v>
       </c>
       <c r="G51" t="n">
-        <v>1.57791662216187</v>
+        <v>1.57791650295258</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>1.90799999237061</v>
       </c>
       <c r="G56" t="n">
-        <v>1.70479321479797</v>
+        <v>1.70479309558868</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G57" t="n">
-        <v>1.72445023059845</v>
+        <v>1.72445011138916</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>1.93599998950958</v>
       </c>
       <c r="G60" t="n">
-        <v>1.72981107234955</v>
+        <v>1.72981119155884</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>1.94599997997284</v>
       </c>
       <c r="G61" t="n">
-        <v>1.73874592781067</v>
+        <v>1.73874604701996</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G63" t="n">
-        <v>1.75125503540039</v>
+        <v>1.75125515460968</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G65" t="n">
-        <v>1.72445023059845</v>
+        <v>1.72445011138916</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G68" t="n">
-        <v>1.69317758083344</v>
+        <v>1.69317770004272</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G71" t="n">
-        <v>1.6708402633667</v>
+        <v>1.67084014415741</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>1.88100004196167</v>
       </c>
       <c r="G72" t="n">
-        <v>1.68066883087158</v>
+        <v>1.68066871166229</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G75" t="n">
-        <v>1.71998262405396</v>
+        <v>1.71998250484467</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G76" t="n">
-        <v>1.71104764938354</v>
+        <v>1.71104776859283</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G77" t="n">
-        <v>1.70658004283905</v>
+        <v>1.70658016204834</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G78" t="n">
-        <v>1.71998262405396</v>
+        <v>1.71998250484467</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G80" t="n">
-        <v>1.71998262405396</v>
+        <v>1.71998250484467</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>1.92700004577637</v>
       </c>
       <c r="G82" t="n">
-        <v>1.72176969051361</v>
+        <v>1.72176957130432</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>1.91600000858307</v>
       </c>
       <c r="G86" t="n">
-        <v>1.71194112300873</v>
+        <v>1.71194124221802</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G87" t="n">
-        <v>1.70658004283905</v>
+        <v>1.70658016204834</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>1.84800004959106</v>
       </c>
       <c r="G90" t="n">
-        <v>1.65118324756622</v>
+        <v>1.65118336677551</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>1.85199999809265</v>
       </c>
       <c r="G93" t="n">
-        <v>1.65475738048553</v>
+        <v>1.65475726127625</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>1.88699996471405</v>
       </c>
       <c r="G94" t="n">
-        <v>1.68602955341339</v>
+        <v>1.68602967262268</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>1.90600001811981</v>
       </c>
       <c r="G97" t="n">
-        <v>1.70300626754761</v>
+        <v>1.70300614833832</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>1.9190000295639</v>
       </c>
       <c r="G99" t="n">
-        <v>1.71462166309357</v>
+        <v>1.71462178230286</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>1.93799996376038</v>
       </c>
       <c r="G104" t="n">
-        <v>1.74048626422882</v>
+        <v>1.74048638343811</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G106" t="n">
-        <v>1.73330187797546</v>
+        <v>1.73330175876617</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G109" t="n">
-        <v>1.7153400182724</v>
+        <v>1.71534013748169</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G112" t="n">
-        <v>1.7153400182724</v>
+        <v>1.71534013748169</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G120" t="n">
-        <v>1.63451242446899</v>
+        <v>1.63451254367828</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>1.875</v>
       </c>
       <c r="G121" t="n">
-        <v>1.68390727043152</v>
+        <v>1.68390715122223</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>1.82400000095367</v>
       </c>
       <c r="G122" t="n">
-        <v>1.6381049156189</v>
+        <v>1.63810479640961</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G131" t="n">
-        <v>1.59409880638123</v>
+        <v>1.59409868717194</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G136" t="n">
-        <v>1.45489585399628</v>
+        <v>1.45489573478699</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>1.6690000295639</v>
       </c>
       <c r="G140" t="n">
-        <v>1.49890196323395</v>
+        <v>1.49890184402466</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>1.67900002002716</v>
       </c>
       <c r="G142" t="n">
-        <v>1.50788271427155</v>
+        <v>1.50788283348083</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G155" t="n">
-        <v>1.5267425775528</v>
+        <v>1.52674245834351</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G156" t="n">
-        <v>1.50878071784973</v>
+        <v>1.50878083705902</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G157" t="n">
-        <v>1.5267425775528</v>
+        <v>1.52674245834351</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>1.69900000095367</v>
       </c>
       <c r="G165" t="n">
-        <v>1.52584445476532</v>
+        <v>1.52584433555603</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>1.71399998664856</v>
       </c>
       <c r="G166" t="n">
-        <v>1.5393158197403</v>
+        <v>1.53931570053101</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>1.89300000667572</v>
       </c>
       <c r="G172" t="n">
-        <v>1.70007252693176</v>
+        <v>1.70007264614105</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>1.84800004959106</v>
       </c>
       <c r="G173" t="n">
-        <v>1.65965902805328</v>
+        <v>1.65965890884399</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>1.87800002098083</v>
       </c>
       <c r="G174" t="n">
-        <v>1.68660151958466</v>
+        <v>1.68660140037537</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>1.85899996757507</v>
       </c>
       <c r="G176" t="n">
-        <v>1.66953766345978</v>
+        <v>1.66953778266907</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>1.81400001049042</v>
       </c>
       <c r="G183" t="n">
-        <v>1.62912404537201</v>
+        <v>1.6291241645813</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G184" t="n">
-        <v>1.63451242446899</v>
+        <v>1.63451254367828</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>1.80099999904633</v>
       </c>
       <c r="G187" t="n">
-        <v>1.61744904518127</v>
+        <v>1.61744892597198</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>1.80200004577637</v>
       </c>
       <c r="G192" t="n">
-        <v>1.61834704875946</v>
+        <v>1.61834692955017</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>1.80200004577637</v>
       </c>
       <c r="G193" t="n">
-        <v>1.61834704875946</v>
+        <v>1.61834692955017</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G194" t="n">
-        <v>1.63451242446899</v>
+        <v>1.63451254367828</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G195" t="n">
-        <v>1.63451242446899</v>
+        <v>1.63451254367828</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>1.89699995517731</v>
       </c>
       <c r="G197" t="n">
-        <v>1.70366501808167</v>
+        <v>1.70366489887238</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>1.875</v>
       </c>
       <c r="G198" t="n">
-        <v>1.68390727043152</v>
+        <v>1.68390715122223</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G203" t="n">
-        <v>1.66594552993774</v>
+        <v>1.66594541072845</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G208" t="n">
-        <v>1.63451242446899</v>
+        <v>1.63451254367828</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>1.86899995803833</v>
       </c>
       <c r="G212" t="n">
-        <v>1.67851877212524</v>
+        <v>1.67851865291595</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>1.86899995803833</v>
       </c>
       <c r="G213" t="n">
-        <v>1.67851877212524</v>
+        <v>1.67851865291595</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G217" t="n">
-        <v>1.63451242446899</v>
+        <v>1.63451254367828</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>1.83700001239777</v>
       </c>
       <c r="G219" t="n">
-        <v>1.64977991580963</v>
+        <v>1.64978003501892</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>1.80200004577637</v>
       </c>
       <c r="G221" t="n">
-        <v>1.61834704875946</v>
+        <v>1.61834692955017</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>1.83700001239777</v>
       </c>
       <c r="G222" t="n">
-        <v>1.64977991580963</v>
+        <v>1.64978003501892</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>1.84800004959106</v>
       </c>
       <c r="G223" t="n">
-        <v>1.65965902805328</v>
+        <v>1.65965890884399</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G226" t="n">
-        <v>1.5267425775528</v>
+        <v>1.52674245834351</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>1.65799999237061</v>
       </c>
       <c r="G228" t="n">
-        <v>1.4890228509903</v>
+        <v>1.48902297019958</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>1.49199998378754</v>
       </c>
       <c r="G231" t="n">
-        <v>1.33994114398956</v>
+        <v>1.33994102478027</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>1.49199998378754</v>
       </c>
       <c r="G232" t="n">
-        <v>1.33994114398956</v>
+        <v>1.33994102478027</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>1.47500002384186</v>
       </c>
       <c r="G234" t="n">
-        <v>1.32467353343964</v>
+        <v>1.32467365264893</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>1.4650000333786</v>
       </c>
       <c r="G235" t="n">
-        <v>1.31569290161133</v>
+        <v>1.31569278240204</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>1.4650000333786</v>
       </c>
       <c r="G236" t="n">
-        <v>1.31569290161133</v>
+        <v>1.31569278240204</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>1.55900001525879</v>
       </c>
       <c r="G239" t="n">
-        <v>1.40011274814606</v>
+        <v>1.40011262893677</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>1.67900002002716</v>
       </c>
       <c r="G246" t="n">
-        <v>1.50788271427155</v>
+        <v>1.50788283348083</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>1.71899998188019</v>
       </c>
       <c r="G247" t="n">
-        <v>1.54380595684052</v>
+        <v>1.5438060760498</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>1.70200002193451</v>
       </c>
       <c r="G248" t="n">
-        <v>1.52853870391846</v>
+        <v>1.52853858470917</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G249" t="n">
-        <v>1.54470419883728</v>
+        <v>1.54470407962799</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G250" t="n">
-        <v>1.54470419883728</v>
+        <v>1.54470407962799</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>1.81400001049042</v>
       </c>
       <c r="G254" t="n">
-        <v>1.62912404537201</v>
+        <v>1.6291241645813</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G257" t="n">
-        <v>1.66594552993774</v>
+        <v>1.66594541072845</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G258" t="n">
-        <v>1.66594552993774</v>
+        <v>1.66594541072845</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G259" t="n">
-        <v>1.66594552993774</v>
+        <v>1.66594541072845</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>1.81400001049042</v>
       </c>
       <c r="G261" t="n">
-        <v>1.62912404537201</v>
+        <v>1.6291241645813</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G265" t="n">
-        <v>1.64798378944397</v>
+        <v>1.64798390865326</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>1.81099998950958</v>
       </c>
       <c r="G268" t="n">
-        <v>1.62642967700958</v>
+        <v>1.62642979621887</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G269" t="n">
-        <v>1.63451242446899</v>
+        <v>1.63451254367828</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>1.80099999904633</v>
       </c>
       <c r="G270" t="n">
-        <v>1.61744904518127</v>
+        <v>1.61744892597198</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>1.71899998188019</v>
       </c>
       <c r="G274" t="n">
-        <v>1.54380595684052</v>
+        <v>1.5438060760498</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>1.70200002193451</v>
       </c>
       <c r="G275" t="n">
-        <v>1.52853870391846</v>
+        <v>1.52853858470917</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G278" t="n">
-        <v>1.50878071784973</v>
+        <v>1.50878083705902</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G279" t="n">
-        <v>1.50878071784973</v>
+        <v>1.50878083705902</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G280" t="n">
-        <v>1.54470419883728</v>
+        <v>1.54470407962799</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G282" t="n">
-        <v>1.54470419883728</v>
+        <v>1.54470407962799</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G284" t="n">
-        <v>1.48183834552765</v>
+        <v>1.48183822631836</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>1.63100004196167</v>
       </c>
       <c r="G287" t="n">
-        <v>1.46477472782135</v>
+        <v>1.46477484703064</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>1.48599994182587</v>
       </c>
       <c r="G292" t="n">
-        <v>1.334552526474</v>
+        <v>1.33455240726471</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>1.47500002384186</v>
       </c>
       <c r="G294" t="n">
-        <v>1.32467353343964</v>
+        <v>1.32467365264893</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>1.5789999961853</v>
       </c>
       <c r="G301" t="n">
-        <v>1.41807425022125</v>
+        <v>1.41807436943054</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G308" t="n">
-        <v>1.39202988147736</v>
+        <v>1.39203000068665</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>1.54499995708466</v>
       </c>
       <c r="G312" t="n">
-        <v>1.38753950595856</v>
+        <v>1.38753938674927</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G315" t="n">
-        <v>1.39202988147736</v>
+        <v>1.39203000068665</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G316" t="n">
-        <v>1.41448211669922</v>
+        <v>1.41448199748993</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G317" t="n">
-        <v>1.41897249221802</v>
+        <v>1.41897237300873</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G318" t="n">
-        <v>1.46387660503387</v>
+        <v>1.46387672424316</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>1.62600004673004</v>
       </c>
       <c r="G320" t="n">
-        <v>1.46028435230255</v>
+        <v>1.46028423309326</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G323" t="n">
-        <v>1.46387660503387</v>
+        <v>1.46387672424316</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>1.65199995040894</v>
       </c>
       <c r="G326" t="n">
-        <v>1.48363435268402</v>
+        <v>1.48363447189331</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G333" t="n">
-        <v>1.42346286773682</v>
+        <v>1.42346298694611</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G341" t="n">
-        <v>1.48183834552765</v>
+        <v>1.48183822631836</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>1.67900002002716</v>
       </c>
       <c r="G343" t="n">
-        <v>1.50788271427155</v>
+        <v>1.50788283348083</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>1.67900002002716</v>
       </c>
       <c r="G345" t="n">
-        <v>1.50788271427155</v>
+        <v>1.50788283348083</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>1.81099998950958</v>
       </c>
       <c r="G349" t="n">
-        <v>1.62642967700958</v>
+        <v>1.62642979621887</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>1.85399997234344</v>
       </c>
       <c r="G352" t="n">
-        <v>1.66504740715027</v>
+        <v>1.66504728794098</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>1.80099999904633</v>
       </c>
       <c r="G353" t="n">
-        <v>1.61744904518127</v>
+        <v>1.61744892597198</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>1.78699994087219</v>
       </c>
       <c r="G354" t="n">
-        <v>1.60487580299377</v>
+        <v>1.60487568378448</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G357" t="n">
-        <v>1.74228262901306</v>
+        <v>1.74228274822235</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G358" t="n">
-        <v>1.73330187797546</v>
+        <v>1.73330175876617</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>1.875</v>
       </c>
       <c r="G361" t="n">
-        <v>1.68390727043152</v>
+        <v>1.68390715122223</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>1.8860000371933</v>
       </c>
       <c r="G362" t="n">
-        <v>1.6937860250473</v>
+        <v>1.69378614425659</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G364" t="n">
-        <v>1.7153400182724</v>
+        <v>1.71534013748169</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>1.85899996757507</v>
       </c>
       <c r="G366" t="n">
-        <v>1.66953766345978</v>
+        <v>1.66953778266907</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>1.83700001239777</v>
       </c>
       <c r="G373" t="n">
-        <v>1.64977991580963</v>
+        <v>1.64978003501892</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>1.72099995613098</v>
       </c>
       <c r="G385" t="n">
-        <v>1.54560232162476</v>
+        <v>1.54560220241547</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>1.72099995613098</v>
       </c>
       <c r="G386" t="n">
-        <v>1.54560232162476</v>
+        <v>1.54560220241547</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>1.78299999237061</v>
       </c>
       <c r="G404" t="n">
-        <v>1.60128343105316</v>
+        <v>1.60128355026245</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G407" t="n">
-        <v>1.63451242446899</v>
+        <v>1.63451254367828</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>1.80099999904633</v>
       </c>
       <c r="G412" t="n">
-        <v>1.61744904518127</v>
+        <v>1.61744892597198</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>1.77100002765656</v>
       </c>
       <c r="G414" t="n">
-        <v>1.59050643444061</v>
+        <v>1.5905065536499</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>1.75399994850159</v>
       </c>
       <c r="G415" t="n">
-        <v>1.57523906230927</v>
+        <v>1.57523894309998</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>1.75899994373322</v>
       </c>
       <c r="G417" t="n">
-        <v>1.57972919940948</v>
+        <v>1.57972931861877</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>1.73099994659424</v>
       </c>
       <c r="G419" t="n">
-        <v>1.55458295345306</v>
+        <v>1.55458307266235</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G421" t="n">
-        <v>1.60307955741882</v>
+        <v>1.60307967662811</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>1.8309999704361</v>
       </c>
       <c r="G423" t="n">
-        <v>1.64439141750336</v>
+        <v>1.64439129829407</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>1.88199996948242</v>
       </c>
       <c r="G428" t="n">
-        <v>1.69019377231598</v>
+        <v>1.69019365310669</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>1.89600002765656</v>
       </c>
       <c r="G432" t="n">
-        <v>1.70276689529419</v>
+        <v>1.70276701450348</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G433" t="n">
-        <v>1.814129114151</v>
+        <v>1.81412923336029</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>2.41199994087219</v>
       </c>
       <c r="G438" t="n">
-        <v>2.16617846488953</v>
+        <v>2.16617822647095</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>2.53800010681152</v>
       </c>
       <c r="G442" t="n">
-        <v>2.27933669090271</v>
+        <v>2.27933692932129</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>2.57599997520447</v>
       </c>
       <c r="G443" t="n">
-        <v>2.31346416473389</v>
+        <v>2.31346392631531</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G445" t="n">
-        <v>2.35297966003418</v>
+        <v>2.3529794216156</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>2.53600001335144</v>
       </c>
       <c r="G448" t="n">
-        <v>2.27754044532776</v>
+        <v>2.27754068374634</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>2.49600005149841</v>
       </c>
       <c r="G453" t="n">
-        <v>2.24161720275879</v>
+        <v>2.24161744117737</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>2.43600010871887</v>
       </c>
       <c r="G456" t="n">
-        <v>2.18773221969604</v>
+        <v>2.18773245811462</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>2.32200002670288</v>
       </c>
       <c r="G457" t="n">
-        <v>2.08535075187683</v>
+        <v>2.08535051345825</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>2.83800005912781</v>
       </c>
       <c r="G462" t="n">
-        <v>2.54876208305359</v>
+        <v>2.54876184463501</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>2.7279999256134</v>
       </c>
       <c r="G465" t="n">
-        <v>2.44997262954712</v>
+        <v>2.44997239112854</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G472" t="n">
-        <v>2.55055809020996</v>
+        <v>2.55055785179138</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>2.79200005531311</v>
       </c>
       <c r="G474" t="n">
-        <v>2.50745010375977</v>
+        <v>2.50744986534119</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>2.89800000190735</v>
       </c>
       <c r="G475" t="n">
-        <v>2.60264682769775</v>
+        <v>2.60264706611633</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>2.82200002670288</v>
       </c>
       <c r="G476" t="n">
-        <v>2.53439259529114</v>
+        <v>2.53439235687256</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>2.42400002479553</v>
       </c>
       <c r="G478" t="n">
-        <v>2.1769552230835</v>
+        <v>2.17695498466492</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>2.49399995803833</v>
       </c>
       <c r="G484" t="n">
-        <v>2.23982095718384</v>
+        <v>2.23982119560242</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>2.55800008773804</v>
       </c>
       <c r="G491" t="n">
-        <v>2.29729866981506</v>
+        <v>2.29729843139648</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>2.48399996757507</v>
       </c>
       <c r="G493" t="n">
-        <v>2.23083996772766</v>
+        <v>2.23084020614624</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G496" t="n">
-        <v>2.23622870445251</v>
+        <v>2.23622894287109</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G501" t="n">
-        <v>2.23622870445251</v>
+        <v>2.23622894287109</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>2.47399997711182</v>
       </c>
       <c r="G503" t="n">
-        <v>2.22185945510864</v>
+        <v>2.22185921669006</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>2.45199990272522</v>
       </c>
       <c r="G508" t="n">
-        <v>2.20210123062134</v>
+        <v>2.20210146903992</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G510" t="n">
-        <v>2.19850921630859</v>
+        <v>2.19850945472717</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G513" t="n">
-        <v>2.18234395980835</v>
+        <v>2.18234372138977</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G523" t="n">
-        <v>2.12845849990845</v>
+        <v>2.12845826148987</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G528" t="n">
-        <v>2.08355402946472</v>
+        <v>2.0835542678833</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G532" t="n">
-        <v>2.12845849990845</v>
+        <v>2.12845826148987</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G534" t="n">
-        <v>2.1374397277832</v>
+        <v>2.13743948936462</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G536" t="n">
-        <v>2.01170778274536</v>
+        <v>2.01170802116394</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>2.36500000953674</v>
       </c>
       <c r="G541" t="n">
-        <v>2.12396812438965</v>
+        <v>2.12396836280823</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>2.34500002861023</v>
       </c>
       <c r="G543" t="n">
-        <v>2.10600662231445</v>
+        <v>2.10600638389587</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G555" t="n">
-        <v>1.90393769741058</v>
+        <v>1.903937458992</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G557" t="n">
-        <v>1.91291868686676</v>
+        <v>1.91291880607605</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G561" t="n">
-        <v>2.01170778274536</v>
+        <v>2.01170802116394</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G566" t="n">
-        <v>1.99374616146088</v>
+        <v>1.9937459230423</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G568" t="n">
-        <v>2.01170778274536</v>
+        <v>2.01170802116394</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G572" t="n">
-        <v>1.91291868686676</v>
+        <v>1.91291880607605</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G582" t="n">
-        <v>2.05661201477051</v>
+        <v>2.05661225318909</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>2.24499988555908</v>
       </c>
       <c r="G584" t="n">
-        <v>2.01619815826416</v>
+        <v>2.01619791984558</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G586" t="n">
-        <v>2.08355402946472</v>
+        <v>2.0835542678833</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G593" t="n">
-        <v>2.01170778274536</v>
+        <v>2.01170802116394</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G596" t="n">
-        <v>2.08355402946472</v>
+        <v>2.0835542678833</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G598" t="n">
-        <v>2.23622870445251</v>
+        <v>2.23622894287109</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G599" t="n">
-        <v>2.23622870445251</v>
+        <v>2.23622894287109</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>2.24499988555908</v>
       </c>
       <c r="G610" t="n">
-        <v>2.01619815826416</v>
+        <v>2.01619791984558</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G631" t="n">
-        <v>1.99374616146088</v>
+        <v>1.9937459230423</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G632" t="n">
-        <v>2.05661201477051</v>
+        <v>2.05661225318909</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G633" t="n">
-        <v>2.01170778274536</v>
+        <v>2.01170802116394</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G636" t="n">
-        <v>1.95782268047333</v>
+        <v>1.95782291889191</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>2.24499988555908</v>
       </c>
       <c r="G638" t="n">
-        <v>2.01619815826416</v>
+        <v>2.01619791984558</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G639" t="n">
-        <v>1.99374616146088</v>
+        <v>1.9937459230423</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G641" t="n">
-        <v>1.99374616146088</v>
+        <v>1.9937459230423</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G643" t="n">
-        <v>1.99374616146088</v>
+        <v>1.9937459230423</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G645" t="n">
-        <v>1.95782268047333</v>
+        <v>1.95782291889191</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>2.1949999332428</v>
       </c>
       <c r="G647" t="n">
-        <v>1.97129368782043</v>
+        <v>1.97129392623901</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G649" t="n">
-        <v>1.95782268047333</v>
+        <v>1.95782291889191</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>2.18499994277954</v>
       </c>
       <c r="G650" t="n">
-        <v>1.96231329441071</v>
+        <v>1.96231305599213</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>2.20499992370605</v>
       </c>
       <c r="G651" t="n">
-        <v>1.98027467727661</v>
+        <v>1.98027491569519</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>2.13499999046326</v>
       </c>
       <c r="G652" t="n">
-        <v>1.91740906238556</v>
+        <v>1.91740894317627</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G653" t="n">
-        <v>1.95782268047333</v>
+        <v>1.95782291889191</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G659" t="n">
-        <v>1.93088018894196</v>
+        <v>1.93088030815125</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G661" t="n">
-        <v>1.90393769741058</v>
+        <v>1.903937458992</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G662" t="n">
-        <v>1.90393769741058</v>
+        <v>1.903937458992</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>2.125</v>
       </c>
       <c r="G663" t="n">
-        <v>1.90842819213867</v>
+        <v>1.90842807292938</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G664" t="n">
-        <v>1.93088018894196</v>
+        <v>1.93088030815125</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G665" t="n">
-        <v>1.93088018894196</v>
+        <v>1.93088030815125</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G667" t="n">
-        <v>1.90393769741058</v>
+        <v>1.903937458992</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G670" t="n">
-        <v>1.93088018894196</v>
+        <v>1.93088030815125</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G671" t="n">
-        <v>1.93088018894196</v>
+        <v>1.93088030815125</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G672" t="n">
-        <v>1.95782268047333</v>
+        <v>1.95782291889191</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G675" t="n">
-        <v>2.01170778274536</v>
+        <v>2.01170802116394</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G681" t="n">
-        <v>1.99374616146088</v>
+        <v>1.9937459230423</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G686" t="n">
-        <v>2.05661201477051</v>
+        <v>2.05661225318909</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G687" t="n">
-        <v>2.05661201477051</v>
+        <v>2.05661225318909</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G695" t="n">
-        <v>2.05661201477051</v>
+        <v>2.05661225318909</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G696" t="n">
-        <v>2.01170778274536</v>
+        <v>2.01170802116394</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G707" t="n">
-        <v>1.91291868686676</v>
+        <v>1.91291880607605</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G711" t="n">
-        <v>1.82311022281647</v>
+        <v>1.82311010360718</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G715" t="n">
-        <v>1.80514848232269</v>
+        <v>1.8051483631134</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>1.99199998378754</v>
       </c>
       <c r="G716" t="n">
-        <v>1.78898286819458</v>
+        <v>1.78898298740387</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G717" t="n">
-        <v>1.76024425029755</v>
+        <v>1.76024436950684</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G725" t="n">
-        <v>1.76024425029755</v>
+        <v>1.76024436950684</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G729" t="n">
-        <v>1.63451242446899</v>
+        <v>1.63451254367828</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G731" t="n">
-        <v>1.63451242446899</v>
+        <v>1.63451254367828</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G732" t="n">
-        <v>1.63451242446899</v>
+        <v>1.63451254367828</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>1.76199996471405</v>
       </c>
       <c r="G733" t="n">
-        <v>1.58242356777191</v>
+        <v>1.5824236869812</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>1.65199995040894</v>
       </c>
       <c r="G737" t="n">
-        <v>1.48363435268402</v>
+        <v>1.48363447189331</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G738" t="n">
-        <v>1.41897249221802</v>
+        <v>1.41897237300873</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>1.57400000095367</v>
       </c>
       <c r="G742" t="n">
-        <v>1.41358399391174</v>
+        <v>1.41358387470245</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G747" t="n">
-        <v>1.39202988147736</v>
+        <v>1.39203000068665</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>1.45200002193451</v>
       </c>
       <c r="G750" t="n">
-        <v>1.30401766300201</v>
+        <v>1.3040177822113</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G757" t="n">
-        <v>1.21241307258606</v>
+        <v>1.21241319179535</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>1.25399994850159</v>
       </c>
       <c r="G760" t="n">
-        <v>1.12619698047638</v>
+        <v>1.12619709968567</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>1.36800003051758</v>
       </c>
       <c r="G764" t="n">
-        <v>1.22857868671417</v>
+        <v>1.22857856750488</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>1.52799999713898</v>
       </c>
       <c r="G766" t="n">
-        <v>1.37227213382721</v>
+        <v>1.3722722530365</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>1.47599995136261</v>
       </c>
       <c r="G778" t="n">
-        <v>1.32557165622711</v>
+        <v>1.3255717754364</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>1.47200000286102</v>
       </c>
       <c r="G780" t="n">
-        <v>1.32197940349579</v>
+        <v>1.3219792842865</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>1.49199998378754</v>
       </c>
       <c r="G783" t="n">
-        <v>1.33994114398956</v>
+        <v>1.33994102478027</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>1.47599995136261</v>
       </c>
       <c r="G784" t="n">
-        <v>1.32557165622711</v>
+        <v>1.3255717754364</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>1.40199995040894</v>
       </c>
       <c r="G789" t="n">
-        <v>1.25911343097687</v>
+        <v>1.25911355018616</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>1.38800001144409</v>
       </c>
       <c r="G792" t="n">
-        <v>1.24654030799866</v>
+        <v>1.24654042720795</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>1.41799998283386</v>
       </c>
       <c r="G793" t="n">
-        <v>1.27348279953003</v>
+        <v>1.27348268032074</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G795" t="n">
-        <v>1.45489585399628</v>
+        <v>1.45489573478699</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G805" t="n">
-        <v>1.82311022281647</v>
+        <v>1.82311010360718</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>1.98199999332428</v>
       </c>
       <c r="G810" t="n">
-        <v>1.78000223636627</v>
+        <v>1.78000211715698</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G811" t="n">
-        <v>1.814129114151</v>
+        <v>1.81412923336029</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G813" t="n">
-        <v>1.814129114151</v>
+        <v>1.81412923336029</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G814" t="n">
-        <v>1.80514848232269</v>
+        <v>1.8051483631134</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>1.95799994468689</v>
       </c>
       <c r="G816" t="n">
-        <v>1.75844812393188</v>
+        <v>1.7584480047226</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>1.90600001811981</v>
       </c>
       <c r="G820" t="n">
-        <v>1.71174776554108</v>
+        <v>1.71174764633179</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G821" t="n">
-        <v>1.73330187797546</v>
+        <v>1.73330175876617</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>1.87600004673004</v>
       </c>
       <c r="G823" t="n">
-        <v>1.68480539321899</v>
+        <v>1.6848052740097</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>1.90600001811981</v>
       </c>
       <c r="G825" t="n">
-        <v>1.71174776554108</v>
+        <v>1.71174764633179</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G828" t="n">
-        <v>1.99374616146088</v>
+        <v>1.9937459230423</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>2.34500002861023</v>
       </c>
       <c r="G831" t="n">
-        <v>2.10600662231445</v>
+        <v>2.10600638389587</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G832" t="n">
-        <v>2.01170778274536</v>
+        <v>2.01170802116394</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G834" t="n">
-        <v>1.99374616146088</v>
+        <v>1.9937459230423</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G837" t="n">
-        <v>1.99374616146088</v>
+        <v>1.9937459230423</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G838" t="n">
-        <v>2.1374397277832</v>
+        <v>2.13743948936462</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>2.36500000953674</v>
       </c>
       <c r="G850" t="n">
-        <v>2.12396812438965</v>
+        <v>2.12396836280823</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G855" t="n">
-        <v>1.95782268047333</v>
+        <v>1.95782291889191</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G856" t="n">
-        <v>1.95782268047333</v>
+        <v>1.95782291889191</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>2.24499988555908</v>
       </c>
       <c r="G859" t="n">
-        <v>2.01619815826416</v>
+        <v>2.01619791984558</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G867" t="n">
-        <v>2.05661201477051</v>
+        <v>2.05661225318909</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G871" t="n">
-        <v>2.05661201477051</v>
+        <v>2.05661225318909</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G872" t="n">
-        <v>2.05661201477051</v>
+        <v>2.05661225318909</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G881" t="n">
-        <v>1.814129114151</v>
+        <v>1.81412923336029</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G886" t="n">
-        <v>1.82311022281647</v>
+        <v>1.82311010360718</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G887" t="n">
-        <v>1.82311022281647</v>
+        <v>1.82311010360718</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G891" t="n">
-        <v>1.814129114151</v>
+        <v>1.81412923336029</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G892" t="n">
-        <v>1.82311022281647</v>
+        <v>1.82311010360718</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G893" t="n">
-        <v>1.82311022281647</v>
+        <v>1.82311010360718</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G894" t="n">
-        <v>1.80514848232269</v>
+        <v>1.8051483631134</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G898" t="n">
-        <v>1.814129114151</v>
+        <v>1.81412923336029</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G899" t="n">
-        <v>1.80514848232269</v>
+        <v>1.8051483631134</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>2</v>
       </c>
       <c r="G900" t="n">
-        <v>1.7961677312851</v>
+        <v>1.79616761207581</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>2.1949999332428</v>
       </c>
       <c r="G906" t="n">
-        <v>1.97129368782043</v>
+        <v>1.97129392623901</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G907" t="n">
-        <v>1.95782268047333</v>
+        <v>1.95782291889191</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>2.24499988555908</v>
       </c>
       <c r="G908" t="n">
-        <v>2.01619815826416</v>
+        <v>2.01619791984558</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G909" t="n">
-        <v>1.99374616146088</v>
+        <v>1.9937459230423</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G911" t="n">
-        <v>1.93088018894196</v>
+        <v>1.93088030815125</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>2.20499992370605</v>
       </c>
       <c r="G912" t="n">
-        <v>1.98027467727661</v>
+        <v>1.98027491569519</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>2.125</v>
       </c>
       <c r="G914" t="n">
-        <v>1.90842819213867</v>
+        <v>1.90842807292938</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>2.13499999046326</v>
       </c>
       <c r="G915" t="n">
-        <v>1.91740906238556</v>
+        <v>1.91740894317627</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G918" t="n">
-        <v>1.90393769741058</v>
+        <v>1.903937458992</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>1.99199998378754</v>
       </c>
       <c r="G921" t="n">
-        <v>1.78898286819458</v>
+        <v>1.78898298740387</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>1.96599996089935</v>
       </c>
       <c r="G924" t="n">
-        <v>1.76563262939453</v>
+        <v>1.76563274860382</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G925" t="n">
-        <v>1.814129114151</v>
+        <v>1.81412923336029</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G927" t="n">
-        <v>1.76024425029755</v>
+        <v>1.76024436950684</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>1.94799995422363</v>
       </c>
       <c r="G928" t="n">
-        <v>1.74946737289429</v>
+        <v>1.749467253685</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G929" t="n">
-        <v>1.76024425029755</v>
+        <v>1.76024436950684</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G930" t="n">
-        <v>1.73330187797546</v>
+        <v>1.73330175876617</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>1.94799995422363</v>
       </c>
       <c r="G932" t="n">
-        <v>1.74946737289429</v>
+        <v>1.749467253685</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>1.98199999332428</v>
       </c>
       <c r="G933" t="n">
-        <v>1.78000223636627</v>
+        <v>1.78000211715698</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G935" t="n">
-        <v>1.814129114151</v>
+        <v>1.81412923336029</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G941" t="n">
-        <v>2.1464204788208</v>
+        <v>2.14642071723938</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G953" t="n">
-        <v>2.05661201477051</v>
+        <v>2.05661225318909</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G957" t="n">
-        <v>1.99374616146088</v>
+        <v>1.9937459230423</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G960" t="n">
-        <v>1.95782268047333</v>
+        <v>1.95782291889191</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G962" t="n">
-        <v>1.99374616146088</v>
+        <v>1.9937459230423</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G964" t="n">
-        <v>2.08355402946472</v>
+        <v>2.0835542678833</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>2.40499997138977</v>
       </c>
       <c r="G965" t="n">
-        <v>2.1598916053772</v>
+        <v>2.15989136695862</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>2.40499997138977</v>
       </c>
       <c r="G968" t="n">
-        <v>2.1598916053772</v>
+        <v>2.15989136695862</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>2.36500000953674</v>
       </c>
       <c r="G969" t="n">
-        <v>2.12396812438965</v>
+        <v>2.12396836280823</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G971" t="n">
-        <v>2.05661201477051</v>
+        <v>2.05661225318909</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>2.24499988555908</v>
       </c>
       <c r="G973" t="n">
-        <v>2.01619815826416</v>
+        <v>2.01619791984558</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G975" t="n">
-        <v>2.1464204788208</v>
+        <v>2.14642071723938</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>2.51500010490417</v>
       </c>
       <c r="G977" t="n">
-        <v>2.25868082046509</v>
+        <v>2.25868105888367</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G982" t="n">
-        <v>2.56851935386658</v>
+        <v>2.56851959228516</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G983" t="n">
-        <v>2.55055809020996</v>
+        <v>2.55055785179138</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G985" t="n">
-        <v>2.64934706687927</v>
+        <v>2.64934730529785</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>2.96499991416931</v>
       </c>
       <c r="G986" t="n">
-        <v>2.66281867027283</v>
+        <v>2.66281843185425</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G988" t="n">
-        <v>2.6852707862854</v>
+        <v>2.68527054786682</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G990" t="n">
-        <v>2.6852707862854</v>
+        <v>2.68527054786682</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>2.96499991416931</v>
       </c>
       <c r="G991" t="n">
-        <v>2.66281867027283</v>
+        <v>2.66281843185425</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G995" t="n">
-        <v>3.05348515510559</v>
+        <v>3.05348491668701</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1001" t="n">
-        <v>2.73915553092957</v>
+        <v>2.73915576934814</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>2.96499991416931</v>
       </c>
       <c r="G1003" t="n">
-        <v>2.66281867027283</v>
+        <v>2.66281843185425</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1005" t="n">
-        <v>2.6852707862854</v>
+        <v>2.68527054786682</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1010" t="n">
-        <v>2.64934706687927</v>
+        <v>2.64934730529785</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1012" t="n">
-        <v>2.78405976295471</v>
+        <v>2.78406000137329</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1014" t="n">
-        <v>2.77507901191711</v>
+        <v>2.77507877349854</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>2.92499995231628</v>
       </c>
       <c r="G1018" t="n">
-        <v>2.6268949508667</v>
+        <v>2.62689518928528</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>2.96499991416931</v>
       </c>
       <c r="G1019" t="n">
-        <v>2.66281867027283</v>
+        <v>2.66281843185425</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1026" t="n">
-        <v>2.9636766910553</v>
+        <v>2.96367645263672</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>3.6949999332428</v>
       </c>
       <c r="G1029" t="n">
-        <v>3.31841945648193</v>
+        <v>3.31841969490051</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1032" t="n">
-        <v>3.07144665718079</v>
+        <v>3.07144689559937</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1033" t="n">
-        <v>2.9636766910553</v>
+        <v>2.96367645263672</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1038" t="n">
-        <v>3.07144665718079</v>
+        <v>3.07144689559937</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>3.81500005722046</v>
       </c>
       <c r="G1041" t="n">
-        <v>3.42618989944458</v>
+        <v>3.426189661026</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1042" t="n">
-        <v>3.2420825958252</v>
+        <v>3.24208235740662</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>3.85500001907349</v>
       </c>
       <c r="G1045" t="n">
-        <v>3.46211314201355</v>
+        <v>3.46211338043213</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1057" t="n">
-        <v>2.78405976295471</v>
+        <v>2.78406000137329</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1062" t="n">
-        <v>2.56851935386658</v>
+        <v>2.56851959228516</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>2</v>
       </c>
       <c r="G1067" t="n">
-        <v>1.7961677312851</v>
+        <v>1.79616761207581</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1069" t="n">
-        <v>1.814129114151</v>
+        <v>1.81412923336029</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>1.9559999704361</v>
       </c>
       <c r="G1071" t="n">
-        <v>1.75665187835693</v>
+        <v>1.75665175914764</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>2</v>
       </c>
       <c r="G1073" t="n">
-        <v>1.7961677312851</v>
+        <v>1.79616761207581</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>2.16499996185303</v>
       </c>
       <c r="G1074" t="n">
-        <v>1.94435119628906</v>
+        <v>1.94435143470764</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>2.5550000667572</v>
       </c>
       <c r="G1081" t="n">
-        <v>2.29460430145264</v>
+        <v>2.29460406303406</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>2.86500000953674</v>
       </c>
       <c r="G1093" t="n">
-        <v>2.57301020622253</v>
+        <v>2.57300996780396</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1094" t="n">
-        <v>2.51463437080383</v>
+        <v>2.51463460922241</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>2.86500000953674</v>
       </c>
       <c r="G1095" t="n">
-        <v>2.57301020622253</v>
+        <v>2.57300996780396</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1096" t="n">
-        <v>2.6852707862854</v>
+        <v>2.68527054786682</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>2.97499990463257</v>
       </c>
       <c r="G1097" t="n">
-        <v>2.67179918289185</v>
+        <v>2.67179942131042</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1101" t="n">
-        <v>2.64934706687927</v>
+        <v>2.64934730529785</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29021,7 +29021,7 @@
         <v>2.92499995231628</v>
       </c>
       <c r="G1102" t="n">
-        <v>2.6268949508667</v>
+        <v>2.62689518928528</v>
       </c>
       <c r="H1102" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1104" t="n">
-        <v>2.56851935386658</v>
+        <v>2.56851959228516</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1107" t="n">
-        <v>2.64934706687927</v>
+        <v>2.64934730529785</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>2.86500000953674</v>
       </c>
       <c r="G1108" t="n">
-        <v>2.57301020622253</v>
+        <v>2.57300996780396</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>2.96499991416931</v>
       </c>
       <c r="G1110" t="n">
-        <v>2.66281867027283</v>
+        <v>2.66281843185425</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G1115" t="n">
-        <v>2.52810597419739</v>
+        <v>2.52810573577881</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>2.86500000953674</v>
       </c>
       <c r="G1117" t="n">
-        <v>2.57301020622253</v>
+        <v>2.57300996780396</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29879,7 +29879,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1135" t="n">
-        <v>2.51463437080383</v>
+        <v>2.51463460922241</v>
       </c>
       <c r="H1135" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1137" t="n">
-        <v>2.42482614517212</v>
+        <v>2.4248263835907</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1150" t="n">
-        <v>2.42482614517212</v>
+        <v>2.4248263835907</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G1151" t="n">
-        <v>2.4068648815155</v>
+        <v>2.40686464309692</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1163" t="n">
-        <v>2.27215218544006</v>
+        <v>2.27215194702148</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30633,7 +30633,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1164" t="n">
-        <v>2.27215218544006</v>
+        <v>2.27215194702148</v>
       </c>
       <c r="H1164" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1170" t="n">
-        <v>2.42482614517212</v>
+        <v>2.4248263835907</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>2.82500004768372</v>
       </c>
       <c r="G1172" t="n">
-        <v>2.53708672523499</v>
+        <v>2.53708696365356</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1182" t="n">
-        <v>2.37094140052795</v>
+        <v>2.37094163894653</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>2.65499997138977</v>
       </c>
       <c r="G1186" t="n">
-        <v>2.38441252708435</v>
+        <v>2.38441228866577</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>2.67499995231628</v>
       </c>
       <c r="G1188" t="n">
-        <v>2.40237402915955</v>
+        <v>2.40237426757812</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1189" t="n">
-        <v>2.37094140052795</v>
+        <v>2.37094163894653</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>2.67499995231628</v>
       </c>
       <c r="G1191" t="n">
-        <v>2.40237402915955</v>
+        <v>2.40237426757812</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>2.66499996185303</v>
       </c>
       <c r="G1198" t="n">
-        <v>2.39339327812195</v>
+        <v>2.39339351654053</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1204" t="n">
-        <v>2.27215218544006</v>
+        <v>2.27215194702148</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31725,7 +31725,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1206" t="n">
-        <v>2.23622870445251</v>
+        <v>2.23622894287109</v>
       </c>
       <c r="H1206" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1207" t="n">
-        <v>2.27215218544006</v>
+        <v>2.27215194702148</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1214" t="n">
-        <v>2.37094140052795</v>
+        <v>2.37094163894653</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>2.86500000953674</v>
       </c>
       <c r="G1223" t="n">
-        <v>2.57301020622253</v>
+        <v>2.57300996780396</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1227" t="n">
-        <v>2.27215218544006</v>
+        <v>2.27215194702148</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32297,7 +32297,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G1228" t="n">
-        <v>2.35297966003418</v>
+        <v>2.3529794216156</v>
       </c>
       <c r="H1228" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G1229" t="n">
-        <v>2.29011344909668</v>
+        <v>2.29011368751526</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32401,7 +32401,7 @@
         <v>2.5550000667572</v>
       </c>
       <c r="G1232" t="n">
-        <v>2.29460430145264</v>
+        <v>2.29460406303406</v>
       </c>
       <c r="H1232" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1248" t="n">
-        <v>2.56851935386658</v>
+        <v>2.56851959228516</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1252" t="n">
-        <v>2.6852707862854</v>
+        <v>2.68527054786682</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -33025,7 +33025,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G1256" t="n">
-        <v>2.76160788536072</v>
+        <v>2.7616081237793</v>
       </c>
       <c r="H1256" t="s">
         <v>8</v>
@@ -33051,7 +33051,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1257" t="n">
-        <v>2.73915553092957</v>
+        <v>2.73915576934814</v>
       </c>
       <c r="H1257" t="s">
         <v>8</v>
@@ -33129,7 +33129,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1260" t="n">
-        <v>2.77507901191711</v>
+        <v>2.77507877349854</v>
       </c>
       <c r="H1260" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1261" t="n">
-        <v>2.78405976295471</v>
+        <v>2.78406000137329</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1262" t="n">
-        <v>2.77507901191711</v>
+        <v>2.77507877349854</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1263" t="n">
-        <v>2.84692573547363</v>
+        <v>2.84692597389221</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33233,7 +33233,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1264" t="n">
-        <v>2.83794498443604</v>
+        <v>2.83794474601746</v>
       </c>
       <c r="H1264" t="s">
         <v>8</v>
@@ -33363,7 +33363,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1269" t="n">
-        <v>2.78405976295471</v>
+        <v>2.78406000137329</v>
       </c>
       <c r="H1269" t="s">
         <v>8</v>
@@ -33415,7 +33415,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1271" t="n">
-        <v>2.77507901191711</v>
+        <v>2.77507877349854</v>
       </c>
       <c r="H1271" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1272" t="n">
-        <v>2.78405976295471</v>
+        <v>2.78406000137329</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1274" t="n">
-        <v>2.77507901191711</v>
+        <v>2.77507877349854</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33779,7 +33779,7 @@
         <v>2.92499995231628</v>
       </c>
       <c r="G1285" t="n">
-        <v>2.6268949508667</v>
+        <v>2.62689518928528</v>
       </c>
       <c r="H1285" t="s">
         <v>8</v>
@@ -33883,7 +33883,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G1289" t="n">
-        <v>2.63138580322266</v>
+        <v>2.63138556480408</v>
       </c>
       <c r="H1289" t="s">
         <v>8</v>
@@ -34013,7 +34013,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G1294" t="n">
-        <v>2.76160788536072</v>
+        <v>2.7616081237793</v>
       </c>
       <c r="H1294" t="s">
         <v>8</v>
@@ -34117,7 +34117,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1298" t="n">
-        <v>2.81100249290466</v>
+        <v>2.81100225448608</v>
       </c>
       <c r="H1298" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1299" t="n">
-        <v>3.08940839767456</v>
+        <v>3.08940815925598</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34169,7 +34169,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G1300" t="n">
-        <v>3.12982177734375</v>
+        <v>3.12982201576233</v>
       </c>
       <c r="H1300" t="s">
         <v>8</v>
@@ -34299,7 +34299,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G1305" t="n">
-        <v>3.12982177734375</v>
+        <v>3.12982201576233</v>
       </c>
       <c r="H1305" t="s">
         <v>8</v>
@@ -34351,7 +34351,7 @@
         <v>3.42499995231628</v>
       </c>
       <c r="G1307" t="n">
-        <v>3.07593727111816</v>
+        <v>3.07593703269958</v>
       </c>
       <c r="H1307" t="s">
         <v>8</v>
@@ -34377,7 +34377,7 @@
         <v>3.42499995231628</v>
       </c>
       <c r="G1308" t="n">
-        <v>3.07593727111816</v>
+        <v>3.07593703269958</v>
       </c>
       <c r="H1308" t="s">
         <v>8</v>
@@ -34481,7 +34481,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1312" t="n">
-        <v>3.01756143569946</v>
+        <v>3.01756167411804</v>
       </c>
       <c r="H1312" t="s">
         <v>8</v>
@@ -34585,7 +34585,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1316" t="n">
-        <v>3.05348515510559</v>
+        <v>3.05348491668701</v>
       </c>
       <c r="H1316" t="s">
         <v>8</v>
@@ -34741,7 +34741,7 @@
         <v>3.28500008583069</v>
       </c>
       <c r="G1322" t="n">
-        <v>2.9502055644989</v>
+        <v>2.95020532608032</v>
       </c>
       <c r="H1322" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1332" t="n">
-        <v>3.01756143569946</v>
+        <v>3.01756167411804</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35079,7 +35079,7 @@
         <v>3.31500005722046</v>
       </c>
       <c r="G1335" t="n">
-        <v>2.97714805603027</v>
+        <v>2.97714781761169</v>
       </c>
       <c r="H1335" t="s">
         <v>8</v>
@@ -35365,7 +35365,7 @@
         <v>3.11500000953674</v>
       </c>
       <c r="G1346" t="n">
-        <v>2.79753136634827</v>
+        <v>2.79753112792969</v>
       </c>
       <c r="H1346" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1349" t="n">
-        <v>3.05348515510559</v>
+        <v>3.05348491668701</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35495,7 +35495,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1351" t="n">
-        <v>3.08940839767456</v>
+        <v>3.08940815925598</v>
       </c>
       <c r="H1351" t="s">
         <v>8</v>
@@ -35521,7 +35521,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1352" t="n">
-        <v>3.08940839767456</v>
+        <v>3.08940815925598</v>
       </c>
       <c r="H1352" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1353" t="n">
-        <v>3.08940839767456</v>
+        <v>3.08940815925598</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35573,7 +35573,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1354" t="n">
-        <v>3.05348515510559</v>
+        <v>3.05348491668701</v>
       </c>
       <c r="H1354" t="s">
         <v>8</v>
@@ -35599,7 +35599,7 @@
         <v>3.4449999332428</v>
       </c>
       <c r="G1355" t="n">
-        <v>3.09389853477478</v>
+        <v>3.09389877319336</v>
       </c>
       <c r="H1355" t="s">
         <v>8</v>
@@ -35729,7 +35729,7 @@
         <v>3.60500001907349</v>
       </c>
       <c r="G1360" t="n">
-        <v>3.2375922203064</v>
+        <v>3.23759245872498</v>
       </c>
       <c r="H1360" t="s">
         <v>8</v>
@@ -35807,7 +35807,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1363" t="n">
-        <v>3.18819761276245</v>
+        <v>3.18819737434387</v>
       </c>
       <c r="H1363" t="s">
         <v>8</v>
@@ -35859,7 +35859,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G1365" t="n">
-        <v>3.21963047981262</v>
+        <v>3.21963024139404</v>
       </c>
       <c r="H1365" t="s">
         <v>8</v>
@@ -36041,7 +36041,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1372" t="n">
-        <v>3.05348515510559</v>
+        <v>3.05348491668701</v>
       </c>
       <c r="H1372" t="s">
         <v>8</v>
@@ -36093,7 +36093,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1374" t="n">
-        <v>3.08940839767456</v>
+        <v>3.08940815925598</v>
       </c>
       <c r="H1374" t="s">
         <v>8</v>
@@ -36145,7 +36145,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1376" t="n">
-        <v>3.07144665718079</v>
+        <v>3.07144689559937</v>
       </c>
       <c r="H1376" t="s">
         <v>8</v>
@@ -36171,7 +36171,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1377" t="n">
-        <v>3.08940839767456</v>
+        <v>3.08940815925598</v>
       </c>
       <c r="H1377" t="s">
         <v>8</v>
@@ -36197,7 +36197,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1378" t="n">
-        <v>3.08940839767456</v>
+        <v>3.08940815925598</v>
       </c>
       <c r="H1378" t="s">
         <v>8</v>
@@ -36223,7 +36223,7 @@
         <v>3.4449999332428</v>
       </c>
       <c r="G1379" t="n">
-        <v>3.09389853477478</v>
+        <v>3.09389877319336</v>
       </c>
       <c r="H1379" t="s">
         <v>8</v>
@@ -36379,7 +36379,7 @@
         <v>3.54500007629395</v>
       </c>
       <c r="G1385" t="n">
-        <v>3.18370699882507</v>
+        <v>3.18370723724365</v>
       </c>
       <c r="H1385" t="s">
         <v>8</v>
@@ -36457,7 +36457,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1388" t="n">
-        <v>3.01756143569946</v>
+        <v>3.01756167411804</v>
       </c>
       <c r="H1388" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>3.28500008583069</v>
       </c>
       <c r="G1393" t="n">
-        <v>2.9502055644989</v>
+        <v>2.95020532608032</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36613,7 +36613,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1394" t="n">
-        <v>2.92775321006775</v>
+        <v>2.92775344848633</v>
       </c>
       <c r="H1394" t="s">
         <v>8</v>
@@ -36639,7 +36639,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G1395" t="n">
-        <v>3.21963047981262</v>
+        <v>3.21963024139404</v>
       </c>
       <c r="H1395" t="s">
         <v>8</v>
@@ -37003,7 +37003,7 @@
         <v>3.23499989509583</v>
       </c>
       <c r="G1409" t="n">
-        <v>2.9053008556366</v>
+        <v>2.90530109405518</v>
       </c>
       <c r="H1409" t="s">
         <v>8</v>
@@ -37029,7 +37029,7 @@
         <v>3.23499989509583</v>
       </c>
       <c r="G1410" t="n">
-        <v>2.9053008556366</v>
+        <v>2.90530109405518</v>
       </c>
       <c r="H1410" t="s">
         <v>8</v>
@@ -37107,7 +37107,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1413" t="n">
-        <v>3.01756143569946</v>
+        <v>3.01756167411804</v>
       </c>
       <c r="H1413" t="s">
         <v>8</v>
@@ -37211,7 +37211,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1417" t="n">
-        <v>3.01756143569946</v>
+        <v>3.01756167411804</v>
       </c>
       <c r="H1417" t="s">
         <v>8</v>
@@ -37367,7 +37367,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1423" t="n">
-        <v>2.9636766910553</v>
+        <v>2.96367645263672</v>
       </c>
       <c r="H1423" t="s">
         <v>8</v>
@@ -37523,7 +37523,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1429" t="n">
-        <v>2.90979170799255</v>
+        <v>2.90979146957397</v>
       </c>
       <c r="H1429" t="s">
         <v>8</v>
@@ -37653,7 +37653,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G1434" t="n">
-        <v>2.95918607711792</v>
+        <v>2.9591863155365</v>
       </c>
       <c r="H1434" t="s">
         <v>8</v>
@@ -37809,7 +37809,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1440" t="n">
-        <v>2.92775321006775</v>
+        <v>2.92775344848633</v>
       </c>
       <c r="H1440" t="s">
         <v>8</v>
@@ -37835,7 +37835,7 @@
         <v>3.28500008583069</v>
       </c>
       <c r="G1441" t="n">
-        <v>2.9502055644989</v>
+        <v>2.95020532608032</v>
       </c>
       <c r="H1441" t="s">
         <v>8</v>
@@ -37887,7 +37887,7 @@
         <v>3.31500005722046</v>
       </c>
       <c r="G1443" t="n">
-        <v>2.97714805603027</v>
+        <v>2.97714781761169</v>
       </c>
       <c r="H1443" t="s">
         <v>8</v>
@@ -37965,7 +37965,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1446" t="n">
-        <v>2.92775321006775</v>
+        <v>2.92775344848633</v>
       </c>
       <c r="H1446" t="s">
         <v>8</v>
@@ -38173,7 +38173,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1454" t="n">
-        <v>2.82896423339844</v>
+        <v>2.82896399497986</v>
       </c>
       <c r="H1454" t="s">
         <v>8</v>
@@ -38303,7 +38303,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1459" t="n">
-        <v>3.08940839767456</v>
+        <v>3.08940815925598</v>
       </c>
       <c r="H1459" t="s">
         <v>8</v>
@@ -38329,7 +38329,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1460" t="n">
-        <v>3.05348515510559</v>
+        <v>3.05348491668701</v>
       </c>
       <c r="H1460" t="s">
         <v>8</v>
@@ -38407,7 +38407,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1463" t="n">
-        <v>3.05348515510559</v>
+        <v>3.05348491668701</v>
       </c>
       <c r="H1463" t="s">
         <v>8</v>
@@ -38485,7 +38485,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1466" t="n">
-        <v>2.9636766910553</v>
+        <v>2.96367645263672</v>
       </c>
       <c r="H1466" t="s">
         <v>8</v>
@@ -38563,7 +38563,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1469" t="n">
-        <v>2.92775321006775</v>
+        <v>2.92775344848633</v>
       </c>
       <c r="H1469" t="s">
         <v>8</v>
@@ -38589,7 +38589,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1470" t="n">
-        <v>2.90979170799255</v>
+        <v>2.90979146957397</v>
       </c>
       <c r="H1470" t="s">
         <v>8</v>
@@ -38693,7 +38693,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1474" t="n">
-        <v>3.08940839767456</v>
+        <v>3.08940815925598</v>
       </c>
       <c r="H1474" t="s">
         <v>8</v>
@@ -38875,7 +38875,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1481" t="n">
-        <v>3.26902484893799</v>
+        <v>3.26902508735657</v>
       </c>
       <c r="H1481" t="s">
         <v>8</v>
@@ -38979,7 +38979,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1485" t="n">
-        <v>3.1522741317749</v>
+        <v>3.15227437019348</v>
       </c>
       <c r="H1485" t="s">
         <v>8</v>
@@ -39187,7 +39187,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1493" t="n">
-        <v>3.2420825958252</v>
+        <v>3.24208235740662</v>
       </c>
       <c r="H1493" t="s">
         <v>8</v>
@@ -39213,7 +39213,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1494" t="n">
-        <v>3.20615911483765</v>
+        <v>3.20615935325623</v>
       </c>
       <c r="H1494" t="s">
         <v>8</v>
@@ -39239,7 +39239,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1495" t="n">
-        <v>3.2420825958252</v>
+        <v>3.24208235740662</v>
       </c>
       <c r="H1495" t="s">
         <v>8</v>
@@ -39421,7 +39421,7 @@
         <v>3.54500007629395</v>
       </c>
       <c r="G1502" t="n">
-        <v>3.18370699882507</v>
+        <v>3.18370723724365</v>
       </c>
       <c r="H1502" t="s">
         <v>8</v>
@@ -39551,7 +39551,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1507" t="n">
-        <v>3.08940839767456</v>
+        <v>3.08940815925598</v>
       </c>
       <c r="H1507" t="s">
         <v>8</v>
@@ -39785,7 +39785,7 @@
         <v>3.54500007629395</v>
       </c>
       <c r="G1516" t="n">
-        <v>3.18370699882507</v>
+        <v>3.18370723724365</v>
       </c>
       <c r="H1516" t="s">
         <v>8</v>
@@ -39993,7 +39993,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1524" t="n">
-        <v>3.26902484893799</v>
+        <v>3.26902508735657</v>
       </c>
       <c r="H1524" t="s">
         <v>8</v>
@@ -40123,7 +40123,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1529" t="n">
-        <v>3.26902484893799</v>
+        <v>3.26902508735657</v>
       </c>
       <c r="H1529" t="s">
         <v>8</v>
@@ -40305,7 +40305,7 @@
         <v>3.42499995231628</v>
       </c>
       <c r="G1536" t="n">
-        <v>3.07593727111816</v>
+        <v>3.07593703269958</v>
       </c>
       <c r="H1536" t="s">
         <v>8</v>
@@ -40383,7 +40383,7 @@
         <v>3.4449999332428</v>
       </c>
       <c r="G1539" t="n">
-        <v>3.09389853477478</v>
+        <v>3.09389877319336</v>
       </c>
       <c r="H1539" t="s">
         <v>8</v>
@@ -40409,7 +40409,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1540" t="n">
-        <v>3.07144665718079</v>
+        <v>3.07144689559937</v>
       </c>
       <c r="H1540" t="s">
         <v>8</v>
@@ -40435,7 +40435,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1541" t="n">
-        <v>3.08940839767456</v>
+        <v>3.08940815925598</v>
       </c>
       <c r="H1541" t="s">
         <v>8</v>
@@ -40513,7 +40513,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1544" t="n">
-        <v>3.07144665718079</v>
+        <v>3.07144689559937</v>
       </c>
       <c r="H1544" t="s">
         <v>8</v>
@@ -40539,7 +40539,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1545" t="n">
-        <v>3.07144665718079</v>
+        <v>3.07144689559937</v>
       </c>
       <c r="H1545" t="s">
         <v>8</v>
@@ -40747,7 +40747,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G1553" t="n">
-        <v>2.95918607711792</v>
+        <v>2.9591863155365</v>
       </c>
       <c r="H1553" t="s">
         <v>8</v>
@@ -40799,7 +40799,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1555" t="n">
-        <v>3.01756143569946</v>
+        <v>3.01756167411804</v>
       </c>
       <c r="H1555" t="s">
         <v>8</v>
@@ -40877,7 +40877,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1558" t="n">
-        <v>3.05348515510559</v>
+        <v>3.05348491668701</v>
       </c>
       <c r="H1558" t="s">
         <v>8</v>
@@ -41033,7 +41033,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1564" t="n">
-        <v>2.92775321006775</v>
+        <v>2.92775344848633</v>
       </c>
       <c r="H1564" t="s">
         <v>8</v>
@@ -41163,7 +41163,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G1569" t="n">
-        <v>2.63138580322266</v>
+        <v>2.63138556480408</v>
       </c>
       <c r="H1569" t="s">
         <v>8</v>
@@ -41319,7 +41319,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1575" t="n">
-        <v>2.55055809020996</v>
+        <v>2.55055785179138</v>
       </c>
       <c r="H1575" t="s">
         <v>8</v>
@@ -41397,7 +41397,7 @@
         <v>2.92499995231628</v>
       </c>
       <c r="G1578" t="n">
-        <v>2.6268949508667</v>
+        <v>2.62689518928528</v>
       </c>
       <c r="H1578" t="s">
         <v>8</v>
@@ -41423,7 +41423,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1579" t="n">
-        <v>2.81100249290466</v>
+        <v>2.81100225448608</v>
       </c>
       <c r="H1579" t="s">
         <v>8</v>
@@ -41501,7 +41501,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1582" t="n">
-        <v>2.78405976295471</v>
+        <v>2.78406000137329</v>
       </c>
       <c r="H1582" t="s">
         <v>8</v>
@@ -41527,7 +41527,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1583" t="n">
-        <v>2.82896423339844</v>
+        <v>2.82896399497986</v>
       </c>
       <c r="H1583" t="s">
         <v>8</v>
@@ -41787,7 +41787,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1593" t="n">
-        <v>2.82896423339844</v>
+        <v>2.82896399497986</v>
       </c>
       <c r="H1593" t="s">
         <v>8</v>
@@ -41813,7 +41813,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G1594" t="n">
-        <v>2.76160788536072</v>
+        <v>2.7616081237793</v>
       </c>
       <c r="H1594" t="s">
         <v>8</v>
@@ -41891,7 +41891,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1597" t="n">
-        <v>2.81100249290466</v>
+        <v>2.81100225448608</v>
       </c>
       <c r="H1597" t="s">
         <v>8</v>
@@ -41917,7 +41917,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1598" t="n">
-        <v>2.77507901191711</v>
+        <v>2.77507877349854</v>
       </c>
       <c r="H1598" t="s">
         <v>8</v>
@@ -41943,7 +41943,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1599" t="n">
-        <v>2.78405976295471</v>
+        <v>2.78406000137329</v>
       </c>
       <c r="H1599" t="s">
         <v>8</v>
@@ -41969,7 +41969,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1600" t="n">
-        <v>2.9636766910553</v>
+        <v>2.96367645263672</v>
       </c>
       <c r="H1600" t="s">
         <v>8</v>
@@ -42021,7 +42021,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1602" t="n">
-        <v>3.01756143569946</v>
+        <v>3.01756167411804</v>
       </c>
       <c r="H1602" t="s">
         <v>8</v>
@@ -42177,7 +42177,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1608" t="n">
-        <v>3.05348515510559</v>
+        <v>3.05348491668701</v>
       </c>
       <c r="H1608" t="s">
         <v>8</v>
@@ -42229,7 +42229,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1610" t="n">
-        <v>3.01756143569946</v>
+        <v>3.01756167411804</v>
       </c>
       <c r="H1610" t="s">
         <v>8</v>
@@ -42411,7 +42411,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1617" t="n">
-        <v>2.77507901191711</v>
+        <v>2.77507877349854</v>
       </c>
       <c r="H1617" t="s">
         <v>8</v>
@@ -42437,7 +42437,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1618" t="n">
-        <v>2.84692573547363</v>
+        <v>2.84692597389221</v>
       </c>
       <c r="H1618" t="s">
         <v>8</v>
@@ -42515,7 +42515,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1621" t="n">
-        <v>2.84692573547363</v>
+        <v>2.84692597389221</v>
       </c>
       <c r="H1621" t="s">
         <v>8</v>
@@ -42567,7 +42567,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1623" t="n">
-        <v>2.92775321006775</v>
+        <v>2.92775344848633</v>
       </c>
       <c r="H1623" t="s">
         <v>8</v>
@@ -42645,7 +42645,7 @@
         <v>3.11500000953674</v>
       </c>
       <c r="G1626" t="n">
-        <v>2.79753136634827</v>
+        <v>2.79753112792969</v>
       </c>
       <c r="H1626" t="s">
         <v>8</v>
@@ -42697,7 +42697,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1628" t="n">
-        <v>2.77507901191711</v>
+        <v>2.77507877349854</v>
       </c>
       <c r="H1628" t="s">
         <v>8</v>
@@ -42749,7 +42749,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1630" t="n">
-        <v>2.73915553092957</v>
+        <v>2.73915576934814</v>
       </c>
       <c r="H1630" t="s">
         <v>8</v>
@@ -42957,7 +42957,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1638" t="n">
-        <v>2.81100249290466</v>
+        <v>2.81100225448608</v>
       </c>
       <c r="H1638" t="s">
         <v>8</v>
@@ -42983,7 +42983,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1639" t="n">
-        <v>2.6852707862854</v>
+        <v>2.68527054786682</v>
       </c>
       <c r="H1639" t="s">
         <v>8</v>
@@ -43035,7 +43035,7 @@
         <v>2.92499995231628</v>
       </c>
       <c r="G1641" t="n">
-        <v>2.6268949508667</v>
+        <v>2.62689518928528</v>
       </c>
       <c r="H1641" t="s">
         <v>8</v>
@@ -43061,7 +43061,7 @@
         <v>2.98499989509583</v>
       </c>
       <c r="G1642" t="n">
-        <v>2.68077993392944</v>
+        <v>2.68078017234802</v>
       </c>
       <c r="H1642" t="s">
         <v>8</v>
@@ -43165,7 +43165,7 @@
         <v>2.98499989509583</v>
       </c>
       <c r="G1646" t="n">
-        <v>2.68077993392944</v>
+        <v>2.68078017234802</v>
       </c>
       <c r="H1646" t="s">
         <v>8</v>
@@ -43295,7 +43295,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G1651" t="n">
-        <v>2.52810597419739</v>
+        <v>2.52810573577881</v>
       </c>
       <c r="H1651" t="s">
         <v>8</v>
@@ -43477,7 +43477,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G1658" t="n">
-        <v>2.52810597419739</v>
+        <v>2.52810573577881</v>
       </c>
       <c r="H1658" t="s">
         <v>8</v>
@@ -43555,7 +43555,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1661" t="n">
-        <v>2.56851935386658</v>
+        <v>2.56851959228516</v>
       </c>
       <c r="H1661" t="s">
         <v>8</v>
@@ -43659,7 +43659,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1665" t="n">
-        <v>2.55055809020996</v>
+        <v>2.55055785179138</v>
       </c>
       <c r="H1665" t="s">
         <v>8</v>
@@ -43737,7 +43737,7 @@
         <v>2.82500004768372</v>
       </c>
       <c r="G1668" t="n">
-        <v>2.53708672523499</v>
+        <v>2.53708696365356</v>
       </c>
       <c r="H1668" t="s">
         <v>8</v>
@@ -43789,7 +43789,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1670" t="n">
-        <v>2.55055809020996</v>
+        <v>2.55055785179138</v>
       </c>
       <c r="H1670" t="s">
         <v>8</v>
@@ -43867,7 +43867,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1673" t="n">
-        <v>2.51463437080383</v>
+        <v>2.51463460922241</v>
       </c>
       <c r="H1673" t="s">
         <v>8</v>
@@ -43893,7 +43893,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1674" t="n">
-        <v>2.55055809020996</v>
+        <v>2.55055785179138</v>
       </c>
       <c r="H1674" t="s">
         <v>8</v>
@@ -44101,7 +44101,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1682" t="n">
-        <v>2.56851935386658</v>
+        <v>2.56851959228516</v>
       </c>
       <c r="H1682" t="s">
         <v>8</v>
@@ -44205,7 +44205,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1686" t="n">
-        <v>2.64934706687927</v>
+        <v>2.64934730529785</v>
       </c>
       <c r="H1686" t="s">
         <v>8</v>
@@ -44257,7 +44257,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1688" t="n">
-        <v>2.78405976295471</v>
+        <v>2.78406000137329</v>
       </c>
       <c r="H1688" t="s">
         <v>8</v>
@@ -44465,7 +44465,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1696" t="n">
-        <v>2.6852707862854</v>
+        <v>2.68527054786682</v>
       </c>
       <c r="H1696" t="s">
         <v>8</v>
@@ -44595,7 +44595,7 @@
         <v>2.8050000667572</v>
       </c>
       <c r="G1701" t="n">
-        <v>2.51912522315979</v>
+        <v>2.51912498474121</v>
       </c>
       <c r="H1701" t="s">
         <v>8</v>
@@ -44699,7 +44699,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1705" t="n">
-        <v>2.55055809020996</v>
+        <v>2.55055785179138</v>
       </c>
       <c r="H1705" t="s">
         <v>8</v>
@@ -44803,7 +44803,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1709" t="n">
-        <v>2.42482614517212</v>
+        <v>2.4248263835907</v>
       </c>
       <c r="H1709" t="s">
         <v>8</v>
@@ -44855,7 +44855,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1711" t="n">
-        <v>2.37094140052795</v>
+        <v>2.37094163894653</v>
       </c>
       <c r="H1711" t="s">
         <v>8</v>
@@ -44881,7 +44881,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G1712" t="n">
-        <v>2.29011344909668</v>
+        <v>2.29011368751526</v>
       </c>
       <c r="H1712" t="s">
         <v>8</v>
@@ -44907,7 +44907,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1713" t="n">
-        <v>2.18234395980835</v>
+        <v>2.18234372138977</v>
       </c>
       <c r="H1713" t="s">
         <v>8</v>
@@ -45037,7 +45037,7 @@
         <v>2.40499997138977</v>
       </c>
       <c r="G1718" t="n">
-        <v>2.1598916053772</v>
+        <v>2.15989136695862</v>
       </c>
       <c r="H1718" t="s">
         <v>8</v>
@@ -45063,7 +45063,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1719" t="n">
-        <v>2.15528583526611</v>
+        <v>2.15528607368469</v>
       </c>
       <c r="H1719" t="s">
         <v>8</v>
@@ -45089,7 +45089,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1720" t="n">
-        <v>2.16449666023254</v>
+        <v>2.16449689865112</v>
       </c>
       <c r="H1720" t="s">
         <v>8</v>
@@ -45219,7 +45219,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G1725" t="n">
-        <v>2.07699608802795</v>
+        <v>2.07699584960938</v>
       </c>
       <c r="H1725" t="s">
         <v>8</v>
@@ -45349,7 +45349,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1730" t="n">
-        <v>2.16449666023254</v>
+        <v>2.16449689865112</v>
       </c>
       <c r="H1730" t="s">
         <v>8</v>
@@ -45427,7 +45427,7 @@
         <v>2.58500003814697</v>
       </c>
       <c r="G1733" t="n">
-        <v>2.38094639778137</v>
+        <v>2.38094663619995</v>
       </c>
       <c r="H1733" t="s">
         <v>8</v>
@@ -45453,7 +45453,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1734" t="n">
-        <v>2.37634134292603</v>
+        <v>2.37634110450745</v>
       </c>
       <c r="H1734" t="s">
         <v>8</v>
@@ -45505,7 +45505,7 @@
         <v>2.58500003814697</v>
       </c>
       <c r="G1736" t="n">
-        <v>2.38094639778137</v>
+        <v>2.38094663619995</v>
       </c>
       <c r="H1736" t="s">
         <v>8</v>
@@ -45531,7 +45531,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G1737" t="n">
-        <v>2.42239427566528</v>
+        <v>2.42239451408386</v>
       </c>
       <c r="H1737" t="s">
         <v>8</v>
@@ -45583,7 +45583,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1739" t="n">
-        <v>2.47765827178955</v>
+        <v>2.47765803337097</v>
       </c>
       <c r="H1739" t="s">
         <v>8</v>
@@ -45609,7 +45609,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G1740" t="n">
-        <v>2.403972864151</v>
+        <v>2.40397310256958</v>
       </c>
       <c r="H1740" t="s">
         <v>8</v>
@@ -45661,7 +45661,7 @@
         <v>2.56500005722046</v>
       </c>
       <c r="G1742" t="n">
-        <v>2.36252522468567</v>
+        <v>2.36252546310425</v>
       </c>
       <c r="H1742" t="s">
         <v>8</v>
@@ -45791,7 +45791,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1747" t="n">
-        <v>2.47765827178955</v>
+        <v>2.47765803337097</v>
       </c>
       <c r="H1747" t="s">
         <v>8</v>
@@ -45999,7 +45999,7 @@
         <v>2.66499996185303</v>
       </c>
       <c r="G1755" t="n">
-        <v>2.45463156700134</v>
+        <v>2.45463132858276</v>
       </c>
       <c r="H1755" t="s">
         <v>8</v>
@@ -46025,7 +46025,7 @@
         <v>2.66499996185303</v>
       </c>
       <c r="G1756" t="n">
-        <v>2.45463156700134</v>
+        <v>2.45463132858276</v>
       </c>
       <c r="H1756" t="s">
         <v>8</v>
@@ -46155,7 +46155,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1761" t="n">
-        <v>2.54213237762451</v>
+        <v>2.54213261604309</v>
       </c>
       <c r="H1761" t="s">
         <v>8</v>
@@ -46207,7 +46207,7 @@
         <v>2.75500011444092</v>
       </c>
       <c r="G1763" t="n">
-        <v>2.53752732276917</v>
+        <v>2.53752708435059</v>
       </c>
       <c r="H1763" t="s">
         <v>8</v>
@@ -46259,7 +46259,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1765" t="n">
-        <v>2.52371096611023</v>
+        <v>2.52371120452881</v>
       </c>
       <c r="H1765" t="s">
         <v>8</v>
@@ -46285,7 +46285,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1766" t="n">
-        <v>2.52371096611023</v>
+        <v>2.52371120452881</v>
       </c>
       <c r="H1766" t="s">
         <v>8</v>
@@ -46337,7 +46337,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1768" t="n">
-        <v>2.49607944488525</v>
+        <v>2.49607920646667</v>
       </c>
       <c r="H1768" t="s">
         <v>8</v>
@@ -46363,7 +46363,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1769" t="n">
-        <v>2.52371096611023</v>
+        <v>2.52371120452881</v>
       </c>
       <c r="H1769" t="s">
         <v>8</v>
@@ -46389,7 +46389,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1770" t="n">
-        <v>2.47765827178955</v>
+        <v>2.47765803337097</v>
       </c>
       <c r="H1770" t="s">
         <v>8</v>
@@ -46441,7 +46441,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1772" t="n">
-        <v>2.50529026985168</v>
+        <v>2.50529003143311</v>
       </c>
       <c r="H1772" t="s">
         <v>8</v>
@@ -46467,7 +46467,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1773" t="n">
-        <v>2.50529026985168</v>
+        <v>2.50529003143311</v>
       </c>
       <c r="H1773" t="s">
         <v>8</v>
@@ -46493,7 +46493,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1774" t="n">
-        <v>2.52371096611023</v>
+        <v>2.52371120452881</v>
       </c>
       <c r="H1774" t="s">
         <v>8</v>
@@ -46519,7 +46519,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1775" t="n">
-        <v>2.52371096611023</v>
+        <v>2.52371120452881</v>
       </c>
       <c r="H1775" t="s">
         <v>8</v>
@@ -46545,7 +46545,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1776" t="n">
-        <v>2.5973961353302</v>
+        <v>2.59739589691162</v>
       </c>
       <c r="H1776" t="s">
         <v>8</v>
@@ -46675,7 +46675,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1781" t="n">
-        <v>2.73555564880371</v>
+        <v>2.73555541038513</v>
       </c>
       <c r="H1781" t="s">
         <v>8</v>
@@ -46701,7 +46701,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1782" t="n">
-        <v>2.73555564880371</v>
+        <v>2.73555541038513</v>
       </c>
       <c r="H1782" t="s">
         <v>8</v>
@@ -46753,7 +46753,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1784" t="n">
-        <v>2.78160858154297</v>
+        <v>2.78160881996155</v>
       </c>
       <c r="H1784" t="s">
         <v>8</v>
@@ -46831,7 +46831,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1787" t="n">
-        <v>2.74476647377014</v>
+        <v>2.74476623535156</v>
       </c>
       <c r="H1787" t="s">
         <v>8</v>
@@ -47091,7 +47091,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G1797" t="n">
-        <v>2.84147763252258</v>
+        <v>2.84147787094116</v>
       </c>
       <c r="H1797" t="s">
         <v>8</v>
@@ -47169,7 +47169,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1800" t="n">
-        <v>2.78160858154297</v>
+        <v>2.78160881996155</v>
       </c>
       <c r="H1800" t="s">
         <v>8</v>
@@ -47221,7 +47221,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1802" t="n">
-        <v>2.74476647377014</v>
+        <v>2.74476623535156</v>
       </c>
       <c r="H1802" t="s">
         <v>8</v>
@@ -47247,7 +47247,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1803" t="n">
-        <v>2.73555564880371</v>
+        <v>2.73555541038513</v>
       </c>
       <c r="H1803" t="s">
         <v>8</v>
@@ -47325,7 +47325,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1806" t="n">
-        <v>2.71713447570801</v>
+        <v>2.71713423728943</v>
       </c>
       <c r="H1806" t="s">
         <v>8</v>
@@ -47351,7 +47351,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G1807" t="n">
-        <v>2.69871306419373</v>
+        <v>2.6987133026123</v>
       </c>
       <c r="H1807" t="s">
         <v>8</v>
@@ -47429,7 +47429,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1810" t="n">
-        <v>2.66187071800232</v>
+        <v>2.6618709564209</v>
       </c>
       <c r="H1810" t="s">
         <v>8</v>
@@ -47481,7 +47481,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G1812" t="n">
-        <v>2.64344906806946</v>
+        <v>2.64344930648804</v>
       </c>
       <c r="H1812" t="s">
         <v>8</v>
@@ -47507,7 +47507,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1813" t="n">
-        <v>2.62502813339233</v>
+        <v>2.62502789497375</v>
       </c>
       <c r="H1813" t="s">
         <v>8</v>
@@ -47533,7 +47533,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1814" t="n">
-        <v>2.61581754684448</v>
+        <v>2.6158173084259</v>
       </c>
       <c r="H1814" t="s">
         <v>8</v>
@@ -47585,7 +47585,7 @@
         <v>2.95499992370605</v>
       </c>
       <c r="G1816" t="n">
-        <v>2.72173929214478</v>
+        <v>2.72173953056335</v>
       </c>
       <c r="H1816" t="s">
         <v>8</v>
@@ -47663,7 +47663,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G1819" t="n">
-        <v>2.81384611129761</v>
+        <v>2.81384587287903</v>
       </c>
       <c r="H1819" t="s">
         <v>8</v>
@@ -47715,7 +47715,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1821" t="n">
-        <v>2.78160858154297</v>
+        <v>2.78160881996155</v>
       </c>
       <c r="H1821" t="s">
         <v>8</v>
@@ -48001,7 +48001,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G1832" t="n">
-        <v>2.69871306419373</v>
+        <v>2.6987133026123</v>
       </c>
       <c r="H1832" t="s">
         <v>8</v>
@@ -48079,7 +48079,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1835" t="n">
-        <v>2.61581754684448</v>
+        <v>2.6158173084259</v>
       </c>
       <c r="H1835" t="s">
         <v>8</v>
@@ -48131,7 +48131,7 @@
         <v>2.93499994277954</v>
       </c>
       <c r="G1837" t="n">
-        <v>2.70331835746765</v>
+        <v>2.70331859588623</v>
       </c>
       <c r="H1837" t="s">
         <v>8</v>
@@ -48157,7 +48157,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1838" t="n">
-        <v>2.66187071800232</v>
+        <v>2.6618709564209</v>
       </c>
       <c r="H1838" t="s">
         <v>8</v>
@@ -48183,7 +48183,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G1839" t="n">
-        <v>2.69871306419373</v>
+        <v>2.6987133026123</v>
       </c>
       <c r="H1839" t="s">
         <v>8</v>
@@ -48235,7 +48235,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1841" t="n">
-        <v>2.71713447570801</v>
+        <v>2.71713423728943</v>
       </c>
       <c r="H1841" t="s">
         <v>8</v>
@@ -48261,7 +48261,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1842" t="n">
-        <v>2.66187071800232</v>
+        <v>2.6618709564209</v>
       </c>
       <c r="H1842" t="s">
         <v>8</v>
@@ -48365,7 +48365,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1846" t="n">
-        <v>2.5973961353302</v>
+        <v>2.59739589691162</v>
       </c>
       <c r="H1846" t="s">
         <v>8</v>
@@ -48391,7 +48391,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1847" t="n">
-        <v>2.61581754684448</v>
+        <v>2.6158173084259</v>
       </c>
       <c r="H1847" t="s">
         <v>8</v>
@@ -48417,7 +48417,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1848" t="n">
-        <v>2.61581754684448</v>
+        <v>2.6158173084259</v>
       </c>
       <c r="H1848" t="s">
         <v>8</v>
@@ -48443,7 +48443,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1849" t="n">
-        <v>2.5973961353302</v>
+        <v>2.59739589691162</v>
       </c>
       <c r="H1849" t="s">
         <v>8</v>
@@ -48469,7 +48469,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1850" t="n">
-        <v>2.61581754684448</v>
+        <v>2.6158173084259</v>
       </c>
       <c r="H1850" t="s">
         <v>8</v>
@@ -48521,7 +48521,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1852" t="n">
-        <v>2.61581754684448</v>
+        <v>2.6158173084259</v>
       </c>
       <c r="H1852" t="s">
         <v>8</v>
@@ -48547,7 +48547,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1853" t="n">
-        <v>2.5973961353302</v>
+        <v>2.59739589691162</v>
       </c>
       <c r="H1853" t="s">
         <v>8</v>
@@ -48573,7 +48573,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1854" t="n">
-        <v>2.57897472381592</v>
+        <v>2.5789749622345</v>
       </c>
       <c r="H1854" t="s">
         <v>8</v>
@@ -48599,7 +48599,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1855" t="n">
-        <v>2.57897472381592</v>
+        <v>2.5789749622345</v>
       </c>
       <c r="H1855" t="s">
         <v>8</v>
@@ -48625,7 +48625,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.5973961353302</v>
+        <v>2.59739589691162</v>
       </c>
       <c r="H1856" t="s">
         <v>8</v>
@@ -48651,7 +48651,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.64344906806946</v>
+        <v>2.64344930648804</v>
       </c>
       <c r="H1857" t="s">
         <v>8</v>
@@ -48677,7 +48677,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.64344906806946</v>
+        <v>2.64344930648804</v>
       </c>
       <c r="H1858" t="s">
         <v>8</v>
@@ -48729,7 +48729,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.61581754684448</v>
+        <v>2.6158173084259</v>
       </c>
       <c r="H1860" t="s">
         <v>8</v>
@@ -48781,7 +48781,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.5973961353302</v>
+        <v>2.59739589691162</v>
       </c>
       <c r="H1862" t="s">
         <v>8</v>
@@ -48807,7 +48807,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.57897472381592</v>
+        <v>2.5789749622345</v>
       </c>
       <c r="H1863" t="s">
         <v>8</v>
@@ -48989,7 +48989,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.50529026985168</v>
+        <v>2.50529003143311</v>
       </c>
       <c r="H1870" t="s">
         <v>8</v>
@@ -49067,7 +49067,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.54213237762451</v>
+        <v>2.54213261604309</v>
       </c>
       <c r="H1873" t="s">
         <v>8</v>
@@ -49119,7 +49119,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.52371096611023</v>
+        <v>2.52371120452881</v>
       </c>
       <c r="H1875" t="s">
         <v>8</v>
@@ -49145,7 +49145,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.49607944488525</v>
+        <v>2.49607920646667</v>
       </c>
       <c r="H1876" t="s">
         <v>8</v>
@@ -49171,7 +49171,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.50529026985168</v>
+        <v>2.50529003143311</v>
       </c>
       <c r="H1877" t="s">
         <v>8</v>
@@ -49405,7 +49405,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.47765827178955</v>
+        <v>2.47765803337097</v>
       </c>
       <c r="H1886" t="s">
         <v>8</v>
@@ -49743,7 +49743,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.49607944488525</v>
+        <v>2.49607920646667</v>
       </c>
       <c r="H1899" t="s">
         <v>8</v>
@@ -49769,7 +49769,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.50529026985168</v>
+        <v>2.50529003143311</v>
       </c>
       <c r="H1900" t="s">
         <v>8</v>
@@ -49821,7 +49821,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.54213237762451</v>
+        <v>2.54213261604309</v>
       </c>
       <c r="H1902" t="s">
         <v>8</v>
@@ -49847,7 +49847,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.49607944488525</v>
+        <v>2.49607920646667</v>
       </c>
       <c r="H1903" t="s">
         <v>8</v>
@@ -49925,7 +49925,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.50529026985168</v>
+        <v>2.50529003143311</v>
       </c>
       <c r="H1906" t="s">
         <v>8</v>
@@ -50003,7 +50003,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.52371096611023</v>
+        <v>2.52371120452881</v>
       </c>
       <c r="H1909" t="s">
         <v>8</v>
@@ -71222,6 +71222,32 @@
         <v>1.13999998569489</v>
       </c>
       <c r="H2725" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2726">
+      <c r="A2726" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B2726" t="n">
+        <v>7077</v>
+      </c>
+      <c r="C2726" t="n">
+        <v>1.14499998092651</v>
+      </c>
+      <c r="D2726" t="n">
+        <v>1.12000000476837</v>
+      </c>
+      <c r="E2726" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="F2726" t="n">
+        <v>1.12000000476837</v>
+      </c>
+      <c r="G2726" t="n">
+        <v>1.12000000476837</v>
+      </c>
+      <c r="H2726" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/ELC.MI.xlsx
+++ b/data/ELC.MI.xlsx
@@ -421,7 +421,7 @@
         <v>1.93700003623962</v>
       </c>
       <c r="G2" t="n">
-        <v>1.73070466518402</v>
+        <v>1.73070478439331</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G3" t="n">
-        <v>1.73338520526886</v>
+        <v>1.73338508605957</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>1.87399995326996</v>
       </c>
       <c r="G5" t="n">
-        <v>1.67441415786743</v>
+        <v>1.67441427707672</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>1.81900000572205</v>
       </c>
       <c r="G10" t="n">
-        <v>1.62527179718018</v>
+        <v>1.62527203559875</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G11" t="n">
-        <v>1.59936046600342</v>
+        <v>1.59936034679413</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>1.70700001716614</v>
       </c>
       <c r="G16" t="n">
-        <v>1.52520036697388</v>
+        <v>1.52520024776459</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G17" t="n">
-        <v>1.44746589660645</v>
+        <v>1.44746601581573</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G19" t="n">
-        <v>1.46533584594727</v>
+        <v>1.46533572673798</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G26" t="n">
-        <v>1.38492119312286</v>
+        <v>1.38492095470428</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G28" t="n">
-        <v>1.28216886520386</v>
+        <v>1.28216874599457</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G29" t="n">
-        <v>1.313441157341</v>
+        <v>1.31344127655029</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G30" t="n">
-        <v>1.25983154773712</v>
+        <v>1.25983142852783</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>1.63199996948242</v>
       </c>
       <c r="G32" t="n">
-        <v>1.45818781852722</v>
+        <v>1.45818769931793</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>1.6710000038147</v>
       </c>
       <c r="G33" t="n">
-        <v>1.49303424358368</v>
+        <v>1.49303448200226</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>1.65900003910065</v>
       </c>
       <c r="G34" t="n">
-        <v>1.4823123216629</v>
+        <v>1.48231220245361</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G35" t="n">
-        <v>1.51001083850861</v>
+        <v>1.5100109577179</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>1.75</v>
       </c>
       <c r="G38" t="n">
-        <v>1.56362056732178</v>
+        <v>1.56362044811249</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>1.74699997901917</v>
       </c>
       <c r="G39" t="n">
-        <v>1.56094002723694</v>
+        <v>1.56094014644623</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G42" t="n">
-        <v>1.58149039745331</v>
+        <v>1.5814905166626</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G44" t="n">
-        <v>1.51894581317902</v>
+        <v>1.51894569396973</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G45" t="n">
-        <v>1.58149039745331</v>
+        <v>1.5814905166626</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>1.77300000190735</v>
       </c>
       <c r="G46" t="n">
-        <v>1.58417093753815</v>
+        <v>1.58417105674744</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>1.75</v>
       </c>
       <c r="G47" t="n">
-        <v>1.56362056732178</v>
+        <v>1.56362044811249</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>1.75</v>
       </c>
       <c r="G48" t="n">
-        <v>1.56362056732178</v>
+        <v>1.56362044811249</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>1.75</v>
       </c>
       <c r="G49" t="n">
-        <v>1.56362056732178</v>
+        <v>1.56362044811249</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G50" t="n">
-        <v>1.58149039745331</v>
+        <v>1.5814905166626</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>1.89300000667572</v>
       </c>
       <c r="G53" t="n">
-        <v>1.69139075279236</v>
+        <v>1.69139063358307</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>1.90900003910065</v>
       </c>
       <c r="G54" t="n">
-        <v>1.70568668842316</v>
+        <v>1.70568680763245</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G55" t="n">
-        <v>1.67977511882782</v>
+        <v>1.6797753572464</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G58" t="n">
-        <v>1.7691251039505</v>
+        <v>1.76912486553192</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>1.93599998950958</v>
       </c>
       <c r="G60" t="n">
-        <v>1.72981119155884</v>
+        <v>1.72981107234955</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>1.94599997997284</v>
       </c>
       <c r="G61" t="n">
-        <v>1.73874604701996</v>
+        <v>1.73874616622925</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>1.97599995136261</v>
       </c>
       <c r="G62" t="n">
-        <v>1.76555097103119</v>
+        <v>1.7655508518219</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G66" t="n">
-        <v>1.68871021270752</v>
+        <v>1.68871033191681</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>1.87899994850159</v>
       </c>
       <c r="G67" t="n">
-        <v>1.67888176441193</v>
+        <v>1.67888164520264</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G68" t="n">
-        <v>1.69317770004272</v>
+        <v>1.69317781925201</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>1.88100004196167</v>
       </c>
       <c r="G72" t="n">
-        <v>1.68066871166229</v>
+        <v>1.68066883087158</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G74" t="n">
-        <v>1.71551513671875</v>
+        <v>1.71551501750946</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G75" t="n">
-        <v>1.71998250484467</v>
+        <v>1.71998262405396</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G76" t="n">
-        <v>1.71104776859283</v>
+        <v>1.71104753017426</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G78" t="n">
-        <v>1.71998250484467</v>
+        <v>1.71998262405396</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>1.89800000190735</v>
       </c>
       <c r="G79" t="n">
-        <v>1.69585812091827</v>
+        <v>1.69585824012756</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G80" t="n">
-        <v>1.71998250484467</v>
+        <v>1.71998262405396</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>1.92700004577637</v>
       </c>
       <c r="G82" t="n">
-        <v>1.72176957130432</v>
+        <v>1.72176969051361</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>1.92599999904633</v>
       </c>
       <c r="G89" t="n">
-        <v>1.72087621688843</v>
+        <v>1.72087609767914</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>1.84800004959106</v>
       </c>
       <c r="G90" t="n">
-        <v>1.65118336677551</v>
+        <v>1.6511834859848</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>1.875</v>
       </c>
       <c r="G91" t="n">
-        <v>1.6753077507019</v>
+        <v>1.67530786991119</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>1.84700000286102</v>
       </c>
       <c r="G92" t="n">
-        <v>1.65028989315033</v>
+        <v>1.65028977394104</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G95" t="n">
-        <v>1.68871021270752</v>
+        <v>1.68871033191681</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G96" t="n">
-        <v>1.68871021270752</v>
+        <v>1.68871033191681</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>1.9190000295639</v>
       </c>
       <c r="G99" t="n">
-        <v>1.71462178230286</v>
+        <v>1.71462154388428</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>1.9190000295639</v>
       </c>
       <c r="G101" t="n">
-        <v>1.7234228849411</v>
+        <v>1.72342276573181</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>1.93799996376038</v>
       </c>
       <c r="G104" t="n">
-        <v>1.74048638343811</v>
+        <v>1.74048626422882</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G109" t="n">
-        <v>1.71534013748169</v>
+        <v>1.7153400182724</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G112" t="n">
-        <v>1.71534013748169</v>
+        <v>1.7153400182724</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G119" t="n">
-        <v>1.60757005214691</v>
+        <v>1.60756993293762</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>1.875</v>
       </c>
       <c r="G121" t="n">
-        <v>1.68390715122223</v>
+        <v>1.68390727043152</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>1.82400000095367</v>
       </c>
       <c r="G122" t="n">
-        <v>1.63810479640961</v>
+        <v>1.6381049156189</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>1.69700002670288</v>
       </c>
       <c r="G132" t="n">
-        <v>1.52404832839966</v>
+        <v>1.52404820919037</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G133" t="n">
-        <v>1.46836709976196</v>
+        <v>1.46836698055267</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>1.62100005149841</v>
       </c>
       <c r="G135" t="n">
-        <v>1.45579397678375</v>
+        <v>1.45579385757446</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G136" t="n">
-        <v>1.45489573478699</v>
+        <v>1.45489585399628</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>1.6690000295639</v>
       </c>
       <c r="G140" t="n">
-        <v>1.49890184402466</v>
+        <v>1.49890196323395</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>1.67900002002716</v>
       </c>
       <c r="G142" t="n">
-        <v>1.50788283348083</v>
+        <v>1.50788271427155</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>1.65400004386902</v>
       </c>
       <c r="G149" t="n">
-        <v>1.48543071746826</v>
+        <v>1.48543059825897</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>1.69400000572205</v>
       </c>
       <c r="G153" t="n">
-        <v>1.52135396003723</v>
+        <v>1.52135407924652</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>1.69400000572205</v>
       </c>
       <c r="G154" t="n">
-        <v>1.52135396003723</v>
+        <v>1.52135407924652</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G159" t="n">
-        <v>1.51776170730591</v>
+        <v>1.5177618265152</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>1.66299998760223</v>
       </c>
       <c r="G162" t="n">
-        <v>1.49351334571838</v>
+        <v>1.49351322650909</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>1.69900000095367</v>
       </c>
       <c r="G165" t="n">
-        <v>1.52584433555603</v>
+        <v>1.52584445476532</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G167" t="n">
-        <v>1.64349341392517</v>
+        <v>1.64349353313446</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>1.93299996852875</v>
       </c>
       <c r="G170" t="n">
-        <v>1.73599600791931</v>
+        <v>1.73599588871002</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>1.89300000667572</v>
       </c>
       <c r="G172" t="n">
-        <v>1.70007264614105</v>
+        <v>1.70007252693176</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>1.84800004959106</v>
       </c>
       <c r="G173" t="n">
-        <v>1.65965890884399</v>
+        <v>1.65965902805328</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>1.85899996757507</v>
       </c>
       <c r="G176" t="n">
-        <v>1.66953778266907</v>
+        <v>1.66953766345978</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>1.85099995136261</v>
       </c>
       <c r="G178" t="n">
-        <v>1.66235315799713</v>
+        <v>1.66235303878784</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G181" t="n">
-        <v>1.68839752674103</v>
+        <v>1.68839764595032</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>1.81400001049042</v>
       </c>
       <c r="G183" t="n">
-        <v>1.6291241645813</v>
+        <v>1.62912404537201</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>1.80099999904633</v>
       </c>
       <c r="G187" t="n">
-        <v>1.61744892597198</v>
+        <v>1.61744904518127</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>1.80200004577637</v>
       </c>
       <c r="G192" t="n">
-        <v>1.61834692955017</v>
+        <v>1.61834704875946</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>1.80200004577637</v>
       </c>
       <c r="G193" t="n">
-        <v>1.61834692955017</v>
+        <v>1.61834704875946</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>1.83299994468689</v>
       </c>
       <c r="G196" t="n">
-        <v>1.64618766307831</v>
+        <v>1.64618754386902</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>1.875</v>
       </c>
       <c r="G198" t="n">
-        <v>1.68390715122223</v>
+        <v>1.68390727043152</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G199" t="n">
-        <v>1.69737839698792</v>
+        <v>1.6973785161972</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G200" t="n">
-        <v>1.68839752674103</v>
+        <v>1.68839764595032</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G203" t="n">
-        <v>1.66594541072845</v>
+        <v>1.66594552993774</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G207" t="n">
-        <v>1.64349341392517</v>
+        <v>1.64349353313446</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G211" t="n">
-        <v>1.65247428417206</v>
+        <v>1.65247416496277</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G214" t="n">
-        <v>1.65247428417206</v>
+        <v>1.65247416496277</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G218" t="n">
-        <v>1.64349341392517</v>
+        <v>1.64349353313446</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>1.83700001239777</v>
       </c>
       <c r="G219" t="n">
-        <v>1.64978003501892</v>
+        <v>1.64977991580963</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>1.80200004577637</v>
       </c>
       <c r="G221" t="n">
-        <v>1.61834692955017</v>
+        <v>1.61834704875946</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>1.83700001239777</v>
       </c>
       <c r="G222" t="n">
-        <v>1.64978003501892</v>
+        <v>1.64977991580963</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>1.84800004959106</v>
       </c>
       <c r="G223" t="n">
-        <v>1.65965890884399</v>
+        <v>1.65965902805328</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>1.62899994850159</v>
       </c>
       <c r="G229" t="n">
-        <v>1.46297860145569</v>
+        <v>1.4629784822464</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>1.4650000333786</v>
       </c>
       <c r="G235" t="n">
-        <v>1.31569278240204</v>
+        <v>1.31569290161133</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>1.4650000333786</v>
       </c>
       <c r="G236" t="n">
-        <v>1.31569278240204</v>
+        <v>1.31569290161133</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>1.52199995517731</v>
       </c>
       <c r="G237" t="n">
-        <v>1.36688339710236</v>
+        <v>1.36688351631165</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>1.55900001525879</v>
       </c>
       <c r="G239" t="n">
-        <v>1.40011262893677</v>
+        <v>1.40011274814606</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G243" t="n">
-        <v>1.45040535926819</v>
+        <v>1.45040547847748</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>1.67900002002716</v>
       </c>
       <c r="G246" t="n">
-        <v>1.50788283348083</v>
+        <v>1.50788271427155</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>1.71899998188019</v>
       </c>
       <c r="G247" t="n">
-        <v>1.5438060760498</v>
+        <v>1.54380595684052</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>1.70200002193451</v>
       </c>
       <c r="G248" t="n">
-        <v>1.52853858470917</v>
+        <v>1.52853870391846</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>1.81400001049042</v>
       </c>
       <c r="G254" t="n">
-        <v>1.6291241645813</v>
+        <v>1.62912404537201</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G257" t="n">
-        <v>1.66594541072845</v>
+        <v>1.66594552993774</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G258" t="n">
-        <v>1.66594541072845</v>
+        <v>1.66594552993774</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G259" t="n">
-        <v>1.66594541072845</v>
+        <v>1.66594552993774</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>1.81400001049042</v>
       </c>
       <c r="G261" t="n">
-        <v>1.6291241645813</v>
+        <v>1.62912404537201</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G262" t="n">
-        <v>1.64349341392517</v>
+        <v>1.64349353313446</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G263" t="n">
-        <v>1.65247428417206</v>
+        <v>1.65247416496277</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G265" t="n">
-        <v>1.64798390865326</v>
+        <v>1.64798378944397</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G267" t="n">
-        <v>1.65247428417206</v>
+        <v>1.65247416496277</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>1.80099999904633</v>
       </c>
       <c r="G270" t="n">
-        <v>1.61744892597198</v>
+        <v>1.61744904518127</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>1.71899998188019</v>
       </c>
       <c r="G274" t="n">
-        <v>1.5438060760498</v>
+        <v>1.54380595684052</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>1.70200002193451</v>
       </c>
       <c r="G275" t="n">
-        <v>1.52853858470917</v>
+        <v>1.52853870391846</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>1.69599997997284</v>
       </c>
       <c r="G276" t="n">
-        <v>1.52315020561218</v>
+        <v>1.52315008640289</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>1.62100005149841</v>
       </c>
       <c r="G285" t="n">
-        <v>1.45579397678375</v>
+        <v>1.45579385757446</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>1.63100004196167</v>
       </c>
       <c r="G287" t="n">
-        <v>1.46477484703064</v>
+        <v>1.46477472782135</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G290" t="n">
-        <v>1.38304901123047</v>
+        <v>1.38304913043976</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>1.48599994182587</v>
       </c>
       <c r="G292" t="n">
-        <v>1.33455240726471</v>
+        <v>1.33455264568329</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>1.47800004482269</v>
       </c>
       <c r="G297" t="n">
-        <v>1.32736802101135</v>
+        <v>1.32736790180206</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G298" t="n">
-        <v>1.33814489841461</v>
+        <v>1.3381450176239</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>1.55299997329712</v>
       </c>
       <c r="G299" t="n">
-        <v>1.39472424983978</v>
+        <v>1.39472413063049</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>1.58599996566772</v>
       </c>
       <c r="G302" t="n">
-        <v>1.42436099052429</v>
+        <v>1.424360871315</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G308" t="n">
-        <v>1.39203000068665</v>
+        <v>1.39202976226807</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>1.53600001335144</v>
       </c>
       <c r="G311" t="n">
-        <v>1.37945663928986</v>
+        <v>1.37945675849915</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>1.54499995708466</v>
       </c>
       <c r="G312" t="n">
-        <v>1.38753938674927</v>
+        <v>1.38753950595856</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G313" t="n">
-        <v>1.38304901123047</v>
+        <v>1.38304913043976</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G315" t="n">
-        <v>1.39203000068665</v>
+        <v>1.39202976226807</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>1.62600004673004</v>
       </c>
       <c r="G320" t="n">
-        <v>1.46028423309326</v>
+        <v>1.46028435230255</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>1.62899994850159</v>
       </c>
       <c r="G322" t="n">
-        <v>1.46297860145569</v>
+        <v>1.4629784822464</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>1.65199995040894</v>
       </c>
       <c r="G326" t="n">
-        <v>1.48363447189331</v>
+        <v>1.48363435268402</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>1.63399994373322</v>
       </c>
       <c r="G327" t="n">
-        <v>1.4674688577652</v>
+        <v>1.46746897697449</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>1.62199997901917</v>
       </c>
       <c r="G329" t="n">
-        <v>1.45669186115265</v>
+        <v>1.45669198036194</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G333" t="n">
-        <v>1.42346298694611</v>
+        <v>1.42346286773682</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>1.63399994373322</v>
       </c>
       <c r="G336" t="n">
-        <v>1.4674688577652</v>
+        <v>1.46746897697449</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>1.67900002002716</v>
       </c>
       <c r="G343" t="n">
-        <v>1.50788283348083</v>
+        <v>1.50788271427155</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G344" t="n">
-        <v>1.52225208282471</v>
+        <v>1.522252202034</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>1.67900002002716</v>
       </c>
       <c r="G345" t="n">
-        <v>1.50788283348083</v>
+        <v>1.50788271427155</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G348" t="n">
-        <v>1.51776170730591</v>
+        <v>1.5177618265152</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>1.80099999904633</v>
       </c>
       <c r="G353" t="n">
-        <v>1.61744892597198</v>
+        <v>1.61744904518127</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>1.78699994087219</v>
       </c>
       <c r="G354" t="n">
-        <v>1.60487568378448</v>
+        <v>1.60487580299377</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G355" t="n">
-        <v>1.65247428417206</v>
+        <v>1.65247416496277</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G356" t="n">
-        <v>1.7108496427536</v>
+        <v>1.71084952354431</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G357" t="n">
-        <v>1.74228274822235</v>
+        <v>1.74228262901306</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>1.875</v>
       </c>
       <c r="G361" t="n">
-        <v>1.68390715122223</v>
+        <v>1.68390727043152</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>1.8860000371933</v>
       </c>
       <c r="G362" t="n">
-        <v>1.69378614425659</v>
+        <v>1.6937860250473</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G364" t="n">
-        <v>1.71534013748169</v>
+        <v>1.7153400182724</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>1.85899996757507</v>
       </c>
       <c r="G366" t="n">
-        <v>1.66953778266907</v>
+        <v>1.66953766345978</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G372" t="n">
-        <v>1.65247428417206</v>
+        <v>1.65247416496277</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>1.83700001239777</v>
       </c>
       <c r="G373" t="n">
-        <v>1.64978003501892</v>
+        <v>1.64977991580963</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G377" t="n">
-        <v>1.64349341392517</v>
+        <v>1.64349353313446</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>1.7610000371933</v>
       </c>
       <c r="G381" t="n">
-        <v>1.58152568340302</v>
+        <v>1.58152556419373</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>1.72099995613098</v>
       </c>
       <c r="G385" t="n">
-        <v>1.54560220241547</v>
+        <v>1.54560232162476</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>1.72099995613098</v>
       </c>
       <c r="G386" t="n">
-        <v>1.54560220241547</v>
+        <v>1.54560232162476</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>1.69700002670288</v>
       </c>
       <c r="G389" t="n">
-        <v>1.52404832839966</v>
+        <v>1.52404820919037</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G394" t="n">
-        <v>1.60757005214691</v>
+        <v>1.60756993293762</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>1.7610000371933</v>
       </c>
       <c r="G399" t="n">
-        <v>1.58152568340302</v>
+        <v>1.58152556419373</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>1.78400003910065</v>
       </c>
       <c r="G401" t="n">
-        <v>1.60218155384064</v>
+        <v>1.60218143463135</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>1.78299999237061</v>
       </c>
       <c r="G404" t="n">
-        <v>1.60128355026245</v>
+        <v>1.60128343105316</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G406" t="n">
-        <v>1.60757005214691</v>
+        <v>1.60756993293762</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>1.78400003910065</v>
       </c>
       <c r="G408" t="n">
-        <v>1.60218155384064</v>
+        <v>1.60218143463135</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>1.80099999904633</v>
       </c>
       <c r="G412" t="n">
-        <v>1.61744892597198</v>
+        <v>1.61744904518127</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>1.77100002765656</v>
       </c>
       <c r="G414" t="n">
-        <v>1.5905065536499</v>
+        <v>1.59050643444061</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>1.75399994850159</v>
       </c>
       <c r="G415" t="n">
-        <v>1.57523894309998</v>
+        <v>1.57523906230927</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>1.73699998855591</v>
       </c>
       <c r="G418" t="n">
-        <v>1.55997157096863</v>
+        <v>1.55997169017792</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>1.73099994659424</v>
       </c>
       <c r="G419" t="n">
-        <v>1.55458307266235</v>
+        <v>1.55458295345306</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G421" t="n">
-        <v>1.60307967662811</v>
+        <v>1.60307955741882</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G422" t="n">
-        <v>1.60757005214691</v>
+        <v>1.60756993293762</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>1.8309999704361</v>
       </c>
       <c r="G423" t="n">
-        <v>1.64439129829407</v>
+        <v>1.64439141750336</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>1.85300004482269</v>
       </c>
       <c r="G429" t="n">
-        <v>1.66414928436279</v>
+        <v>1.66414940357208</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>1.89600002765656</v>
       </c>
       <c r="G432" t="n">
-        <v>1.70276701450348</v>
+        <v>1.70276689529419</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G434" t="n">
-        <v>1.88597595691681</v>
+        <v>1.88597583770752</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G437" t="n">
-        <v>2.02966952323914</v>
+        <v>2.02966928482056</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G441" t="n">
-        <v>2.25419044494629</v>
+        <v>2.25419020652771</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>2.53800010681152</v>
       </c>
       <c r="G442" t="n">
-        <v>2.27933692932129</v>
+        <v>2.27933669090271</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>2.61800003051758</v>
       </c>
       <c r="G446" t="n">
-        <v>2.35118341445923</v>
+        <v>2.35118365287781</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>2.61800003051758</v>
       </c>
       <c r="G447" t="n">
-        <v>2.35118341445923</v>
+        <v>2.35118365287781</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>2.53600001335144</v>
       </c>
       <c r="G448" t="n">
-        <v>2.27754068374634</v>
+        <v>2.27754044532776</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>2.49600005149841</v>
       </c>
       <c r="G453" t="n">
-        <v>2.24161744117737</v>
+        <v>2.24161720275879</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G454" t="n">
-        <v>2.26317095756531</v>
+        <v>2.26317119598389</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>2.50600004196167</v>
       </c>
       <c r="G458" t="n">
-        <v>2.25059795379639</v>
+        <v>2.25059819221497</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>2.54800009727478</v>
       </c>
       <c r="G459" t="n">
-        <v>2.28831791877747</v>
+        <v>2.28831768035889</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>2.83800005912781</v>
       </c>
       <c r="G462" t="n">
-        <v>2.54876184463501</v>
+        <v>2.54876208305359</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>2.86199998855591</v>
       </c>
       <c r="G463" t="n">
-        <v>2.57031607627869</v>
+        <v>2.57031583786011</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>2.7279999256134</v>
       </c>
       <c r="G465" t="n">
-        <v>2.44997239112854</v>
+        <v>2.44997262954712</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G468" t="n">
-        <v>2.50565385818481</v>
+        <v>2.50565361976624</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G472" t="n">
-        <v>2.55055785179138</v>
+        <v>2.55055809020996</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>2.79200005531311</v>
       </c>
       <c r="G474" t="n">
-        <v>2.50744986534119</v>
+        <v>2.50745010375977</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>2.89800000190735</v>
       </c>
       <c r="G475" t="n">
-        <v>2.60264706611633</v>
+        <v>2.60264682769775</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>2.82200002670288</v>
       </c>
       <c r="G476" t="n">
-        <v>2.53439235687256</v>
+        <v>2.53439283370972</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>2.49399995803833</v>
       </c>
       <c r="G484" t="n">
-        <v>2.23982119560242</v>
+        <v>2.23982095718384</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G488" t="n">
-        <v>2.25419044494629</v>
+        <v>2.25419020652771</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>2.54399991035461</v>
       </c>
       <c r="G489" t="n">
-        <v>2.28472518920898</v>
+        <v>2.28472542762756</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>2.55800008773804</v>
       </c>
       <c r="G491" t="n">
-        <v>2.29729843139648</v>
+        <v>2.29729866981506</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>2.51399993896484</v>
       </c>
       <c r="G492" t="n">
-        <v>2.25778245925903</v>
+        <v>2.25778269767761</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G494" t="n">
-        <v>2.20928621292114</v>
+        <v>2.20928645133972</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G496" t="n">
-        <v>2.23622894287109</v>
+        <v>2.23622870445251</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G497" t="n">
-        <v>2.20928621292114</v>
+        <v>2.20928645133972</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>2.51399993896484</v>
       </c>
       <c r="G498" t="n">
-        <v>2.25778245925903</v>
+        <v>2.25778269767761</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>2.54800009727478</v>
       </c>
       <c r="G500" t="n">
-        <v>2.28831791877747</v>
+        <v>2.28831768035889</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G501" t="n">
-        <v>2.23622894287109</v>
+        <v>2.23622870445251</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>2.47399997711182</v>
       </c>
       <c r="G503" t="n">
-        <v>2.22185921669006</v>
+        <v>2.22185945510864</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G504" t="n">
-        <v>2.22724795341492</v>
+        <v>2.22724771499634</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G507" t="n">
-        <v>2.22724795341492</v>
+        <v>2.22724771499634</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>2.45199990272522</v>
       </c>
       <c r="G508" t="n">
-        <v>2.20210146903992</v>
+        <v>2.20210123062134</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G510" t="n">
-        <v>2.19850945472717</v>
+        <v>2.19850921630859</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>2.42199993133545</v>
       </c>
       <c r="G511" t="n">
-        <v>2.17515897750854</v>
+        <v>2.17515921592712</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G513" t="n">
-        <v>2.18234372138977</v>
+        <v>2.18234395980835</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G516" t="n">
-        <v>2.22724795341492</v>
+        <v>2.22724771499634</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G517" t="n">
-        <v>2.22724795341492</v>
+        <v>2.22724771499634</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>2.43499994277954</v>
       </c>
       <c r="G519" t="n">
-        <v>2.18683409690857</v>
+        <v>2.18683385848999</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G523" t="n">
-        <v>2.12845826148987</v>
+        <v>2.12845849990845</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G526" t="n">
-        <v>2.06559276580811</v>
+        <v>2.06559300422668</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G527" t="n">
-        <v>2.09253525733948</v>
+        <v>2.09253549575806</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G530" t="n">
-        <v>2.10151624679565</v>
+        <v>2.10151600837708</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>2.41499996185303</v>
       </c>
       <c r="G531" t="n">
-        <v>2.16887259483337</v>
+        <v>2.16887235641479</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G532" t="n">
-        <v>2.12845826148987</v>
+        <v>2.12845849990845</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G534" t="n">
-        <v>2.13743948936462</v>
+        <v>2.1374397277832</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G536" t="n">
-        <v>2.01170802116394</v>
+        <v>2.01170778274536</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>2.27500009536743</v>
       </c>
       <c r="G537" t="n">
-        <v>2.04314064979553</v>
+        <v>2.04314041137695</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G539" t="n">
-        <v>2.06559276580811</v>
+        <v>2.06559300422668</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>2.36500000953674</v>
       </c>
       <c r="G541" t="n">
-        <v>2.12396836280823</v>
+        <v>2.12396812438965</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>2.34500002861023</v>
       </c>
       <c r="G543" t="n">
-        <v>2.10600638389587</v>
+        <v>2.10600662231445</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G544" t="n">
-        <v>2.06559276580811</v>
+        <v>2.06559300422668</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G545" t="n">
-        <v>2.06559276580811</v>
+        <v>2.06559300422668</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G546" t="n">
-        <v>2.10151624679565</v>
+        <v>2.10151600837708</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G547" t="n">
-        <v>2.06559276580811</v>
+        <v>2.06559300422668</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>2.21499991416931</v>
       </c>
       <c r="G552" t="n">
-        <v>1.98925566673279</v>
+        <v>1.98925542831421</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G554" t="n">
-        <v>1.87699496746063</v>
+        <v>1.87699508666992</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G555" t="n">
-        <v>1.903937458992</v>
+        <v>1.90393769741058</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G556" t="n">
-        <v>1.85005259513855</v>
+        <v>1.85005271434784</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G557" t="n">
-        <v>1.91291880607605</v>
+        <v>1.91291868686676</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G561" t="n">
-        <v>2.01170802116394</v>
+        <v>2.01170778274536</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>2.27500009536743</v>
       </c>
       <c r="G565" t="n">
-        <v>2.04314064979553</v>
+        <v>2.04314041137695</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G566" t="n">
-        <v>1.9937459230423</v>
+        <v>1.99374616146088</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G568" t="n">
-        <v>2.01170802116394</v>
+        <v>2.01170778274536</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>2.15499997138977</v>
       </c>
       <c r="G571" t="n">
-        <v>1.93537068367004</v>
+        <v>1.93537044525146</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G572" t="n">
-        <v>1.91291880607605</v>
+        <v>1.91291868686676</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>2.15499997138977</v>
       </c>
       <c r="G573" t="n">
-        <v>1.93537068367004</v>
+        <v>1.93537044525146</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G582" t="n">
-        <v>2.05661225318909</v>
+        <v>2.05661201477051</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G583" t="n">
-        <v>2.03865003585815</v>
+        <v>2.03865027427673</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>2.24499988555908</v>
       </c>
       <c r="G584" t="n">
-        <v>2.01619791984558</v>
+        <v>2.01619815826416</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G590" t="n">
-        <v>2.06559276580811</v>
+        <v>2.06559300422668</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G593" t="n">
-        <v>2.01170802116394</v>
+        <v>2.01170778274536</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G598" t="n">
-        <v>2.23622894287109</v>
+        <v>2.23622870445251</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G599" t="n">
-        <v>2.23622894287109</v>
+        <v>2.23622870445251</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>2.47499990463257</v>
       </c>
       <c r="G602" t="n">
-        <v>2.22275733947754</v>
+        <v>2.22275757789612</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>2.24499988555908</v>
       </c>
       <c r="G610" t="n">
-        <v>2.01619791984558</v>
+        <v>2.01619815826416</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>2.27500009536743</v>
       </c>
       <c r="G612" t="n">
-        <v>2.04314064979553</v>
+        <v>2.04314041137695</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>2.22499990463257</v>
       </c>
       <c r="G613" t="n">
-        <v>1.9982362985611</v>
+        <v>1.99823653697968</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>2.15499997138977</v>
       </c>
       <c r="G615" t="n">
-        <v>1.93537068367004</v>
+        <v>1.93537044525146</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G616" t="n">
-        <v>2.02966952323914</v>
+        <v>2.02966928482056</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G619" t="n">
-        <v>2.06559276580811</v>
+        <v>2.06559300422668</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G620" t="n">
-        <v>2.02966952323914</v>
+        <v>2.02966928482056</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G624" t="n">
-        <v>2.02966952323914</v>
+        <v>2.02966928482056</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G628" t="n">
-        <v>2.06559276580811</v>
+        <v>2.06559300422668</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G629" t="n">
-        <v>2.02517914772034</v>
+        <v>2.02517938613892</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G631" t="n">
-        <v>1.9937459230423</v>
+        <v>1.99374616146088</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G632" t="n">
-        <v>2.05661225318909</v>
+        <v>2.05661201477051</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G633" t="n">
-        <v>2.01170802116394</v>
+        <v>2.01170778274536</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>2.24499988555908</v>
       </c>
       <c r="G638" t="n">
-        <v>2.01619791984558</v>
+        <v>2.01619815826416</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G639" t="n">
-        <v>1.9937459230423</v>
+        <v>1.99374616146088</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>2.22499990463257</v>
       </c>
       <c r="G640" t="n">
-        <v>1.9982362985611</v>
+        <v>1.99823653697968</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G641" t="n">
-        <v>1.9937459230423</v>
+        <v>1.99374616146088</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G643" t="n">
-        <v>1.9937459230423</v>
+        <v>1.99374616146088</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G644" t="n">
-        <v>1.96680343151093</v>
+        <v>1.9668036699295</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G646" t="n">
-        <v>1.96680343151093</v>
+        <v>1.9668036699295</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G648" t="n">
-        <v>1.96680343151093</v>
+        <v>1.9668036699295</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>2.20499992370605</v>
       </c>
       <c r="G651" t="n">
-        <v>1.98027491569519</v>
+        <v>1.98027467727661</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>2.13499999046326</v>
       </c>
       <c r="G652" t="n">
-        <v>1.91740894317627</v>
+        <v>1.91740882396698</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>2.15499997138977</v>
       </c>
       <c r="G654" t="n">
-        <v>1.93537068367004</v>
+        <v>1.93537044525146</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G656" t="n">
-        <v>1.8949568271637</v>
+        <v>1.89495658874512</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G658" t="n">
-        <v>1.8949568271637</v>
+        <v>1.89495658874512</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G659" t="n">
-        <v>1.93088030815125</v>
+        <v>1.93088042736053</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G661" t="n">
-        <v>1.903937458992</v>
+        <v>1.90393769741058</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G662" t="n">
-        <v>1.903937458992</v>
+        <v>1.90393769741058</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>2.125</v>
       </c>
       <c r="G663" t="n">
-        <v>1.90842807292938</v>
+        <v>1.90842819213867</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G664" t="n">
-        <v>1.93088030815125</v>
+        <v>1.93088042736053</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G665" t="n">
-        <v>1.93088030815125</v>
+        <v>1.93088042736053</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G667" t="n">
-        <v>1.903937458992</v>
+        <v>1.90393769741058</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G670" t="n">
-        <v>1.93088030815125</v>
+        <v>1.93088042736053</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G671" t="n">
-        <v>1.93088030815125</v>
+        <v>1.93088042736053</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G673" t="n">
-        <v>1.97578454017639</v>
+        <v>1.97578430175781</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G674" t="n">
-        <v>1.96680343151093</v>
+        <v>1.9668036699295</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G675" t="n">
-        <v>2.01170802116394</v>
+        <v>2.01170778274536</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G677" t="n">
-        <v>2.03865003585815</v>
+        <v>2.03865027427673</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G678" t="n">
-        <v>2.03865003585815</v>
+        <v>2.03865027427673</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G679" t="n">
-        <v>2.06559276580811</v>
+        <v>2.06559300422668</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G681" t="n">
-        <v>1.9937459230423</v>
+        <v>1.99374616146088</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G684" t="n">
-        <v>1.96680343151093</v>
+        <v>1.9668036699295</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>2.21499991416931</v>
       </c>
       <c r="G685" t="n">
-        <v>1.98925566673279</v>
+        <v>1.98925542831421</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G686" t="n">
-        <v>2.05661225318909</v>
+        <v>2.05661201477051</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G687" t="n">
-        <v>2.05661225318909</v>
+        <v>2.05661201477051</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>2.27500009536743</v>
       </c>
       <c r="G689" t="n">
-        <v>2.04314064979553</v>
+        <v>2.04314041137695</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G691" t="n">
-        <v>2.03865003585815</v>
+        <v>2.03865027427673</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G692" t="n">
-        <v>2.02517914772034</v>
+        <v>2.02517938613892</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G695" t="n">
-        <v>2.05661225318909</v>
+        <v>2.05661201477051</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G696" t="n">
-        <v>2.01170802116394</v>
+        <v>2.01170778274536</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>2.27500009536743</v>
       </c>
       <c r="G697" t="n">
-        <v>2.04314064979553</v>
+        <v>2.04314041137695</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>2.27500009536743</v>
       </c>
       <c r="G699" t="n">
-        <v>2.04314064979553</v>
+        <v>2.04314041137695</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G700" t="n">
-        <v>2.02966952323914</v>
+        <v>2.02966928482056</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G702" t="n">
-        <v>2.02517914772034</v>
+        <v>2.02517938613892</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G703" t="n">
-        <v>2.03865003585815</v>
+        <v>2.03865027427673</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G705" t="n">
-        <v>2.02517914772034</v>
+        <v>2.02517938613892</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G706" t="n">
-        <v>1.97578454017639</v>
+        <v>1.97578430175781</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G707" t="n">
-        <v>1.91291880607605</v>
+        <v>1.91291868686676</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G709" t="n">
-        <v>1.85005259513855</v>
+        <v>1.85005271434784</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G710" t="n">
-        <v>1.77820599079132</v>
+        <v>1.77820587158203</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G711" t="n">
-        <v>1.82311010360718</v>
+        <v>1.82311022281647</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G712" t="n">
-        <v>1.85903346538544</v>
+        <v>1.85903334617615</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G715" t="n">
-        <v>1.8051483631134</v>
+        <v>1.80514848232269</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G721" t="n">
-        <v>1.65247428417206</v>
+        <v>1.65247416496277</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G722" t="n">
-        <v>1.65247428417206</v>
+        <v>1.65247416496277</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>1.85599994659424</v>
       </c>
       <c r="G723" t="n">
-        <v>1.66684341430664</v>
+        <v>1.66684353351593</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>1.81599998474121</v>
       </c>
       <c r="G727" t="n">
-        <v>1.63092017173767</v>
+        <v>1.63092029094696</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>1.83399999141693</v>
       </c>
       <c r="G728" t="n">
-        <v>1.64708566665649</v>
+        <v>1.64708578586578</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>1.81599998474121</v>
       </c>
       <c r="G730" t="n">
-        <v>1.63092017173767</v>
+        <v>1.63092029094696</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>1.65400004386902</v>
       </c>
       <c r="G736" t="n">
-        <v>1.48543071746826</v>
+        <v>1.48543059825897</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>1.65199995040894</v>
       </c>
       <c r="G737" t="n">
-        <v>1.48363447189331</v>
+        <v>1.48363435268402</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>1.55599999427795</v>
       </c>
       <c r="G741" t="n">
-        <v>1.39741849899292</v>
+        <v>1.39741837978363</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>1.57400000095367</v>
       </c>
       <c r="G742" t="n">
-        <v>1.41358387470245</v>
+        <v>1.41358399391174</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>1.49600005149841</v>
       </c>
       <c r="G746" t="n">
-        <v>1.34353339672089</v>
+        <v>1.3435332775116</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G747" t="n">
-        <v>1.39203000068665</v>
+        <v>1.39202976226807</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G756" t="n">
-        <v>1.23935568332672</v>
+        <v>1.23935556411743</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G757" t="n">
-        <v>1.21241319179535</v>
+        <v>1.21241307258606</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>1.29200005531311</v>
       </c>
       <c r="G758" t="n">
-        <v>1.16032445430756</v>
+        <v>1.16032433509827</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>1.25399994850159</v>
       </c>
       <c r="G760" t="n">
-        <v>1.12619709968567</v>
+        <v>1.12619698047638</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G761" t="n">
-        <v>1.16750884056091</v>
+        <v>1.1675089597702</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>1.36800003051758</v>
       </c>
       <c r="G764" t="n">
-        <v>1.22857856750488</v>
+        <v>1.22857868671417</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>1.52799999713898</v>
       </c>
       <c r="G766" t="n">
-        <v>1.3722722530365</v>
+        <v>1.37227213382721</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G770" t="n">
-        <v>1.35610663890839</v>
+        <v>1.3561065196991</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>1.51800000667572</v>
       </c>
       <c r="G771" t="n">
-        <v>1.36329114437103</v>
+        <v>1.36329126358032</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>1.47800004482269</v>
       </c>
       <c r="G773" t="n">
-        <v>1.32736802101135</v>
+        <v>1.32736790180206</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G774" t="n">
-        <v>1.33814489841461</v>
+        <v>1.3381450176239</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>1.49600005149841</v>
       </c>
       <c r="G775" t="n">
-        <v>1.34353339672089</v>
+        <v>1.3435332775116</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>1.47200000286102</v>
       </c>
       <c r="G780" t="n">
-        <v>1.3219792842865</v>
+        <v>1.32197952270508</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>1.49600005149841</v>
       </c>
       <c r="G781" t="n">
-        <v>1.34353339672089</v>
+        <v>1.3435332775116</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>1.40199995040894</v>
       </c>
       <c r="G789" t="n">
-        <v>1.25911355018616</v>
+        <v>1.25911343097687</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>1.41799998283386</v>
       </c>
       <c r="G793" t="n">
-        <v>1.27348268032074</v>
+        <v>1.27348291873932</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G794" t="n">
-        <v>1.45309960842133</v>
+        <v>1.45309948921204</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G795" t="n">
-        <v>1.45489573478699</v>
+        <v>1.45489585399628</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>1.89800000190735</v>
       </c>
       <c r="G797" t="n">
-        <v>1.70456302165985</v>
+        <v>1.70456314086914</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G798" t="n">
-        <v>1.65247428417206</v>
+        <v>1.65247416496277</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G800" t="n">
-        <v>1.65247428417206</v>
+        <v>1.65247416496277</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G803" t="n">
-        <v>1.88597595691681</v>
+        <v>1.88597583770752</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G804" t="n">
-        <v>1.85005259513855</v>
+        <v>1.85005271434784</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G805" t="n">
-        <v>1.82311010360718</v>
+        <v>1.82311022281647</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G807" t="n">
-        <v>1.85903346538544</v>
+        <v>1.85903334617615</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G809" t="n">
-        <v>1.85005259513855</v>
+        <v>1.85005271434784</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>1.98199999332428</v>
       </c>
       <c r="G810" t="n">
-        <v>1.78000211715698</v>
+        <v>1.78000223636627</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>2.04500007629395</v>
       </c>
       <c r="G812" t="n">
-        <v>1.83658134937286</v>
+        <v>1.83658146858215</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G814" t="n">
-        <v>1.8051483631134</v>
+        <v>1.80514848232269</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>1.95799994468689</v>
       </c>
       <c r="G816" t="n">
-        <v>1.7584480047226</v>
+        <v>1.75844812393188</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G818" t="n">
-        <v>1.68839752674103</v>
+        <v>1.68839764595032</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>1.90600001811981</v>
       </c>
       <c r="G820" t="n">
-        <v>1.71174764633179</v>
+        <v>1.71174776554108</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>1.87600004673004</v>
       </c>
       <c r="G823" t="n">
-        <v>1.6848052740097</v>
+        <v>1.68480539321899</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>1.90600001811981</v>
       </c>
       <c r="G825" t="n">
-        <v>1.71174764633179</v>
+        <v>1.71174776554108</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>2.21499991416931</v>
       </c>
       <c r="G827" t="n">
-        <v>1.98925566673279</v>
+        <v>1.98925542831421</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G828" t="n">
-        <v>1.9937459230423</v>
+        <v>1.99374616146088</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G829" t="n">
-        <v>2.06559276580811</v>
+        <v>2.06559300422668</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>2.34500002861023</v>
       </c>
       <c r="G831" t="n">
-        <v>2.10600638389587</v>
+        <v>2.10600662231445</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G832" t="n">
-        <v>2.01170802116394</v>
+        <v>2.01170778274536</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G834" t="n">
-        <v>1.9937459230423</v>
+        <v>1.99374616146088</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G835" t="n">
-        <v>1.97578454017639</v>
+        <v>1.97578430175781</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G836" t="n">
-        <v>1.97578454017639</v>
+        <v>1.97578430175781</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G837" t="n">
-        <v>1.9937459230423</v>
+        <v>1.99374616146088</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G838" t="n">
-        <v>2.13743948936462</v>
+        <v>2.1374397277832</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>2.39499998092651</v>
       </c>
       <c r="G845" t="n">
-        <v>2.15091061592102</v>
+        <v>2.1509108543396</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G846" t="n">
-        <v>2.09253525733948</v>
+        <v>2.09253549575806</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>2.46499991416931</v>
       </c>
       <c r="G849" t="n">
-        <v>2.21377658843994</v>
+        <v>2.21377635002136</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>2.36500000953674</v>
       </c>
       <c r="G850" t="n">
-        <v>2.12396836280823</v>
+        <v>2.12396812438965</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G852" t="n">
-        <v>1.96680343151093</v>
+        <v>1.9668036699295</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G853" t="n">
-        <v>1.97578454017639</v>
+        <v>1.97578430175781</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G854" t="n">
-        <v>1.96680343151093</v>
+        <v>1.9668036699295</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>2.24499988555908</v>
       </c>
       <c r="G859" t="n">
-        <v>2.01619791984558</v>
+        <v>2.01619815826416</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>2.27500009536743</v>
       </c>
       <c r="G860" t="n">
-        <v>2.04314064979553</v>
+        <v>2.04314041137695</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G864" t="n">
-        <v>2.06559276580811</v>
+        <v>2.06559300422668</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G865" t="n">
-        <v>2.03865003585815</v>
+        <v>2.03865027427673</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G867" t="n">
-        <v>2.05661225318909</v>
+        <v>2.05661201477051</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G869" t="n">
-        <v>2.06559276580811</v>
+        <v>2.06559300422668</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G871" t="n">
-        <v>2.05661225318909</v>
+        <v>2.05661201477051</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G872" t="n">
-        <v>2.05661225318909</v>
+        <v>2.05661201477051</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G873" t="n">
-        <v>2.02966952323914</v>
+        <v>2.02966928482056</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>2.27500009536743</v>
       </c>
       <c r="G874" t="n">
-        <v>2.04314064979553</v>
+        <v>2.04314041137695</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>2.22499990463257</v>
       </c>
       <c r="G875" t="n">
-        <v>1.9982362985611</v>
+        <v>1.99823653697968</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G877" t="n">
-        <v>1.85903346538544</v>
+        <v>1.85903334617615</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G878" t="n">
-        <v>1.86801433563232</v>
+        <v>1.86801421642303</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G886" t="n">
-        <v>1.82311010360718</v>
+        <v>1.82311022281647</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G887" t="n">
-        <v>1.82311010360718</v>
+        <v>1.82311022281647</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G892" t="n">
-        <v>1.82311010360718</v>
+        <v>1.82311022281647</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G893" t="n">
-        <v>1.82311010360718</v>
+        <v>1.82311022281647</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G894" t="n">
-        <v>1.8051483631134</v>
+        <v>1.80514848232269</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>1.99600005149841</v>
       </c>
       <c r="G896" t="n">
-        <v>1.79257535934448</v>
+        <v>1.79257547855377</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>1.99399995803833</v>
       </c>
       <c r="G897" t="n">
-        <v>1.79077911376953</v>
+        <v>1.79077899456024</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G899" t="n">
-        <v>1.8051483631134</v>
+        <v>1.80514848232269</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>2</v>
       </c>
       <c r="G900" t="n">
-        <v>1.79616761207581</v>
+        <v>1.7961677312851</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>1.99399995803833</v>
       </c>
       <c r="G901" t="n">
-        <v>1.79077911376953</v>
+        <v>1.79077899456024</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>1.97800004482269</v>
       </c>
       <c r="G902" t="n">
-        <v>1.77640974521637</v>
+        <v>1.77640986442566</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>1.89800000190735</v>
       </c>
       <c r="G903" t="n">
-        <v>1.70456302165985</v>
+        <v>1.70456314086914</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>2.24499988555908</v>
       </c>
       <c r="G908" t="n">
-        <v>2.01619791984558</v>
+        <v>2.01619815826416</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G909" t="n">
-        <v>1.9937459230423</v>
+        <v>1.99374616146088</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G911" t="n">
-        <v>1.93088030815125</v>
+        <v>1.93088042736053</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>2.20499992370605</v>
       </c>
       <c r="G912" t="n">
-        <v>1.98027491569519</v>
+        <v>1.98027467727661</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>2.125</v>
       </c>
       <c r="G914" t="n">
-        <v>1.90842807292938</v>
+        <v>1.90842819213867</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>2.13499999046326</v>
       </c>
       <c r="G915" t="n">
-        <v>1.91740894317627</v>
+        <v>1.91740882396698</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G918" t="n">
-        <v>1.903937458992</v>
+        <v>1.90393769741058</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>2.04500007629395</v>
       </c>
       <c r="G919" t="n">
-        <v>1.83658134937286</v>
+        <v>1.83658146858215</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G920" t="n">
-        <v>1.85005259513855</v>
+        <v>1.85005271434784</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>1.98199999332428</v>
       </c>
       <c r="G933" t="n">
-        <v>1.78000211715698</v>
+        <v>1.78000223636627</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G936" t="n">
-        <v>1.85903346538544</v>
+        <v>1.85903334617615</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G937" t="n">
-        <v>1.84556233882904</v>
+        <v>1.84556221961975</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G939" t="n">
-        <v>1.83209097385406</v>
+        <v>1.83209085464478</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G941" t="n">
-        <v>2.14642071723938</v>
+        <v>2.14642024040222</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>2.41499996185303</v>
       </c>
       <c r="G942" t="n">
-        <v>2.16887259483337</v>
+        <v>2.16887235641479</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G944" t="n">
-        <v>2.09253525733948</v>
+        <v>2.09253549575806</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G946" t="n">
-        <v>2.03865003585815</v>
+        <v>2.03865027427673</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G948" t="n">
-        <v>1.97578454017639</v>
+        <v>1.97578430175781</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G950" t="n">
-        <v>2.03865003585815</v>
+        <v>2.03865027427673</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>2.27500009536743</v>
       </c>
       <c r="G951" t="n">
-        <v>2.04314064979553</v>
+        <v>2.04314041137695</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G953" t="n">
-        <v>2.05661225318909</v>
+        <v>2.05661201477051</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>2.27500009536743</v>
       </c>
       <c r="G955" t="n">
-        <v>2.04314064979553</v>
+        <v>2.04314041137695</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G956" t="n">
-        <v>1.96680343151093</v>
+        <v>1.9668036699295</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G957" t="n">
-        <v>1.9937459230423</v>
+        <v>1.99374616146088</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G958" t="n">
-        <v>1.97578454017639</v>
+        <v>1.97578430175781</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G962" t="n">
-        <v>1.9937459230423</v>
+        <v>1.99374616146088</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G963" t="n">
-        <v>2.09253525733948</v>
+        <v>2.09253549575806</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G967" t="n">
-        <v>2.09253525733948</v>
+        <v>2.09253549575806</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>2.36500000953674</v>
       </c>
       <c r="G969" t="n">
-        <v>2.12396836280823</v>
+        <v>2.12396812438965</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G971" t="n">
-        <v>2.05661225318909</v>
+        <v>2.05661201477051</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G972" t="n">
-        <v>2.06559276580811</v>
+        <v>2.06559300422668</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>2.24499988555908</v>
       </c>
       <c r="G973" t="n">
-        <v>2.01619791984558</v>
+        <v>2.01619815826416</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G975" t="n">
-        <v>2.14642071723938</v>
+        <v>2.14642024040222</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>2.51500010490417</v>
       </c>
       <c r="G977" t="n">
-        <v>2.25868105888367</v>
+        <v>2.25868082046509</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>2.75500011444092</v>
       </c>
       <c r="G981" t="n">
-        <v>2.47422075271606</v>
+        <v>2.47422099113464</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G983" t="n">
-        <v>2.55055785179138</v>
+        <v>2.55055809020996</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>2.875</v>
       </c>
       <c r="G984" t="n">
-        <v>2.58199095726013</v>
+        <v>2.58199119567871</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>2.96499991416931</v>
       </c>
       <c r="G986" t="n">
-        <v>2.66281843185425</v>
+        <v>2.66281867027283</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G988" t="n">
-        <v>2.68527054786682</v>
+        <v>2.6852707862854</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G990" t="n">
-        <v>2.68527054786682</v>
+        <v>2.6852707862854</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>2.96499991416931</v>
       </c>
       <c r="G991" t="n">
-        <v>2.66281843185425</v>
+        <v>2.66281867027283</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G993" t="n">
-        <v>2.76609802246094</v>
+        <v>2.76609826087952</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G996" t="n">
-        <v>3.08042764663696</v>
+        <v>3.08042740821838</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1001" t="n">
-        <v>2.73915576934814</v>
+        <v>2.73915553092957</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>2.96499991416931</v>
       </c>
       <c r="G1003" t="n">
-        <v>2.66281843185425</v>
+        <v>2.66281867027283</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1005" t="n">
-        <v>2.68527054786682</v>
+        <v>2.6852707862854</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G1007" t="n">
-        <v>2.72568440437317</v>
+        <v>2.72568464279175</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G1011" t="n">
-        <v>2.72568440437317</v>
+        <v>2.72568464279175</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1012" t="n">
-        <v>2.78406000137329</v>
+        <v>2.78405952453613</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1014" t="n">
-        <v>2.77507877349854</v>
+        <v>2.77507901191711</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>2.96499991416931</v>
       </c>
       <c r="G1019" t="n">
-        <v>2.66281843185425</v>
+        <v>2.66281867027283</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>3.3050000667572</v>
       </c>
       <c r="G1027" t="n">
-        <v>2.96816682815552</v>
+        <v>2.9681670665741</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>3.6949999332428</v>
       </c>
       <c r="G1029" t="n">
-        <v>3.31841969490051</v>
+        <v>3.31841945648193</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1032" t="n">
-        <v>3.07144689559937</v>
+        <v>3.07144665718079</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1038" t="n">
-        <v>3.07144689559937</v>
+        <v>3.07144665718079</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>3.81500005722046</v>
       </c>
       <c r="G1041" t="n">
-        <v>3.426189661026</v>
+        <v>3.42618989944458</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1042" t="n">
-        <v>3.24208235740662</v>
+        <v>3.2420825958252</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>3.85500001907349</v>
       </c>
       <c r="G1045" t="n">
-        <v>3.46211338043213</v>
+        <v>3.46211314201355</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1048" t="n">
-        <v>3.30494856834412</v>
+        <v>3.30494832992554</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1057" t="n">
-        <v>2.78406000137329</v>
+        <v>2.78405952453613</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G1058" t="n">
-        <v>2.77058863639832</v>
+        <v>2.77058839797974</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G1060" t="n">
-        <v>2.57750058174133</v>
+        <v>2.57750034332275</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>2.39499998092651</v>
       </c>
       <c r="G1065" t="n">
-        <v>2.15091061592102</v>
+        <v>2.1509108543396</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>2</v>
       </c>
       <c r="G1067" t="n">
-        <v>1.79616761207581</v>
+        <v>1.7961677312851</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>1.99399995803833</v>
       </c>
       <c r="G1068" t="n">
-        <v>1.79077911376953</v>
+        <v>1.79077899456024</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1070" t="n">
-        <v>1.86801433563232</v>
+        <v>1.86801421642303</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>1.9559999704361</v>
       </c>
       <c r="G1071" t="n">
-        <v>1.75665175914764</v>
+        <v>1.75665187835693</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>1.99399995803833</v>
       </c>
       <c r="G1072" t="n">
-        <v>1.79077911376953</v>
+        <v>1.79077899456024</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>2</v>
       </c>
       <c r="G1073" t="n">
-        <v>1.79616761207581</v>
+        <v>1.7961677312851</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>2.21499991416931</v>
       </c>
       <c r="G1077" t="n">
-        <v>1.98925566673279</v>
+        <v>1.98925542831421</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1082" t="n">
-        <v>2.26317095756531</v>
+        <v>2.26317119598389</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1087" t="n">
-        <v>2.53259658813477</v>
+        <v>2.53259634971619</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1090" t="n">
-        <v>2.54157710075378</v>
+        <v>2.54157733917236</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>2.9449999332428</v>
       </c>
       <c r="G1091" t="n">
-        <v>2.64485692977905</v>
+        <v>2.64485669136047</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1096" t="n">
-        <v>2.68527054786682</v>
+        <v>2.6852707862854</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>2.97499990463257</v>
       </c>
       <c r="G1097" t="n">
-        <v>2.67179942131042</v>
+        <v>2.67179918289185</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1100" t="n">
-        <v>2.67628979682922</v>
+        <v>2.6762900352478</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>2.96499991416931</v>
       </c>
       <c r="G1110" t="n">
-        <v>2.66281843185425</v>
+        <v>2.66281867027283</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>2.78500008583069</v>
       </c>
       <c r="G1112" t="n">
-        <v>2.50116348266602</v>
+        <v>2.50116372108459</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G1115" t="n">
-        <v>2.52810573577881</v>
+        <v>2.52810597419739</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>2.9449999332428</v>
       </c>
       <c r="G1118" t="n">
-        <v>2.64485692977905</v>
+        <v>2.64485669136047</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1130" t="n">
-        <v>2.53259658813477</v>
+        <v>2.53259634971619</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G1131" t="n">
-        <v>2.57750058174133</v>
+        <v>2.57750034332275</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G1134" t="n">
-        <v>2.57750058174133</v>
+        <v>2.57750034332275</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1137" t="n">
-        <v>2.4248263835907</v>
+        <v>2.42482614517212</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G1138" t="n">
-        <v>2.50565385818481</v>
+        <v>2.50565361976624</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>2.6949999332428</v>
       </c>
       <c r="G1141" t="n">
-        <v>2.4203360080719</v>
+        <v>2.42033576965332</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1145" t="n">
-        <v>2.47871136665344</v>
+        <v>2.47871112823486</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1150" t="n">
-        <v>2.4248263835907</v>
+        <v>2.42482614517212</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G1151" t="n">
-        <v>2.40686464309692</v>
+        <v>2.4068648815155</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1155" t="n">
-        <v>2.53259658813477</v>
+        <v>2.53259634971619</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30555,7 +30555,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1161" t="n">
-        <v>2.33501768112183</v>
+        <v>2.33501791954041</v>
       </c>
       <c r="H1161" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1163" t="n">
-        <v>2.27215194702148</v>
+        <v>2.27215218544006</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30633,7 +30633,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1164" t="n">
-        <v>2.27215194702148</v>
+        <v>2.27215218544006</v>
       </c>
       <c r="H1164" t="s">
         <v>8</v>
@@ -30685,7 +30685,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1166" t="n">
-        <v>2.33501768112183</v>
+        <v>2.33501791954041</v>
       </c>
       <c r="H1166" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1167" t="n">
-        <v>2.33501768112183</v>
+        <v>2.33501791954041</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1170" t="n">
-        <v>2.4248263835907</v>
+        <v>2.42482614517212</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>2.74499988555908</v>
       </c>
       <c r="G1171" t="n">
-        <v>2.46524000167847</v>
+        <v>2.46523976325989</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>2.82500004768372</v>
       </c>
       <c r="G1172" t="n">
-        <v>2.53708696365356</v>
+        <v>2.53708672523499</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30919,7 +30919,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1175" t="n">
-        <v>2.47871136665344</v>
+        <v>2.47871112823486</v>
       </c>
       <c r="H1175" t="s">
         <v>8</v>
@@ -30945,7 +30945,7 @@
         <v>2.74499988555908</v>
       </c>
       <c r="G1176" t="n">
-        <v>2.46524000167847</v>
+        <v>2.46523976325989</v>
       </c>
       <c r="H1176" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1182" t="n">
-        <v>2.37094163894653</v>
+        <v>2.37094140052795</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>2.625</v>
       </c>
       <c r="G1184" t="n">
-        <v>2.35747003555298</v>
+        <v>2.35747027397156</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>2.65499997138977</v>
       </c>
       <c r="G1186" t="n">
-        <v>2.38441228866577</v>
+        <v>2.38441276550293</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>2.67499995231628</v>
       </c>
       <c r="G1188" t="n">
-        <v>2.40237426757812</v>
+        <v>2.40237402915955</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1189" t="n">
-        <v>2.37094163894653</v>
+        <v>2.37094140052795</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>2.67499995231628</v>
       </c>
       <c r="G1191" t="n">
-        <v>2.40237426757812</v>
+        <v>2.40237402915955</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>2.625</v>
       </c>
       <c r="G1192" t="n">
-        <v>2.35747003555298</v>
+        <v>2.35747027397156</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>2.78500008583069</v>
       </c>
       <c r="G1196" t="n">
-        <v>2.50116348266602</v>
+        <v>2.50116372108459</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>2.66499996185303</v>
       </c>
       <c r="G1198" t="n">
-        <v>2.39339351654053</v>
+        <v>2.39339327812195</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G1203" t="n">
-        <v>2.28113317489624</v>
+        <v>2.28113293647766</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1204" t="n">
-        <v>2.27215194702148</v>
+        <v>2.27215218544006</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31725,7 +31725,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1206" t="n">
-        <v>2.23622894287109</v>
+        <v>2.23622870445251</v>
       </c>
       <c r="H1206" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1207" t="n">
-        <v>2.27215194702148</v>
+        <v>2.27215218544006</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>2.6949999332428</v>
       </c>
       <c r="G1208" t="n">
-        <v>2.4203360080719</v>
+        <v>2.42033576965332</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1209" t="n">
-        <v>2.31705617904663</v>
+        <v>2.31705641746521</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31907,7 +31907,7 @@
         <v>2.6949999332428</v>
       </c>
       <c r="G1213" t="n">
-        <v>2.4203360080719</v>
+        <v>2.42033576965332</v>
       </c>
       <c r="H1213" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1214" t="n">
-        <v>2.37094163894653</v>
+        <v>2.37094140052795</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -32011,7 +32011,7 @@
         <v>2.74499988555908</v>
       </c>
       <c r="G1217" t="n">
-        <v>2.46524000167847</v>
+        <v>2.46523976325989</v>
       </c>
       <c r="H1217" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1220" t="n">
-        <v>2.53259658813477</v>
+        <v>2.53259634971619</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32141,7 +32141,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G1222" t="n">
-        <v>2.57750058174133</v>
+        <v>2.57750034332275</v>
       </c>
       <c r="H1222" t="s">
         <v>8</v>
@@ -32193,7 +32193,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1224" t="n">
-        <v>2.53259658813477</v>
+        <v>2.53259634971619</v>
       </c>
       <c r="H1224" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>2.75500011444092</v>
       </c>
       <c r="G1226" t="n">
-        <v>2.47422075271606</v>
+        <v>2.47422099113464</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1227" t="n">
-        <v>2.27215194702148</v>
+        <v>2.27215218544006</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32349,7 +32349,7 @@
         <v>2.59500002861023</v>
       </c>
       <c r="G1230" t="n">
-        <v>2.33052730560303</v>
+        <v>2.33052754402161</v>
       </c>
       <c r="H1230" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>2.59500002861023</v>
       </c>
       <c r="G1231" t="n">
-        <v>2.33052730560303</v>
+        <v>2.33052754402161</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1234" t="n">
-        <v>2.31705617904663</v>
+        <v>2.31705641746521</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1243" t="n">
-        <v>2.47871136665344</v>
+        <v>2.47871112823486</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1246" t="n">
-        <v>2.53259658813477</v>
+        <v>2.53259634971619</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32843,7 +32843,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1249" t="n">
-        <v>2.53259658813477</v>
+        <v>2.53259634971619</v>
       </c>
       <c r="H1249" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1252" t="n">
-        <v>2.68527054786682</v>
+        <v>2.6852707862854</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1253" t="n">
-        <v>2.67628979682922</v>
+        <v>2.6762900352478</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -33025,7 +33025,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G1256" t="n">
-        <v>2.7616081237793</v>
+        <v>2.76160764694214</v>
       </c>
       <c r="H1256" t="s">
         <v>8</v>
@@ -33051,7 +33051,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1257" t="n">
-        <v>2.73915576934814</v>
+        <v>2.73915553092957</v>
       </c>
       <c r="H1257" t="s">
         <v>8</v>
@@ -33129,7 +33129,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1260" t="n">
-        <v>2.77507877349854</v>
+        <v>2.77507901191711</v>
       </c>
       <c r="H1260" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1261" t="n">
-        <v>2.78406000137329</v>
+        <v>2.78405952453613</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1262" t="n">
-        <v>2.77507877349854</v>
+        <v>2.77507901191711</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1263" t="n">
-        <v>2.84692597389221</v>
+        <v>2.84692573547363</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33285,7 +33285,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G1266" t="n">
-        <v>2.77058863639832</v>
+        <v>2.77058839797974</v>
       </c>
       <c r="H1266" t="s">
         <v>8</v>
@@ -33363,7 +33363,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1269" t="n">
-        <v>2.78406000137329</v>
+        <v>2.78405952453613</v>
       </c>
       <c r="H1269" t="s">
         <v>8</v>
@@ -33415,7 +33415,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1271" t="n">
-        <v>2.77507877349854</v>
+        <v>2.77507901191711</v>
       </c>
       <c r="H1271" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1272" t="n">
-        <v>2.78406000137329</v>
+        <v>2.78405952453613</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1274" t="n">
-        <v>2.77507877349854</v>
+        <v>2.77507901191711</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G1275" t="n">
-        <v>2.77058863639832</v>
+        <v>2.77058839797974</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33623,7 +33623,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G1279" t="n">
-        <v>2.72568440437317</v>
+        <v>2.72568464279175</v>
       </c>
       <c r="H1279" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>2.9449999332428</v>
       </c>
       <c r="G1283" t="n">
-        <v>2.64485692977905</v>
+        <v>2.64485669136047</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G1286" t="n">
-        <v>2.54606771469116</v>
+        <v>2.54606747627258</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33883,7 +33883,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G1289" t="n">
-        <v>2.63138556480408</v>
+        <v>2.63138580322266</v>
       </c>
       <c r="H1289" t="s">
         <v>8</v>
@@ -34013,7 +34013,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G1294" t="n">
-        <v>2.7616081237793</v>
+        <v>2.76160764694214</v>
       </c>
       <c r="H1294" t="s">
         <v>8</v>
@@ -34117,7 +34117,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1298" t="n">
-        <v>2.81100225448608</v>
+        <v>2.81100249290466</v>
       </c>
       <c r="H1298" t="s">
         <v>8</v>
@@ -34169,7 +34169,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G1300" t="n">
-        <v>3.12982201576233</v>
+        <v>3.12982177734375</v>
       </c>
       <c r="H1300" t="s">
         <v>8</v>
@@ -34299,7 +34299,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G1305" t="n">
-        <v>3.12982201576233</v>
+        <v>3.12982177734375</v>
       </c>
       <c r="H1305" t="s">
         <v>8</v>
@@ -34351,7 +34351,7 @@
         <v>3.42499995231628</v>
       </c>
       <c r="G1307" t="n">
-        <v>3.07593703269958</v>
+        <v>3.07593727111816</v>
       </c>
       <c r="H1307" t="s">
         <v>8</v>
@@ -34377,7 +34377,7 @@
         <v>3.42499995231628</v>
       </c>
       <c r="G1308" t="n">
-        <v>3.07593703269958</v>
+        <v>3.07593727111816</v>
       </c>
       <c r="H1308" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>3.22499990463257</v>
       </c>
       <c r="G1310" t="n">
-        <v>2.89632034301758</v>
+        <v>2.896320104599</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>3.43499994277954</v>
       </c>
       <c r="G1311" t="n">
-        <v>3.08491778373718</v>
+        <v>3.08491802215576</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34741,7 +34741,7 @@
         <v>3.28500008583069</v>
       </c>
       <c r="G1322" t="n">
-        <v>2.95020532608032</v>
+        <v>2.9502055644989</v>
       </c>
       <c r="H1322" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>3.3050000667572</v>
       </c>
       <c r="G1327" t="n">
-        <v>2.96816682815552</v>
+        <v>2.9681670665741</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -34923,7 +34923,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1329" t="n">
-        <v>3.03552341461182</v>
+        <v>3.0355236530304</v>
       </c>
       <c r="H1329" t="s">
         <v>8</v>
@@ -34949,7 +34949,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1330" t="n">
-        <v>3.04450416564941</v>
+        <v>3.04450440406799</v>
       </c>
       <c r="H1330" t="s">
         <v>8</v>
@@ -35027,7 +35027,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1333" t="n">
-        <v>3.03552341461182</v>
+        <v>3.0355236530304</v>
       </c>
       <c r="H1333" t="s">
         <v>8</v>
@@ -35079,7 +35079,7 @@
         <v>3.31500005722046</v>
       </c>
       <c r="G1335" t="n">
-        <v>2.97714781761169</v>
+        <v>2.97714805603027</v>
       </c>
       <c r="H1335" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1340" t="n">
-        <v>2.90081071853638</v>
+        <v>2.90081095695496</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>3.14499998092651</v>
       </c>
       <c r="G1345" t="n">
-        <v>2.82447361946106</v>
+        <v>2.82447338104248</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35599,7 +35599,7 @@
         <v>3.4449999332428</v>
       </c>
       <c r="G1355" t="n">
-        <v>3.09389877319336</v>
+        <v>3.09389853477478</v>
       </c>
       <c r="H1355" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1356" t="n">
-        <v>3.21514010429382</v>
+        <v>3.21513986587524</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35677,7 +35677,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1358" t="n">
-        <v>3.30494856834412</v>
+        <v>3.30494832992554</v>
       </c>
       <c r="H1358" t="s">
         <v>8</v>
@@ -35729,7 +35729,7 @@
         <v>3.60500001907349</v>
       </c>
       <c r="G1360" t="n">
-        <v>3.23759245872498</v>
+        <v>3.23759198188782</v>
       </c>
       <c r="H1360" t="s">
         <v>8</v>
@@ -35781,7 +35781,7 @@
         <v>3.68499994277954</v>
       </c>
       <c r="G1362" t="n">
-        <v>3.30943846702576</v>
+        <v>3.30943870544434</v>
       </c>
       <c r="H1362" t="s">
         <v>8</v>
@@ -35859,7 +35859,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G1365" t="n">
-        <v>3.21963024139404</v>
+        <v>3.2196307182312</v>
       </c>
       <c r="H1365" t="s">
         <v>8</v>
@@ -35911,7 +35911,7 @@
         <v>3.46499991416931</v>
       </c>
       <c r="G1367" t="n">
-        <v>3.11186027526855</v>
+        <v>3.11186051368713</v>
       </c>
       <c r="H1367" t="s">
         <v>8</v>
@@ -35937,7 +35937,7 @@
         <v>3.46499991416931</v>
       </c>
       <c r="G1368" t="n">
-        <v>3.11186027526855</v>
+        <v>3.11186051368713</v>
       </c>
       <c r="H1368" t="s">
         <v>8</v>
@@ -36015,7 +36015,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1371" t="n">
-        <v>3.08042764663696</v>
+        <v>3.08042740821838</v>
       </c>
       <c r="H1371" t="s">
         <v>8</v>
@@ -36067,7 +36067,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1373" t="n">
-        <v>3.04450416564941</v>
+        <v>3.04450440406799</v>
       </c>
       <c r="H1373" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1375" t="n">
-        <v>3.04450416564941</v>
+        <v>3.04450440406799</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36145,7 +36145,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1376" t="n">
-        <v>3.07144689559937</v>
+        <v>3.07144665718079</v>
       </c>
       <c r="H1376" t="s">
         <v>8</v>
@@ -36223,7 +36223,7 @@
         <v>3.4449999332428</v>
       </c>
       <c r="G1379" t="n">
-        <v>3.09389877319336</v>
+        <v>3.09389853477478</v>
       </c>
       <c r="H1379" t="s">
         <v>8</v>
@@ -36301,7 +36301,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1382" t="n">
-        <v>3.04450416564941</v>
+        <v>3.04450440406799</v>
       </c>
       <c r="H1382" t="s">
         <v>8</v>
@@ -36327,7 +36327,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1383" t="n">
-        <v>3.08042764663696</v>
+        <v>3.08042740821838</v>
       </c>
       <c r="H1383" t="s">
         <v>8</v>
@@ -36379,7 +36379,7 @@
         <v>3.54500007629395</v>
       </c>
       <c r="G1385" t="n">
-        <v>3.18370723724365</v>
+        <v>3.18370699882507</v>
       </c>
       <c r="H1385" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>3.43499994277954</v>
       </c>
       <c r="G1387" t="n">
-        <v>3.08491778373718</v>
+        <v>3.08491802215576</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>3.28500008583069</v>
       </c>
       <c r="G1393" t="n">
-        <v>2.95020532608032</v>
+        <v>2.9502055644989</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36639,7 +36639,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G1395" t="n">
-        <v>3.21963024139404</v>
+        <v>3.2196307182312</v>
       </c>
       <c r="H1395" t="s">
         <v>8</v>
@@ -36691,7 +36691,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1397" t="n">
-        <v>3.21514010429382</v>
+        <v>3.21513986587524</v>
       </c>
       <c r="H1397" t="s">
         <v>8</v>
@@ -36873,7 +36873,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1404" t="n">
-        <v>3.04450416564941</v>
+        <v>3.04450440406799</v>
       </c>
       <c r="H1404" t="s">
         <v>8</v>
@@ -36951,7 +36951,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1407" t="n">
-        <v>3.04450416564941</v>
+        <v>3.04450440406799</v>
       </c>
       <c r="H1407" t="s">
         <v>8</v>
@@ -37003,7 +37003,7 @@
         <v>3.23499989509583</v>
       </c>
       <c r="G1409" t="n">
-        <v>2.90530109405518</v>
+        <v>2.9053008556366</v>
       </c>
       <c r="H1409" t="s">
         <v>8</v>
@@ -37029,7 +37029,7 @@
         <v>3.23499989509583</v>
       </c>
       <c r="G1410" t="n">
-        <v>2.90530109405518</v>
+        <v>2.9053008556366</v>
       </c>
       <c r="H1410" t="s">
         <v>8</v>
@@ -37133,7 +37133,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1414" t="n">
-        <v>3.04450416564941</v>
+        <v>3.04450440406799</v>
       </c>
       <c r="H1414" t="s">
         <v>8</v>
@@ -37523,7 +37523,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1429" t="n">
-        <v>2.90979146957397</v>
+        <v>2.90979170799255</v>
       </c>
       <c r="H1429" t="s">
         <v>8</v>
@@ -37549,7 +37549,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1430" t="n">
-        <v>3.04450416564941</v>
+        <v>3.04450440406799</v>
       </c>
       <c r="H1430" t="s">
         <v>8</v>
@@ -37653,7 +37653,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G1434" t="n">
-        <v>2.9591863155365</v>
+        <v>2.95918607711792</v>
       </c>
       <c r="H1434" t="s">
         <v>8</v>
@@ -37679,7 +37679,7 @@
         <v>3.3050000667572</v>
       </c>
       <c r="G1435" t="n">
-        <v>2.96816682815552</v>
+        <v>2.9681670665741</v>
       </c>
       <c r="H1435" t="s">
         <v>8</v>
@@ -37705,7 +37705,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1436" t="n">
-        <v>2.93673419952393</v>
+        <v>2.93673396110535</v>
       </c>
       <c r="H1436" t="s">
         <v>8</v>
@@ -37731,7 +37731,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1437" t="n">
-        <v>2.93673419952393</v>
+        <v>2.93673396110535</v>
       </c>
       <c r="H1437" t="s">
         <v>8</v>
@@ -37783,7 +37783,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1439" t="n">
-        <v>2.93673419952393</v>
+        <v>2.93673396110535</v>
       </c>
       <c r="H1439" t="s">
         <v>8</v>
@@ -37835,7 +37835,7 @@
         <v>3.28500008583069</v>
       </c>
       <c r="G1441" t="n">
-        <v>2.95020532608032</v>
+        <v>2.9502055644989</v>
       </c>
       <c r="H1441" t="s">
         <v>8</v>
@@ -37887,7 +37887,7 @@
         <v>3.31500005722046</v>
       </c>
       <c r="G1443" t="n">
-        <v>2.97714781761169</v>
+        <v>2.97714805603027</v>
       </c>
       <c r="H1443" t="s">
         <v>8</v>
@@ -37939,7 +37939,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1445" t="n">
-        <v>2.93673419952393</v>
+        <v>2.93673396110535</v>
       </c>
       <c r="H1445" t="s">
         <v>8</v>
@@ -38043,7 +38043,7 @@
         <v>3.22499990463257</v>
       </c>
       <c r="G1449" t="n">
-        <v>2.89632034301758</v>
+        <v>2.896320104599</v>
       </c>
       <c r="H1449" t="s">
         <v>8</v>
@@ -38069,7 +38069,7 @@
         <v>3.22499990463257</v>
       </c>
       <c r="G1450" t="n">
-        <v>2.89632034301758</v>
+        <v>2.896320104599</v>
       </c>
       <c r="H1450" t="s">
         <v>8</v>
@@ -38199,7 +38199,7 @@
         <v>3.15499997138977</v>
       </c>
       <c r="G1455" t="n">
-        <v>2.83345413208008</v>
+        <v>2.83345437049866</v>
       </c>
       <c r="H1455" t="s">
         <v>8</v>
@@ -38589,7 +38589,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1470" t="n">
-        <v>2.90979146957397</v>
+        <v>2.90979170799255</v>
       </c>
       <c r="H1470" t="s">
         <v>8</v>
@@ -38745,7 +38745,7 @@
         <v>3.45499992370605</v>
       </c>
       <c r="G1476" t="n">
-        <v>3.10287976264954</v>
+        <v>3.10287952423096</v>
       </c>
       <c r="H1476" t="s">
         <v>8</v>
@@ -39057,7 +39057,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1488" t="n">
-        <v>3.21514010429382</v>
+        <v>3.21513986587524</v>
       </c>
       <c r="H1488" t="s">
         <v>8</v>
@@ -39187,7 +39187,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1493" t="n">
-        <v>3.24208235740662</v>
+        <v>3.2420825958252</v>
       </c>
       <c r="H1493" t="s">
         <v>8</v>
@@ -39213,7 +39213,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1494" t="n">
-        <v>3.20615935325623</v>
+        <v>3.20615911483765</v>
       </c>
       <c r="H1494" t="s">
         <v>8</v>
@@ -39239,7 +39239,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1495" t="n">
-        <v>3.24208235740662</v>
+        <v>3.2420825958252</v>
       </c>
       <c r="H1495" t="s">
         <v>8</v>
@@ -39395,7 +39395,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1501" t="n">
-        <v>3.08042764663696</v>
+        <v>3.08042740821838</v>
       </c>
       <c r="H1501" t="s">
         <v>8</v>
@@ -39421,7 +39421,7 @@
         <v>3.54500007629395</v>
       </c>
       <c r="G1502" t="n">
-        <v>3.18370723724365</v>
+        <v>3.18370699882507</v>
       </c>
       <c r="H1502" t="s">
         <v>8</v>
@@ -39577,7 +39577,7 @@
         <v>3.46499991416931</v>
       </c>
       <c r="G1508" t="n">
-        <v>3.11186027526855</v>
+        <v>3.11186051368713</v>
       </c>
       <c r="H1508" t="s">
         <v>8</v>
@@ -39681,7 +39681,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1512" t="n">
-        <v>3.08042764663696</v>
+        <v>3.08042740821838</v>
       </c>
       <c r="H1512" t="s">
         <v>8</v>
@@ -39785,7 +39785,7 @@
         <v>3.54500007629395</v>
       </c>
       <c r="G1516" t="n">
-        <v>3.18370723724365</v>
+        <v>3.18370699882507</v>
       </c>
       <c r="H1516" t="s">
         <v>8</v>
@@ -39863,7 +39863,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1519" t="n">
-        <v>3.30494856834412</v>
+        <v>3.30494832992554</v>
       </c>
       <c r="H1519" t="s">
         <v>8</v>
@@ -40019,7 +40019,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1525" t="n">
-        <v>3.30494856834412</v>
+        <v>3.30494832992554</v>
       </c>
       <c r="H1525" t="s">
         <v>8</v>
@@ -40071,7 +40071,7 @@
         <v>3.68499994277954</v>
       </c>
       <c r="G1527" t="n">
-        <v>3.30943846702576</v>
+        <v>3.30943870544434</v>
       </c>
       <c r="H1527" t="s">
         <v>8</v>
@@ -40305,7 +40305,7 @@
         <v>3.42499995231628</v>
       </c>
       <c r="G1536" t="n">
-        <v>3.07593703269958</v>
+        <v>3.07593727111816</v>
       </c>
       <c r="H1536" t="s">
         <v>8</v>
@@ -40383,7 +40383,7 @@
         <v>3.4449999332428</v>
       </c>
       <c r="G1539" t="n">
-        <v>3.09389877319336</v>
+        <v>3.09389853477478</v>
       </c>
       <c r="H1539" t="s">
         <v>8</v>
@@ -40409,7 +40409,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1540" t="n">
-        <v>3.07144689559937</v>
+        <v>3.07144665718079</v>
       </c>
       <c r="H1540" t="s">
         <v>8</v>
@@ -40513,7 +40513,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1544" t="n">
-        <v>3.07144689559937</v>
+        <v>3.07144665718079</v>
       </c>
       <c r="H1544" t="s">
         <v>8</v>
@@ -40539,7 +40539,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1545" t="n">
-        <v>3.07144689559937</v>
+        <v>3.07144665718079</v>
       </c>
       <c r="H1545" t="s">
         <v>8</v>
@@ -40617,7 +40617,7 @@
         <v>3.46499991416931</v>
       </c>
       <c r="G1548" t="n">
-        <v>3.11186027526855</v>
+        <v>3.11186051368713</v>
       </c>
       <c r="H1548" t="s">
         <v>8</v>
@@ -40747,7 +40747,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G1553" t="n">
-        <v>2.9591863155365</v>
+        <v>2.95918607711792</v>
       </c>
       <c r="H1553" t="s">
         <v>8</v>
@@ -40851,7 +40851,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1557" t="n">
-        <v>2.93673419952393</v>
+        <v>2.93673396110535</v>
       </c>
       <c r="H1557" t="s">
         <v>8</v>
@@ -40903,7 +40903,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1559" t="n">
-        <v>3.03552341461182</v>
+        <v>3.0355236530304</v>
       </c>
       <c r="H1559" t="s">
         <v>8</v>
@@ -41085,7 +41085,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1566" t="n">
-        <v>2.76609802246094</v>
+        <v>2.76609826087952</v>
       </c>
       <c r="H1566" t="s">
         <v>8</v>
@@ -41111,7 +41111,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G1567" t="n">
-        <v>2.72568440437317</v>
+        <v>2.72568464279175</v>
       </c>
       <c r="H1567" t="s">
         <v>8</v>
@@ -41163,7 +41163,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G1569" t="n">
-        <v>2.63138556480408</v>
+        <v>2.63138580322266</v>
       </c>
       <c r="H1569" t="s">
         <v>8</v>
@@ -41215,7 +41215,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1571" t="n">
-        <v>2.54157710075378</v>
+        <v>2.54157733917236</v>
       </c>
       <c r="H1571" t="s">
         <v>8</v>
@@ -41267,7 +41267,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1573" t="n">
-        <v>2.47871136665344</v>
+        <v>2.47871112823486</v>
       </c>
       <c r="H1573" t="s">
         <v>8</v>
@@ -41293,7 +41293,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G1574" t="n">
-        <v>2.57750058174133</v>
+        <v>2.57750034332275</v>
       </c>
       <c r="H1574" t="s">
         <v>8</v>
@@ -41319,7 +41319,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1575" t="n">
-        <v>2.55055785179138</v>
+        <v>2.55055809020996</v>
       </c>
       <c r="H1575" t="s">
         <v>8</v>
@@ -41345,7 +41345,7 @@
         <v>2.9449999332428</v>
       </c>
       <c r="G1576" t="n">
-        <v>2.64485692977905</v>
+        <v>2.64485669136047</v>
       </c>
       <c r="H1576" t="s">
         <v>8</v>
@@ -41371,7 +41371,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1577" t="n">
-        <v>2.67628979682922</v>
+        <v>2.6762900352478</v>
       </c>
       <c r="H1577" t="s">
         <v>8</v>
@@ -41423,7 +41423,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1579" t="n">
-        <v>2.81100225448608</v>
+        <v>2.81100249290466</v>
       </c>
       <c r="H1579" t="s">
         <v>8</v>
@@ -41449,7 +41449,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1580" t="n">
-        <v>2.76609802246094</v>
+        <v>2.76609826087952</v>
       </c>
       <c r="H1580" t="s">
         <v>8</v>
@@ -41501,7 +41501,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1582" t="n">
-        <v>2.78406000137329</v>
+        <v>2.78405952453613</v>
       </c>
       <c r="H1582" t="s">
         <v>8</v>
@@ -41553,7 +41553,7 @@
         <v>3.15499997138977</v>
       </c>
       <c r="G1584" t="n">
-        <v>2.83345413208008</v>
+        <v>2.83345437049866</v>
       </c>
       <c r="H1584" t="s">
         <v>8</v>
@@ -41605,7 +41605,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G1586" t="n">
-        <v>2.77058863639832</v>
+        <v>2.77058839797974</v>
       </c>
       <c r="H1586" t="s">
         <v>8</v>
@@ -41683,7 +41683,7 @@
         <v>3.14499998092651</v>
       </c>
       <c r="G1589" t="n">
-        <v>2.82447361946106</v>
+        <v>2.82447338104248</v>
       </c>
       <c r="H1589" t="s">
         <v>8</v>
@@ -41813,7 +41813,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G1594" t="n">
-        <v>2.7616081237793</v>
+        <v>2.76160764694214</v>
       </c>
       <c r="H1594" t="s">
         <v>8</v>
@@ -41891,7 +41891,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1597" t="n">
-        <v>2.81100225448608</v>
+        <v>2.81100249290466</v>
       </c>
       <c r="H1597" t="s">
         <v>8</v>
@@ -41917,7 +41917,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1598" t="n">
-        <v>2.77507877349854</v>
+        <v>2.77507901191711</v>
       </c>
       <c r="H1598" t="s">
         <v>8</v>
@@ -41943,7 +41943,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1599" t="n">
-        <v>2.78406000137329</v>
+        <v>2.78405952453613</v>
       </c>
       <c r="H1599" t="s">
         <v>8</v>
@@ -42099,7 +42099,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1605" t="n">
-        <v>3.03552341461182</v>
+        <v>3.0355236530304</v>
       </c>
       <c r="H1605" t="s">
         <v>8</v>
@@ -42385,7 +42385,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1616" t="n">
-        <v>2.71221327781677</v>
+        <v>2.71221303939819</v>
       </c>
       <c r="H1616" t="s">
         <v>8</v>
@@ -42411,7 +42411,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1617" t="n">
-        <v>2.77507877349854</v>
+        <v>2.77507901191711</v>
       </c>
       <c r="H1617" t="s">
         <v>8</v>
@@ -42437,7 +42437,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1618" t="n">
-        <v>2.84692597389221</v>
+        <v>2.84692573547363</v>
       </c>
       <c r="H1618" t="s">
         <v>8</v>
@@ -42515,7 +42515,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1621" t="n">
-        <v>2.84692597389221</v>
+        <v>2.84692573547363</v>
       </c>
       <c r="H1621" t="s">
         <v>8</v>
@@ -42671,7 +42671,7 @@
         <v>3.06500005722046</v>
       </c>
       <c r="G1627" t="n">
-        <v>2.75262689590454</v>
+        <v>2.75262713432312</v>
       </c>
       <c r="H1627" t="s">
         <v>8</v>
@@ -42697,7 +42697,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1628" t="n">
-        <v>2.77507877349854</v>
+        <v>2.77507901191711</v>
       </c>
       <c r="H1628" t="s">
         <v>8</v>
@@ -42749,7 +42749,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1630" t="n">
-        <v>2.73915576934814</v>
+        <v>2.73915553092957</v>
       </c>
       <c r="H1630" t="s">
         <v>8</v>
@@ -42801,7 +42801,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G1632" t="n">
-        <v>2.72568440437317</v>
+        <v>2.72568464279175</v>
       </c>
       <c r="H1632" t="s">
         <v>8</v>
@@ -42957,7 +42957,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1638" t="n">
-        <v>2.81100225448608</v>
+        <v>2.81100249290466</v>
       </c>
       <c r="H1638" t="s">
         <v>8</v>
@@ -42983,7 +42983,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1639" t="n">
-        <v>2.68527054786682</v>
+        <v>2.6852707862854</v>
       </c>
       <c r="H1639" t="s">
         <v>8</v>
@@ -43061,7 +43061,7 @@
         <v>2.98499989509583</v>
       </c>
       <c r="G1642" t="n">
-        <v>2.68078017234802</v>
+        <v>2.68077993392944</v>
       </c>
       <c r="H1642" t="s">
         <v>8</v>
@@ -43113,7 +43113,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1644" t="n">
-        <v>2.67628979682922</v>
+        <v>2.6762900352478</v>
       </c>
       <c r="H1644" t="s">
         <v>8</v>
@@ -43165,7 +43165,7 @@
         <v>2.98499989509583</v>
       </c>
       <c r="G1646" t="n">
-        <v>2.68078017234802</v>
+        <v>2.68077993392944</v>
       </c>
       <c r="H1646" t="s">
         <v>8</v>
@@ -43269,7 +43269,7 @@
         <v>2.78500008583069</v>
       </c>
       <c r="G1650" t="n">
-        <v>2.50116348266602</v>
+        <v>2.50116372108459</v>
       </c>
       <c r="H1650" t="s">
         <v>8</v>
@@ -43295,7 +43295,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G1651" t="n">
-        <v>2.52810573577881</v>
+        <v>2.52810597419739</v>
       </c>
       <c r="H1651" t="s">
         <v>8</v>
@@ -43399,7 +43399,7 @@
         <v>2.78500008583069</v>
       </c>
       <c r="G1655" t="n">
-        <v>2.50116348266602</v>
+        <v>2.50116372108459</v>
       </c>
       <c r="H1655" t="s">
         <v>8</v>
@@ -43477,7 +43477,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G1658" t="n">
-        <v>2.52810573577881</v>
+        <v>2.52810597419739</v>
       </c>
       <c r="H1658" t="s">
         <v>8</v>
@@ -43529,7 +43529,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G1660" t="n">
-        <v>2.57750058174133</v>
+        <v>2.57750034332275</v>
       </c>
       <c r="H1660" t="s">
         <v>8</v>
@@ -43581,7 +43581,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1662" t="n">
-        <v>2.53259658813477</v>
+        <v>2.53259634971619</v>
       </c>
       <c r="H1662" t="s">
         <v>8</v>
@@ -43607,7 +43607,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1663" t="n">
-        <v>2.53259658813477</v>
+        <v>2.53259634971619</v>
       </c>
       <c r="H1663" t="s">
         <v>8</v>
@@ -43633,7 +43633,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1664" t="n">
-        <v>2.53259658813477</v>
+        <v>2.53259634971619</v>
       </c>
       <c r="H1664" t="s">
         <v>8</v>
@@ -43659,7 +43659,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1665" t="n">
-        <v>2.55055785179138</v>
+        <v>2.55055809020996</v>
       </c>
       <c r="H1665" t="s">
         <v>8</v>
@@ -43737,7 +43737,7 @@
         <v>2.82500004768372</v>
       </c>
       <c r="G1668" t="n">
-        <v>2.53708696365356</v>
+        <v>2.53708672523499</v>
       </c>
       <c r="H1668" t="s">
         <v>8</v>
@@ -43763,7 +43763,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G1669" t="n">
-        <v>2.57750058174133</v>
+        <v>2.57750034332275</v>
       </c>
       <c r="H1669" t="s">
         <v>8</v>
@@ -43789,7 +43789,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1670" t="n">
-        <v>2.55055785179138</v>
+        <v>2.55055809020996</v>
       </c>
       <c r="H1670" t="s">
         <v>8</v>
@@ -43815,7 +43815,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1671" t="n">
-        <v>2.53259658813477</v>
+        <v>2.53259634971619</v>
       </c>
       <c r="H1671" t="s">
         <v>8</v>
@@ -43893,7 +43893,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1674" t="n">
-        <v>2.55055785179138</v>
+        <v>2.55055809020996</v>
       </c>
       <c r="H1674" t="s">
         <v>8</v>
@@ -43919,7 +43919,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G1675" t="n">
-        <v>2.54606771469116</v>
+        <v>2.54606747627258</v>
       </c>
       <c r="H1675" t="s">
         <v>8</v>
@@ -44127,7 +44127,7 @@
         <v>2.875</v>
       </c>
       <c r="G1683" t="n">
-        <v>2.58199095726013</v>
+        <v>2.58199119567871</v>
       </c>
       <c r="H1683" t="s">
         <v>8</v>
@@ -44231,7 +44231,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1687" t="n">
-        <v>2.76609802246094</v>
+        <v>2.76609826087952</v>
       </c>
       <c r="H1687" t="s">
         <v>8</v>
@@ -44257,7 +44257,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1688" t="n">
-        <v>2.78406000137329</v>
+        <v>2.78405952453613</v>
       </c>
       <c r="H1688" t="s">
         <v>8</v>
@@ -44309,7 +44309,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1690" t="n">
-        <v>2.71221327781677</v>
+        <v>2.71221303939819</v>
       </c>
       <c r="H1690" t="s">
         <v>8</v>
@@ -44465,7 +44465,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1696" t="n">
-        <v>2.68527054786682</v>
+        <v>2.6852707862854</v>
       </c>
       <c r="H1696" t="s">
         <v>8</v>
@@ -44543,7 +44543,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G1699" t="n">
-        <v>2.57750058174133</v>
+        <v>2.57750034332275</v>
       </c>
       <c r="H1699" t="s">
         <v>8</v>
@@ -44699,7 +44699,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1705" t="n">
-        <v>2.55055785179138</v>
+        <v>2.55055809020996</v>
       </c>
       <c r="H1705" t="s">
         <v>8</v>
@@ -44777,7 +44777,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1708" t="n">
-        <v>2.47871136665344</v>
+        <v>2.47871112823486</v>
       </c>
       <c r="H1708" t="s">
         <v>8</v>
@@ -44803,7 +44803,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1709" t="n">
-        <v>2.4248263835907</v>
+        <v>2.42482614517212</v>
       </c>
       <c r="H1709" t="s">
         <v>8</v>
@@ -44855,7 +44855,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1711" t="n">
-        <v>2.37094163894653</v>
+        <v>2.37094140052795</v>
       </c>
       <c r="H1711" t="s">
         <v>8</v>
@@ -44907,7 +44907,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1713" t="n">
-        <v>2.18234372138977</v>
+        <v>2.18234395980835</v>
       </c>
       <c r="H1713" t="s">
         <v>8</v>
@@ -44933,7 +44933,7 @@
         <v>2.43499994277954</v>
       </c>
       <c r="G1714" t="n">
-        <v>2.18683409690857</v>
+        <v>2.18683385848999</v>
       </c>
       <c r="H1714" t="s">
         <v>8</v>
@@ -45063,7 +45063,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1719" t="n">
-        <v>2.15528607368469</v>
+        <v>2.15528583526611</v>
       </c>
       <c r="H1719" t="s">
         <v>8</v>
@@ -45089,7 +45089,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1720" t="n">
-        <v>2.16449689865112</v>
+        <v>2.16449666023254</v>
       </c>
       <c r="H1720" t="s">
         <v>8</v>
@@ -45219,7 +45219,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G1725" t="n">
-        <v>2.07699584960938</v>
+        <v>2.07699608802795</v>
       </c>
       <c r="H1725" t="s">
         <v>8</v>
@@ -45349,7 +45349,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1730" t="n">
-        <v>2.16449689865112</v>
+        <v>2.16449666023254</v>
       </c>
       <c r="H1730" t="s">
         <v>8</v>
@@ -45427,7 +45427,7 @@
         <v>2.58500003814697</v>
       </c>
       <c r="G1733" t="n">
-        <v>2.38094663619995</v>
+        <v>2.38094639778137</v>
       </c>
       <c r="H1733" t="s">
         <v>8</v>
@@ -45453,7 +45453,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1734" t="n">
-        <v>2.37634110450745</v>
+        <v>2.37634134292603</v>
       </c>
       <c r="H1734" t="s">
         <v>8</v>
@@ -45505,7 +45505,7 @@
         <v>2.58500003814697</v>
       </c>
       <c r="G1736" t="n">
-        <v>2.38094663619995</v>
+        <v>2.38094639778137</v>
       </c>
       <c r="H1736" t="s">
         <v>8</v>
@@ -45531,7 +45531,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G1737" t="n">
-        <v>2.42239451408386</v>
+        <v>2.42239427566528</v>
       </c>
       <c r="H1737" t="s">
         <v>8</v>
@@ -45583,7 +45583,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1739" t="n">
-        <v>2.47765803337097</v>
+        <v>2.47765827178955</v>
       </c>
       <c r="H1739" t="s">
         <v>8</v>
@@ -45609,7 +45609,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G1740" t="n">
-        <v>2.40397310256958</v>
+        <v>2.403972864151</v>
       </c>
       <c r="H1740" t="s">
         <v>8</v>
@@ -45661,7 +45661,7 @@
         <v>2.56500005722046</v>
       </c>
       <c r="G1742" t="n">
-        <v>2.36252546310425</v>
+        <v>2.36252522468567</v>
       </c>
       <c r="H1742" t="s">
         <v>8</v>
@@ -45791,7 +45791,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1747" t="n">
-        <v>2.47765803337097</v>
+        <v>2.47765827178955</v>
       </c>
       <c r="H1747" t="s">
         <v>8</v>
@@ -45999,7 +45999,7 @@
         <v>2.66499996185303</v>
       </c>
       <c r="G1755" t="n">
-        <v>2.45463132858276</v>
+        <v>2.45463156700134</v>
       </c>
       <c r="H1755" t="s">
         <v>8</v>
@@ -46025,7 +46025,7 @@
         <v>2.66499996185303</v>
       </c>
       <c r="G1756" t="n">
-        <v>2.45463132858276</v>
+        <v>2.45463156700134</v>
       </c>
       <c r="H1756" t="s">
         <v>8</v>
@@ -46155,7 +46155,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1761" t="n">
-        <v>2.54213261604309</v>
+        <v>2.54213237762451</v>
       </c>
       <c r="H1761" t="s">
         <v>8</v>
@@ -46207,7 +46207,7 @@
         <v>2.75500011444092</v>
       </c>
       <c r="G1763" t="n">
-        <v>2.53752708435059</v>
+        <v>2.53752732276917</v>
       </c>
       <c r="H1763" t="s">
         <v>8</v>
@@ -46259,7 +46259,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1765" t="n">
-        <v>2.52371120452881</v>
+        <v>2.52371096611023</v>
       </c>
       <c r="H1765" t="s">
         <v>8</v>
@@ -46285,7 +46285,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1766" t="n">
-        <v>2.52371120452881</v>
+        <v>2.52371096611023</v>
       </c>
       <c r="H1766" t="s">
         <v>8</v>
@@ -46337,7 +46337,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1768" t="n">
-        <v>2.49607920646667</v>
+        <v>2.49607944488525</v>
       </c>
       <c r="H1768" t="s">
         <v>8</v>
@@ -46363,7 +46363,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1769" t="n">
-        <v>2.52371120452881</v>
+        <v>2.52371096611023</v>
       </c>
       <c r="H1769" t="s">
         <v>8</v>
@@ -46389,7 +46389,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1770" t="n">
-        <v>2.47765803337097</v>
+        <v>2.47765827178955</v>
       </c>
       <c r="H1770" t="s">
         <v>8</v>
@@ -46441,7 +46441,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1772" t="n">
-        <v>2.50529003143311</v>
+        <v>2.50529026985168</v>
       </c>
       <c r="H1772" t="s">
         <v>8</v>
@@ -46467,7 +46467,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1773" t="n">
-        <v>2.50529003143311</v>
+        <v>2.50529026985168</v>
       </c>
       <c r="H1773" t="s">
         <v>8</v>
@@ -46493,7 +46493,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1774" t="n">
-        <v>2.52371120452881</v>
+        <v>2.52371096611023</v>
       </c>
       <c r="H1774" t="s">
         <v>8</v>
@@ -46519,7 +46519,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1775" t="n">
-        <v>2.52371120452881</v>
+        <v>2.52371096611023</v>
       </c>
       <c r="H1775" t="s">
         <v>8</v>
@@ -46545,7 +46545,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1776" t="n">
-        <v>2.59739589691162</v>
+        <v>2.5973961353302</v>
       </c>
       <c r="H1776" t="s">
         <v>8</v>
@@ -46675,7 +46675,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1781" t="n">
-        <v>2.73555541038513</v>
+        <v>2.73555564880371</v>
       </c>
       <c r="H1781" t="s">
         <v>8</v>
@@ -46701,7 +46701,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1782" t="n">
-        <v>2.73555541038513</v>
+        <v>2.73555564880371</v>
       </c>
       <c r="H1782" t="s">
         <v>8</v>
@@ -46753,7 +46753,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1784" t="n">
-        <v>2.78160881996155</v>
+        <v>2.78160858154297</v>
       </c>
       <c r="H1784" t="s">
         <v>8</v>
@@ -46831,7 +46831,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1787" t="n">
-        <v>2.74476623535156</v>
+        <v>2.74476647377014</v>
       </c>
       <c r="H1787" t="s">
         <v>8</v>
@@ -47091,7 +47091,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G1797" t="n">
-        <v>2.84147787094116</v>
+        <v>2.84147763252258</v>
       </c>
       <c r="H1797" t="s">
         <v>8</v>
@@ -47169,7 +47169,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1800" t="n">
-        <v>2.78160881996155</v>
+        <v>2.78160858154297</v>
       </c>
       <c r="H1800" t="s">
         <v>8</v>
@@ -47221,7 +47221,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1802" t="n">
-        <v>2.74476623535156</v>
+        <v>2.74476647377014</v>
       </c>
       <c r="H1802" t="s">
         <v>8</v>
@@ -47247,7 +47247,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1803" t="n">
-        <v>2.73555541038513</v>
+        <v>2.73555564880371</v>
       </c>
       <c r="H1803" t="s">
         <v>8</v>
@@ -47325,7 +47325,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1806" t="n">
-        <v>2.71713423728943</v>
+        <v>2.71713447570801</v>
       </c>
       <c r="H1806" t="s">
         <v>8</v>
@@ -47351,7 +47351,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G1807" t="n">
-        <v>2.6987133026123</v>
+        <v>2.69871306419373</v>
       </c>
       <c r="H1807" t="s">
         <v>8</v>
@@ -47429,7 +47429,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1810" t="n">
-        <v>2.6618709564209</v>
+        <v>2.66187071800232</v>
       </c>
       <c r="H1810" t="s">
         <v>8</v>
@@ -47481,7 +47481,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G1812" t="n">
-        <v>2.64344930648804</v>
+        <v>2.64344906806946</v>
       </c>
       <c r="H1812" t="s">
         <v>8</v>
@@ -47507,7 +47507,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1813" t="n">
-        <v>2.62502789497375</v>
+        <v>2.62502813339233</v>
       </c>
       <c r="H1813" t="s">
         <v>8</v>
@@ -47533,7 +47533,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1814" t="n">
-        <v>2.6158173084259</v>
+        <v>2.61581754684448</v>
       </c>
       <c r="H1814" t="s">
         <v>8</v>
@@ -47585,7 +47585,7 @@
         <v>2.95499992370605</v>
       </c>
       <c r="G1816" t="n">
-        <v>2.72173953056335</v>
+        <v>2.72173929214478</v>
       </c>
       <c r="H1816" t="s">
         <v>8</v>
@@ -47663,7 +47663,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G1819" t="n">
-        <v>2.81384587287903</v>
+        <v>2.81384611129761</v>
       </c>
       <c r="H1819" t="s">
         <v>8</v>
@@ -47715,7 +47715,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1821" t="n">
-        <v>2.78160881996155</v>
+        <v>2.78160858154297</v>
       </c>
       <c r="H1821" t="s">
         <v>8</v>
@@ -48001,7 +48001,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G1832" t="n">
-        <v>2.6987133026123</v>
+        <v>2.69871306419373</v>
       </c>
       <c r="H1832" t="s">
         <v>8</v>
@@ -48079,7 +48079,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1835" t="n">
-        <v>2.6158173084259</v>
+        <v>2.61581754684448</v>
       </c>
       <c r="H1835" t="s">
         <v>8</v>
@@ -48131,7 +48131,7 @@
         <v>2.93499994277954</v>
       </c>
       <c r="G1837" t="n">
-        <v>2.70331859588623</v>
+        <v>2.70331835746765</v>
       </c>
       <c r="H1837" t="s">
         <v>8</v>
@@ -48157,7 +48157,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1838" t="n">
-        <v>2.6618709564209</v>
+        <v>2.66187071800232</v>
       </c>
       <c r="H1838" t="s">
         <v>8</v>
@@ -48183,7 +48183,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G1839" t="n">
-        <v>2.6987133026123</v>
+        <v>2.69871306419373</v>
       </c>
       <c r="H1839" t="s">
         <v>8</v>
@@ -48235,7 +48235,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1841" t="n">
-        <v>2.71713423728943</v>
+        <v>2.71713447570801</v>
       </c>
       <c r="H1841" t="s">
         <v>8</v>
@@ -48261,7 +48261,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1842" t="n">
-        <v>2.6618709564209</v>
+        <v>2.66187071800232</v>
       </c>
       <c r="H1842" t="s">
         <v>8</v>
@@ -48365,7 +48365,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1846" t="n">
-        <v>2.59739589691162</v>
+        <v>2.5973961353302</v>
       </c>
       <c r="H1846" t="s">
         <v>8</v>
@@ -48391,7 +48391,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1847" t="n">
-        <v>2.6158173084259</v>
+        <v>2.61581754684448</v>
       </c>
       <c r="H1847" t="s">
         <v>8</v>
@@ -48417,7 +48417,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1848" t="n">
-        <v>2.6158173084259</v>
+        <v>2.61581754684448</v>
       </c>
       <c r="H1848" t="s">
         <v>8</v>
@@ -48443,7 +48443,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1849" t="n">
-        <v>2.59739589691162</v>
+        <v>2.5973961353302</v>
       </c>
       <c r="H1849" t="s">
         <v>8</v>
@@ -48469,7 +48469,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1850" t="n">
-        <v>2.6158173084259</v>
+        <v>2.61581754684448</v>
       </c>
       <c r="H1850" t="s">
         <v>8</v>
@@ -48521,7 +48521,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1852" t="n">
-        <v>2.6158173084259</v>
+        <v>2.61581754684448</v>
       </c>
       <c r="H1852" t="s">
         <v>8</v>
@@ -48547,7 +48547,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1853" t="n">
-        <v>2.59739589691162</v>
+        <v>2.5973961353302</v>
       </c>
       <c r="H1853" t="s">
         <v>8</v>
@@ -48573,7 +48573,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1854" t="n">
-        <v>2.5789749622345</v>
+        <v>2.57897472381592</v>
       </c>
       <c r="H1854" t="s">
         <v>8</v>
@@ -48599,7 +48599,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1855" t="n">
-        <v>2.5789749622345</v>
+        <v>2.57897472381592</v>
       </c>
       <c r="H1855" t="s">
         <v>8</v>
@@ -48625,7 +48625,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.59739589691162</v>
+        <v>2.5973961353302</v>
       </c>
       <c r="H1856" t="s">
         <v>8</v>
@@ -48651,7 +48651,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.64344930648804</v>
+        <v>2.64344906806946</v>
       </c>
       <c r="H1857" t="s">
         <v>8</v>
@@ -48677,7 +48677,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.64344930648804</v>
+        <v>2.64344906806946</v>
       </c>
       <c r="H1858" t="s">
         <v>8</v>
@@ -48729,7 +48729,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.6158173084259</v>
+        <v>2.61581754684448</v>
       </c>
       <c r="H1860" t="s">
         <v>8</v>
@@ -48781,7 +48781,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.59739589691162</v>
+        <v>2.5973961353302</v>
       </c>
       <c r="H1862" t="s">
         <v>8</v>
@@ -48807,7 +48807,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.5789749622345</v>
+        <v>2.57897472381592</v>
       </c>
       <c r="H1863" t="s">
         <v>8</v>
@@ -48989,7 +48989,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.50529003143311</v>
+        <v>2.50529026985168</v>
       </c>
       <c r="H1870" t="s">
         <v>8</v>
@@ -49067,7 +49067,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.54213261604309</v>
+        <v>2.54213237762451</v>
       </c>
       <c r="H1873" t="s">
         <v>8</v>
@@ -49119,7 +49119,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.52371120452881</v>
+        <v>2.52371096611023</v>
       </c>
       <c r="H1875" t="s">
         <v>8</v>
@@ -49145,7 +49145,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.49607920646667</v>
+        <v>2.49607944488525</v>
       </c>
       <c r="H1876" t="s">
         <v>8</v>
@@ -49171,7 +49171,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.50529003143311</v>
+        <v>2.50529026985168</v>
       </c>
       <c r="H1877" t="s">
         <v>8</v>
@@ -49405,7 +49405,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.47765803337097</v>
+        <v>2.47765827178955</v>
       </c>
       <c r="H1886" t="s">
         <v>8</v>
@@ -49743,7 +49743,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.49607920646667</v>
+        <v>2.49607944488525</v>
       </c>
       <c r="H1899" t="s">
         <v>8</v>
@@ -49769,7 +49769,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.50529003143311</v>
+        <v>2.50529026985168</v>
       </c>
       <c r="H1900" t="s">
         <v>8</v>
@@ -49821,7 +49821,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.54213261604309</v>
+        <v>2.54213237762451</v>
       </c>
       <c r="H1902" t="s">
         <v>8</v>
@@ -49847,7 +49847,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.49607920646667</v>
+        <v>2.49607944488525</v>
       </c>
       <c r="H1903" t="s">
         <v>8</v>
@@ -49925,7 +49925,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.50529003143311</v>
+        <v>2.50529026985168</v>
       </c>
       <c r="H1906" t="s">
         <v>8</v>
@@ -50003,7 +50003,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.52371120452881</v>
+        <v>2.52371096611023</v>
       </c>
       <c r="H1909" t="s">
         <v>8</v>
@@ -71248,6 +71248,32 @@
         <v>1.12000000476837</v>
       </c>
       <c r="H2726" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2727">
+      <c r="A2727" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B2727" t="n">
+        <v>11950</v>
+      </c>
+      <c r="C2727" t="n">
+        <v>1.16499996185303</v>
+      </c>
+      <c r="D2727" t="n">
+        <v>1.12999999523163</v>
+      </c>
+      <c r="E2727" t="n">
+        <v>1.16499996185303</v>
+      </c>
+      <c r="F2727" t="n">
+        <v>1.13499999046326</v>
+      </c>
+      <c r="G2727" t="n">
+        <v>1.13499999046326</v>
+      </c>
+      <c r="H2727" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/ELC.MI.xlsx
+++ b/data/ELC.MI.xlsx
@@ -421,7 +421,7 @@
         <v>1.93700003623962</v>
       </c>
       <c r="G2" t="n">
-        <v>1.73070478439331</v>
+        <v>1.73070466518402</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G3" t="n">
-        <v>1.73338508605957</v>
+        <v>1.73338532447815</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>1.87399995326996</v>
       </c>
       <c r="G5" t="n">
-        <v>1.67441427707672</v>
+        <v>1.67441415786743</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G6" t="n">
-        <v>1.69764518737793</v>
+        <v>1.69764530658722</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G9" t="n">
-        <v>1.69764518737793</v>
+        <v>1.69764530658722</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>1.81900000572205</v>
       </c>
       <c r="G10" t="n">
-        <v>1.62527203559875</v>
+        <v>1.62527191638947</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G11" t="n">
-        <v>1.59936034679413</v>
+        <v>1.59936046600342</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>1.65199995040894</v>
       </c>
       <c r="G12" t="n">
-        <v>1.47605776786804</v>
+        <v>1.47605788707733</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>1.61099994182587</v>
       </c>
       <c r="G14" t="n">
-        <v>1.43942439556122</v>
+        <v>1.43942451477051</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>1.71800005435944</v>
       </c>
       <c r="G15" t="n">
-        <v>1.53502869606018</v>
+        <v>1.53502881526947</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>1.70700001716614</v>
       </c>
       <c r="G16" t="n">
-        <v>1.52520024776459</v>
+        <v>1.5252001285553</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G17" t="n">
-        <v>1.44746601581573</v>
+        <v>1.44746589660645</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>1.625</v>
       </c>
       <c r="G18" t="n">
-        <v>1.45193326473236</v>
+        <v>1.45193338394165</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G19" t="n">
-        <v>1.46533572673798</v>
+        <v>1.46533584594727</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>1.59099996089935</v>
       </c>
       <c r="G22" t="n">
-        <v>1.42155432701111</v>
+        <v>1.42155456542969</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G23" t="n">
-        <v>1.39832365512848</v>
+        <v>1.39832353591919</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>1.54499995708466</v>
       </c>
       <c r="G24" t="n">
-        <v>1.38045358657837</v>
+        <v>1.38045346736908</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>1.51699995994568</v>
       </c>
       <c r="G25" t="n">
-        <v>1.3554356098175</v>
+        <v>1.35543572902679</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G26" t="n">
-        <v>1.38492095470428</v>
+        <v>1.38492119312286</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G28" t="n">
-        <v>1.28216874599457</v>
+        <v>1.28216886520386</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G29" t="n">
-        <v>1.31344127655029</v>
+        <v>1.31344139575958</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G30" t="n">
-        <v>1.25983142852783</v>
+        <v>1.25983154773712</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G31" t="n">
-        <v>1.42959594726562</v>
+        <v>1.42959606647491</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>1.63199996948242</v>
       </c>
       <c r="G32" t="n">
-        <v>1.45818769931793</v>
+        <v>1.45818793773651</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>1.6710000038147</v>
       </c>
       <c r="G33" t="n">
-        <v>1.49303448200226</v>
+        <v>1.49303424358368</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>1.65900003910065</v>
       </c>
       <c r="G34" t="n">
-        <v>1.48231220245361</v>
+        <v>1.4823123216629</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G35" t="n">
-        <v>1.5100109577179</v>
+        <v>1.51001060009003</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>1.75</v>
       </c>
       <c r="G38" t="n">
-        <v>1.56362044811249</v>
+        <v>1.56362056732178</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>1.74699997901917</v>
       </c>
       <c r="G39" t="n">
-        <v>1.56094014644623</v>
+        <v>1.56094002723694</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G44" t="n">
-        <v>1.51894569396973</v>
+        <v>1.51894581317902</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>1.77300000190735</v>
       </c>
       <c r="G46" t="n">
-        <v>1.58417105674744</v>
+        <v>1.58417093753815</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>1.75</v>
       </c>
       <c r="G47" t="n">
-        <v>1.56362044811249</v>
+        <v>1.56362056732178</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>1.75</v>
       </c>
       <c r="G48" t="n">
-        <v>1.56362044811249</v>
+        <v>1.56362056732178</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>1.75</v>
       </c>
       <c r="G49" t="n">
-        <v>1.56362044811249</v>
+        <v>1.56362056732178</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>1.89300000667572</v>
       </c>
       <c r="G53" t="n">
-        <v>1.69139063358307</v>
+        <v>1.69139075279236</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>1.90900003910065</v>
       </c>
       <c r="G54" t="n">
-        <v>1.70568680763245</v>
+        <v>1.70568668842316</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G55" t="n">
-        <v>1.6797753572464</v>
+        <v>1.67977523803711</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>1.90799999237061</v>
       </c>
       <c r="G56" t="n">
-        <v>1.70479309558868</v>
+        <v>1.70479321479797</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G58" t="n">
-        <v>1.76912486553192</v>
+        <v>1.7691251039505</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>1.95200002193451</v>
       </c>
       <c r="G59" t="n">
-        <v>1.74410700798035</v>
+        <v>1.74410688877106</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>1.93599998950958</v>
       </c>
       <c r="G60" t="n">
-        <v>1.72981107234955</v>
+        <v>1.72981119155884</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>1.94599997997284</v>
       </c>
       <c r="G61" t="n">
-        <v>1.73874616622925</v>
+        <v>1.73874604701996</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>1.97599995136261</v>
       </c>
       <c r="G62" t="n">
-        <v>1.7655508518219</v>
+        <v>1.76555097103119</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G63" t="n">
-        <v>1.75125515460968</v>
+        <v>1.75125503540039</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G66" t="n">
-        <v>1.68871033191681</v>
+        <v>1.68871021270752</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>1.87899994850159</v>
       </c>
       <c r="G67" t="n">
-        <v>1.67888164520264</v>
+        <v>1.67888176441193</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G68" t="n">
-        <v>1.69317781925201</v>
+        <v>1.69317758083344</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G69" t="n">
-        <v>1.69764518737793</v>
+        <v>1.69764530658722</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G70" t="n">
-        <v>1.69764518737793</v>
+        <v>1.69764530658722</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G71" t="n">
-        <v>1.67084014415741</v>
+        <v>1.67084038257599</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G73" t="n">
-        <v>1.69764518737793</v>
+        <v>1.69764530658722</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G74" t="n">
-        <v>1.71551501750946</v>
+        <v>1.71551513671875</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G75" t="n">
-        <v>1.71998262405396</v>
+        <v>1.71998250484467</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G78" t="n">
-        <v>1.71998262405396</v>
+        <v>1.71998250484467</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G80" t="n">
-        <v>1.71998262405396</v>
+        <v>1.71998250484467</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G84" t="n">
-        <v>1.74232017993927</v>
+        <v>1.74232006072998</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>1.91600000858307</v>
       </c>
       <c r="G86" t="n">
-        <v>1.71194124221802</v>
+        <v>1.71194100379944</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G88" t="n">
-        <v>1.69764518737793</v>
+        <v>1.69764530658722</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>1.84800004959106</v>
       </c>
       <c r="G90" t="n">
-        <v>1.6511834859848</v>
+        <v>1.65118336677551</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>1.875</v>
       </c>
       <c r="G91" t="n">
-        <v>1.67530786991119</v>
+        <v>1.6753077507019</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>1.88699996471405</v>
       </c>
       <c r="G94" t="n">
-        <v>1.68602967262268</v>
+        <v>1.68602979183197</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G95" t="n">
-        <v>1.68871033191681</v>
+        <v>1.68871021270752</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G96" t="n">
-        <v>1.68871033191681</v>
+        <v>1.68871021270752</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>1.91799998283386</v>
       </c>
       <c r="G98" t="n">
-        <v>1.71372818946838</v>
+        <v>1.71372830867767</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>1.9190000295639</v>
       </c>
       <c r="G99" t="n">
-        <v>1.71462154388428</v>
+        <v>1.71462178230286</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>1.9190000295639</v>
       </c>
       <c r="G101" t="n">
-        <v>1.72342276573181</v>
+        <v>1.72342300415039</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>1.93799996376038</v>
       </c>
       <c r="G104" t="n">
-        <v>1.74048626422882</v>
+        <v>1.7404865026474</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G107" t="n">
-        <v>1.72432076931</v>
+        <v>1.72432088851929</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>1.92900002002716</v>
       </c>
       <c r="G108" t="n">
-        <v>1.7324036359787</v>
+        <v>1.73240375518799</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G109" t="n">
-        <v>1.7153400182724</v>
+        <v>1.71534013748169</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G110" t="n">
-        <v>1.72432076931</v>
+        <v>1.72432088851929</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G111" t="n">
-        <v>1.72432076931</v>
+        <v>1.72432088851929</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G112" t="n">
-        <v>1.7153400182724</v>
+        <v>1.71534013748169</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G119" t="n">
-        <v>1.60756993293762</v>
+        <v>1.60757005214691</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>1.875</v>
       </c>
       <c r="G121" t="n">
-        <v>1.68390727043152</v>
+        <v>1.68390715122223</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>1.82400000095367</v>
       </c>
       <c r="G122" t="n">
-        <v>1.6381049156189</v>
+        <v>1.63810479640961</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>1.79799997806549</v>
       </c>
       <c r="G128" t="n">
-        <v>1.61475467681885</v>
+        <v>1.61475455760956</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G130" t="n">
-        <v>1.63002228736877</v>
+        <v>1.63002216815948</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G133" t="n">
-        <v>1.46836698055267</v>
+        <v>1.46836709976196</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G136" t="n">
-        <v>1.45489585399628</v>
+        <v>1.45489573478699</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>1.66400003433228</v>
       </c>
       <c r="G138" t="n">
-        <v>1.49441158771515</v>
+        <v>1.49441146850586</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>1.67299997806549</v>
       </c>
       <c r="G139" t="n">
-        <v>1.50249421596527</v>
+        <v>1.50249409675598</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>1.6690000295639</v>
       </c>
       <c r="G140" t="n">
-        <v>1.49890196323395</v>
+        <v>1.49890184402466</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G141" t="n">
-        <v>1.49081921577454</v>
+        <v>1.49081909656525</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>1.67900002002716</v>
       </c>
       <c r="G142" t="n">
-        <v>1.50788271427155</v>
+        <v>1.50788283348083</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G143" t="n">
-        <v>1.49081921577454</v>
+        <v>1.49081909656525</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>1.66100001335144</v>
       </c>
       <c r="G145" t="n">
-        <v>1.49171721935272</v>
+        <v>1.49171733856201</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>1.66100001335144</v>
       </c>
       <c r="G146" t="n">
-        <v>1.49171721935272</v>
+        <v>1.49171733856201</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>1.67400002479553</v>
       </c>
       <c r="G148" t="n">
-        <v>1.50339233875275</v>
+        <v>1.50339221954346</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>1.65400004386902</v>
       </c>
       <c r="G149" t="n">
-        <v>1.48543059825897</v>
+        <v>1.48543071746826</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>1.67400002479553</v>
       </c>
       <c r="G152" t="n">
-        <v>1.50339233875275</v>
+        <v>1.50339221954346</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>1.69400000572205</v>
       </c>
       <c r="G153" t="n">
-        <v>1.52135407924652</v>
+        <v>1.52135396003723</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>1.69400000572205</v>
       </c>
       <c r="G154" t="n">
-        <v>1.52135407924652</v>
+        <v>1.52135396003723</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G156" t="n">
-        <v>1.50878083705902</v>
+        <v>1.50878071784973</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G159" t="n">
-        <v>1.5177618265152</v>
+        <v>1.51776158809662</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>1.66299998760223</v>
       </c>
       <c r="G162" t="n">
-        <v>1.49351322650909</v>
+        <v>1.49351334571838</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>1.69900000095367</v>
       </c>
       <c r="G165" t="n">
-        <v>1.52584445476532</v>
+        <v>1.52584433555603</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G167" t="n">
-        <v>1.64349353313446</v>
+        <v>1.64349329471588</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>1.93299996852875</v>
       </c>
       <c r="G170" t="n">
-        <v>1.73599588871002</v>
+        <v>1.73599600791931</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>1.89300000667572</v>
       </c>
       <c r="G172" t="n">
-        <v>1.70007252693176</v>
+        <v>1.70007276535034</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>1.84800004959106</v>
       </c>
       <c r="G173" t="n">
-        <v>1.65965902805328</v>
+        <v>1.6596587896347</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>1.85899996757507</v>
       </c>
       <c r="G176" t="n">
-        <v>1.66953766345978</v>
+        <v>1.66953778266907</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>1.86800003051758</v>
       </c>
       <c r="G177" t="n">
-        <v>1.67762053012848</v>
+        <v>1.67762064933777</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>1.85099995136261</v>
       </c>
       <c r="G178" t="n">
-        <v>1.66235303878784</v>
+        <v>1.66235315799713</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G181" t="n">
-        <v>1.68839764595032</v>
+        <v>1.68839752674103</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>1.80099999904633</v>
       </c>
       <c r="G187" t="n">
-        <v>1.61744904518127</v>
+        <v>1.61744892597198</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>1.80200004577637</v>
       </c>
       <c r="G192" t="n">
-        <v>1.61834704875946</v>
+        <v>1.61834692955017</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>1.80200004577637</v>
       </c>
       <c r="G193" t="n">
-        <v>1.61834704875946</v>
+        <v>1.61834692955017</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>1.83299994468689</v>
       </c>
       <c r="G196" t="n">
-        <v>1.64618754386902</v>
+        <v>1.64618766307831</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>1.89699995517731</v>
       </c>
       <c r="G197" t="n">
-        <v>1.70366489887238</v>
+        <v>1.70366501808167</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>1.875</v>
       </c>
       <c r="G198" t="n">
-        <v>1.68390727043152</v>
+        <v>1.68390715122223</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G200" t="n">
-        <v>1.68839764595032</v>
+        <v>1.68839752674103</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G203" t="n">
-        <v>1.66594552993774</v>
+        <v>1.66594541072845</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G207" t="n">
-        <v>1.64349353313446</v>
+        <v>1.64349329471588</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G211" t="n">
-        <v>1.65247416496277</v>
+        <v>1.65247428417206</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>1.86899995803833</v>
       </c>
       <c r="G212" t="n">
-        <v>1.67851865291595</v>
+        <v>1.67851877212524</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>1.86899995803833</v>
       </c>
       <c r="G213" t="n">
-        <v>1.67851865291595</v>
+        <v>1.67851877212524</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G214" t="n">
-        <v>1.65247416496277</v>
+        <v>1.65247428417206</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>1.86800003051758</v>
       </c>
       <c r="G215" t="n">
-        <v>1.67762053012848</v>
+        <v>1.67762064933777</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>1.8289999961853</v>
       </c>
       <c r="G216" t="n">
-        <v>1.6425952911377</v>
+        <v>1.64259517192841</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G218" t="n">
-        <v>1.64349353313446</v>
+        <v>1.64349329471588</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>1.80200004577637</v>
       </c>
       <c r="G221" t="n">
-        <v>1.61834704875946</v>
+        <v>1.61834692955017</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>1.84800004959106</v>
       </c>
       <c r="G223" t="n">
-        <v>1.65965902805328</v>
+        <v>1.6596587896347</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>1.74600005149841</v>
       </c>
       <c r="G224" t="n">
-        <v>1.56805443763733</v>
+        <v>1.56805431842804</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G227" t="n">
-        <v>1.49081921577454</v>
+        <v>1.49081909656525</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>1.62899994850159</v>
       </c>
       <c r="G229" t="n">
-        <v>1.4629784822464</v>
+        <v>1.46297860145569</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>1.4650000333786</v>
       </c>
       <c r="G235" t="n">
-        <v>1.31569290161133</v>
+        <v>1.31569278240204</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>1.4650000333786</v>
       </c>
       <c r="G236" t="n">
-        <v>1.31569290161133</v>
+        <v>1.31569278240204</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>1.52199995517731</v>
       </c>
       <c r="G237" t="n">
-        <v>1.36688351631165</v>
+        <v>1.36688339710236</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>1.5</v>
       </c>
       <c r="G238" t="n">
-        <v>1.3471257686615</v>
+        <v>1.34712588787079</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>1.58200001716614</v>
       </c>
       <c r="G240" t="n">
-        <v>1.42076861858368</v>
+        <v>1.42076873779297</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>1.59399998188019</v>
       </c>
       <c r="G241" t="n">
-        <v>1.43154561519623</v>
+        <v>1.43154549598694</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>1.60800004005432</v>
       </c>
       <c r="G242" t="n">
-        <v>1.44411885738373</v>
+        <v>1.44411873817444</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G243" t="n">
-        <v>1.45040547847748</v>
+        <v>1.45040535926819</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>1.65299999713898</v>
       </c>
       <c r="G245" t="n">
-        <v>1.48453271389008</v>
+        <v>1.48453259468079</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>1.67900002002716</v>
       </c>
       <c r="G246" t="n">
-        <v>1.50788271427155</v>
+        <v>1.50788283348083</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>1.70200002193451</v>
       </c>
       <c r="G248" t="n">
-        <v>1.52853870391846</v>
+        <v>1.52853858470917</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G257" t="n">
-        <v>1.66594552993774</v>
+        <v>1.66594541072845</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G258" t="n">
-        <v>1.66594552993774</v>
+        <v>1.66594541072845</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G259" t="n">
-        <v>1.66594552993774</v>
+        <v>1.66594541072845</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G262" t="n">
-        <v>1.64349353313446</v>
+        <v>1.64349329471588</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G263" t="n">
-        <v>1.65247416496277</v>
+        <v>1.65247428417206</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G267" t="n">
-        <v>1.65247416496277</v>
+        <v>1.65247428417206</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>1.80099999904633</v>
       </c>
       <c r="G270" t="n">
-        <v>1.61744904518127</v>
+        <v>1.61744892597198</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>1.70200002193451</v>
       </c>
       <c r="G275" t="n">
-        <v>1.52853870391846</v>
+        <v>1.52853858470917</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G278" t="n">
-        <v>1.50878083705902</v>
+        <v>1.50878071784973</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G279" t="n">
-        <v>1.50878083705902</v>
+        <v>1.50878071784973</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>1.72599995136261</v>
       </c>
       <c r="G281" t="n">
-        <v>1.55009257793427</v>
+        <v>1.55009245872498</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>1.51900005340576</v>
       </c>
       <c r="G288" t="n">
-        <v>1.3641893863678</v>
+        <v>1.36418926715851</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G290" t="n">
-        <v>1.38304913043976</v>
+        <v>1.38304901123047</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>1.48599994182587</v>
       </c>
       <c r="G292" t="n">
-        <v>1.33455264568329</v>
+        <v>1.33455240726471</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>1.48399996757507</v>
       </c>
       <c r="G295" t="n">
-        <v>1.33275628089905</v>
+        <v>1.33275640010834</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>1.47800004482269</v>
       </c>
       <c r="G297" t="n">
-        <v>1.32736790180206</v>
+        <v>1.32736802101135</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G298" t="n">
-        <v>1.3381450176239</v>
+        <v>1.33814489841461</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>1.55299997329712</v>
       </c>
       <c r="G299" t="n">
-        <v>1.39472413063049</v>
+        <v>1.39472424983978</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>1.58599996566772</v>
       </c>
       <c r="G302" t="n">
-        <v>1.424360871315</v>
+        <v>1.42436099052429</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>1.58200001716614</v>
       </c>
       <c r="G305" t="n">
-        <v>1.42076861858368</v>
+        <v>1.42076873779297</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G308" t="n">
-        <v>1.39202976226807</v>
+        <v>1.39203000068665</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G309" t="n">
-        <v>1.37406814098358</v>
+        <v>1.37406826019287</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>1.53900003433228</v>
       </c>
       <c r="G310" t="n">
-        <v>1.38215100765228</v>
+        <v>1.38215112686157</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>1.54499995708466</v>
       </c>
       <c r="G312" t="n">
-        <v>1.38753950595856</v>
+        <v>1.38753938674927</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G313" t="n">
-        <v>1.38304913043976</v>
+        <v>1.38304901123047</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G315" t="n">
-        <v>1.39202976226807</v>
+        <v>1.39203000068665</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G317" t="n">
-        <v>1.41897237300873</v>
+        <v>1.41897249221802</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G318" t="n">
-        <v>1.46387672424316</v>
+        <v>1.46387660503387</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>1.62600004673004</v>
       </c>
       <c r="G320" t="n">
-        <v>1.46028435230255</v>
+        <v>1.46028423309326</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>1.62899994850159</v>
       </c>
       <c r="G322" t="n">
-        <v>1.4629784822464</v>
+        <v>1.46297860145569</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G323" t="n">
-        <v>1.46387672424316</v>
+        <v>1.46387660503387</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>1.65299999713898</v>
       </c>
       <c r="G325" t="n">
-        <v>1.48453271389008</v>
+        <v>1.48453259468079</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>1.65199995040894</v>
       </c>
       <c r="G326" t="n">
-        <v>1.48363435268402</v>
+        <v>1.48363447189331</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>1.63399994373322</v>
       </c>
       <c r="G327" t="n">
-        <v>1.46746897697449</v>
+        <v>1.4674688577652</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>1.62399995326996</v>
       </c>
       <c r="G328" t="n">
-        <v>1.4584881067276</v>
+        <v>1.45848798751831</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>1.62199997901917</v>
       </c>
       <c r="G329" t="n">
-        <v>1.45669198036194</v>
+        <v>1.45669186115265</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>1.625</v>
       </c>
       <c r="G330" t="n">
-        <v>1.45938611030579</v>
+        <v>1.45938622951508</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>1.63399994373322</v>
       </c>
       <c r="G336" t="n">
-        <v>1.46746897697449</v>
+        <v>1.4674688577652</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G337" t="n">
-        <v>1.49081921577454</v>
+        <v>1.49081909656525</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G338" t="n">
-        <v>1.49081921577454</v>
+        <v>1.49081909656525</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G339" t="n">
-        <v>1.49081921577454</v>
+        <v>1.49081909656525</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G340" t="n">
-        <v>1.49081921577454</v>
+        <v>1.49081909656525</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>1.67900002002716</v>
       </c>
       <c r="G343" t="n">
-        <v>1.50788271427155</v>
+        <v>1.50788283348083</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G344" t="n">
-        <v>1.522252202034</v>
+        <v>1.52225208282471</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>1.67900002002716</v>
       </c>
       <c r="G345" t="n">
-        <v>1.50788271427155</v>
+        <v>1.50788283348083</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G348" t="n">
-        <v>1.5177618265152</v>
+        <v>1.51776158809662</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G350" t="n">
-        <v>1.67941665649414</v>
+        <v>1.67941677570343</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>1.89199995994568</v>
       </c>
       <c r="G351" t="n">
-        <v>1.69917452335358</v>
+        <v>1.69917464256287</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>1.85399997234344</v>
       </c>
       <c r="G352" t="n">
-        <v>1.66504728794098</v>
+        <v>1.66504740715027</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>1.80099999904633</v>
       </c>
       <c r="G353" t="n">
-        <v>1.61744904518127</v>
+        <v>1.61744892597198</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>1.78699994087219</v>
       </c>
       <c r="G354" t="n">
-        <v>1.60487580299377</v>
+        <v>1.60487568378448</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G355" t="n">
-        <v>1.65247416496277</v>
+        <v>1.65247428417206</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G356" t="n">
-        <v>1.71084952354431</v>
+        <v>1.7108496427536</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G357" t="n">
-        <v>1.74228262901306</v>
+        <v>1.74228274822235</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G359" t="n">
-        <v>1.72432076931</v>
+        <v>1.72432088851929</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G360" t="n">
-        <v>1.72432076931</v>
+        <v>1.72432088851929</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>1.875</v>
       </c>
       <c r="G361" t="n">
-        <v>1.68390727043152</v>
+        <v>1.68390715122223</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>1.8860000371933</v>
       </c>
       <c r="G362" t="n">
-        <v>1.6937860250473</v>
+        <v>1.69378626346588</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G364" t="n">
-        <v>1.7153400182724</v>
+        <v>1.71534013748169</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>1.85899996757507</v>
       </c>
       <c r="G366" t="n">
-        <v>1.66953766345978</v>
+        <v>1.66953778266907</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>1.82200002670288</v>
       </c>
       <c r="G367" t="n">
-        <v>1.63630878925323</v>
+        <v>1.63630867004395</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G372" t="n">
-        <v>1.65247416496277</v>
+        <v>1.65247428417206</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>1.82200002670288</v>
       </c>
       <c r="G374" t="n">
-        <v>1.63630878925323</v>
+        <v>1.63630867004395</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>1.83899998664856</v>
       </c>
       <c r="G375" t="n">
-        <v>1.65157616138458</v>
+        <v>1.65157604217529</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>1.84200000762939</v>
       </c>
       <c r="G376" t="n">
-        <v>1.65427041053772</v>
+        <v>1.65427029132843</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G377" t="n">
-        <v>1.64349353313446</v>
+        <v>1.64349329471588</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>1.81200003623962</v>
       </c>
       <c r="G378" t="n">
-        <v>1.62732791900635</v>
+        <v>1.62732779979706</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>1.7610000371933</v>
       </c>
       <c r="G381" t="n">
-        <v>1.58152556419373</v>
+        <v>1.58152568340302</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>1.70299994945526</v>
       </c>
       <c r="G383" t="n">
-        <v>1.52943670749664</v>
+        <v>1.52943658828735</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>1.74800002574921</v>
       </c>
       <c r="G384" t="n">
-        <v>1.56985056400299</v>
+        <v>1.5698504447937</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>1.72099995613098</v>
       </c>
       <c r="G385" t="n">
-        <v>1.54560232162476</v>
+        <v>1.54560220241547</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>1.72099995613098</v>
       </c>
       <c r="G386" t="n">
-        <v>1.54560232162476</v>
+        <v>1.54560220241547</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>1.71700000762939</v>
       </c>
       <c r="G387" t="n">
-        <v>1.54200994968414</v>
+        <v>1.54200983047485</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G391" t="n">
-        <v>1.55368506908417</v>
+        <v>1.55368494987488</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G394" t="n">
-        <v>1.60756993293762</v>
+        <v>1.60757005214691</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>1.7610000371933</v>
       </c>
       <c r="G399" t="n">
-        <v>1.58152556419373</v>
+        <v>1.58152568340302</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>1.78400003910065</v>
       </c>
       <c r="G401" t="n">
-        <v>1.60218143463135</v>
+        <v>1.60218155384064</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>1.75300002098083</v>
       </c>
       <c r="G402" t="n">
-        <v>1.57434093952179</v>
+        <v>1.5743408203125</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>1.77799999713898</v>
       </c>
       <c r="G403" t="n">
-        <v>1.59679305553436</v>
+        <v>1.59679293632507</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>1.78900003433228</v>
       </c>
       <c r="G405" t="n">
-        <v>1.60667204856873</v>
+        <v>1.60667192935944</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G406" t="n">
-        <v>1.60756993293762</v>
+        <v>1.60757005214691</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>1.78400003910065</v>
       </c>
       <c r="G408" t="n">
-        <v>1.60218143463135</v>
+        <v>1.60218155384064</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>1.80099999904633</v>
       </c>
       <c r="G412" t="n">
-        <v>1.61744904518127</v>
+        <v>1.61744892597198</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>1.79799997806549</v>
       </c>
       <c r="G413" t="n">
-        <v>1.61475467681885</v>
+        <v>1.61475455760956</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>1.75399994850159</v>
       </c>
       <c r="G415" t="n">
-        <v>1.57523906230927</v>
+        <v>1.57523894309998</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>1.73699998855591</v>
       </c>
       <c r="G418" t="n">
-        <v>1.55997169017792</v>
+        <v>1.55997157096863</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>1.73099994659424</v>
       </c>
       <c r="G419" t="n">
-        <v>1.55458295345306</v>
+        <v>1.55458307266235</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G422" t="n">
-        <v>1.60756993293762</v>
+        <v>1.60757005214691</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>1.8309999704361</v>
       </c>
       <c r="G423" t="n">
-        <v>1.64439141750336</v>
+        <v>1.64439129829407</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G425" t="n">
-        <v>1.72432076931</v>
+        <v>1.72432088851929</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>1.87899994850159</v>
       </c>
       <c r="G427" t="n">
-        <v>1.68749940395355</v>
+        <v>1.68749952316284</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>1.88199996948242</v>
       </c>
       <c r="G428" t="n">
-        <v>1.69019365310669</v>
+        <v>1.69019377231598</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>1.85300004482269</v>
       </c>
       <c r="G429" t="n">
-        <v>1.66414940357208</v>
+        <v>1.66414928436279</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>1.89600002765656</v>
       </c>
       <c r="G432" t="n">
-        <v>1.70276689529419</v>
+        <v>1.70276701450348</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G434" t="n">
-        <v>1.88597583770752</v>
+        <v>1.88597595691681</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G437" t="n">
-        <v>2.02966928482056</v>
+        <v>2.02966952323914</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>2.53800010681152</v>
       </c>
       <c r="G442" t="n">
-        <v>2.27933669090271</v>
+        <v>2.27933692932129</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>2.57599997520447</v>
       </c>
       <c r="G443" t="n">
-        <v>2.31346392631531</v>
+        <v>2.31346368789673</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>2.61800003051758</v>
       </c>
       <c r="G446" t="n">
-        <v>2.35118365287781</v>
+        <v>2.35118341445923</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>2.61800003051758</v>
       </c>
       <c r="G447" t="n">
-        <v>2.35118365287781</v>
+        <v>2.35118341445923</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>2.61400008201599</v>
       </c>
       <c r="G450" t="n">
-        <v>2.34759116172791</v>
+        <v>2.34759092330933</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G454" t="n">
-        <v>2.26317119598389</v>
+        <v>2.26317095756531</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G455" t="n">
-        <v>2.20030546188354</v>
+        <v>2.20030522346497</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>2.43600010871887</v>
       </c>
       <c r="G456" t="n">
-        <v>2.18773245811462</v>
+        <v>2.18773221969604</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>2.50600004196167</v>
       </c>
       <c r="G458" t="n">
-        <v>2.25059819221497</v>
+        <v>2.25059795379639</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>2.83800005912781</v>
       </c>
       <c r="G462" t="n">
-        <v>2.54876208305359</v>
+        <v>2.54876184463501</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>2.86199998855591</v>
       </c>
       <c r="G463" t="n">
-        <v>2.57031583786011</v>
+        <v>2.57031607627869</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>2.75</v>
       </c>
       <c r="G467" t="n">
-        <v>2.46973037719727</v>
+        <v>2.46973061561584</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G468" t="n">
-        <v>2.50565361976624</v>
+        <v>2.50565385818481</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G472" t="n">
-        <v>2.55055809020996</v>
+        <v>2.55055785179138</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>2.89800000190735</v>
       </c>
       <c r="G475" t="n">
-        <v>2.60264682769775</v>
+        <v>2.60264706611633</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>2.82200002670288</v>
       </c>
       <c r="G476" t="n">
-        <v>2.53439283370972</v>
+        <v>2.53439259529114</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>2.54399991035461</v>
       </c>
       <c r="G489" t="n">
-        <v>2.28472542762756</v>
+        <v>2.28472518920898</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>2.62199997901917</v>
       </c>
       <c r="G490" t="n">
-        <v>2.35477566719055</v>
+        <v>2.35477542877197</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>2.55800008773804</v>
       </c>
       <c r="G491" t="n">
-        <v>2.29729866981506</v>
+        <v>2.29729843139648</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>2.51399993896484</v>
       </c>
       <c r="G492" t="n">
-        <v>2.25778269767761</v>
+        <v>2.25778245925903</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G494" t="n">
-        <v>2.20928645133972</v>
+        <v>2.20928621292114</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G497" t="n">
-        <v>2.20928645133972</v>
+        <v>2.20928621292114</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>2.51399993896484</v>
       </c>
       <c r="G498" t="n">
-        <v>2.25778269767761</v>
+        <v>2.25778245925903</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>2.47399997711182</v>
       </c>
       <c r="G503" t="n">
-        <v>2.22185945510864</v>
+        <v>2.22185921669006</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>2.5220000743866</v>
       </c>
       <c r="G506" t="n">
-        <v>2.26496744155884</v>
+        <v>2.26496720314026</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>2.45199990272522</v>
       </c>
       <c r="G508" t="n">
-        <v>2.20210123062134</v>
+        <v>2.20210146903992</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>2.43799996376038</v>
       </c>
       <c r="G509" t="n">
-        <v>2.18952822685242</v>
+        <v>2.189528465271</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>2.42199993133545</v>
       </c>
       <c r="G511" t="n">
-        <v>2.17515921592712</v>
+        <v>2.17515873908997</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G513" t="n">
-        <v>2.18234395980835</v>
+        <v>2.18234348297119</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>2.43499994277954</v>
       </c>
       <c r="G519" t="n">
-        <v>2.18683385848999</v>
+        <v>2.18683409690857</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>2.42499995231628</v>
       </c>
       <c r="G522" t="n">
-        <v>2.17785310745239</v>
+        <v>2.17785334587097</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G523" t="n">
-        <v>2.12845849990845</v>
+        <v>2.12845826148987</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G526" t="n">
-        <v>2.06559300422668</v>
+        <v>2.06559276580811</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G527" t="n">
-        <v>2.09253549575806</v>
+        <v>2.0925350189209</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G530" t="n">
-        <v>2.10151600837708</v>
+        <v>2.10151624679565</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>2.41499996185303</v>
       </c>
       <c r="G531" t="n">
-        <v>2.16887235641479</v>
+        <v>2.16887259483337</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G532" t="n">
-        <v>2.12845849990845</v>
+        <v>2.12845826148987</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G534" t="n">
-        <v>2.1374397277832</v>
+        <v>2.13743948936462</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>2.27500009536743</v>
       </c>
       <c r="G537" t="n">
-        <v>2.04314041137695</v>
+        <v>2.04314088821411</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G539" t="n">
-        <v>2.06559300422668</v>
+        <v>2.06559276580811</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>2.36500000953674</v>
       </c>
       <c r="G541" t="n">
-        <v>2.12396812438965</v>
+        <v>2.12396836280823</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>2.34500002861023</v>
       </c>
       <c r="G543" t="n">
-        <v>2.10600662231445</v>
+        <v>2.10600638389587</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G544" t="n">
-        <v>2.06559300422668</v>
+        <v>2.06559276580811</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G545" t="n">
-        <v>2.06559300422668</v>
+        <v>2.06559276580811</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G546" t="n">
-        <v>2.10151600837708</v>
+        <v>2.10151624679565</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G547" t="n">
-        <v>2.06559300422668</v>
+        <v>2.06559276580811</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>2.21499991416931</v>
       </c>
       <c r="G552" t="n">
-        <v>1.98925542831421</v>
+        <v>1.98925578594208</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>2.14499998092651</v>
       </c>
       <c r="G553" t="n">
-        <v>1.92638969421387</v>
+        <v>1.92638957500458</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G555" t="n">
-        <v>1.90393769741058</v>
+        <v>1.903937458992</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G556" t="n">
-        <v>1.85005271434784</v>
+        <v>1.85005259513855</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G557" t="n">
-        <v>1.91291868686676</v>
+        <v>1.91291880607605</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G558" t="n">
-        <v>1.92189931869507</v>
+        <v>1.92189943790436</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G559" t="n">
-        <v>1.94884192943573</v>
+        <v>1.94884181022644</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>2.27500009536743</v>
       </c>
       <c r="G565" t="n">
-        <v>2.04314041137695</v>
+        <v>2.04314088821411</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G566" t="n">
-        <v>1.99374616146088</v>
+        <v>1.99374604225159</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G570" t="n">
-        <v>1.94884192943573</v>
+        <v>1.94884181022644</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>2.15499997138977</v>
       </c>
       <c r="G571" t="n">
-        <v>1.93537044525146</v>
+        <v>1.93537068367004</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G572" t="n">
-        <v>1.91291868686676</v>
+        <v>1.91291880607605</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>2.15499997138977</v>
       </c>
       <c r="G573" t="n">
-        <v>1.93537044525146</v>
+        <v>1.93537068367004</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G583" t="n">
-        <v>2.03865027427673</v>
+        <v>2.03865003585815</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>2.24499988555908</v>
       </c>
       <c r="G584" t="n">
-        <v>2.01619815826416</v>
+        <v>2.01619791984558</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G590" t="n">
-        <v>2.06559300422668</v>
+        <v>2.06559276580811</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>2.47499990463257</v>
       </c>
       <c r="G602" t="n">
-        <v>2.22275757789612</v>
+        <v>2.22275733947754</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G604" t="n">
-        <v>2.20030546188354</v>
+        <v>2.20030522346497</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>2.24499988555908</v>
       </c>
       <c r="G610" t="n">
-        <v>2.01619815826416</v>
+        <v>2.01619791984558</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>2.27500009536743</v>
       </c>
       <c r="G612" t="n">
-        <v>2.04314041137695</v>
+        <v>2.04314088821411</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>2.22499990463257</v>
       </c>
       <c r="G613" t="n">
-        <v>1.99823653697968</v>
+        <v>1.9982362985611</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>2.15499997138977</v>
       </c>
       <c r="G615" t="n">
-        <v>1.93537044525146</v>
+        <v>1.93537068367004</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G616" t="n">
-        <v>2.02966928482056</v>
+        <v>2.02966952323914</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G619" t="n">
-        <v>2.06559300422668</v>
+        <v>2.06559276580811</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G620" t="n">
-        <v>2.02966928482056</v>
+        <v>2.02966952323914</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G624" t="n">
-        <v>2.02966928482056</v>
+        <v>2.02966952323914</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G628" t="n">
-        <v>2.06559300422668</v>
+        <v>2.06559276580811</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G631" t="n">
-        <v>1.99374616146088</v>
+        <v>1.99374604225159</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G636" t="n">
-        <v>1.95782291889191</v>
+        <v>1.95782279968262</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>2.24499988555908</v>
       </c>
       <c r="G638" t="n">
-        <v>2.01619815826416</v>
+        <v>2.01619791984558</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G639" t="n">
-        <v>1.99374616146088</v>
+        <v>1.99374604225159</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>2.22499990463257</v>
       </c>
       <c r="G640" t="n">
-        <v>1.99823653697968</v>
+        <v>1.9982362985611</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G641" t="n">
-        <v>1.99374616146088</v>
+        <v>1.99374604225159</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G643" t="n">
-        <v>1.99374616146088</v>
+        <v>1.99374604225159</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G644" t="n">
-        <v>1.9668036699295</v>
+        <v>1.96680355072021</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G645" t="n">
-        <v>1.95782291889191</v>
+        <v>1.95782279968262</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G646" t="n">
-        <v>1.9668036699295</v>
+        <v>1.96680355072021</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>2.1949999332428</v>
       </c>
       <c r="G647" t="n">
-        <v>1.97129392623901</v>
+        <v>1.97129380702972</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G648" t="n">
-        <v>1.9668036699295</v>
+        <v>1.96680355072021</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G649" t="n">
-        <v>1.95782291889191</v>
+        <v>1.95782279968262</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>2.20499992370605</v>
       </c>
       <c r="G651" t="n">
-        <v>1.98027467727661</v>
+        <v>1.9802747964859</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>2.13499999046326</v>
       </c>
       <c r="G652" t="n">
-        <v>1.91740882396698</v>
+        <v>1.91740894317627</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G653" t="n">
-        <v>1.95782291889191</v>
+        <v>1.95782279968262</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>2.15499997138977</v>
       </c>
       <c r="G654" t="n">
-        <v>1.93537044525146</v>
+        <v>1.93537068367004</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G655" t="n">
-        <v>1.94884192943573</v>
+        <v>1.94884181022644</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G656" t="n">
-        <v>1.89495658874512</v>
+        <v>1.8949568271637</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G657" t="n">
-        <v>1.92189931869507</v>
+        <v>1.92189943790436</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G658" t="n">
-        <v>1.89495658874512</v>
+        <v>1.8949568271637</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G659" t="n">
-        <v>1.93088042736053</v>
+        <v>1.93088030815125</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G660" t="n">
-        <v>1.92189931869507</v>
+        <v>1.92189943790436</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G661" t="n">
-        <v>1.90393769741058</v>
+        <v>1.903937458992</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G662" t="n">
-        <v>1.90393769741058</v>
+        <v>1.903937458992</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>2.125</v>
       </c>
       <c r="G663" t="n">
-        <v>1.90842819213867</v>
+        <v>1.90842807292938</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G664" t="n">
-        <v>1.93088042736053</v>
+        <v>1.93088030815125</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G665" t="n">
-        <v>1.93088042736053</v>
+        <v>1.93088030815125</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>2.14499998092651</v>
       </c>
       <c r="G666" t="n">
-        <v>1.92638969421387</v>
+        <v>1.92638957500458</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G667" t="n">
-        <v>1.90393769741058</v>
+        <v>1.903937458992</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>2.14499998092651</v>
       </c>
       <c r="G669" t="n">
-        <v>1.92638969421387</v>
+        <v>1.92638957500458</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G670" t="n">
-        <v>1.93088042736053</v>
+        <v>1.93088030815125</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G671" t="n">
-        <v>1.93088042736053</v>
+        <v>1.93088030815125</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G672" t="n">
-        <v>1.95782291889191</v>
+        <v>1.95782279968262</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G674" t="n">
-        <v>1.9668036699295</v>
+        <v>1.96680355072021</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G677" t="n">
-        <v>2.03865027427673</v>
+        <v>2.03865003585815</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G678" t="n">
-        <v>2.03865027427673</v>
+        <v>2.03865003585815</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G679" t="n">
-        <v>2.06559300422668</v>
+        <v>2.06559276580811</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G681" t="n">
-        <v>1.99374616146088</v>
+        <v>1.99374604225159</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G682" t="n">
-        <v>1.94884192943573</v>
+        <v>1.94884181022644</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G684" t="n">
-        <v>1.9668036699295</v>
+        <v>1.96680355072021</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>2.21499991416931</v>
       </c>
       <c r="G685" t="n">
-        <v>1.98925542831421</v>
+        <v>1.98925578594208</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>2.27500009536743</v>
       </c>
       <c r="G689" t="n">
-        <v>2.04314041137695</v>
+        <v>2.04314088821411</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G691" t="n">
-        <v>2.03865027427673</v>
+        <v>2.03865003585815</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>2.27500009536743</v>
       </c>
       <c r="G697" t="n">
-        <v>2.04314041137695</v>
+        <v>2.04314088821411</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>2.27500009536743</v>
       </c>
       <c r="G699" t="n">
-        <v>2.04314041137695</v>
+        <v>2.04314088821411</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G700" t="n">
-        <v>2.02966928482056</v>
+        <v>2.02966952323914</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G703" t="n">
-        <v>2.03865027427673</v>
+        <v>2.03865003585815</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G707" t="n">
-        <v>1.91291868686676</v>
+        <v>1.91291880607605</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G708" t="n">
-        <v>1.92189931869507</v>
+        <v>1.92189943790436</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G709" t="n">
-        <v>1.85005271434784</v>
+        <v>1.85005259513855</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G710" t="n">
-        <v>1.77820587158203</v>
+        <v>1.77820599079132</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G711" t="n">
-        <v>1.82311022281647</v>
+        <v>1.82311010360718</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G712" t="n">
-        <v>1.85903334617615</v>
+        <v>1.85903346538544</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G713" t="n">
-        <v>1.92189931869507</v>
+        <v>1.92189943790436</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G715" t="n">
-        <v>1.80514848232269</v>
+        <v>1.8051483631134</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>1.92599999904633</v>
       </c>
       <c r="G720" t="n">
-        <v>1.72970938682556</v>
+        <v>1.72970950603485</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G721" t="n">
-        <v>1.65247416496277</v>
+        <v>1.65247428417206</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G722" t="n">
-        <v>1.65247416496277</v>
+        <v>1.65247428417206</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G726" t="n">
-        <v>1.67941665649414</v>
+        <v>1.67941677570343</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>1.81599998474121</v>
       </c>
       <c r="G727" t="n">
-        <v>1.63092029094696</v>
+        <v>1.63092017173767</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>1.83399999141693</v>
       </c>
       <c r="G728" t="n">
-        <v>1.64708578586578</v>
+        <v>1.64708566665649</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>1.81599998474121</v>
       </c>
       <c r="G730" t="n">
-        <v>1.63092029094696</v>
+        <v>1.63092017173767</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>1.76199996471405</v>
       </c>
       <c r="G733" t="n">
-        <v>1.5824236869812</v>
+        <v>1.58242356777191</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>1.75</v>
       </c>
       <c r="G734" t="n">
-        <v>1.57164657115936</v>
+        <v>1.57164669036865</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>1.72599995136261</v>
       </c>
       <c r="G735" t="n">
-        <v>1.55009257793427</v>
+        <v>1.55009245872498</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>1.65400004386902</v>
       </c>
       <c r="G736" t="n">
-        <v>1.48543059825897</v>
+        <v>1.48543071746826</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>1.65199995040894</v>
       </c>
       <c r="G737" t="n">
-        <v>1.48363435268402</v>
+        <v>1.48363447189331</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G738" t="n">
-        <v>1.41897237300873</v>
+        <v>1.41897249221802</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>1.55599999427795</v>
       </c>
       <c r="G741" t="n">
-        <v>1.39741837978363</v>
+        <v>1.39741849899292</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>1.57400000095367</v>
       </c>
       <c r="G742" t="n">
-        <v>1.41358399391174</v>
+        <v>1.41358387470245</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>1.48399996757507</v>
       </c>
       <c r="G745" t="n">
-        <v>1.33275628089905</v>
+        <v>1.33275640010834</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>1.49600005149841</v>
       </c>
       <c r="G746" t="n">
-        <v>1.3435332775116</v>
+        <v>1.34353339672089</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G747" t="n">
-        <v>1.39202976226807</v>
+        <v>1.39203000068665</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G752" t="n">
-        <v>1.30222153663635</v>
+        <v>1.30222165584564</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G756" t="n">
-        <v>1.23935556411743</v>
+        <v>1.23935568332672</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G757" t="n">
-        <v>1.21241307258606</v>
+        <v>1.21241319179535</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G761" t="n">
-        <v>1.1675089597702</v>
+        <v>1.16750884056091</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>1.30400002002716</v>
       </c>
       <c r="G763" t="n">
-        <v>1.17110133171082</v>
+        <v>1.17110121250153</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>1.41400003433228</v>
       </c>
       <c r="G765" t="n">
-        <v>1.26989042758942</v>
+        <v>1.26989054679871</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G770" t="n">
-        <v>1.3561065196991</v>
+        <v>1.35610663890839</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>1.51800000667572</v>
       </c>
       <c r="G771" t="n">
-        <v>1.36329126358032</v>
+        <v>1.36329114437103</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>1.47800004482269</v>
       </c>
       <c r="G773" t="n">
-        <v>1.32736790180206</v>
+        <v>1.32736802101135</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G774" t="n">
-        <v>1.3381450176239</v>
+        <v>1.33814489841461</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>1.49600005149841</v>
       </c>
       <c r="G775" t="n">
-        <v>1.3435332775116</v>
+        <v>1.34353339672089</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>1.5</v>
       </c>
       <c r="G776" t="n">
-        <v>1.3471257686615</v>
+        <v>1.34712588787079</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>1.48399996757507</v>
       </c>
       <c r="G777" t="n">
-        <v>1.33275628089905</v>
+        <v>1.33275640010834</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>1.47599995136261</v>
       </c>
       <c r="G778" t="n">
-        <v>1.3255717754364</v>
+        <v>1.32557165622711</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>1.47200000286102</v>
       </c>
       <c r="G780" t="n">
-        <v>1.32197952270508</v>
+        <v>1.3219792842865</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>1.49600005149841</v>
       </c>
       <c r="G781" t="n">
-        <v>1.3435332775116</v>
+        <v>1.34353339672089</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>1.47599995136261</v>
       </c>
       <c r="G784" t="n">
-        <v>1.3255717754364</v>
+        <v>1.32557165622711</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>1.42799997329712</v>
       </c>
       <c r="G788" t="n">
-        <v>1.28246366977692</v>
+        <v>1.28246378898621</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>1.40199995040894</v>
       </c>
       <c r="G789" t="n">
-        <v>1.25911343097687</v>
+        <v>1.25911355018616</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>1.41799998283386</v>
       </c>
       <c r="G793" t="n">
-        <v>1.27348291873932</v>
+        <v>1.27348279953003</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G794" t="n">
-        <v>1.45309948921204</v>
+        <v>1.45309960842133</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G795" t="n">
-        <v>1.45489585399628</v>
+        <v>1.45489573478699</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>1.89800000190735</v>
       </c>
       <c r="G797" t="n">
-        <v>1.70456314086914</v>
+        <v>1.70456302165985</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G798" t="n">
-        <v>1.65247416496277</v>
+        <v>1.65247428417206</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>1.78199994564056</v>
       </c>
       <c r="G799" t="n">
-        <v>1.60038542747498</v>
+        <v>1.60038530826569</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G800" t="n">
-        <v>1.65247416496277</v>
+        <v>1.65247428417206</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G801" t="n">
-        <v>1.84107184410095</v>
+        <v>1.84107172489166</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G803" t="n">
-        <v>1.88597583770752</v>
+        <v>1.88597595691681</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G804" t="n">
-        <v>1.85005271434784</v>
+        <v>1.85005259513855</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G805" t="n">
-        <v>1.82311022281647</v>
+        <v>1.82311010360718</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>2.14499998092651</v>
       </c>
       <c r="G806" t="n">
-        <v>1.92638969421387</v>
+        <v>1.92638957500458</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G807" t="n">
-        <v>1.85903334617615</v>
+        <v>1.85903346538544</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G809" t="n">
-        <v>1.85005271434784</v>
+        <v>1.85005259513855</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>1.98199999332428</v>
       </c>
       <c r="G810" t="n">
-        <v>1.78000223636627</v>
+        <v>1.78000211715698</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G814" t="n">
-        <v>1.80514848232269</v>
+        <v>1.8051483631134</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>1.98599994182587</v>
       </c>
       <c r="G815" t="n">
-        <v>1.78359436988831</v>
+        <v>1.7835944890976</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G818" t="n">
-        <v>1.68839764595032</v>
+        <v>1.68839752674103</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>2.21499991416931</v>
       </c>
       <c r="G827" t="n">
-        <v>1.98925542831421</v>
+        <v>1.98925578594208</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G828" t="n">
-        <v>1.99374616146088</v>
+        <v>1.99374604225159</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G829" t="n">
-        <v>2.06559300422668</v>
+        <v>2.06559276580811</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>2.31500005722046</v>
       </c>
       <c r="G830" t="n">
-        <v>2.07906413078308</v>
+        <v>2.07906436920166</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>2.34500002861023</v>
       </c>
       <c r="G831" t="n">
-        <v>2.10600662231445</v>
+        <v>2.10600638389587</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>2.14499998092651</v>
       </c>
       <c r="G833" t="n">
-        <v>1.92638969421387</v>
+        <v>1.92638957500458</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G834" t="n">
-        <v>1.99374616146088</v>
+        <v>1.99374604225159</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G837" t="n">
-        <v>1.99374616146088</v>
+        <v>1.99374604225159</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G838" t="n">
-        <v>2.1374397277832</v>
+        <v>2.13743948936462</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>2.38499999046326</v>
       </c>
       <c r="G839" t="n">
-        <v>2.141930103302</v>
+        <v>2.14192986488342</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>2.42499995231628</v>
       </c>
       <c r="G841" t="n">
-        <v>2.17785310745239</v>
+        <v>2.17785334587097</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>2.39499998092651</v>
       </c>
       <c r="G845" t="n">
-        <v>2.1509108543396</v>
+        <v>2.15091061592102</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G846" t="n">
-        <v>2.09253549575806</v>
+        <v>2.0925350189209</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>2.38499999046326</v>
       </c>
       <c r="G848" t="n">
-        <v>2.141930103302</v>
+        <v>2.14192986488342</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>2.46499991416931</v>
       </c>
       <c r="G849" t="n">
-        <v>2.21377635002136</v>
+        <v>2.21377682685852</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>2.36500000953674</v>
       </c>
       <c r="G850" t="n">
-        <v>2.12396812438965</v>
+        <v>2.12396836280823</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G852" t="n">
-        <v>1.9668036699295</v>
+        <v>1.96680355072021</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G854" t="n">
-        <v>1.9668036699295</v>
+        <v>1.96680355072021</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G855" t="n">
-        <v>1.95782291889191</v>
+        <v>1.95782279968262</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G856" t="n">
-        <v>1.95782291889191</v>
+        <v>1.95782279968262</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>2.24499988555908</v>
       </c>
       <c r="G859" t="n">
-        <v>2.01619815826416</v>
+        <v>2.01619791984558</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>2.27500009536743</v>
       </c>
       <c r="G860" t="n">
-        <v>2.04314041137695</v>
+        <v>2.04314088821411</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G864" t="n">
-        <v>2.06559300422668</v>
+        <v>2.06559276580811</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G865" t="n">
-        <v>2.03865027427673</v>
+        <v>2.03865003585815</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G869" t="n">
-        <v>2.06559300422668</v>
+        <v>2.06559276580811</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G873" t="n">
-        <v>2.02966928482056</v>
+        <v>2.02966952323914</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>2.27500009536743</v>
       </c>
       <c r="G874" t="n">
-        <v>2.04314041137695</v>
+        <v>2.04314088821411</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>2.22499990463257</v>
       </c>
       <c r="G875" t="n">
-        <v>1.99823653697968</v>
+        <v>1.9982362985611</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G876" t="n">
-        <v>1.92189931869507</v>
+        <v>1.92189943790436</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G877" t="n">
-        <v>1.85903334617615</v>
+        <v>1.85903346538544</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G878" t="n">
-        <v>1.86801421642303</v>
+        <v>1.86801433563232</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G879" t="n">
-        <v>1.84107184410095</v>
+        <v>1.84107172489166</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>2.01500010490417</v>
       </c>
       <c r="G880" t="n">
-        <v>1.80963897705078</v>
+        <v>1.80963909626007</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>1.98399996757507</v>
       </c>
       <c r="G883" t="n">
-        <v>1.78179824352264</v>
+        <v>1.78179812431335</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G886" t="n">
-        <v>1.82311022281647</v>
+        <v>1.82311010360718</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G887" t="n">
-        <v>1.82311022281647</v>
+        <v>1.82311010360718</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>2.01500010490417</v>
       </c>
       <c r="G888" t="n">
-        <v>1.80963897705078</v>
+        <v>1.80963909626007</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>1.98800003528595</v>
       </c>
       <c r="G890" t="n">
-        <v>1.78539061546326</v>
+        <v>1.78539073467255</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G892" t="n">
-        <v>1.82311022281647</v>
+        <v>1.82311010360718</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G893" t="n">
-        <v>1.82311022281647</v>
+        <v>1.82311010360718</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G894" t="n">
-        <v>1.80514848232269</v>
+        <v>1.8051483631134</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>2.01500010490417</v>
       </c>
       <c r="G895" t="n">
-        <v>1.80963897705078</v>
+        <v>1.80963909626007</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>1.99600005149841</v>
       </c>
       <c r="G896" t="n">
-        <v>1.79257547855377</v>
+        <v>1.79257535934448</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>1.99399995803833</v>
       </c>
       <c r="G897" t="n">
-        <v>1.79077899456024</v>
+        <v>1.79077911376953</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G899" t="n">
-        <v>1.80514848232269</v>
+        <v>1.8051483631134</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>2</v>
       </c>
       <c r="G900" t="n">
-        <v>1.7961677312851</v>
+        <v>1.79616761207581</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>1.99399995803833</v>
       </c>
       <c r="G901" t="n">
-        <v>1.79077899456024</v>
+        <v>1.79077911376953</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>1.89800000190735</v>
       </c>
       <c r="G903" t="n">
-        <v>1.70456314086914</v>
+        <v>1.70456302165985</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G904" t="n">
-        <v>1.72432076931</v>
+        <v>1.72432088851929</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>1.92200005054474</v>
       </c>
       <c r="G905" t="n">
-        <v>1.72611713409424</v>
+        <v>1.72611725330353</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>2.1949999332428</v>
       </c>
       <c r="G906" t="n">
-        <v>1.97129392623901</v>
+        <v>1.97129380702972</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G907" t="n">
-        <v>1.95782291889191</v>
+        <v>1.95782279968262</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>2.24499988555908</v>
       </c>
       <c r="G908" t="n">
-        <v>2.01619815826416</v>
+        <v>2.01619791984558</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G909" t="n">
-        <v>1.99374616146088</v>
+        <v>1.99374604225159</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G911" t="n">
-        <v>1.93088042736053</v>
+        <v>1.93088030815125</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>2.20499992370605</v>
       </c>
       <c r="G912" t="n">
-        <v>1.98027467727661</v>
+        <v>1.9802747964859</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G913" t="n">
-        <v>1.94884192943573</v>
+        <v>1.94884181022644</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>2.125</v>
       </c>
       <c r="G914" t="n">
-        <v>1.90842819213867</v>
+        <v>1.90842807292938</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>2.13499999046326</v>
       </c>
       <c r="G915" t="n">
-        <v>1.91740882396698</v>
+        <v>1.91740894317627</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G916" t="n">
-        <v>1.92189931869507</v>
+        <v>1.92189943790436</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>2.14499998092651</v>
       </c>
       <c r="G917" t="n">
-        <v>1.92638969421387</v>
+        <v>1.92638957500458</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G918" t="n">
-        <v>1.90393769741058</v>
+        <v>1.903937458992</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G920" t="n">
-        <v>1.85005271434784</v>
+        <v>1.85005259513855</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>1.98399996757507</v>
       </c>
       <c r="G926" t="n">
-        <v>1.78179824352264</v>
+        <v>1.78179812431335</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>1.94799995422363</v>
       </c>
       <c r="G928" t="n">
-        <v>1.749467253685</v>
+        <v>1.74946737289429</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>1.94799995422363</v>
       </c>
       <c r="G932" t="n">
-        <v>1.749467253685</v>
+        <v>1.74946737289429</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>1.98199999332428</v>
       </c>
       <c r="G933" t="n">
-        <v>1.78000223636627</v>
+        <v>1.78000211715698</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G936" t="n">
-        <v>1.85903334617615</v>
+        <v>1.85903346538544</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G937" t="n">
-        <v>1.84556221961975</v>
+        <v>1.84556233882904</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G939" t="n">
-        <v>1.83209085464478</v>
+        <v>1.83209097385406</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G941" t="n">
-        <v>2.14642024040222</v>
+        <v>2.1464204788208</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>2.41499996185303</v>
       </c>
       <c r="G942" t="n">
-        <v>2.16887235641479</v>
+        <v>2.16887259483337</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G944" t="n">
-        <v>2.09253549575806</v>
+        <v>2.0925350189209</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>2.31500005722046</v>
       </c>
       <c r="G945" t="n">
-        <v>2.07906413078308</v>
+        <v>2.07906436920166</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G946" t="n">
-        <v>2.03865027427673</v>
+        <v>2.03865003585815</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G949" t="n">
-        <v>1.92189931869507</v>
+        <v>1.92189943790436</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G950" t="n">
-        <v>2.03865027427673</v>
+        <v>2.03865003585815</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>2.27500009536743</v>
       </c>
       <c r="G951" t="n">
-        <v>2.04314041137695</v>
+        <v>2.04314088821411</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>2.27500009536743</v>
       </c>
       <c r="G955" t="n">
-        <v>2.04314041137695</v>
+        <v>2.04314088821411</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G956" t="n">
-        <v>1.9668036699295</v>
+        <v>1.96680355072021</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G957" t="n">
-        <v>1.99374616146088</v>
+        <v>1.99374604225159</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G960" t="n">
-        <v>1.95782291889191</v>
+        <v>1.95782279968262</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G962" t="n">
-        <v>1.99374616146088</v>
+        <v>1.99374604225159</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G963" t="n">
-        <v>2.09253549575806</v>
+        <v>2.0925350189209</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>2.40499997138977</v>
       </c>
       <c r="G965" t="n">
-        <v>2.15989136695862</v>
+        <v>2.1598916053772</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G967" t="n">
-        <v>2.09253549575806</v>
+        <v>2.0925350189209</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>2.40499997138977</v>
       </c>
       <c r="G968" t="n">
-        <v>2.15989136695862</v>
+        <v>2.1598916053772</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>2.36500000953674</v>
       </c>
       <c r="G969" t="n">
-        <v>2.12396812438965</v>
+        <v>2.12396836280823</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G972" t="n">
-        <v>2.06559300422668</v>
+        <v>2.06559276580811</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>2.24499988555908</v>
       </c>
       <c r="G973" t="n">
-        <v>2.01619815826416</v>
+        <v>2.01619791984558</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G975" t="n">
-        <v>2.14642024040222</v>
+        <v>2.1464204788208</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>2.51500010490417</v>
       </c>
       <c r="G977" t="n">
-        <v>2.25868082046509</v>
+        <v>2.25868105888367</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G979" t="n">
-        <v>2.38890290260315</v>
+        <v>2.38890314102173</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G982" t="n">
-        <v>2.56851959228516</v>
+        <v>2.56851983070374</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G983" t="n">
-        <v>2.55055809020996</v>
+        <v>2.55055785179138</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>2.875</v>
       </c>
       <c r="G984" t="n">
-        <v>2.58199119567871</v>
+        <v>2.58199095726013</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>2.96499991416931</v>
       </c>
       <c r="G986" t="n">
-        <v>2.66281867027283</v>
+        <v>2.66281819343567</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G988" t="n">
-        <v>2.6852707862854</v>
+        <v>2.68527054786682</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G990" t="n">
-        <v>2.6852707862854</v>
+        <v>2.68527054786682</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>2.96499991416931</v>
       </c>
       <c r="G991" t="n">
-        <v>2.66281867027283</v>
+        <v>2.66281819343567</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G993" t="n">
-        <v>2.76609826087952</v>
+        <v>2.76609802246094</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G994" t="n">
-        <v>2.91428184509277</v>
+        <v>2.91428208351135</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G996" t="n">
-        <v>3.08042740821838</v>
+        <v>3.08042764663696</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1000" t="n">
-        <v>2.75711750984192</v>
+        <v>2.75711727142334</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1001" t="n">
-        <v>2.73915553092957</v>
+        <v>2.73915576934814</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>2.96499991416931</v>
       </c>
       <c r="G1003" t="n">
-        <v>2.66281867027283</v>
+        <v>2.66281819343567</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>3.02500009536743</v>
       </c>
       <c r="G1004" t="n">
-        <v>2.71670389175415</v>
+        <v>2.71670365333557</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1005" t="n">
-        <v>2.6852707862854</v>
+        <v>2.68527054786682</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>3.01500010490417</v>
       </c>
       <c r="G1006" t="n">
-        <v>2.70772290229797</v>
+        <v>2.70772266387939</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G1007" t="n">
-        <v>2.72568464279175</v>
+        <v>2.72568440437317</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>3</v>
       </c>
       <c r="G1008" t="n">
-        <v>2.694251537323</v>
+        <v>2.69425177574158</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G1011" t="n">
-        <v>2.72568464279175</v>
+        <v>2.72568440437317</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1012" t="n">
-        <v>2.78405952453613</v>
+        <v>2.78406000137329</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1014" t="n">
-        <v>2.77507901191711</v>
+        <v>2.77507877349854</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1015" t="n">
-        <v>2.74813628196716</v>
+        <v>2.74813652038574</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1016" t="n">
-        <v>2.75711750984192</v>
+        <v>2.75711727142334</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>2.92499995231628</v>
       </c>
       <c r="G1018" t="n">
-        <v>2.62689518928528</v>
+        <v>2.6268949508667</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>2.96499991416931</v>
       </c>
       <c r="G1019" t="n">
-        <v>2.66281867027283</v>
+        <v>2.66281819343567</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>2.88499999046326</v>
       </c>
       <c r="G1020" t="n">
-        <v>2.59097194671631</v>
+        <v>2.59097170829773</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1023" t="n">
-        <v>3.12533187866211</v>
+        <v>3.12533164024353</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1028" t="n">
-        <v>3.10737013816833</v>
+        <v>3.10736989974976</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>3.6949999332428</v>
       </c>
       <c r="G1029" t="n">
-        <v>3.31841945648193</v>
+        <v>3.31841969490051</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1034" t="n">
-        <v>3.12533187866211</v>
+        <v>3.12533164024353</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1036" t="n">
-        <v>3.10737013816833</v>
+        <v>3.10736989974976</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>3.5</v>
       </c>
       <c r="G1040" t="n">
-        <v>3.14329314231873</v>
+        <v>3.1432933807373</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>3.81500005722046</v>
       </c>
       <c r="G1041" t="n">
-        <v>3.42618989944458</v>
+        <v>3.426189661026</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1042" t="n">
-        <v>3.2420825958252</v>
+        <v>3.24208211898804</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>3.74499988555908</v>
       </c>
       <c r="G1044" t="n">
-        <v>3.36332368850708</v>
+        <v>3.36332392692566</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1048" t="n">
-        <v>3.30494832992554</v>
+        <v>3.30494856834412</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>3.375</v>
       </c>
       <c r="G1052" t="n">
-        <v>3.03103280067444</v>
+        <v>3.03103303909302</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1057" t="n">
-        <v>2.78405952453613</v>
+        <v>2.78406000137329</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G1058" t="n">
-        <v>2.77058839797974</v>
+        <v>2.77058863639832</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G1060" t="n">
-        <v>2.57750034332275</v>
+        <v>2.57750058174133</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1062" t="n">
-        <v>2.56851959228516</v>
+        <v>2.56851983070374</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>2.39499998092651</v>
       </c>
       <c r="G1065" t="n">
-        <v>2.1509108543396</v>
+        <v>2.15091061592102</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1066" t="n">
-        <v>1.84107184410095</v>
+        <v>1.84107172489166</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>2</v>
       </c>
       <c r="G1067" t="n">
-        <v>1.7961677312851</v>
+        <v>1.79616761207581</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>1.99399995803833</v>
       </c>
       <c r="G1068" t="n">
-        <v>1.79077899456024</v>
+        <v>1.79077911376953</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1070" t="n">
-        <v>1.86801421642303</v>
+        <v>1.86801433563232</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>1.99399995803833</v>
       </c>
       <c r="G1072" t="n">
-        <v>1.79077899456024</v>
+        <v>1.79077911376953</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>2</v>
       </c>
       <c r="G1073" t="n">
-        <v>1.7961677312851</v>
+        <v>1.79616761207581</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>2.16499996185303</v>
       </c>
       <c r="G1074" t="n">
-        <v>1.94435143470764</v>
+        <v>1.94435131549835</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>2.375</v>
       </c>
       <c r="G1076" t="n">
-        <v>2.13294887542725</v>
+        <v>2.13294911384583</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>2.21499991416931</v>
       </c>
       <c r="G1077" t="n">
-        <v>1.98925542831421</v>
+        <v>1.98925578594208</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1082" t="n">
-        <v>2.26317119598389</v>
+        <v>2.26317095756531</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>2.75</v>
       </c>
       <c r="G1086" t="n">
-        <v>2.46973037719727</v>
+        <v>2.46973061561584</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1090" t="n">
-        <v>2.54157733917236</v>
+        <v>2.54157710075378</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1096" t="n">
-        <v>2.6852707862854</v>
+        <v>2.68527054786682</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1098" t="n">
-        <v>2.65832805633545</v>
+        <v>2.65832829475403</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1100" t="n">
-        <v>2.6762900352478</v>
+        <v>2.67628979682922</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -29021,7 +29021,7 @@
         <v>2.92499995231628</v>
       </c>
       <c r="G1102" t="n">
-        <v>2.62689518928528</v>
+        <v>2.6268949508667</v>
       </c>
       <c r="H1102" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1104" t="n">
-        <v>2.56851959228516</v>
+        <v>2.56851983070374</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1109" t="n">
-        <v>2.64036631584167</v>
+        <v>2.64036655426025</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>2.96499991416931</v>
       </c>
       <c r="G1110" t="n">
-        <v>2.66281867027283</v>
+        <v>2.66281819343567</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>2.78500008583069</v>
       </c>
       <c r="G1112" t="n">
-        <v>2.50116372108459</v>
+        <v>2.50116348266602</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G1121" t="n">
-        <v>2.6134238243103</v>
+        <v>2.61342406272888</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G1122" t="n">
-        <v>2.6134238243103</v>
+        <v>2.61342406272888</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1123" t="n">
-        <v>2.60444307327271</v>
+        <v>2.60444331169128</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1124" t="n">
-        <v>2.60444307327271</v>
+        <v>2.60444331169128</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1126" t="n">
-        <v>2.74813628196716</v>
+        <v>2.74813652038574</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G1131" t="n">
-        <v>2.57750034332275</v>
+        <v>2.57750058174133</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G1134" t="n">
-        <v>2.57750034332275</v>
+        <v>2.57750058174133</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29905,7 +29905,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G1136" t="n">
-        <v>2.52361536026001</v>
+        <v>2.52361559867859</v>
       </c>
       <c r="H1136" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1137" t="n">
-        <v>2.42482614517212</v>
+        <v>2.4248263835907</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G1138" t="n">
-        <v>2.50565361976624</v>
+        <v>2.50565385818481</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -29983,7 +29983,7 @@
         <v>2.72499990463257</v>
       </c>
       <c r="G1139" t="n">
-        <v>2.44727849960327</v>
+        <v>2.44727826118469</v>
       </c>
       <c r="H1139" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1142" t="n">
-        <v>2.4338071346283</v>
+        <v>2.43380737304688</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1145" t="n">
-        <v>2.47871112823486</v>
+        <v>2.47871136665344</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30191,7 +30191,7 @@
         <v>2.75</v>
       </c>
       <c r="G1147" t="n">
-        <v>2.46973037719727</v>
+        <v>2.46973061561584</v>
       </c>
       <c r="H1147" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G1148" t="n">
-        <v>2.38890290260315</v>
+        <v>2.38890314102173</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G1149" t="n">
-        <v>2.38890290260315</v>
+        <v>2.38890314102173</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1150" t="n">
-        <v>2.42482614517212</v>
+        <v>2.4248263835907</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G1151" t="n">
-        <v>2.4068648815155</v>
+        <v>2.40686464309692</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1152" t="n">
-        <v>2.4158456325531</v>
+        <v>2.41584587097168</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1159" t="n">
-        <v>2.4158456325531</v>
+        <v>2.41584587097168</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1160" t="n">
-        <v>2.4158456325531</v>
+        <v>2.41584587097168</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30555,7 +30555,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1161" t="n">
-        <v>2.33501791954041</v>
+        <v>2.33501768112183</v>
       </c>
       <c r="H1161" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1163" t="n">
-        <v>2.27215218544006</v>
+        <v>2.27215170860291</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30633,7 +30633,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1164" t="n">
-        <v>2.27215218544006</v>
+        <v>2.27215170860291</v>
       </c>
       <c r="H1164" t="s">
         <v>8</v>
@@ -30685,7 +30685,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1166" t="n">
-        <v>2.33501791954041</v>
+        <v>2.33501768112183</v>
       </c>
       <c r="H1166" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1167" t="n">
-        <v>2.33501791954041</v>
+        <v>2.33501768112183</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>2.57500004768372</v>
       </c>
       <c r="G1168" t="n">
-        <v>2.31256604194641</v>
+        <v>2.31256580352783</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1170" t="n">
-        <v>2.42482614517212</v>
+        <v>2.4248263835907</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>2.74499988555908</v>
       </c>
       <c r="G1171" t="n">
-        <v>2.46523976325989</v>
+        <v>2.46524000167847</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30919,7 +30919,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1175" t="n">
-        <v>2.47871112823486</v>
+        <v>2.47871136665344</v>
       </c>
       <c r="H1175" t="s">
         <v>8</v>
@@ -30945,7 +30945,7 @@
         <v>2.74499988555908</v>
       </c>
       <c r="G1176" t="n">
-        <v>2.46523976325989</v>
+        <v>2.46524000167847</v>
       </c>
       <c r="H1176" t="s">
         <v>8</v>
@@ -30997,7 +30997,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G1178" t="n">
-        <v>2.38890290260315</v>
+        <v>2.38890314102173</v>
       </c>
       <c r="H1178" t="s">
         <v>8</v>
@@ -31023,7 +31023,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1179" t="n">
-        <v>2.4158456325531</v>
+        <v>2.41584587097168</v>
       </c>
       <c r="H1179" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>2.625</v>
       </c>
       <c r="G1184" t="n">
-        <v>2.35747027397156</v>
+        <v>2.35747003555298</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>2.65499997138977</v>
       </c>
       <c r="G1186" t="n">
-        <v>2.38441276550293</v>
+        <v>2.38441228866577</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>2.625</v>
       </c>
       <c r="G1192" t="n">
-        <v>2.35747027397156</v>
+        <v>2.35747003555298</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1193" t="n">
-        <v>2.4338071346283</v>
+        <v>2.43380737304688</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>2.78500008583069</v>
       </c>
       <c r="G1196" t="n">
-        <v>2.50116372108459</v>
+        <v>2.50116348266602</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>2.66499996185303</v>
       </c>
       <c r="G1198" t="n">
-        <v>2.39339327812195</v>
+        <v>2.39339351654053</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>2.57500004768372</v>
       </c>
       <c r="G1201" t="n">
-        <v>2.31256604194641</v>
+        <v>2.31256580352783</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1204" t="n">
-        <v>2.27215218544006</v>
+        <v>2.27215170860291</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1207" t="n">
-        <v>2.27215218544006</v>
+        <v>2.27215170860291</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1209" t="n">
-        <v>2.31705641746521</v>
+        <v>2.31705594062805</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -32011,7 +32011,7 @@
         <v>2.74499988555908</v>
       </c>
       <c r="G1217" t="n">
-        <v>2.46523976325989</v>
+        <v>2.46524000167847</v>
       </c>
       <c r="H1217" t="s">
         <v>8</v>
@@ -32115,7 +32115,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1221" t="n">
-        <v>2.60444307327271</v>
+        <v>2.60444331169128</v>
       </c>
       <c r="H1221" t="s">
         <v>8</v>
@@ -32141,7 +32141,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G1222" t="n">
-        <v>2.57750034332275</v>
+        <v>2.57750058174133</v>
       </c>
       <c r="H1222" t="s">
         <v>8</v>
@@ -32219,7 +32219,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1225" t="n">
-        <v>2.4338071346283</v>
+        <v>2.43380737304688</v>
       </c>
       <c r="H1225" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1227" t="n">
-        <v>2.27215218544006</v>
+        <v>2.27215170860291</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32349,7 +32349,7 @@
         <v>2.59500002861023</v>
       </c>
       <c r="G1230" t="n">
-        <v>2.33052754402161</v>
+        <v>2.33052730560303</v>
       </c>
       <c r="H1230" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>2.59500002861023</v>
       </c>
       <c r="G1231" t="n">
-        <v>2.33052754402161</v>
+        <v>2.33052730560303</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1234" t="n">
-        <v>2.31705641746521</v>
+        <v>2.31705594062805</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1236" t="n">
-        <v>2.4338071346283</v>
+        <v>2.43380737304688</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1237" t="n">
-        <v>2.4158456325531</v>
+        <v>2.41584587097168</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>2.75</v>
       </c>
       <c r="G1239" t="n">
-        <v>2.46973037719727</v>
+        <v>2.46973061561584</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1243" t="n">
-        <v>2.47871112823486</v>
+        <v>2.47871136665344</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1248" t="n">
-        <v>2.56851959228516</v>
+        <v>2.56851983070374</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1250" t="n">
-        <v>2.58648133277893</v>
+        <v>2.58648157119751</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1251" t="n">
-        <v>2.65832805633545</v>
+        <v>2.65832829475403</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1252" t="n">
-        <v>2.6852707862854</v>
+        <v>2.68527054786682</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1253" t="n">
-        <v>2.6762900352478</v>
+        <v>2.67628979682922</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>3</v>
       </c>
       <c r="G1254" t="n">
-        <v>2.694251537323</v>
+        <v>2.69425177574158</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -32999,7 +32999,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1255" t="n">
-        <v>2.74813628196716</v>
+        <v>2.74813652038574</v>
       </c>
       <c r="H1255" t="s">
         <v>8</v>
@@ -33025,7 +33025,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G1256" t="n">
-        <v>2.76160764694214</v>
+        <v>2.76160788536072</v>
       </c>
       <c r="H1256" t="s">
         <v>8</v>
@@ -33051,7 +33051,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1257" t="n">
-        <v>2.73915553092957</v>
+        <v>2.73915576934814</v>
       </c>
       <c r="H1257" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1259" t="n">
-        <v>2.64036631584167</v>
+        <v>2.64036655426025</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33129,7 +33129,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1260" t="n">
-        <v>2.77507901191711</v>
+        <v>2.77507877349854</v>
       </c>
       <c r="H1260" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1261" t="n">
-        <v>2.78405952453613</v>
+        <v>2.78406000137329</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1262" t="n">
-        <v>2.77507901191711</v>
+        <v>2.77507877349854</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33233,7 +33233,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1264" t="n">
-        <v>2.83794474601746</v>
+        <v>2.83794498443604</v>
       </c>
       <c r="H1264" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>3.02500009536743</v>
       </c>
       <c r="G1265" t="n">
-        <v>2.71670389175415</v>
+        <v>2.71670365333557</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33285,7 +33285,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G1266" t="n">
-        <v>2.77058839797974</v>
+        <v>2.77058863639832</v>
       </c>
       <c r="H1266" t="s">
         <v>8</v>
@@ -33311,7 +33311,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1267" t="n">
-        <v>2.75711750984192</v>
+        <v>2.75711727142334</v>
       </c>
       <c r="H1267" t="s">
         <v>8</v>
@@ -33363,7 +33363,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1269" t="n">
-        <v>2.78405952453613</v>
+        <v>2.78406000137329</v>
       </c>
       <c r="H1269" t="s">
         <v>8</v>
@@ -33415,7 +33415,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1271" t="n">
-        <v>2.77507901191711</v>
+        <v>2.77507877349854</v>
       </c>
       <c r="H1271" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1272" t="n">
-        <v>2.78405952453613</v>
+        <v>2.78406000137329</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1274" t="n">
-        <v>2.77507901191711</v>
+        <v>2.77507877349854</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G1275" t="n">
-        <v>2.77058839797974</v>
+        <v>2.77058863639832</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1278" t="n">
-        <v>2.75711750984192</v>
+        <v>2.75711727142334</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33623,7 +33623,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G1279" t="n">
-        <v>2.72568464279175</v>
+        <v>2.72568440437317</v>
       </c>
       <c r="H1279" t="s">
         <v>8</v>
@@ -33753,7 +33753,7 @@
         <v>3</v>
       </c>
       <c r="G1284" t="n">
-        <v>2.694251537323</v>
+        <v>2.69425177574158</v>
       </c>
       <c r="H1284" t="s">
         <v>8</v>
@@ -33779,7 +33779,7 @@
         <v>2.92499995231628</v>
       </c>
       <c r="G1285" t="n">
-        <v>2.62689518928528</v>
+        <v>2.6268949508667</v>
       </c>
       <c r="H1285" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G1286" t="n">
-        <v>2.54606747627258</v>
+        <v>2.54606771469116</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1287" t="n">
-        <v>2.65832805633545</v>
+        <v>2.65832829475403</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1288" t="n">
-        <v>2.60444307327271</v>
+        <v>2.60444331169128</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33883,7 +33883,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G1289" t="n">
-        <v>2.63138580322266</v>
+        <v>2.63138556480408</v>
       </c>
       <c r="H1289" t="s">
         <v>8</v>
@@ -33909,7 +33909,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1290" t="n">
-        <v>2.60444307327271</v>
+        <v>2.60444331169128</v>
       </c>
       <c r="H1290" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>3</v>
       </c>
       <c r="G1291" t="n">
-        <v>2.694251537323</v>
+        <v>2.69425177574158</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -33961,7 +33961,7 @@
         <v>3.02500009536743</v>
       </c>
       <c r="G1292" t="n">
-        <v>2.71670389175415</v>
+        <v>2.71670365333557</v>
       </c>
       <c r="H1292" t="s">
         <v>8</v>
@@ -34013,7 +34013,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G1294" t="n">
-        <v>2.76160764694214</v>
+        <v>2.76160788536072</v>
       </c>
       <c r="H1294" t="s">
         <v>8</v>
@@ -34117,7 +34117,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1298" t="n">
-        <v>2.81100249290466</v>
+        <v>2.81100225448608</v>
       </c>
       <c r="H1298" t="s">
         <v>8</v>
@@ -34169,7 +34169,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G1300" t="n">
-        <v>3.12982177734375</v>
+        <v>3.12982201576233</v>
       </c>
       <c r="H1300" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>3.5</v>
       </c>
       <c r="G1301" t="n">
-        <v>3.14329314231873</v>
+        <v>3.1432933807373</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34221,7 +34221,7 @@
         <v>3.49499988555908</v>
       </c>
       <c r="G1302" t="n">
-        <v>3.13880276679993</v>
+        <v>3.13880300521851</v>
       </c>
       <c r="H1302" t="s">
         <v>8</v>
@@ -34299,7 +34299,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G1305" t="n">
-        <v>3.12982177734375</v>
+        <v>3.12982201576233</v>
       </c>
       <c r="H1305" t="s">
         <v>8</v>
@@ -34351,7 +34351,7 @@
         <v>3.42499995231628</v>
       </c>
       <c r="G1307" t="n">
-        <v>3.07593727111816</v>
+        <v>3.07593703269958</v>
       </c>
       <c r="H1307" t="s">
         <v>8</v>
@@ -34377,7 +34377,7 @@
         <v>3.42499995231628</v>
       </c>
       <c r="G1308" t="n">
-        <v>3.07593727111816</v>
+        <v>3.07593703269958</v>
       </c>
       <c r="H1308" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>3.22499990463257</v>
       </c>
       <c r="G1310" t="n">
-        <v>2.896320104599</v>
+        <v>2.89632034301758</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34481,7 +34481,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1312" t="n">
-        <v>3.01756167411804</v>
+        <v>3.01756143569946</v>
       </c>
       <c r="H1312" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>3.375</v>
       </c>
       <c r="G1317" t="n">
-        <v>3.03103280067444</v>
+        <v>3.03103303909302</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34637,7 +34637,7 @@
         <v>3.375</v>
       </c>
       <c r="G1318" t="n">
-        <v>3.03103280067444</v>
+        <v>3.03103303909302</v>
       </c>
       <c r="H1318" t="s">
         <v>8</v>
@@ -34715,7 +34715,7 @@
         <v>3.39499998092651</v>
       </c>
       <c r="G1321" t="n">
-        <v>3.04899454116821</v>
+        <v>3.04899477958679</v>
       </c>
       <c r="H1321" t="s">
         <v>8</v>
@@ -34767,7 +34767,7 @@
         <v>3.375</v>
       </c>
       <c r="G1323" t="n">
-        <v>3.03103280067444</v>
+        <v>3.03103303909302</v>
       </c>
       <c r="H1323" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>3.375</v>
       </c>
       <c r="G1324" t="n">
-        <v>3.03103280067444</v>
+        <v>3.03103303909302</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34923,7 +34923,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1329" t="n">
-        <v>3.0355236530304</v>
+        <v>3.03552317619324</v>
       </c>
       <c r="H1329" t="s">
         <v>8</v>
@@ -34949,7 +34949,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1330" t="n">
-        <v>3.04450440406799</v>
+        <v>3.04450416564941</v>
       </c>
       <c r="H1330" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1332" t="n">
-        <v>3.01756167411804</v>
+        <v>3.01756143569946</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35027,7 +35027,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1333" t="n">
-        <v>3.0355236530304</v>
+        <v>3.03552317619324</v>
       </c>
       <c r="H1333" t="s">
         <v>8</v>
@@ -35079,7 +35079,7 @@
         <v>3.31500005722046</v>
       </c>
       <c r="G1335" t="n">
-        <v>2.97714805603027</v>
+        <v>2.97714781761169</v>
       </c>
       <c r="H1335" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1339" t="n">
-        <v>2.86488723754883</v>
+        <v>2.86488747596741</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1340" t="n">
-        <v>2.90081095695496</v>
+        <v>2.90081071853638</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>3.14499998092651</v>
       </c>
       <c r="G1345" t="n">
-        <v>2.82447338104248</v>
+        <v>2.82447361946106</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35365,7 +35365,7 @@
         <v>3.11500000953674</v>
       </c>
       <c r="G1346" t="n">
-        <v>2.79753112792969</v>
+        <v>2.79753088951111</v>
       </c>
       <c r="H1346" t="s">
         <v>8</v>
@@ -35391,7 +35391,7 @@
         <v>3.25</v>
       </c>
       <c r="G1347" t="n">
-        <v>2.91877222061157</v>
+        <v>2.91877245903015</v>
       </c>
       <c r="H1347" t="s">
         <v>8</v>
@@ -35417,7 +35417,7 @@
         <v>3.34500002861023</v>
       </c>
       <c r="G1348" t="n">
-        <v>3.00409030914307</v>
+        <v>3.00409054756165</v>
       </c>
       <c r="H1348" t="s">
         <v>8</v>
@@ -35599,7 +35599,7 @@
         <v>3.4449999332428</v>
       </c>
       <c r="G1355" t="n">
-        <v>3.09389853477478</v>
+        <v>3.09389877319336</v>
       </c>
       <c r="H1355" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1356" t="n">
-        <v>3.21513986587524</v>
+        <v>3.21514010429382</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35677,7 +35677,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1358" t="n">
-        <v>3.30494832992554</v>
+        <v>3.30494856834412</v>
       </c>
       <c r="H1358" t="s">
         <v>8</v>
@@ -35703,7 +35703,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1359" t="n">
-        <v>3.35883331298828</v>
+        <v>3.35883355140686</v>
       </c>
       <c r="H1359" t="s">
         <v>8</v>
@@ -35729,7 +35729,7 @@
         <v>3.60500001907349</v>
       </c>
       <c r="G1360" t="n">
-        <v>3.23759198188782</v>
+        <v>3.2375922203064</v>
       </c>
       <c r="H1360" t="s">
         <v>8</v>
@@ -35833,7 +35833,7 @@
         <v>3.53500008583069</v>
       </c>
       <c r="G1364" t="n">
-        <v>3.17472624778748</v>
+        <v>3.17472648620605</v>
       </c>
       <c r="H1364" t="s">
         <v>8</v>
@@ -35859,7 +35859,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G1365" t="n">
-        <v>3.2196307182312</v>
+        <v>3.21963024139404</v>
       </c>
       <c r="H1365" t="s">
         <v>8</v>
@@ -35885,7 +35885,7 @@
         <v>3.5</v>
       </c>
       <c r="G1366" t="n">
-        <v>3.14329314231873</v>
+        <v>3.1432933807373</v>
       </c>
       <c r="H1366" t="s">
         <v>8</v>
@@ -35911,7 +35911,7 @@
         <v>3.46499991416931</v>
       </c>
       <c r="G1367" t="n">
-        <v>3.11186051368713</v>
+        <v>3.11186027526855</v>
       </c>
       <c r="H1367" t="s">
         <v>8</v>
@@ -35937,7 +35937,7 @@
         <v>3.46499991416931</v>
       </c>
       <c r="G1368" t="n">
-        <v>3.11186051368713</v>
+        <v>3.11186027526855</v>
       </c>
       <c r="H1368" t="s">
         <v>8</v>
@@ -35989,7 +35989,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1370" t="n">
-        <v>3.12533187866211</v>
+        <v>3.12533164024353</v>
       </c>
       <c r="H1370" t="s">
         <v>8</v>
@@ -36015,7 +36015,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1371" t="n">
-        <v>3.08042740821838</v>
+        <v>3.08042764663696</v>
       </c>
       <c r="H1371" t="s">
         <v>8</v>
@@ -36067,7 +36067,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1373" t="n">
-        <v>3.04450440406799</v>
+        <v>3.04450416564941</v>
       </c>
       <c r="H1373" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1375" t="n">
-        <v>3.04450440406799</v>
+        <v>3.04450416564941</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36223,7 +36223,7 @@
         <v>3.4449999332428</v>
       </c>
       <c r="G1379" t="n">
-        <v>3.09389853477478</v>
+        <v>3.09389877319336</v>
       </c>
       <c r="H1379" t="s">
         <v>8</v>
@@ -36249,7 +36249,7 @@
         <v>3.40499997138977</v>
       </c>
       <c r="G1380" t="n">
-        <v>3.05797529220581</v>
+        <v>3.05797553062439</v>
       </c>
       <c r="H1380" t="s">
         <v>8</v>
@@ -36275,7 +36275,7 @@
         <v>3.39499998092651</v>
       </c>
       <c r="G1381" t="n">
-        <v>3.04899454116821</v>
+        <v>3.04899477958679</v>
       </c>
       <c r="H1381" t="s">
         <v>8</v>
@@ -36301,7 +36301,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1382" t="n">
-        <v>3.04450440406799</v>
+        <v>3.04450416564941</v>
       </c>
       <c r="H1382" t="s">
         <v>8</v>
@@ -36327,7 +36327,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1383" t="n">
-        <v>3.08042740821838</v>
+        <v>3.08042764663696</v>
       </c>
       <c r="H1383" t="s">
         <v>8</v>
@@ -36353,7 +36353,7 @@
         <v>3.5</v>
       </c>
       <c r="G1384" t="n">
-        <v>3.14329314231873</v>
+        <v>3.1432933807373</v>
       </c>
       <c r="H1384" t="s">
         <v>8</v>
@@ -36379,7 +36379,7 @@
         <v>3.54500007629395</v>
       </c>
       <c r="G1385" t="n">
-        <v>3.18370699882507</v>
+        <v>3.18370723724365</v>
       </c>
       <c r="H1385" t="s">
         <v>8</v>
@@ -36457,7 +36457,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1388" t="n">
-        <v>3.01756167411804</v>
+        <v>3.01756143569946</v>
       </c>
       <c r="H1388" t="s">
         <v>8</v>
@@ -36483,7 +36483,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1389" t="n">
-        <v>2.98163843154907</v>
+        <v>2.98163819313049</v>
       </c>
       <c r="H1389" t="s">
         <v>8</v>
@@ -36561,7 +36561,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1392" t="n">
-        <v>2.98163843154907</v>
+        <v>2.98163819313049</v>
       </c>
       <c r="H1392" t="s">
         <v>8</v>
@@ -36613,7 +36613,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1394" t="n">
-        <v>2.92775344848633</v>
+        <v>2.92775321006775</v>
       </c>
       <c r="H1394" t="s">
         <v>8</v>
@@ -36639,7 +36639,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G1395" t="n">
-        <v>3.2196307182312</v>
+        <v>3.21963024139404</v>
       </c>
       <c r="H1395" t="s">
         <v>8</v>
@@ -36691,7 +36691,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1397" t="n">
-        <v>3.21513986587524</v>
+        <v>3.21514010429382</v>
       </c>
       <c r="H1397" t="s">
         <v>8</v>
@@ -36873,7 +36873,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1404" t="n">
-        <v>3.04450440406799</v>
+        <v>3.04450416564941</v>
       </c>
       <c r="H1404" t="s">
         <v>8</v>
@@ -36899,7 +36899,7 @@
         <v>3.39499998092651</v>
       </c>
       <c r="G1405" t="n">
-        <v>3.04899454116821</v>
+        <v>3.04899477958679</v>
       </c>
       <c r="H1405" t="s">
         <v>8</v>
@@ -36951,7 +36951,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1407" t="n">
-        <v>3.04450440406799</v>
+        <v>3.04450416564941</v>
       </c>
       <c r="H1407" t="s">
         <v>8</v>
@@ -37003,7 +37003,7 @@
         <v>3.23499989509583</v>
       </c>
       <c r="G1409" t="n">
-        <v>2.9053008556366</v>
+        <v>2.90530109405518</v>
       </c>
       <c r="H1409" t="s">
         <v>8</v>
@@ -37029,7 +37029,7 @@
         <v>3.23499989509583</v>
       </c>
       <c r="G1410" t="n">
-        <v>2.9053008556366</v>
+        <v>2.90530109405518</v>
       </c>
       <c r="H1410" t="s">
         <v>8</v>
@@ -37107,7 +37107,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1413" t="n">
-        <v>3.01756167411804</v>
+        <v>3.01756143569946</v>
       </c>
       <c r="H1413" t="s">
         <v>8</v>
@@ -37133,7 +37133,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1414" t="n">
-        <v>3.04450440406799</v>
+        <v>3.04450416564941</v>
       </c>
       <c r="H1414" t="s">
         <v>8</v>
@@ -37211,7 +37211,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1417" t="n">
-        <v>3.01756167411804</v>
+        <v>3.01756143569946</v>
       </c>
       <c r="H1417" t="s">
         <v>8</v>
@@ -37237,7 +37237,7 @@
         <v>3.34500002861023</v>
       </c>
       <c r="G1418" t="n">
-        <v>3.00409030914307</v>
+        <v>3.00409054756165</v>
       </c>
       <c r="H1418" t="s">
         <v>8</v>
@@ -37263,7 +37263,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1419" t="n">
-        <v>2.98163843154907</v>
+        <v>2.98163819313049</v>
       </c>
       <c r="H1419" t="s">
         <v>8</v>
@@ -37393,7 +37393,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1424" t="n">
-        <v>2.98163843154907</v>
+        <v>2.98163819313049</v>
       </c>
       <c r="H1424" t="s">
         <v>8</v>
@@ -37523,7 +37523,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1429" t="n">
-        <v>2.90979170799255</v>
+        <v>2.90979146957397</v>
       </c>
       <c r="H1429" t="s">
         <v>8</v>
@@ -37549,7 +37549,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1430" t="n">
-        <v>3.04450440406799</v>
+        <v>3.04450416564941</v>
       </c>
       <c r="H1430" t="s">
         <v>8</v>
@@ -37653,7 +37653,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G1434" t="n">
-        <v>2.95918607711792</v>
+        <v>2.9591863155365</v>
       </c>
       <c r="H1434" t="s">
         <v>8</v>
@@ -37705,7 +37705,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1436" t="n">
-        <v>2.93673396110535</v>
+        <v>2.93673419952393</v>
       </c>
       <c r="H1436" t="s">
         <v>8</v>
@@ -37731,7 +37731,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1437" t="n">
-        <v>2.93673396110535</v>
+        <v>2.93673419952393</v>
       </c>
       <c r="H1437" t="s">
         <v>8</v>
@@ -37757,7 +37757,7 @@
         <v>3.25</v>
       </c>
       <c r="G1438" t="n">
-        <v>2.91877222061157</v>
+        <v>2.91877245903015</v>
       </c>
       <c r="H1438" t="s">
         <v>8</v>
@@ -37783,7 +37783,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1439" t="n">
-        <v>2.93673396110535</v>
+        <v>2.93673419952393</v>
       </c>
       <c r="H1439" t="s">
         <v>8</v>
@@ -37809,7 +37809,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1440" t="n">
-        <v>2.92775344848633</v>
+        <v>2.92775321006775</v>
       </c>
       <c r="H1440" t="s">
         <v>8</v>
@@ -37861,7 +37861,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1442" t="n">
-        <v>2.98163843154907</v>
+        <v>2.98163819313049</v>
       </c>
       <c r="H1442" t="s">
         <v>8</v>
@@ -37887,7 +37887,7 @@
         <v>3.31500005722046</v>
       </c>
       <c r="G1443" t="n">
-        <v>2.97714805603027</v>
+        <v>2.97714781761169</v>
       </c>
       <c r="H1443" t="s">
         <v>8</v>
@@ -37939,7 +37939,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1445" t="n">
-        <v>2.93673396110535</v>
+        <v>2.93673419952393</v>
       </c>
       <c r="H1445" t="s">
         <v>8</v>
@@ -37965,7 +37965,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1446" t="n">
-        <v>2.92775344848633</v>
+        <v>2.92775321006775</v>
       </c>
       <c r="H1446" t="s">
         <v>8</v>
@@ -38017,7 +38017,7 @@
         <v>3.25</v>
       </c>
       <c r="G1448" t="n">
-        <v>2.91877222061157</v>
+        <v>2.91877245903015</v>
       </c>
       <c r="H1448" t="s">
         <v>8</v>
@@ -38043,7 +38043,7 @@
         <v>3.22499990463257</v>
       </c>
       <c r="G1449" t="n">
-        <v>2.896320104599</v>
+        <v>2.89632034301758</v>
       </c>
       <c r="H1449" t="s">
         <v>8</v>
@@ -38069,7 +38069,7 @@
         <v>3.22499990463257</v>
       </c>
       <c r="G1450" t="n">
-        <v>2.896320104599</v>
+        <v>2.89632034301758</v>
       </c>
       <c r="H1450" t="s">
         <v>8</v>
@@ -38199,7 +38199,7 @@
         <v>3.15499997138977</v>
       </c>
       <c r="G1455" t="n">
-        <v>2.83345437049866</v>
+        <v>2.83345413208008</v>
       </c>
       <c r="H1455" t="s">
         <v>8</v>
@@ -38225,7 +38225,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G1456" t="n">
-        <v>2.91428184509277</v>
+        <v>2.91428208351135</v>
       </c>
       <c r="H1456" t="s">
         <v>8</v>
@@ -38277,7 +38277,7 @@
         <v>3.25</v>
       </c>
       <c r="G1458" t="n">
-        <v>2.91877222061157</v>
+        <v>2.91877245903015</v>
       </c>
       <c r="H1458" t="s">
         <v>8</v>
@@ -38433,7 +38433,7 @@
         <v>3.375</v>
       </c>
       <c r="G1464" t="n">
-        <v>3.03103280067444</v>
+        <v>3.03103303909302</v>
       </c>
       <c r="H1464" t="s">
         <v>8</v>
@@ -38563,7 +38563,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1469" t="n">
-        <v>2.92775344848633</v>
+        <v>2.92775321006775</v>
       </c>
       <c r="H1469" t="s">
         <v>8</v>
@@ -38589,7 +38589,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1470" t="n">
-        <v>2.90979170799255</v>
+        <v>2.90979146957397</v>
       </c>
       <c r="H1470" t="s">
         <v>8</v>
@@ -38667,7 +38667,7 @@
         <v>3.49499988555908</v>
       </c>
       <c r="G1473" t="n">
-        <v>3.13880276679993</v>
+        <v>3.13880300521851</v>
       </c>
       <c r="H1473" t="s">
         <v>8</v>
@@ -38745,7 +38745,7 @@
         <v>3.45499992370605</v>
       </c>
       <c r="G1476" t="n">
-        <v>3.10287952423096</v>
+        <v>3.10287976264954</v>
       </c>
       <c r="H1476" t="s">
         <v>8</v>
@@ -38771,7 +38771,7 @@
         <v>3.49499988555908</v>
       </c>
       <c r="G1477" t="n">
-        <v>3.13880276679993</v>
+        <v>3.13880300521851</v>
       </c>
       <c r="H1477" t="s">
         <v>8</v>
@@ -38797,7 +38797,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1478" t="n">
-        <v>3.12533187866211</v>
+        <v>3.12533164024353</v>
       </c>
       <c r="H1478" t="s">
         <v>8</v>
@@ -38823,7 +38823,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1479" t="n">
-        <v>3.12533187866211</v>
+        <v>3.12533164024353</v>
       </c>
       <c r="H1479" t="s">
         <v>8</v>
@@ -38849,7 +38849,7 @@
         <v>3.5</v>
       </c>
       <c r="G1480" t="n">
-        <v>3.14329314231873</v>
+        <v>3.1432933807373</v>
       </c>
       <c r="H1480" t="s">
         <v>8</v>
@@ -38979,7 +38979,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1485" t="n">
-        <v>3.15227437019348</v>
+        <v>3.1522741317749</v>
       </c>
       <c r="H1485" t="s">
         <v>8</v>
@@ -39057,7 +39057,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1488" t="n">
-        <v>3.21513986587524</v>
+        <v>3.21514010429382</v>
       </c>
       <c r="H1488" t="s">
         <v>8</v>
@@ -39187,7 +39187,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1493" t="n">
-        <v>3.2420825958252</v>
+        <v>3.24208211898804</v>
       </c>
       <c r="H1493" t="s">
         <v>8</v>
@@ -39239,7 +39239,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1495" t="n">
-        <v>3.2420825958252</v>
+        <v>3.24208211898804</v>
       </c>
       <c r="H1495" t="s">
         <v>8</v>
@@ -39291,7 +39291,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1497" t="n">
-        <v>3.10737013816833</v>
+        <v>3.10736989974976</v>
       </c>
       <c r="H1497" t="s">
         <v>8</v>
@@ -39395,7 +39395,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1501" t="n">
-        <v>3.08042740821838</v>
+        <v>3.08042764663696</v>
       </c>
       <c r="H1501" t="s">
         <v>8</v>
@@ -39421,7 +39421,7 @@
         <v>3.54500007629395</v>
       </c>
       <c r="G1502" t="n">
-        <v>3.18370699882507</v>
+        <v>3.18370723724365</v>
       </c>
       <c r="H1502" t="s">
         <v>8</v>
@@ -39499,7 +39499,7 @@
         <v>3.5</v>
       </c>
       <c r="G1505" t="n">
-        <v>3.14329314231873</v>
+        <v>3.1432933807373</v>
       </c>
       <c r="H1505" t="s">
         <v>8</v>
@@ -39577,7 +39577,7 @@
         <v>3.46499991416931</v>
       </c>
       <c r="G1508" t="n">
-        <v>3.11186051368713</v>
+        <v>3.11186027526855</v>
       </c>
       <c r="H1508" t="s">
         <v>8</v>
@@ -39629,7 +39629,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1510" t="n">
-        <v>3.10737013816833</v>
+        <v>3.10736989974976</v>
       </c>
       <c r="H1510" t="s">
         <v>8</v>
@@ -39655,7 +39655,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1511" t="n">
-        <v>3.10737013816833</v>
+        <v>3.10736989974976</v>
       </c>
       <c r="H1511" t="s">
         <v>8</v>
@@ -39681,7 +39681,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1512" t="n">
-        <v>3.08042740821838</v>
+        <v>3.08042764663696</v>
       </c>
       <c r="H1512" t="s">
         <v>8</v>
@@ -39707,7 +39707,7 @@
         <v>3.53500008583069</v>
       </c>
       <c r="G1513" t="n">
-        <v>3.17472624778748</v>
+        <v>3.17472648620605</v>
       </c>
       <c r="H1513" t="s">
         <v>8</v>
@@ -39785,7 +39785,7 @@
         <v>3.54500007629395</v>
       </c>
       <c r="G1516" t="n">
-        <v>3.18370699882507</v>
+        <v>3.18370723724365</v>
       </c>
       <c r="H1516" t="s">
         <v>8</v>
@@ -39863,7 +39863,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1519" t="n">
-        <v>3.30494832992554</v>
+        <v>3.30494856834412</v>
       </c>
       <c r="H1519" t="s">
         <v>8</v>
@@ -40019,7 +40019,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1525" t="n">
-        <v>3.30494832992554</v>
+        <v>3.30494856834412</v>
       </c>
       <c r="H1525" t="s">
         <v>8</v>
@@ -40201,7 +40201,7 @@
         <v>3.53500008583069</v>
       </c>
       <c r="G1532" t="n">
-        <v>3.17472624778748</v>
+        <v>3.17472648620605</v>
       </c>
       <c r="H1532" t="s">
         <v>8</v>
@@ -40305,7 +40305,7 @@
         <v>3.42499995231628</v>
       </c>
       <c r="G1536" t="n">
-        <v>3.07593727111816</v>
+        <v>3.07593703269958</v>
       </c>
       <c r="H1536" t="s">
         <v>8</v>
@@ -40357,7 +40357,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1538" t="n">
-        <v>3.10737013816833</v>
+        <v>3.10736989974976</v>
       </c>
       <c r="H1538" t="s">
         <v>8</v>
@@ -40383,7 +40383,7 @@
         <v>3.4449999332428</v>
       </c>
       <c r="G1539" t="n">
-        <v>3.09389853477478</v>
+        <v>3.09389877319336</v>
       </c>
       <c r="H1539" t="s">
         <v>8</v>
@@ -40461,7 +40461,7 @@
         <v>3.375</v>
       </c>
       <c r="G1542" t="n">
-        <v>3.03103280067444</v>
+        <v>3.03103303909302</v>
       </c>
       <c r="H1542" t="s">
         <v>8</v>
@@ -40565,7 +40565,7 @@
         <v>3.39499998092651</v>
       </c>
       <c r="G1546" t="n">
-        <v>3.04899454116821</v>
+        <v>3.04899477958679</v>
       </c>
       <c r="H1546" t="s">
         <v>8</v>
@@ -40591,7 +40591,7 @@
         <v>3.40499997138977</v>
       </c>
       <c r="G1547" t="n">
-        <v>3.05797529220581</v>
+        <v>3.05797553062439</v>
       </c>
       <c r="H1547" t="s">
         <v>8</v>
@@ -40617,7 +40617,7 @@
         <v>3.46499991416931</v>
       </c>
       <c r="G1548" t="n">
-        <v>3.11186051368713</v>
+        <v>3.11186027526855</v>
       </c>
       <c r="H1548" t="s">
         <v>8</v>
@@ -40643,7 +40643,7 @@
         <v>3.5</v>
       </c>
       <c r="G1549" t="n">
-        <v>3.14329314231873</v>
+        <v>3.1432933807373</v>
       </c>
       <c r="H1549" t="s">
         <v>8</v>
@@ -40695,7 +40695,7 @@
         <v>3.40499997138977</v>
       </c>
       <c r="G1551" t="n">
-        <v>3.05797529220581</v>
+        <v>3.05797553062439</v>
       </c>
       <c r="H1551" t="s">
         <v>8</v>
@@ -40721,7 +40721,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1552" t="n">
-        <v>2.98163843154907</v>
+        <v>2.98163819313049</v>
       </c>
       <c r="H1552" t="s">
         <v>8</v>
@@ -40747,7 +40747,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G1553" t="n">
-        <v>2.95918607711792</v>
+        <v>2.9591863155365</v>
       </c>
       <c r="H1553" t="s">
         <v>8</v>
@@ -40799,7 +40799,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1555" t="n">
-        <v>3.01756167411804</v>
+        <v>3.01756143569946</v>
       </c>
       <c r="H1555" t="s">
         <v>8</v>
@@ -40851,7 +40851,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1557" t="n">
-        <v>2.93673396110535</v>
+        <v>2.93673419952393</v>
       </c>
       <c r="H1557" t="s">
         <v>8</v>
@@ -40903,7 +40903,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1559" t="n">
-        <v>3.0355236530304</v>
+        <v>3.03552317619324</v>
       </c>
       <c r="H1559" t="s">
         <v>8</v>
@@ -40955,7 +40955,7 @@
         <v>3.34500002861023</v>
       </c>
       <c r="G1561" t="n">
-        <v>3.00409030914307</v>
+        <v>3.00409054756165</v>
       </c>
       <c r="H1561" t="s">
         <v>8</v>
@@ -41007,7 +41007,7 @@
         <v>3.25</v>
       </c>
       <c r="G1563" t="n">
-        <v>2.91877222061157</v>
+        <v>2.91877245903015</v>
       </c>
       <c r="H1563" t="s">
         <v>8</v>
@@ -41033,7 +41033,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1564" t="n">
-        <v>2.92775344848633</v>
+        <v>2.92775321006775</v>
       </c>
       <c r="H1564" t="s">
         <v>8</v>
@@ -41059,7 +41059,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1565" t="n">
-        <v>2.74813628196716</v>
+        <v>2.74813652038574</v>
       </c>
       <c r="H1565" t="s">
         <v>8</v>
@@ -41085,7 +41085,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1566" t="n">
-        <v>2.76609826087952</v>
+        <v>2.76609802246094</v>
       </c>
       <c r="H1566" t="s">
         <v>8</v>
@@ -41111,7 +41111,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G1567" t="n">
-        <v>2.72568464279175</v>
+        <v>2.72568440437317</v>
       </c>
       <c r="H1567" t="s">
         <v>8</v>
@@ -41163,7 +41163,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G1569" t="n">
-        <v>2.63138580322266</v>
+        <v>2.63138556480408</v>
       </c>
       <c r="H1569" t="s">
         <v>8</v>
@@ -41215,7 +41215,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1571" t="n">
-        <v>2.54157733917236</v>
+        <v>2.54157710075378</v>
       </c>
       <c r="H1571" t="s">
         <v>8</v>
@@ -41241,7 +41241,7 @@
         <v>2.88499999046326</v>
       </c>
       <c r="G1572" t="n">
-        <v>2.59097194671631</v>
+        <v>2.59097170829773</v>
       </c>
       <c r="H1572" t="s">
         <v>8</v>
@@ -41267,7 +41267,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1573" t="n">
-        <v>2.47871112823486</v>
+        <v>2.47871136665344</v>
       </c>
       <c r="H1573" t="s">
         <v>8</v>
@@ -41293,7 +41293,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G1574" t="n">
-        <v>2.57750034332275</v>
+        <v>2.57750058174133</v>
       </c>
       <c r="H1574" t="s">
         <v>8</v>
@@ -41319,7 +41319,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1575" t="n">
-        <v>2.55055809020996</v>
+        <v>2.55055785179138</v>
       </c>
       <c r="H1575" t="s">
         <v>8</v>
@@ -41371,7 +41371,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1577" t="n">
-        <v>2.6762900352478</v>
+        <v>2.67628979682922</v>
       </c>
       <c r="H1577" t="s">
         <v>8</v>
@@ -41397,7 +41397,7 @@
         <v>2.92499995231628</v>
       </c>
       <c r="G1578" t="n">
-        <v>2.62689518928528</v>
+        <v>2.6268949508667</v>
       </c>
       <c r="H1578" t="s">
         <v>8</v>
@@ -41423,7 +41423,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1579" t="n">
-        <v>2.81100249290466</v>
+        <v>2.81100225448608</v>
       </c>
       <c r="H1579" t="s">
         <v>8</v>
@@ -41449,7 +41449,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1580" t="n">
-        <v>2.76609826087952</v>
+        <v>2.76609802246094</v>
       </c>
       <c r="H1580" t="s">
         <v>8</v>
@@ -41501,7 +41501,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1582" t="n">
-        <v>2.78405952453613</v>
+        <v>2.78406000137329</v>
       </c>
       <c r="H1582" t="s">
         <v>8</v>
@@ -41553,7 +41553,7 @@
         <v>3.15499997138977</v>
       </c>
       <c r="G1584" t="n">
-        <v>2.83345437049866</v>
+        <v>2.83345413208008</v>
       </c>
       <c r="H1584" t="s">
         <v>8</v>
@@ -41579,7 +41579,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1585" t="n">
-        <v>2.75711750984192</v>
+        <v>2.75711727142334</v>
       </c>
       <c r="H1585" t="s">
         <v>8</v>
@@ -41605,7 +41605,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G1586" t="n">
-        <v>2.77058839797974</v>
+        <v>2.77058863639832</v>
       </c>
       <c r="H1586" t="s">
         <v>8</v>
@@ -41657,7 +41657,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G1588" t="n">
-        <v>2.87835836410522</v>
+        <v>2.8783586025238</v>
       </c>
       <c r="H1588" t="s">
         <v>8</v>
@@ -41683,7 +41683,7 @@
         <v>3.14499998092651</v>
       </c>
       <c r="G1589" t="n">
-        <v>2.82447338104248</v>
+        <v>2.82447361946106</v>
       </c>
       <c r="H1589" t="s">
         <v>8</v>
@@ -41813,7 +41813,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G1594" t="n">
-        <v>2.76160764694214</v>
+        <v>2.76160788536072</v>
       </c>
       <c r="H1594" t="s">
         <v>8</v>
@@ -41891,7 +41891,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1597" t="n">
-        <v>2.81100249290466</v>
+        <v>2.81100225448608</v>
       </c>
       <c r="H1597" t="s">
         <v>8</v>
@@ -41917,7 +41917,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1598" t="n">
-        <v>2.77507901191711</v>
+        <v>2.77507877349854</v>
       </c>
       <c r="H1598" t="s">
         <v>8</v>
@@ -41943,7 +41943,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1599" t="n">
-        <v>2.78405952453613</v>
+        <v>2.78406000137329</v>
       </c>
       <c r="H1599" t="s">
         <v>8</v>
@@ -42021,7 +42021,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1602" t="n">
-        <v>3.01756167411804</v>
+        <v>3.01756143569946</v>
       </c>
       <c r="H1602" t="s">
         <v>8</v>
@@ -42099,7 +42099,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1605" t="n">
-        <v>3.0355236530304</v>
+        <v>3.03552317619324</v>
       </c>
       <c r="H1605" t="s">
         <v>8</v>
@@ -42125,7 +42125,7 @@
         <v>3.39499998092651</v>
       </c>
       <c r="G1606" t="n">
-        <v>3.04899454116821</v>
+        <v>3.04899477958679</v>
       </c>
       <c r="H1606" t="s">
         <v>8</v>
@@ -42151,7 +42151,7 @@
         <v>3.39499998092651</v>
       </c>
       <c r="G1607" t="n">
-        <v>3.04899454116821</v>
+        <v>3.04899477958679</v>
       </c>
       <c r="H1607" t="s">
         <v>8</v>
@@ -42229,7 +42229,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1610" t="n">
-        <v>3.01756167411804</v>
+        <v>3.01756143569946</v>
       </c>
       <c r="H1610" t="s">
         <v>8</v>
@@ -42333,7 +42333,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1614" t="n">
-        <v>2.74813628196716</v>
+        <v>2.74813652038574</v>
       </c>
       <c r="H1614" t="s">
         <v>8</v>
@@ -42385,7 +42385,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1616" t="n">
-        <v>2.71221303939819</v>
+        <v>2.71221327781677</v>
       </c>
       <c r="H1616" t="s">
         <v>8</v>
@@ -42411,7 +42411,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1617" t="n">
-        <v>2.77507901191711</v>
+        <v>2.77507877349854</v>
       </c>
       <c r="H1617" t="s">
         <v>8</v>
@@ -42463,7 +42463,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1619" t="n">
-        <v>2.86488723754883</v>
+        <v>2.86488747596741</v>
       </c>
       <c r="H1619" t="s">
         <v>8</v>
@@ -42541,7 +42541,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G1622" t="n">
-        <v>2.91428184509277</v>
+        <v>2.91428208351135</v>
       </c>
       <c r="H1622" t="s">
         <v>8</v>
@@ -42567,7 +42567,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1623" t="n">
-        <v>2.92775344848633</v>
+        <v>2.92775321006775</v>
       </c>
       <c r="H1623" t="s">
         <v>8</v>
@@ -42645,7 +42645,7 @@
         <v>3.11500000953674</v>
       </c>
       <c r="G1626" t="n">
-        <v>2.79753112792969</v>
+        <v>2.79753088951111</v>
       </c>
       <c r="H1626" t="s">
         <v>8</v>
@@ -42671,7 +42671,7 @@
         <v>3.06500005722046</v>
       </c>
       <c r="G1627" t="n">
-        <v>2.75262713432312</v>
+        <v>2.75262689590454</v>
       </c>
       <c r="H1627" t="s">
         <v>8</v>
@@ -42697,7 +42697,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1628" t="n">
-        <v>2.77507901191711</v>
+        <v>2.77507877349854</v>
       </c>
       <c r="H1628" t="s">
         <v>8</v>
@@ -42749,7 +42749,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1630" t="n">
-        <v>2.73915553092957</v>
+        <v>2.73915576934814</v>
       </c>
       <c r="H1630" t="s">
         <v>8</v>
@@ -42775,7 +42775,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1631" t="n">
-        <v>2.74813628196716</v>
+        <v>2.74813652038574</v>
       </c>
       <c r="H1631" t="s">
         <v>8</v>
@@ -42801,7 +42801,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G1632" t="n">
-        <v>2.72568464279175</v>
+        <v>2.72568440437317</v>
       </c>
       <c r="H1632" t="s">
         <v>8</v>
@@ -42853,7 +42853,7 @@
         <v>3.02500009536743</v>
       </c>
       <c r="G1634" t="n">
-        <v>2.71670389175415</v>
+        <v>2.71670365333557</v>
       </c>
       <c r="H1634" t="s">
         <v>8</v>
@@ -42957,7 +42957,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1638" t="n">
-        <v>2.81100249290466</v>
+        <v>2.81100225448608</v>
       </c>
       <c r="H1638" t="s">
         <v>8</v>
@@ -42983,7 +42983,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1639" t="n">
-        <v>2.6852707862854</v>
+        <v>2.68527054786682</v>
       </c>
       <c r="H1639" t="s">
         <v>8</v>
@@ -43009,7 +43009,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1640" t="n">
-        <v>2.64036631584167</v>
+        <v>2.64036655426025</v>
       </c>
       <c r="H1640" t="s">
         <v>8</v>
@@ -43035,7 +43035,7 @@
         <v>2.92499995231628</v>
       </c>
       <c r="G1641" t="n">
-        <v>2.62689518928528</v>
+        <v>2.6268949508667</v>
       </c>
       <c r="H1641" t="s">
         <v>8</v>
@@ -43113,7 +43113,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1644" t="n">
-        <v>2.6762900352478</v>
+        <v>2.67628979682922</v>
       </c>
       <c r="H1644" t="s">
         <v>8</v>
@@ -43269,7 +43269,7 @@
         <v>2.78500008583069</v>
       </c>
       <c r="G1650" t="n">
-        <v>2.50116372108459</v>
+        <v>2.50116348266602</v>
       </c>
       <c r="H1650" t="s">
         <v>8</v>
@@ -43321,7 +43321,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G1652" t="n">
-        <v>2.52361536026001</v>
+        <v>2.52361559867859</v>
       </c>
       <c r="H1652" t="s">
         <v>8</v>
@@ -43347,7 +43347,7 @@
         <v>2.75</v>
       </c>
       <c r="G1653" t="n">
-        <v>2.46973037719727</v>
+        <v>2.46973061561584</v>
       </c>
       <c r="H1653" t="s">
         <v>8</v>
@@ -43399,7 +43399,7 @@
         <v>2.78500008583069</v>
       </c>
       <c r="G1655" t="n">
-        <v>2.50116372108459</v>
+        <v>2.50116348266602</v>
       </c>
       <c r="H1655" t="s">
         <v>8</v>
@@ -43425,7 +43425,7 @@
         <v>2.71499991416931</v>
       </c>
       <c r="G1656" t="n">
-        <v>2.43829751014709</v>
+        <v>2.43829774856567</v>
       </c>
       <c r="H1656" t="s">
         <v>8</v>
@@ -43451,7 +43451,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1657" t="n">
-        <v>2.4338071346283</v>
+        <v>2.43380737304688</v>
       </c>
       <c r="H1657" t="s">
         <v>8</v>
@@ -43529,7 +43529,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G1660" t="n">
-        <v>2.57750034332275</v>
+        <v>2.57750058174133</v>
       </c>
       <c r="H1660" t="s">
         <v>8</v>
@@ -43555,7 +43555,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1661" t="n">
-        <v>2.56851959228516</v>
+        <v>2.56851983070374</v>
       </c>
       <c r="H1661" t="s">
         <v>8</v>
@@ -43659,7 +43659,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1665" t="n">
-        <v>2.55055809020996</v>
+        <v>2.55055785179138</v>
       </c>
       <c r="H1665" t="s">
         <v>8</v>
@@ -43763,7 +43763,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G1669" t="n">
-        <v>2.57750034332275</v>
+        <v>2.57750058174133</v>
       </c>
       <c r="H1669" t="s">
         <v>8</v>
@@ -43789,7 +43789,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1670" t="n">
-        <v>2.55055809020996</v>
+        <v>2.55055785179138</v>
       </c>
       <c r="H1670" t="s">
         <v>8</v>
@@ -43841,7 +43841,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G1672" t="n">
-        <v>2.52361536026001</v>
+        <v>2.52361559867859</v>
       </c>
       <c r="H1672" t="s">
         <v>8</v>
@@ -43893,7 +43893,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1674" t="n">
-        <v>2.55055809020996</v>
+        <v>2.55055785179138</v>
       </c>
       <c r="H1674" t="s">
         <v>8</v>
@@ -43919,7 +43919,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G1675" t="n">
-        <v>2.54606747627258</v>
+        <v>2.54606771469116</v>
       </c>
       <c r="H1675" t="s">
         <v>8</v>
@@ -43945,7 +43945,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1676" t="n">
-        <v>2.60444307327271</v>
+        <v>2.60444331169128</v>
       </c>
       <c r="H1676" t="s">
         <v>8</v>
@@ -43971,7 +43971,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1677" t="n">
-        <v>2.60444307327271</v>
+        <v>2.60444331169128</v>
       </c>
       <c r="H1677" t="s">
         <v>8</v>
@@ -43997,7 +43997,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G1678" t="n">
-        <v>2.6134238243103</v>
+        <v>2.61342406272888</v>
       </c>
       <c r="H1678" t="s">
         <v>8</v>
@@ -44023,7 +44023,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1679" t="n">
-        <v>2.60444307327271</v>
+        <v>2.60444331169128</v>
       </c>
       <c r="H1679" t="s">
         <v>8</v>
@@ -44101,7 +44101,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1682" t="n">
-        <v>2.56851959228516</v>
+        <v>2.56851983070374</v>
       </c>
       <c r="H1682" t="s">
         <v>8</v>
@@ -44127,7 +44127,7 @@
         <v>2.875</v>
       </c>
       <c r="G1683" t="n">
-        <v>2.58199119567871</v>
+        <v>2.58199095726013</v>
       </c>
       <c r="H1683" t="s">
         <v>8</v>
@@ -44153,7 +44153,7 @@
         <v>2.88499999046326</v>
       </c>
       <c r="G1684" t="n">
-        <v>2.59097194671631</v>
+        <v>2.59097170829773</v>
       </c>
       <c r="H1684" t="s">
         <v>8</v>
@@ -44179,7 +44179,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1685" t="n">
-        <v>2.60444307327271</v>
+        <v>2.60444331169128</v>
       </c>
       <c r="H1685" t="s">
         <v>8</v>
@@ -44231,7 +44231,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1687" t="n">
-        <v>2.76609826087952</v>
+        <v>2.76609802246094</v>
       </c>
       <c r="H1687" t="s">
         <v>8</v>
@@ -44257,7 +44257,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1688" t="n">
-        <v>2.78405952453613</v>
+        <v>2.78406000137329</v>
       </c>
       <c r="H1688" t="s">
         <v>8</v>
@@ -44309,7 +44309,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1690" t="n">
-        <v>2.71221303939819</v>
+        <v>2.71221327781677</v>
       </c>
       <c r="H1690" t="s">
         <v>8</v>
@@ -44335,7 +44335,7 @@
         <v>3</v>
       </c>
       <c r="G1691" t="n">
-        <v>2.694251537323</v>
+        <v>2.69425177574158</v>
       </c>
       <c r="H1691" t="s">
         <v>8</v>
@@ -44465,7 +44465,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1696" t="n">
-        <v>2.6852707862854</v>
+        <v>2.68527054786682</v>
       </c>
       <c r="H1696" t="s">
         <v>8</v>
@@ -44491,7 +44491,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1697" t="n">
-        <v>2.60444307327271</v>
+        <v>2.60444331169128</v>
       </c>
       <c r="H1697" t="s">
         <v>8</v>
@@ -44543,7 +44543,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G1699" t="n">
-        <v>2.57750034332275</v>
+        <v>2.57750058174133</v>
       </c>
       <c r="H1699" t="s">
         <v>8</v>
@@ -44699,7 +44699,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1705" t="n">
-        <v>2.55055809020996</v>
+        <v>2.55055785179138</v>
       </c>
       <c r="H1705" t="s">
         <v>8</v>
@@ -44751,7 +44751,7 @@
         <v>2.75</v>
       </c>
       <c r="G1707" t="n">
-        <v>2.46973037719727</v>
+        <v>2.46973061561584</v>
       </c>
       <c r="H1707" t="s">
         <v>8</v>
@@ -44777,7 +44777,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1708" t="n">
-        <v>2.47871112823486</v>
+        <v>2.47871136665344</v>
       </c>
       <c r="H1708" t="s">
         <v>8</v>
@@ -44803,7 +44803,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1709" t="n">
-        <v>2.42482614517212</v>
+        <v>2.4248263835907</v>
       </c>
       <c r="H1709" t="s">
         <v>8</v>
@@ -44907,7 +44907,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1713" t="n">
-        <v>2.18234395980835</v>
+        <v>2.18234348297119</v>
       </c>
       <c r="H1713" t="s">
         <v>8</v>
@@ -44933,7 +44933,7 @@
         <v>2.43499994277954</v>
       </c>
       <c r="G1714" t="n">
-        <v>2.18683385848999</v>
+        <v>2.18683409690857</v>
       </c>
       <c r="H1714" t="s">
         <v>8</v>
@@ -44959,7 +44959,7 @@
         <v>2.42499995231628</v>
       </c>
       <c r="G1715" t="n">
-        <v>2.17785310745239</v>
+        <v>2.17785334587097</v>
       </c>
       <c r="H1715" t="s">
         <v>8</v>
@@ -45037,7 +45037,7 @@
         <v>2.40499997138977</v>
       </c>
       <c r="G1718" t="n">
-        <v>2.15989136695862</v>
+        <v>2.1598916053772</v>
       </c>
       <c r="H1718" t="s">
         <v>8</v>
@@ -45063,7 +45063,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1719" t="n">
-        <v>2.15528583526611</v>
+        <v>2.15528607368469</v>
       </c>
       <c r="H1719" t="s">
         <v>8</v>
@@ -45193,7 +45193,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1724" t="n">
-        <v>2.10923314094543</v>
+        <v>2.10923290252686</v>
       </c>
       <c r="H1724" t="s">
         <v>8</v>
@@ -45427,7 +45427,7 @@
         <v>2.58500003814697</v>
       </c>
       <c r="G1733" t="n">
-        <v>2.38094639778137</v>
+        <v>2.38094687461853</v>
       </c>
       <c r="H1733" t="s">
         <v>8</v>
@@ -45453,7 +45453,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1734" t="n">
-        <v>2.37634134292603</v>
+        <v>2.37634110450745</v>
       </c>
       <c r="H1734" t="s">
         <v>8</v>
@@ -45505,7 +45505,7 @@
         <v>2.58500003814697</v>
       </c>
       <c r="G1736" t="n">
-        <v>2.38094639778137</v>
+        <v>2.38094687461853</v>
       </c>
       <c r="H1736" t="s">
         <v>8</v>
@@ -45531,7 +45531,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G1737" t="n">
-        <v>2.42239427566528</v>
+        <v>2.42239451408386</v>
       </c>
       <c r="H1737" t="s">
         <v>8</v>
@@ -45583,7 +45583,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1739" t="n">
-        <v>2.47765827178955</v>
+        <v>2.47765803337097</v>
       </c>
       <c r="H1739" t="s">
         <v>8</v>
@@ -45609,7 +45609,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G1740" t="n">
-        <v>2.403972864151</v>
+        <v>2.40397310256958</v>
       </c>
       <c r="H1740" t="s">
         <v>8</v>
@@ -45661,7 +45661,7 @@
         <v>2.56500005722046</v>
       </c>
       <c r="G1742" t="n">
-        <v>2.36252522468567</v>
+        <v>2.36252546310425</v>
       </c>
       <c r="H1742" t="s">
         <v>8</v>
@@ -45765,7 +45765,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G1746" t="n">
-        <v>2.45923686027527</v>
+        <v>2.45923662185669</v>
       </c>
       <c r="H1746" t="s">
         <v>8</v>
@@ -45791,7 +45791,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1747" t="n">
-        <v>2.47765827178955</v>
+        <v>2.47765803337097</v>
       </c>
       <c r="H1747" t="s">
         <v>8</v>
@@ -46207,7 +46207,7 @@
         <v>2.75500011444092</v>
       </c>
       <c r="G1763" t="n">
-        <v>2.53752732276917</v>
+        <v>2.53752708435059</v>
       </c>
       <c r="H1763" t="s">
         <v>8</v>
@@ -46259,7 +46259,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1765" t="n">
-        <v>2.52371096611023</v>
+        <v>2.52371144294739</v>
       </c>
       <c r="H1765" t="s">
         <v>8</v>
@@ -46285,7 +46285,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1766" t="n">
-        <v>2.52371096611023</v>
+        <v>2.52371144294739</v>
       </c>
       <c r="H1766" t="s">
         <v>8</v>
@@ -46337,7 +46337,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1768" t="n">
-        <v>2.49607944488525</v>
+        <v>2.49607920646667</v>
       </c>
       <c r="H1768" t="s">
         <v>8</v>
@@ -46363,7 +46363,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1769" t="n">
-        <v>2.52371096611023</v>
+        <v>2.52371144294739</v>
       </c>
       <c r="H1769" t="s">
         <v>8</v>
@@ -46389,7 +46389,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1770" t="n">
-        <v>2.47765827178955</v>
+        <v>2.47765803337097</v>
       </c>
       <c r="H1770" t="s">
         <v>8</v>
@@ -46415,7 +46415,7 @@
         <v>2.72499990463257</v>
       </c>
       <c r="G1771" t="n">
-        <v>2.50989508628845</v>
+        <v>2.50989532470703</v>
       </c>
       <c r="H1771" t="s">
         <v>8</v>
@@ -46441,7 +46441,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1772" t="n">
-        <v>2.50529026985168</v>
+        <v>2.50529003143311</v>
       </c>
       <c r="H1772" t="s">
         <v>8</v>
@@ -46467,7 +46467,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1773" t="n">
-        <v>2.50529026985168</v>
+        <v>2.50529003143311</v>
       </c>
       <c r="H1773" t="s">
         <v>8</v>
@@ -46493,7 +46493,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1774" t="n">
-        <v>2.52371096611023</v>
+        <v>2.52371144294739</v>
       </c>
       <c r="H1774" t="s">
         <v>8</v>
@@ -46519,7 +46519,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1775" t="n">
-        <v>2.52371096611023</v>
+        <v>2.52371144294739</v>
       </c>
       <c r="H1775" t="s">
         <v>8</v>
@@ -46597,7 +46597,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G1778" t="n">
-        <v>2.59279084205627</v>
+        <v>2.59279108047485</v>
       </c>
       <c r="H1778" t="s">
         <v>8</v>
@@ -46753,7 +46753,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1784" t="n">
-        <v>2.78160858154297</v>
+        <v>2.78160881996155</v>
       </c>
       <c r="H1784" t="s">
         <v>8</v>
@@ -46857,7 +46857,7 @@
         <v>3.06500005722046</v>
       </c>
       <c r="G1788" t="n">
-        <v>2.82305669784546</v>
+        <v>2.82305645942688</v>
       </c>
       <c r="H1788" t="s">
         <v>8</v>
@@ -46909,7 +46909,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1790" t="n">
-        <v>2.94739985466003</v>
+        <v>2.94740009307861</v>
       </c>
       <c r="H1790" t="s">
         <v>8</v>
@@ -46987,7 +46987,7 @@
         <v>3.09500002861023</v>
       </c>
       <c r="G1793" t="n">
-        <v>2.85068821907043</v>
+        <v>2.85068845748901</v>
       </c>
       <c r="H1793" t="s">
         <v>8</v>
@@ -47013,7 +47013,7 @@
         <v>3.09500002861023</v>
       </c>
       <c r="G1794" t="n">
-        <v>2.85068821907043</v>
+        <v>2.85068845748901</v>
       </c>
       <c r="H1794" t="s">
         <v>8</v>
@@ -47039,7 +47039,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1795" t="n">
-        <v>2.83687233924866</v>
+        <v>2.83687210083008</v>
       </c>
       <c r="H1795" t="s">
         <v>8</v>
@@ -47065,7 +47065,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1796" t="n">
-        <v>2.84608316421509</v>
+        <v>2.84608292579651</v>
       </c>
       <c r="H1796" t="s">
         <v>8</v>
@@ -47091,7 +47091,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G1797" t="n">
-        <v>2.84147763252258</v>
+        <v>2.84147787094116</v>
       </c>
       <c r="H1797" t="s">
         <v>8</v>
@@ -47169,7 +47169,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1800" t="n">
-        <v>2.78160858154297</v>
+        <v>2.78160881996155</v>
       </c>
       <c r="H1800" t="s">
         <v>8</v>
@@ -47325,7 +47325,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1806" t="n">
-        <v>2.71713447570801</v>
+        <v>2.71713423728943</v>
       </c>
       <c r="H1806" t="s">
         <v>8</v>
@@ -47351,7 +47351,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G1807" t="n">
-        <v>2.69871306419373</v>
+        <v>2.6987133026123</v>
       </c>
       <c r="H1807" t="s">
         <v>8</v>
@@ -47377,7 +47377,7 @@
         <v>2.875</v>
       </c>
       <c r="G1808" t="n">
-        <v>2.64805483818054</v>
+        <v>2.64805459976196</v>
       </c>
       <c r="H1808" t="s">
         <v>8</v>
@@ -47403,7 +47403,7 @@
         <v>2.875</v>
       </c>
       <c r="G1809" t="n">
-        <v>2.64805483818054</v>
+        <v>2.64805459976196</v>
       </c>
       <c r="H1809" t="s">
         <v>8</v>
@@ -47455,7 +47455,7 @@
         <v>2.875</v>
       </c>
       <c r="G1811" t="n">
-        <v>2.64805483818054</v>
+        <v>2.64805459976196</v>
       </c>
       <c r="H1811" t="s">
         <v>8</v>
@@ -47481,7 +47481,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G1812" t="n">
-        <v>2.64344906806946</v>
+        <v>2.64344930648804</v>
       </c>
       <c r="H1812" t="s">
         <v>8</v>
@@ -47507,7 +47507,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1813" t="n">
-        <v>2.62502813339233</v>
+        <v>2.62502789497375</v>
       </c>
       <c r="H1813" t="s">
         <v>8</v>
@@ -47533,7 +47533,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1814" t="n">
-        <v>2.61581754684448</v>
+        <v>2.6158173084259</v>
       </c>
       <c r="H1814" t="s">
         <v>8</v>
@@ -47585,7 +47585,7 @@
         <v>2.95499992370605</v>
       </c>
       <c r="G1816" t="n">
-        <v>2.72173929214478</v>
+        <v>2.72173976898193</v>
       </c>
       <c r="H1816" t="s">
         <v>8</v>
@@ -47663,7 +47663,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G1819" t="n">
-        <v>2.81384611129761</v>
+        <v>2.81384587287903</v>
       </c>
       <c r="H1819" t="s">
         <v>8</v>
@@ -47715,7 +47715,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1821" t="n">
-        <v>2.78160858154297</v>
+        <v>2.78160881996155</v>
       </c>
       <c r="H1821" t="s">
         <v>8</v>
@@ -47767,7 +47767,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1823" t="n">
-        <v>2.68950271606445</v>
+        <v>2.68950247764587</v>
       </c>
       <c r="H1823" t="s">
         <v>8</v>
@@ -47845,7 +47845,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1826" t="n">
-        <v>2.68950271606445</v>
+        <v>2.68950247764587</v>
       </c>
       <c r="H1826" t="s">
         <v>8</v>
@@ -47897,7 +47897,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1828" t="n">
-        <v>2.68950271606445</v>
+        <v>2.68950247764587</v>
       </c>
       <c r="H1828" t="s">
         <v>8</v>
@@ -48001,7 +48001,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G1832" t="n">
-        <v>2.69871306419373</v>
+        <v>2.6987133026123</v>
       </c>
       <c r="H1832" t="s">
         <v>8</v>
@@ -48079,7 +48079,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1835" t="n">
-        <v>2.61581754684448</v>
+        <v>2.6158173084259</v>
       </c>
       <c r="H1835" t="s">
         <v>8</v>
@@ -48105,7 +48105,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1836" t="n">
-        <v>2.63423871994019</v>
+        <v>2.63423848152161</v>
       </c>
       <c r="H1836" t="s">
         <v>8</v>
@@ -48183,7 +48183,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G1839" t="n">
-        <v>2.69871306419373</v>
+        <v>2.6987133026123</v>
       </c>
       <c r="H1839" t="s">
         <v>8</v>
@@ -48209,7 +48209,7 @@
         <v>2.91499996185303</v>
       </c>
       <c r="G1840" t="n">
-        <v>2.68489718437195</v>
+        <v>2.68489694595337</v>
       </c>
       <c r="H1840" t="s">
         <v>8</v>
@@ -48235,7 +48235,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1841" t="n">
-        <v>2.71713447570801</v>
+        <v>2.71713423728943</v>
       </c>
       <c r="H1841" t="s">
         <v>8</v>
@@ -48287,7 +48287,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1843" t="n">
-        <v>2.65265989303589</v>
+        <v>2.65266013145447</v>
       </c>
       <c r="H1843" t="s">
         <v>8</v>
@@ -48313,7 +48313,7 @@
         <v>2.875</v>
       </c>
       <c r="G1844" t="n">
-        <v>2.64805483818054</v>
+        <v>2.64805459976196</v>
       </c>
       <c r="H1844" t="s">
         <v>8</v>
@@ -48339,7 +48339,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1845" t="n">
-        <v>2.63423871994019</v>
+        <v>2.63423848152161</v>
       </c>
       <c r="H1845" t="s">
         <v>8</v>
@@ -48391,7 +48391,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1847" t="n">
-        <v>2.61581754684448</v>
+        <v>2.6158173084259</v>
       </c>
       <c r="H1847" t="s">
         <v>8</v>
@@ -48417,7 +48417,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1848" t="n">
-        <v>2.61581754684448</v>
+        <v>2.6158173084259</v>
       </c>
       <c r="H1848" t="s">
         <v>8</v>
@@ -48469,7 +48469,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1850" t="n">
-        <v>2.61581754684448</v>
+        <v>2.6158173084259</v>
       </c>
       <c r="H1850" t="s">
         <v>8</v>
@@ -48495,7 +48495,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1851" t="n">
-        <v>2.63423871994019</v>
+        <v>2.63423848152161</v>
       </c>
       <c r="H1851" t="s">
         <v>8</v>
@@ -48521,7 +48521,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1852" t="n">
-        <v>2.61581754684448</v>
+        <v>2.6158173084259</v>
       </c>
       <c r="H1852" t="s">
         <v>8</v>
@@ -48573,7 +48573,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1854" t="n">
-        <v>2.57897472381592</v>
+        <v>2.5789749622345</v>
       </c>
       <c r="H1854" t="s">
         <v>8</v>
@@ -48599,7 +48599,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1855" t="n">
-        <v>2.57897472381592</v>
+        <v>2.5789749622345</v>
       </c>
       <c r="H1855" t="s">
         <v>8</v>
@@ -48651,7 +48651,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.64344906806946</v>
+        <v>2.64344930648804</v>
       </c>
       <c r="H1857" t="s">
         <v>8</v>
@@ -48677,7 +48677,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.64344906806946</v>
+        <v>2.64344930648804</v>
       </c>
       <c r="H1858" t="s">
         <v>8</v>
@@ -48729,7 +48729,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.61581754684448</v>
+        <v>2.6158173084259</v>
       </c>
       <c r="H1860" t="s">
         <v>8</v>
@@ -48807,7 +48807,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.57897472381592</v>
+        <v>2.5789749622345</v>
       </c>
       <c r="H1863" t="s">
         <v>8</v>
@@ -48963,7 +48963,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.45923686027527</v>
+        <v>2.45923662185669</v>
       </c>
       <c r="H1869" t="s">
         <v>8</v>
@@ -48989,7 +48989,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.50529026985168</v>
+        <v>2.50529003143311</v>
       </c>
       <c r="H1870" t="s">
         <v>8</v>
@@ -49119,7 +49119,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.52371096611023</v>
+        <v>2.52371144294739</v>
       </c>
       <c r="H1875" t="s">
         <v>8</v>
@@ -49145,7 +49145,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.49607944488525</v>
+        <v>2.49607920646667</v>
       </c>
       <c r="H1876" t="s">
         <v>8</v>
@@ -49171,7 +49171,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.50529026985168</v>
+        <v>2.50529003143311</v>
       </c>
       <c r="H1877" t="s">
         <v>8</v>
@@ -49249,7 +49249,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.45923686027527</v>
+        <v>2.45923662185669</v>
       </c>
       <c r="H1880" t="s">
         <v>8</v>
@@ -49275,7 +49275,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.45923686027527</v>
+        <v>2.45923662185669</v>
       </c>
       <c r="H1881" t="s">
         <v>8</v>
@@ -49301,7 +49301,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.45923686027527</v>
+        <v>2.45923662185669</v>
       </c>
       <c r="H1882" t="s">
         <v>8</v>
@@ -49327,7 +49327,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.45923686027527</v>
+        <v>2.45923662185669</v>
       </c>
       <c r="H1883" t="s">
         <v>8</v>
@@ -49353,7 +49353,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.44081568717957</v>
+        <v>2.44081592559814</v>
       </c>
       <c r="H1884" t="s">
         <v>8</v>
@@ -49405,7 +49405,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.47765827178955</v>
+        <v>2.47765803337097</v>
       </c>
       <c r="H1886" t="s">
         <v>8</v>
@@ -49509,7 +49509,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.44081568717957</v>
+        <v>2.44081592559814</v>
       </c>
       <c r="H1890" t="s">
         <v>8</v>
@@ -49535,7 +49535,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.44081568717957</v>
+        <v>2.44081592559814</v>
       </c>
       <c r="H1891" t="s">
         <v>8</v>
@@ -49587,7 +49587,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.44081568717957</v>
+        <v>2.44081592559814</v>
       </c>
       <c r="H1893" t="s">
         <v>8</v>
@@ -49639,7 +49639,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.44081568717957</v>
+        <v>2.44081592559814</v>
       </c>
       <c r="H1895" t="s">
         <v>8</v>
@@ -49665,7 +49665,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.45923686027527</v>
+        <v>2.45923662185669</v>
       </c>
       <c r="H1896" t="s">
         <v>8</v>
@@ -49691,7 +49691,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.45923686027527</v>
+        <v>2.45923662185669</v>
       </c>
       <c r="H1897" t="s">
         <v>8</v>
@@ -49743,7 +49743,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.49607944488525</v>
+        <v>2.49607920646667</v>
       </c>
       <c r="H1899" t="s">
         <v>8</v>
@@ -49769,7 +49769,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.50529026985168</v>
+        <v>2.50529003143311</v>
       </c>
       <c r="H1900" t="s">
         <v>8</v>
@@ -49847,7 +49847,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.49607944488525</v>
+        <v>2.49607920646667</v>
       </c>
       <c r="H1903" t="s">
         <v>8</v>
@@ -49925,7 +49925,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.50529026985168</v>
+        <v>2.50529003143311</v>
       </c>
       <c r="H1906" t="s">
         <v>8</v>
@@ -50003,7 +50003,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.52371096611023</v>
+        <v>2.52371144294739</v>
       </c>
       <c r="H1909" t="s">
         <v>8</v>
@@ -50081,7 +50081,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.48590278625488</v>
+        <v>2.48590302467346</v>
       </c>
       <c r="H1912" t="s">
         <v>8</v>
@@ -50185,7 +50185,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.48590278625488</v>
+        <v>2.48590302467346</v>
       </c>
       <c r="H1916" t="s">
         <v>8</v>
@@ -50211,7 +50211,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.47645044326782</v>
+        <v>2.4764506816864</v>
       </c>
       <c r="H1917" t="s">
         <v>8</v>
@@ -50419,7 +50419,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.35357332229614</v>
+        <v>2.35357356071472</v>
       </c>
       <c r="H1925" t="s">
         <v>8</v>
@@ -50601,7 +50601,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.47645044326782</v>
+        <v>2.4764506816864</v>
       </c>
       <c r="H1932" t="s">
         <v>8</v>
@@ -50757,7 +50757,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.47645044326782</v>
+        <v>2.4764506816864</v>
       </c>
       <c r="H1938" t="s">
         <v>8</v>
@@ -50783,7 +50783,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.48590278625488</v>
+        <v>2.48590302467346</v>
       </c>
       <c r="H1939" t="s">
         <v>8</v>
@@ -50809,7 +50809,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.48590278625488</v>
+        <v>2.48590302467346</v>
       </c>
       <c r="H1940" t="s">
         <v>8</v>
@@ -51069,7 +51069,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.48590278625488</v>
+        <v>2.48590302467346</v>
       </c>
       <c r="H1950" t="s">
         <v>8</v>
@@ -51277,7 +51277,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.25905251502991</v>
+        <v>2.25905227661133</v>
       </c>
       <c r="H1958" t="s">
         <v>8</v>
@@ -51355,7 +51355,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.25905251502991</v>
+        <v>2.25905227661133</v>
       </c>
       <c r="H1961" t="s">
         <v>8</v>
@@ -51459,7 +51459,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.20233988761902</v>
+        <v>2.20233964920044</v>
       </c>
       <c r="H1965" t="s">
         <v>8</v>
@@ -51537,7 +51537,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.09836649894714</v>
+        <v>2.09836673736572</v>
       </c>
       <c r="H1968" t="s">
         <v>8</v>
@@ -51563,7 +51563,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.09836649894714</v>
+        <v>2.09836673736572</v>
       </c>
       <c r="H1969" t="s">
         <v>8</v>
@@ -51745,7 +51745,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1976" t="n">
-        <v>1.95658493041992</v>
+        <v>1.95658504962921</v>
       </c>
       <c r="H1976" t="s">
         <v>8</v>
@@ -51771,7 +51771,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G1977" t="n">
-        <v>1.89987254142761</v>
+        <v>1.89987242221832</v>
       </c>
       <c r="H1977" t="s">
         <v>8</v>
@@ -51797,7 +51797,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1978" t="n">
-        <v>1.88096821308136</v>
+        <v>1.88096833229065</v>
       </c>
       <c r="H1978" t="s">
         <v>8</v>
@@ -52057,7 +52057,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G1988" t="n">
-        <v>1.76281702518463</v>
+        <v>1.76281690597534</v>
       </c>
       <c r="H1988" t="s">
         <v>8</v>
@@ -52083,7 +52083,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1989" t="n">
-        <v>1.72028267383575</v>
+        <v>1.72028255462646</v>
       </c>
       <c r="H1989" t="s">
         <v>8</v>
@@ -52109,7 +52109,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1990" t="n">
-        <v>1.71083045005798</v>
+        <v>1.71083033084869</v>
       </c>
       <c r="H1990" t="s">
         <v>8</v>
@@ -52135,7 +52135,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G1991" t="n">
-        <v>1.69665229320526</v>
+        <v>1.69665217399597</v>
       </c>
       <c r="H1991" t="s">
         <v>8</v>
@@ -52343,7 +52343,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1999" t="n">
-        <v>1.71083045005798</v>
+        <v>1.71083033084869</v>
       </c>
       <c r="H1999" t="s">
         <v>8</v>
@@ -52369,7 +52369,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G2000" t="n">
-        <v>1.72028267383575</v>
+        <v>1.72028255462646</v>
       </c>
       <c r="H2000" t="s">
         <v>8</v>
@@ -52395,7 +52395,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G2001" t="n">
-        <v>1.71555662155151</v>
+        <v>1.71555650234222</v>
       </c>
       <c r="H2001" t="s">
         <v>8</v>
@@ -52421,7 +52421,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G2002" t="n">
-        <v>1.71555662155151</v>
+        <v>1.71555650234222</v>
       </c>
       <c r="H2002" t="s">
         <v>8</v>
@@ -52447,7 +52447,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G2003" t="n">
-        <v>1.72028267383575</v>
+        <v>1.72028255462646</v>
       </c>
       <c r="H2003" t="s">
         <v>8</v>
@@ -52473,7 +52473,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G2004" t="n">
-        <v>1.67302191257477</v>
+        <v>1.67302203178406</v>
       </c>
       <c r="H2004" t="s">
         <v>8</v>
@@ -52499,7 +52499,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G2005" t="n">
-        <v>1.69665229320526</v>
+        <v>1.69665217399597</v>
       </c>
       <c r="H2005" t="s">
         <v>8</v>
@@ -52525,7 +52525,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G2006" t="n">
-        <v>1.71555662155151</v>
+        <v>1.71555650234222</v>
       </c>
       <c r="H2006" t="s">
         <v>8</v>
@@ -52577,7 +52577,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G2008" t="n">
-        <v>1.88096821308136</v>
+        <v>1.88096833229065</v>
       </c>
       <c r="H2008" t="s">
         <v>8</v>
@@ -52603,7 +52603,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G2009" t="n">
-        <v>1.90932464599609</v>
+        <v>1.9093245267868</v>
       </c>
       <c r="H2009" t="s">
         <v>8</v>
@@ -52629,7 +52629,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2010" t="n">
-        <v>1.89987254142761</v>
+        <v>1.89987242221832</v>
       </c>
       <c r="H2010" t="s">
         <v>8</v>
@@ -52837,7 +52837,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G2018" t="n">
-        <v>1.97548913955688</v>
+        <v>1.97548937797546</v>
       </c>
       <c r="H2018" t="s">
         <v>8</v>
@@ -53253,7 +53253,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G2034" t="n">
-        <v>2.20233988761902</v>
+        <v>2.20233964920044</v>
       </c>
       <c r="H2034" t="s">
         <v>8</v>
@@ -53305,7 +53305,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G2036" t="n">
-        <v>2.14562702178955</v>
+        <v>2.14562726020813</v>
       </c>
       <c r="H2036" t="s">
         <v>8</v>
@@ -53487,7 +53487,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G2043" t="n">
-        <v>2.14562702178955</v>
+        <v>2.14562726020813</v>
       </c>
       <c r="H2043" t="s">
         <v>8</v>
@@ -53981,7 +53981,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G2062" t="n">
-        <v>2.13617491722107</v>
+        <v>2.13617515563965</v>
       </c>
       <c r="H2062" t="s">
         <v>8</v>
@@ -54007,7 +54007,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G2063" t="n">
-        <v>2.10781860351562</v>
+        <v>2.1078188419342</v>
       </c>
       <c r="H2063" t="s">
         <v>8</v>
@@ -54033,7 +54033,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G2064" t="n">
-        <v>1.94713306427002</v>
+        <v>1.94713282585144</v>
       </c>
       <c r="H2064" t="s">
         <v>8</v>
@@ -54059,7 +54059,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2065" t="n">
-        <v>1.87151610851288</v>
+        <v>1.87151622772217</v>
       </c>
       <c r="H2065" t="s">
         <v>8</v>
@@ -54215,7 +54215,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G2071" t="n">
-        <v>1.72973477840424</v>
+        <v>1.72973465919495</v>
       </c>
       <c r="H2071" t="s">
         <v>8</v>
@@ -54241,7 +54241,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G2072" t="n">
-        <v>1.81007742881775</v>
+        <v>1.81007754802704</v>
       </c>
       <c r="H2072" t="s">
         <v>8</v>
@@ -54267,7 +54267,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2073" t="n">
-        <v>1.87151610851288</v>
+        <v>1.87151622772217</v>
       </c>
       <c r="H2073" t="s">
         <v>8</v>
@@ -54293,7 +54293,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2074" t="n">
-        <v>1.87151610851288</v>
+        <v>1.87151622772217</v>
       </c>
       <c r="H2074" t="s">
         <v>8</v>
@@ -54319,7 +54319,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G2075" t="n">
-        <v>1.8620640039444</v>
+        <v>1.86206412315369</v>
       </c>
       <c r="H2075" t="s">
         <v>8</v>
@@ -54345,7 +54345,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2076" t="n">
-        <v>1.89987254142761</v>
+        <v>1.89987242221832</v>
       </c>
       <c r="H2076" t="s">
         <v>8</v>
@@ -54371,7 +54371,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G2077" t="n">
-        <v>1.90932464599609</v>
+        <v>1.9093245267868</v>
       </c>
       <c r="H2077" t="s">
         <v>8</v>
@@ -54397,7 +54397,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G2078" t="n">
-        <v>1.90932464599609</v>
+        <v>1.9093245267868</v>
       </c>
       <c r="H2078" t="s">
         <v>8</v>
@@ -54423,7 +54423,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G2079" t="n">
-        <v>1.90932464599609</v>
+        <v>1.9093245267868</v>
       </c>
       <c r="H2079" t="s">
         <v>8</v>
@@ -54449,7 +54449,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G2080" t="n">
-        <v>1.90932464599609</v>
+        <v>1.9093245267868</v>
       </c>
       <c r="H2080" t="s">
         <v>8</v>
@@ -54475,7 +54475,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2081" t="n">
-        <v>1.89987254142761</v>
+        <v>1.89987242221832</v>
       </c>
       <c r="H2081" t="s">
         <v>8</v>
@@ -54579,7 +54579,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2085" t="n">
-        <v>1.89987254142761</v>
+        <v>1.89987242221832</v>
       </c>
       <c r="H2085" t="s">
         <v>8</v>
@@ -54683,7 +54683,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G2089" t="n">
-        <v>1.76281702518463</v>
+        <v>1.76281690597534</v>
       </c>
       <c r="H2089" t="s">
         <v>8</v>
@@ -54761,7 +54761,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G2092" t="n">
-        <v>1.76281702518463</v>
+        <v>1.76281690597534</v>
       </c>
       <c r="H2092" t="s">
         <v>8</v>
@@ -54865,7 +54865,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G2096" t="n">
-        <v>1.82898163795471</v>
+        <v>1.828981757164</v>
       </c>
       <c r="H2096" t="s">
         <v>8</v>
@@ -54891,7 +54891,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G2097" t="n">
-        <v>1.82898163795471</v>
+        <v>1.828981757164</v>
       </c>
       <c r="H2097" t="s">
         <v>8</v>
@@ -55047,7 +55047,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G2103" t="n">
-        <v>1.81007742881775</v>
+        <v>1.81007754802704</v>
       </c>
       <c r="H2103" t="s">
         <v>8</v>
@@ -55073,7 +55073,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G2104" t="n">
-        <v>1.78172123432159</v>
+        <v>1.7817211151123</v>
       </c>
       <c r="H2104" t="s">
         <v>8</v>
@@ -55229,7 +55229,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G2110" t="n">
-        <v>1.74391281604767</v>
+        <v>1.74391293525696</v>
       </c>
       <c r="H2110" t="s">
         <v>8</v>
@@ -55307,7 +55307,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G2113" t="n">
-        <v>1.78172123432159</v>
+        <v>1.7817211151123</v>
       </c>
       <c r="H2113" t="s">
         <v>8</v>
@@ -55385,7 +55385,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G2116" t="n">
-        <v>1.76281702518463</v>
+        <v>1.76281690597534</v>
       </c>
       <c r="H2116" t="s">
         <v>8</v>
@@ -55619,7 +55619,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G2125" t="n">
-        <v>1.78172123432159</v>
+        <v>1.7817211151123</v>
       </c>
       <c r="H2125" t="s">
         <v>8</v>
@@ -55671,7 +55671,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G2127" t="n">
-        <v>1.81007742881775</v>
+        <v>1.81007754802704</v>
       </c>
       <c r="H2127" t="s">
         <v>8</v>
@@ -55723,7 +55723,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G2129" t="n">
-        <v>1.82898163795471</v>
+        <v>1.828981757164</v>
       </c>
       <c r="H2129" t="s">
         <v>8</v>
@@ -55905,7 +55905,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G2136" t="n">
-        <v>1.78172123432159</v>
+        <v>1.7817211151123</v>
       </c>
       <c r="H2136" t="s">
         <v>8</v>
@@ -56009,7 +56009,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G2140" t="n">
-        <v>1.74391281604767</v>
+        <v>1.74391293525696</v>
       </c>
       <c r="H2140" t="s">
         <v>8</v>
@@ -56217,7 +56217,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G2148" t="n">
-        <v>1.74391281604767</v>
+        <v>1.74391293525696</v>
       </c>
       <c r="H2148" t="s">
         <v>8</v>
@@ -56269,7 +56269,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G2150" t="n">
-        <v>1.72973477840424</v>
+        <v>1.72973465919495</v>
       </c>
       <c r="H2150" t="s">
         <v>8</v>
@@ -56295,7 +56295,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G2151" t="n">
-        <v>1.68720006942749</v>
+        <v>1.68720018863678</v>
       </c>
       <c r="H2151" t="s">
         <v>8</v>
@@ -56347,7 +56347,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G2153" t="n">
-        <v>1.71083045005798</v>
+        <v>1.71083033084869</v>
       </c>
       <c r="H2153" t="s">
         <v>8</v>
@@ -56373,7 +56373,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G2154" t="n">
-        <v>1.68247401714325</v>
+        <v>1.68247413635254</v>
       </c>
       <c r="H2154" t="s">
         <v>8</v>
@@ -56477,7 +56477,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G2158" t="n">
-        <v>1.69665229320526</v>
+        <v>1.69665217399597</v>
       </c>
       <c r="H2158" t="s">
         <v>8</v>
@@ -56503,7 +56503,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G2159" t="n">
-        <v>1.67302191257477</v>
+        <v>1.67302203178406</v>
       </c>
       <c r="H2159" t="s">
         <v>8</v>
@@ -71274,6 +71274,32 @@
         <v>1.13499999046326</v>
       </c>
       <c r="H2727" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2728">
+      <c r="A2728" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B2728" t="n">
+        <v>188258</v>
+      </c>
+      <c r="C2728" t="n">
+        <v>1.15499997138977</v>
+      </c>
+      <c r="D2728" t="n">
+        <v>1.11000001430511</v>
+      </c>
+      <c r="E2728" t="n">
+        <v>1.13499999046326</v>
+      </c>
+      <c r="F2728" t="n">
+        <v>1.15499997138977</v>
+      </c>
+      <c r="G2728" t="n">
+        <v>1.15499997138977</v>
+      </c>
+      <c r="H2728" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/ELC.MI.xlsx
+++ b/data/ELC.MI.xlsx
@@ -421,7 +421,7 @@
         <v>1.93700003623962</v>
       </c>
       <c r="G2" t="n">
-        <v>1.73070466518402</v>
+        <v>1.73070478439331</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G3" t="n">
-        <v>1.73338532447815</v>
+        <v>1.73338508605957</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G4" t="n">
-        <v>1.72445011138916</v>
+        <v>1.72444999217987</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>1.87399995326996</v>
       </c>
       <c r="G5" t="n">
-        <v>1.67441415786743</v>
+        <v>1.67441439628601</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G6" t="n">
-        <v>1.69764530658722</v>
+        <v>1.69764518737793</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G7" t="n">
-        <v>1.65297031402588</v>
+        <v>1.65297043323517</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G8" t="n">
-        <v>1.66190528869629</v>
+        <v>1.661905169487</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G9" t="n">
-        <v>1.69764530658722</v>
+        <v>1.69764518737793</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G11" t="n">
-        <v>1.59936046600342</v>
+        <v>1.59936034679413</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>1.65199995040894</v>
       </c>
       <c r="G12" t="n">
-        <v>1.47605788707733</v>
+        <v>1.47605776786804</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>1.61099994182587</v>
       </c>
       <c r="G14" t="n">
-        <v>1.43942451477051</v>
+        <v>1.43942439556122</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>1.71800005435944</v>
       </c>
       <c r="G15" t="n">
-        <v>1.53502881526947</v>
+        <v>1.53502869606018</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>1.70700001716614</v>
       </c>
       <c r="G16" t="n">
-        <v>1.5252001285553</v>
+        <v>1.52520024776459</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G17" t="n">
-        <v>1.44746589660645</v>
+        <v>1.44746601581573</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G19" t="n">
-        <v>1.46533584594727</v>
+        <v>1.46533572673798</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>1.59099996089935</v>
       </c>
       <c r="G22" t="n">
-        <v>1.42155456542969</v>
+        <v>1.42155432701111</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G23" t="n">
-        <v>1.39832353591919</v>
+        <v>1.39832365512848</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>1.54499995708466</v>
       </c>
       <c r="G24" t="n">
-        <v>1.38045346736908</v>
+        <v>1.38045358657837</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G26" t="n">
-        <v>1.38492119312286</v>
+        <v>1.38492107391357</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>1.40199995040894</v>
       </c>
       <c r="G27" t="n">
-        <v>1.25268340110779</v>
+        <v>1.25268352031708</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G28" t="n">
-        <v>1.28216886520386</v>
+        <v>1.28216874599457</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G29" t="n">
-        <v>1.31344139575958</v>
+        <v>1.31344127655029</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G30" t="n">
-        <v>1.25983154773712</v>
+        <v>1.25983142852783</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G31" t="n">
-        <v>1.42959606647491</v>
+        <v>1.42959594726562</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>1.63199996948242</v>
       </c>
       <c r="G32" t="n">
-        <v>1.45818793773651</v>
+        <v>1.45818781852722</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>1.6710000038147</v>
       </c>
       <c r="G33" t="n">
-        <v>1.49303424358368</v>
+        <v>1.49303436279297</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G35" t="n">
-        <v>1.51001060009003</v>
+        <v>1.51001083850861</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>1.75399994850159</v>
       </c>
       <c r="G36" t="n">
-        <v>1.5671945810318</v>
+        <v>1.56719446182251</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>1.75</v>
       </c>
       <c r="G38" t="n">
-        <v>1.56362056732178</v>
+        <v>1.56362068653107</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>1.74699997901917</v>
       </c>
       <c r="G39" t="n">
-        <v>1.56094002723694</v>
+        <v>1.56094014644623</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G44" t="n">
-        <v>1.51894581317902</v>
+        <v>1.51894569396973</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>1.75</v>
       </c>
       <c r="G47" t="n">
-        <v>1.56362056732178</v>
+        <v>1.56362068653107</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>1.75</v>
       </c>
       <c r="G48" t="n">
-        <v>1.56362056732178</v>
+        <v>1.56362068653107</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>1.75</v>
       </c>
       <c r="G49" t="n">
-        <v>1.56362056732178</v>
+        <v>1.56362068653107</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>1.76600003242493</v>
       </c>
       <c r="G51" t="n">
-        <v>1.57791650295258</v>
+        <v>1.57791662216187</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>1.89300000667572</v>
       </c>
       <c r="G53" t="n">
-        <v>1.69139075279236</v>
+        <v>1.69139087200165</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G55" t="n">
-        <v>1.67977523803711</v>
+        <v>1.6797753572464</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G57" t="n">
-        <v>1.72445011138916</v>
+        <v>1.72444999217987</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G58" t="n">
-        <v>1.7691251039505</v>
+        <v>1.76912498474121</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>1.95200002193451</v>
       </c>
       <c r="G59" t="n">
-        <v>1.74410688877106</v>
+        <v>1.74410700798035</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>1.93599998950958</v>
       </c>
       <c r="G60" t="n">
-        <v>1.72981119155884</v>
+        <v>1.72981107234955</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>1.94599997997284</v>
       </c>
       <c r="G61" t="n">
-        <v>1.73874604701996</v>
+        <v>1.73874616622925</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>1.97599995136261</v>
       </c>
       <c r="G62" t="n">
-        <v>1.76555097103119</v>
+        <v>1.7655508518219</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G65" t="n">
-        <v>1.72445011138916</v>
+        <v>1.72444999217987</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>1.87899994850159</v>
       </c>
       <c r="G67" t="n">
-        <v>1.67888176441193</v>
+        <v>1.67888164520264</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G68" t="n">
-        <v>1.69317758083344</v>
+        <v>1.69317781925201</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G69" t="n">
-        <v>1.69764530658722</v>
+        <v>1.69764518737793</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G70" t="n">
-        <v>1.69764530658722</v>
+        <v>1.69764518737793</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G71" t="n">
-        <v>1.67084038257599</v>
+        <v>1.6708402633667</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>1.88100004196167</v>
       </c>
       <c r="G72" t="n">
-        <v>1.68066883087158</v>
+        <v>1.68066871166229</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G73" t="n">
-        <v>1.69764530658722</v>
+        <v>1.69764518737793</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G74" t="n">
-        <v>1.71551513671875</v>
+        <v>1.71551525592804</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>1.89800000190735</v>
       </c>
       <c r="G79" t="n">
-        <v>1.69585824012756</v>
+        <v>1.69585812091827</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>1.89900004863739</v>
       </c>
       <c r="G81" t="n">
-        <v>1.69675183296204</v>
+        <v>1.69675195217133</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G84" t="n">
-        <v>1.74232006072998</v>
+        <v>1.74232029914856</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>1.91600000858307</v>
       </c>
       <c r="G86" t="n">
-        <v>1.71194100379944</v>
+        <v>1.71194124221802</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G88" t="n">
-        <v>1.69764530658722</v>
+        <v>1.69764518737793</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>1.92599999904633</v>
       </c>
       <c r="G89" t="n">
-        <v>1.72087609767914</v>
+        <v>1.72087621688843</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>1.84700000286102</v>
       </c>
       <c r="G92" t="n">
-        <v>1.65028977394104</v>
+        <v>1.65028989315033</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>1.88699996471405</v>
       </c>
       <c r="G94" t="n">
-        <v>1.68602979183197</v>
+        <v>1.68602967262268</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>1.90600001811981</v>
       </c>
       <c r="G97" t="n">
-        <v>1.70300614833832</v>
+        <v>1.70300602912903</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>1.91799998283386</v>
       </c>
       <c r="G98" t="n">
-        <v>1.71372830867767</v>
+        <v>1.71372818946838</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>1.9190000295639</v>
       </c>
       <c r="G99" t="n">
-        <v>1.71462178230286</v>
+        <v>1.71462154388428</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>1.9190000295639</v>
       </c>
       <c r="G101" t="n">
-        <v>1.72342300415039</v>
+        <v>1.72342276573181</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>1.93799996376038</v>
       </c>
       <c r="G104" t="n">
-        <v>1.7404865026474</v>
+        <v>1.74048638343811</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G106" t="n">
-        <v>1.73330175876617</v>
+        <v>1.73330163955688</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G107" t="n">
-        <v>1.72432088851929</v>
+        <v>1.72432100772858</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G109" t="n">
-        <v>1.71534013748169</v>
+        <v>1.7153400182724</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G110" t="n">
-        <v>1.72432088851929</v>
+        <v>1.72432100772858</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G111" t="n">
-        <v>1.72432088851929</v>
+        <v>1.72432100772858</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G112" t="n">
-        <v>1.71534013748169</v>
+        <v>1.7153400182724</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G116" t="n">
-        <v>1.63900291919708</v>
+        <v>1.63900303840637</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G119" t="n">
-        <v>1.60757005214691</v>
+        <v>1.60756993293762</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G120" t="n">
-        <v>1.63451254367828</v>
+        <v>1.63451278209686</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>1.82400000095367</v>
       </c>
       <c r="G122" t="n">
-        <v>1.63810479640961</v>
+        <v>1.6381049156189</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G123" t="n">
-        <v>1.66145503520966</v>
+        <v>1.66145515441895</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G127" t="n">
-        <v>1.63900291919708</v>
+        <v>1.63900303840637</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G131" t="n">
-        <v>1.59409868717194</v>
+        <v>1.59409880638123</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G133" t="n">
-        <v>1.46836709976196</v>
+        <v>1.46836698055267</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G136" t="n">
-        <v>1.45489573478699</v>
+        <v>1.45489585399628</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>1.6690000295639</v>
       </c>
       <c r="G140" t="n">
-        <v>1.49890184402466</v>
+        <v>1.49890196323395</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>1.67900002002716</v>
       </c>
       <c r="G142" t="n">
-        <v>1.50788283348083</v>
+        <v>1.50788271427155</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>1.66100001335144</v>
       </c>
       <c r="G145" t="n">
-        <v>1.49171733856201</v>
+        <v>1.49171721935272</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>1.66100001335144</v>
       </c>
       <c r="G146" t="n">
-        <v>1.49171733856201</v>
+        <v>1.49171721935272</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G147" t="n">
-        <v>1.50429034233093</v>
+        <v>1.50429046154022</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>1.67400002479553</v>
       </c>
       <c r="G148" t="n">
-        <v>1.50339221954346</v>
+        <v>1.50339233875275</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>1.65400004386902</v>
       </c>
       <c r="G149" t="n">
-        <v>1.48543071746826</v>
+        <v>1.48543059825897</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G150" t="n">
-        <v>1.50429034233093</v>
+        <v>1.50429046154022</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>1.67400002479553</v>
       </c>
       <c r="G152" t="n">
-        <v>1.50339221954346</v>
+        <v>1.50339233875275</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G156" t="n">
-        <v>1.50878071784973</v>
+        <v>1.50878083705902</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G159" t="n">
-        <v>1.51776158809662</v>
+        <v>1.51776170730591</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>1.66299998760223</v>
       </c>
       <c r="G162" t="n">
-        <v>1.49351334571838</v>
+        <v>1.49351346492767</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>1.69900000095367</v>
       </c>
       <c r="G165" t="n">
-        <v>1.52584433555603</v>
+        <v>1.52584445476532</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>1.71399998664856</v>
       </c>
       <c r="G166" t="n">
-        <v>1.53931570053101</v>
+        <v>1.53931558132172</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G167" t="n">
-        <v>1.64349329471588</v>
+        <v>1.64349341392517</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G169" t="n">
-        <v>1.75126349925995</v>
+        <v>1.75126361846924</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>1.93299996852875</v>
       </c>
       <c r="G170" t="n">
-        <v>1.73599600791931</v>
+        <v>1.73599588871002</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>1.84800004959106</v>
       </c>
       <c r="G173" t="n">
-        <v>1.6596587896347</v>
+        <v>1.65965890884399</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G175" t="n">
-        <v>1.67043590545654</v>
+        <v>1.67043578624725</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>1.86800003051758</v>
       </c>
       <c r="G177" t="n">
-        <v>1.67762064933777</v>
+        <v>1.67762053012848</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>1.85099995136261</v>
       </c>
       <c r="G178" t="n">
-        <v>1.66235315799713</v>
+        <v>1.66235303878784</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G180" t="n">
-        <v>1.67043590545654</v>
+        <v>1.67043578624725</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G181" t="n">
-        <v>1.68839752674103</v>
+        <v>1.68839764595032</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G184" t="n">
-        <v>1.63451254367828</v>
+        <v>1.63451278209686</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>1.80400002002716</v>
       </c>
       <c r="G185" t="n">
-        <v>1.62014317512512</v>
+        <v>1.62014329433441</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>1.80099999904633</v>
       </c>
       <c r="G187" t="n">
-        <v>1.61744892597198</v>
+        <v>1.61744904518127</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>1.80200004577637</v>
       </c>
       <c r="G192" t="n">
-        <v>1.61834692955017</v>
+        <v>1.61834716796875</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>1.80200004577637</v>
       </c>
       <c r="G193" t="n">
-        <v>1.61834692955017</v>
+        <v>1.61834716796875</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G194" t="n">
-        <v>1.63451254367828</v>
+        <v>1.63451278209686</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G195" t="n">
-        <v>1.63451254367828</v>
+        <v>1.63451278209686</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>1.83299994468689</v>
       </c>
       <c r="G196" t="n">
-        <v>1.64618766307831</v>
+        <v>1.64618754386902</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>1.89699995517731</v>
       </c>
       <c r="G197" t="n">
-        <v>1.70366501808167</v>
+        <v>1.70366489887238</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G199" t="n">
-        <v>1.6973785161972</v>
+        <v>1.69737839698792</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G200" t="n">
-        <v>1.68839752674103</v>
+        <v>1.68839764595032</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G201" t="n">
-        <v>1.67043590545654</v>
+        <v>1.67043578624725</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G202" t="n">
-        <v>1.66145503520966</v>
+        <v>1.66145515441895</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G204" t="n">
-        <v>1.66145503520966</v>
+        <v>1.66145515441895</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G207" t="n">
-        <v>1.64349329471588</v>
+        <v>1.64349341392517</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G208" t="n">
-        <v>1.63451254367828</v>
+        <v>1.63451278209686</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G210" t="n">
-        <v>1.66145503520966</v>
+        <v>1.66145515441895</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G211" t="n">
-        <v>1.65247428417206</v>
+        <v>1.65247416496277</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>1.86899995803833</v>
       </c>
       <c r="G212" t="n">
-        <v>1.67851877212524</v>
+        <v>1.67851853370667</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>1.86899995803833</v>
       </c>
       <c r="G213" t="n">
-        <v>1.67851877212524</v>
+        <v>1.67851853370667</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G214" t="n">
-        <v>1.65247428417206</v>
+        <v>1.65247416496277</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>1.86800003051758</v>
       </c>
       <c r="G215" t="n">
-        <v>1.67762064933777</v>
+        <v>1.67762053012848</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>1.8289999961853</v>
       </c>
       <c r="G216" t="n">
-        <v>1.64259517192841</v>
+        <v>1.64259541034698</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G217" t="n">
-        <v>1.63451254367828</v>
+        <v>1.63451278209686</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G218" t="n">
-        <v>1.64349329471588</v>
+        <v>1.64349341392517</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>1.83700001239777</v>
       </c>
       <c r="G219" t="n">
-        <v>1.64977991580963</v>
+        <v>1.64978003501892</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>1.80200004577637</v>
       </c>
       <c r="G221" t="n">
-        <v>1.61834692955017</v>
+        <v>1.61834716796875</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>1.83700001239777</v>
       </c>
       <c r="G222" t="n">
-        <v>1.64977991580963</v>
+        <v>1.64978003501892</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>1.84800004959106</v>
       </c>
       <c r="G223" t="n">
-        <v>1.6596587896347</v>
+        <v>1.65965890884399</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>1.74600005149841</v>
       </c>
       <c r="G224" t="n">
-        <v>1.56805431842804</v>
+        <v>1.56805443763733</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>1.65799999237061</v>
       </c>
       <c r="G228" t="n">
-        <v>1.48902297019958</v>
+        <v>1.48902308940887</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G230" t="n">
-        <v>1.42795324325562</v>
+        <v>1.4279533624649</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>1.52199995517731</v>
       </c>
       <c r="G237" t="n">
-        <v>1.36688339710236</v>
+        <v>1.36688351631165</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>1.5</v>
       </c>
       <c r="G238" t="n">
-        <v>1.34712588787079</v>
+        <v>1.34712564945221</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>1.58200001716614</v>
       </c>
       <c r="G240" t="n">
-        <v>1.42076873779297</v>
+        <v>1.42076861858368</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>1.67900002002716</v>
       </c>
       <c r="G246" t="n">
-        <v>1.50788283348083</v>
+        <v>1.50788271427155</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>1.70200002193451</v>
       </c>
       <c r="G248" t="n">
-        <v>1.52853858470917</v>
+        <v>1.52853870391846</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G249" t="n">
-        <v>1.54470407962799</v>
+        <v>1.54470419883728</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G250" t="n">
-        <v>1.54470407962799</v>
+        <v>1.54470419883728</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G262" t="n">
-        <v>1.64349329471588</v>
+        <v>1.64349341392517</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G263" t="n">
-        <v>1.65247428417206</v>
+        <v>1.65247416496277</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G267" t="n">
-        <v>1.65247428417206</v>
+        <v>1.65247416496277</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G269" t="n">
-        <v>1.63451254367828</v>
+        <v>1.63451278209686</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>1.80099999904633</v>
       </c>
       <c r="G270" t="n">
-        <v>1.61744892597198</v>
+        <v>1.61744904518127</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>1.72399997711182</v>
       </c>
       <c r="G273" t="n">
-        <v>1.5482964515686</v>
+        <v>1.54829633235931</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>1.70200002193451</v>
       </c>
       <c r="G275" t="n">
-        <v>1.52853858470917</v>
+        <v>1.52853870391846</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>1.69599997997284</v>
       </c>
       <c r="G276" t="n">
-        <v>1.52315008640289</v>
+        <v>1.52315020561218</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G278" t="n">
-        <v>1.50878071784973</v>
+        <v>1.50878083705902</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G279" t="n">
-        <v>1.50878071784973</v>
+        <v>1.50878083705902</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G280" t="n">
-        <v>1.54470407962799</v>
+        <v>1.54470419883728</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>1.72599995136261</v>
       </c>
       <c r="G281" t="n">
-        <v>1.55009245872498</v>
+        <v>1.55009269714355</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G282" t="n">
-        <v>1.54470407962799</v>
+        <v>1.54470419883728</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G284" t="n">
-        <v>1.48183822631836</v>
+        <v>1.48183834552765</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>1.56200003623962</v>
       </c>
       <c r="G289" t="n">
-        <v>1.40280699729919</v>
+        <v>1.4028068780899</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>1.48599994182587</v>
       </c>
       <c r="G292" t="n">
-        <v>1.33455240726471</v>
+        <v>1.334552526474</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>1.46700000762939</v>
       </c>
       <c r="G293" t="n">
-        <v>1.31748902797699</v>
+        <v>1.3174889087677</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>1.47800004482269</v>
       </c>
       <c r="G297" t="n">
-        <v>1.32736802101135</v>
+        <v>1.32736790180206</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G298" t="n">
-        <v>1.33814489841461</v>
+        <v>1.3381450176239</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>1.55299997329712</v>
       </c>
       <c r="G299" t="n">
-        <v>1.39472424983978</v>
+        <v>1.39472413063049</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G300" t="n">
-        <v>1.42795324325562</v>
+        <v>1.4279533624649</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>1.5789999961853</v>
       </c>
       <c r="G301" t="n">
-        <v>1.41807436943054</v>
+        <v>1.41807425022125</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>1.58599996566772</v>
       </c>
       <c r="G302" t="n">
-        <v>1.42436099052429</v>
+        <v>1.424360871315</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G303" t="n">
-        <v>1.40999162197113</v>
+        <v>1.40999150276184</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>1.58200001716614</v>
       </c>
       <c r="G305" t="n">
-        <v>1.42076873779297</v>
+        <v>1.42076861858368</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G306" t="n">
-        <v>1.40999162197113</v>
+        <v>1.40999150276184</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G308" t="n">
-        <v>1.39203000068665</v>
+        <v>1.39202988147736</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G309" t="n">
-        <v>1.37406826019287</v>
+        <v>1.37406814098358</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>1.53900003433228</v>
       </c>
       <c r="G310" t="n">
-        <v>1.38215112686157</v>
+        <v>1.38215100765228</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>1.54499995708466</v>
       </c>
       <c r="G312" t="n">
-        <v>1.38753938674927</v>
+        <v>1.38753950595856</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G314" t="n">
-        <v>1.39652025699615</v>
+        <v>1.39652037620544</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G315" t="n">
-        <v>1.39203000068665</v>
+        <v>1.39202988147736</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G316" t="n">
-        <v>1.41448199748993</v>
+        <v>1.41448211669922</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>1.62600004673004</v>
       </c>
       <c r="G320" t="n">
-        <v>1.46028423309326</v>
+        <v>1.46028435230255</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>1.62300002574921</v>
       </c>
       <c r="G321" t="n">
-        <v>1.45758998394012</v>
+        <v>1.45759010314941</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>1.65199995040894</v>
       </c>
       <c r="G326" t="n">
-        <v>1.48363447189331</v>
+        <v>1.48363435268402</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>1.63399994373322</v>
       </c>
       <c r="G327" t="n">
-        <v>1.4674688577652</v>
+        <v>1.46746897697449</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>1.56299996376038</v>
       </c>
       <c r="G331" t="n">
-        <v>1.40370500087738</v>
+        <v>1.40370512008667</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>1.56299996376038</v>
       </c>
       <c r="G332" t="n">
-        <v>1.40370500087738</v>
+        <v>1.40370512008667</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>1.60300004482269</v>
       </c>
       <c r="G334" t="n">
-        <v>1.43962848186493</v>
+        <v>1.43962824344635</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>1.63399994373322</v>
       </c>
       <c r="G336" t="n">
-        <v>1.4674688577652</v>
+        <v>1.46746897697449</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G341" t="n">
-        <v>1.48183822631836</v>
+        <v>1.48183834552765</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>1.67900002002716</v>
       </c>
       <c r="G343" t="n">
-        <v>1.50788283348083</v>
+        <v>1.50788271427155</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>1.67900002002716</v>
       </c>
       <c r="G345" t="n">
-        <v>1.50788283348083</v>
+        <v>1.50788271427155</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>1.70099997520447</v>
       </c>
       <c r="G346" t="n">
-        <v>1.52764046192169</v>
+        <v>1.52764058113098</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G348" t="n">
-        <v>1.51776158809662</v>
+        <v>1.51776170730591</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>1.89199995994568</v>
       </c>
       <c r="G351" t="n">
-        <v>1.69917464256287</v>
+        <v>1.69917452335358</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>1.85399997234344</v>
       </c>
       <c r="G352" t="n">
-        <v>1.66504740715027</v>
+        <v>1.66504728794098</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>1.80099999904633</v>
       </c>
       <c r="G353" t="n">
-        <v>1.61744892597198</v>
+        <v>1.61744904518127</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>1.78699994087219</v>
       </c>
       <c r="G354" t="n">
-        <v>1.60487568378448</v>
+        <v>1.60487580299377</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G355" t="n">
-        <v>1.65247428417206</v>
+        <v>1.65247416496277</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G357" t="n">
-        <v>1.74228274822235</v>
+        <v>1.74228262901306</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G358" t="n">
-        <v>1.73330175876617</v>
+        <v>1.73330163955688</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G359" t="n">
-        <v>1.72432088851929</v>
+        <v>1.72432100772858</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G360" t="n">
-        <v>1.72432088851929</v>
+        <v>1.72432100772858</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>1.8860000371933</v>
       </c>
       <c r="G362" t="n">
-        <v>1.69378626346588</v>
+        <v>1.69378614425659</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G364" t="n">
-        <v>1.71534013748169</v>
+        <v>1.7153400182724</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G365" t="n">
-        <v>1.66145503520966</v>
+        <v>1.66145515441895</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G371" t="n">
-        <v>1.63900291919708</v>
+        <v>1.63900303840637</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G372" t="n">
-        <v>1.65247428417206</v>
+        <v>1.65247416496277</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>1.83700001239777</v>
       </c>
       <c r="G373" t="n">
-        <v>1.64977991580963</v>
+        <v>1.64978003501892</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>1.83899998664856</v>
       </c>
       <c r="G375" t="n">
-        <v>1.65157604217529</v>
+        <v>1.65157616138458</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>1.84200000762939</v>
       </c>
       <c r="G376" t="n">
-        <v>1.65427029132843</v>
+        <v>1.65427041053772</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G377" t="n">
-        <v>1.64349329471588</v>
+        <v>1.64349341392517</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>1.81200003623962</v>
       </c>
       <c r="G378" t="n">
-        <v>1.62732779979706</v>
+        <v>1.62732791900635</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>1.80400002002716</v>
       </c>
       <c r="G380" t="n">
-        <v>1.62014317512512</v>
+        <v>1.62014329433441</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>1.7610000371933</v>
       </c>
       <c r="G381" t="n">
-        <v>1.58152568340302</v>
+        <v>1.58152556419373</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>1.71700000762939</v>
       </c>
       <c r="G387" t="n">
-        <v>1.54200983047485</v>
+        <v>1.54200994968414</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G394" t="n">
-        <v>1.60757005214691</v>
+        <v>1.60756993293762</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>1.78799998760223</v>
       </c>
       <c r="G396" t="n">
-        <v>1.60577380657196</v>
+        <v>1.60577392578125</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>1.7610000371933</v>
       </c>
       <c r="G399" t="n">
-        <v>1.58152568340302</v>
+        <v>1.58152556419373</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>1.75300002098083</v>
       </c>
       <c r="G402" t="n">
-        <v>1.5743408203125</v>
+        <v>1.57434093952179</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>1.77799999713898</v>
       </c>
       <c r="G403" t="n">
-        <v>1.59679293632507</v>
+        <v>1.59679305553436</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>1.78299999237061</v>
       </c>
       <c r="G404" t="n">
-        <v>1.60128343105316</v>
+        <v>1.60128355026245</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G406" t="n">
-        <v>1.60757005214691</v>
+        <v>1.60756993293762</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G407" t="n">
-        <v>1.63451254367828</v>
+        <v>1.63451278209686</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>1.80400002002716</v>
       </c>
       <c r="G409" t="n">
-        <v>1.62014317512512</v>
+        <v>1.62014329433441</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>1.80099999904633</v>
       </c>
       <c r="G412" t="n">
-        <v>1.61744892597198</v>
+        <v>1.61744904518127</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>1.75899994373322</v>
       </c>
       <c r="G417" t="n">
-        <v>1.57972931861877</v>
+        <v>1.57972943782806</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>1.73699998855591</v>
       </c>
       <c r="G418" t="n">
-        <v>1.55997157096863</v>
+        <v>1.55997169017792</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G422" t="n">
-        <v>1.60757005214691</v>
+        <v>1.60756993293762</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>1.8309999704361</v>
       </c>
       <c r="G423" t="n">
-        <v>1.64439129829407</v>
+        <v>1.64439141750336</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G425" t="n">
-        <v>1.72432088851929</v>
+        <v>1.72432100772858</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>1.87899994850159</v>
       </c>
       <c r="G427" t="n">
-        <v>1.68749952316284</v>
+        <v>1.68749940395355</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>1.88199996948242</v>
       </c>
       <c r="G428" t="n">
-        <v>1.69019377231598</v>
+        <v>1.69019365310669</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>1.85300004482269</v>
       </c>
       <c r="G429" t="n">
-        <v>1.66414928436279</v>
+        <v>1.66414940357208</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G433" t="n">
-        <v>1.81412923336029</v>
+        <v>1.81412935256958</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G434" t="n">
-        <v>1.88597595691681</v>
+        <v>1.88597583770752</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>2.19600009918213</v>
       </c>
       <c r="G435" t="n">
-        <v>1.97219228744507</v>
+        <v>1.97219216823578</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>2.24600005149841</v>
       </c>
       <c r="G436" t="n">
-        <v>2.01709628105164</v>
+        <v>2.01709651947021</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>2.41199994087219</v>
       </c>
       <c r="G438" t="n">
-        <v>2.16617822647095</v>
+        <v>2.16617846488953</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>2.53600001335144</v>
       </c>
       <c r="G448" t="n">
-        <v>2.27754044532776</v>
+        <v>2.27754068374634</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G449" t="n">
-        <v>2.343998670578</v>
+        <v>2.34399843215942</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>2.61400008201599</v>
       </c>
       <c r="G450" t="n">
-        <v>2.34759092330933</v>
+        <v>2.34759116172791</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G451" t="n">
-        <v>2.30807518959045</v>
+        <v>2.30807542800903</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>2.49600005149841</v>
       </c>
       <c r="G453" t="n">
-        <v>2.24161720275879</v>
+        <v>2.24161744117737</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G454" t="n">
-        <v>2.26317095756531</v>
+        <v>2.26317143440247</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G455" t="n">
-        <v>2.20030522346497</v>
+        <v>2.20030546188354</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>2.50600004196167</v>
       </c>
       <c r="G458" t="n">
-        <v>2.25059795379639</v>
+        <v>2.25059819221497</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>2.86199998855591</v>
       </c>
       <c r="G463" t="n">
-        <v>2.57031607627869</v>
+        <v>2.57031583786011</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>2.75</v>
       </c>
       <c r="G467" t="n">
-        <v>2.46973061561584</v>
+        <v>2.46973037719727</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G468" t="n">
-        <v>2.50565385818481</v>
+        <v>2.50565361976624</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>2.84400010108948</v>
       </c>
       <c r="G469" t="n">
-        <v>2.55415058135986</v>
+        <v>2.55415034294128</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G472" t="n">
-        <v>2.55055785179138</v>
+        <v>2.55055809020996</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>2.7739999294281</v>
       </c>
       <c r="G473" t="n">
-        <v>2.49128437042236</v>
+        <v>2.49128460884094</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>2.89800000190735</v>
       </c>
       <c r="G475" t="n">
-        <v>2.60264706611633</v>
+        <v>2.60264658927917</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>2.42400002479553</v>
       </c>
       <c r="G478" t="n">
-        <v>2.17695498466492</v>
+        <v>2.1769552230835</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>2.48799991607666</v>
       </c>
       <c r="G486" t="n">
-        <v>2.23443245887756</v>
+        <v>2.23443269729614</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>2.62199997901917</v>
       </c>
       <c r="G490" t="n">
-        <v>2.35477542877197</v>
+        <v>2.35477566719055</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>2.51399993896484</v>
       </c>
       <c r="G492" t="n">
-        <v>2.25778245925903</v>
+        <v>2.25778269767761</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G494" t="n">
-        <v>2.20928621292114</v>
+        <v>2.20928645133972</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G497" t="n">
-        <v>2.20928621292114</v>
+        <v>2.20928645133972</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>2.51399993896484</v>
       </c>
       <c r="G498" t="n">
-        <v>2.25778245925903</v>
+        <v>2.25778269767761</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>2.5220000743866</v>
       </c>
       <c r="G506" t="n">
-        <v>2.26496720314026</v>
+        <v>2.26496744155884</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>2.45199990272522</v>
       </c>
       <c r="G508" t="n">
-        <v>2.20210146903992</v>
+        <v>2.20210123062134</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>2.43799996376038</v>
       </c>
       <c r="G509" t="n">
-        <v>2.189528465271</v>
+        <v>2.18952822685242</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>2.42199993133545</v>
       </c>
       <c r="G511" t="n">
-        <v>2.17515873908997</v>
+        <v>2.17515897750854</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G513" t="n">
-        <v>2.18234348297119</v>
+        <v>2.18234395980835</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G518" t="n">
-        <v>2.21826672554016</v>
+        <v>2.21826696395874</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>2.43499994277954</v>
       </c>
       <c r="G519" t="n">
-        <v>2.18683409690857</v>
+        <v>2.18683385848999</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G523" t="n">
-        <v>2.12845826148987</v>
+        <v>2.12845849990845</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G524" t="n">
-        <v>2.04763126373291</v>
+        <v>2.04763102531433</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G527" t="n">
-        <v>2.0925350189209</v>
+        <v>2.09253525733948</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G528" t="n">
-        <v>2.0835542678833</v>
+        <v>2.08355474472046</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G530" t="n">
-        <v>2.10151624679565</v>
+        <v>2.1015157699585</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>2.41499996185303</v>
       </c>
       <c r="G531" t="n">
-        <v>2.16887259483337</v>
+        <v>2.16887235641479</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G532" t="n">
-        <v>2.12845826148987</v>
+        <v>2.12845849990845</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G534" t="n">
-        <v>2.13743948936462</v>
+        <v>2.1374397277832</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G535" t="n">
-        <v>2.11947774887085</v>
+        <v>2.11947751045227</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>2.26500010490417</v>
       </c>
       <c r="G540" t="n">
-        <v>2.03416013717651</v>
+        <v>2.03415989875793</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>2.36500000953674</v>
       </c>
       <c r="G541" t="n">
-        <v>2.12396836280823</v>
+        <v>2.12396812438965</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>2.34500002861023</v>
       </c>
       <c r="G543" t="n">
-        <v>2.10600638389587</v>
+        <v>2.10600662231445</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G546" t="n">
-        <v>2.10151624679565</v>
+        <v>2.1015157699585</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G551" t="n">
-        <v>2.04763126373291</v>
+        <v>2.04763102531433</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>2.14499998092651</v>
       </c>
       <c r="G553" t="n">
-        <v>1.92638957500458</v>
+        <v>1.92638969421387</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G554" t="n">
-        <v>1.87699508666992</v>
+        <v>1.87699496746063</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G555" t="n">
-        <v>1.903937458992</v>
+        <v>1.90393769741058</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G557" t="n">
-        <v>1.91291880607605</v>
+        <v>1.91291868686676</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G559" t="n">
-        <v>1.94884181022644</v>
+        <v>1.94884204864502</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G560" t="n">
-        <v>1.98476529121399</v>
+        <v>1.9847651720047</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G566" t="n">
-        <v>1.99374604225159</v>
+        <v>1.9937459230423</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G570" t="n">
-        <v>1.94884181022644</v>
+        <v>1.94884204864502</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>2.15499997138977</v>
       </c>
       <c r="G571" t="n">
-        <v>1.93537068367004</v>
+        <v>1.93537056446075</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G572" t="n">
-        <v>1.91291880607605</v>
+        <v>1.91291868686676</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>2.15499997138977</v>
       </c>
       <c r="G573" t="n">
-        <v>1.93537068367004</v>
+        <v>1.93537056446075</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G574" t="n">
-        <v>1.93986117839813</v>
+        <v>1.93986105918884</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G575" t="n">
-        <v>1.98476529121399</v>
+        <v>1.9847651720047</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G576" t="n">
-        <v>1.98476529121399</v>
+        <v>1.9847651720047</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>2.26500010490417</v>
       </c>
       <c r="G579" t="n">
-        <v>2.03416013717651</v>
+        <v>2.03415989875793</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>2.26500010490417</v>
       </c>
       <c r="G580" t="n">
-        <v>2.03416013717651</v>
+        <v>2.03415989875793</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>2.23499989509583</v>
       </c>
       <c r="G581" t="n">
-        <v>2.00721740722656</v>
+        <v>2.00721716880798</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G583" t="n">
-        <v>2.03865003585815</v>
+        <v>2.03865027427673</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>2.24499988555908</v>
       </c>
       <c r="G584" t="n">
-        <v>2.01619791984558</v>
+        <v>2.01619815826416</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G585" t="n">
-        <v>2.04763126373291</v>
+        <v>2.04763102531433</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G586" t="n">
-        <v>2.0835542678833</v>
+        <v>2.08355474472046</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G596" t="n">
-        <v>2.0835542678833</v>
+        <v>2.08355474472046</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>2.47499990463257</v>
       </c>
       <c r="G602" t="n">
-        <v>2.22275733947754</v>
+        <v>2.22275757789612</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G603" t="n">
-        <v>2.21826672554016</v>
+        <v>2.21826696395874</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G604" t="n">
-        <v>2.20030522346497</v>
+        <v>2.20030546188354</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G605" t="n">
-        <v>2.11947774887085</v>
+        <v>2.11947751045227</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>2.26500010490417</v>
       </c>
       <c r="G609" t="n">
-        <v>2.03416013717651</v>
+        <v>2.03415989875793</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>2.24499988555908</v>
       </c>
       <c r="G610" t="n">
-        <v>2.01619791984558</v>
+        <v>2.01619815826416</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>2.22499990463257</v>
       </c>
       <c r="G613" t="n">
-        <v>1.9982362985611</v>
+        <v>1.99823653697968</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G614" t="n">
-        <v>1.93986117839813</v>
+        <v>1.93986105918884</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>2.15499997138977</v>
       </c>
       <c r="G615" t="n">
-        <v>1.93537068367004</v>
+        <v>1.93537056446075</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G617" t="n">
-        <v>2.04763126373291</v>
+        <v>2.04763102531433</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G621" t="n">
-        <v>2.04763126373291</v>
+        <v>2.04763102531433</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G627" t="n">
-        <v>2.04763126373291</v>
+        <v>2.04763102531433</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G629" t="n">
-        <v>2.02517938613892</v>
+        <v>2.02517914772034</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>2.26500010490417</v>
       </c>
       <c r="G630" t="n">
-        <v>2.03416013717651</v>
+        <v>2.03415989875793</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G631" t="n">
-        <v>1.99374604225159</v>
+        <v>1.9937459230423</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G636" t="n">
-        <v>1.95782279968262</v>
+        <v>1.95782291889191</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G637" t="n">
-        <v>1.93986117839813</v>
+        <v>1.93986105918884</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>2.24499988555908</v>
       </c>
       <c r="G638" t="n">
-        <v>2.01619791984558</v>
+        <v>2.01619815826416</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G639" t="n">
-        <v>1.99374604225159</v>
+        <v>1.9937459230423</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>2.22499990463257</v>
       </c>
       <c r="G640" t="n">
-        <v>1.9982362985611</v>
+        <v>1.99823653697968</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G641" t="n">
-        <v>1.99374604225159</v>
+        <v>1.9937459230423</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G643" t="n">
-        <v>1.99374604225159</v>
+        <v>1.9937459230423</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G644" t="n">
-        <v>1.96680355072021</v>
+        <v>1.96680378913879</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G645" t="n">
-        <v>1.95782279968262</v>
+        <v>1.95782291889191</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G646" t="n">
-        <v>1.96680355072021</v>
+        <v>1.96680378913879</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>2.1949999332428</v>
       </c>
       <c r="G647" t="n">
-        <v>1.97129380702972</v>
+        <v>1.97129392623901</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G648" t="n">
-        <v>1.96680355072021</v>
+        <v>1.96680378913879</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G649" t="n">
-        <v>1.95782279968262</v>
+        <v>1.95782291889191</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>2.18499994277954</v>
       </c>
       <c r="G650" t="n">
-        <v>1.96231305599213</v>
+        <v>1.96231317520142</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>2.20499992370605</v>
       </c>
       <c r="G651" t="n">
-        <v>1.9802747964859</v>
+        <v>1.98027467727661</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>2.13499999046326</v>
       </c>
       <c r="G652" t="n">
-        <v>1.91740894317627</v>
+        <v>1.91740882396698</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G653" t="n">
-        <v>1.95782279968262</v>
+        <v>1.95782291889191</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>2.15499997138977</v>
       </c>
       <c r="G654" t="n">
-        <v>1.93537068367004</v>
+        <v>1.93537056446075</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G655" t="n">
-        <v>1.94884181022644</v>
+        <v>1.94884204864502</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G656" t="n">
-        <v>1.8949568271637</v>
+        <v>1.89495670795441</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G658" t="n">
-        <v>1.8949568271637</v>
+        <v>1.89495670795441</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G661" t="n">
-        <v>1.903937458992</v>
+        <v>1.90393769741058</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G662" t="n">
-        <v>1.903937458992</v>
+        <v>1.90393769741058</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>2.125</v>
       </c>
       <c r="G663" t="n">
-        <v>1.90842807292938</v>
+        <v>1.90842819213867</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>2.14499998092651</v>
       </c>
       <c r="G666" t="n">
-        <v>1.92638957500458</v>
+        <v>1.92638969421387</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G667" t="n">
-        <v>1.903937458992</v>
+        <v>1.90393769741058</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>2.09500002861023</v>
       </c>
       <c r="G668" t="n">
-        <v>1.88148558139801</v>
+        <v>1.8814857006073</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>2.14499998092651</v>
       </c>
       <c r="G669" t="n">
-        <v>1.92638957500458</v>
+        <v>1.92638969421387</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G672" t="n">
-        <v>1.95782279968262</v>
+        <v>1.95782291889191</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G674" t="n">
-        <v>1.96680355072021</v>
+        <v>1.96680378913879</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G677" t="n">
-        <v>2.03865003585815</v>
+        <v>2.03865027427673</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G678" t="n">
-        <v>2.03865003585815</v>
+        <v>2.03865027427673</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G681" t="n">
-        <v>1.99374604225159</v>
+        <v>1.9937459230423</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G682" t="n">
-        <v>1.94884181022644</v>
+        <v>1.94884204864502</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>2.17499995231628</v>
       </c>
       <c r="G683" t="n">
-        <v>1.95333230495453</v>
+        <v>1.95333206653595</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G684" t="n">
-        <v>1.96680355072021</v>
+        <v>1.96680378913879</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>2.26500010490417</v>
       </c>
       <c r="G690" t="n">
-        <v>2.03416013717651</v>
+        <v>2.03415989875793</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G691" t="n">
-        <v>2.03865003585815</v>
+        <v>2.03865027427673</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G692" t="n">
-        <v>2.02517938613892</v>
+        <v>2.02517914772034</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>2.23499989509583</v>
       </c>
       <c r="G693" t="n">
-        <v>2.00721740722656</v>
+        <v>2.00721716880798</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G702" t="n">
-        <v>2.02517938613892</v>
+        <v>2.02517914772034</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G703" t="n">
-        <v>2.03865003585815</v>
+        <v>2.03865027427673</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G705" t="n">
-        <v>2.02517938613892</v>
+        <v>2.02517914772034</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G707" t="n">
-        <v>1.91291880607605</v>
+        <v>1.91291868686676</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G712" t="n">
-        <v>1.85903346538544</v>
+        <v>1.85903334617615</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G715" t="n">
-        <v>1.8051483631134</v>
+        <v>1.80514848232269</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G717" t="n">
-        <v>1.76024436950684</v>
+        <v>1.76024425029755</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G718" t="n">
-        <v>1.75126349925995</v>
+        <v>1.75126361846924</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G721" t="n">
-        <v>1.65247428417206</v>
+        <v>1.65247416496277</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G722" t="n">
-        <v>1.65247428417206</v>
+        <v>1.65247416496277</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>1.89400005340576</v>
       </c>
       <c r="G724" t="n">
-        <v>1.70097088813782</v>
+        <v>1.70097076892853</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G725" t="n">
-        <v>1.76024436950684</v>
+        <v>1.76024425029755</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>1.81599998474121</v>
       </c>
       <c r="G727" t="n">
-        <v>1.63092017173767</v>
+        <v>1.63092029094696</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>1.83399999141693</v>
       </c>
       <c r="G728" t="n">
-        <v>1.64708566665649</v>
+        <v>1.64708578586578</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G729" t="n">
-        <v>1.63451254367828</v>
+        <v>1.63451278209686</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>1.81599998474121</v>
       </c>
       <c r="G730" t="n">
-        <v>1.63092017173767</v>
+        <v>1.63092029094696</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G731" t="n">
-        <v>1.63451254367828</v>
+        <v>1.63451278209686</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G732" t="n">
-        <v>1.63451254367828</v>
+        <v>1.63451278209686</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>1.76199996471405</v>
       </c>
       <c r="G733" t="n">
-        <v>1.58242356777191</v>
+        <v>1.5824236869812</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>1.75</v>
       </c>
       <c r="G734" t="n">
-        <v>1.57164669036865</v>
+        <v>1.57164680957794</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>1.72599995136261</v>
       </c>
       <c r="G735" t="n">
-        <v>1.55009245872498</v>
+        <v>1.55009269714355</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>1.65400004386902</v>
       </c>
       <c r="G736" t="n">
-        <v>1.48543071746826</v>
+        <v>1.48543059825897</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>1.65199995040894</v>
       </c>
       <c r="G737" t="n">
-        <v>1.48363447189331</v>
+        <v>1.48363435268402</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G739" t="n">
-        <v>1.42795324325562</v>
+        <v>1.4279533624649</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>1.59800004959106</v>
       </c>
       <c r="G740" t="n">
-        <v>1.43513786792755</v>
+        <v>1.43513798713684</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>1.55599999427795</v>
       </c>
       <c r="G741" t="n">
-        <v>1.39741849899292</v>
+        <v>1.39741837978363</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>1.57400000095367</v>
       </c>
       <c r="G742" t="n">
-        <v>1.41358387470245</v>
+        <v>1.41358399391174</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>1.57200002670288</v>
       </c>
       <c r="G743" t="n">
-        <v>1.41178774833679</v>
+        <v>1.41178786754608</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G747" t="n">
-        <v>1.39203000068665</v>
+        <v>1.39202988147736</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>1.46599996089935</v>
       </c>
       <c r="G751" t="n">
-        <v>1.31659078598022</v>
+        <v>1.31659090518951</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G752" t="n">
-        <v>1.30222165584564</v>
+        <v>1.30222153663635</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G754" t="n">
-        <v>1.22139406204224</v>
+        <v>1.22139418125153</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>1.29200005531311</v>
       </c>
       <c r="G758" t="n">
-        <v>1.16032433509827</v>
+        <v>1.16032421588898</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>1.30400002002716</v>
       </c>
       <c r="G763" t="n">
-        <v>1.17110121250153</v>
+        <v>1.17110133171082</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>1.36800003051758</v>
       </c>
       <c r="G764" t="n">
-        <v>1.22857868671417</v>
+        <v>1.22857880592346</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>1.41400003433228</v>
       </c>
       <c r="G765" t="n">
-        <v>1.26989054679871</v>
+        <v>1.269890666008</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>1.52799999713898</v>
       </c>
       <c r="G766" t="n">
-        <v>1.37227213382721</v>
+        <v>1.37227201461792</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G767" t="n">
-        <v>1.40999162197113</v>
+        <v>1.40999150276184</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G768" t="n">
-        <v>1.40999162197113</v>
+        <v>1.40999150276184</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G770" t="n">
-        <v>1.35610663890839</v>
+        <v>1.3561065196991</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>1.51800000667572</v>
       </c>
       <c r="G771" t="n">
-        <v>1.36329114437103</v>
+        <v>1.36329126358032</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>1.47800004482269</v>
       </c>
       <c r="G773" t="n">
-        <v>1.32736802101135</v>
+        <v>1.32736790180206</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G774" t="n">
-        <v>1.33814489841461</v>
+        <v>1.3381450176239</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>1.5</v>
       </c>
       <c r="G776" t="n">
-        <v>1.34712588787079</v>
+        <v>1.34712564945221</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>1.46599996089935</v>
       </c>
       <c r="G779" t="n">
-        <v>1.31659078598022</v>
+        <v>1.31659090518951</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>1.47200000286102</v>
       </c>
       <c r="G780" t="n">
-        <v>1.3219792842865</v>
+        <v>1.32197952270508</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>1.49800002574921</v>
       </c>
       <c r="G782" t="n">
-        <v>1.34532952308655</v>
+        <v>1.34532964229584</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>1.46599996089935</v>
       </c>
       <c r="G785" t="n">
-        <v>1.31659078598022</v>
+        <v>1.31659090518951</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>1.42799997329712</v>
       </c>
       <c r="G788" t="n">
-        <v>1.28246378898621</v>
+        <v>1.28246366977692</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G790" t="n">
-        <v>1.24833643436432</v>
+        <v>1.24833655357361</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G791" t="n">
-        <v>1.23037481307983</v>
+        <v>1.23037469387054</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>1.38800001144409</v>
       </c>
       <c r="G792" t="n">
-        <v>1.24654042720795</v>
+        <v>1.24654030799866</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G795" t="n">
-        <v>1.45489573478699</v>
+        <v>1.45489585399628</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G798" t="n">
-        <v>1.65247428417206</v>
+        <v>1.65247416496277</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G800" t="n">
-        <v>1.65247428417206</v>
+        <v>1.65247416496277</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G801" t="n">
-        <v>1.84107172489166</v>
+        <v>1.84107184410095</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>2.09500002861023</v>
       </c>
       <c r="G802" t="n">
-        <v>1.88148558139801</v>
+        <v>1.8814857006073</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G803" t="n">
-        <v>1.88597595691681</v>
+        <v>1.88597583770752</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>2.14499998092651</v>
       </c>
       <c r="G806" t="n">
-        <v>1.92638957500458</v>
+        <v>1.92638969421387</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G807" t="n">
-        <v>1.85903346538544</v>
+        <v>1.85903334617615</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G811" t="n">
-        <v>1.81412923336029</v>
+        <v>1.81412935256958</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G813" t="n">
-        <v>1.81412923336029</v>
+        <v>1.81412935256958</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G814" t="n">
-        <v>1.8051483631134</v>
+        <v>1.80514848232269</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G818" t="n">
-        <v>1.68839752674103</v>
+        <v>1.68839764595032</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>1.8639999628067</v>
       </c>
       <c r="G819" t="n">
-        <v>1.67402827739716</v>
+        <v>1.67402815818787</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>1.90600001811981</v>
       </c>
       <c r="G820" t="n">
-        <v>1.71174776554108</v>
+        <v>1.71174764633179</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G821" t="n">
-        <v>1.73330175876617</v>
+        <v>1.73330163955688</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>1.87600004673004</v>
       </c>
       <c r="G823" t="n">
-        <v>1.68480539321899</v>
+        <v>1.6848052740097</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>1.90600001811981</v>
       </c>
       <c r="G825" t="n">
-        <v>1.71174776554108</v>
+        <v>1.71174764633179</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G828" t="n">
-        <v>1.99374604225159</v>
+        <v>1.9937459230423</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>2.31500005722046</v>
       </c>
       <c r="G830" t="n">
-        <v>2.07906436920166</v>
+        <v>2.0790638923645</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>2.34500002861023</v>
       </c>
       <c r="G831" t="n">
-        <v>2.10600638389587</v>
+        <v>2.10600662231445</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>2.14499998092651</v>
       </c>
       <c r="G833" t="n">
-        <v>1.92638957500458</v>
+        <v>1.92638969421387</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G834" t="n">
-        <v>1.99374604225159</v>
+        <v>1.9937459230423</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G837" t="n">
-        <v>1.99374604225159</v>
+        <v>1.9937459230423</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G838" t="n">
-        <v>2.13743948936462</v>
+        <v>2.1374397277832</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G840" t="n">
-        <v>2.17336273193359</v>
+        <v>2.17336297035217</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>2.39499998092651</v>
       </c>
       <c r="G845" t="n">
-        <v>2.15091061592102</v>
+        <v>2.1509108543396</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G846" t="n">
-        <v>2.0925350189209</v>
+        <v>2.09253525733948</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>2.46499991416931</v>
       </c>
       <c r="G849" t="n">
-        <v>2.21377682685852</v>
+        <v>2.21377658843994</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>2.36500000953674</v>
       </c>
       <c r="G850" t="n">
-        <v>2.12396836280823</v>
+        <v>2.12396812438965</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G851" t="n">
-        <v>2.04763126373291</v>
+        <v>2.04763102531433</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G852" t="n">
-        <v>1.96680355072021</v>
+        <v>1.96680378913879</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G854" t="n">
-        <v>1.96680355072021</v>
+        <v>1.96680378913879</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G855" t="n">
-        <v>1.95782279968262</v>
+        <v>1.95782291889191</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G856" t="n">
-        <v>1.95782279968262</v>
+        <v>1.95782291889191</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>2.24499988555908</v>
       </c>
       <c r="G859" t="n">
-        <v>2.01619791984558</v>
+        <v>2.01619815826416</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G865" t="n">
-        <v>2.03865003585815</v>
+        <v>2.03865027427673</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>2.22499990463257</v>
       </c>
       <c r="G875" t="n">
-        <v>1.9982362985611</v>
+        <v>1.99823653697968</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G877" t="n">
-        <v>1.85903346538544</v>
+        <v>1.85903334617615</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G878" t="n">
-        <v>1.86801433563232</v>
+        <v>1.86801421642303</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G879" t="n">
-        <v>1.84107172489166</v>
+        <v>1.84107184410095</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G881" t="n">
-        <v>1.81412923336029</v>
+        <v>1.81412935256958</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>2.00500011444092</v>
       </c>
       <c r="G889" t="n">
-        <v>1.80065822601318</v>
+        <v>1.80065810680389</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G891" t="n">
-        <v>1.81412923336029</v>
+        <v>1.81412935256958</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G894" t="n">
-        <v>1.8051483631134</v>
+        <v>1.80514848232269</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>1.99399995803833</v>
       </c>
       <c r="G897" t="n">
-        <v>1.79077911376953</v>
+        <v>1.79077899456024</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G898" t="n">
-        <v>1.81412923336029</v>
+        <v>1.81412935256958</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G899" t="n">
-        <v>1.8051483631134</v>
+        <v>1.80514848232269</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>1.99399995803833</v>
       </c>
       <c r="G901" t="n">
-        <v>1.79077911376953</v>
+        <v>1.79077899456024</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G904" t="n">
-        <v>1.72432088851929</v>
+        <v>1.72432100772858</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>1.92200005054474</v>
       </c>
       <c r="G905" t="n">
-        <v>1.72611725330353</v>
+        <v>1.72611713409424</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>2.1949999332428</v>
       </c>
       <c r="G906" t="n">
-        <v>1.97129380702972</v>
+        <v>1.97129392623901</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G907" t="n">
-        <v>1.95782279968262</v>
+        <v>1.95782291889191</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>2.24499988555908</v>
       </c>
       <c r="G908" t="n">
-        <v>2.01619791984558</v>
+        <v>2.01619815826416</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G909" t="n">
-        <v>1.99374604225159</v>
+        <v>1.9937459230423</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G910" t="n">
-        <v>1.93986117839813</v>
+        <v>1.93986105918884</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>2.20499992370605</v>
       </c>
       <c r="G912" t="n">
-        <v>1.9802747964859</v>
+        <v>1.98027467727661</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G913" t="n">
-        <v>1.94884181022644</v>
+        <v>1.94884204864502</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>2.125</v>
       </c>
       <c r="G914" t="n">
-        <v>1.90842807292938</v>
+        <v>1.90842819213867</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>2.13499999046326</v>
       </c>
       <c r="G915" t="n">
-        <v>1.91740894317627</v>
+        <v>1.91740882396698</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>2.14499998092651</v>
       </c>
       <c r="G917" t="n">
-        <v>1.92638957500458</v>
+        <v>1.92638969421387</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G918" t="n">
-        <v>1.903937458992</v>
+        <v>1.90393769741058</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>2.00500011444092</v>
       </c>
       <c r="G923" t="n">
-        <v>1.80065822601318</v>
+        <v>1.80065810680389</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G925" t="n">
-        <v>1.81412923336029</v>
+        <v>1.81412935256958</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G927" t="n">
-        <v>1.76024436950684</v>
+        <v>1.76024425029755</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>1.94799995422363</v>
       </c>
       <c r="G928" t="n">
-        <v>1.74946737289429</v>
+        <v>1.74946713447571</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G929" t="n">
-        <v>1.76024436950684</v>
+        <v>1.76024425029755</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G930" t="n">
-        <v>1.73330175876617</v>
+        <v>1.73330163955688</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>1.94799995422363</v>
       </c>
       <c r="G932" t="n">
-        <v>1.74946737289429</v>
+        <v>1.74946713447571</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G935" t="n">
-        <v>1.81412923336029</v>
+        <v>1.81412935256958</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G936" t="n">
-        <v>1.85903346538544</v>
+        <v>1.85903334617615</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G937" t="n">
-        <v>1.84556233882904</v>
+        <v>1.84556221961975</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>2.26500010490417</v>
       </c>
       <c r="G940" t="n">
-        <v>2.03416013717651</v>
+        <v>2.03415989875793</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>2.41499996185303</v>
       </c>
       <c r="G942" t="n">
-        <v>2.16887259483337</v>
+        <v>2.16887235641479</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G944" t="n">
-        <v>2.0925350189209</v>
+        <v>2.09253525733948</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>2.31500005722046</v>
       </c>
       <c r="G945" t="n">
-        <v>2.07906436920166</v>
+        <v>2.0790638923645</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G946" t="n">
-        <v>2.03865003585815</v>
+        <v>2.03865027427673</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G947" t="n">
-        <v>1.98476529121399</v>
+        <v>1.9847651720047</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G950" t="n">
-        <v>2.03865003585815</v>
+        <v>2.03865027427673</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G956" t="n">
-        <v>1.96680355072021</v>
+        <v>1.96680378913879</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G957" t="n">
-        <v>1.99374604225159</v>
+        <v>1.9937459230423</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G960" t="n">
-        <v>1.95782279968262</v>
+        <v>1.95782291889191</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G961" t="n">
-        <v>1.98476529121399</v>
+        <v>1.9847651720047</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G962" t="n">
-        <v>1.99374604225159</v>
+        <v>1.9937459230423</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G963" t="n">
-        <v>2.0925350189209</v>
+        <v>2.09253525733948</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G964" t="n">
-        <v>2.0835542678833</v>
+        <v>2.08355474472046</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>2.40499997138977</v>
       </c>
       <c r="G965" t="n">
-        <v>2.1598916053772</v>
+        <v>2.15989136695862</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G967" t="n">
-        <v>2.0925350189209</v>
+        <v>2.09253525733948</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>2.40499997138977</v>
       </c>
       <c r="G968" t="n">
-        <v>2.1598916053772</v>
+        <v>2.15989136695862</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>2.36500000953674</v>
       </c>
       <c r="G969" t="n">
-        <v>2.12396836280823</v>
+        <v>2.12396812438965</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>2.24499988555908</v>
       </c>
       <c r="G973" t="n">
-        <v>2.01619791984558</v>
+        <v>2.01619815826416</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>2.51500010490417</v>
       </c>
       <c r="G977" t="n">
-        <v>2.25868105888367</v>
+        <v>2.25868082046509</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G979" t="n">
-        <v>2.38890314102173</v>
+        <v>2.38890290260315</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G980" t="n">
-        <v>2.49667286872864</v>
+        <v>2.49667310714722</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G983" t="n">
-        <v>2.55055785179138</v>
+        <v>2.55055809020996</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>2.875</v>
       </c>
       <c r="G984" t="n">
-        <v>2.58199095726013</v>
+        <v>2.58199119567871</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>2.96499991416931</v>
       </c>
       <c r="G986" t="n">
-        <v>2.66281819343567</v>
+        <v>2.66281843185425</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G989" t="n">
-        <v>2.79304051399231</v>
+        <v>2.79304075241089</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>2.96499991416931</v>
       </c>
       <c r="G991" t="n">
-        <v>2.66281819343567</v>
+        <v>2.66281843185425</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G994" t="n">
-        <v>2.91428208351135</v>
+        <v>2.91428160667419</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G996" t="n">
-        <v>3.08042764663696</v>
+        <v>3.08042740821838</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G997" t="n">
-        <v>2.95469570159912</v>
+        <v>2.95469546318054</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G998" t="n">
-        <v>2.74364590644836</v>
+        <v>2.74364638328552</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1001" t="n">
-        <v>2.73915576934814</v>
+        <v>2.73915553092957</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>2.96499991416931</v>
       </c>
       <c r="G1003" t="n">
-        <v>2.66281819343567</v>
+        <v>2.66281843185425</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>3.01500010490417</v>
       </c>
       <c r="G1006" t="n">
-        <v>2.70772266387939</v>
+        <v>2.70772290229797</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>3</v>
       </c>
       <c r="G1008" t="n">
-        <v>2.69425177574158</v>
+        <v>2.69425129890442</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1012" t="n">
-        <v>2.78406000137329</v>
+        <v>2.78405976295471</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G1013" t="n">
-        <v>2.78855013847351</v>
+        <v>2.78855037689209</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1014" t="n">
-        <v>2.77507877349854</v>
+        <v>2.77507901191711</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1015" t="n">
-        <v>2.74813652038574</v>
+        <v>2.74813628196716</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>2.92499995231628</v>
       </c>
       <c r="G1018" t="n">
-        <v>2.6268949508667</v>
+        <v>2.62689518928528</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>2.96499991416931</v>
       </c>
       <c r="G1019" t="n">
-        <v>2.66281819343567</v>
+        <v>2.66281843185425</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>2.88499999046326</v>
       </c>
       <c r="G1020" t="n">
-        <v>2.59097170829773</v>
+        <v>2.59097194671631</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1025" t="n">
-        <v>2.95469570159912</v>
+        <v>2.95469546318054</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1026" t="n">
-        <v>2.96367645263672</v>
+        <v>2.9636766910553</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1033" t="n">
-        <v>2.96367645263672</v>
+        <v>2.9636766910553</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>3.5</v>
       </c>
       <c r="G1040" t="n">
-        <v>3.1432933807373</v>
+        <v>3.14329361915588</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1042" t="n">
-        <v>3.24208211898804</v>
+        <v>3.2420825958252</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>3.74499988555908</v>
       </c>
       <c r="G1044" t="n">
-        <v>3.36332392692566</v>
+        <v>3.36332368850708</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>3.85500001907349</v>
       </c>
       <c r="G1045" t="n">
-        <v>3.46211314201355</v>
+        <v>3.46211338043213</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1048" t="n">
-        <v>3.30494856834412</v>
+        <v>3.30494832992554</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>3.375</v>
       </c>
       <c r="G1052" t="n">
-        <v>3.03103303909302</v>
+        <v>3.03103280067444</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1054" t="n">
-        <v>2.85590648651123</v>
+        <v>2.85590672492981</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1056" t="n">
-        <v>2.79304051399231</v>
+        <v>2.79304075241089</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1057" t="n">
-        <v>2.78406000137329</v>
+        <v>2.78405976295471</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G1058" t="n">
-        <v>2.77058863639832</v>
+        <v>2.77058839797974</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G1060" t="n">
-        <v>2.57750058174133</v>
+        <v>2.57750034332275</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G1063" t="n">
-        <v>2.30807518959045</v>
+        <v>2.30807542800903</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>2.39499998092651</v>
       </c>
       <c r="G1065" t="n">
-        <v>2.15091061592102</v>
+        <v>2.1509108543396</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1066" t="n">
-        <v>1.84107172489166</v>
+        <v>1.84107184410095</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>1.99399995803833</v>
       </c>
       <c r="G1068" t="n">
-        <v>1.79077911376953</v>
+        <v>1.79077899456024</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1069" t="n">
-        <v>1.81412923336029</v>
+        <v>1.81412935256958</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1070" t="n">
-        <v>1.86801433563232</v>
+        <v>1.86801421642303</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>1.99399995803833</v>
       </c>
       <c r="G1072" t="n">
-        <v>1.79077911376953</v>
+        <v>1.79077899456024</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>2.16499996185303</v>
       </c>
       <c r="G1074" t="n">
-        <v>1.94435131549835</v>
+        <v>1.94435155391693</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1075" t="n">
-        <v>2.04763126373291</v>
+        <v>2.04763102531433</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G1078" t="n">
-        <v>1.98476529121399</v>
+        <v>1.9847651720047</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1079" t="n">
-        <v>2.04763126373291</v>
+        <v>2.04763102531433</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1082" t="n">
-        <v>2.26317095756531</v>
+        <v>2.26317143440247</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G1083" t="n">
-        <v>2.30807518959045</v>
+        <v>2.30807542800903</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>2.75</v>
       </c>
       <c r="G1086" t="n">
-        <v>2.46973061561584</v>
+        <v>2.46973037719727</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1088" t="n">
-        <v>2.44278812408447</v>
+        <v>2.44278836250305</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>2.86500000953674</v>
       </c>
       <c r="G1093" t="n">
-        <v>2.57300996780396</v>
+        <v>2.57301020622253</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1094" t="n">
-        <v>2.51463460922241</v>
+        <v>2.51463437080383</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>2.86500000953674</v>
       </c>
       <c r="G1095" t="n">
-        <v>2.57300996780396</v>
+        <v>2.57301020622253</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1100" t="n">
-        <v>2.67628979682922</v>
+        <v>2.6762900352478</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -29021,7 +29021,7 @@
         <v>2.92499995231628</v>
       </c>
       <c r="G1102" t="n">
-        <v>2.6268949508667</v>
+        <v>2.62689518928528</v>
       </c>
       <c r="H1102" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>2.86500000953674</v>
       </c>
       <c r="G1108" t="n">
-        <v>2.57300996780396</v>
+        <v>2.57301020622253</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1109" t="n">
-        <v>2.64036655426025</v>
+        <v>2.64036631584167</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>2.96499991416931</v>
       </c>
       <c r="G1110" t="n">
-        <v>2.66281819343567</v>
+        <v>2.66281843185425</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1114" t="n">
-        <v>2.48769235610962</v>
+        <v>2.48769211769104</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>2.86500000953674</v>
       </c>
       <c r="G1117" t="n">
-        <v>2.57300996780396</v>
+        <v>2.57301020622253</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>2.89499998092651</v>
       </c>
       <c r="G1119" t="n">
-        <v>2.59995269775391</v>
+        <v>2.59995245933533</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>2.89499998092651</v>
       </c>
       <c r="G1120" t="n">
-        <v>2.59995269775391</v>
+        <v>2.59995245933533</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1123" t="n">
-        <v>2.60444331169128</v>
+        <v>2.60444307327271</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1124" t="n">
-        <v>2.60444331169128</v>
+        <v>2.60444307327271</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1125" t="n">
-        <v>2.81998324394226</v>
+        <v>2.81998300552368</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1126" t="n">
-        <v>2.74813652038574</v>
+        <v>2.74813628196716</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G1131" t="n">
-        <v>2.57750058174133</v>
+        <v>2.57750034332275</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1133" t="n">
-        <v>2.48769235610962</v>
+        <v>2.48769211769104</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G1134" t="n">
-        <v>2.57750058174133</v>
+        <v>2.57750034332275</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29879,7 +29879,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1135" t="n">
-        <v>2.51463460922241</v>
+        <v>2.51463437080383</v>
       </c>
       <c r="H1135" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G1138" t="n">
-        <v>2.50565385818481</v>
+        <v>2.50565361976624</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1140" t="n">
-        <v>2.44278812408447</v>
+        <v>2.44278836250305</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>2.6949999332428</v>
       </c>
       <c r="G1141" t="n">
-        <v>2.42033576965332</v>
+        <v>2.42033553123474</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1142" t="n">
-        <v>2.43380737304688</v>
+        <v>2.4338071346283</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1143" t="n">
-        <v>2.48769235610962</v>
+        <v>2.48769211769104</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30113,7 +30113,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1144" t="n">
-        <v>2.46074962615967</v>
+        <v>2.46074938774109</v>
       </c>
       <c r="H1144" t="s">
         <v>8</v>
@@ -30191,7 +30191,7 @@
         <v>2.75</v>
       </c>
       <c r="G1147" t="n">
-        <v>2.46973061561584</v>
+        <v>2.46973037719727</v>
       </c>
       <c r="H1147" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G1148" t="n">
-        <v>2.38890314102173</v>
+        <v>2.38890290260315</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G1149" t="n">
-        <v>2.38890314102173</v>
+        <v>2.38890290260315</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1152" t="n">
-        <v>2.41584587097168</v>
+        <v>2.4158456325531</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>2.76500010490417</v>
       </c>
       <c r="G1153" t="n">
-        <v>2.48320174217224</v>
+        <v>2.48320198059082</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1154" t="n">
-        <v>2.46074962615967</v>
+        <v>2.46074938774109</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30425,7 +30425,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1156" t="n">
-        <v>2.48769235610962</v>
+        <v>2.48769211769104</v>
       </c>
       <c r="H1156" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1158" t="n">
-        <v>2.46074962615967</v>
+        <v>2.46074938774109</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1159" t="n">
-        <v>2.41584587097168</v>
+        <v>2.4158456325531</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1160" t="n">
-        <v>2.41584587097168</v>
+        <v>2.4158456325531</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1163" t="n">
-        <v>2.27215170860291</v>
+        <v>2.27215194702148</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30633,7 +30633,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1164" t="n">
-        <v>2.27215170860291</v>
+        <v>2.27215194702148</v>
       </c>
       <c r="H1164" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>2.76500010490417</v>
       </c>
       <c r="G1173" t="n">
-        <v>2.48320174217224</v>
+        <v>2.48320198059082</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1174" t="n">
-        <v>2.44278812408447</v>
+        <v>2.44278836250305</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -30971,7 +30971,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1177" t="n">
-        <v>2.48769235610962</v>
+        <v>2.48769211769104</v>
       </c>
       <c r="H1177" t="s">
         <v>8</v>
@@ -30997,7 +30997,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G1178" t="n">
-        <v>2.38890314102173</v>
+        <v>2.38890290260315</v>
       </c>
       <c r="H1178" t="s">
         <v>8</v>
@@ -31023,7 +31023,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1179" t="n">
-        <v>2.41584587097168</v>
+        <v>2.4158456325531</v>
       </c>
       <c r="H1179" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>2.65499997138977</v>
       </c>
       <c r="G1186" t="n">
-        <v>2.38441228866577</v>
+        <v>2.38441252708435</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>2.67499995231628</v>
       </c>
       <c r="G1188" t="n">
-        <v>2.40237402915955</v>
+        <v>2.40237426757812</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>2.67499995231628</v>
       </c>
       <c r="G1191" t="n">
-        <v>2.40237402915955</v>
+        <v>2.40237426757812</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1193" t="n">
-        <v>2.43380737304688</v>
+        <v>2.4338071346283</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1194" t="n">
-        <v>2.46074962615967</v>
+        <v>2.46074938774109</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G1195" t="n">
-        <v>2.49667286872864</v>
+        <v>2.49667310714722</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>2.76500010490417</v>
       </c>
       <c r="G1197" t="n">
-        <v>2.48320174217224</v>
+        <v>2.48320198059082</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G1203" t="n">
-        <v>2.28113293647766</v>
+        <v>2.28113269805908</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1204" t="n">
-        <v>2.27215170860291</v>
+        <v>2.27215194702148</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1207" t="n">
-        <v>2.27215170860291</v>
+        <v>2.27215194702148</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>2.6949999332428</v>
       </c>
       <c r="G1208" t="n">
-        <v>2.42033576965332</v>
+        <v>2.42033553123474</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1209" t="n">
-        <v>2.31705594062805</v>
+        <v>2.31705641746521</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31907,7 +31907,7 @@
         <v>2.6949999332428</v>
       </c>
       <c r="G1213" t="n">
-        <v>2.42033576965332</v>
+        <v>2.42033553123474</v>
       </c>
       <c r="H1213" t="s">
         <v>8</v>
@@ -32037,7 +32037,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G1218" t="n">
-        <v>2.49667286872864</v>
+        <v>2.49667310714722</v>
       </c>
       <c r="H1218" t="s">
         <v>8</v>
@@ -32115,7 +32115,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1221" t="n">
-        <v>2.60444331169128</v>
+        <v>2.60444307327271</v>
       </c>
       <c r="H1221" t="s">
         <v>8</v>
@@ -32141,7 +32141,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G1222" t="n">
-        <v>2.57750058174133</v>
+        <v>2.57750034332275</v>
       </c>
       <c r="H1222" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>2.86500000953674</v>
       </c>
       <c r="G1223" t="n">
-        <v>2.57300996780396</v>
+        <v>2.57301020622253</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32219,7 +32219,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1225" t="n">
-        <v>2.43380737304688</v>
+        <v>2.4338071346283</v>
       </c>
       <c r="H1225" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1227" t="n">
-        <v>2.27215170860291</v>
+        <v>2.27215194702148</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32349,7 +32349,7 @@
         <v>2.59500002861023</v>
       </c>
       <c r="G1230" t="n">
-        <v>2.33052730560303</v>
+        <v>2.33052754402161</v>
       </c>
       <c r="H1230" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>2.59500002861023</v>
       </c>
       <c r="G1231" t="n">
-        <v>2.33052730560303</v>
+        <v>2.33052754402161</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G1233" t="n">
-        <v>2.343998670578</v>
+        <v>2.34399843215942</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1234" t="n">
-        <v>2.31705594062805</v>
+        <v>2.31705641746521</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1236" t="n">
-        <v>2.43380737304688</v>
+        <v>2.4338071346283</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1237" t="n">
-        <v>2.41584587097168</v>
+        <v>2.4158456325531</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>2.75</v>
       </c>
       <c r="G1239" t="n">
-        <v>2.46973061561584</v>
+        <v>2.46973037719727</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32713,7 +32713,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1244" t="n">
-        <v>2.44278812408447</v>
+        <v>2.44278836250305</v>
       </c>
       <c r="H1244" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1245" t="n">
-        <v>2.44278812408447</v>
+        <v>2.44278836250305</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1250" t="n">
-        <v>2.58648157119751</v>
+        <v>2.58648133277893</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1253" t="n">
-        <v>2.67628979682922</v>
+        <v>2.6762900352478</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>3</v>
       </c>
       <c r="G1254" t="n">
-        <v>2.69425177574158</v>
+        <v>2.69425129890442</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -32999,7 +32999,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1255" t="n">
-        <v>2.74813652038574</v>
+        <v>2.74813628196716</v>
       </c>
       <c r="H1255" t="s">
         <v>8</v>
@@ -33025,7 +33025,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G1256" t="n">
-        <v>2.76160788536072</v>
+        <v>2.76160764694214</v>
       </c>
       <c r="H1256" t="s">
         <v>8</v>
@@ -33051,7 +33051,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1257" t="n">
-        <v>2.73915576934814</v>
+        <v>2.73915553092957</v>
       </c>
       <c r="H1257" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1259" t="n">
-        <v>2.64036655426025</v>
+        <v>2.64036631584167</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33129,7 +33129,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1260" t="n">
-        <v>2.77507877349854</v>
+        <v>2.77507901191711</v>
       </c>
       <c r="H1260" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1261" t="n">
-        <v>2.78406000137329</v>
+        <v>2.78405976295471</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1262" t="n">
-        <v>2.77507877349854</v>
+        <v>2.77507901191711</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33285,7 +33285,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G1266" t="n">
-        <v>2.77058863639832</v>
+        <v>2.77058839797974</v>
       </c>
       <c r="H1266" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G1268" t="n">
-        <v>2.78855013847351</v>
+        <v>2.78855037689209</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33363,7 +33363,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1269" t="n">
-        <v>2.78406000137329</v>
+        <v>2.78405976295471</v>
       </c>
       <c r="H1269" t="s">
         <v>8</v>
@@ -33389,7 +33389,7 @@
         <v>3.09500002861023</v>
       </c>
       <c r="G1270" t="n">
-        <v>2.77956938743591</v>
+        <v>2.77956914901733</v>
       </c>
       <c r="H1270" t="s">
         <v>8</v>
@@ -33415,7 +33415,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1271" t="n">
-        <v>2.77507877349854</v>
+        <v>2.77507901191711</v>
       </c>
       <c r="H1271" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1272" t="n">
-        <v>2.78406000137329</v>
+        <v>2.78405976295471</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33467,7 +33467,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1273" t="n">
-        <v>2.79304051399231</v>
+        <v>2.79304075241089</v>
       </c>
       <c r="H1273" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1274" t="n">
-        <v>2.77507877349854</v>
+        <v>2.77507901191711</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G1275" t="n">
-        <v>2.77058863639832</v>
+        <v>2.77058839797974</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1276" t="n">
-        <v>2.79304051399231</v>
+        <v>2.79304075241089</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33571,7 +33571,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1277" t="n">
-        <v>2.79304051399231</v>
+        <v>2.79304075241089</v>
       </c>
       <c r="H1277" t="s">
         <v>8</v>
@@ -33753,7 +33753,7 @@
         <v>3</v>
       </c>
       <c r="G1284" t="n">
-        <v>2.69425177574158</v>
+        <v>2.69425129890442</v>
       </c>
       <c r="H1284" t="s">
         <v>8</v>
@@ -33779,7 +33779,7 @@
         <v>2.92499995231628</v>
       </c>
       <c r="G1285" t="n">
-        <v>2.6268949508667</v>
+        <v>2.62689518928528</v>
       </c>
       <c r="H1285" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G1286" t="n">
-        <v>2.54606771469116</v>
+        <v>2.54606747627258</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1288" t="n">
-        <v>2.60444331169128</v>
+        <v>2.60444307327271</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33909,7 +33909,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1290" t="n">
-        <v>2.60444331169128</v>
+        <v>2.60444307327271</v>
       </c>
       <c r="H1290" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>3</v>
       </c>
       <c r="G1291" t="n">
-        <v>2.69425177574158</v>
+        <v>2.69425129890442</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -33987,7 +33987,7 @@
         <v>3.04500007629395</v>
       </c>
       <c r="G1293" t="n">
-        <v>2.73466539382935</v>
+        <v>2.73466515541077</v>
       </c>
       <c r="H1293" t="s">
         <v>8</v>
@@ -34013,7 +34013,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G1294" t="n">
-        <v>2.76160788536072</v>
+        <v>2.76160764694214</v>
       </c>
       <c r="H1294" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1295" t="n">
-        <v>2.79304051399231</v>
+        <v>2.79304075241089</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34065,7 +34065,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1296" t="n">
-        <v>2.81998324394226</v>
+        <v>2.81998300552368</v>
       </c>
       <c r="H1296" t="s">
         <v>8</v>
@@ -34091,7 +34091,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1297" t="n">
-        <v>2.81998324394226</v>
+        <v>2.81998300552368</v>
       </c>
       <c r="H1297" t="s">
         <v>8</v>
@@ -34117,7 +34117,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1298" t="n">
-        <v>2.81100225448608</v>
+        <v>2.81100249290466</v>
       </c>
       <c r="H1298" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1299" t="n">
-        <v>3.08940815925598</v>
+        <v>3.08940839767456</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34169,7 +34169,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G1300" t="n">
-        <v>3.12982201576233</v>
+        <v>3.12982177734375</v>
       </c>
       <c r="H1300" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>3.5</v>
       </c>
       <c r="G1301" t="n">
-        <v>3.1432933807373</v>
+        <v>3.14329361915588</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34221,7 +34221,7 @@
         <v>3.49499988555908</v>
       </c>
       <c r="G1302" t="n">
-        <v>3.13880300521851</v>
+        <v>3.13880276679993</v>
       </c>
       <c r="H1302" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>3.41499996185303</v>
       </c>
       <c r="G1303" t="n">
-        <v>3.06695628166199</v>
+        <v>3.06695604324341</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34299,7 +34299,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G1305" t="n">
-        <v>3.12982201576233</v>
+        <v>3.12982177734375</v>
       </c>
       <c r="H1305" t="s">
         <v>8</v>
@@ -34325,7 +34325,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1306" t="n">
-        <v>3.16125512123108</v>
+        <v>3.1612548828125</v>
       </c>
       <c r="H1306" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>3.22499990463257</v>
       </c>
       <c r="G1310" t="n">
-        <v>2.89632034301758</v>
+        <v>2.896320104599</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>3.43499994277954</v>
       </c>
       <c r="G1311" t="n">
-        <v>3.08491802215576</v>
+        <v>3.08491778373718</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34481,7 +34481,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1312" t="n">
-        <v>3.01756143569946</v>
+        <v>3.01756167411804</v>
       </c>
       <c r="H1312" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>3.375</v>
       </c>
       <c r="G1317" t="n">
-        <v>3.03103303909302</v>
+        <v>3.03103280067444</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34637,7 +34637,7 @@
         <v>3.375</v>
       </c>
       <c r="G1318" t="n">
-        <v>3.03103303909302</v>
+        <v>3.03103280067444</v>
       </c>
       <c r="H1318" t="s">
         <v>8</v>
@@ -34741,7 +34741,7 @@
         <v>3.28500008583069</v>
       </c>
       <c r="G1322" t="n">
-        <v>2.9502055644989</v>
+        <v>2.95020532608032</v>
       </c>
       <c r="H1322" t="s">
         <v>8</v>
@@ -34767,7 +34767,7 @@
         <v>3.375</v>
       </c>
       <c r="G1323" t="n">
-        <v>3.03103303909302</v>
+        <v>3.03103280067444</v>
       </c>
       <c r="H1323" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>3.375</v>
       </c>
       <c r="G1324" t="n">
-        <v>3.03103303909302</v>
+        <v>3.03103280067444</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34923,7 +34923,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1329" t="n">
-        <v>3.03552317619324</v>
+        <v>3.03552341461182</v>
       </c>
       <c r="H1329" t="s">
         <v>8</v>
@@ -34975,7 +34975,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1331" t="n">
-        <v>3.00858068466187</v>
+        <v>3.00858092308044</v>
       </c>
       <c r="H1331" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1332" t="n">
-        <v>3.01756143569946</v>
+        <v>3.01756167411804</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35027,7 +35027,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1333" t="n">
-        <v>3.03552317619324</v>
+        <v>3.03552341461182</v>
       </c>
       <c r="H1333" t="s">
         <v>8</v>
@@ -35079,7 +35079,7 @@
         <v>3.31500005722046</v>
       </c>
       <c r="G1335" t="n">
-        <v>2.97714781761169</v>
+        <v>2.97714805603027</v>
       </c>
       <c r="H1335" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1336" t="n">
-        <v>2.85590648651123</v>
+        <v>2.85590672492981</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35131,7 +35131,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1337" t="n">
-        <v>2.79304051399231</v>
+        <v>2.79304075241089</v>
       </c>
       <c r="H1337" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1339" t="n">
-        <v>2.86488747596741</v>
+        <v>2.86488723754883</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35313,7 +35313,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1344" t="n">
-        <v>2.85590648651123</v>
+        <v>2.85590672492981</v>
       </c>
       <c r="H1344" t="s">
         <v>8</v>
@@ -35365,7 +35365,7 @@
         <v>3.11500000953674</v>
       </c>
       <c r="G1346" t="n">
-        <v>2.79753088951111</v>
+        <v>2.79753112792969</v>
       </c>
       <c r="H1346" t="s">
         <v>8</v>
@@ -35495,7 +35495,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1351" t="n">
-        <v>3.08940815925598</v>
+        <v>3.08940839767456</v>
       </c>
       <c r="H1351" t="s">
         <v>8</v>
@@ -35521,7 +35521,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1352" t="n">
-        <v>3.08940815925598</v>
+        <v>3.08940839767456</v>
       </c>
       <c r="H1352" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1353" t="n">
-        <v>3.08940815925598</v>
+        <v>3.08940839767456</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1356" t="n">
-        <v>3.21514010429382</v>
+        <v>3.21513986587524</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35677,7 +35677,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1358" t="n">
-        <v>3.30494856834412</v>
+        <v>3.30494832992554</v>
       </c>
       <c r="H1358" t="s">
         <v>8</v>
@@ -35807,7 +35807,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1363" t="n">
-        <v>3.18819737434387</v>
+        <v>3.18819761276245</v>
       </c>
       <c r="H1363" t="s">
         <v>8</v>
@@ -35833,7 +35833,7 @@
         <v>3.53500008583069</v>
       </c>
       <c r="G1364" t="n">
-        <v>3.17472648620605</v>
+        <v>3.17472624778748</v>
       </c>
       <c r="H1364" t="s">
         <v>8</v>
@@ -35859,7 +35859,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G1365" t="n">
-        <v>3.21963024139404</v>
+        <v>3.21963047981262</v>
       </c>
       <c r="H1365" t="s">
         <v>8</v>
@@ -35885,7 +35885,7 @@
         <v>3.5</v>
       </c>
       <c r="G1366" t="n">
-        <v>3.1432933807373</v>
+        <v>3.14329361915588</v>
       </c>
       <c r="H1366" t="s">
         <v>8</v>
@@ -35911,7 +35911,7 @@
         <v>3.46499991416931</v>
       </c>
       <c r="G1367" t="n">
-        <v>3.11186027526855</v>
+        <v>3.11186051368713</v>
       </c>
       <c r="H1367" t="s">
         <v>8</v>
@@ -35937,7 +35937,7 @@
         <v>3.46499991416931</v>
       </c>
       <c r="G1368" t="n">
-        <v>3.11186027526855</v>
+        <v>3.11186051368713</v>
       </c>
       <c r="H1368" t="s">
         <v>8</v>
@@ -36015,7 +36015,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1371" t="n">
-        <v>3.08042764663696</v>
+        <v>3.08042740821838</v>
       </c>
       <c r="H1371" t="s">
         <v>8</v>
@@ -36093,7 +36093,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1374" t="n">
-        <v>3.08940815925598</v>
+        <v>3.08940839767456</v>
       </c>
       <c r="H1374" t="s">
         <v>8</v>
@@ -36171,7 +36171,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1377" t="n">
-        <v>3.08940815925598</v>
+        <v>3.08940839767456</v>
       </c>
       <c r="H1377" t="s">
         <v>8</v>
@@ -36197,7 +36197,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1378" t="n">
-        <v>3.08940815925598</v>
+        <v>3.08940839767456</v>
       </c>
       <c r="H1378" t="s">
         <v>8</v>
@@ -36327,7 +36327,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1383" t="n">
-        <v>3.08042764663696</v>
+        <v>3.08042740821838</v>
       </c>
       <c r="H1383" t="s">
         <v>8</v>
@@ -36353,7 +36353,7 @@
         <v>3.5</v>
       </c>
       <c r="G1384" t="n">
-        <v>3.1432933807373</v>
+        <v>3.14329361915588</v>
       </c>
       <c r="H1384" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>3.43499994277954</v>
       </c>
       <c r="G1387" t="n">
-        <v>3.08491802215576</v>
+        <v>3.08491778373718</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36457,7 +36457,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1388" t="n">
-        <v>3.01756143569946</v>
+        <v>3.01756167411804</v>
       </c>
       <c r="H1388" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>3.28500008583069</v>
       </c>
       <c r="G1393" t="n">
-        <v>2.9502055644989</v>
+        <v>2.95020532608032</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36639,7 +36639,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G1395" t="n">
-        <v>3.21963024139404</v>
+        <v>3.21963047981262</v>
       </c>
       <c r="H1395" t="s">
         <v>8</v>
@@ -36691,7 +36691,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1397" t="n">
-        <v>3.21514010429382</v>
+        <v>3.21513986587524</v>
       </c>
       <c r="H1397" t="s">
         <v>8</v>
@@ -36769,7 +36769,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G1400" t="n">
-        <v>3.19268822669983</v>
+        <v>3.19268798828125</v>
       </c>
       <c r="H1400" t="s">
         <v>8</v>
@@ -36795,7 +36795,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1401" t="n">
-        <v>3.22412061691284</v>
+        <v>3.22412085533142</v>
       </c>
       <c r="H1401" t="s">
         <v>8</v>
@@ -36847,7 +36847,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1403" t="n">
-        <v>3.00858068466187</v>
+        <v>3.00858092308044</v>
       </c>
       <c r="H1403" t="s">
         <v>8</v>
@@ -36925,7 +36925,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1406" t="n">
-        <v>3.00858068466187</v>
+        <v>3.00858092308044</v>
       </c>
       <c r="H1406" t="s">
         <v>8</v>
@@ -36977,7 +36977,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1408" t="n">
-        <v>3.00858068466187</v>
+        <v>3.00858092308044</v>
       </c>
       <c r="H1408" t="s">
         <v>8</v>
@@ -37003,7 +37003,7 @@
         <v>3.23499989509583</v>
       </c>
       <c r="G1409" t="n">
-        <v>2.90530109405518</v>
+        <v>2.9053008556366</v>
       </c>
       <c r="H1409" t="s">
         <v>8</v>
@@ -37029,7 +37029,7 @@
         <v>3.23499989509583</v>
       </c>
       <c r="G1410" t="n">
-        <v>2.90530109405518</v>
+        <v>2.9053008556366</v>
       </c>
       <c r="H1410" t="s">
         <v>8</v>
@@ -37081,7 +37081,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1412" t="n">
-        <v>3.00858068466187</v>
+        <v>3.00858092308044</v>
       </c>
       <c r="H1412" t="s">
         <v>8</v>
@@ -37107,7 +37107,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1413" t="n">
-        <v>3.01756143569946</v>
+        <v>3.01756167411804</v>
       </c>
       <c r="H1413" t="s">
         <v>8</v>
@@ -37185,7 +37185,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1416" t="n">
-        <v>3.00858068466187</v>
+        <v>3.00858092308044</v>
       </c>
       <c r="H1416" t="s">
         <v>8</v>
@@ -37211,7 +37211,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1417" t="n">
-        <v>3.01756143569946</v>
+        <v>3.01756167411804</v>
       </c>
       <c r="H1417" t="s">
         <v>8</v>
@@ -37367,7 +37367,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1423" t="n">
-        <v>2.96367645263672</v>
+        <v>2.9636766910553</v>
       </c>
       <c r="H1423" t="s">
         <v>8</v>
@@ -37471,7 +37471,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1427" t="n">
-        <v>2.95469570159912</v>
+        <v>2.95469546318054</v>
       </c>
       <c r="H1427" t="s">
         <v>8</v>
@@ -37497,7 +37497,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1428" t="n">
-        <v>2.95469570159912</v>
+        <v>2.95469546318054</v>
       </c>
       <c r="H1428" t="s">
         <v>8</v>
@@ -37523,7 +37523,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1429" t="n">
-        <v>2.90979146957397</v>
+        <v>2.90979170799255</v>
       </c>
       <c r="H1429" t="s">
         <v>8</v>
@@ -37575,7 +37575,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1431" t="n">
-        <v>3.00858068466187</v>
+        <v>3.00858092308044</v>
       </c>
       <c r="H1431" t="s">
         <v>8</v>
@@ -37627,7 +37627,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1433" t="n">
-        <v>2.95469570159912</v>
+        <v>2.95469546318054</v>
       </c>
       <c r="H1433" t="s">
         <v>8</v>
@@ -37653,7 +37653,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G1434" t="n">
-        <v>2.9591863155365</v>
+        <v>2.95918607711792</v>
       </c>
       <c r="H1434" t="s">
         <v>8</v>
@@ -37705,7 +37705,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1436" t="n">
-        <v>2.93673419952393</v>
+        <v>2.93673396110535</v>
       </c>
       <c r="H1436" t="s">
         <v>8</v>
@@ -37731,7 +37731,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1437" t="n">
-        <v>2.93673419952393</v>
+        <v>2.93673396110535</v>
       </c>
       <c r="H1437" t="s">
         <v>8</v>
@@ -37783,7 +37783,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1439" t="n">
-        <v>2.93673419952393</v>
+        <v>2.93673396110535</v>
       </c>
       <c r="H1439" t="s">
         <v>8</v>
@@ -37835,7 +37835,7 @@
         <v>3.28500008583069</v>
       </c>
       <c r="G1441" t="n">
-        <v>2.9502055644989</v>
+        <v>2.95020532608032</v>
       </c>
       <c r="H1441" t="s">
         <v>8</v>
@@ -37887,7 +37887,7 @@
         <v>3.31500005722046</v>
       </c>
       <c r="G1443" t="n">
-        <v>2.97714781761169</v>
+        <v>2.97714805603027</v>
       </c>
       <c r="H1443" t="s">
         <v>8</v>
@@ -37939,7 +37939,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1445" t="n">
-        <v>2.93673419952393</v>
+        <v>2.93673396110535</v>
       </c>
       <c r="H1445" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>3.25500011444092</v>
       </c>
       <c r="G1447" t="n">
-        <v>2.92326283454895</v>
+        <v>2.92326307296753</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38043,7 +38043,7 @@
         <v>3.22499990463257</v>
       </c>
       <c r="G1449" t="n">
-        <v>2.89632034301758</v>
+        <v>2.896320104599</v>
       </c>
       <c r="H1449" t="s">
         <v>8</v>
@@ -38069,7 +38069,7 @@
         <v>3.22499990463257</v>
       </c>
       <c r="G1450" t="n">
-        <v>2.89632034301758</v>
+        <v>2.896320104599</v>
       </c>
       <c r="H1450" t="s">
         <v>8</v>
@@ -38173,7 +38173,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1454" t="n">
-        <v>2.82896399497986</v>
+        <v>2.82896423339844</v>
       </c>
       <c r="H1454" t="s">
         <v>8</v>
@@ -38199,7 +38199,7 @@
         <v>3.15499997138977</v>
       </c>
       <c r="G1455" t="n">
-        <v>2.83345413208008</v>
+        <v>2.83345437049866</v>
       </c>
       <c r="H1455" t="s">
         <v>8</v>
@@ -38225,7 +38225,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G1456" t="n">
-        <v>2.91428208351135</v>
+        <v>2.91428160667419</v>
       </c>
       <c r="H1456" t="s">
         <v>8</v>
@@ -38303,7 +38303,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1459" t="n">
-        <v>3.08940815925598</v>
+        <v>3.08940839767456</v>
       </c>
       <c r="H1459" t="s">
         <v>8</v>
@@ -38433,7 +38433,7 @@
         <v>3.375</v>
       </c>
       <c r="G1464" t="n">
-        <v>3.03103303909302</v>
+        <v>3.03103280067444</v>
       </c>
       <c r="H1464" t="s">
         <v>8</v>
@@ -38485,7 +38485,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1466" t="n">
-        <v>2.96367645263672</v>
+        <v>2.9636766910553</v>
       </c>
       <c r="H1466" t="s">
         <v>8</v>
@@ -38589,7 +38589,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1470" t="n">
-        <v>2.90979146957397</v>
+        <v>2.90979170799255</v>
       </c>
       <c r="H1470" t="s">
         <v>8</v>
@@ -38667,7 +38667,7 @@
         <v>3.49499988555908</v>
       </c>
       <c r="G1473" t="n">
-        <v>3.13880300521851</v>
+        <v>3.13880276679993</v>
       </c>
       <c r="H1473" t="s">
         <v>8</v>
@@ -38693,7 +38693,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1474" t="n">
-        <v>3.08940815925598</v>
+        <v>3.08940839767456</v>
       </c>
       <c r="H1474" t="s">
         <v>8</v>
@@ -38771,7 +38771,7 @@
         <v>3.49499988555908</v>
       </c>
       <c r="G1477" t="n">
-        <v>3.13880300521851</v>
+        <v>3.13880276679993</v>
       </c>
       <c r="H1477" t="s">
         <v>8</v>
@@ -38849,7 +38849,7 @@
         <v>3.5</v>
       </c>
       <c r="G1480" t="n">
-        <v>3.1432933807373</v>
+        <v>3.14329361915588</v>
       </c>
       <c r="H1480" t="s">
         <v>8</v>
@@ -38875,7 +38875,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1481" t="n">
-        <v>3.26902508735657</v>
+        <v>3.26902556419373</v>
       </c>
       <c r="H1481" t="s">
         <v>8</v>
@@ -38927,7 +38927,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1483" t="n">
-        <v>3.22412061691284</v>
+        <v>3.22412085533142</v>
       </c>
       <c r="H1483" t="s">
         <v>8</v>
@@ -38979,7 +38979,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1485" t="n">
-        <v>3.1522741317749</v>
+        <v>3.15227437019348</v>
       </c>
       <c r="H1485" t="s">
         <v>8</v>
@@ -39005,7 +39005,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G1486" t="n">
-        <v>3.19268822669983</v>
+        <v>3.19268798828125</v>
       </c>
       <c r="H1486" t="s">
         <v>8</v>
@@ -39031,7 +39031,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G1487" t="n">
-        <v>3.19268822669983</v>
+        <v>3.19268798828125</v>
       </c>
       <c r="H1487" t="s">
         <v>8</v>
@@ -39057,7 +39057,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1488" t="n">
-        <v>3.21514010429382</v>
+        <v>3.21513986587524</v>
       </c>
       <c r="H1488" t="s">
         <v>8</v>
@@ -39161,7 +39161,7 @@
         <v>3.61500000953674</v>
       </c>
       <c r="G1492" t="n">
-        <v>3.24657297134399</v>
+        <v>3.24657273292542</v>
       </c>
       <c r="H1492" t="s">
         <v>8</v>
@@ -39187,7 +39187,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1493" t="n">
-        <v>3.24208211898804</v>
+        <v>3.2420825958252</v>
       </c>
       <c r="H1493" t="s">
         <v>8</v>
@@ -39239,7 +39239,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1495" t="n">
-        <v>3.24208211898804</v>
+        <v>3.2420825958252</v>
       </c>
       <c r="H1495" t="s">
         <v>8</v>
@@ -39343,7 +39343,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G1499" t="n">
-        <v>3.14778399467468</v>
+        <v>3.1477837562561</v>
       </c>
       <c r="H1499" t="s">
         <v>8</v>
@@ -39395,7 +39395,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1501" t="n">
-        <v>3.08042764663696</v>
+        <v>3.08042740821838</v>
       </c>
       <c r="H1501" t="s">
         <v>8</v>
@@ -39499,7 +39499,7 @@
         <v>3.5</v>
       </c>
       <c r="G1505" t="n">
-        <v>3.1432933807373</v>
+        <v>3.14329361915588</v>
       </c>
       <c r="H1505" t="s">
         <v>8</v>
@@ -39551,7 +39551,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1507" t="n">
-        <v>3.08940815925598</v>
+        <v>3.08940839767456</v>
       </c>
       <c r="H1507" t="s">
         <v>8</v>
@@ -39577,7 +39577,7 @@
         <v>3.46499991416931</v>
       </c>
       <c r="G1508" t="n">
-        <v>3.11186027526855</v>
+        <v>3.11186051368713</v>
       </c>
       <c r="H1508" t="s">
         <v>8</v>
@@ -39681,7 +39681,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1512" t="n">
-        <v>3.08042764663696</v>
+        <v>3.08042740821838</v>
       </c>
       <c r="H1512" t="s">
         <v>8</v>
@@ -39707,7 +39707,7 @@
         <v>3.53500008583069</v>
       </c>
       <c r="G1513" t="n">
-        <v>3.17472648620605</v>
+        <v>3.17472624778748</v>
       </c>
       <c r="H1513" t="s">
         <v>8</v>
@@ -39733,7 +39733,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G1514" t="n">
-        <v>3.14778399467468</v>
+        <v>3.1477837562561</v>
       </c>
       <c r="H1514" t="s">
         <v>8</v>
@@ -39811,7 +39811,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1517" t="n">
-        <v>3.27800583839417</v>
+        <v>3.27800607681274</v>
       </c>
       <c r="H1517" t="s">
         <v>8</v>
@@ -39837,7 +39837,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1518" t="n">
-        <v>3.27800583839417</v>
+        <v>3.27800607681274</v>
       </c>
       <c r="H1518" t="s">
         <v>8</v>
@@ -39863,7 +39863,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1519" t="n">
-        <v>3.30494856834412</v>
+        <v>3.30494832992554</v>
       </c>
       <c r="H1519" t="s">
         <v>8</v>
@@ -39915,7 +39915,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1521" t="n">
-        <v>3.27800583839417</v>
+        <v>3.27800607681274</v>
       </c>
       <c r="H1521" t="s">
         <v>8</v>
@@ -39941,7 +39941,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1522" t="n">
-        <v>3.27800583839417</v>
+        <v>3.27800607681274</v>
       </c>
       <c r="H1522" t="s">
         <v>8</v>
@@ -39993,7 +39993,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1524" t="n">
-        <v>3.26902508735657</v>
+        <v>3.26902556419373</v>
       </c>
       <c r="H1524" t="s">
         <v>8</v>
@@ -40019,7 +40019,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1525" t="n">
-        <v>3.30494856834412</v>
+        <v>3.30494832992554</v>
       </c>
       <c r="H1525" t="s">
         <v>8</v>
@@ -40097,7 +40097,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1528" t="n">
-        <v>3.27800583839417</v>
+        <v>3.27800607681274</v>
       </c>
       <c r="H1528" t="s">
         <v>8</v>
@@ -40123,7 +40123,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1529" t="n">
-        <v>3.26902508735657</v>
+        <v>3.26902556419373</v>
       </c>
       <c r="H1529" t="s">
         <v>8</v>
@@ -40201,7 +40201,7 @@
         <v>3.53500008583069</v>
       </c>
       <c r="G1532" t="n">
-        <v>3.17472648620605</v>
+        <v>3.17472624778748</v>
       </c>
       <c r="H1532" t="s">
         <v>8</v>
@@ -40227,7 +40227,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G1533" t="n">
-        <v>3.14778399467468</v>
+        <v>3.1477837562561</v>
       </c>
       <c r="H1533" t="s">
         <v>8</v>
@@ -40253,7 +40253,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G1534" t="n">
-        <v>3.14778399467468</v>
+        <v>3.1477837562561</v>
       </c>
       <c r="H1534" t="s">
         <v>8</v>
@@ -40279,7 +40279,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1535" t="n">
-        <v>3.16125512123108</v>
+        <v>3.1612548828125</v>
       </c>
       <c r="H1535" t="s">
         <v>8</v>
@@ -40435,7 +40435,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1541" t="n">
-        <v>3.08940815925598</v>
+        <v>3.08940839767456</v>
       </c>
       <c r="H1541" t="s">
         <v>8</v>
@@ -40461,7 +40461,7 @@
         <v>3.375</v>
       </c>
       <c r="G1542" t="n">
-        <v>3.03103303909302</v>
+        <v>3.03103280067444</v>
       </c>
       <c r="H1542" t="s">
         <v>8</v>
@@ -40487,7 +40487,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1543" t="n">
-        <v>3.00858068466187</v>
+        <v>3.00858092308044</v>
       </c>
       <c r="H1543" t="s">
         <v>8</v>
@@ -40617,7 +40617,7 @@
         <v>3.46499991416931</v>
       </c>
       <c r="G1548" t="n">
-        <v>3.11186027526855</v>
+        <v>3.11186051368713</v>
       </c>
       <c r="H1548" t="s">
         <v>8</v>
@@ -40643,7 +40643,7 @@
         <v>3.5</v>
       </c>
       <c r="G1549" t="n">
-        <v>3.1432933807373</v>
+        <v>3.14329361915588</v>
       </c>
       <c r="H1549" t="s">
         <v>8</v>
@@ -40747,7 +40747,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G1553" t="n">
-        <v>2.9591863155365</v>
+        <v>2.95918607711792</v>
       </c>
       <c r="H1553" t="s">
         <v>8</v>
@@ -40799,7 +40799,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1555" t="n">
-        <v>3.01756143569946</v>
+        <v>3.01756167411804</v>
       </c>
       <c r="H1555" t="s">
         <v>8</v>
@@ -40825,7 +40825,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1556" t="n">
-        <v>3.00858068466187</v>
+        <v>3.00858092308044</v>
       </c>
       <c r="H1556" t="s">
         <v>8</v>
@@ -40851,7 +40851,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1557" t="n">
-        <v>2.93673419952393</v>
+        <v>2.93673396110535</v>
       </c>
       <c r="H1557" t="s">
         <v>8</v>
@@ -40903,7 +40903,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1559" t="n">
-        <v>3.03552317619324</v>
+        <v>3.03552341461182</v>
       </c>
       <c r="H1559" t="s">
         <v>8</v>
@@ -40981,7 +40981,7 @@
         <v>3.25500011444092</v>
       </c>
       <c r="G1562" t="n">
-        <v>2.92326283454895</v>
+        <v>2.92326307296753</v>
       </c>
       <c r="H1562" t="s">
         <v>8</v>
@@ -41059,7 +41059,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1565" t="n">
-        <v>2.74813652038574</v>
+        <v>2.74813628196716</v>
       </c>
       <c r="H1565" t="s">
         <v>8</v>
@@ -41241,7 +41241,7 @@
         <v>2.88499999046326</v>
       </c>
       <c r="G1572" t="n">
-        <v>2.59097170829773</v>
+        <v>2.59097194671631</v>
       </c>
       <c r="H1572" t="s">
         <v>8</v>
@@ -41293,7 +41293,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G1574" t="n">
-        <v>2.57750058174133</v>
+        <v>2.57750034332275</v>
       </c>
       <c r="H1574" t="s">
         <v>8</v>
@@ -41319,7 +41319,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1575" t="n">
-        <v>2.55055785179138</v>
+        <v>2.55055809020996</v>
       </c>
       <c r="H1575" t="s">
         <v>8</v>
@@ -41371,7 +41371,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1577" t="n">
-        <v>2.67628979682922</v>
+        <v>2.6762900352478</v>
       </c>
       <c r="H1577" t="s">
         <v>8</v>
@@ -41397,7 +41397,7 @@
         <v>2.92499995231628</v>
       </c>
       <c r="G1578" t="n">
-        <v>2.6268949508667</v>
+        <v>2.62689518928528</v>
       </c>
       <c r="H1578" t="s">
         <v>8</v>
@@ -41423,7 +41423,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1579" t="n">
-        <v>2.81100225448608</v>
+        <v>2.81100249290466</v>
       </c>
       <c r="H1579" t="s">
         <v>8</v>
@@ -41475,7 +41475,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G1581" t="n">
-        <v>2.78855013847351</v>
+        <v>2.78855037689209</v>
       </c>
       <c r="H1581" t="s">
         <v>8</v>
@@ -41501,7 +41501,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1582" t="n">
-        <v>2.78406000137329</v>
+        <v>2.78405976295471</v>
       </c>
       <c r="H1582" t="s">
         <v>8</v>
@@ -41527,7 +41527,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1583" t="n">
-        <v>2.82896399497986</v>
+        <v>2.82896423339844</v>
       </c>
       <c r="H1583" t="s">
         <v>8</v>
@@ -41553,7 +41553,7 @@
         <v>3.15499997138977</v>
       </c>
       <c r="G1584" t="n">
-        <v>2.83345413208008</v>
+        <v>2.83345437049866</v>
       </c>
       <c r="H1584" t="s">
         <v>8</v>
@@ -41605,7 +41605,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G1586" t="n">
-        <v>2.77058863639832</v>
+        <v>2.77058839797974</v>
       </c>
       <c r="H1586" t="s">
         <v>8</v>
@@ -41631,7 +41631,7 @@
         <v>3.09500002861023</v>
       </c>
       <c r="G1587" t="n">
-        <v>2.77956938743591</v>
+        <v>2.77956914901733</v>
       </c>
       <c r="H1587" t="s">
         <v>8</v>
@@ -41709,7 +41709,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1590" t="n">
-        <v>2.85590648651123</v>
+        <v>2.85590672492981</v>
       </c>
       <c r="H1590" t="s">
         <v>8</v>
@@ -41761,7 +41761,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1592" t="n">
-        <v>2.81998324394226</v>
+        <v>2.81998300552368</v>
       </c>
       <c r="H1592" t="s">
         <v>8</v>
@@ -41787,7 +41787,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1593" t="n">
-        <v>2.82896399497986</v>
+        <v>2.82896423339844</v>
       </c>
       <c r="H1593" t="s">
         <v>8</v>
@@ -41813,7 +41813,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G1594" t="n">
-        <v>2.76160788536072</v>
+        <v>2.76160764694214</v>
       </c>
       <c r="H1594" t="s">
         <v>8</v>
@@ -41891,7 +41891,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1597" t="n">
-        <v>2.81100225448608</v>
+        <v>2.81100249290466</v>
       </c>
       <c r="H1597" t="s">
         <v>8</v>
@@ -41917,7 +41917,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1598" t="n">
-        <v>2.77507877349854</v>
+        <v>2.77507901191711</v>
       </c>
       <c r="H1598" t="s">
         <v>8</v>
@@ -41943,7 +41943,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1599" t="n">
-        <v>2.78406000137329</v>
+        <v>2.78405976295471</v>
       </c>
       <c r="H1599" t="s">
         <v>8</v>
@@ -41969,7 +41969,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1600" t="n">
-        <v>2.96367645263672</v>
+        <v>2.9636766910553</v>
       </c>
       <c r="H1600" t="s">
         <v>8</v>
@@ -42021,7 +42021,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1602" t="n">
-        <v>3.01756143569946</v>
+        <v>3.01756167411804</v>
       </c>
       <c r="H1602" t="s">
         <v>8</v>
@@ -42099,7 +42099,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1605" t="n">
-        <v>3.03552317619324</v>
+        <v>3.03552341461182</v>
       </c>
       <c r="H1605" t="s">
         <v>8</v>
@@ -42229,7 +42229,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1610" t="n">
-        <v>3.01756143569946</v>
+        <v>3.01756167411804</v>
       </c>
       <c r="H1610" t="s">
         <v>8</v>
@@ -42255,7 +42255,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1611" t="n">
-        <v>2.95469570159912</v>
+        <v>2.95469546318054</v>
       </c>
       <c r="H1611" t="s">
         <v>8</v>
@@ -42281,7 +42281,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1612" t="n">
-        <v>2.95469570159912</v>
+        <v>2.95469546318054</v>
       </c>
       <c r="H1612" t="s">
         <v>8</v>
@@ -42307,7 +42307,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1613" t="n">
-        <v>2.81998324394226</v>
+        <v>2.81998300552368</v>
       </c>
       <c r="H1613" t="s">
         <v>8</v>
@@ -42333,7 +42333,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1614" t="n">
-        <v>2.74813652038574</v>
+        <v>2.74813628196716</v>
       </c>
       <c r="H1614" t="s">
         <v>8</v>
@@ -42385,7 +42385,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1616" t="n">
-        <v>2.71221327781677</v>
+        <v>2.71221303939819</v>
       </c>
       <c r="H1616" t="s">
         <v>8</v>
@@ -42411,7 +42411,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1617" t="n">
-        <v>2.77507877349854</v>
+        <v>2.77507901191711</v>
       </c>
       <c r="H1617" t="s">
         <v>8</v>
@@ -42463,7 +42463,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1619" t="n">
-        <v>2.86488747596741</v>
+        <v>2.86488723754883</v>
       </c>
       <c r="H1619" t="s">
         <v>8</v>
@@ -42541,7 +42541,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G1622" t="n">
-        <v>2.91428208351135</v>
+        <v>2.91428160667419</v>
       </c>
       <c r="H1622" t="s">
         <v>8</v>
@@ -42645,7 +42645,7 @@
         <v>3.11500000953674</v>
       </c>
       <c r="G1626" t="n">
-        <v>2.79753088951111</v>
+        <v>2.79753112792969</v>
       </c>
       <c r="H1626" t="s">
         <v>8</v>
@@ -42671,7 +42671,7 @@
         <v>3.06500005722046</v>
       </c>
       <c r="G1627" t="n">
-        <v>2.75262689590454</v>
+        <v>2.75262713432312</v>
       </c>
       <c r="H1627" t="s">
         <v>8</v>
@@ -42697,7 +42697,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1628" t="n">
-        <v>2.77507877349854</v>
+        <v>2.77507901191711</v>
       </c>
       <c r="H1628" t="s">
         <v>8</v>
@@ -42723,7 +42723,7 @@
         <v>3.04500007629395</v>
       </c>
       <c r="G1629" t="n">
-        <v>2.73466539382935</v>
+        <v>2.73466515541077</v>
       </c>
       <c r="H1629" t="s">
         <v>8</v>
@@ -42749,7 +42749,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1630" t="n">
-        <v>2.73915576934814</v>
+        <v>2.73915553092957</v>
       </c>
       <c r="H1630" t="s">
         <v>8</v>
@@ -42775,7 +42775,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1631" t="n">
-        <v>2.74813652038574</v>
+        <v>2.74813628196716</v>
       </c>
       <c r="H1631" t="s">
         <v>8</v>
@@ -42827,7 +42827,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G1633" t="n">
-        <v>2.74364590644836</v>
+        <v>2.74364638328552</v>
       </c>
       <c r="H1633" t="s">
         <v>8</v>
@@ -42879,7 +42879,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1635" t="n">
-        <v>2.79304051399231</v>
+        <v>2.79304075241089</v>
       </c>
       <c r="H1635" t="s">
         <v>8</v>
@@ -42957,7 +42957,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1638" t="n">
-        <v>2.81100225448608</v>
+        <v>2.81100249290466</v>
       </c>
       <c r="H1638" t="s">
         <v>8</v>
@@ -43009,7 +43009,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1640" t="n">
-        <v>2.64036655426025</v>
+        <v>2.64036631584167</v>
       </c>
       <c r="H1640" t="s">
         <v>8</v>
@@ -43035,7 +43035,7 @@
         <v>2.92499995231628</v>
       </c>
       <c r="G1641" t="n">
-        <v>2.6268949508667</v>
+        <v>2.62689518928528</v>
       </c>
       <c r="H1641" t="s">
         <v>8</v>
@@ -43113,7 +43113,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1644" t="n">
-        <v>2.67628979682922</v>
+        <v>2.6762900352478</v>
       </c>
       <c r="H1644" t="s">
         <v>8</v>
@@ -43139,7 +43139,7 @@
         <v>2.89499998092651</v>
       </c>
       <c r="G1645" t="n">
-        <v>2.59995269775391</v>
+        <v>2.59995245933533</v>
       </c>
       <c r="H1645" t="s">
         <v>8</v>
@@ -43347,7 +43347,7 @@
         <v>2.75</v>
       </c>
       <c r="G1653" t="n">
-        <v>2.46973061561584</v>
+        <v>2.46973037719727</v>
       </c>
       <c r="H1653" t="s">
         <v>8</v>
@@ -43425,7 +43425,7 @@
         <v>2.71499991416931</v>
       </c>
       <c r="G1656" t="n">
-        <v>2.43829774856567</v>
+        <v>2.43829751014709</v>
       </c>
       <c r="H1656" t="s">
         <v>8</v>
@@ -43451,7 +43451,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1657" t="n">
-        <v>2.43380737304688</v>
+        <v>2.4338071346283</v>
       </c>
       <c r="H1657" t="s">
         <v>8</v>
@@ -43503,7 +43503,7 @@
         <v>2.84500002861023</v>
       </c>
       <c r="G1659" t="n">
-        <v>2.55504846572876</v>
+        <v>2.55504822731018</v>
       </c>
       <c r="H1659" t="s">
         <v>8</v>
@@ -43529,7 +43529,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G1660" t="n">
-        <v>2.57750058174133</v>
+        <v>2.57750034332275</v>
       </c>
       <c r="H1660" t="s">
         <v>8</v>
@@ -43659,7 +43659,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1665" t="n">
-        <v>2.55055785179138</v>
+        <v>2.55055809020996</v>
       </c>
       <c r="H1665" t="s">
         <v>8</v>
@@ -43763,7 +43763,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G1669" t="n">
-        <v>2.57750058174133</v>
+        <v>2.57750034332275</v>
       </c>
       <c r="H1669" t="s">
         <v>8</v>
@@ -43789,7 +43789,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1670" t="n">
-        <v>2.55055785179138</v>
+        <v>2.55055809020996</v>
       </c>
       <c r="H1670" t="s">
         <v>8</v>
@@ -43867,7 +43867,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1673" t="n">
-        <v>2.51463460922241</v>
+        <v>2.51463437080383</v>
       </c>
       <c r="H1673" t="s">
         <v>8</v>
@@ -43893,7 +43893,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1674" t="n">
-        <v>2.55055785179138</v>
+        <v>2.55055809020996</v>
       </c>
       <c r="H1674" t="s">
         <v>8</v>
@@ -43919,7 +43919,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G1675" t="n">
-        <v>2.54606771469116</v>
+        <v>2.54606747627258</v>
       </c>
       <c r="H1675" t="s">
         <v>8</v>
@@ -43945,7 +43945,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1676" t="n">
-        <v>2.60444331169128</v>
+        <v>2.60444307327271</v>
       </c>
       <c r="H1676" t="s">
         <v>8</v>
@@ -43971,7 +43971,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1677" t="n">
-        <v>2.60444331169128</v>
+        <v>2.60444307327271</v>
       </c>
       <c r="H1677" t="s">
         <v>8</v>
@@ -44023,7 +44023,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1679" t="n">
-        <v>2.60444331169128</v>
+        <v>2.60444307327271</v>
       </c>
       <c r="H1679" t="s">
         <v>8</v>
@@ -44127,7 +44127,7 @@
         <v>2.875</v>
       </c>
       <c r="G1683" t="n">
-        <v>2.58199095726013</v>
+        <v>2.58199119567871</v>
       </c>
       <c r="H1683" t="s">
         <v>8</v>
@@ -44153,7 +44153,7 @@
         <v>2.88499999046326</v>
       </c>
       <c r="G1684" t="n">
-        <v>2.59097170829773</v>
+        <v>2.59097194671631</v>
       </c>
       <c r="H1684" t="s">
         <v>8</v>
@@ -44179,7 +44179,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1685" t="n">
-        <v>2.60444331169128</v>
+        <v>2.60444307327271</v>
       </c>
       <c r="H1685" t="s">
         <v>8</v>
@@ -44257,7 +44257,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1688" t="n">
-        <v>2.78406000137329</v>
+        <v>2.78405976295471</v>
       </c>
       <c r="H1688" t="s">
         <v>8</v>
@@ -44309,7 +44309,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1690" t="n">
-        <v>2.71221327781677</v>
+        <v>2.71221303939819</v>
       </c>
       <c r="H1690" t="s">
         <v>8</v>
@@ -44335,7 +44335,7 @@
         <v>3</v>
       </c>
       <c r="G1691" t="n">
-        <v>2.69425177574158</v>
+        <v>2.69425129890442</v>
       </c>
       <c r="H1691" t="s">
         <v>8</v>
@@ -44387,7 +44387,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G1693" t="n">
-        <v>2.74364590644836</v>
+        <v>2.74364638328552</v>
       </c>
       <c r="H1693" t="s">
         <v>8</v>
@@ -44439,7 +44439,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G1695" t="n">
-        <v>2.74364590644836</v>
+        <v>2.74364638328552</v>
       </c>
       <c r="H1695" t="s">
         <v>8</v>
@@ -44491,7 +44491,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1697" t="n">
-        <v>2.60444331169128</v>
+        <v>2.60444307327271</v>
       </c>
       <c r="H1697" t="s">
         <v>8</v>
@@ -44517,7 +44517,7 @@
         <v>2.91499996185303</v>
       </c>
       <c r="G1698" t="n">
-        <v>2.6179141998291</v>
+        <v>2.61791443824768</v>
       </c>
       <c r="H1698" t="s">
         <v>8</v>
@@ -44543,7 +44543,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G1699" t="n">
-        <v>2.57750058174133</v>
+        <v>2.57750034332275</v>
       </c>
       <c r="H1699" t="s">
         <v>8</v>
@@ -44621,7 +44621,7 @@
         <v>2.84500002861023</v>
       </c>
       <c r="G1702" t="n">
-        <v>2.55504846572876</v>
+        <v>2.55504822731018</v>
       </c>
       <c r="H1702" t="s">
         <v>8</v>
@@ -44647,7 +44647,7 @@
         <v>2.91499996185303</v>
       </c>
       <c r="G1703" t="n">
-        <v>2.6179141998291</v>
+        <v>2.61791443824768</v>
       </c>
       <c r="H1703" t="s">
         <v>8</v>
@@ -44699,7 +44699,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1705" t="n">
-        <v>2.55055785179138</v>
+        <v>2.55055809020996</v>
       </c>
       <c r="H1705" t="s">
         <v>8</v>
@@ -44751,7 +44751,7 @@
         <v>2.75</v>
       </c>
       <c r="G1707" t="n">
-        <v>2.46973061561584</v>
+        <v>2.46973037719727</v>
       </c>
       <c r="H1707" t="s">
         <v>8</v>
@@ -44907,7 +44907,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1713" t="n">
-        <v>2.18234348297119</v>
+        <v>2.18234395980835</v>
       </c>
       <c r="H1713" t="s">
         <v>8</v>
@@ -44933,7 +44933,7 @@
         <v>2.43499994277954</v>
       </c>
       <c r="G1714" t="n">
-        <v>2.18683409690857</v>
+        <v>2.18683385848999</v>
       </c>
       <c r="H1714" t="s">
         <v>8</v>
@@ -45037,7 +45037,7 @@
         <v>2.40499997138977</v>
       </c>
       <c r="G1718" t="n">
-        <v>2.1598916053772</v>
+        <v>2.15989136695862</v>
       </c>
       <c r="H1718" t="s">
         <v>8</v>
@@ -45063,7 +45063,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1719" t="n">
-        <v>2.15528607368469</v>
+        <v>2.15528583526611</v>
       </c>
       <c r="H1719" t="s">
         <v>8</v>
@@ -45193,7 +45193,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1724" t="n">
-        <v>2.10923290252686</v>
+        <v>2.10923314094543</v>
       </c>
       <c r="H1724" t="s">
         <v>8</v>
@@ -45427,7 +45427,7 @@
         <v>2.58500003814697</v>
       </c>
       <c r="G1733" t="n">
-        <v>2.38094687461853</v>
+        <v>2.38094639778137</v>
       </c>
       <c r="H1733" t="s">
         <v>8</v>
@@ -45453,7 +45453,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1734" t="n">
-        <v>2.37634110450745</v>
+        <v>2.37634134292603</v>
       </c>
       <c r="H1734" t="s">
         <v>8</v>
@@ -45505,7 +45505,7 @@
         <v>2.58500003814697</v>
       </c>
       <c r="G1736" t="n">
-        <v>2.38094687461853</v>
+        <v>2.38094639778137</v>
       </c>
       <c r="H1736" t="s">
         <v>8</v>
@@ -45531,7 +45531,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G1737" t="n">
-        <v>2.42239451408386</v>
+        <v>2.42239427566528</v>
       </c>
       <c r="H1737" t="s">
         <v>8</v>
@@ -45583,7 +45583,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1739" t="n">
-        <v>2.47765803337097</v>
+        <v>2.47765827178955</v>
       </c>
       <c r="H1739" t="s">
         <v>8</v>
@@ -45609,7 +45609,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G1740" t="n">
-        <v>2.40397310256958</v>
+        <v>2.403972864151</v>
       </c>
       <c r="H1740" t="s">
         <v>8</v>
@@ -45661,7 +45661,7 @@
         <v>2.56500005722046</v>
       </c>
       <c r="G1742" t="n">
-        <v>2.36252546310425</v>
+        <v>2.36252522468567</v>
       </c>
       <c r="H1742" t="s">
         <v>8</v>
@@ -45765,7 +45765,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G1746" t="n">
-        <v>2.45923662185669</v>
+        <v>2.45923686027527</v>
       </c>
       <c r="H1746" t="s">
         <v>8</v>
@@ -45791,7 +45791,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1747" t="n">
-        <v>2.47765803337097</v>
+        <v>2.47765827178955</v>
       </c>
       <c r="H1747" t="s">
         <v>8</v>
@@ -46207,7 +46207,7 @@
         <v>2.75500011444092</v>
       </c>
       <c r="G1763" t="n">
-        <v>2.53752708435059</v>
+        <v>2.53752732276917</v>
       </c>
       <c r="H1763" t="s">
         <v>8</v>
@@ -46259,7 +46259,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1765" t="n">
-        <v>2.52371144294739</v>
+        <v>2.52371096611023</v>
       </c>
       <c r="H1765" t="s">
         <v>8</v>
@@ -46285,7 +46285,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1766" t="n">
-        <v>2.52371144294739</v>
+        <v>2.52371096611023</v>
       </c>
       <c r="H1766" t="s">
         <v>8</v>
@@ -46337,7 +46337,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1768" t="n">
-        <v>2.49607920646667</v>
+        <v>2.49607944488525</v>
       </c>
       <c r="H1768" t="s">
         <v>8</v>
@@ -46363,7 +46363,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1769" t="n">
-        <v>2.52371144294739</v>
+        <v>2.52371096611023</v>
       </c>
       <c r="H1769" t="s">
         <v>8</v>
@@ -46389,7 +46389,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1770" t="n">
-        <v>2.47765803337097</v>
+        <v>2.47765827178955</v>
       </c>
       <c r="H1770" t="s">
         <v>8</v>
@@ -46415,7 +46415,7 @@
         <v>2.72499990463257</v>
       </c>
       <c r="G1771" t="n">
-        <v>2.50989532470703</v>
+        <v>2.50989508628845</v>
       </c>
       <c r="H1771" t="s">
         <v>8</v>
@@ -46441,7 +46441,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1772" t="n">
-        <v>2.50529003143311</v>
+        <v>2.50529026985168</v>
       </c>
       <c r="H1772" t="s">
         <v>8</v>
@@ -46467,7 +46467,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1773" t="n">
-        <v>2.50529003143311</v>
+        <v>2.50529026985168</v>
       </c>
       <c r="H1773" t="s">
         <v>8</v>
@@ -46493,7 +46493,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1774" t="n">
-        <v>2.52371144294739</v>
+        <v>2.52371096611023</v>
       </c>
       <c r="H1774" t="s">
         <v>8</v>
@@ -46519,7 +46519,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1775" t="n">
-        <v>2.52371144294739</v>
+        <v>2.52371096611023</v>
       </c>
       <c r="H1775" t="s">
         <v>8</v>
@@ -46597,7 +46597,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G1778" t="n">
-        <v>2.59279108047485</v>
+        <v>2.59279084205627</v>
       </c>
       <c r="H1778" t="s">
         <v>8</v>
@@ -46753,7 +46753,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1784" t="n">
-        <v>2.78160881996155</v>
+        <v>2.78160858154297</v>
       </c>
       <c r="H1784" t="s">
         <v>8</v>
@@ -46857,7 +46857,7 @@
         <v>3.06500005722046</v>
       </c>
       <c r="G1788" t="n">
-        <v>2.82305645942688</v>
+        <v>2.82305669784546</v>
       </c>
       <c r="H1788" t="s">
         <v>8</v>
@@ -46909,7 +46909,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1790" t="n">
-        <v>2.94740009307861</v>
+        <v>2.94739985466003</v>
       </c>
       <c r="H1790" t="s">
         <v>8</v>
@@ -46987,7 +46987,7 @@
         <v>3.09500002861023</v>
       </c>
       <c r="G1793" t="n">
-        <v>2.85068845748901</v>
+        <v>2.85068821907043</v>
       </c>
       <c r="H1793" t="s">
         <v>8</v>
@@ -47013,7 +47013,7 @@
         <v>3.09500002861023</v>
       </c>
       <c r="G1794" t="n">
-        <v>2.85068845748901</v>
+        <v>2.85068821907043</v>
       </c>
       <c r="H1794" t="s">
         <v>8</v>
@@ -47039,7 +47039,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1795" t="n">
-        <v>2.83687210083008</v>
+        <v>2.83687233924866</v>
       </c>
       <c r="H1795" t="s">
         <v>8</v>
@@ -47065,7 +47065,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1796" t="n">
-        <v>2.84608292579651</v>
+        <v>2.84608316421509</v>
       </c>
       <c r="H1796" t="s">
         <v>8</v>
@@ -47091,7 +47091,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G1797" t="n">
-        <v>2.84147787094116</v>
+        <v>2.84147763252258</v>
       </c>
       <c r="H1797" t="s">
         <v>8</v>
@@ -47169,7 +47169,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1800" t="n">
-        <v>2.78160881996155</v>
+        <v>2.78160858154297</v>
       </c>
       <c r="H1800" t="s">
         <v>8</v>
@@ -47325,7 +47325,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1806" t="n">
-        <v>2.71713423728943</v>
+        <v>2.71713447570801</v>
       </c>
       <c r="H1806" t="s">
         <v>8</v>
@@ -47351,7 +47351,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G1807" t="n">
-        <v>2.6987133026123</v>
+        <v>2.69871306419373</v>
       </c>
       <c r="H1807" t="s">
         <v>8</v>
@@ -47377,7 +47377,7 @@
         <v>2.875</v>
       </c>
       <c r="G1808" t="n">
-        <v>2.64805459976196</v>
+        <v>2.64805483818054</v>
       </c>
       <c r="H1808" t="s">
         <v>8</v>
@@ -47403,7 +47403,7 @@
         <v>2.875</v>
       </c>
       <c r="G1809" t="n">
-        <v>2.64805459976196</v>
+        <v>2.64805483818054</v>
       </c>
       <c r="H1809" t="s">
         <v>8</v>
@@ -47455,7 +47455,7 @@
         <v>2.875</v>
       </c>
       <c r="G1811" t="n">
-        <v>2.64805459976196</v>
+        <v>2.64805483818054</v>
       </c>
       <c r="H1811" t="s">
         <v>8</v>
@@ -47481,7 +47481,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G1812" t="n">
-        <v>2.64344930648804</v>
+        <v>2.64344906806946</v>
       </c>
       <c r="H1812" t="s">
         <v>8</v>
@@ -47507,7 +47507,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1813" t="n">
-        <v>2.62502789497375</v>
+        <v>2.62502813339233</v>
       </c>
       <c r="H1813" t="s">
         <v>8</v>
@@ -47533,7 +47533,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1814" t="n">
-        <v>2.6158173084259</v>
+        <v>2.61581754684448</v>
       </c>
       <c r="H1814" t="s">
         <v>8</v>
@@ -47585,7 +47585,7 @@
         <v>2.95499992370605</v>
       </c>
       <c r="G1816" t="n">
-        <v>2.72173976898193</v>
+        <v>2.72173929214478</v>
       </c>
       <c r="H1816" t="s">
         <v>8</v>
@@ -47663,7 +47663,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G1819" t="n">
-        <v>2.81384587287903</v>
+        <v>2.81384611129761</v>
       </c>
       <c r="H1819" t="s">
         <v>8</v>
@@ -47715,7 +47715,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1821" t="n">
-        <v>2.78160881996155</v>
+        <v>2.78160858154297</v>
       </c>
       <c r="H1821" t="s">
         <v>8</v>
@@ -47767,7 +47767,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1823" t="n">
-        <v>2.68950247764587</v>
+        <v>2.68950271606445</v>
       </c>
       <c r="H1823" t="s">
         <v>8</v>
@@ -47845,7 +47845,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1826" t="n">
-        <v>2.68950247764587</v>
+        <v>2.68950271606445</v>
       </c>
       <c r="H1826" t="s">
         <v>8</v>
@@ -47897,7 +47897,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1828" t="n">
-        <v>2.68950247764587</v>
+        <v>2.68950271606445</v>
       </c>
       <c r="H1828" t="s">
         <v>8</v>
@@ -48001,7 +48001,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G1832" t="n">
-        <v>2.6987133026123</v>
+        <v>2.69871306419373</v>
       </c>
       <c r="H1832" t="s">
         <v>8</v>
@@ -48079,7 +48079,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1835" t="n">
-        <v>2.6158173084259</v>
+        <v>2.61581754684448</v>
       </c>
       <c r="H1835" t="s">
         <v>8</v>
@@ -48105,7 +48105,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1836" t="n">
-        <v>2.63423848152161</v>
+        <v>2.63423871994019</v>
       </c>
       <c r="H1836" t="s">
         <v>8</v>
@@ -48183,7 +48183,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G1839" t="n">
-        <v>2.6987133026123</v>
+        <v>2.69871306419373</v>
       </c>
       <c r="H1839" t="s">
         <v>8</v>
@@ -48209,7 +48209,7 @@
         <v>2.91499996185303</v>
       </c>
       <c r="G1840" t="n">
-        <v>2.68489694595337</v>
+        <v>2.68489718437195</v>
       </c>
       <c r="H1840" t="s">
         <v>8</v>
@@ -48235,7 +48235,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1841" t="n">
-        <v>2.71713423728943</v>
+        <v>2.71713447570801</v>
       </c>
       <c r="H1841" t="s">
         <v>8</v>
@@ -48287,7 +48287,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1843" t="n">
-        <v>2.65266013145447</v>
+        <v>2.65265989303589</v>
       </c>
       <c r="H1843" t="s">
         <v>8</v>
@@ -48313,7 +48313,7 @@
         <v>2.875</v>
       </c>
       <c r="G1844" t="n">
-        <v>2.64805459976196</v>
+        <v>2.64805483818054</v>
       </c>
       <c r="H1844" t="s">
         <v>8</v>
@@ -48339,7 +48339,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1845" t="n">
-        <v>2.63423848152161</v>
+        <v>2.63423871994019</v>
       </c>
       <c r="H1845" t="s">
         <v>8</v>
@@ -48391,7 +48391,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1847" t="n">
-        <v>2.6158173084259</v>
+        <v>2.61581754684448</v>
       </c>
       <c r="H1847" t="s">
         <v>8</v>
@@ -48417,7 +48417,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1848" t="n">
-        <v>2.6158173084259</v>
+        <v>2.61581754684448</v>
       </c>
       <c r="H1848" t="s">
         <v>8</v>
@@ -48469,7 +48469,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1850" t="n">
-        <v>2.6158173084259</v>
+        <v>2.61581754684448</v>
       </c>
       <c r="H1850" t="s">
         <v>8</v>
@@ -48495,7 +48495,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1851" t="n">
-        <v>2.63423848152161</v>
+        <v>2.63423871994019</v>
       </c>
       <c r="H1851" t="s">
         <v>8</v>
@@ -48521,7 +48521,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1852" t="n">
-        <v>2.6158173084259</v>
+        <v>2.61581754684448</v>
       </c>
       <c r="H1852" t="s">
         <v>8</v>
@@ -48573,7 +48573,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1854" t="n">
-        <v>2.5789749622345</v>
+        <v>2.57897472381592</v>
       </c>
       <c r="H1854" t="s">
         <v>8</v>
@@ -48599,7 +48599,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1855" t="n">
-        <v>2.5789749622345</v>
+        <v>2.57897472381592</v>
       </c>
       <c r="H1855" t="s">
         <v>8</v>
@@ -48651,7 +48651,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.64344930648804</v>
+        <v>2.64344906806946</v>
       </c>
       <c r="H1857" t="s">
         <v>8</v>
@@ -48677,7 +48677,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.64344930648804</v>
+        <v>2.64344906806946</v>
       </c>
       <c r="H1858" t="s">
         <v>8</v>
@@ -48729,7 +48729,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.6158173084259</v>
+        <v>2.61581754684448</v>
       </c>
       <c r="H1860" t="s">
         <v>8</v>
@@ -48807,7 +48807,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.5789749622345</v>
+        <v>2.57897472381592</v>
       </c>
       <c r="H1863" t="s">
         <v>8</v>
@@ -48963,7 +48963,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.45923662185669</v>
+        <v>2.45923686027527</v>
       </c>
       <c r="H1869" t="s">
         <v>8</v>
@@ -48989,7 +48989,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.50529003143311</v>
+        <v>2.50529026985168</v>
       </c>
       <c r="H1870" t="s">
         <v>8</v>
@@ -49119,7 +49119,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.52371144294739</v>
+        <v>2.52371096611023</v>
       </c>
       <c r="H1875" t="s">
         <v>8</v>
@@ -49145,7 +49145,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.49607920646667</v>
+        <v>2.49607944488525</v>
       </c>
       <c r="H1876" t="s">
         <v>8</v>
@@ -49171,7 +49171,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.50529003143311</v>
+        <v>2.50529026985168</v>
       </c>
       <c r="H1877" t="s">
         <v>8</v>
@@ -49249,7 +49249,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.45923662185669</v>
+        <v>2.45923686027527</v>
       </c>
       <c r="H1880" t="s">
         <v>8</v>
@@ -49275,7 +49275,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.45923662185669</v>
+        <v>2.45923686027527</v>
       </c>
       <c r="H1881" t="s">
         <v>8</v>
@@ -49301,7 +49301,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.45923662185669</v>
+        <v>2.45923686027527</v>
       </c>
       <c r="H1882" t="s">
         <v>8</v>
@@ -49327,7 +49327,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.45923662185669</v>
+        <v>2.45923686027527</v>
       </c>
       <c r="H1883" t="s">
         <v>8</v>
@@ -49353,7 +49353,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.44081592559814</v>
+        <v>2.44081568717957</v>
       </c>
       <c r="H1884" t="s">
         <v>8</v>
@@ -49405,7 +49405,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.47765803337097</v>
+        <v>2.47765827178955</v>
       </c>
       <c r="H1886" t="s">
         <v>8</v>
@@ -49509,7 +49509,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.44081592559814</v>
+        <v>2.44081568717957</v>
       </c>
       <c r="H1890" t="s">
         <v>8</v>
@@ -49535,7 +49535,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.44081592559814</v>
+        <v>2.44081568717957</v>
       </c>
       <c r="H1891" t="s">
         <v>8</v>
@@ -49587,7 +49587,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.44081592559814</v>
+        <v>2.44081568717957</v>
       </c>
       <c r="H1893" t="s">
         <v>8</v>
@@ -49639,7 +49639,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.44081592559814</v>
+        <v>2.44081568717957</v>
       </c>
       <c r="H1895" t="s">
         <v>8</v>
@@ -49665,7 +49665,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.45923662185669</v>
+        <v>2.45923686027527</v>
       </c>
       <c r="H1896" t="s">
         <v>8</v>
@@ -49691,7 +49691,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.45923662185669</v>
+        <v>2.45923686027527</v>
       </c>
       <c r="H1897" t="s">
         <v>8</v>
@@ -49743,7 +49743,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.49607920646667</v>
+        <v>2.49607944488525</v>
       </c>
       <c r="H1899" t="s">
         <v>8</v>
@@ -49769,7 +49769,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.50529003143311</v>
+        <v>2.50529026985168</v>
       </c>
       <c r="H1900" t="s">
         <v>8</v>
@@ -49847,7 +49847,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.49607920646667</v>
+        <v>2.49607944488525</v>
       </c>
       <c r="H1903" t="s">
         <v>8</v>
@@ -49925,7 +49925,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.50529003143311</v>
+        <v>2.50529026985168</v>
       </c>
       <c r="H1906" t="s">
         <v>8</v>
@@ -50003,7 +50003,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.52371144294739</v>
+        <v>2.52371096611023</v>
       </c>
       <c r="H1909" t="s">
         <v>8</v>
@@ -50081,7 +50081,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.48590302467346</v>
+        <v>2.48590278625488</v>
       </c>
       <c r="H1912" t="s">
         <v>8</v>
@@ -50185,7 +50185,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.48590302467346</v>
+        <v>2.48590278625488</v>
       </c>
       <c r="H1916" t="s">
         <v>8</v>
@@ -50211,7 +50211,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.4764506816864</v>
+        <v>2.47645044326782</v>
       </c>
       <c r="H1917" t="s">
         <v>8</v>
@@ -50419,7 +50419,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.35357356071472</v>
+        <v>2.35357332229614</v>
       </c>
       <c r="H1925" t="s">
         <v>8</v>
@@ -50601,7 +50601,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.4764506816864</v>
+        <v>2.47645044326782</v>
       </c>
       <c r="H1932" t="s">
         <v>8</v>
@@ -50757,7 +50757,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.4764506816864</v>
+        <v>2.47645044326782</v>
       </c>
       <c r="H1938" t="s">
         <v>8</v>
@@ -50783,7 +50783,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.48590302467346</v>
+        <v>2.48590278625488</v>
       </c>
       <c r="H1939" t="s">
         <v>8</v>
@@ -50809,7 +50809,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.48590302467346</v>
+        <v>2.48590278625488</v>
       </c>
       <c r="H1940" t="s">
         <v>8</v>
@@ -51069,7 +51069,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.48590302467346</v>
+        <v>2.48590278625488</v>
       </c>
       <c r="H1950" t="s">
         <v>8</v>
@@ -51277,7 +51277,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.25905227661133</v>
+        <v>2.25905251502991</v>
       </c>
       <c r="H1958" t="s">
         <v>8</v>
@@ -51355,7 +51355,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.25905227661133</v>
+        <v>2.25905251502991</v>
       </c>
       <c r="H1961" t="s">
         <v>8</v>
@@ -51459,7 +51459,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.20233964920044</v>
+        <v>2.20233988761902</v>
       </c>
       <c r="H1965" t="s">
         <v>8</v>
@@ -51537,7 +51537,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.09836673736572</v>
+        <v>2.09836649894714</v>
       </c>
       <c r="H1968" t="s">
         <v>8</v>
@@ -51563,7 +51563,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.09836673736572</v>
+        <v>2.09836649894714</v>
       </c>
       <c r="H1969" t="s">
         <v>8</v>
@@ -51745,7 +51745,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1976" t="n">
-        <v>1.95658504962921</v>
+        <v>1.95658493041992</v>
       </c>
       <c r="H1976" t="s">
         <v>8</v>
@@ -51771,7 +51771,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G1977" t="n">
-        <v>1.89987242221832</v>
+        <v>1.89987254142761</v>
       </c>
       <c r="H1977" t="s">
         <v>8</v>
@@ -51797,7 +51797,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1978" t="n">
-        <v>1.88096833229065</v>
+        <v>1.88096821308136</v>
       </c>
       <c r="H1978" t="s">
         <v>8</v>
@@ -52057,7 +52057,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G1988" t="n">
-        <v>1.76281690597534</v>
+        <v>1.76281702518463</v>
       </c>
       <c r="H1988" t="s">
         <v>8</v>
@@ -52083,7 +52083,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1989" t="n">
-        <v>1.72028255462646</v>
+        <v>1.72028267383575</v>
       </c>
       <c r="H1989" t="s">
         <v>8</v>
@@ -52109,7 +52109,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1990" t="n">
-        <v>1.71083033084869</v>
+        <v>1.71083045005798</v>
       </c>
       <c r="H1990" t="s">
         <v>8</v>
@@ -52135,7 +52135,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G1991" t="n">
-        <v>1.69665217399597</v>
+        <v>1.69665229320526</v>
       </c>
       <c r="H1991" t="s">
         <v>8</v>
@@ -52343,7 +52343,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1999" t="n">
-        <v>1.71083033084869</v>
+        <v>1.71083045005798</v>
       </c>
       <c r="H1999" t="s">
         <v>8</v>
@@ -52369,7 +52369,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G2000" t="n">
-        <v>1.72028255462646</v>
+        <v>1.72028267383575</v>
       </c>
       <c r="H2000" t="s">
         <v>8</v>
@@ -52395,7 +52395,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G2001" t="n">
-        <v>1.71555650234222</v>
+        <v>1.71555662155151</v>
       </c>
       <c r="H2001" t="s">
         <v>8</v>
@@ -52421,7 +52421,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G2002" t="n">
-        <v>1.71555650234222</v>
+        <v>1.71555662155151</v>
       </c>
       <c r="H2002" t="s">
         <v>8</v>
@@ -52447,7 +52447,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G2003" t="n">
-        <v>1.72028255462646</v>
+        <v>1.72028267383575</v>
       </c>
       <c r="H2003" t="s">
         <v>8</v>
@@ -52473,7 +52473,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G2004" t="n">
-        <v>1.67302203178406</v>
+        <v>1.67302191257477</v>
       </c>
       <c r="H2004" t="s">
         <v>8</v>
@@ -52499,7 +52499,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G2005" t="n">
-        <v>1.69665217399597</v>
+        <v>1.69665229320526</v>
       </c>
       <c r="H2005" t="s">
         <v>8</v>
@@ -52525,7 +52525,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G2006" t="n">
-        <v>1.71555650234222</v>
+        <v>1.71555662155151</v>
       </c>
       <c r="H2006" t="s">
         <v>8</v>
@@ -52577,7 +52577,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G2008" t="n">
-        <v>1.88096833229065</v>
+        <v>1.88096821308136</v>
       </c>
       <c r="H2008" t="s">
         <v>8</v>
@@ -52603,7 +52603,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G2009" t="n">
-        <v>1.9093245267868</v>
+        <v>1.90932464599609</v>
       </c>
       <c r="H2009" t="s">
         <v>8</v>
@@ -52629,7 +52629,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2010" t="n">
-        <v>1.89987242221832</v>
+        <v>1.89987254142761</v>
       </c>
       <c r="H2010" t="s">
         <v>8</v>
@@ -52837,7 +52837,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G2018" t="n">
-        <v>1.97548937797546</v>
+        <v>1.97548913955688</v>
       </c>
       <c r="H2018" t="s">
         <v>8</v>
@@ -53253,7 +53253,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G2034" t="n">
-        <v>2.20233964920044</v>
+        <v>2.20233988761902</v>
       </c>
       <c r="H2034" t="s">
         <v>8</v>
@@ -53305,7 +53305,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G2036" t="n">
-        <v>2.14562726020813</v>
+        <v>2.14562702178955</v>
       </c>
       <c r="H2036" t="s">
         <v>8</v>
@@ -53487,7 +53487,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G2043" t="n">
-        <v>2.14562726020813</v>
+        <v>2.14562702178955</v>
       </c>
       <c r="H2043" t="s">
         <v>8</v>
@@ -53981,7 +53981,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G2062" t="n">
-        <v>2.13617515563965</v>
+        <v>2.13617491722107</v>
       </c>
       <c r="H2062" t="s">
         <v>8</v>
@@ -54007,7 +54007,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G2063" t="n">
-        <v>2.1078188419342</v>
+        <v>2.10781860351562</v>
       </c>
       <c r="H2063" t="s">
         <v>8</v>
@@ -54033,7 +54033,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G2064" t="n">
-        <v>1.94713282585144</v>
+        <v>1.94713306427002</v>
       </c>
       <c r="H2064" t="s">
         <v>8</v>
@@ -54059,7 +54059,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2065" t="n">
-        <v>1.87151622772217</v>
+        <v>1.87151610851288</v>
       </c>
       <c r="H2065" t="s">
         <v>8</v>
@@ -54215,7 +54215,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G2071" t="n">
-        <v>1.72973465919495</v>
+        <v>1.72973477840424</v>
       </c>
       <c r="H2071" t="s">
         <v>8</v>
@@ -54241,7 +54241,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G2072" t="n">
-        <v>1.81007754802704</v>
+        <v>1.81007742881775</v>
       </c>
       <c r="H2072" t="s">
         <v>8</v>
@@ -54267,7 +54267,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2073" t="n">
-        <v>1.87151622772217</v>
+        <v>1.87151610851288</v>
       </c>
       <c r="H2073" t="s">
         <v>8</v>
@@ -54293,7 +54293,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2074" t="n">
-        <v>1.87151622772217</v>
+        <v>1.87151610851288</v>
       </c>
       <c r="H2074" t="s">
         <v>8</v>
@@ -54319,7 +54319,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G2075" t="n">
-        <v>1.86206412315369</v>
+        <v>1.8620640039444</v>
       </c>
       <c r="H2075" t="s">
         <v>8</v>
@@ -54345,7 +54345,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2076" t="n">
-        <v>1.89987242221832</v>
+        <v>1.89987254142761</v>
       </c>
       <c r="H2076" t="s">
         <v>8</v>
@@ -54371,7 +54371,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G2077" t="n">
-        <v>1.9093245267868</v>
+        <v>1.90932464599609</v>
       </c>
       <c r="H2077" t="s">
         <v>8</v>
@@ -54397,7 +54397,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G2078" t="n">
-        <v>1.9093245267868</v>
+        <v>1.90932464599609</v>
       </c>
       <c r="H2078" t="s">
         <v>8</v>
@@ -54423,7 +54423,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G2079" t="n">
-        <v>1.9093245267868</v>
+        <v>1.90932464599609</v>
       </c>
       <c r="H2079" t="s">
         <v>8</v>
@@ -54449,7 +54449,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G2080" t="n">
-        <v>1.9093245267868</v>
+        <v>1.90932464599609</v>
       </c>
       <c r="H2080" t="s">
         <v>8</v>
@@ -54475,7 +54475,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2081" t="n">
-        <v>1.89987242221832</v>
+        <v>1.89987254142761</v>
       </c>
       <c r="H2081" t="s">
         <v>8</v>
@@ -54579,7 +54579,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2085" t="n">
-        <v>1.89987242221832</v>
+        <v>1.89987254142761</v>
       </c>
       <c r="H2085" t="s">
         <v>8</v>
@@ -54683,7 +54683,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G2089" t="n">
-        <v>1.76281690597534</v>
+        <v>1.76281702518463</v>
       </c>
       <c r="H2089" t="s">
         <v>8</v>
@@ -54761,7 +54761,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G2092" t="n">
-        <v>1.76281690597534</v>
+        <v>1.76281702518463</v>
       </c>
       <c r="H2092" t="s">
         <v>8</v>
@@ -54865,7 +54865,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G2096" t="n">
-        <v>1.828981757164</v>
+        <v>1.82898163795471</v>
       </c>
       <c r="H2096" t="s">
         <v>8</v>
@@ -54891,7 +54891,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G2097" t="n">
-        <v>1.828981757164</v>
+        <v>1.82898163795471</v>
       </c>
       <c r="H2097" t="s">
         <v>8</v>
@@ -55047,7 +55047,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G2103" t="n">
-        <v>1.81007754802704</v>
+        <v>1.81007742881775</v>
       </c>
       <c r="H2103" t="s">
         <v>8</v>
@@ -55073,7 +55073,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G2104" t="n">
-        <v>1.7817211151123</v>
+        <v>1.78172123432159</v>
       </c>
       <c r="H2104" t="s">
         <v>8</v>
@@ -55229,7 +55229,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G2110" t="n">
-        <v>1.74391293525696</v>
+        <v>1.74391281604767</v>
       </c>
       <c r="H2110" t="s">
         <v>8</v>
@@ -55307,7 +55307,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G2113" t="n">
-        <v>1.7817211151123</v>
+        <v>1.78172123432159</v>
       </c>
       <c r="H2113" t="s">
         <v>8</v>
@@ -55385,7 +55385,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G2116" t="n">
-        <v>1.76281690597534</v>
+        <v>1.76281702518463</v>
       </c>
       <c r="H2116" t="s">
         <v>8</v>
@@ -55619,7 +55619,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G2125" t="n">
-        <v>1.7817211151123</v>
+        <v>1.78172123432159</v>
       </c>
       <c r="H2125" t="s">
         <v>8</v>
@@ -55671,7 +55671,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G2127" t="n">
-        <v>1.81007754802704</v>
+        <v>1.81007742881775</v>
       </c>
       <c r="H2127" t="s">
         <v>8</v>
@@ -55723,7 +55723,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G2129" t="n">
-        <v>1.828981757164</v>
+        <v>1.82898163795471</v>
       </c>
       <c r="H2129" t="s">
         <v>8</v>
@@ -55905,7 +55905,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G2136" t="n">
-        <v>1.7817211151123</v>
+        <v>1.78172123432159</v>
       </c>
       <c r="H2136" t="s">
         <v>8</v>
@@ -56009,7 +56009,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G2140" t="n">
-        <v>1.74391293525696</v>
+        <v>1.74391281604767</v>
       </c>
       <c r="H2140" t="s">
         <v>8</v>
@@ -56217,7 +56217,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G2148" t="n">
-        <v>1.74391293525696</v>
+        <v>1.74391281604767</v>
       </c>
       <c r="H2148" t="s">
         <v>8</v>
@@ -56269,7 +56269,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G2150" t="n">
-        <v>1.72973465919495</v>
+        <v>1.72973477840424</v>
       </c>
       <c r="H2150" t="s">
         <v>8</v>
@@ -56295,7 +56295,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G2151" t="n">
-        <v>1.68720018863678</v>
+        <v>1.68720006942749</v>
       </c>
       <c r="H2151" t="s">
         <v>8</v>
@@ -56347,7 +56347,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G2153" t="n">
-        <v>1.71083033084869</v>
+        <v>1.71083045005798</v>
       </c>
       <c r="H2153" t="s">
         <v>8</v>
@@ -56373,7 +56373,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G2154" t="n">
-        <v>1.68247413635254</v>
+        <v>1.68247401714325</v>
       </c>
       <c r="H2154" t="s">
         <v>8</v>
@@ -56477,7 +56477,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G2158" t="n">
-        <v>1.69665217399597</v>
+        <v>1.69665229320526</v>
       </c>
       <c r="H2158" t="s">
         <v>8</v>
@@ -56503,7 +56503,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G2159" t="n">
-        <v>1.67302203178406</v>
+        <v>1.67302191257477</v>
       </c>
       <c r="H2159" t="s">
         <v>8</v>
@@ -71300,6 +71300,32 @@
         <v>1.15499997138977</v>
       </c>
       <c r="H2728" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2729">
+      <c r="A2729" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B2729" t="n">
+        <v>14536</v>
+      </c>
+      <c r="C2729" t="n">
+        <v>1.16999995708466</v>
+      </c>
+      <c r="D2729" t="n">
+        <v>1.11500000953674</v>
+      </c>
+      <c r="E2729" t="n">
+        <v>1.13999998569489</v>
+      </c>
+      <c r="F2729" t="n">
+        <v>1.13499999046326</v>
+      </c>
+      <c r="G2729" t="n">
+        <v>1.13499999046326</v>
+      </c>
+      <c r="H2729" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/ELC.MI.xlsx
+++ b/data/ELC.MI.xlsx
@@ -447,7 +447,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G3" t="n">
-        <v>1.73338508605957</v>
+        <v>1.73338496685028</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G7" t="n">
-        <v>1.65297031402588</v>
+        <v>1.65297043323517</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G11" t="n">
-        <v>1.59936046600342</v>
+        <v>1.59936034679413</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>1.65199995040894</v>
       </c>
       <c r="G12" t="n">
-        <v>1.47605764865875</v>
+        <v>1.47605776786804</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>1.71800005435944</v>
       </c>
       <c r="G15" t="n">
-        <v>1.53502881526947</v>
+        <v>1.53502869606018</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G17" t="n">
-        <v>1.44746589660645</v>
+        <v>1.44746601581573</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>1.625</v>
       </c>
       <c r="G18" t="n">
-        <v>1.45193338394165</v>
+        <v>1.45193350315094</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>1.59099996089935</v>
       </c>
       <c r="G22" t="n">
-        <v>1.42155432701111</v>
+        <v>1.4215544462204</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>1.54499995708466</v>
       </c>
       <c r="G24" t="n">
-        <v>1.38045346736908</v>
+        <v>1.38045358657837</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>1.51699995994568</v>
       </c>
       <c r="G25" t="n">
-        <v>1.35543572902679</v>
+        <v>1.35543549060822</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G26" t="n">
-        <v>1.38492107391357</v>
+        <v>1.38492119312286</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>1.40199995040894</v>
       </c>
       <c r="G27" t="n">
-        <v>1.25268340110779</v>
+        <v>1.25268352031708</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>1.6710000038147</v>
       </c>
       <c r="G33" t="n">
-        <v>1.49303436279297</v>
+        <v>1.49303424358368</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G35" t="n">
-        <v>1.51001060009003</v>
+        <v>1.51001071929932</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>1.75399994850159</v>
       </c>
       <c r="G36" t="n">
-        <v>1.5671945810318</v>
+        <v>1.56719434261322</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G37" t="n">
-        <v>1.57255554199219</v>
+        <v>1.5725554227829</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>1.74699997901917</v>
       </c>
       <c r="G39" t="n">
-        <v>1.56094026565552</v>
+        <v>1.56094002723694</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G40" t="n">
-        <v>1.57702326774597</v>
+        <v>1.57702302932739</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G41" t="n">
-        <v>1.59042537212372</v>
+        <v>1.59042549133301</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G43" t="n">
-        <v>1.57255554199219</v>
+        <v>1.5725554227829</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>1.77300000190735</v>
       </c>
       <c r="G46" t="n">
-        <v>1.58417093753815</v>
+        <v>1.58417105674744</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>1.89300000667572</v>
       </c>
       <c r="G53" t="n">
-        <v>1.69139063358307</v>
+        <v>1.69139075279236</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>1.90900003910065</v>
       </c>
       <c r="G54" t="n">
-        <v>1.70568680763245</v>
+        <v>1.70568668842316</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G55" t="n">
-        <v>1.67977523803711</v>
+        <v>1.6797753572464</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>1.90799999237061</v>
       </c>
       <c r="G56" t="n">
-        <v>1.70479321479797</v>
+        <v>1.70479309558868</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>1.93599998950958</v>
       </c>
       <c r="G60" t="n">
-        <v>1.72981119155884</v>
+        <v>1.72981107234955</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>1.94599997997284</v>
       </c>
       <c r="G61" t="n">
-        <v>1.73874604701996</v>
+        <v>1.73874592781067</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G63" t="n">
-        <v>1.7512549161911</v>
+        <v>1.75125503540039</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>1.96399998664856</v>
       </c>
       <c r="G64" t="n">
-        <v>1.75482892990112</v>
+        <v>1.75482904911041</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G71" t="n">
-        <v>1.6708402633667</v>
+        <v>1.67084038257599</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G74" t="n">
-        <v>1.71551501750946</v>
+        <v>1.71551513671875</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G75" t="n">
-        <v>1.71998262405396</v>
+        <v>1.71998274326324</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G76" t="n">
-        <v>1.71104764938354</v>
+        <v>1.71104753017426</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G77" t="n">
-        <v>1.70658016204834</v>
+        <v>1.70658028125763</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G78" t="n">
-        <v>1.71998262405396</v>
+        <v>1.71998274326324</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G80" t="n">
-        <v>1.71998262405396</v>
+        <v>1.71998274326324</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>1.89900004863739</v>
       </c>
       <c r="G81" t="n">
-        <v>1.69675171375275</v>
+        <v>1.69675183296204</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>1.92700004577637</v>
       </c>
       <c r="G82" t="n">
-        <v>1.72176969051361</v>
+        <v>1.72176957130432</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>1.91600000858307</v>
       </c>
       <c r="G86" t="n">
-        <v>1.71194124221802</v>
+        <v>1.71194112300873</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G87" t="n">
-        <v>1.70658016204834</v>
+        <v>1.70658028125763</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>1.85199999809265</v>
       </c>
       <c r="G93" t="n">
-        <v>1.65475738048553</v>
+        <v>1.65475726127625</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>1.91799998283386</v>
       </c>
       <c r="G98" t="n">
-        <v>1.71372830867767</v>
+        <v>1.71372818946838</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>1.9190000295639</v>
       </c>
       <c r="G99" t="n">
-        <v>1.71462178230286</v>
+        <v>1.71462166309357</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>1.9190000295639</v>
       </c>
       <c r="G101" t="n">
-        <v>1.7234228849411</v>
+        <v>1.72342276573181</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>1.95700001716614</v>
       </c>
       <c r="G103" t="n">
-        <v>1.7575501203537</v>
+        <v>1.75755000114441</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>1.9210000038147</v>
       </c>
       <c r="G105" t="n">
-        <v>1.72521889209747</v>
+        <v>1.72521901130676</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G107" t="n">
-        <v>1.72432088851929</v>
+        <v>1.72432076931</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G110" t="n">
-        <v>1.72432088851929</v>
+        <v>1.72432076931</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G111" t="n">
-        <v>1.72432088851929</v>
+        <v>1.72432076931</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G117" t="n">
-        <v>1.6255316734314</v>
+        <v>1.62553155422211</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G118" t="n">
-        <v>1.58960843086243</v>
+        <v>1.58960831165314</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G120" t="n">
-        <v>1.63451254367828</v>
+        <v>1.63451266288757</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>1.875</v>
       </c>
       <c r="G121" t="n">
-        <v>1.68390715122223</v>
+        <v>1.68390727043152</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>1.82400000095367</v>
       </c>
       <c r="G122" t="n">
-        <v>1.63810479640961</v>
+        <v>1.6381049156189</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G123" t="n">
-        <v>1.66145515441895</v>
+        <v>1.66145503520966</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G125" t="n">
-        <v>1.58960843086243</v>
+        <v>1.58960831165314</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G131" t="n">
-        <v>1.59409880638123</v>
+        <v>1.59409868717194</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>1.69700002670288</v>
       </c>
       <c r="G132" t="n">
-        <v>1.52404832839966</v>
+        <v>1.52404820919037</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G133" t="n">
-        <v>1.46836709976196</v>
+        <v>1.46836698055267</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>1.64300000667572</v>
       </c>
       <c r="G134" t="n">
-        <v>1.47555184364319</v>
+        <v>1.4755517244339</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>1.62100005149841</v>
       </c>
       <c r="G135" t="n">
-        <v>1.45579397678375</v>
+        <v>1.45579385757446</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G136" t="n">
-        <v>1.45489573478699</v>
+        <v>1.45489585399628</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>1.66400003433228</v>
       </c>
       <c r="G138" t="n">
-        <v>1.49441158771515</v>
+        <v>1.49441146850586</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>1.67299997806549</v>
       </c>
       <c r="G139" t="n">
-        <v>1.50249421596527</v>
+        <v>1.50249409675598</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>1.65400004386902</v>
       </c>
       <c r="G149" t="n">
-        <v>1.48543071746826</v>
+        <v>1.48543059825897</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>1.69400000572205</v>
       </c>
       <c r="G153" t="n">
-        <v>1.52135396003723</v>
+        <v>1.52135407924652</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>1.69400000572205</v>
       </c>
       <c r="G154" t="n">
-        <v>1.52135396003723</v>
+        <v>1.52135407924652</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G155" t="n">
-        <v>1.52674269676208</v>
+        <v>1.52674245834351</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G156" t="n">
-        <v>1.50878071784973</v>
+        <v>1.50878083705902</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G157" t="n">
-        <v>1.52674269676208</v>
+        <v>1.52674245834351</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G159" t="n">
-        <v>1.51776158809662</v>
+        <v>1.5177618265152</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>1.68599998950958</v>
       </c>
       <c r="G160" t="n">
-        <v>1.51416945457458</v>
+        <v>1.5141693353653</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G167" t="n">
-        <v>1.64349341392517</v>
+        <v>1.64349353313446</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>1.93400001525879</v>
       </c>
       <c r="G168" t="n">
-        <v>1.7368940114975</v>
+        <v>1.73689413070679</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>1.93299996852875</v>
       </c>
       <c r="G170" t="n">
-        <v>1.73599600791931</v>
+        <v>1.73599588871002</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>1.89300000667572</v>
       </c>
       <c r="G172" t="n">
-        <v>1.70007276535034</v>
+        <v>1.70007264614105</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G175" t="n">
-        <v>1.67043590545654</v>
+        <v>1.67043602466583</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G180" t="n">
-        <v>1.67043590545654</v>
+        <v>1.67043602466583</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>1.81400001049042</v>
       </c>
       <c r="G183" t="n">
-        <v>1.62912404537201</v>
+        <v>1.62912392616272</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G184" t="n">
-        <v>1.63451254367828</v>
+        <v>1.63451266288757</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>1.80400002002716</v>
       </c>
       <c r="G185" t="n">
-        <v>1.62014329433441</v>
+        <v>1.62014317512512</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G194" t="n">
-        <v>1.63451254367828</v>
+        <v>1.63451266288757</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G195" t="n">
-        <v>1.63451254367828</v>
+        <v>1.63451266288757</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>1.89699995517731</v>
       </c>
       <c r="G197" t="n">
-        <v>1.70366501808167</v>
+        <v>1.70366489887238</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>1.875</v>
       </c>
       <c r="G198" t="n">
-        <v>1.68390715122223</v>
+        <v>1.68390727043152</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G199" t="n">
-        <v>1.69737839698792</v>
+        <v>1.6973785161972</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G201" t="n">
-        <v>1.67043590545654</v>
+        <v>1.67043602466583</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G202" t="n">
-        <v>1.66145515441895</v>
+        <v>1.66145503520966</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G204" t="n">
-        <v>1.66145515441895</v>
+        <v>1.66145503520966</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G207" t="n">
-        <v>1.64349341392517</v>
+        <v>1.64349353313446</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G208" t="n">
-        <v>1.63451254367828</v>
+        <v>1.63451266288757</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G210" t="n">
-        <v>1.66145515441895</v>
+        <v>1.66145503520966</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G211" t="n">
-        <v>1.65247428417206</v>
+        <v>1.65247416496277</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>1.86899995803833</v>
       </c>
       <c r="G212" t="n">
-        <v>1.67851865291595</v>
+        <v>1.67851853370667</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>1.86899995803833</v>
       </c>
       <c r="G213" t="n">
-        <v>1.67851865291595</v>
+        <v>1.67851853370667</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G214" t="n">
-        <v>1.65247428417206</v>
+        <v>1.65247416496277</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G217" t="n">
-        <v>1.63451254367828</v>
+        <v>1.63451266288757</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G218" t="n">
-        <v>1.64349341392517</v>
+        <v>1.64349353313446</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G220" t="n">
-        <v>1.6255316734314</v>
+        <v>1.62553155422211</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>1.74600005149841</v>
       </c>
       <c r="G224" t="n">
-        <v>1.56805431842804</v>
+        <v>1.56805443763733</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G225" t="n">
-        <v>1.58960843086243</v>
+        <v>1.58960831165314</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G226" t="n">
-        <v>1.52674269676208</v>
+        <v>1.52674245834351</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>1.65799999237061</v>
       </c>
       <c r="G228" t="n">
-        <v>1.4890228509903</v>
+        <v>1.48902297019958</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>1.62899994850159</v>
       </c>
       <c r="G229" t="n">
-        <v>1.46297860145569</v>
+        <v>1.4629784822464</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G230" t="n">
-        <v>1.4279533624649</v>
+        <v>1.42795324325562</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>1.47500002384186</v>
       </c>
       <c r="G234" t="n">
-        <v>1.32467353343964</v>
+        <v>1.32467377185822</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>1.52199995517731</v>
       </c>
       <c r="G237" t="n">
-        <v>1.36688351631165</v>
+        <v>1.36688363552094</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>1.58200001716614</v>
       </c>
       <c r="G240" t="n">
-        <v>1.42076873779297</v>
+        <v>1.42076861858368</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>1.59399998188019</v>
       </c>
       <c r="G241" t="n">
-        <v>1.43154561519623</v>
+        <v>1.43154549598694</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G243" t="n">
-        <v>1.4504052400589</v>
+        <v>1.45040547847748</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>1.65299999713898</v>
       </c>
       <c r="G245" t="n">
-        <v>1.48453259468079</v>
+        <v>1.48453271389008</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>1.71899998188019</v>
       </c>
       <c r="G247" t="n">
-        <v>1.5438060760498</v>
+        <v>1.54380595684052</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G253" t="n">
-        <v>1.6255316734314</v>
+        <v>1.62553155422211</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>1.81400001049042</v>
       </c>
       <c r="G254" t="n">
-        <v>1.62912404537201</v>
+        <v>1.62912392616272</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G256" t="n">
-        <v>1.6255316734314</v>
+        <v>1.62553155422211</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G260" t="n">
-        <v>1.6255316734314</v>
+        <v>1.62553155422211</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>1.81400001049042</v>
       </c>
       <c r="G261" t="n">
-        <v>1.62912404537201</v>
+        <v>1.62912392616272</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G262" t="n">
-        <v>1.64349341392517</v>
+        <v>1.64349353313446</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G263" t="n">
-        <v>1.65247428417206</v>
+        <v>1.65247416496277</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G266" t="n">
-        <v>1.6255316734314</v>
+        <v>1.62553155422211</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G267" t="n">
-        <v>1.65247428417206</v>
+        <v>1.65247416496277</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>1.81099998950958</v>
       </c>
       <c r="G268" t="n">
-        <v>1.62642979621887</v>
+        <v>1.62642991542816</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G269" t="n">
-        <v>1.63451254367828</v>
+        <v>1.63451266288757</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G271" t="n">
-        <v>1.6255316734314</v>
+        <v>1.62553155422211</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>1.71899998188019</v>
       </c>
       <c r="G274" t="n">
-        <v>1.5438060760498</v>
+        <v>1.54380595684052</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>1.69599997997284</v>
       </c>
       <c r="G276" t="n">
-        <v>1.52315020561218</v>
+        <v>1.52315008640289</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G278" t="n">
-        <v>1.50878071784973</v>
+        <v>1.50878083705902</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G279" t="n">
-        <v>1.50878071784973</v>
+        <v>1.50878083705902</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>1.62100005149841</v>
       </c>
       <c r="G285" t="n">
-        <v>1.45579397678375</v>
+        <v>1.45579385757446</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>1.56200003623962</v>
       </c>
       <c r="G289" t="n">
-        <v>1.4028068780899</v>
+        <v>1.40280699729919</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>1.48599994182587</v>
       </c>
       <c r="G292" t="n">
-        <v>1.33455240726471</v>
+        <v>1.33455264568329</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>1.46700000762939</v>
       </c>
       <c r="G293" t="n">
-        <v>1.3174889087677</v>
+        <v>1.31748902797699</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>1.47500002384186</v>
       </c>
       <c r="G294" t="n">
-        <v>1.32467353343964</v>
+        <v>1.32467377185822</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>1.47800004482269</v>
       </c>
       <c r="G297" t="n">
-        <v>1.32736790180206</v>
+        <v>1.32736778259277</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G298" t="n">
-        <v>1.33814489841461</v>
+        <v>1.3381450176239</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G300" t="n">
-        <v>1.4279533624649</v>
+        <v>1.42795324325562</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>1.58599996566772</v>
       </c>
       <c r="G302" t="n">
-        <v>1.42436099052429</v>
+        <v>1.424360871315</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>1.58200001716614</v>
       </c>
       <c r="G305" t="n">
-        <v>1.42076873779297</v>
+        <v>1.42076861858368</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>1.57700002193451</v>
       </c>
       <c r="G307" t="n">
-        <v>1.41627824306488</v>
+        <v>1.41627836227417</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>1.53900003433228</v>
       </c>
       <c r="G310" t="n">
-        <v>1.38215112686157</v>
+        <v>1.38215100765228</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>1.53600001335144</v>
       </c>
       <c r="G311" t="n">
-        <v>1.37945675849915</v>
+        <v>1.37945687770844</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>1.54499995708466</v>
       </c>
       <c r="G312" t="n">
-        <v>1.38753938674927</v>
+        <v>1.38753950595856</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G316" t="n">
-        <v>1.41448211669922</v>
+        <v>1.41448199748993</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>1.6139999628067</v>
       </c>
       <c r="G319" t="n">
-        <v>1.44950735569</v>
+        <v>1.44950723648071</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>1.62300002574921</v>
       </c>
       <c r="G321" t="n">
-        <v>1.45758998394012</v>
+        <v>1.45759010314941</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>1.62899994850159</v>
       </c>
       <c r="G322" t="n">
-        <v>1.46297860145569</v>
+        <v>1.4629784822464</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>1.65299999713898</v>
       </c>
       <c r="G325" t="n">
-        <v>1.48453259468079</v>
+        <v>1.48453271389008</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>1.63399994373322</v>
       </c>
       <c r="G327" t="n">
-        <v>1.4674688577652</v>
+        <v>1.46746897697449</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>1.625</v>
       </c>
       <c r="G330" t="n">
-        <v>1.45938634872437</v>
+        <v>1.45938622951508</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G333" t="n">
-        <v>1.42346274852753</v>
+        <v>1.42346286773682</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>1.60300004482269</v>
       </c>
       <c r="G334" t="n">
-        <v>1.43962848186493</v>
+        <v>1.43962836265564</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>1.63399994373322</v>
       </c>
       <c r="G336" t="n">
-        <v>1.4674688577652</v>
+        <v>1.46746897697449</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G344" t="n">
-        <v>1.52225208282471</v>
+        <v>1.522252202034</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G348" t="n">
-        <v>1.51776158809662</v>
+        <v>1.5177618265152</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>1.81099998950958</v>
       </c>
       <c r="G349" t="n">
-        <v>1.62642979621887</v>
+        <v>1.62642991542816</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G355" t="n">
-        <v>1.65247428417206</v>
+        <v>1.65247416496277</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G356" t="n">
-        <v>1.71084976196289</v>
+        <v>1.71084952354431</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G359" t="n">
-        <v>1.72432088851929</v>
+        <v>1.72432076931</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G360" t="n">
-        <v>1.72432088851929</v>
+        <v>1.72432076931</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>1.875</v>
       </c>
       <c r="G361" t="n">
-        <v>1.68390715122223</v>
+        <v>1.68390727043152</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G365" t="n">
-        <v>1.66145515441895</v>
+        <v>1.66145503520966</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>1.81700003147125</v>
       </c>
       <c r="G368" t="n">
-        <v>1.63181841373444</v>
+        <v>1.63181829452515</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G372" t="n">
-        <v>1.65247428417206</v>
+        <v>1.65247416496277</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G377" t="n">
-        <v>1.64349341392517</v>
+        <v>1.64349353313446</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>1.80400002002716</v>
       </c>
       <c r="G380" t="n">
-        <v>1.62014329433441</v>
+        <v>1.62014317512512</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>1.7610000371933</v>
       </c>
       <c r="G381" t="n">
-        <v>1.58152568340302</v>
+        <v>1.58152556419373</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G382" t="n">
-        <v>1.58960843086243</v>
+        <v>1.58960831165314</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>1.70299994945526</v>
       </c>
       <c r="G383" t="n">
-        <v>1.52943658828735</v>
+        <v>1.52943670749664</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>1.72099995613098</v>
       </c>
       <c r="G385" t="n">
-        <v>1.54560232162476</v>
+        <v>1.54560220241547</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>1.72099995613098</v>
       </c>
       <c r="G386" t="n">
-        <v>1.54560232162476</v>
+        <v>1.54560220241547</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>1.69700002670288</v>
       </c>
       <c r="G389" t="n">
-        <v>1.52404832839966</v>
+        <v>1.52404820919037</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G398" t="n">
-        <v>1.58960843086243</v>
+        <v>1.58960831165314</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>1.7610000371933</v>
       </c>
       <c r="G399" t="n">
-        <v>1.58152568340302</v>
+        <v>1.58152556419373</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>1.75300002098083</v>
       </c>
       <c r="G402" t="n">
-        <v>1.57434093952179</v>
+        <v>1.5743408203125</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>1.77799999713898</v>
       </c>
       <c r="G403" t="n">
-        <v>1.59679317474365</v>
+        <v>1.59679305553436</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>1.78299999237061</v>
       </c>
       <c r="G404" t="n">
-        <v>1.60128355026245</v>
+        <v>1.60128343105316</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G407" t="n">
-        <v>1.63451254367828</v>
+        <v>1.63451266288757</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>1.80400002002716</v>
       </c>
       <c r="G409" t="n">
-        <v>1.62014329433441</v>
+        <v>1.62014317512512</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>1.81700003147125</v>
       </c>
       <c r="G411" t="n">
-        <v>1.63181841373444</v>
+        <v>1.63181829452515</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>1.75399994850159</v>
       </c>
       <c r="G415" t="n">
-        <v>1.57523894309998</v>
+        <v>1.57523906230927</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>1.73699998855591</v>
       </c>
       <c r="G418" t="n">
-        <v>1.55997157096863</v>
+        <v>1.55997169017792</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G425" t="n">
-        <v>1.72432088851929</v>
+        <v>1.72432076931</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>1.88199996948242</v>
       </c>
       <c r="G428" t="n">
-        <v>1.69019365310669</v>
+        <v>1.6901935338974</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>1.89600002765656</v>
       </c>
       <c r="G432" t="n">
-        <v>1.70276701450348</v>
+        <v>1.70276689529419</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G433" t="n">
-        <v>1.81412923336029</v>
+        <v>1.81412935256958</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G434" t="n">
-        <v>1.88597595691681</v>
+        <v>1.88597583770752</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>2.24600005149841</v>
       </c>
       <c r="G436" t="n">
-        <v>2.01709651947021</v>
+        <v>2.01709628105164</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G439" t="n">
-        <v>2.32603693008423</v>
+        <v>2.32603716850281</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>2.5239999294281</v>
       </c>
       <c r="G440" t="n">
-        <v>2.26676368713379</v>
+        <v>2.26676344871521</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G444" t="n">
-        <v>2.36196064949036</v>
+        <v>2.36196041107178</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G445" t="n">
-        <v>2.35297966003418</v>
+        <v>2.3529794216156</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>2.61800003051758</v>
       </c>
       <c r="G446" t="n">
-        <v>2.35118341445923</v>
+        <v>2.35118365287781</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>2.61800003051758</v>
       </c>
       <c r="G447" t="n">
-        <v>2.35118341445923</v>
+        <v>2.35118365287781</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G451" t="n">
-        <v>2.30807518959045</v>
+        <v>2.30807542800903</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>2.56399989128113</v>
       </c>
       <c r="G452" t="n">
-        <v>2.30268669128418</v>
+        <v>2.30268692970276</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>2.32200002670288</v>
       </c>
       <c r="G457" t="n">
-        <v>2.08535075187683</v>
+        <v>2.08535051345825</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>2.50600004196167</v>
       </c>
       <c r="G458" t="n">
-        <v>2.25059795379639</v>
+        <v>2.25059819221497</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G460" t="n">
-        <v>2.32603693008423</v>
+        <v>2.32603716850281</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>2.80200004577637</v>
       </c>
       <c r="G461" t="n">
-        <v>2.51643085479736</v>
+        <v>2.51643109321594</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G466" t="n">
-        <v>2.45176863670349</v>
+        <v>2.45176887512207</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>2.84400010108948</v>
       </c>
       <c r="G469" t="n">
-        <v>2.55415034294128</v>
+        <v>2.55415058135986</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>2.82200002670288</v>
       </c>
       <c r="G476" t="n">
-        <v>2.53439259529114</v>
+        <v>2.53439283370972</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G479" t="n">
-        <v>2.16438221931458</v>
+        <v>2.164381980896</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G483" t="n">
-        <v>2.16438221931458</v>
+        <v>2.164381980896</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>2.49399995803833</v>
       </c>
       <c r="G484" t="n">
-        <v>2.23982095718384</v>
+        <v>2.23982119560242</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>2.54399991035461</v>
       </c>
       <c r="G489" t="n">
-        <v>2.28472518920898</v>
+        <v>2.28472542762756</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>2.62199997901917</v>
       </c>
       <c r="G490" t="n">
-        <v>2.35477590560913</v>
+        <v>2.35477566719055</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>2.55800008773804</v>
       </c>
       <c r="G491" t="n">
-        <v>2.29729819297791</v>
+        <v>2.29729843139648</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>2.51399993896484</v>
       </c>
       <c r="G492" t="n">
-        <v>2.25778245925903</v>
+        <v>2.25778269767761</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>2.48399996757507</v>
       </c>
       <c r="G493" t="n">
-        <v>2.23083996772766</v>
+        <v>2.23084020614624</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G494" t="n">
-        <v>2.20928621292114</v>
+        <v>2.20928645133972</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G496" t="n">
-        <v>2.23622894287109</v>
+        <v>2.23622870445251</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G497" t="n">
-        <v>2.20928621292114</v>
+        <v>2.20928645133972</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>2.51399993896484</v>
       </c>
       <c r="G498" t="n">
-        <v>2.25778245925903</v>
+        <v>2.25778269767761</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G501" t="n">
-        <v>2.23622894287109</v>
+        <v>2.23622870445251</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G504" t="n">
-        <v>2.22724795341492</v>
+        <v>2.22724771499634</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>2.5239999294281</v>
       </c>
       <c r="G505" t="n">
-        <v>2.26676368713379</v>
+        <v>2.26676344871521</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>2.5220000743866</v>
       </c>
       <c r="G506" t="n">
-        <v>2.26496720314026</v>
+        <v>2.26496744155884</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G507" t="n">
-        <v>2.22724795341492</v>
+        <v>2.22724771499634</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G510" t="n">
-        <v>2.19850921630859</v>
+        <v>2.19850897789001</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>2.42199993133545</v>
       </c>
       <c r="G511" t="n">
-        <v>2.17515897750854</v>
+        <v>2.17515921592712</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G513" t="n">
-        <v>2.18234372138977</v>
+        <v>2.18234395980835</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G514" t="n">
-        <v>2.1554012298584</v>
+        <v>2.15540146827698</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G516" t="n">
-        <v>2.22724795341492</v>
+        <v>2.22724771499634</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G517" t="n">
-        <v>2.22724795341492</v>
+        <v>2.22724771499634</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G520" t="n">
-        <v>2.1554012298584</v>
+        <v>2.15540146827698</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G521" t="n">
-        <v>2.16438221931458</v>
+        <v>2.164381980896</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G523" t="n">
-        <v>2.12845826148987</v>
+        <v>2.12845849990845</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G528" t="n">
-        <v>2.0835542678833</v>
+        <v>2.08355450630188</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G530" t="n">
-        <v>2.10151624679565</v>
+        <v>2.10151600837708</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G532" t="n">
-        <v>2.12845826148987</v>
+        <v>2.12845849990845</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G533" t="n">
-        <v>2.1554012298584</v>
+        <v>2.15540146827698</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G534" t="n">
-        <v>2.1374397277832</v>
+        <v>2.13743948936462</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G538" t="n">
-        <v>2.1554012298584</v>
+        <v>2.15540146827698</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>2.36500000953674</v>
       </c>
       <c r="G541" t="n">
-        <v>2.12396812438965</v>
+        <v>2.12396836280823</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G546" t="n">
-        <v>2.10151624679565</v>
+        <v>2.10151600837708</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>2.3050000667572</v>
       </c>
       <c r="G548" t="n">
-        <v>2.07008337974548</v>
+        <v>2.0700831413269</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>2.3050000667572</v>
       </c>
       <c r="G549" t="n">
-        <v>2.07008337974548</v>
+        <v>2.0700831413269</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G554" t="n">
-        <v>1.87699496746063</v>
+        <v>1.87699508666992</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G555" t="n">
-        <v>1.903937458992</v>
+        <v>1.90393769741058</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G556" t="n">
-        <v>1.85005259513855</v>
+        <v>1.85005271434784</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G557" t="n">
-        <v>1.91291868686676</v>
+        <v>1.91291856765747</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G558" t="n">
-        <v>1.92189943790436</v>
+        <v>1.92189931869507</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G559" t="n">
-        <v>1.94884181022644</v>
+        <v>1.94884192943573</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G563" t="n">
-        <v>2.00272703170776</v>
+        <v>2.00272679328918</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G564" t="n">
-        <v>2.06110215187073</v>
+        <v>2.06110239028931</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G567" t="n">
-        <v>2.00272703170776</v>
+        <v>2.00272679328918</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G569" t="n">
-        <v>2.00272703170776</v>
+        <v>2.00272679328918</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G570" t="n">
-        <v>1.94884181022644</v>
+        <v>1.94884192943573</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>2.15499997138977</v>
       </c>
       <c r="G571" t="n">
-        <v>1.93537056446075</v>
+        <v>1.93537044525146</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G572" t="n">
-        <v>1.91291868686676</v>
+        <v>1.91291856765747</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>2.15499997138977</v>
       </c>
       <c r="G573" t="n">
-        <v>1.93537056446075</v>
+        <v>1.93537044525146</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>2.23499989509583</v>
       </c>
       <c r="G581" t="n">
-        <v>2.00721740722656</v>
+        <v>2.00721716880798</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G586" t="n">
-        <v>2.0835542678833</v>
+        <v>2.08355450630188</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G587" t="n">
-        <v>2.06110215187073</v>
+        <v>2.06110239028931</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G592" t="n">
-        <v>2.06110215187073</v>
+        <v>2.06110239028931</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G596" t="n">
-        <v>2.0835542678833</v>
+        <v>2.08355450630188</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G598" t="n">
-        <v>2.23622894287109</v>
+        <v>2.23622870445251</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G599" t="n">
-        <v>2.23622894287109</v>
+        <v>2.23622870445251</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G600" t="n">
-        <v>2.32603693008423</v>
+        <v>2.32603716850281</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>2.47499990463257</v>
       </c>
       <c r="G602" t="n">
-        <v>2.22275733947754</v>
+        <v>2.22275757789612</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>2.35500001907349</v>
       </c>
       <c r="G606" t="n">
-        <v>2.11498737335205</v>
+        <v>2.11498761177063</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>2.35500001907349</v>
       </c>
       <c r="G608" t="n">
-        <v>2.11498737335205</v>
+        <v>2.11498761177063</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>2.22499990463257</v>
       </c>
       <c r="G613" t="n">
-        <v>1.99823641777039</v>
+        <v>1.99823665618896</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>2.15499997138977</v>
       </c>
       <c r="G615" t="n">
-        <v>1.93537056446075</v>
+        <v>1.93537044525146</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>2.3050000667572</v>
       </c>
       <c r="G618" t="n">
-        <v>2.07008337974548</v>
+        <v>2.0700831413269</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G623" t="n">
-        <v>2.06110215187073</v>
+        <v>2.06110239028931</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G635" t="n">
-        <v>2.00272703170776</v>
+        <v>2.00272679328918</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G636" t="n">
-        <v>1.95782279968262</v>
+        <v>1.9578230381012</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>2.22499990463257</v>
       </c>
       <c r="G640" t="n">
-        <v>1.99823641777039</v>
+        <v>1.99823665618896</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G644" t="n">
-        <v>1.96680343151093</v>
+        <v>1.9668036699295</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G645" t="n">
-        <v>1.95782279968262</v>
+        <v>1.9578230381012</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G646" t="n">
-        <v>1.96680343151093</v>
+        <v>1.9668036699295</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>2.1949999332428</v>
       </c>
       <c r="G647" t="n">
-        <v>1.97129380702972</v>
+        <v>1.9712940454483</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G648" t="n">
-        <v>1.96680343151093</v>
+        <v>1.9668036699295</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G649" t="n">
-        <v>1.95782279968262</v>
+        <v>1.9578230381012</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>2.18499994277954</v>
       </c>
       <c r="G650" t="n">
-        <v>1.96231317520142</v>
+        <v>1.96231293678284</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G653" t="n">
-        <v>1.95782279968262</v>
+        <v>1.9578230381012</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>2.15499997138977</v>
       </c>
       <c r="G654" t="n">
-        <v>1.93537056446075</v>
+        <v>1.93537044525146</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G655" t="n">
-        <v>1.94884181022644</v>
+        <v>1.94884192943573</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G656" t="n">
-        <v>1.89495694637299</v>
+        <v>1.89495670795441</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G657" t="n">
-        <v>1.92189943790436</v>
+        <v>1.92189931869507</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G658" t="n">
-        <v>1.89495694637299</v>
+        <v>1.89495670795441</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G659" t="n">
-        <v>1.93088030815125</v>
+        <v>1.93088042736053</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G660" t="n">
-        <v>1.92189943790436</v>
+        <v>1.92189931869507</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G661" t="n">
-        <v>1.903937458992</v>
+        <v>1.90393769741058</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G662" t="n">
-        <v>1.903937458992</v>
+        <v>1.90393769741058</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G664" t="n">
-        <v>1.93088030815125</v>
+        <v>1.93088042736053</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G665" t="n">
-        <v>1.93088030815125</v>
+        <v>1.93088042736053</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G667" t="n">
-        <v>1.903937458992</v>
+        <v>1.90393769741058</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>2.09500002861023</v>
       </c>
       <c r="G668" t="n">
-        <v>1.88148546218872</v>
+        <v>1.8814857006073</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G670" t="n">
-        <v>1.93088030815125</v>
+        <v>1.93088042736053</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G671" t="n">
-        <v>1.93088030815125</v>
+        <v>1.93088042736053</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G672" t="n">
-        <v>1.95782279968262</v>
+        <v>1.9578230381012</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G673" t="n">
-        <v>1.97578454017639</v>
+        <v>1.97578430175781</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G674" t="n">
-        <v>1.96680343151093</v>
+        <v>1.9668036699295</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G682" t="n">
-        <v>1.94884181022644</v>
+        <v>1.94884192943573</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>2.17499995231628</v>
       </c>
       <c r="G683" t="n">
-        <v>1.95333230495453</v>
+        <v>1.95333206653595</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G684" t="n">
-        <v>1.96680343151093</v>
+        <v>1.9668036699295</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>2.23499989509583</v>
       </c>
       <c r="G693" t="n">
-        <v>2.00721740722656</v>
+        <v>2.00721716880798</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G698" t="n">
-        <v>2.06110215187073</v>
+        <v>2.06110239028931</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G706" t="n">
-        <v>1.97578454017639</v>
+        <v>1.97578430175781</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G707" t="n">
-        <v>1.91291868686676</v>
+        <v>1.91291856765747</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G708" t="n">
-        <v>1.92189943790436</v>
+        <v>1.92189931869507</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G709" t="n">
-        <v>1.85005259513855</v>
+        <v>1.85005271434784</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G710" t="n">
-        <v>1.77820599079132</v>
+        <v>1.77820587158203</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G713" t="n">
-        <v>1.92189943790436</v>
+        <v>1.92189931869507</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>2.07500004768372</v>
       </c>
       <c r="G714" t="n">
-        <v>1.86352407932281</v>
+        <v>1.86352396011353</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>1.92599999904633</v>
       </c>
       <c r="G720" t="n">
-        <v>1.72970938682556</v>
+        <v>1.72970950603485</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G721" t="n">
-        <v>1.65247428417206</v>
+        <v>1.65247416496277</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G722" t="n">
-        <v>1.65247428417206</v>
+        <v>1.65247416496277</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>1.85599994659424</v>
       </c>
       <c r="G723" t="n">
-        <v>1.66684341430664</v>
+        <v>1.66684365272522</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>1.89400005340576</v>
       </c>
       <c r="G724" t="n">
-        <v>1.70097076892853</v>
+        <v>1.70097088813782</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>1.81599998474121</v>
       </c>
       <c r="G727" t="n">
-        <v>1.63092005252838</v>
+        <v>1.63092029094696</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>1.83399999141693</v>
       </c>
       <c r="G728" t="n">
-        <v>1.64708566665649</v>
+        <v>1.64708578586578</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G729" t="n">
-        <v>1.63451254367828</v>
+        <v>1.63451266288757</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>1.81599998474121</v>
       </c>
       <c r="G730" t="n">
-        <v>1.63092005252838</v>
+        <v>1.63092029094696</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G731" t="n">
-        <v>1.63451254367828</v>
+        <v>1.63451266288757</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G732" t="n">
-        <v>1.63451254367828</v>
+        <v>1.63451266288757</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>1.65400004386902</v>
       </c>
       <c r="G736" t="n">
-        <v>1.48543071746826</v>
+        <v>1.48543059825897</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G739" t="n">
-        <v>1.4279533624649</v>
+        <v>1.42795324325562</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>1.55599999427795</v>
       </c>
       <c r="G741" t="n">
-        <v>1.39741837978363</v>
+        <v>1.39741826057434</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>1.49600005149841</v>
       </c>
       <c r="G746" t="n">
-        <v>1.34353351593018</v>
+        <v>1.34353339672089</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>1.45200002193451</v>
       </c>
       <c r="G750" t="n">
-        <v>1.3040177822113</v>
+        <v>1.30401790142059</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>1.40600001811981</v>
       </c>
       <c r="G753" t="n">
-        <v>1.26270592212677</v>
+        <v>1.26270580291748</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>1.41600000858307</v>
       </c>
       <c r="G755" t="n">
-        <v>1.27168667316437</v>
+        <v>1.27168679237366</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G756" t="n">
-        <v>1.23935568332672</v>
+        <v>1.23935556411743</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>1.29200005531311</v>
       </c>
       <c r="G758" t="n">
-        <v>1.16032433509827</v>
+        <v>1.16032421588898</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>1.25399994850159</v>
       </c>
       <c r="G760" t="n">
-        <v>1.12619709968567</v>
+        <v>1.12619698047638</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>1.30400002002716</v>
       </c>
       <c r="G763" t="n">
-        <v>1.17110121250153</v>
+        <v>1.17110133171082</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>1.41400003433228</v>
       </c>
       <c r="G765" t="n">
-        <v>1.26989042758942</v>
+        <v>1.26989054679871</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G769" t="n">
-        <v>1.36508750915527</v>
+        <v>1.36508738994598</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>1.51800000667572</v>
       </c>
       <c r="G771" t="n">
-        <v>1.36329114437103</v>
+        <v>1.36329126358032</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>1.47800004482269</v>
       </c>
       <c r="G773" t="n">
-        <v>1.32736790180206</v>
+        <v>1.32736778259277</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G774" t="n">
-        <v>1.33814489841461</v>
+        <v>1.3381450176239</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>1.49600005149841</v>
       </c>
       <c r="G775" t="n">
-        <v>1.34353351593018</v>
+        <v>1.34353339672089</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>1.49600005149841</v>
       </c>
       <c r="G781" t="n">
-        <v>1.34353351593018</v>
+        <v>1.34353339672089</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>1.44200003147125</v>
       </c>
       <c r="G787" t="n">
-        <v>1.29503703117371</v>
+        <v>1.29503691196442</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>1.42799997329712</v>
       </c>
       <c r="G788" t="n">
-        <v>1.28246378898621</v>
+        <v>1.28246366977692</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>1.40199995040894</v>
       </c>
       <c r="G789" t="n">
-        <v>1.25911355018616</v>
+        <v>1.25911343097687</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G791" t="n">
-        <v>1.23037493228912</v>
+        <v>1.23037481307983</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>1.38800001144409</v>
       </c>
       <c r="G792" t="n">
-        <v>1.24654030799866</v>
+        <v>1.24654042720795</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>1.41799998283386</v>
       </c>
       <c r="G793" t="n">
-        <v>1.27348279953003</v>
+        <v>1.27348291873932</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G794" t="n">
-        <v>1.45309972763062</v>
+        <v>1.45309960842133</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G795" t="n">
-        <v>1.45489573478699</v>
+        <v>1.45489585399628</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>1.89800000190735</v>
       </c>
       <c r="G797" t="n">
-        <v>1.70456302165985</v>
+        <v>1.70456314086914</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G798" t="n">
-        <v>1.65247428417206</v>
+        <v>1.65247416496277</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G800" t="n">
-        <v>1.65247428417206</v>
+        <v>1.65247416496277</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>2.09500002861023</v>
       </c>
       <c r="G802" t="n">
-        <v>1.88148546218872</v>
+        <v>1.8814857006073</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G803" t="n">
-        <v>1.88597595691681</v>
+        <v>1.88597583770752</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G804" t="n">
-        <v>1.85005259513855</v>
+        <v>1.85005271434784</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>2.07500004768372</v>
       </c>
       <c r="G808" t="n">
-        <v>1.86352407932281</v>
+        <v>1.86352396011353</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G809" t="n">
-        <v>1.85005259513855</v>
+        <v>1.85005271434784</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G811" t="n">
-        <v>1.81412923336029</v>
+        <v>1.81412935256958</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G813" t="n">
-        <v>1.81412923336029</v>
+        <v>1.81412935256958</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>1.8639999628067</v>
       </c>
       <c r="G819" t="n">
-        <v>1.67402815818787</v>
+        <v>1.67402827739716</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>2.07500004768372</v>
       </c>
       <c r="G826" t="n">
-        <v>1.86352407932281</v>
+        <v>1.86352396011353</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>2.31500005722046</v>
       </c>
       <c r="G830" t="n">
-        <v>2.07906436920166</v>
+        <v>2.07906413078308</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G835" t="n">
-        <v>1.97578454017639</v>
+        <v>1.97578430175781</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G836" t="n">
-        <v>1.97578454017639</v>
+        <v>1.97578430175781</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G838" t="n">
-        <v>2.1374397277832</v>
+        <v>2.13743948936462</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>2.3050000667572</v>
       </c>
       <c r="G844" t="n">
-        <v>2.07008337974548</v>
+        <v>2.0700831413269</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>2.46499991416931</v>
       </c>
       <c r="G849" t="n">
-        <v>2.21377658843994</v>
+        <v>2.21377635002136</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>2.36500000953674</v>
       </c>
       <c r="G850" t="n">
-        <v>2.12396812438965</v>
+        <v>2.12396836280823</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G852" t="n">
-        <v>1.96680343151093</v>
+        <v>1.9668036699295</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G853" t="n">
-        <v>1.97578454017639</v>
+        <v>1.97578430175781</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G854" t="n">
-        <v>1.96680343151093</v>
+        <v>1.9668036699295</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G855" t="n">
-        <v>1.95782279968262</v>
+        <v>1.9578230381012</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G856" t="n">
-        <v>1.95782279968262</v>
+        <v>1.9578230381012</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>2.3050000667572</v>
       </c>
       <c r="G857" t="n">
-        <v>2.07008337974548</v>
+        <v>2.0700831413269</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G858" t="n">
-        <v>2.06110215187073</v>
+        <v>2.06110239028931</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>2.3050000667572</v>
       </c>
       <c r="G862" t="n">
-        <v>2.07008337974548</v>
+        <v>2.0700831413269</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G870" t="n">
-        <v>2.06110215187073</v>
+        <v>2.06110239028931</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>2.22499990463257</v>
       </c>
       <c r="G875" t="n">
-        <v>1.99823641777039</v>
+        <v>1.99823665618896</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G876" t="n">
-        <v>1.92189943790436</v>
+        <v>1.92189931869507</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G878" t="n">
-        <v>1.86801433563232</v>
+        <v>1.86801421642303</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G881" t="n">
-        <v>1.81412923336029</v>
+        <v>1.81412935256958</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>2.02500009536743</v>
       </c>
       <c r="G882" t="n">
-        <v>1.81861972808838</v>
+        <v>1.81861984729767</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>1.98399996757507</v>
       </c>
       <c r="G883" t="n">
-        <v>1.78179824352264</v>
+        <v>1.78179812431335</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>1.96399998664856</v>
       </c>
       <c r="G885" t="n">
-        <v>1.76383650302887</v>
+        <v>1.76383662223816</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G891" t="n">
-        <v>1.81412923336029</v>
+        <v>1.81412935256958</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>1.99600005149841</v>
       </c>
       <c r="G896" t="n">
-        <v>1.79257524013519</v>
+        <v>1.79257535934448</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>1.99399995803833</v>
       </c>
       <c r="G897" t="n">
-        <v>1.79077911376953</v>
+        <v>1.79077899456024</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G898" t="n">
-        <v>1.81412923336029</v>
+        <v>1.81412935256958</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>2</v>
       </c>
       <c r="G900" t="n">
-        <v>1.79616761207581</v>
+        <v>1.7961677312851</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>1.99399995803833</v>
       </c>
       <c r="G901" t="n">
-        <v>1.79077911376953</v>
+        <v>1.79077899456024</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>1.97800004482269</v>
       </c>
       <c r="G902" t="n">
-        <v>1.77640974521637</v>
+        <v>1.77640986442566</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>1.89800000190735</v>
       </c>
       <c r="G903" t="n">
-        <v>1.70456302165985</v>
+        <v>1.70456314086914</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G904" t="n">
-        <v>1.72432088851929</v>
+        <v>1.72432076931</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>1.92200005054474</v>
       </c>
       <c r="G905" t="n">
-        <v>1.72611725330353</v>
+        <v>1.72611713409424</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>2.1949999332428</v>
       </c>
       <c r="G906" t="n">
-        <v>1.97129380702972</v>
+        <v>1.9712940454483</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G907" t="n">
-        <v>1.95782279968262</v>
+        <v>1.9578230381012</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G911" t="n">
-        <v>1.93088030815125</v>
+        <v>1.93088042736053</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G913" t="n">
-        <v>1.94884181022644</v>
+        <v>1.94884192943573</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G916" t="n">
-        <v>1.92189943790436</v>
+        <v>1.92189931869507</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G918" t="n">
-        <v>1.903937458992</v>
+        <v>1.90393769741058</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G920" t="n">
-        <v>1.85005259513855</v>
+        <v>1.85005271434784</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>1.96599996089935</v>
       </c>
       <c r="G924" t="n">
-        <v>1.76563262939453</v>
+        <v>1.76563274860382</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G925" t="n">
-        <v>1.81412923336029</v>
+        <v>1.81412935256958</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>1.98399996757507</v>
       </c>
       <c r="G926" t="n">
-        <v>1.78179824352264</v>
+        <v>1.78179812431335</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>1.93400001525879</v>
       </c>
       <c r="G931" t="n">
-        <v>1.7368940114975</v>
+        <v>1.73689413070679</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G935" t="n">
-        <v>1.81412923336029</v>
+        <v>1.81412935256958</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G939" t="n">
-        <v>1.83209097385406</v>
+        <v>1.83209085464478</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G941" t="n">
-        <v>2.1464204788208</v>
+        <v>2.14642024040222</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G943" t="n">
-        <v>2.16438221931458</v>
+        <v>2.164381980896</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>2.31500005722046</v>
       </c>
       <c r="G945" t="n">
-        <v>2.07906436920166</v>
+        <v>2.07906413078308</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G948" t="n">
-        <v>1.97578454017639</v>
+        <v>1.97578430175781</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G949" t="n">
-        <v>1.92189943790436</v>
+        <v>1.92189931869507</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G952" t="n">
-        <v>2.00272703170776</v>
+        <v>2.00272679328918</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>2.3050000667572</v>
       </c>
       <c r="G954" t="n">
-        <v>2.07008337974548</v>
+        <v>2.0700831413269</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G956" t="n">
-        <v>1.96680343151093</v>
+        <v>1.9668036699295</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G958" t="n">
-        <v>1.97578454017639</v>
+        <v>1.97578430175781</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G960" t="n">
-        <v>1.95782279968262</v>
+        <v>1.9578230381012</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G964" t="n">
-        <v>2.0835542678833</v>
+        <v>2.08355450630188</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>2.40499997138977</v>
       </c>
       <c r="G965" t="n">
-        <v>2.1598916053772</v>
+        <v>2.15989136695862</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G966" t="n">
-        <v>2.16438221931458</v>
+        <v>2.164381980896</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>2.40499997138977</v>
       </c>
       <c r="G968" t="n">
-        <v>2.1598916053772</v>
+        <v>2.15989136695862</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>2.36500000953674</v>
       </c>
       <c r="G969" t="n">
-        <v>2.12396812438965</v>
+        <v>2.12396836280823</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>2.35500001907349</v>
       </c>
       <c r="G970" t="n">
-        <v>2.11498737335205</v>
+        <v>2.11498761177063</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G975" t="n">
-        <v>2.1464204788208</v>
+        <v>2.14642024040222</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G976" t="n">
-        <v>2.1554012298584</v>
+        <v>2.15540146827698</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G982" t="n">
-        <v>2.56851959228516</v>
+        <v>2.56851983070374</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>2.875</v>
       </c>
       <c r="G984" t="n">
-        <v>2.58199071884155</v>
+        <v>2.58199095726013</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G985" t="n">
-        <v>2.64934706687927</v>
+        <v>2.64934754371643</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G987" t="n">
-        <v>2.73017501831055</v>
+        <v>2.73017477989197</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>2.99499988555908</v>
       </c>
       <c r="G992" t="n">
-        <v>2.68976092338562</v>
+        <v>2.6897611618042</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G994" t="n">
-        <v>2.91428184509277</v>
+        <v>2.91428208351135</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G995" t="n">
-        <v>3.05348539352417</v>
+        <v>3.05348491668701</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G996" t="n">
-        <v>3.08042764663696</v>
+        <v>3.08042740821838</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>2.99499988555908</v>
       </c>
       <c r="G999" t="n">
-        <v>2.68976092338562</v>
+        <v>2.6897611618042</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1001" t="n">
-        <v>2.73915576934814</v>
+        <v>2.73915553092957</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1009" t="n">
-        <v>2.66730928421021</v>
+        <v>2.66730904579163</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1010" t="n">
-        <v>2.64934706687927</v>
+        <v>2.64934754371643</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1014" t="n">
-        <v>2.77507877349854</v>
+        <v>2.77507901191711</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>2.99499988555908</v>
       </c>
       <c r="G1017" t="n">
-        <v>2.68976092338562</v>
+        <v>2.6897611618042</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>2.92499995231628</v>
       </c>
       <c r="G1018" t="n">
-        <v>2.6268949508667</v>
+        <v>2.62689518928528</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1021" t="n">
-        <v>2.66730928421021</v>
+        <v>2.66730904579163</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1023" t="n">
-        <v>3.12533187866211</v>
+        <v>3.12533164024353</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>3.3050000667572</v>
       </c>
       <c r="G1027" t="n">
-        <v>2.96816682815552</v>
+        <v>2.9681670665741</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>3.6949999332428</v>
       </c>
       <c r="G1029" t="n">
-        <v>3.31841993331909</v>
+        <v>3.31841969490051</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1031" t="n">
-        <v>3.17921686172485</v>
+        <v>3.17921662330627</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1034" t="n">
-        <v>3.12533187866211</v>
+        <v>3.12533164024353</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>3.81500005722046</v>
       </c>
       <c r="G1041" t="n">
-        <v>3.426189661026</v>
+        <v>3.42618989944458</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1042" t="n">
-        <v>3.24208235740662</v>
+        <v>3.2420825958252</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>3.85500001907349</v>
       </c>
       <c r="G1045" t="n">
-        <v>3.46211338043213</v>
+        <v>3.46211314201355</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1047" t="n">
-        <v>3.25106334686279</v>
+        <v>3.25106310844421</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1048" t="n">
-        <v>3.30494856834412</v>
+        <v>3.30494832992554</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>3.625</v>
       </c>
       <c r="G1049" t="n">
-        <v>3.25555396080017</v>
+        <v>3.25555372238159</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1051" t="n">
-        <v>3.09838914871216</v>
+        <v>3.09838938713074</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1054" t="n">
-        <v>2.85590672492981</v>
+        <v>2.85590648651123</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G1058" t="n">
-        <v>2.77058863639832</v>
+        <v>2.77058839797974</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1059" t="n">
-        <v>2.70323204994202</v>
+        <v>2.7032322883606</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1062" t="n">
-        <v>2.56851959228516</v>
+        <v>2.56851983070374</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G1063" t="n">
-        <v>2.30807518959045</v>
+        <v>2.30807542800903</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>2.45499992370605</v>
       </c>
       <c r="G1064" t="n">
-        <v>2.20479583740234</v>
+        <v>2.20479559898376</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>2</v>
       </c>
       <c r="G1067" t="n">
-        <v>1.79616761207581</v>
+        <v>1.7961677312851</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>1.99399995803833</v>
       </c>
       <c r="G1068" t="n">
-        <v>1.79077911376953</v>
+        <v>1.79077899456024</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1069" t="n">
-        <v>1.81412923336029</v>
+        <v>1.81412935256958</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1070" t="n">
-        <v>1.86801433563232</v>
+        <v>1.86801421642303</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>1.99399995803833</v>
       </c>
       <c r="G1072" t="n">
-        <v>1.79077911376953</v>
+        <v>1.79077899456024</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>2</v>
       </c>
       <c r="G1073" t="n">
-        <v>1.79616761207581</v>
+        <v>1.7961677312851</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>2.16499996185303</v>
       </c>
       <c r="G1074" t="n">
-        <v>1.94435131549835</v>
+        <v>1.94435143470764</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>2.375</v>
       </c>
       <c r="G1076" t="n">
-        <v>2.13294911384583</v>
+        <v>2.13294887542725</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1080" t="n">
-        <v>2.1554012298584</v>
+        <v>2.15540146827698</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G1083" t="n">
-        <v>2.30807518959045</v>
+        <v>2.30807542800903</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1084" t="n">
-        <v>2.45176863670349</v>
+        <v>2.45176887512207</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1085" t="n">
-        <v>2.45176863670349</v>
+        <v>2.45176887512207</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1087" t="n">
-        <v>2.53259634971619</v>
+        <v>2.53259611129761</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>2.9449999332428</v>
       </c>
       <c r="G1091" t="n">
-        <v>2.64485692977905</v>
+        <v>2.64485669136047</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>2.86500000953674</v>
       </c>
       <c r="G1093" t="n">
-        <v>2.57301020622253</v>
+        <v>2.57300996780396</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1094" t="n">
-        <v>2.51463437080383</v>
+        <v>2.51463460922241</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>2.86500000953674</v>
       </c>
       <c r="G1095" t="n">
-        <v>2.57301020622253</v>
+        <v>2.57300996780396</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1100" t="n">
-        <v>2.67628979682922</v>
+        <v>2.6762900352478</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1101" t="n">
-        <v>2.64934706687927</v>
+        <v>2.64934754371643</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29021,7 +29021,7 @@
         <v>2.92499995231628</v>
       </c>
       <c r="G1102" t="n">
-        <v>2.6268949508667</v>
+        <v>2.62689518928528</v>
       </c>
       <c r="H1102" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1104" t="n">
-        <v>2.56851959228516</v>
+        <v>2.56851983070374</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>2.85500001907349</v>
       </c>
       <c r="G1105" t="n">
-        <v>2.56402921676636</v>
+        <v>2.56402945518494</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1106" t="n">
-        <v>2.73017501831055</v>
+        <v>2.73017477989197</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1107" t="n">
-        <v>2.64934706687927</v>
+        <v>2.64934754371643</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>2.86500000953674</v>
       </c>
       <c r="G1108" t="n">
-        <v>2.57301020622253</v>
+        <v>2.57300996780396</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>2.77500009536743</v>
       </c>
       <c r="G1113" t="n">
-        <v>2.49218249320984</v>
+        <v>2.49218273162842</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1114" t="n">
-        <v>2.48769235610962</v>
+        <v>2.48769211769104</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G1115" t="n">
-        <v>2.52810621261597</v>
+        <v>2.52810597419739</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>2.86500000953674</v>
       </c>
       <c r="G1117" t="n">
-        <v>2.57301020622253</v>
+        <v>2.57300996780396</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>2.9449999332428</v>
       </c>
       <c r="G1118" t="n">
-        <v>2.64485692977905</v>
+        <v>2.64485669136047</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>2.89499998092651</v>
       </c>
       <c r="G1119" t="n">
-        <v>2.59995269775391</v>
+        <v>2.59995245933533</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>2.89499998092651</v>
       </c>
       <c r="G1120" t="n">
-        <v>2.59995269775391</v>
+        <v>2.59995245933533</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G1121" t="n">
-        <v>2.61342406272888</v>
+        <v>2.6134238243103</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G1122" t="n">
-        <v>2.61342406272888</v>
+        <v>2.6134238243103</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>2.99499988555908</v>
       </c>
       <c r="G1127" t="n">
-        <v>2.68976092338562</v>
+        <v>2.6897611618042</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>2.85500001907349</v>
       </c>
       <c r="G1128" t="n">
-        <v>2.56402921676636</v>
+        <v>2.56402945518494</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1130" t="n">
-        <v>2.53259634971619</v>
+        <v>2.53259611129761</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>2.85500001907349</v>
       </c>
       <c r="G1132" t="n">
-        <v>2.56402921676636</v>
+        <v>2.56402945518494</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1133" t="n">
-        <v>2.48769235610962</v>
+        <v>2.48769211769104</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -29879,7 +29879,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1135" t="n">
-        <v>2.51463437080383</v>
+        <v>2.51463460922241</v>
       </c>
       <c r="H1135" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1143" t="n">
-        <v>2.48769235610962</v>
+        <v>2.48769211769104</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30113,7 +30113,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1144" t="n">
-        <v>2.46074986457825</v>
+        <v>2.46074962615967</v>
       </c>
       <c r="H1144" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1145" t="n">
-        <v>2.47871136665344</v>
+        <v>2.47871112823486</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1146" t="n">
-        <v>2.45176863670349</v>
+        <v>2.45176887512207</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G1151" t="n">
-        <v>2.40686464309692</v>
+        <v>2.4068648815155</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1152" t="n">
-        <v>2.4158456325531</v>
+        <v>2.41584539413452</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1154" t="n">
-        <v>2.46074986457825</v>
+        <v>2.46074962615967</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1155" t="n">
-        <v>2.53259634971619</v>
+        <v>2.53259611129761</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30425,7 +30425,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1156" t="n">
-        <v>2.48769235610962</v>
+        <v>2.48769211769104</v>
       </c>
       <c r="H1156" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1157" t="n">
-        <v>2.45176863670349</v>
+        <v>2.45176887512207</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1158" t="n">
-        <v>2.46074986457825</v>
+        <v>2.46074962615967</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1159" t="n">
-        <v>2.4158456325531</v>
+        <v>2.41584539413452</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1160" t="n">
-        <v>2.4158456325531</v>
+        <v>2.41584539413452</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>2.57500004768372</v>
       </c>
       <c r="G1168" t="n">
-        <v>2.31256556510925</v>
+        <v>2.31256580352783</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>2.74499988555908</v>
       </c>
       <c r="G1171" t="n">
-        <v>2.46524024009705</v>
+        <v>2.46524000167847</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30919,7 +30919,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1175" t="n">
-        <v>2.47871136665344</v>
+        <v>2.47871112823486</v>
       </c>
       <c r="H1175" t="s">
         <v>8</v>
@@ -30945,7 +30945,7 @@
         <v>2.74499988555908</v>
       </c>
       <c r="G1176" t="n">
-        <v>2.46524024009705</v>
+        <v>2.46524000167847</v>
       </c>
       <c r="H1176" t="s">
         <v>8</v>
@@ -30971,7 +30971,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1177" t="n">
-        <v>2.48769235610962</v>
+        <v>2.48769211769104</v>
       </c>
       <c r="H1177" t="s">
         <v>8</v>
@@ -31023,7 +31023,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1179" t="n">
-        <v>2.4158456325531</v>
+        <v>2.41584539413452</v>
       </c>
       <c r="H1179" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1181" t="n">
-        <v>2.37992215156555</v>
+        <v>2.37992238998413</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>2.625</v>
       </c>
       <c r="G1184" t="n">
-        <v>2.3574697971344</v>
+        <v>2.35747003555298</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G1185" t="n">
-        <v>2.36196064949036</v>
+        <v>2.36196041107178</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>2.65499997138977</v>
       </c>
       <c r="G1186" t="n">
-        <v>2.38441252708435</v>
+        <v>2.38441276550293</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>2.67499995231628</v>
       </c>
       <c r="G1188" t="n">
-        <v>2.40237426757812</v>
+        <v>2.40237402915955</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1190" t="n">
-        <v>2.37992215156555</v>
+        <v>2.37992238998413</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>2.67499995231628</v>
       </c>
       <c r="G1191" t="n">
-        <v>2.40237426757812</v>
+        <v>2.40237402915955</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>2.625</v>
       </c>
       <c r="G1192" t="n">
-        <v>2.3574697971344</v>
+        <v>2.35747003555298</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1194" t="n">
-        <v>2.46074986457825</v>
+        <v>2.46074962615967</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>2.57500004768372</v>
       </c>
       <c r="G1201" t="n">
-        <v>2.31256556510925</v>
+        <v>2.31256580352783</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31725,7 +31725,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1206" t="n">
-        <v>2.23622894287109</v>
+        <v>2.23622870445251</v>
       </c>
       <c r="H1206" t="s">
         <v>8</v>
@@ -31855,7 +31855,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G1211" t="n">
-        <v>2.32603693008423</v>
+        <v>2.32603716850281</v>
       </c>
       <c r="H1211" t="s">
         <v>8</v>
@@ -31881,7 +31881,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1212" t="n">
-        <v>2.37992215156555</v>
+        <v>2.37992238998413</v>
       </c>
       <c r="H1212" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1215" t="n">
-        <v>2.37992215156555</v>
+        <v>2.37992238998413</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -31985,7 +31985,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G1216" t="n">
-        <v>2.32603693008423</v>
+        <v>2.32603716850281</v>
       </c>
       <c r="H1216" t="s">
         <v>8</v>
@@ -32011,7 +32011,7 @@
         <v>2.74499988555908</v>
       </c>
       <c r="G1217" t="n">
-        <v>2.46524024009705</v>
+        <v>2.46524000167847</v>
       </c>
       <c r="H1217" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1220" t="n">
-        <v>2.53259634971619</v>
+        <v>2.53259611129761</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>2.86500000953674</v>
       </c>
       <c r="G1223" t="n">
-        <v>2.57301020622253</v>
+        <v>2.57300996780396</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32193,7 +32193,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1224" t="n">
-        <v>2.53259634971619</v>
+        <v>2.53259611129761</v>
       </c>
       <c r="H1224" t="s">
         <v>8</v>
@@ -32297,7 +32297,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G1228" t="n">
-        <v>2.35297966003418</v>
+        <v>2.3529794216156</v>
       </c>
       <c r="H1228" t="s">
         <v>8</v>
@@ -32479,7 +32479,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1235" t="n">
-        <v>2.37992215156555</v>
+        <v>2.37992238998413</v>
       </c>
       <c r="H1235" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1237" t="n">
-        <v>2.4158456325531</v>
+        <v>2.41584539413452</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -32557,7 +32557,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1238" t="n">
-        <v>2.37992215156555</v>
+        <v>2.37992238998413</v>
       </c>
       <c r="H1238" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1240" t="n">
-        <v>2.45176863670349</v>
+        <v>2.45176887512207</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>2.77500009536743</v>
       </c>
       <c r="G1242" t="n">
-        <v>2.49218249320984</v>
+        <v>2.49218273162842</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1243" t="n">
-        <v>2.47871136665344</v>
+        <v>2.47871112823486</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1246" t="n">
-        <v>2.53259634971619</v>
+        <v>2.53259611129761</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1248" t="n">
-        <v>2.56851959228516</v>
+        <v>2.56851983070374</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32843,7 +32843,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1249" t="n">
-        <v>2.53259634971619</v>
+        <v>2.53259611129761</v>
       </c>
       <c r="H1249" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1253" t="n">
-        <v>2.67628979682922</v>
+        <v>2.6762900352478</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -33025,7 +33025,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G1256" t="n">
-        <v>2.76160788536072</v>
+        <v>2.76160764694214</v>
       </c>
       <c r="H1256" t="s">
         <v>8</v>
@@ -33051,7 +33051,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1257" t="n">
-        <v>2.73915576934814</v>
+        <v>2.73915553092957</v>
       </c>
       <c r="H1257" t="s">
         <v>8</v>
@@ -33077,7 +33077,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1258" t="n">
-        <v>2.73017501831055</v>
+        <v>2.73017477989197</v>
       </c>
       <c r="H1258" t="s">
         <v>8</v>
@@ -33129,7 +33129,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1260" t="n">
-        <v>2.77507877349854</v>
+        <v>2.77507901191711</v>
       </c>
       <c r="H1260" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1262" t="n">
-        <v>2.77507877349854</v>
+        <v>2.77507901191711</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1263" t="n">
-        <v>2.84692549705505</v>
+        <v>2.84692573547363</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33285,7 +33285,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G1266" t="n">
-        <v>2.77058863639832</v>
+        <v>2.77058839797974</v>
       </c>
       <c r="H1266" t="s">
         <v>8</v>
@@ -33415,7 +33415,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1271" t="n">
-        <v>2.77507877349854</v>
+        <v>2.77507901191711</v>
       </c>
       <c r="H1271" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1274" t="n">
-        <v>2.77507877349854</v>
+        <v>2.77507901191711</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G1275" t="n">
-        <v>2.77058863639832</v>
+        <v>2.77058839797974</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33649,7 +33649,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1280" t="n">
-        <v>2.73017501831055</v>
+        <v>2.73017477989197</v>
       </c>
       <c r="H1280" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>2.99499988555908</v>
       </c>
       <c r="G1282" t="n">
-        <v>2.68976092338562</v>
+        <v>2.6897611618042</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>2.9449999332428</v>
       </c>
       <c r="G1283" t="n">
-        <v>2.64485692977905</v>
+        <v>2.64485669136047</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33779,7 +33779,7 @@
         <v>2.92499995231628</v>
       </c>
       <c r="G1285" t="n">
-        <v>2.6268949508667</v>
+        <v>2.62689518928528</v>
       </c>
       <c r="H1285" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G1286" t="n">
-        <v>2.54606771469116</v>
+        <v>2.54606747627258</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -34013,7 +34013,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G1294" t="n">
-        <v>2.76160788536072</v>
+        <v>2.76160764694214</v>
       </c>
       <c r="H1294" t="s">
         <v>8</v>
@@ -34169,7 +34169,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G1300" t="n">
-        <v>3.12982201576233</v>
+        <v>3.12982177734375</v>
       </c>
       <c r="H1300" t="s">
         <v>8</v>
@@ -34221,7 +34221,7 @@
         <v>3.49499988555908</v>
       </c>
       <c r="G1302" t="n">
-        <v>3.13880300521851</v>
+        <v>3.13880276679993</v>
       </c>
       <c r="H1302" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>3.41499996185303</v>
       </c>
       <c r="G1303" t="n">
-        <v>3.06695628166199</v>
+        <v>3.06695604324341</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34299,7 +34299,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G1305" t="n">
-        <v>3.12982201576233</v>
+        <v>3.12982177734375</v>
       </c>
       <c r="H1305" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>3.22499990463257</v>
       </c>
       <c r="G1310" t="n">
-        <v>2.89632034301758</v>
+        <v>2.896320104599</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>3.43499994277954</v>
       </c>
       <c r="G1311" t="n">
-        <v>3.08491778373718</v>
+        <v>3.08491802215576</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34481,7 +34481,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1312" t="n">
-        <v>3.01756143569946</v>
+        <v>3.01756167411804</v>
       </c>
       <c r="H1312" t="s">
         <v>8</v>
@@ -34585,7 +34585,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1316" t="n">
-        <v>3.05348539352417</v>
+        <v>3.05348491668701</v>
       </c>
       <c r="H1316" t="s">
         <v>8</v>
@@ -34663,7 +34663,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1319" t="n">
-        <v>3.09838914871216</v>
+        <v>3.09838938713074</v>
       </c>
       <c r="H1319" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>3.3050000667572</v>
       </c>
       <c r="G1327" t="n">
-        <v>2.96816682815552</v>
+        <v>2.9681670665741</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -34923,7 +34923,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1329" t="n">
-        <v>3.03552317619324</v>
+        <v>3.0355236530304</v>
       </c>
       <c r="H1329" t="s">
         <v>8</v>
@@ -34949,7 +34949,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1330" t="n">
-        <v>3.04450416564941</v>
+        <v>3.04450440406799</v>
       </c>
       <c r="H1330" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1332" t="n">
-        <v>3.01756143569946</v>
+        <v>3.01756167411804</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35027,7 +35027,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1333" t="n">
-        <v>3.03552317619324</v>
+        <v>3.0355236530304</v>
       </c>
       <c r="H1333" t="s">
         <v>8</v>
@@ -35079,7 +35079,7 @@
         <v>3.31500005722046</v>
       </c>
       <c r="G1335" t="n">
-        <v>2.97714781761169</v>
+        <v>2.97714805603027</v>
       </c>
       <c r="H1335" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1336" t="n">
-        <v>2.85590672492981</v>
+        <v>2.85590648651123</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1339" t="n">
-        <v>2.86488747596741</v>
+        <v>2.86488723754883</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1340" t="n">
-        <v>2.9008104801178</v>
+        <v>2.90081095695496</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35313,7 +35313,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1344" t="n">
-        <v>2.85590672492981</v>
+        <v>2.85590648651123</v>
       </c>
       <c r="H1344" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>3.14499998092651</v>
       </c>
       <c r="G1345" t="n">
-        <v>2.82447361946106</v>
+        <v>2.82447338104248</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35365,7 +35365,7 @@
         <v>3.11500000953674</v>
       </c>
       <c r="G1346" t="n">
-        <v>2.79753112792969</v>
+        <v>2.79753088951111</v>
       </c>
       <c r="H1346" t="s">
         <v>8</v>
@@ -35391,7 +35391,7 @@
         <v>3.25</v>
       </c>
       <c r="G1347" t="n">
-        <v>2.91877269744873</v>
+        <v>2.91877245903015</v>
       </c>
       <c r="H1347" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1349" t="n">
-        <v>3.05348539352417</v>
+        <v>3.05348491668701</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35573,7 +35573,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1354" t="n">
-        <v>3.05348539352417</v>
+        <v>3.05348491668701</v>
       </c>
       <c r="H1354" t="s">
         <v>8</v>
@@ -35677,7 +35677,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1358" t="n">
-        <v>3.30494856834412</v>
+        <v>3.30494832992554</v>
       </c>
       <c r="H1358" t="s">
         <v>8</v>
@@ -35729,7 +35729,7 @@
         <v>3.60500001907349</v>
       </c>
       <c r="G1360" t="n">
-        <v>3.2375922203064</v>
+        <v>3.23759198188782</v>
       </c>
       <c r="H1360" t="s">
         <v>8</v>
@@ -35781,7 +35781,7 @@
         <v>3.68499994277954</v>
       </c>
       <c r="G1362" t="n">
-        <v>3.30943870544434</v>
+        <v>3.30943894386292</v>
       </c>
       <c r="H1362" t="s">
         <v>8</v>
@@ -35807,7 +35807,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1363" t="n">
-        <v>3.18819761276245</v>
+        <v>3.18819737434387</v>
       </c>
       <c r="H1363" t="s">
         <v>8</v>
@@ -35859,7 +35859,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G1365" t="n">
-        <v>3.21963047981262</v>
+        <v>3.2196307182312</v>
       </c>
       <c r="H1365" t="s">
         <v>8</v>
@@ -35911,7 +35911,7 @@
         <v>3.46499991416931</v>
       </c>
       <c r="G1367" t="n">
-        <v>3.11186003684998</v>
+        <v>3.11186051368713</v>
       </c>
       <c r="H1367" t="s">
         <v>8</v>
@@ -35937,7 +35937,7 @@
         <v>3.46499991416931</v>
       </c>
       <c r="G1368" t="n">
-        <v>3.11186003684998</v>
+        <v>3.11186051368713</v>
       </c>
       <c r="H1368" t="s">
         <v>8</v>
@@ -35963,7 +35963,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1369" t="n">
-        <v>3.11635112762451</v>
+        <v>3.11635088920593</v>
       </c>
       <c r="H1369" t="s">
         <v>8</v>
@@ -35989,7 +35989,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1370" t="n">
-        <v>3.12533187866211</v>
+        <v>3.12533164024353</v>
       </c>
       <c r="H1370" t="s">
         <v>8</v>
@@ -36015,7 +36015,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1371" t="n">
-        <v>3.08042764663696</v>
+        <v>3.08042740821838</v>
       </c>
       <c r="H1371" t="s">
         <v>8</v>
@@ -36041,7 +36041,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1372" t="n">
-        <v>3.05348539352417</v>
+        <v>3.05348491668701</v>
       </c>
       <c r="H1372" t="s">
         <v>8</v>
@@ -36067,7 +36067,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1373" t="n">
-        <v>3.04450416564941</v>
+        <v>3.04450440406799</v>
       </c>
       <c r="H1373" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1375" t="n">
-        <v>3.04450416564941</v>
+        <v>3.04450440406799</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36301,7 +36301,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1382" t="n">
-        <v>3.04450416564941</v>
+        <v>3.04450440406799</v>
       </c>
       <c r="H1382" t="s">
         <v>8</v>
@@ -36327,7 +36327,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1383" t="n">
-        <v>3.08042764663696</v>
+        <v>3.08042740821838</v>
       </c>
       <c r="H1383" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>3.43499994277954</v>
       </c>
       <c r="G1387" t="n">
-        <v>3.08491778373718</v>
+        <v>3.08491802215576</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36457,7 +36457,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1388" t="n">
-        <v>3.01756143569946</v>
+        <v>3.01756167411804</v>
       </c>
       <c r="H1388" t="s">
         <v>8</v>
@@ -36639,7 +36639,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G1395" t="n">
-        <v>3.21963047981262</v>
+        <v>3.2196307182312</v>
       </c>
       <c r="H1395" t="s">
         <v>8</v>
@@ -36743,7 +36743,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1399" t="n">
-        <v>3.25106334686279</v>
+        <v>3.25106310844421</v>
       </c>
       <c r="H1399" t="s">
         <v>8</v>
@@ -36795,7 +36795,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1401" t="n">
-        <v>3.22412085533142</v>
+        <v>3.22412061691284</v>
       </c>
       <c r="H1401" t="s">
         <v>8</v>
@@ -36873,7 +36873,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1404" t="n">
-        <v>3.04450416564941</v>
+        <v>3.04450440406799</v>
       </c>
       <c r="H1404" t="s">
         <v>8</v>
@@ -36951,7 +36951,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1407" t="n">
-        <v>3.04450416564941</v>
+        <v>3.04450440406799</v>
       </c>
       <c r="H1407" t="s">
         <v>8</v>
@@ -37107,7 +37107,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1413" t="n">
-        <v>3.01756143569946</v>
+        <v>3.01756167411804</v>
       </c>
       <c r="H1413" t="s">
         <v>8</v>
@@ -37133,7 +37133,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1414" t="n">
-        <v>3.04450416564941</v>
+        <v>3.04450440406799</v>
       </c>
       <c r="H1414" t="s">
         <v>8</v>
@@ -37211,7 +37211,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1417" t="n">
-        <v>3.01756143569946</v>
+        <v>3.01756167411804</v>
       </c>
       <c r="H1417" t="s">
         <v>8</v>
@@ -37523,7 +37523,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1429" t="n">
-        <v>2.90979146957397</v>
+        <v>2.90979170799255</v>
       </c>
       <c r="H1429" t="s">
         <v>8</v>
@@ -37549,7 +37549,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1430" t="n">
-        <v>3.04450416564941</v>
+        <v>3.04450440406799</v>
       </c>
       <c r="H1430" t="s">
         <v>8</v>
@@ -37679,7 +37679,7 @@
         <v>3.3050000667572</v>
       </c>
       <c r="G1435" t="n">
-        <v>2.96816682815552</v>
+        <v>2.9681670665741</v>
       </c>
       <c r="H1435" t="s">
         <v>8</v>
@@ -37705,7 +37705,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1436" t="n">
-        <v>2.93673419952393</v>
+        <v>2.93673396110535</v>
       </c>
       <c r="H1436" t="s">
         <v>8</v>
@@ -37731,7 +37731,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1437" t="n">
-        <v>2.93673419952393</v>
+        <v>2.93673396110535</v>
       </c>
       <c r="H1437" t="s">
         <v>8</v>
@@ -37757,7 +37757,7 @@
         <v>3.25</v>
       </c>
       <c r="G1438" t="n">
-        <v>2.91877269744873</v>
+        <v>2.91877245903015</v>
       </c>
       <c r="H1438" t="s">
         <v>8</v>
@@ -37783,7 +37783,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1439" t="n">
-        <v>2.93673419952393</v>
+        <v>2.93673396110535</v>
       </c>
       <c r="H1439" t="s">
         <v>8</v>
@@ -37887,7 +37887,7 @@
         <v>3.31500005722046</v>
       </c>
       <c r="G1443" t="n">
-        <v>2.97714781761169</v>
+        <v>2.97714805603027</v>
       </c>
       <c r="H1443" t="s">
         <v>8</v>
@@ -37939,7 +37939,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1445" t="n">
-        <v>2.93673419952393</v>
+        <v>2.93673396110535</v>
       </c>
       <c r="H1445" t="s">
         <v>8</v>
@@ -38017,7 +38017,7 @@
         <v>3.25</v>
       </c>
       <c r="G1448" t="n">
-        <v>2.91877269744873</v>
+        <v>2.91877245903015</v>
       </c>
       <c r="H1448" t="s">
         <v>8</v>
@@ -38043,7 +38043,7 @@
         <v>3.22499990463257</v>
       </c>
       <c r="G1449" t="n">
-        <v>2.89632034301758</v>
+        <v>2.896320104599</v>
       </c>
       <c r="H1449" t="s">
         <v>8</v>
@@ -38069,7 +38069,7 @@
         <v>3.22499990463257</v>
       </c>
       <c r="G1450" t="n">
-        <v>2.89632034301758</v>
+        <v>2.896320104599</v>
       </c>
       <c r="H1450" t="s">
         <v>8</v>
@@ -38173,7 +38173,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1454" t="n">
-        <v>2.82896423339844</v>
+        <v>2.82896399497986</v>
       </c>
       <c r="H1454" t="s">
         <v>8</v>
@@ -38199,7 +38199,7 @@
         <v>3.15499997138977</v>
       </c>
       <c r="G1455" t="n">
-        <v>2.83345437049866</v>
+        <v>2.83345460891724</v>
       </c>
       <c r="H1455" t="s">
         <v>8</v>
@@ -38225,7 +38225,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G1456" t="n">
-        <v>2.91428184509277</v>
+        <v>2.91428208351135</v>
       </c>
       <c r="H1456" t="s">
         <v>8</v>
@@ -38277,7 +38277,7 @@
         <v>3.25</v>
       </c>
       <c r="G1458" t="n">
-        <v>2.91877269744873</v>
+        <v>2.91877245903015</v>
       </c>
       <c r="H1458" t="s">
         <v>8</v>
@@ -38329,7 +38329,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1460" t="n">
-        <v>3.05348539352417</v>
+        <v>3.05348491668701</v>
       </c>
       <c r="H1460" t="s">
         <v>8</v>
@@ -38355,7 +38355,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1461" t="n">
-        <v>3.09838914871216</v>
+        <v>3.09838938713074</v>
       </c>
       <c r="H1461" t="s">
         <v>8</v>
@@ -38407,7 +38407,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1463" t="n">
-        <v>3.05348539352417</v>
+        <v>3.05348491668701</v>
       </c>
       <c r="H1463" t="s">
         <v>8</v>
@@ -38589,7 +38589,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1470" t="n">
-        <v>2.90979146957397</v>
+        <v>2.90979170799255</v>
       </c>
       <c r="H1470" t="s">
         <v>8</v>
@@ -38667,7 +38667,7 @@
         <v>3.49499988555908</v>
       </c>
       <c r="G1473" t="n">
-        <v>3.13880300521851</v>
+        <v>3.13880276679993</v>
       </c>
       <c r="H1473" t="s">
         <v>8</v>
@@ -38719,7 +38719,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1475" t="n">
-        <v>3.09838914871216</v>
+        <v>3.09838938713074</v>
       </c>
       <c r="H1475" t="s">
         <v>8</v>
@@ -38771,7 +38771,7 @@
         <v>3.49499988555908</v>
       </c>
       <c r="G1477" t="n">
-        <v>3.13880300521851</v>
+        <v>3.13880276679993</v>
       </c>
       <c r="H1477" t="s">
         <v>8</v>
@@ -38797,7 +38797,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1478" t="n">
-        <v>3.12533187866211</v>
+        <v>3.12533164024353</v>
       </c>
       <c r="H1478" t="s">
         <v>8</v>
@@ -38823,7 +38823,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1479" t="n">
-        <v>3.12533187866211</v>
+        <v>3.12533164024353</v>
       </c>
       <c r="H1479" t="s">
         <v>8</v>
@@ -38875,7 +38875,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1481" t="n">
-        <v>3.26902508735657</v>
+        <v>3.26902532577515</v>
       </c>
       <c r="H1481" t="s">
         <v>8</v>
@@ -38901,7 +38901,7 @@
         <v>3.625</v>
       </c>
       <c r="G1482" t="n">
-        <v>3.25555396080017</v>
+        <v>3.25555372238159</v>
       </c>
       <c r="H1482" t="s">
         <v>8</v>
@@ -38927,7 +38927,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1483" t="n">
-        <v>3.22412085533142</v>
+        <v>3.22412061691284</v>
       </c>
       <c r="H1483" t="s">
         <v>8</v>
@@ -38979,7 +38979,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1485" t="n">
-        <v>3.15227389335632</v>
+        <v>3.1522741317749</v>
       </c>
       <c r="H1485" t="s">
         <v>8</v>
@@ -39187,7 +39187,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1493" t="n">
-        <v>3.24208235740662</v>
+        <v>3.2420825958252</v>
       </c>
       <c r="H1493" t="s">
         <v>8</v>
@@ -39239,7 +39239,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1495" t="n">
-        <v>3.24208235740662</v>
+        <v>3.2420825958252</v>
       </c>
       <c r="H1495" t="s">
         <v>8</v>
@@ -39317,7 +39317,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1498" t="n">
-        <v>3.17921686172485</v>
+        <v>3.17921662330627</v>
       </c>
       <c r="H1498" t="s">
         <v>8</v>
@@ -39343,7 +39343,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G1499" t="n">
-        <v>3.14778399467468</v>
+        <v>3.1477837562561</v>
       </c>
       <c r="H1499" t="s">
         <v>8</v>
@@ -39369,7 +39369,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1500" t="n">
-        <v>3.09838914871216</v>
+        <v>3.09838938713074</v>
       </c>
       <c r="H1500" t="s">
         <v>8</v>
@@ -39395,7 +39395,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1501" t="n">
-        <v>3.08042764663696</v>
+        <v>3.08042740821838</v>
       </c>
       <c r="H1501" t="s">
         <v>8</v>
@@ -39473,7 +39473,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1504" t="n">
-        <v>3.11635112762451</v>
+        <v>3.11635088920593</v>
       </c>
       <c r="H1504" t="s">
         <v>8</v>
@@ -39577,7 +39577,7 @@
         <v>3.46499991416931</v>
       </c>
       <c r="G1508" t="n">
-        <v>3.11186003684998</v>
+        <v>3.11186051368713</v>
       </c>
       <c r="H1508" t="s">
         <v>8</v>
@@ -39681,7 +39681,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1512" t="n">
-        <v>3.08042764663696</v>
+        <v>3.08042740821838</v>
       </c>
       <c r="H1512" t="s">
         <v>8</v>
@@ -39733,7 +39733,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G1514" t="n">
-        <v>3.14778399467468</v>
+        <v>3.1477837562561</v>
       </c>
       <c r="H1514" t="s">
         <v>8</v>
@@ -39863,7 +39863,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1519" t="n">
-        <v>3.30494856834412</v>
+        <v>3.30494832992554</v>
       </c>
       <c r="H1519" t="s">
         <v>8</v>
@@ -39889,7 +39889,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1520" t="n">
-        <v>3.25106334686279</v>
+        <v>3.25106310844421</v>
       </c>
       <c r="H1520" t="s">
         <v>8</v>
@@ -39967,7 +39967,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1523" t="n">
-        <v>3.25106334686279</v>
+        <v>3.25106310844421</v>
       </c>
       <c r="H1523" t="s">
         <v>8</v>
@@ -39993,7 +39993,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1524" t="n">
-        <v>3.26902508735657</v>
+        <v>3.26902532577515</v>
       </c>
       <c r="H1524" t="s">
         <v>8</v>
@@ -40019,7 +40019,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1525" t="n">
-        <v>3.30494856834412</v>
+        <v>3.30494832992554</v>
       </c>
       <c r="H1525" t="s">
         <v>8</v>
@@ -40071,7 +40071,7 @@
         <v>3.68499994277954</v>
       </c>
       <c r="G1527" t="n">
-        <v>3.30943870544434</v>
+        <v>3.30943894386292</v>
       </c>
       <c r="H1527" t="s">
         <v>8</v>
@@ -40123,7 +40123,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1529" t="n">
-        <v>3.26902508735657</v>
+        <v>3.26902532577515</v>
       </c>
       <c r="H1529" t="s">
         <v>8</v>
@@ -40175,7 +40175,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1531" t="n">
-        <v>3.17921686172485</v>
+        <v>3.17921662330627</v>
       </c>
       <c r="H1531" t="s">
         <v>8</v>
@@ -40227,7 +40227,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G1533" t="n">
-        <v>3.14778399467468</v>
+        <v>3.1477837562561</v>
       </c>
       <c r="H1533" t="s">
         <v>8</v>
@@ -40253,7 +40253,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G1534" t="n">
-        <v>3.14778399467468</v>
+        <v>3.1477837562561</v>
       </c>
       <c r="H1534" t="s">
         <v>8</v>
@@ -40331,7 +40331,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1537" t="n">
-        <v>3.09838914871216</v>
+        <v>3.09838938713074</v>
       </c>
       <c r="H1537" t="s">
         <v>8</v>
@@ -40617,7 +40617,7 @@
         <v>3.46499991416931</v>
       </c>
       <c r="G1548" t="n">
-        <v>3.11186003684998</v>
+        <v>3.11186051368713</v>
       </c>
       <c r="H1548" t="s">
         <v>8</v>
@@ -40669,7 +40669,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1550" t="n">
-        <v>3.11635112762451</v>
+        <v>3.11635088920593</v>
       </c>
       <c r="H1550" t="s">
         <v>8</v>
@@ -40799,7 +40799,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1555" t="n">
-        <v>3.01756143569946</v>
+        <v>3.01756167411804</v>
       </c>
       <c r="H1555" t="s">
         <v>8</v>
@@ -40851,7 +40851,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1557" t="n">
-        <v>2.93673419952393</v>
+        <v>2.93673396110535</v>
       </c>
       <c r="H1557" t="s">
         <v>8</v>
@@ -40877,7 +40877,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1558" t="n">
-        <v>3.05348539352417</v>
+        <v>3.05348491668701</v>
       </c>
       <c r="H1558" t="s">
         <v>8</v>
@@ -40903,7 +40903,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1559" t="n">
-        <v>3.03552317619324</v>
+        <v>3.0355236530304</v>
       </c>
       <c r="H1559" t="s">
         <v>8</v>
@@ -41007,7 +41007,7 @@
         <v>3.25</v>
       </c>
       <c r="G1563" t="n">
-        <v>2.91877269744873</v>
+        <v>2.91877245903015</v>
       </c>
       <c r="H1563" t="s">
         <v>8</v>
@@ -41137,7 +41137,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1568" t="n">
-        <v>2.70323204994202</v>
+        <v>2.7032322883606</v>
       </c>
       <c r="H1568" t="s">
         <v>8</v>
@@ -41189,7 +41189,7 @@
         <v>2.95499992370605</v>
       </c>
       <c r="G1570" t="n">
-        <v>2.65383768081665</v>
+        <v>2.65383744239807</v>
       </c>
       <c r="H1570" t="s">
         <v>8</v>
@@ -41267,7 +41267,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1573" t="n">
-        <v>2.47871136665344</v>
+        <v>2.47871112823486</v>
       </c>
       <c r="H1573" t="s">
         <v>8</v>
@@ -41345,7 +41345,7 @@
         <v>2.9449999332428</v>
       </c>
       <c r="G1576" t="n">
-        <v>2.64485692977905</v>
+        <v>2.64485669136047</v>
       </c>
       <c r="H1576" t="s">
         <v>8</v>
@@ -41371,7 +41371,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1577" t="n">
-        <v>2.67628979682922</v>
+        <v>2.6762900352478</v>
       </c>
       <c r="H1577" t="s">
         <v>8</v>
@@ -41397,7 +41397,7 @@
         <v>2.92499995231628</v>
       </c>
       <c r="G1578" t="n">
-        <v>2.6268949508667</v>
+        <v>2.62689518928528</v>
       </c>
       <c r="H1578" t="s">
         <v>8</v>
@@ -41527,7 +41527,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1583" t="n">
-        <v>2.82896423339844</v>
+        <v>2.82896399497986</v>
       </c>
       <c r="H1583" t="s">
         <v>8</v>
@@ -41553,7 +41553,7 @@
         <v>3.15499997138977</v>
       </c>
       <c r="G1584" t="n">
-        <v>2.83345437049866</v>
+        <v>2.83345460891724</v>
       </c>
       <c r="H1584" t="s">
         <v>8</v>
@@ -41605,7 +41605,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G1586" t="n">
-        <v>2.77058863639832</v>
+        <v>2.77058839797974</v>
       </c>
       <c r="H1586" t="s">
         <v>8</v>
@@ -41657,7 +41657,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G1588" t="n">
-        <v>2.8783586025238</v>
+        <v>2.87835836410522</v>
       </c>
       <c r="H1588" t="s">
         <v>8</v>
@@ -41683,7 +41683,7 @@
         <v>3.14499998092651</v>
       </c>
       <c r="G1589" t="n">
-        <v>2.82447361946106</v>
+        <v>2.82447338104248</v>
       </c>
       <c r="H1589" t="s">
         <v>8</v>
@@ -41709,7 +41709,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1590" t="n">
-        <v>2.85590672492981</v>
+        <v>2.85590648651123</v>
       </c>
       <c r="H1590" t="s">
         <v>8</v>
@@ -41787,7 +41787,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1593" t="n">
-        <v>2.82896423339844</v>
+        <v>2.82896399497986</v>
       </c>
       <c r="H1593" t="s">
         <v>8</v>
@@ -41813,7 +41813,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G1594" t="n">
-        <v>2.76160788536072</v>
+        <v>2.76160764694214</v>
       </c>
       <c r="H1594" t="s">
         <v>8</v>
@@ -41917,7 +41917,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1598" t="n">
-        <v>2.77507877349854</v>
+        <v>2.77507901191711</v>
       </c>
       <c r="H1598" t="s">
         <v>8</v>
@@ -42021,7 +42021,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1602" t="n">
-        <v>3.01756143569946</v>
+        <v>3.01756167411804</v>
       </c>
       <c r="H1602" t="s">
         <v>8</v>
@@ -42099,7 +42099,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1605" t="n">
-        <v>3.03552317619324</v>
+        <v>3.0355236530304</v>
       </c>
       <c r="H1605" t="s">
         <v>8</v>
@@ -42177,7 +42177,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1608" t="n">
-        <v>3.05348539352417</v>
+        <v>3.05348491668701</v>
       </c>
       <c r="H1608" t="s">
         <v>8</v>
@@ -42229,7 +42229,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1610" t="n">
-        <v>3.01756143569946</v>
+        <v>3.01756167411804</v>
       </c>
       <c r="H1610" t="s">
         <v>8</v>
@@ -42359,7 +42359,7 @@
         <v>2.95499992370605</v>
       </c>
       <c r="G1615" t="n">
-        <v>2.65383768081665</v>
+        <v>2.65383744239807</v>
       </c>
       <c r="H1615" t="s">
         <v>8</v>
@@ -42411,7 +42411,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1617" t="n">
-        <v>2.77507877349854</v>
+        <v>2.77507901191711</v>
       </c>
       <c r="H1617" t="s">
         <v>8</v>
@@ -42437,7 +42437,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1618" t="n">
-        <v>2.84692549705505</v>
+        <v>2.84692573547363</v>
       </c>
       <c r="H1618" t="s">
         <v>8</v>
@@ -42463,7 +42463,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1619" t="n">
-        <v>2.86488747596741</v>
+        <v>2.86488723754883</v>
       </c>
       <c r="H1619" t="s">
         <v>8</v>
@@ -42515,7 +42515,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1621" t="n">
-        <v>2.84692549705505</v>
+        <v>2.84692573547363</v>
       </c>
       <c r="H1621" t="s">
         <v>8</v>
@@ -42541,7 +42541,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G1622" t="n">
-        <v>2.91428184509277</v>
+        <v>2.91428208351135</v>
       </c>
       <c r="H1622" t="s">
         <v>8</v>
@@ -42645,7 +42645,7 @@
         <v>3.11500000953674</v>
       </c>
       <c r="G1626" t="n">
-        <v>2.79753112792969</v>
+        <v>2.79753088951111</v>
       </c>
       <c r="H1626" t="s">
         <v>8</v>
@@ -42671,7 +42671,7 @@
         <v>3.06500005722046</v>
       </c>
       <c r="G1627" t="n">
-        <v>2.75262689590454</v>
+        <v>2.75262713432312</v>
       </c>
       <c r="H1627" t="s">
         <v>8</v>
@@ -42697,7 +42697,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1628" t="n">
-        <v>2.77507877349854</v>
+        <v>2.77507901191711</v>
       </c>
       <c r="H1628" t="s">
         <v>8</v>
@@ -42749,7 +42749,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1630" t="n">
-        <v>2.73915576934814</v>
+        <v>2.73915553092957</v>
       </c>
       <c r="H1630" t="s">
         <v>8</v>
@@ -43035,7 +43035,7 @@
         <v>2.92499995231628</v>
       </c>
       <c r="G1641" t="n">
-        <v>2.6268949508667</v>
+        <v>2.62689518928528</v>
       </c>
       <c r="H1641" t="s">
         <v>8</v>
@@ -43113,7 +43113,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1644" t="n">
-        <v>2.67628979682922</v>
+        <v>2.6762900352478</v>
       </c>
       <c r="H1644" t="s">
         <v>8</v>
@@ -43139,7 +43139,7 @@
         <v>2.89499998092651</v>
       </c>
       <c r="G1645" t="n">
-        <v>2.59995269775391</v>
+        <v>2.59995245933533</v>
       </c>
       <c r="H1645" t="s">
         <v>8</v>
@@ -43295,7 +43295,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G1651" t="n">
-        <v>2.52810621261597</v>
+        <v>2.52810597419739</v>
       </c>
       <c r="H1651" t="s">
         <v>8</v>
@@ -43373,7 +43373,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1654" t="n">
-        <v>2.45176863670349</v>
+        <v>2.45176887512207</v>
       </c>
       <c r="H1654" t="s">
         <v>8</v>
@@ -43425,7 +43425,7 @@
         <v>2.71499991416931</v>
       </c>
       <c r="G1656" t="n">
-        <v>2.43829727172852</v>
+        <v>2.43829751014709</v>
       </c>
       <c r="H1656" t="s">
         <v>8</v>
@@ -43477,7 +43477,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G1658" t="n">
-        <v>2.52810621261597</v>
+        <v>2.52810597419739</v>
       </c>
       <c r="H1658" t="s">
         <v>8</v>
@@ -43555,7 +43555,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1661" t="n">
-        <v>2.56851959228516</v>
+        <v>2.56851983070374</v>
       </c>
       <c r="H1661" t="s">
         <v>8</v>
@@ -43581,7 +43581,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1662" t="n">
-        <v>2.53259634971619</v>
+        <v>2.53259611129761</v>
       </c>
       <c r="H1662" t="s">
         <v>8</v>
@@ -43607,7 +43607,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1663" t="n">
-        <v>2.53259634971619</v>
+        <v>2.53259611129761</v>
       </c>
       <c r="H1663" t="s">
         <v>8</v>
@@ -43633,7 +43633,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1664" t="n">
-        <v>2.53259634971619</v>
+        <v>2.53259611129761</v>
       </c>
       <c r="H1664" t="s">
         <v>8</v>
@@ -43711,7 +43711,7 @@
         <v>2.85500001907349</v>
       </c>
       <c r="G1667" t="n">
-        <v>2.56402921676636</v>
+        <v>2.56402945518494</v>
       </c>
       <c r="H1667" t="s">
         <v>8</v>
@@ -43815,7 +43815,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1671" t="n">
-        <v>2.53259634971619</v>
+        <v>2.53259611129761</v>
       </c>
       <c r="H1671" t="s">
         <v>8</v>
@@ -43867,7 +43867,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1673" t="n">
-        <v>2.51463437080383</v>
+        <v>2.51463460922241</v>
       </c>
       <c r="H1673" t="s">
         <v>8</v>
@@ -43919,7 +43919,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G1675" t="n">
-        <v>2.54606771469116</v>
+        <v>2.54606747627258</v>
       </c>
       <c r="H1675" t="s">
         <v>8</v>
@@ -43997,7 +43997,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G1678" t="n">
-        <v>2.61342406272888</v>
+        <v>2.6134238243103</v>
       </c>
       <c r="H1678" t="s">
         <v>8</v>
@@ -44101,7 +44101,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1682" t="n">
-        <v>2.56851959228516</v>
+        <v>2.56851983070374</v>
       </c>
       <c r="H1682" t="s">
         <v>8</v>
@@ -44127,7 +44127,7 @@
         <v>2.875</v>
       </c>
       <c r="G1683" t="n">
-        <v>2.58199071884155</v>
+        <v>2.58199095726013</v>
       </c>
       <c r="H1683" t="s">
         <v>8</v>
@@ -44205,7 +44205,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1686" t="n">
-        <v>2.64934706687927</v>
+        <v>2.64934754371643</v>
       </c>
       <c r="H1686" t="s">
         <v>8</v>
@@ -44283,7 +44283,7 @@
         <v>2.99499988555908</v>
       </c>
       <c r="G1689" t="n">
-        <v>2.68976092338562</v>
+        <v>2.6897611618042</v>
       </c>
       <c r="H1689" t="s">
         <v>8</v>
@@ -44361,7 +44361,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1692" t="n">
-        <v>2.66730928421021</v>
+        <v>2.66730904579163</v>
       </c>
       <c r="H1692" t="s">
         <v>8</v>
@@ -44413,7 +44413,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1694" t="n">
-        <v>2.73017501831055</v>
+        <v>2.73017477989197</v>
       </c>
       <c r="H1694" t="s">
         <v>8</v>
@@ -44517,7 +44517,7 @@
         <v>2.91499996185303</v>
       </c>
       <c r="G1698" t="n">
-        <v>2.6179141998291</v>
+        <v>2.61791443824768</v>
       </c>
       <c r="H1698" t="s">
         <v>8</v>
@@ -44647,7 +44647,7 @@
         <v>2.91499996185303</v>
       </c>
       <c r="G1703" t="n">
-        <v>2.6179141998291</v>
+        <v>2.61791443824768</v>
       </c>
       <c r="H1703" t="s">
         <v>8</v>
@@ -44777,7 +44777,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1708" t="n">
-        <v>2.47871136665344</v>
+        <v>2.47871112823486</v>
       </c>
       <c r="H1708" t="s">
         <v>8</v>
@@ -44829,7 +44829,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1710" t="n">
-        <v>2.37992215156555</v>
+        <v>2.37992238998413</v>
       </c>
       <c r="H1710" t="s">
         <v>8</v>
@@ -44907,7 +44907,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1713" t="n">
-        <v>2.18234372138977</v>
+        <v>2.18234395980835</v>
       </c>
       <c r="H1713" t="s">
         <v>8</v>
@@ -44985,7 +44985,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1716" t="n">
-        <v>2.1554012298584</v>
+        <v>2.15540146827698</v>
       </c>
       <c r="H1716" t="s">
         <v>8</v>
@@ -45037,7 +45037,7 @@
         <v>2.40499997138977</v>
       </c>
       <c r="G1718" t="n">
-        <v>2.1598916053772</v>
+        <v>2.15989136695862</v>
       </c>
       <c r="H1718" t="s">
         <v>8</v>
@@ -45167,7 +45167,7 @@
         <v>2.28500008583069</v>
       </c>
       <c r="G1723" t="n">
-        <v>2.10462808609009</v>
+        <v>2.10462784767151</v>
       </c>
       <c r="H1723" t="s">
         <v>8</v>
@@ -45219,7 +45219,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G1725" t="n">
-        <v>2.07699584960938</v>
+        <v>2.07699608802795</v>
       </c>
       <c r="H1725" t="s">
         <v>8</v>
@@ -45245,7 +45245,7 @@
         <v>2.28500008583069</v>
       </c>
       <c r="G1726" t="n">
-        <v>2.10462808609009</v>
+        <v>2.10462784767151</v>
       </c>
       <c r="H1726" t="s">
         <v>8</v>
@@ -45271,7 +45271,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1727" t="n">
-        <v>2.09081196784973</v>
+        <v>2.09081172943115</v>
       </c>
       <c r="H1727" t="s">
         <v>8</v>
@@ -45323,7 +45323,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1729" t="n">
-        <v>2.09081196784973</v>
+        <v>2.09081172943115</v>
       </c>
       <c r="H1729" t="s">
         <v>8</v>
@@ -45427,7 +45427,7 @@
         <v>2.58500003814697</v>
       </c>
       <c r="G1733" t="n">
-        <v>2.38094639778137</v>
+        <v>2.38094663619995</v>
       </c>
       <c r="H1733" t="s">
         <v>8</v>
@@ -45505,7 +45505,7 @@
         <v>2.58500003814697</v>
       </c>
       <c r="G1736" t="n">
-        <v>2.38094639778137</v>
+        <v>2.38094663619995</v>
       </c>
       <c r="H1736" t="s">
         <v>8</v>
@@ -45531,7 +45531,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G1737" t="n">
-        <v>2.42239451408386</v>
+        <v>2.42239427566528</v>
       </c>
       <c r="H1737" t="s">
         <v>8</v>
@@ -45635,7 +45635,7 @@
         <v>2.63499999046326</v>
       </c>
       <c r="G1741" t="n">
-        <v>2.42699956893921</v>
+        <v>2.42699980735779</v>
       </c>
       <c r="H1741" t="s">
         <v>8</v>
@@ -45765,7 +45765,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G1746" t="n">
-        <v>2.45923709869385</v>
+        <v>2.45923686027527</v>
       </c>
       <c r="H1746" t="s">
         <v>8</v>
@@ -45843,7 +45843,7 @@
         <v>2.76500010490417</v>
       </c>
       <c r="G1749" t="n">
-        <v>2.54673767089844</v>
+        <v>2.54673790931702</v>
       </c>
       <c r="H1749" t="s">
         <v>8</v>
@@ -45869,7 +45869,7 @@
         <v>2.76500010490417</v>
       </c>
       <c r="G1750" t="n">
-        <v>2.54673767089844</v>
+        <v>2.54673790931702</v>
       </c>
       <c r="H1750" t="s">
         <v>8</v>
@@ -45999,7 +45999,7 @@
         <v>2.66499996185303</v>
       </c>
       <c r="G1755" t="n">
-        <v>2.45463132858276</v>
+        <v>2.45463156700134</v>
       </c>
       <c r="H1755" t="s">
         <v>8</v>
@@ -46025,7 +46025,7 @@
         <v>2.66499996185303</v>
       </c>
       <c r="G1756" t="n">
-        <v>2.45463132858276</v>
+        <v>2.45463156700134</v>
       </c>
       <c r="H1756" t="s">
         <v>8</v>
@@ -46545,7 +46545,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1776" t="n">
-        <v>2.59739589691162</v>
+        <v>2.5973961353302</v>
       </c>
       <c r="H1776" t="s">
         <v>8</v>
@@ -46675,7 +46675,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1781" t="n">
-        <v>2.73555541038513</v>
+        <v>2.73555564880371</v>
       </c>
       <c r="H1781" t="s">
         <v>8</v>
@@ -46701,7 +46701,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1782" t="n">
-        <v>2.73555541038513</v>
+        <v>2.73555564880371</v>
       </c>
       <c r="H1782" t="s">
         <v>8</v>
@@ -46753,7 +46753,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1784" t="n">
-        <v>2.78160881996155</v>
+        <v>2.78160858154297</v>
       </c>
       <c r="H1784" t="s">
         <v>8</v>
@@ -46857,7 +46857,7 @@
         <v>3.06500005722046</v>
       </c>
       <c r="G1788" t="n">
-        <v>2.82305645942688</v>
+        <v>2.82305669784546</v>
       </c>
       <c r="H1788" t="s">
         <v>8</v>
@@ -46961,7 +46961,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1792" t="n">
-        <v>2.82766199111938</v>
+        <v>2.82766175270081</v>
       </c>
       <c r="H1792" t="s">
         <v>8</v>
@@ -47169,7 +47169,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1800" t="n">
-        <v>2.78160881996155</v>
+        <v>2.78160858154297</v>
       </c>
       <c r="H1800" t="s">
         <v>8</v>
@@ -47247,7 +47247,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1803" t="n">
-        <v>2.73555541038513</v>
+        <v>2.73555564880371</v>
       </c>
       <c r="H1803" t="s">
         <v>8</v>
@@ -47429,7 +47429,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1810" t="n">
-        <v>2.6618709564209</v>
+        <v>2.66187071800232</v>
       </c>
       <c r="H1810" t="s">
         <v>8</v>
@@ -47611,7 +47611,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1817" t="n">
-        <v>2.7908194065094</v>
+        <v>2.79081916809082</v>
       </c>
       <c r="H1817" t="s">
         <v>8</v>
@@ -47663,7 +47663,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G1819" t="n">
-        <v>2.81384587287903</v>
+        <v>2.81384611129761</v>
       </c>
       <c r="H1819" t="s">
         <v>8</v>
@@ -47715,7 +47715,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1821" t="n">
-        <v>2.78160881996155</v>
+        <v>2.78160858154297</v>
       </c>
       <c r="H1821" t="s">
         <v>8</v>
@@ -48105,7 +48105,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1836" t="n">
-        <v>2.63423848152161</v>
+        <v>2.63423871994019</v>
       </c>
       <c r="H1836" t="s">
         <v>8</v>
@@ -48131,7 +48131,7 @@
         <v>2.93499994277954</v>
       </c>
       <c r="G1837" t="n">
-        <v>2.70331835746765</v>
+        <v>2.70331811904907</v>
       </c>
       <c r="H1837" t="s">
         <v>8</v>
@@ -48157,7 +48157,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1838" t="n">
-        <v>2.6618709564209</v>
+        <v>2.66187071800232</v>
       </c>
       <c r="H1838" t="s">
         <v>8</v>
@@ -48261,7 +48261,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1842" t="n">
-        <v>2.6618709564209</v>
+        <v>2.66187071800232</v>
       </c>
       <c r="H1842" t="s">
         <v>8</v>
@@ -48339,7 +48339,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1845" t="n">
-        <v>2.63423848152161</v>
+        <v>2.63423871994019</v>
       </c>
       <c r="H1845" t="s">
         <v>8</v>
@@ -48365,7 +48365,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1846" t="n">
-        <v>2.59739589691162</v>
+        <v>2.5973961353302</v>
       </c>
       <c r="H1846" t="s">
         <v>8</v>
@@ -48443,7 +48443,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1849" t="n">
-        <v>2.59739589691162</v>
+        <v>2.5973961353302</v>
       </c>
       <c r="H1849" t="s">
         <v>8</v>
@@ -48495,7 +48495,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1851" t="n">
-        <v>2.63423848152161</v>
+        <v>2.63423871994019</v>
       </c>
       <c r="H1851" t="s">
         <v>8</v>
@@ -48547,7 +48547,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1853" t="n">
-        <v>2.59739589691162</v>
+        <v>2.5973961353302</v>
       </c>
       <c r="H1853" t="s">
         <v>8</v>
@@ -48625,7 +48625,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.59739589691162</v>
+        <v>2.5973961353302</v>
       </c>
       <c r="H1856" t="s">
         <v>8</v>
@@ -48781,7 +48781,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.59739589691162</v>
+        <v>2.5973961353302</v>
       </c>
       <c r="H1862" t="s">
         <v>8</v>
@@ -48833,7 +48833,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.60660672187805</v>
+        <v>2.60660696029663</v>
       </c>
       <c r="H1864" t="s">
         <v>8</v>
@@ -48859,7 +48859,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.60660672187805</v>
+        <v>2.60660696029663</v>
       </c>
       <c r="H1865" t="s">
         <v>8</v>
@@ -48937,7 +48937,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.41318368911743</v>
+        <v>2.41318345069885</v>
       </c>
       <c r="H1868" t="s">
         <v>8</v>
@@ -48963,7 +48963,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.45923709869385</v>
+        <v>2.45923686027527</v>
       </c>
       <c r="H1869" t="s">
         <v>8</v>
@@ -49249,7 +49249,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.45923709869385</v>
+        <v>2.45923686027527</v>
       </c>
       <c r="H1880" t="s">
         <v>8</v>
@@ -49275,7 +49275,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.45923709869385</v>
+        <v>2.45923686027527</v>
       </c>
       <c r="H1881" t="s">
         <v>8</v>
@@ -49301,7 +49301,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.45923709869385</v>
+        <v>2.45923686027527</v>
       </c>
       <c r="H1882" t="s">
         <v>8</v>
@@ -49327,7 +49327,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.45923709869385</v>
+        <v>2.45923686027527</v>
       </c>
       <c r="H1883" t="s">
         <v>8</v>
@@ -49665,7 +49665,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.45923709869385</v>
+        <v>2.45923686027527</v>
       </c>
       <c r="H1896" t="s">
         <v>8</v>
@@ -49691,7 +49691,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.45923709869385</v>
+        <v>2.45923686027527</v>
       </c>
       <c r="H1897" t="s">
         <v>8</v>
@@ -50081,7 +50081,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.48590302467346</v>
+        <v>2.48590278625488</v>
       </c>
       <c r="H1912" t="s">
         <v>8</v>
@@ -50185,7 +50185,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.48590302467346</v>
+        <v>2.48590278625488</v>
       </c>
       <c r="H1916" t="s">
         <v>8</v>
@@ -50211,7 +50211,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.4764506816864</v>
+        <v>2.47645044326782</v>
       </c>
       <c r="H1917" t="s">
         <v>8</v>
@@ -50419,7 +50419,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.35357356071472</v>
+        <v>2.35357332229614</v>
       </c>
       <c r="H1925" t="s">
         <v>8</v>
@@ -50601,7 +50601,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.4764506816864</v>
+        <v>2.47645044326782</v>
       </c>
       <c r="H1932" t="s">
         <v>8</v>
@@ -50757,7 +50757,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.4764506816864</v>
+        <v>2.47645044326782</v>
       </c>
       <c r="H1938" t="s">
         <v>8</v>
@@ -50783,7 +50783,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.48590302467346</v>
+        <v>2.48590278625488</v>
       </c>
       <c r="H1939" t="s">
         <v>8</v>
@@ -50809,7 +50809,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.48590302467346</v>
+        <v>2.48590278625488</v>
       </c>
       <c r="H1940" t="s">
         <v>8</v>
@@ -51069,7 +51069,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.48590302467346</v>
+        <v>2.48590278625488</v>
       </c>
       <c r="H1950" t="s">
         <v>8</v>
@@ -51277,7 +51277,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.25905227661133</v>
+        <v>2.25905251502991</v>
       </c>
       <c r="H1958" t="s">
         <v>8</v>
@@ -51355,7 +51355,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.25905227661133</v>
+        <v>2.25905251502991</v>
       </c>
       <c r="H1961" t="s">
         <v>8</v>
@@ -51459,7 +51459,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.20233964920044</v>
+        <v>2.20233988761902</v>
       </c>
       <c r="H1965" t="s">
         <v>8</v>
@@ -51537,7 +51537,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.09836673736572</v>
+        <v>2.09836649894714</v>
       </c>
       <c r="H1968" t="s">
         <v>8</v>
@@ -51563,7 +51563,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.09836673736572</v>
+        <v>2.09836649894714</v>
       </c>
       <c r="H1969" t="s">
         <v>8</v>
@@ -51745,7 +51745,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1976" t="n">
-        <v>1.95658504962921</v>
+        <v>1.95658493041992</v>
       </c>
       <c r="H1976" t="s">
         <v>8</v>
@@ -51771,7 +51771,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G1977" t="n">
-        <v>1.89987242221832</v>
+        <v>1.89987254142761</v>
       </c>
       <c r="H1977" t="s">
         <v>8</v>
@@ -51797,7 +51797,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1978" t="n">
-        <v>1.88096833229065</v>
+        <v>1.88096821308136</v>
       </c>
       <c r="H1978" t="s">
         <v>8</v>
@@ -52057,7 +52057,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G1988" t="n">
-        <v>1.76281690597534</v>
+        <v>1.76281702518463</v>
       </c>
       <c r="H1988" t="s">
         <v>8</v>
@@ -52083,7 +52083,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1989" t="n">
-        <v>1.72028255462646</v>
+        <v>1.72028267383575</v>
       </c>
       <c r="H1989" t="s">
         <v>8</v>
@@ -52109,7 +52109,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1990" t="n">
-        <v>1.71083033084869</v>
+        <v>1.71083045005798</v>
       </c>
       <c r="H1990" t="s">
         <v>8</v>
@@ -52135,7 +52135,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G1991" t="n">
-        <v>1.69665217399597</v>
+        <v>1.69665229320526</v>
       </c>
       <c r="H1991" t="s">
         <v>8</v>
@@ -52343,7 +52343,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1999" t="n">
-        <v>1.71083033084869</v>
+        <v>1.71083045005798</v>
       </c>
       <c r="H1999" t="s">
         <v>8</v>
@@ -52369,7 +52369,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G2000" t="n">
-        <v>1.72028255462646</v>
+        <v>1.72028267383575</v>
       </c>
       <c r="H2000" t="s">
         <v>8</v>
@@ -52395,7 +52395,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G2001" t="n">
-        <v>1.71555650234222</v>
+        <v>1.71555662155151</v>
       </c>
       <c r="H2001" t="s">
         <v>8</v>
@@ -52421,7 +52421,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G2002" t="n">
-        <v>1.71555650234222</v>
+        <v>1.71555662155151</v>
       </c>
       <c r="H2002" t="s">
         <v>8</v>
@@ -52447,7 +52447,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G2003" t="n">
-        <v>1.72028255462646</v>
+        <v>1.72028267383575</v>
       </c>
       <c r="H2003" t="s">
         <v>8</v>
@@ -52473,7 +52473,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G2004" t="n">
-        <v>1.67302203178406</v>
+        <v>1.67302191257477</v>
       </c>
       <c r="H2004" t="s">
         <v>8</v>
@@ -52499,7 +52499,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G2005" t="n">
-        <v>1.69665217399597</v>
+        <v>1.69665229320526</v>
       </c>
       <c r="H2005" t="s">
         <v>8</v>
@@ -52525,7 +52525,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G2006" t="n">
-        <v>1.71555650234222</v>
+        <v>1.71555662155151</v>
       </c>
       <c r="H2006" t="s">
         <v>8</v>
@@ -52577,7 +52577,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G2008" t="n">
-        <v>1.88096833229065</v>
+        <v>1.88096821308136</v>
       </c>
       <c r="H2008" t="s">
         <v>8</v>
@@ -52603,7 +52603,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G2009" t="n">
-        <v>1.9093245267868</v>
+        <v>1.90932464599609</v>
       </c>
       <c r="H2009" t="s">
         <v>8</v>
@@ -52629,7 +52629,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2010" t="n">
-        <v>1.89987242221832</v>
+        <v>1.89987254142761</v>
       </c>
       <c r="H2010" t="s">
         <v>8</v>
@@ -52837,7 +52837,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G2018" t="n">
-        <v>1.97548937797546</v>
+        <v>1.97548913955688</v>
       </c>
       <c r="H2018" t="s">
         <v>8</v>
@@ -53253,7 +53253,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G2034" t="n">
-        <v>2.20233964920044</v>
+        <v>2.20233988761902</v>
       </c>
       <c r="H2034" t="s">
         <v>8</v>
@@ -53305,7 +53305,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G2036" t="n">
-        <v>2.14562726020813</v>
+        <v>2.14562702178955</v>
       </c>
       <c r="H2036" t="s">
         <v>8</v>
@@ -53487,7 +53487,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G2043" t="n">
-        <v>2.14562726020813</v>
+        <v>2.14562702178955</v>
       </c>
       <c r="H2043" t="s">
         <v>8</v>
@@ -53981,7 +53981,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G2062" t="n">
-        <v>2.13617515563965</v>
+        <v>2.13617491722107</v>
       </c>
       <c r="H2062" t="s">
         <v>8</v>
@@ -54007,7 +54007,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G2063" t="n">
-        <v>2.1078188419342</v>
+        <v>2.10781860351562</v>
       </c>
       <c r="H2063" t="s">
         <v>8</v>
@@ -54033,7 +54033,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G2064" t="n">
-        <v>1.94713282585144</v>
+        <v>1.94713306427002</v>
       </c>
       <c r="H2064" t="s">
         <v>8</v>
@@ -54059,7 +54059,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2065" t="n">
-        <v>1.87151622772217</v>
+        <v>1.87151610851288</v>
       </c>
       <c r="H2065" t="s">
         <v>8</v>
@@ -54215,7 +54215,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G2071" t="n">
-        <v>1.72973465919495</v>
+        <v>1.72973477840424</v>
       </c>
       <c r="H2071" t="s">
         <v>8</v>
@@ -54241,7 +54241,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G2072" t="n">
-        <v>1.81007754802704</v>
+        <v>1.81007742881775</v>
       </c>
       <c r="H2072" t="s">
         <v>8</v>
@@ -54267,7 +54267,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2073" t="n">
-        <v>1.87151622772217</v>
+        <v>1.87151610851288</v>
       </c>
       <c r="H2073" t="s">
         <v>8</v>
@@ -54293,7 +54293,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2074" t="n">
-        <v>1.87151622772217</v>
+        <v>1.87151610851288</v>
       </c>
       <c r="H2074" t="s">
         <v>8</v>
@@ -54319,7 +54319,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G2075" t="n">
-        <v>1.86206412315369</v>
+        <v>1.8620640039444</v>
       </c>
       <c r="H2075" t="s">
         <v>8</v>
@@ -54345,7 +54345,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2076" t="n">
-        <v>1.89987242221832</v>
+        <v>1.89987254142761</v>
       </c>
       <c r="H2076" t="s">
         <v>8</v>
@@ -54371,7 +54371,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G2077" t="n">
-        <v>1.9093245267868</v>
+        <v>1.90932464599609</v>
       </c>
       <c r="H2077" t="s">
         <v>8</v>
@@ -54397,7 +54397,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G2078" t="n">
-        <v>1.9093245267868</v>
+        <v>1.90932464599609</v>
       </c>
       <c r="H2078" t="s">
         <v>8</v>
@@ -54423,7 +54423,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G2079" t="n">
-        <v>1.9093245267868</v>
+        <v>1.90932464599609</v>
       </c>
       <c r="H2079" t="s">
         <v>8</v>
@@ -54449,7 +54449,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G2080" t="n">
-        <v>1.9093245267868</v>
+        <v>1.90932464599609</v>
       </c>
       <c r="H2080" t="s">
         <v>8</v>
@@ -54475,7 +54475,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2081" t="n">
-        <v>1.89987242221832</v>
+        <v>1.89987254142761</v>
       </c>
       <c r="H2081" t="s">
         <v>8</v>
@@ -54579,7 +54579,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2085" t="n">
-        <v>1.89987242221832</v>
+        <v>1.89987254142761</v>
       </c>
       <c r="H2085" t="s">
         <v>8</v>
@@ -54683,7 +54683,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G2089" t="n">
-        <v>1.76281690597534</v>
+        <v>1.76281702518463</v>
       </c>
       <c r="H2089" t="s">
         <v>8</v>
@@ -54761,7 +54761,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G2092" t="n">
-        <v>1.76281690597534</v>
+        <v>1.76281702518463</v>
       </c>
       <c r="H2092" t="s">
         <v>8</v>
@@ -54865,7 +54865,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G2096" t="n">
-        <v>1.828981757164</v>
+        <v>1.82898163795471</v>
       </c>
       <c r="H2096" t="s">
         <v>8</v>
@@ -54891,7 +54891,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G2097" t="n">
-        <v>1.828981757164</v>
+        <v>1.82898163795471</v>
       </c>
       <c r="H2097" t="s">
         <v>8</v>
@@ -55047,7 +55047,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G2103" t="n">
-        <v>1.81007754802704</v>
+        <v>1.81007742881775</v>
       </c>
       <c r="H2103" t="s">
         <v>8</v>
@@ -55073,7 +55073,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G2104" t="n">
-        <v>1.7817211151123</v>
+        <v>1.78172123432159</v>
       </c>
       <c r="H2104" t="s">
         <v>8</v>
@@ -55229,7 +55229,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G2110" t="n">
-        <v>1.74391293525696</v>
+        <v>1.74391281604767</v>
       </c>
       <c r="H2110" t="s">
         <v>8</v>
@@ -55307,7 +55307,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G2113" t="n">
-        <v>1.7817211151123</v>
+        <v>1.78172123432159</v>
       </c>
       <c r="H2113" t="s">
         <v>8</v>
@@ -55385,7 +55385,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G2116" t="n">
-        <v>1.76281690597534</v>
+        <v>1.76281702518463</v>
       </c>
       <c r="H2116" t="s">
         <v>8</v>
@@ -55619,7 +55619,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G2125" t="n">
-        <v>1.7817211151123</v>
+        <v>1.78172123432159</v>
       </c>
       <c r="H2125" t="s">
         <v>8</v>
@@ -55671,7 +55671,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G2127" t="n">
-        <v>1.81007754802704</v>
+        <v>1.81007742881775</v>
       </c>
       <c r="H2127" t="s">
         <v>8</v>
@@ -55723,7 +55723,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G2129" t="n">
-        <v>1.828981757164</v>
+        <v>1.82898163795471</v>
       </c>
       <c r="H2129" t="s">
         <v>8</v>
@@ -55905,7 +55905,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G2136" t="n">
-        <v>1.7817211151123</v>
+        <v>1.78172123432159</v>
       </c>
       <c r="H2136" t="s">
         <v>8</v>
@@ -56009,7 +56009,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G2140" t="n">
-        <v>1.74391293525696</v>
+        <v>1.74391281604767</v>
       </c>
       <c r="H2140" t="s">
         <v>8</v>
@@ -56217,7 +56217,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G2148" t="n">
-        <v>1.74391293525696</v>
+        <v>1.74391281604767</v>
       </c>
       <c r="H2148" t="s">
         <v>8</v>
@@ -56269,7 +56269,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G2150" t="n">
-        <v>1.72973465919495</v>
+        <v>1.72973477840424</v>
       </c>
       <c r="H2150" t="s">
         <v>8</v>
@@ -56295,7 +56295,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G2151" t="n">
-        <v>1.68720018863678</v>
+        <v>1.68720006942749</v>
       </c>
       <c r="H2151" t="s">
         <v>8</v>
@@ -56347,7 +56347,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G2153" t="n">
-        <v>1.71083033084869</v>
+        <v>1.71083045005798</v>
       </c>
       <c r="H2153" t="s">
         <v>8</v>
@@ -56373,7 +56373,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G2154" t="n">
-        <v>1.68247413635254</v>
+        <v>1.68247401714325</v>
       </c>
       <c r="H2154" t="s">
         <v>8</v>
@@ -56477,7 +56477,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G2158" t="n">
-        <v>1.69665217399597</v>
+        <v>1.69665229320526</v>
       </c>
       <c r="H2158" t="s">
         <v>8</v>
@@ -56503,7 +56503,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G2159" t="n">
-        <v>1.67302203178406</v>
+        <v>1.67302191257477</v>
       </c>
       <c r="H2159" t="s">
         <v>8</v>
@@ -71378,6 +71378,32 @@
         <v>1.12999999523163</v>
       </c>
       <c r="H2731" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2732">
+      <c r="A2732" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B2732" t="n">
+        <v>45</v>
+      </c>
+      <c r="C2732" t="n">
+        <v>1.12999999523163</v>
+      </c>
+      <c r="D2732" t="n">
+        <v>1.12999999523163</v>
+      </c>
+      <c r="E2732" t="n">
+        <v>1.12999999523163</v>
+      </c>
+      <c r="F2732" t="n">
+        <v>1.13499999046326</v>
+      </c>
+      <c r="G2732" t="n">
+        <v>1.13499999046326</v>
+      </c>
+      <c r="H2732" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/ELC.MI.xlsx
+++ b/data/ELC.MI.xlsx
@@ -63265,13 +63265,36 @@
         <v>1.14499998092651</v>
       </c>
       <c r="D2735" t="n">
-        <v>1.13499999046326</v>
+        <v>1.12999999523163</v>
       </c>
       <c r="E2735" t="n">
         <v>1.14499998092651</v>
       </c>
-      <c r="F2735"/>
+      <c r="F2735" t="n">
+        <v>1.12999999523163</v>
+      </c>
       <c r="G2735" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2736">
+      <c r="A2736" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2736" t="n">
+        <v>207</v>
+      </c>
+      <c r="C2736" t="n">
+        <v>1.14999997615814</v>
+      </c>
+      <c r="D2736" t="n">
+        <v>1.14999997615814</v>
+      </c>
+      <c r="E2736" t="n">
+        <v>1.14999997615814</v>
+      </c>
+      <c r="F2736"/>
+      <c r="G2736" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ELC.MI.xlsx
+++ b/data/ELC.MI.xlsx
@@ -63288,13 +63288,36 @@
         <v>1.14999997615814</v>
       </c>
       <c r="D2736" t="n">
-        <v>1.14999997615814</v>
+        <v>1.12999999523163</v>
       </c>
       <c r="E2736" t="n">
         <v>1.14999997615814</v>
       </c>
-      <c r="F2736"/>
+      <c r="F2736" t="n">
+        <v>1.12999999523163</v>
+      </c>
       <c r="G2736" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2737">
+      <c r="A2737" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2737" t="n">
+        <v>12645</v>
+      </c>
+      <c r="C2737" t="n">
+        <v>1.1599999666214</v>
+      </c>
+      <c r="D2737" t="n">
+        <v>1.12999999523163</v>
+      </c>
+      <c r="E2737" t="n">
+        <v>1.14499998092651</v>
+      </c>
+      <c r="F2737"/>
+      <c r="G2737" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ELC.MI.xlsx
+++ b/data/ELC.MI.xlsx
@@ -63316,8 +63316,31 @@
       <c r="E2737" t="n">
         <v>1.14499998092651</v>
       </c>
-      <c r="F2737"/>
+      <c r="F2737" t="n">
+        <v>1.13499999046326</v>
+      </c>
       <c r="G2737" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2738">
+      <c r="A2738" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2738" t="n">
+        <v>9260</v>
+      </c>
+      <c r="C2738" t="n">
+        <v>1.14999997615814</v>
+      </c>
+      <c r="D2738" t="n">
+        <v>1.12000000476837</v>
+      </c>
+      <c r="E2738" t="n">
+        <v>1.14999997615814</v>
+      </c>
+      <c r="F2738"/>
+      <c r="G2738" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ELC.MI.xlsx
+++ b/data/ELC.MI.xlsx
@@ -63339,8 +63339,31 @@
       <c r="E2738" t="n">
         <v>1.14999997615814</v>
       </c>
-      <c r="F2738"/>
+      <c r="F2738" t="n">
+        <v>1.13499999046326</v>
+      </c>
       <c r="G2738" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2739">
+      <c r="A2739" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2739" t="n">
+        <v>4082</v>
+      </c>
+      <c r="C2739" t="n">
+        <v>1.14499998092651</v>
+      </c>
+      <c r="D2739" t="n">
+        <v>1.12000000476837</v>
+      </c>
+      <c r="E2739" t="n">
+        <v>1.12000000476837</v>
+      </c>
+      <c r="F2739"/>
+      <c r="G2739" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ELC.MI.xlsx
+++ b/data/ELC.MI.xlsx
@@ -63369,6 +63369,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2740">
+      <c r="A2740" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2740" t="n">
+        <v>15800</v>
+      </c>
+      <c r="C2740" t="n">
+        <v>1.12999999523163</v>
+      </c>
+      <c r="D2740" t="n">
+        <v>1.11000001430511</v>
+      </c>
+      <c r="E2740" t="n">
+        <v>1.12999999523163</v>
+      </c>
+      <c r="F2740" t="n">
+        <v>1.11500000953674</v>
+      </c>
+      <c r="G2740" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ELC.MI.xlsx
+++ b/data/ELC.MI.xlsx
@@ -447,7 +447,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G3" t="n">
-        <v>1.73338520526886</v>
+        <v>1.73338508605957</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G4" t="n">
-        <v>1.72445011138916</v>
+        <v>1.72445023059845</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>1.87399995326996</v>
       </c>
       <c r="G5" t="n">
-        <v>1.67441415786743</v>
+        <v>1.67441427707672</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G7" t="n">
-        <v>1.65297031402588</v>
+        <v>1.65297043323517</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G8" t="n">
-        <v>1.66190540790558</v>
+        <v>1.66190528869629</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>1.81900000572205</v>
       </c>
       <c r="G10" t="n">
-        <v>1.62527203559875</v>
+        <v>1.62527191638947</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G11" t="n">
-        <v>1.59936046600342</v>
+        <v>1.59936034679413</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>1.65199995040894</v>
       </c>
       <c r="G12" t="n">
-        <v>1.47605788707733</v>
+        <v>1.47605776786804</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>1.61099994182587</v>
       </c>
       <c r="G14" t="n">
-        <v>1.43942451477051</v>
+        <v>1.43942439556122</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>1.70700001716614</v>
       </c>
       <c r="G16" t="n">
-        <v>1.5252001285553</v>
+        <v>1.52520024776459</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>1.65100002288818</v>
       </c>
       <c r="G21" t="n">
-        <v>1.47516441345215</v>
+        <v>1.47516429424286</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G23" t="n">
-        <v>1.39832365512848</v>
+        <v>1.39832377433777</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>1.54499995708466</v>
       </c>
       <c r="G24" t="n">
-        <v>1.38045346736908</v>
+        <v>1.38045358657837</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>1.51699995994568</v>
       </c>
       <c r="G25" t="n">
-        <v>1.3554356098175</v>
+        <v>1.35543572902679</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G26" t="n">
-        <v>1.38492107391357</v>
+        <v>1.38492095470428</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G31" t="n">
-        <v>1.42959594726562</v>
+        <v>1.42959606647491</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>1.6710000038147</v>
       </c>
       <c r="G33" t="n">
-        <v>1.49303424358368</v>
+        <v>1.49303436279297</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>1.75399994850159</v>
       </c>
       <c r="G36" t="n">
-        <v>1.5671945810318</v>
+        <v>1.56719470024109</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G37" t="n">
-        <v>1.57255554199219</v>
+        <v>1.57255566120148</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G40" t="n">
-        <v>1.5770229101181</v>
+        <v>1.57702314853668</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G42" t="n">
-        <v>1.5814905166626</v>
+        <v>1.58149063587189</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G43" t="n">
-        <v>1.57255554199219</v>
+        <v>1.57255566120148</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G44" t="n">
-        <v>1.51894581317902</v>
+        <v>1.51894569396973</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G45" t="n">
-        <v>1.5814905166626</v>
+        <v>1.58149063587189</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>1.77300000190735</v>
       </c>
       <c r="G46" t="n">
-        <v>1.58417093753815</v>
+        <v>1.58417105674744</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G50" t="n">
-        <v>1.5814905166626</v>
+        <v>1.58149063587189</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>1.8309999704361</v>
       </c>
       <c r="G52" t="n">
-        <v>1.63599395751953</v>
+        <v>1.63599383831024</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>1.89300000667572</v>
       </c>
       <c r="G53" t="n">
-        <v>1.69139075279236</v>
+        <v>1.69139087200165</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G55" t="n">
-        <v>1.67977523803711</v>
+        <v>1.6797753572464</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G57" t="n">
-        <v>1.72445011138916</v>
+        <v>1.72445023059845</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G58" t="n">
-        <v>1.7691251039505</v>
+        <v>1.76912486553192</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>1.95200002193451</v>
       </c>
       <c r="G59" t="n">
-        <v>1.74410700798035</v>
+        <v>1.74410712718964</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>1.94599997997284</v>
       </c>
       <c r="G61" t="n">
-        <v>1.73874604701996</v>
+        <v>1.73874616622925</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>1.97599995136261</v>
       </c>
       <c r="G62" t="n">
-        <v>1.7655508518219</v>
+        <v>1.76555097103119</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G63" t="n">
-        <v>1.75125503540039</v>
+        <v>1.75125515460968</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G65" t="n">
-        <v>1.72445011138916</v>
+        <v>1.72445023059845</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>1.87899994850159</v>
       </c>
       <c r="G67" t="n">
-        <v>1.67888176441193</v>
+        <v>1.67888152599335</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G74" t="n">
-        <v>1.71551525592804</v>
+        <v>1.71551513671875</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G75" t="n">
-        <v>1.71998250484467</v>
+        <v>1.71998274326324</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G76" t="n">
-        <v>1.71104753017426</v>
+        <v>1.71104764938354</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G78" t="n">
-        <v>1.71998250484467</v>
+        <v>1.71998274326324</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>1.89800000190735</v>
       </c>
       <c r="G79" t="n">
-        <v>1.69585812091827</v>
+        <v>1.69585824012756</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G80" t="n">
-        <v>1.71998250484467</v>
+        <v>1.71998274326324</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>1.93900001049042</v>
       </c>
       <c r="G83" t="n">
-        <v>1.73249173164368</v>
+        <v>1.73249161243439</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G84" t="n">
-        <v>1.74232006072998</v>
+        <v>1.74231994152069</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>1.92599999904633</v>
       </c>
       <c r="G89" t="n">
-        <v>1.72087621688843</v>
+        <v>1.72087609767914</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>1.85199999809265</v>
       </c>
       <c r="G93" t="n">
-        <v>1.65475738048553</v>
+        <v>1.65475726127625</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>1.91799998283386</v>
       </c>
       <c r="G98" t="n">
-        <v>1.71372818946838</v>
+        <v>1.71372807025909</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>1.9190000295639</v>
       </c>
       <c r="G99" t="n">
-        <v>1.71462178230286</v>
+        <v>1.71462166309357</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>1.90299999713898</v>
       </c>
       <c r="G100" t="n">
-        <v>1.70905363559723</v>
+        <v>1.70905351638794</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>1.9190000295639</v>
       </c>
       <c r="G101" t="n">
-        <v>1.72342300415039</v>
+        <v>1.72342276573181</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>1.95700001716614</v>
       </c>
       <c r="G103" t="n">
-        <v>1.75755000114441</v>
+        <v>1.7575501203537</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G109" t="n">
-        <v>1.71534013748169</v>
+        <v>1.7153400182724</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G112" t="n">
-        <v>1.71534013748169</v>
+        <v>1.7153400182724</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G116" t="n">
-        <v>1.63900291919708</v>
+        <v>1.63900303840637</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G117" t="n">
-        <v>1.62553155422211</v>
+        <v>1.6255316734314</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>1.82400000095367</v>
       </c>
       <c r="G122" t="n">
-        <v>1.63810479640961</v>
+        <v>1.6381049156189</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G123" t="n">
-        <v>1.66145503520966</v>
+        <v>1.66145515441895</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G127" t="n">
-        <v>1.63900291919708</v>
+        <v>1.63900303840637</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>1.79799997806549</v>
       </c>
       <c r="G128" t="n">
-        <v>1.61475455760956</v>
+        <v>1.61475467681885</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>1.80900001525879</v>
       </c>
       <c r="G129" t="n">
-        <v>1.62463355064392</v>
+        <v>1.62463366985321</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G130" t="n">
-        <v>1.63002216815948</v>
+        <v>1.6300220489502</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>1.62100005149841</v>
       </c>
       <c r="G135" t="n">
-        <v>1.45579385757446</v>
+        <v>1.45579409599304</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>1.66400003433228</v>
       </c>
       <c r="G138" t="n">
-        <v>1.49441134929657</v>
+        <v>1.49441146850586</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>1.67900002002716</v>
       </c>
       <c r="G142" t="n">
-        <v>1.50788271427155</v>
+        <v>1.50788283348083</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G147" t="n">
-        <v>1.50429034233093</v>
+        <v>1.50429046154022</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>1.67400002479553</v>
       </c>
       <c r="G148" t="n">
-        <v>1.50339221954346</v>
+        <v>1.50339233875275</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>1.65400004386902</v>
       </c>
       <c r="G149" t="n">
-        <v>1.48543059825897</v>
+        <v>1.48543071746826</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G150" t="n">
-        <v>1.50429034233093</v>
+        <v>1.50429046154022</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>1.67400002479553</v>
       </c>
       <c r="G152" t="n">
-        <v>1.50339221954346</v>
+        <v>1.50339233875275</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G156" t="n">
-        <v>1.50878059864044</v>
+        <v>1.50878071784973</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G159" t="n">
-        <v>1.51776158809662</v>
+        <v>1.51776170730591</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>1.89300000667572</v>
       </c>
       <c r="G172" t="n">
-        <v>1.70007276535034</v>
+        <v>1.70007264614105</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>1.80200004577637</v>
       </c>
       <c r="G192" t="n">
-        <v>1.61834704875946</v>
+        <v>1.61834716796875</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>1.80200004577637</v>
       </c>
       <c r="G193" t="n">
-        <v>1.61834704875946</v>
+        <v>1.61834716796875</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G199" t="n">
-        <v>1.6973785161972</v>
+        <v>1.69737839698792</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G202" t="n">
-        <v>1.66145503520966</v>
+        <v>1.66145515441895</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G204" t="n">
-        <v>1.66145503520966</v>
+        <v>1.66145515441895</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G210" t="n">
-        <v>1.66145503520966</v>
+        <v>1.66145515441895</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>1.86899995803833</v>
       </c>
       <c r="G212" t="n">
-        <v>1.67851865291595</v>
+        <v>1.67851853370667</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>1.86899995803833</v>
       </c>
       <c r="G213" t="n">
-        <v>1.67851865291595</v>
+        <v>1.67851853370667</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>1.8289999961853</v>
       </c>
       <c r="G216" t="n">
-        <v>1.6425952911377</v>
+        <v>1.64259541034698</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>1.83700001239777</v>
       </c>
       <c r="G219" t="n">
-        <v>1.64977991580963</v>
+        <v>1.64978003501892</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G220" t="n">
-        <v>1.62553155422211</v>
+        <v>1.6255316734314</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>1.80200004577637</v>
       </c>
       <c r="G221" t="n">
-        <v>1.61834704875946</v>
+        <v>1.61834716796875</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>1.83700001239777</v>
       </c>
       <c r="G222" t="n">
-        <v>1.64977991580963</v>
+        <v>1.64978003501892</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>1.74600005149841</v>
       </c>
       <c r="G224" t="n">
-        <v>1.56805431842804</v>
+        <v>1.56805443763733</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>1.65799999237061</v>
       </c>
       <c r="G228" t="n">
-        <v>1.48902297019958</v>
+        <v>1.48902308940887</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>1.62899994850159</v>
       </c>
       <c r="G229" t="n">
-        <v>1.4629784822464</v>
+        <v>1.46297860145569</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>1.47500002384186</v>
       </c>
       <c r="G234" t="n">
-        <v>1.32467365264893</v>
+        <v>1.32467353343964</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>1.52199995517731</v>
       </c>
       <c r="G237" t="n">
-        <v>1.36688351631165</v>
+        <v>1.36688363552094</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>1.5</v>
       </c>
       <c r="G238" t="n">
-        <v>1.3471257686615</v>
+        <v>1.34712564945221</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>1.58200001716614</v>
       </c>
       <c r="G240" t="n">
-        <v>1.42076873779297</v>
+        <v>1.42076861858368</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G243" t="n">
-        <v>1.45040535926819</v>
+        <v>1.4504052400589</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>1.61300003528595</v>
       </c>
       <c r="G244" t="n">
-        <v>1.44860923290253</v>
+        <v>1.44860935211182</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>1.67900002002716</v>
       </c>
       <c r="G246" t="n">
-        <v>1.50788271427155</v>
+        <v>1.50788283348083</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G249" t="n">
-        <v>1.54470407962799</v>
+        <v>1.54470419883728</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G250" t="n">
-        <v>1.54470407962799</v>
+        <v>1.54470419883728</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>1.78600001335144</v>
       </c>
       <c r="G252" t="n">
-        <v>1.6039776802063</v>
+        <v>1.60397779941559</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G253" t="n">
-        <v>1.62553155422211</v>
+        <v>1.6255316734314</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G256" t="n">
-        <v>1.62553155422211</v>
+        <v>1.6255316734314</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G260" t="n">
-        <v>1.62553155422211</v>
+        <v>1.6255316734314</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G265" t="n">
-        <v>1.64798378944397</v>
+        <v>1.64798390865326</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G266" t="n">
-        <v>1.62553155422211</v>
+        <v>1.6255316734314</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G271" t="n">
-        <v>1.62553155422211</v>
+        <v>1.6255316734314</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>1.78600001335144</v>
       </c>
       <c r="G272" t="n">
-        <v>1.6039776802063</v>
+        <v>1.60397779941559</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>1.68099999427795</v>
       </c>
       <c r="G277" t="n">
-        <v>1.5096789598465</v>
+        <v>1.50967884063721</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G278" t="n">
-        <v>1.50878059864044</v>
+        <v>1.50878071784973</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G279" t="n">
-        <v>1.50878059864044</v>
+        <v>1.50878071784973</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G280" t="n">
-        <v>1.54470407962799</v>
+        <v>1.54470419883728</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G282" t="n">
-        <v>1.54470407962799</v>
+        <v>1.54470419883728</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G284" t="n">
-        <v>1.48183822631836</v>
+        <v>1.48183846473694</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>1.62100005149841</v>
       </c>
       <c r="G285" t="n">
-        <v>1.45579385757446</v>
+        <v>1.45579409599304</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>1.51900005340576</v>
       </c>
       <c r="G288" t="n">
-        <v>1.3641893863678</v>
+        <v>1.36418926715851</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G290" t="n">
-        <v>1.38304901123047</v>
+        <v>1.38304889202118</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>1.48599994182587</v>
       </c>
       <c r="G292" t="n">
-        <v>1.33455240726471</v>
+        <v>1.334552526474</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>1.46700000762939</v>
       </c>
       <c r="G293" t="n">
-        <v>1.31748902797699</v>
+        <v>1.3174889087677</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>1.47500002384186</v>
       </c>
       <c r="G294" t="n">
-        <v>1.32467365264893</v>
+        <v>1.32467353343964</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>1.47800004482269</v>
       </c>
       <c r="G297" t="n">
-        <v>1.32736802101135</v>
+        <v>1.32736790180206</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>1.55299997329712</v>
       </c>
       <c r="G299" t="n">
-        <v>1.39472413063049</v>
+        <v>1.3947240114212</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>1.5789999961853</v>
       </c>
       <c r="G301" t="n">
-        <v>1.41807436943054</v>
+        <v>1.41807425022125</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>1.58200001716614</v>
       </c>
       <c r="G305" t="n">
-        <v>1.42076873779297</v>
+        <v>1.42076861858368</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>1.57700002193451</v>
       </c>
       <c r="G307" t="n">
-        <v>1.41627824306488</v>
+        <v>1.41627812385559</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G309" t="n">
-        <v>1.37406826019287</v>
+        <v>1.37406837940216</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>1.53600001335144</v>
       </c>
       <c r="G311" t="n">
-        <v>1.37945687770844</v>
+        <v>1.37945675849915</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G313" t="n">
-        <v>1.38304901123047</v>
+        <v>1.38304889202118</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G314" t="n">
-        <v>1.39652025699615</v>
+        <v>1.39652037620544</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G316" t="n">
-        <v>1.41448199748993</v>
+        <v>1.41448211669922</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>1.62300002574921</v>
       </c>
       <c r="G321" t="n">
-        <v>1.45759010314941</v>
+        <v>1.45758998394012</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>1.62899994850159</v>
       </c>
       <c r="G322" t="n">
-        <v>1.4629784822464</v>
+        <v>1.46297860145569</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>1.65199995040894</v>
       </c>
       <c r="G326" t="n">
-        <v>1.48363447189331</v>
+        <v>1.48363435268402</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>1.63399994373322</v>
       </c>
       <c r="G327" t="n">
-        <v>1.4674688577652</v>
+        <v>1.46746897697449</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>1.62199997901917</v>
       </c>
       <c r="G329" t="n">
-        <v>1.45669198036194</v>
+        <v>1.45669186115265</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>1.63399994373322</v>
       </c>
       <c r="G336" t="n">
-        <v>1.4674688577652</v>
+        <v>1.46746897697449</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G341" t="n">
-        <v>1.48183822631836</v>
+        <v>1.48183846473694</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>1.67900002002716</v>
       </c>
       <c r="G343" t="n">
-        <v>1.50788271427155</v>
+        <v>1.50788283348083</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>1.67900002002716</v>
       </c>
       <c r="G345" t="n">
-        <v>1.50788271427155</v>
+        <v>1.50788283348083</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G348" t="n">
-        <v>1.51776158809662</v>
+        <v>1.51776170730591</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>1.89199995994568</v>
       </c>
       <c r="G351" t="n">
-        <v>1.69917464256287</v>
+        <v>1.69917452335358</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G357" t="n">
-        <v>1.74228262901306</v>
+        <v>1.74228250980377</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>1.8860000371933</v>
       </c>
       <c r="G362" t="n">
-        <v>1.69378614425659</v>
+        <v>1.6937860250473</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G364" t="n">
-        <v>1.71534013748169</v>
+        <v>1.7153400182724</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G365" t="n">
-        <v>1.66145503520966</v>
+        <v>1.66145515441895</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>1.82200002670288</v>
       </c>
       <c r="G367" t="n">
-        <v>1.63630867004395</v>
+        <v>1.63630878925323</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>1.80900001525879</v>
       </c>
       <c r="G369" t="n">
-        <v>1.62463355064392</v>
+        <v>1.62463366985321</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G371" t="n">
-        <v>1.63900291919708</v>
+        <v>1.63900303840637</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>1.83700001239777</v>
       </c>
       <c r="G373" t="n">
-        <v>1.64977991580963</v>
+        <v>1.64978003501892</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>1.82200002670288</v>
       </c>
       <c r="G374" t="n">
-        <v>1.63630867004395</v>
+        <v>1.63630878925323</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>1.83899998664856</v>
       </c>
       <c r="G375" t="n">
-        <v>1.65157604217529</v>
+        <v>1.65157616138458</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>1.84200000762939</v>
       </c>
       <c r="G376" t="n">
-        <v>1.65427029132843</v>
+        <v>1.65427052974701</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>1.81200003623962</v>
       </c>
       <c r="G378" t="n">
-        <v>1.62732779979706</v>
+        <v>1.62732791900635</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>1.71700000762939</v>
       </c>
       <c r="G387" t="n">
-        <v>1.54200983047485</v>
+        <v>1.54200994968414</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G391" t="n">
-        <v>1.55368494987488</v>
+        <v>1.55368506908417</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G392" t="n">
-        <v>1.58511781692505</v>
+        <v>1.58511793613434</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>1.80900001525879</v>
       </c>
       <c r="G397" t="n">
-        <v>1.62463355064392</v>
+        <v>1.62463366985321</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>1.75300002098083</v>
       </c>
       <c r="G402" t="n">
-        <v>1.5743408203125</v>
+        <v>1.57434093952179</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>1.78900003433228</v>
       </c>
       <c r="G405" t="n">
-        <v>1.60667192935944</v>
+        <v>1.60667204856873</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>1.80900001525879</v>
       </c>
       <c r="G410" t="n">
-        <v>1.62463355064392</v>
+        <v>1.62463366985321</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>1.79799997806549</v>
       </c>
       <c r="G413" t="n">
-        <v>1.61475455760956</v>
+        <v>1.61475467681885</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>1.75399994850159</v>
       </c>
       <c r="G415" t="n">
-        <v>1.57523894309998</v>
+        <v>1.57523906230927</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>1.78600001335144</v>
       </c>
       <c r="G416" t="n">
-        <v>1.6039776802063</v>
+        <v>1.60397779941559</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>1.87899994850159</v>
       </c>
       <c r="G427" t="n">
-        <v>1.68749952316284</v>
+        <v>1.68749940395355</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>1.85300004482269</v>
       </c>
       <c r="G429" t="n">
-        <v>1.66414928436279</v>
+        <v>1.66414940357208</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G433" t="n">
-        <v>1.81412923336029</v>
+        <v>1.81412935256958</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G434" t="n">
-        <v>1.88597595691681</v>
+        <v>1.88597583770752</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>2.19600009918213</v>
       </c>
       <c r="G435" t="n">
-        <v>1.97219204902649</v>
+        <v>1.97219216823578</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>2.24600005149841</v>
       </c>
       <c r="G436" t="n">
-        <v>2.01709628105164</v>
+        <v>2.01709651947021</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>2.41199994087219</v>
       </c>
       <c r="G438" t="n">
-        <v>2.16617798805237</v>
+        <v>2.16617822647095</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>2.57599997520447</v>
       </c>
       <c r="G443" t="n">
-        <v>2.31346368789673</v>
+        <v>2.31346392631531</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>2.61800003051758</v>
       </c>
       <c r="G446" t="n">
-        <v>2.35118317604065</v>
+        <v>2.35118341445923</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>2.61800003051758</v>
       </c>
       <c r="G447" t="n">
-        <v>2.35118317604065</v>
+        <v>2.35118341445923</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>2.53600001335144</v>
       </c>
       <c r="G448" t="n">
-        <v>2.27754044532776</v>
+        <v>2.27754068374634</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>2.61400008201599</v>
       </c>
       <c r="G450" t="n">
-        <v>2.34759092330933</v>
+        <v>2.34759116172791</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>2.49600005149841</v>
       </c>
       <c r="G453" t="n">
-        <v>2.24161696434021</v>
+        <v>2.24161720275879</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>2.43600010871887</v>
       </c>
       <c r="G456" t="n">
-        <v>2.18773198127747</v>
+        <v>2.18773221969604</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>2.32200002670288</v>
       </c>
       <c r="G457" t="n">
-        <v>2.08535051345825</v>
+        <v>2.08535075187683</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>2.54800009727478</v>
       </c>
       <c r="G459" t="n">
-        <v>2.28831744194031</v>
+        <v>2.28831768035889</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>2.80200004577637</v>
       </c>
       <c r="G461" t="n">
-        <v>2.51643109321594</v>
+        <v>2.51643085479736</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>2.86199998855591</v>
       </c>
       <c r="G463" t="n">
-        <v>2.57031607627869</v>
+        <v>2.57031583786011</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>2.91199994087219</v>
       </c>
       <c r="G464" t="n">
-        <v>2.61521983146667</v>
+        <v>2.61522006988525</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>2.75</v>
       </c>
       <c r="G467" t="n">
-        <v>2.46973061561584</v>
+        <v>2.46973037719727</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>2.79200005531311</v>
       </c>
       <c r="G474" t="n">
-        <v>2.50745010375977</v>
+        <v>2.50744986534119</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>2.3659999370575</v>
       </c>
       <c r="G477" t="n">
-        <v>2.12486624717712</v>
+        <v>2.12486600875854</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G479" t="n">
-        <v>2.16438174247742</v>
+        <v>2.164381980896</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>2.25600004196167</v>
       </c>
       <c r="G481" t="n">
-        <v>2.02607703208923</v>
+        <v>2.02607727050781</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G483" t="n">
-        <v>2.16438174247742</v>
+        <v>2.164381980896</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>2.5</v>
       </c>
       <c r="G485" t="n">
-        <v>2.24520945549011</v>
+        <v>2.24520969390869</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>2.50200009346008</v>
       </c>
       <c r="G487" t="n">
-        <v>2.24700546264648</v>
+        <v>2.24700570106506</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G496" t="n">
-        <v>2.23622846603394</v>
+        <v>2.23622870445251</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>2.54800009727478</v>
       </c>
       <c r="G500" t="n">
-        <v>2.28831744194031</v>
+        <v>2.28831768035889</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G501" t="n">
-        <v>2.23622846603394</v>
+        <v>2.23622870445251</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>2.5</v>
       </c>
       <c r="G502" t="n">
-        <v>2.24520945549011</v>
+        <v>2.24520969390869</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>2.5220000743866</v>
       </c>
       <c r="G506" t="n">
-        <v>2.26496720314026</v>
+        <v>2.26496744155884</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G518" t="n">
-        <v>2.21826672554016</v>
+        <v>2.21826720237732</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G521" t="n">
-        <v>2.16438174247742</v>
+        <v>2.164381980896</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G523" t="n">
-        <v>2.12845849990845</v>
+        <v>2.12845873832703</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G526" t="n">
-        <v>2.06559276580811</v>
+        <v>2.06559252738953</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G527" t="n">
-        <v>2.09253525733948</v>
+        <v>2.09253549575806</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G528" t="n">
-        <v>2.0835542678833</v>
+        <v>2.08355450630188</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>2.41499996185303</v>
       </c>
       <c r="G531" t="n">
-        <v>2.16887259483337</v>
+        <v>2.16887235641479</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G532" t="n">
-        <v>2.12845849990845</v>
+        <v>2.12845873832703</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G534" t="n">
-        <v>2.13743948936462</v>
+        <v>2.1374397277832</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G535" t="n">
-        <v>2.11947774887085</v>
+        <v>2.11947751045227</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G536" t="n">
-        <v>2.01170778274536</v>
+        <v>2.01170802116394</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>2.27500009536743</v>
       </c>
       <c r="G537" t="n">
-        <v>2.04314088821411</v>
+        <v>2.04314064979553</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G539" t="n">
-        <v>2.06559276580811</v>
+        <v>2.06559252738953</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>2.36500000953674</v>
       </c>
       <c r="G541" t="n">
-        <v>2.12396812438965</v>
+        <v>2.12396788597107</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>2.34500002861023</v>
       </c>
       <c r="G543" t="n">
-        <v>2.10600638389587</v>
+        <v>2.10600662231445</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G544" t="n">
-        <v>2.06559276580811</v>
+        <v>2.06559252738953</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G545" t="n">
-        <v>2.06559276580811</v>
+        <v>2.06559252738953</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G547" t="n">
-        <v>2.06559276580811</v>
+        <v>2.06559252738953</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>2.14499998092651</v>
       </c>
       <c r="G553" t="n">
-        <v>1.92638957500458</v>
+        <v>1.92638969421387</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G555" t="n">
-        <v>1.90393769741058</v>
+        <v>1.903937458992</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G556" t="n">
-        <v>1.85005259513855</v>
+        <v>1.85005247592926</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G557" t="n">
-        <v>1.91291880607605</v>
+        <v>1.91291868686676</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G559" t="n">
-        <v>1.94884181022644</v>
+        <v>1.94884192943573</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G560" t="n">
-        <v>1.98476529121399</v>
+        <v>1.9847651720047</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G561" t="n">
-        <v>2.01170778274536</v>
+        <v>2.01170802116394</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G563" t="n">
-        <v>2.00272679328918</v>
+        <v>2.00272703170776</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G564" t="n">
-        <v>2.06110262870789</v>
+        <v>2.06110239028931</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>2.27500009536743</v>
       </c>
       <c r="G565" t="n">
-        <v>2.04314088821411</v>
+        <v>2.04314064979553</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G566" t="n">
-        <v>1.99374604225159</v>
+        <v>1.99374616146088</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G567" t="n">
-        <v>2.00272679328918</v>
+        <v>2.00272703170776</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G568" t="n">
-        <v>2.01170778274536</v>
+        <v>2.01170802116394</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G569" t="n">
-        <v>2.00272679328918</v>
+        <v>2.00272703170776</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G570" t="n">
-        <v>1.94884181022644</v>
+        <v>1.94884192943573</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G572" t="n">
-        <v>1.91291880607605</v>
+        <v>1.91291868686676</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G575" t="n">
-        <v>1.98476529121399</v>
+        <v>1.9847651720047</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G576" t="n">
-        <v>1.98476529121399</v>
+        <v>1.9847651720047</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>2.23499989509583</v>
       </c>
       <c r="G581" t="n">
-        <v>2.00721740722656</v>
+        <v>2.00721716880798</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G586" t="n">
-        <v>2.0835542678833</v>
+        <v>2.08355450630188</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G587" t="n">
-        <v>2.06110262870789</v>
+        <v>2.06110239028931</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G590" t="n">
-        <v>2.06559276580811</v>
+        <v>2.06559252738953</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G592" t="n">
-        <v>2.06110262870789</v>
+        <v>2.06110239028931</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G593" t="n">
-        <v>2.01170778274536</v>
+        <v>2.01170802116394</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G596" t="n">
-        <v>2.0835542678833</v>
+        <v>2.08355450630188</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G598" t="n">
-        <v>2.23622846603394</v>
+        <v>2.23622870445251</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G599" t="n">
-        <v>2.23622846603394</v>
+        <v>2.23622870445251</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>2.5</v>
       </c>
       <c r="G601" t="n">
-        <v>2.24520945549011</v>
+        <v>2.24520969390869</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G603" t="n">
-        <v>2.21826672554016</v>
+        <v>2.21826720237732</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G605" t="n">
-        <v>2.11947774887085</v>
+        <v>2.11947751045227</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>2.35500001907349</v>
       </c>
       <c r="G606" t="n">
-        <v>2.11498761177063</v>
+        <v>2.11498737335205</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>2.35500001907349</v>
       </c>
       <c r="G608" t="n">
-        <v>2.11498761177063</v>
+        <v>2.11498737335205</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>2.27500009536743</v>
       </c>
       <c r="G612" t="n">
-        <v>2.04314088821411</v>
+        <v>2.04314064979553</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G619" t="n">
-        <v>2.06559276580811</v>
+        <v>2.06559252738953</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G623" t="n">
-        <v>2.06110262870789</v>
+        <v>2.06110239028931</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G628" t="n">
-        <v>2.06559276580811</v>
+        <v>2.06559252738953</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G631" t="n">
-        <v>1.99374604225159</v>
+        <v>1.99374616146088</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G633" t="n">
-        <v>2.01170778274536</v>
+        <v>2.01170802116394</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G635" t="n">
-        <v>2.00272679328918</v>
+        <v>2.00272703170776</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G636" t="n">
-        <v>1.95782279968262</v>
+        <v>1.95782291889191</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G639" t="n">
-        <v>1.99374604225159</v>
+        <v>1.99374616146088</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G641" t="n">
-        <v>1.99374604225159</v>
+        <v>1.99374616146088</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G643" t="n">
-        <v>1.99374604225159</v>
+        <v>1.99374616146088</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G645" t="n">
-        <v>1.95782279968262</v>
+        <v>1.95782291889191</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>2.1949999332428</v>
       </c>
       <c r="G647" t="n">
-        <v>1.9712940454483</v>
+        <v>1.97129392623901</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G649" t="n">
-        <v>1.95782279968262</v>
+        <v>1.95782291889191</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>2.18499994277954</v>
       </c>
       <c r="G650" t="n">
-        <v>1.96231305599213</v>
+        <v>1.96231317520142</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>2.20499992370605</v>
       </c>
       <c r="G651" t="n">
-        <v>1.98027455806732</v>
+        <v>1.98027467727661</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G653" t="n">
-        <v>1.95782279968262</v>
+        <v>1.95782291889191</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G655" t="n">
-        <v>1.94884181022644</v>
+        <v>1.94884192943573</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G659" t="n">
-        <v>1.93088030815125</v>
+        <v>1.93088018894196</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G661" t="n">
-        <v>1.90393769741058</v>
+        <v>1.903937458992</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G662" t="n">
-        <v>1.90393769741058</v>
+        <v>1.903937458992</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>2.125</v>
       </c>
       <c r="G663" t="n">
-        <v>1.90842807292938</v>
+        <v>1.90842795372009</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G664" t="n">
-        <v>1.93088030815125</v>
+        <v>1.93088018894196</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G665" t="n">
-        <v>1.93088030815125</v>
+        <v>1.93088018894196</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>2.14499998092651</v>
       </c>
       <c r="G666" t="n">
-        <v>1.92638957500458</v>
+        <v>1.92638969421387</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G667" t="n">
-        <v>1.90393769741058</v>
+        <v>1.903937458992</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>2.14499998092651</v>
       </c>
       <c r="G669" t="n">
-        <v>1.92638957500458</v>
+        <v>1.92638969421387</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G670" t="n">
-        <v>1.93088030815125</v>
+        <v>1.93088018894196</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G671" t="n">
-        <v>1.93088030815125</v>
+        <v>1.93088018894196</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G672" t="n">
-        <v>1.95782279968262</v>
+        <v>1.95782291889191</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G675" t="n">
-        <v>2.01170778274536</v>
+        <v>2.01170802116394</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G679" t="n">
-        <v>2.06559276580811</v>
+        <v>2.06559252738953</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G681" t="n">
-        <v>1.99374604225159</v>
+        <v>1.99374616146088</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G682" t="n">
-        <v>1.94884181022644</v>
+        <v>1.94884192943573</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>2.27500009536743</v>
       </c>
       <c r="G689" t="n">
-        <v>2.04314088821411</v>
+        <v>2.04314064979553</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>2.23499989509583</v>
       </c>
       <c r="G693" t="n">
-        <v>2.00721740722656</v>
+        <v>2.00721716880798</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G696" t="n">
-        <v>2.01170778274536</v>
+        <v>2.01170802116394</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>2.27500009536743</v>
       </c>
       <c r="G697" t="n">
-        <v>2.04314088821411</v>
+        <v>2.04314064979553</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G698" t="n">
-        <v>2.06110262870789</v>
+        <v>2.06110239028931</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>2.27500009536743</v>
       </c>
       <c r="G699" t="n">
-        <v>2.04314088821411</v>
+        <v>2.04314064979553</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G707" t="n">
-        <v>1.91291880607605</v>
+        <v>1.91291868686676</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G709" t="n">
-        <v>1.85005259513855</v>
+        <v>1.85005247592926</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G710" t="n">
-        <v>1.77820599079132</v>
+        <v>1.77820587158203</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G712" t="n">
-        <v>1.85903358459473</v>
+        <v>1.85903346538544</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G715" t="n">
-        <v>1.80514848232269</v>
+        <v>1.8051483631134</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>1.99199998378754</v>
       </c>
       <c r="G716" t="n">
-        <v>1.78898298740387</v>
+        <v>1.78898286819458</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>1.92599999904633</v>
       </c>
       <c r="G720" t="n">
-        <v>1.72970950603485</v>
+        <v>1.72970938682556</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>1.89400005340576</v>
       </c>
       <c r="G724" t="n">
-        <v>1.70097088813782</v>
+        <v>1.70097076892853</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>1.81599998474121</v>
       </c>
       <c r="G727" t="n">
-        <v>1.63092017173767</v>
+        <v>1.63092029094696</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>1.83399999141693</v>
       </c>
       <c r="G728" t="n">
-        <v>1.64708566665649</v>
+        <v>1.64708578586578</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>1.81599998474121</v>
       </c>
       <c r="G730" t="n">
-        <v>1.63092017173767</v>
+        <v>1.63092029094696</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>1.76199996471405</v>
       </c>
       <c r="G733" t="n">
-        <v>1.58242356777191</v>
+        <v>1.5824236869812</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>1.65400004386902</v>
       </c>
       <c r="G736" t="n">
-        <v>1.48543059825897</v>
+        <v>1.48543071746826</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>1.65199995040894</v>
       </c>
       <c r="G737" t="n">
-        <v>1.48363447189331</v>
+        <v>1.48363435268402</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>1.55599999427795</v>
       </c>
       <c r="G741" t="n">
-        <v>1.39741849899292</v>
+        <v>1.39741837978363</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>1.50800001621246</v>
       </c>
       <c r="G744" t="n">
-        <v>1.35431039333344</v>
+        <v>1.35431027412415</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G748" t="n">
-        <v>1.40101063251495</v>
+        <v>1.40101075172424</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>1.50399994850159</v>
       </c>
       <c r="G749" t="n">
-        <v>1.35071814060211</v>
+        <v>1.35071802139282</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G752" t="n">
-        <v>1.30222165584564</v>
+        <v>1.30222153663635</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>1.25</v>
       </c>
       <c r="G759" t="n">
-        <v>1.12260472774506</v>
+        <v>1.12260484695435</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G762" t="n">
-        <v>1.14954710006714</v>
+        <v>1.14954721927643</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>1.30400002002716</v>
       </c>
       <c r="G763" t="n">
-        <v>1.17110121250153</v>
+        <v>1.17110133171082</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>1.41400003433228</v>
       </c>
       <c r="G765" t="n">
-        <v>1.269890666008</v>
+        <v>1.26989054679871</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G769" t="n">
-        <v>1.36508750915527</v>
+        <v>1.36508738994598</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G772" t="n">
-        <v>1.31120252609253</v>
+        <v>1.31120240688324</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>1.47800004482269</v>
       </c>
       <c r="G773" t="n">
-        <v>1.32736802101135</v>
+        <v>1.32736790180206</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>1.5</v>
       </c>
       <c r="G776" t="n">
-        <v>1.3471257686615</v>
+        <v>1.34712564945221</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>1.47200000286102</v>
       </c>
       <c r="G780" t="n">
-        <v>1.3219792842865</v>
+        <v>1.32197940349579</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>1.49800002574921</v>
       </c>
       <c r="G782" t="n">
-        <v>1.34532952308655</v>
+        <v>1.34532964229584</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G786" t="n">
-        <v>1.31120252609253</v>
+        <v>1.31120240688324</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>1.38800001144409</v>
       </c>
       <c r="G792" t="n">
-        <v>1.24654042720795</v>
+        <v>1.24654018878937</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>1.78199994564056</v>
       </c>
       <c r="G799" t="n">
-        <v>1.6003851890564</v>
+        <v>1.60038530826569</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G803" t="n">
-        <v>1.88597595691681</v>
+        <v>1.88597583770752</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G804" t="n">
-        <v>1.85005259513855</v>
+        <v>1.85005247592926</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>2.14499998092651</v>
       </c>
       <c r="G806" t="n">
-        <v>1.92638957500458</v>
+        <v>1.92638969421387</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G807" t="n">
-        <v>1.85903358459473</v>
+        <v>1.85903346538544</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G809" t="n">
-        <v>1.85005259513855</v>
+        <v>1.85005247592926</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G811" t="n">
-        <v>1.81412923336029</v>
+        <v>1.81412935256958</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>2.04500007629395</v>
       </c>
       <c r="G812" t="n">
-        <v>1.83658146858215</v>
+        <v>1.83658158779144</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G813" t="n">
-        <v>1.81412923336029</v>
+        <v>1.81412935256958</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G814" t="n">
-        <v>1.80514848232269</v>
+        <v>1.8051483631134</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>1.98599994182587</v>
       </c>
       <c r="G815" t="n">
-        <v>1.78359436988831</v>
+        <v>1.7835944890976</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>1.90600001811981</v>
       </c>
       <c r="G820" t="n">
-        <v>1.71174788475037</v>
+        <v>1.71174764633179</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>1.87600004673004</v>
       </c>
       <c r="G823" t="n">
-        <v>1.68480539321899</v>
+        <v>1.6848052740097</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>1.90600001811981</v>
       </c>
       <c r="G825" t="n">
-        <v>1.71174788475037</v>
+        <v>1.71174764633179</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G828" t="n">
-        <v>1.99374604225159</v>
+        <v>1.99374616146088</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G829" t="n">
-        <v>2.06559276580811</v>
+        <v>2.06559252738953</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>2.31500005722046</v>
       </c>
       <c r="G830" t="n">
-        <v>2.07906413078308</v>
+        <v>2.0790638923645</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>2.34500002861023</v>
       </c>
       <c r="G831" t="n">
-        <v>2.10600638389587</v>
+        <v>2.10600662231445</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G832" t="n">
-        <v>2.01170778274536</v>
+        <v>2.01170802116394</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>2.14499998092651</v>
       </c>
       <c r="G833" t="n">
-        <v>1.92638957500458</v>
+        <v>1.92638969421387</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G834" t="n">
-        <v>1.99374604225159</v>
+        <v>1.99374616146088</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G837" t="n">
-        <v>1.99374604225159</v>
+        <v>1.99374616146088</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G838" t="n">
-        <v>2.13743948936462</v>
+        <v>2.1374397277832</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G840" t="n">
-        <v>2.17336297035217</v>
+        <v>2.17336320877075</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G846" t="n">
-        <v>2.09253525733948</v>
+        <v>2.09253549575806</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>2.36500000953674</v>
       </c>
       <c r="G850" t="n">
-        <v>2.12396812438965</v>
+        <v>2.12396788597107</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G855" t="n">
-        <v>1.95782279968262</v>
+        <v>1.95782291889191</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G856" t="n">
-        <v>1.95782279968262</v>
+        <v>1.95782291889191</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G858" t="n">
-        <v>2.06110262870789</v>
+        <v>2.06110239028931</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>2.27500009536743</v>
       </c>
       <c r="G860" t="n">
-        <v>2.04314088821411</v>
+        <v>2.04314064979553</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G864" t="n">
-        <v>2.06559276580811</v>
+        <v>2.06559252738953</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G869" t="n">
-        <v>2.06559276580811</v>
+        <v>2.06559252738953</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G870" t="n">
-        <v>2.06110262870789</v>
+        <v>2.06110239028931</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>2.27500009536743</v>
       </c>
       <c r="G874" t="n">
-        <v>2.04314088821411</v>
+        <v>2.04314064979553</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G877" t="n">
-        <v>1.85903358459473</v>
+        <v>1.85903346538544</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G878" t="n">
-        <v>1.86801433563232</v>
+        <v>1.86801421642303</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G881" t="n">
-        <v>1.81412923336029</v>
+        <v>1.81412935256958</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>2.02500009536743</v>
       </c>
       <c r="G882" t="n">
-        <v>1.81861984729767</v>
+        <v>1.81861972808838</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>1.96399998664856</v>
       </c>
       <c r="G885" t="n">
-        <v>1.76383662223816</v>
+        <v>1.76383650302887</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>1.98800003528595</v>
       </c>
       <c r="G890" t="n">
-        <v>1.78539073467255</v>
+        <v>1.78539061546326</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G891" t="n">
-        <v>1.81412923336029</v>
+        <v>1.81412935256958</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G894" t="n">
-        <v>1.80514848232269</v>
+        <v>1.8051483631134</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>1.99600005149841</v>
       </c>
       <c r="G896" t="n">
-        <v>1.79257535934448</v>
+        <v>1.79257524013519</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G898" t="n">
-        <v>1.81412923336029</v>
+        <v>1.81412935256958</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G899" t="n">
-        <v>1.80514848232269</v>
+        <v>1.8051483631134</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>1.97800004482269</v>
       </c>
       <c r="G902" t="n">
-        <v>1.77640998363495</v>
+        <v>1.77640986442566</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>1.92200005054474</v>
       </c>
       <c r="G905" t="n">
-        <v>1.72611725330353</v>
+        <v>1.72611701488495</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>2.1949999332428</v>
       </c>
       <c r="G906" t="n">
-        <v>1.9712940454483</v>
+        <v>1.97129392623901</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G907" t="n">
-        <v>1.95782279968262</v>
+        <v>1.95782291889191</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G909" t="n">
-        <v>1.99374604225159</v>
+        <v>1.99374616146088</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G911" t="n">
-        <v>1.93088030815125</v>
+        <v>1.93088018894196</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>2.20499992370605</v>
       </c>
       <c r="G912" t="n">
-        <v>1.98027455806732</v>
+        <v>1.98027467727661</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G913" t="n">
-        <v>1.94884181022644</v>
+        <v>1.94884192943573</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>2.125</v>
       </c>
       <c r="G914" t="n">
-        <v>1.90842807292938</v>
+        <v>1.90842795372009</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>2.14499998092651</v>
       </c>
       <c r="G917" t="n">
-        <v>1.92638957500458</v>
+        <v>1.92638969421387</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G918" t="n">
-        <v>1.90393769741058</v>
+        <v>1.903937458992</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>2.04500007629395</v>
       </c>
       <c r="G919" t="n">
-        <v>1.83658146858215</v>
+        <v>1.83658158779144</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G920" t="n">
-        <v>1.85005259513855</v>
+        <v>1.85005247592926</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>1.99199998378754</v>
       </c>
       <c r="G921" t="n">
-        <v>1.78898298740387</v>
+        <v>1.78898286819458</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G925" t="n">
-        <v>1.81412923336029</v>
+        <v>1.81412935256958</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>1.94799995422363</v>
       </c>
       <c r="G928" t="n">
-        <v>1.74946737289429</v>
+        <v>1.74946713447571</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>1.94799995422363</v>
       </c>
       <c r="G932" t="n">
-        <v>1.74946737289429</v>
+        <v>1.74946713447571</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G935" t="n">
-        <v>1.81412923336029</v>
+        <v>1.81412935256958</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G936" t="n">
-        <v>1.85903358459473</v>
+        <v>1.85903346538544</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G937" t="n">
-        <v>1.84556233882904</v>
+        <v>1.84556221961975</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G939" t="n">
-        <v>1.83209097385406</v>
+        <v>1.83209109306335</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>2.41499996185303</v>
       </c>
       <c r="G942" t="n">
-        <v>2.16887259483337</v>
+        <v>2.16887235641479</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G943" t="n">
-        <v>2.16438174247742</v>
+        <v>2.164381980896</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G944" t="n">
-        <v>2.09253525733948</v>
+        <v>2.09253549575806</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>2.31500005722046</v>
       </c>
       <c r="G945" t="n">
-        <v>2.07906413078308</v>
+        <v>2.0790638923645</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G947" t="n">
-        <v>1.98476529121399</v>
+        <v>1.9847651720047</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>2.27500009536743</v>
       </c>
       <c r="G951" t="n">
-        <v>2.04314088821411</v>
+        <v>2.04314064979553</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G952" t="n">
-        <v>2.00272679328918</v>
+        <v>2.00272703170776</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>2.27500009536743</v>
       </c>
       <c r="G955" t="n">
-        <v>2.04314088821411</v>
+        <v>2.04314064979553</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G957" t="n">
-        <v>1.99374604225159</v>
+        <v>1.99374616146088</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G960" t="n">
-        <v>1.95782279968262</v>
+        <v>1.95782291889191</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G961" t="n">
-        <v>1.98476529121399</v>
+        <v>1.9847651720047</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G962" t="n">
-        <v>1.99374604225159</v>
+        <v>1.99374616146088</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G963" t="n">
-        <v>2.09253525733948</v>
+        <v>2.09253549575806</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G964" t="n">
-        <v>2.0835542678833</v>
+        <v>2.08355450630188</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>2.40499997138977</v>
       </c>
       <c r="G965" t="n">
-        <v>2.1598916053772</v>
+        <v>2.15989136695862</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G966" t="n">
-        <v>2.16438174247742</v>
+        <v>2.164381980896</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G967" t="n">
-        <v>2.09253525733948</v>
+        <v>2.09253549575806</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>2.40499997138977</v>
       </c>
       <c r="G968" t="n">
-        <v>2.1598916053772</v>
+        <v>2.15989136695862</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>2.36500000953674</v>
       </c>
       <c r="G969" t="n">
-        <v>2.12396812438965</v>
+        <v>2.12396788597107</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>2.35500001907349</v>
       </c>
       <c r="G970" t="n">
-        <v>2.11498761177063</v>
+        <v>2.11498737335205</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G972" t="n">
-        <v>2.06559276580811</v>
+        <v>2.06559252738953</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G978" t="n">
-        <v>2.29909420013428</v>
+        <v>2.29909443855286</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G979" t="n">
-        <v>2.38890314102173</v>
+        <v>2.38890290260315</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>2.75500011444092</v>
       </c>
       <c r="G981" t="n">
-        <v>2.47422099113464</v>
+        <v>2.47422075271606</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G982" t="n">
-        <v>2.56851983070374</v>
+        <v>2.56851959228516</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G985" t="n">
-        <v>2.64934730529785</v>
+        <v>2.64934706687927</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>2.96499991416931</v>
       </c>
       <c r="G986" t="n">
-        <v>2.66281819343567</v>
+        <v>2.66281843185425</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G987" t="n">
-        <v>2.73017501831055</v>
+        <v>2.73017477989197</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G988" t="n">
-        <v>2.68527054786682</v>
+        <v>2.68527030944824</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G989" t="n">
-        <v>2.79304051399231</v>
+        <v>2.79304075241089</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G990" t="n">
-        <v>2.68527054786682</v>
+        <v>2.68527030944824</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>2.96499991416931</v>
       </c>
       <c r="G991" t="n">
-        <v>2.66281819343567</v>
+        <v>2.66281843185425</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G993" t="n">
-        <v>2.76609802246094</v>
+        <v>2.76609778404236</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G994" t="n">
-        <v>2.91428208351135</v>
+        <v>2.91428160667419</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G998" t="n">
-        <v>2.74364590644836</v>
+        <v>2.74364614486694</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>2.96499991416931</v>
       </c>
       <c r="G1003" t="n">
-        <v>2.66281819343567</v>
+        <v>2.66281843185425</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>3.02500009536743</v>
       </c>
       <c r="G1004" t="n">
-        <v>2.71670341491699</v>
+        <v>2.71670365333557</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1005" t="n">
-        <v>2.68527054786682</v>
+        <v>2.68527030944824</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G1007" t="n">
-        <v>2.72568416595459</v>
+        <v>2.72568440437317</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>3</v>
       </c>
       <c r="G1008" t="n">
-        <v>2.694251537323</v>
+        <v>2.69425129890442</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1009" t="n">
-        <v>2.66730880737305</v>
+        <v>2.66730904579163</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1010" t="n">
-        <v>2.64934730529785</v>
+        <v>2.64934706687927</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G1011" t="n">
-        <v>2.72568416595459</v>
+        <v>2.72568440437317</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1015" t="n">
-        <v>2.74813652038574</v>
+        <v>2.74813675880432</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>2.96499991416931</v>
       </c>
       <c r="G1019" t="n">
-        <v>2.66281819343567</v>
+        <v>2.66281843185425</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>2.88499999046326</v>
       </c>
       <c r="G1020" t="n">
-        <v>2.59097146987915</v>
+        <v>2.59097170829773</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1021" t="n">
-        <v>2.66730880737305</v>
+        <v>2.66730904579163</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>3.1949999332428</v>
       </c>
       <c r="G1022" t="n">
-        <v>2.86937785148621</v>
+        <v>2.86937761306763</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1026" t="n">
-        <v>2.96367645263672</v>
+        <v>2.96367692947388</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>3.3050000667572</v>
       </c>
       <c r="G1027" t="n">
-        <v>2.96816730499268</v>
+        <v>2.9681670665741</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1028" t="n">
-        <v>3.10736989974976</v>
+        <v>3.10737013816833</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>3.6949999332428</v>
       </c>
       <c r="G1029" t="n">
-        <v>3.31841969490051</v>
+        <v>3.31841993331909</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1032" t="n">
-        <v>3.07144641876221</v>
+        <v>3.07144665718079</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1033" t="n">
-        <v>2.96367645263672</v>
+        <v>2.96367692947388</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>3.57500004768372</v>
       </c>
       <c r="G1035" t="n">
-        <v>3.21064972877502</v>
+        <v>3.21064949035645</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1036" t="n">
-        <v>3.10736989974976</v>
+        <v>3.10737013816833</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1038" t="n">
-        <v>3.07144641876221</v>
+        <v>3.07144665718079</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1042" t="n">
-        <v>3.24208235740662</v>
+        <v>3.2420825958252</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>3.74499988555908</v>
       </c>
       <c r="G1044" t="n">
-        <v>3.36332368850708</v>
+        <v>3.36332392692566</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>3.85500001907349</v>
       </c>
       <c r="G1045" t="n">
-        <v>3.46211290359497</v>
+        <v>3.46211314201355</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G1046" t="n">
-        <v>3.34536218643188</v>
+        <v>3.34536194801331</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1047" t="n">
-        <v>3.25106310844421</v>
+        <v>3.25106334686279</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>3.57500004768372</v>
       </c>
       <c r="G1050" t="n">
-        <v>3.21064972877502</v>
+        <v>3.21064949035645</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1051" t="n">
-        <v>3.09838914871216</v>
+        <v>3.09838938713074</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>3.375</v>
       </c>
       <c r="G1052" t="n">
-        <v>3.03103303909302</v>
+        <v>3.03103280067444</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1053" t="n">
-        <v>2.873868227005</v>
+        <v>2.87386846542358</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1056" t="n">
-        <v>2.79304051399231</v>
+        <v>2.79304075241089</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1062" t="n">
-        <v>2.56851983070374</v>
+        <v>2.56851959228516</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>2.45499992370605</v>
       </c>
       <c r="G1064" t="n">
-        <v>2.20479583740234</v>
+        <v>2.20479559898376</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1069" t="n">
-        <v>1.81412923336029</v>
+        <v>1.81412935256958</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1070" t="n">
-        <v>1.86801433563232</v>
+        <v>1.86801421642303</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>1.9559999704361</v>
       </c>
       <c r="G1071" t="n">
-        <v>1.75665199756622</v>
+        <v>1.75665187835693</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>2.16499996185303</v>
       </c>
       <c r="G1074" t="n">
-        <v>1.94435131549835</v>
+        <v>1.94435143470764</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G1078" t="n">
-        <v>1.98476529121399</v>
+        <v>1.9847651720047</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>2.75</v>
       </c>
       <c r="G1086" t="n">
-        <v>2.46973061561584</v>
+        <v>2.46973037719727</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1087" t="n">
-        <v>2.53259611129761</v>
+        <v>2.53259634971619</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>2.68499994277954</v>
       </c>
       <c r="G1089" t="n">
-        <v>2.41135501861572</v>
+        <v>2.41135478019714</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1090" t="n">
-        <v>2.54157733917236</v>
+        <v>2.54157710075378</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>2.9449999332428</v>
       </c>
       <c r="G1091" t="n">
-        <v>2.64485645294189</v>
+        <v>2.64485669136047</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1092" t="n">
-        <v>2.62240505218506</v>
+        <v>2.62240481376648</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>2.86500000953674</v>
       </c>
       <c r="G1093" t="n">
-        <v>2.57301020622253</v>
+        <v>2.57301044464111</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1094" t="n">
-        <v>2.51463484764099</v>
+        <v>2.51463460922241</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>2.86500000953674</v>
       </c>
       <c r="G1095" t="n">
-        <v>2.57301020622253</v>
+        <v>2.57301044464111</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1096" t="n">
-        <v>2.68527054786682</v>
+        <v>2.68527030944824</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>2.97499990463257</v>
       </c>
       <c r="G1097" t="n">
-        <v>2.67179918289185</v>
+        <v>2.67179942131042</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1101" t="n">
-        <v>2.64934730529785</v>
+        <v>2.64934706687927</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1103" t="n">
-        <v>2.55953884124756</v>
+        <v>2.55953860282898</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1104" t="n">
-        <v>2.56851983070374</v>
+        <v>2.56851959228516</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1106" t="n">
-        <v>2.73017501831055</v>
+        <v>2.73017477989197</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1107" t="n">
-        <v>2.64934730529785</v>
+        <v>2.64934706687927</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>2.86500000953674</v>
       </c>
       <c r="G1108" t="n">
-        <v>2.57301020622253</v>
+        <v>2.57301044464111</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1109" t="n">
-        <v>2.64036655426025</v>
+        <v>2.64036631584167</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>2.96499991416931</v>
       </c>
       <c r="G1110" t="n">
-        <v>2.66281819343567</v>
+        <v>2.66281843185425</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1111" t="n">
-        <v>2.55953884124756</v>
+        <v>2.55953860282898</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>2.77500009536743</v>
       </c>
       <c r="G1113" t="n">
-        <v>2.49218273162842</v>
+        <v>2.49218249320984</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1114" t="n">
-        <v>2.48769235610962</v>
+        <v>2.48769211769104</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G1115" t="n">
-        <v>2.52810597419739</v>
+        <v>2.52810621261597</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1116" t="n">
-        <v>2.59546256065369</v>
+        <v>2.59546232223511</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>2.86500000953674</v>
       </c>
       <c r="G1117" t="n">
-        <v>2.57301020622253</v>
+        <v>2.57301044464111</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>2.9449999332428</v>
       </c>
       <c r="G1118" t="n">
-        <v>2.64485645294189</v>
+        <v>2.64485669136047</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1123" t="n">
-        <v>2.60444331169128</v>
+        <v>2.60444307327271</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1124" t="n">
-        <v>2.60444331169128</v>
+        <v>2.60444307327271</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1126" t="n">
-        <v>2.74813652038574</v>
+        <v>2.74813675880432</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1129" t="n">
-        <v>2.55953884124756</v>
+        <v>2.55953860282898</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1130" t="n">
-        <v>2.53259611129761</v>
+        <v>2.53259634971619</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1133" t="n">
-        <v>2.48769235610962</v>
+        <v>2.48769211769104</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -29879,7 +29879,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1135" t="n">
-        <v>2.51463484764099</v>
+        <v>2.51463460922241</v>
       </c>
       <c r="H1135" t="s">
         <v>8</v>
@@ -29983,7 +29983,7 @@
         <v>2.72499990463257</v>
       </c>
       <c r="G1139" t="n">
-        <v>2.44727826118469</v>
+        <v>2.44727849960327</v>
       </c>
       <c r="H1139" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1142" t="n">
-        <v>2.43380737304688</v>
+        <v>2.4338071346283</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1143" t="n">
-        <v>2.48769235610962</v>
+        <v>2.48769211769104</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30191,7 +30191,7 @@
         <v>2.75</v>
       </c>
       <c r="G1147" t="n">
-        <v>2.46973061561584</v>
+        <v>2.46973037719727</v>
       </c>
       <c r="H1147" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G1148" t="n">
-        <v>2.38890314102173</v>
+        <v>2.38890290260315</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G1149" t="n">
-        <v>2.38890314102173</v>
+        <v>2.38890290260315</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G1151" t="n">
-        <v>2.4068648815155</v>
+        <v>2.40686464309692</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1152" t="n">
-        <v>2.4158456325531</v>
+        <v>2.41584539413452</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>2.76500010490417</v>
       </c>
       <c r="G1153" t="n">
-        <v>2.48320174217224</v>
+        <v>2.48320198059082</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1155" t="n">
-        <v>2.53259611129761</v>
+        <v>2.53259634971619</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30425,7 +30425,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1156" t="n">
-        <v>2.48769235610962</v>
+        <v>2.48769211769104</v>
       </c>
       <c r="H1156" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1159" t="n">
-        <v>2.4158456325531</v>
+        <v>2.41584539413452</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1160" t="n">
-        <v>2.4158456325531</v>
+        <v>2.41584539413452</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G1162" t="n">
-        <v>2.39788389205933</v>
+        <v>2.39788365364075</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1163" t="n">
-        <v>2.27215170860291</v>
+        <v>2.27215194702148</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30633,7 +30633,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1164" t="n">
-        <v>2.27215170860291</v>
+        <v>2.27215194702148</v>
       </c>
       <c r="H1164" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>2.57500004768372</v>
       </c>
       <c r="G1168" t="n">
-        <v>2.31256580352783</v>
+        <v>2.31256604194641</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>2.54500007629395</v>
       </c>
       <c r="G1169" t="n">
-        <v>2.28562355041504</v>
+        <v>2.28562331199646</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>2.76500010490417</v>
       </c>
       <c r="G1173" t="n">
-        <v>2.48320174217224</v>
+        <v>2.48320198059082</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30971,7 +30971,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1177" t="n">
-        <v>2.48769235610962</v>
+        <v>2.48769211769104</v>
       </c>
       <c r="H1177" t="s">
         <v>8</v>
@@ -30997,7 +30997,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G1178" t="n">
-        <v>2.38890314102173</v>
+        <v>2.38890290260315</v>
       </c>
       <c r="H1178" t="s">
         <v>8</v>
@@ -31023,7 +31023,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1179" t="n">
-        <v>2.4158456325531</v>
+        <v>2.41584539413452</v>
       </c>
       <c r="H1179" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G1180" t="n">
-        <v>2.39788389205933</v>
+        <v>2.39788365364075</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1181" t="n">
-        <v>2.37992215156555</v>
+        <v>2.37992238998413</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1182" t="n">
-        <v>2.37094116210938</v>
+        <v>2.37094140052795</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>2.60500001907349</v>
       </c>
       <c r="G1183" t="n">
-        <v>2.3395082950592</v>
+        <v>2.33950805664062</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31231,7 +31231,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G1187" t="n">
-        <v>2.39788389205933</v>
+        <v>2.39788365364075</v>
       </c>
       <c r="H1187" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>2.67499995231628</v>
       </c>
       <c r="G1188" t="n">
-        <v>2.40237402915955</v>
+        <v>2.40237426757812</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1189" t="n">
-        <v>2.37094116210938</v>
+        <v>2.37094140052795</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1190" t="n">
-        <v>2.37992215156555</v>
+        <v>2.37992238998413</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>2.67499995231628</v>
       </c>
       <c r="G1191" t="n">
-        <v>2.40237402915955</v>
+        <v>2.40237426757812</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1193" t="n">
-        <v>2.43380737304688</v>
+        <v>2.4338071346283</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>2.76500010490417</v>
       </c>
       <c r="G1197" t="n">
-        <v>2.48320174217224</v>
+        <v>2.48320198059082</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>2.66499996185303</v>
       </c>
       <c r="G1198" t="n">
-        <v>2.39339327812195</v>
+        <v>2.39339351654053</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G1199" t="n">
-        <v>2.29909420013428</v>
+        <v>2.29909443855286</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>2.57500004768372</v>
       </c>
       <c r="G1201" t="n">
-        <v>2.31256580352783</v>
+        <v>2.31256604194641</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G1202" t="n">
-        <v>2.29909420013428</v>
+        <v>2.29909443855286</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1204" t="n">
-        <v>2.27215170860291</v>
+        <v>2.27215194702148</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31725,7 +31725,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1206" t="n">
-        <v>2.23622846603394</v>
+        <v>2.23622870445251</v>
       </c>
       <c r="H1206" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1207" t="n">
-        <v>2.27215170860291</v>
+        <v>2.27215194702148</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1209" t="n">
-        <v>2.31705594062805</v>
+        <v>2.31705617904663</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31829,7 +31829,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G1210" t="n">
-        <v>2.29909420013428</v>
+        <v>2.29909443855286</v>
       </c>
       <c r="H1210" t="s">
         <v>8</v>
@@ -31881,7 +31881,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1212" t="n">
-        <v>2.37992215156555</v>
+        <v>2.37992238998413</v>
       </c>
       <c r="H1212" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1214" t="n">
-        <v>2.37094116210938</v>
+        <v>2.37094140052795</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1215" t="n">
-        <v>2.37992215156555</v>
+        <v>2.37992238998413</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1220" t="n">
-        <v>2.53259611129761</v>
+        <v>2.53259634971619</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32115,7 +32115,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1221" t="n">
-        <v>2.60444331169128</v>
+        <v>2.60444307327271</v>
       </c>
       <c r="H1221" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>2.86500000953674</v>
       </c>
       <c r="G1223" t="n">
-        <v>2.57301020622253</v>
+        <v>2.57301044464111</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32193,7 +32193,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1224" t="n">
-        <v>2.53259611129761</v>
+        <v>2.53259634971619</v>
       </c>
       <c r="H1224" t="s">
         <v>8</v>
@@ -32219,7 +32219,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1225" t="n">
-        <v>2.43380737304688</v>
+        <v>2.4338071346283</v>
       </c>
       <c r="H1225" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>2.75500011444092</v>
       </c>
       <c r="G1226" t="n">
-        <v>2.47422099113464</v>
+        <v>2.47422075271606</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1227" t="n">
-        <v>2.27215170860291</v>
+        <v>2.27215194702148</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32349,7 +32349,7 @@
         <v>2.59500002861023</v>
       </c>
       <c r="G1230" t="n">
-        <v>2.33052754402161</v>
+        <v>2.33052730560303</v>
       </c>
       <c r="H1230" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>2.59500002861023</v>
       </c>
       <c r="G1231" t="n">
-        <v>2.33052754402161</v>
+        <v>2.33052730560303</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1234" t="n">
-        <v>2.31705594062805</v>
+        <v>2.31705617904663</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32479,7 +32479,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1235" t="n">
-        <v>2.37992215156555</v>
+        <v>2.37992238998413</v>
       </c>
       <c r="H1235" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1236" t="n">
-        <v>2.43380737304688</v>
+        <v>2.4338071346283</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1237" t="n">
-        <v>2.4158456325531</v>
+        <v>2.41584539413452</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -32557,7 +32557,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1238" t="n">
-        <v>2.37992215156555</v>
+        <v>2.37992238998413</v>
       </c>
       <c r="H1238" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>2.75</v>
       </c>
       <c r="G1239" t="n">
-        <v>2.46973061561584</v>
+        <v>2.46973037719727</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>2.77500009536743</v>
       </c>
       <c r="G1242" t="n">
-        <v>2.49218273162842</v>
+        <v>2.49218249320984</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1246" t="n">
-        <v>2.53259611129761</v>
+        <v>2.53259634971619</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32791,7 +32791,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1247" t="n">
-        <v>2.55953884124756</v>
+        <v>2.55953860282898</v>
       </c>
       <c r="H1247" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1248" t="n">
-        <v>2.56851983070374</v>
+        <v>2.56851959228516</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32843,7 +32843,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1249" t="n">
-        <v>2.53259611129761</v>
+        <v>2.53259634971619</v>
       </c>
       <c r="H1249" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1252" t="n">
-        <v>2.68527054786682</v>
+        <v>2.68527030944824</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>3</v>
       </c>
       <c r="G1254" t="n">
-        <v>2.694251537323</v>
+        <v>2.69425129890442</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -32999,7 +32999,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1255" t="n">
-        <v>2.74813652038574</v>
+        <v>2.74813675880432</v>
       </c>
       <c r="H1255" t="s">
         <v>8</v>
@@ -33077,7 +33077,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1258" t="n">
-        <v>2.73017501831055</v>
+        <v>2.73017477989197</v>
       </c>
       <c r="H1258" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1259" t="n">
-        <v>2.64036655426025</v>
+        <v>2.64036631584167</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>3.02500009536743</v>
       </c>
       <c r="G1265" t="n">
-        <v>2.71670341491699</v>
+        <v>2.71670365333557</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33467,7 +33467,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1273" t="n">
-        <v>2.79304051399231</v>
+        <v>2.79304075241089</v>
       </c>
       <c r="H1273" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1276" t="n">
-        <v>2.79304051399231</v>
+        <v>2.79304075241089</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33571,7 +33571,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1277" t="n">
-        <v>2.79304051399231</v>
+        <v>2.79304075241089</v>
       </c>
       <c r="H1277" t="s">
         <v>8</v>
@@ -33623,7 +33623,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G1279" t="n">
-        <v>2.72568416595459</v>
+        <v>2.72568440437317</v>
       </c>
       <c r="H1279" t="s">
         <v>8</v>
@@ -33649,7 +33649,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1280" t="n">
-        <v>2.73017501831055</v>
+        <v>2.73017477989197</v>
       </c>
       <c r="H1280" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>2.9449999332428</v>
       </c>
       <c r="G1283" t="n">
-        <v>2.64485645294189</v>
+        <v>2.64485669136047</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33753,7 +33753,7 @@
         <v>3</v>
       </c>
       <c r="G1284" t="n">
-        <v>2.694251537323</v>
+        <v>2.69425129890442</v>
       </c>
       <c r="H1284" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G1286" t="n">
-        <v>2.54606771469116</v>
+        <v>2.54606747627258</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1288" t="n">
-        <v>2.60444331169128</v>
+        <v>2.60444307327271</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33909,7 +33909,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1290" t="n">
-        <v>2.60444331169128</v>
+        <v>2.60444307327271</v>
       </c>
       <c r="H1290" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>3</v>
       </c>
       <c r="G1291" t="n">
-        <v>2.694251537323</v>
+        <v>2.69425129890442</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -33961,7 +33961,7 @@
         <v>3.02500009536743</v>
       </c>
       <c r="G1292" t="n">
-        <v>2.71670341491699</v>
+        <v>2.71670365333557</v>
       </c>
       <c r="H1292" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1295" t="n">
-        <v>2.79304051399231</v>
+        <v>2.79304075241089</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1299" t="n">
-        <v>3.08940815925598</v>
+        <v>3.08940839767456</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34169,7 +34169,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G1300" t="n">
-        <v>3.12982201576233</v>
+        <v>3.12982177734375</v>
       </c>
       <c r="H1300" t="s">
         <v>8</v>
@@ -34299,7 +34299,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G1305" t="n">
-        <v>3.12982201576233</v>
+        <v>3.12982177734375</v>
       </c>
       <c r="H1305" t="s">
         <v>8</v>
@@ -34351,7 +34351,7 @@
         <v>3.42499995231628</v>
       </c>
       <c r="G1307" t="n">
-        <v>3.07593703269958</v>
+        <v>3.07593679428101</v>
       </c>
       <c r="H1307" t="s">
         <v>8</v>
@@ -34377,7 +34377,7 @@
         <v>3.42499995231628</v>
       </c>
       <c r="G1308" t="n">
-        <v>3.07593703269958</v>
+        <v>3.07593679428101</v>
       </c>
       <c r="H1308" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>3.33500003814697</v>
       </c>
       <c r="G1309" t="n">
-        <v>2.99510955810547</v>
+        <v>2.99510931968689</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>3.22499990463257</v>
       </c>
       <c r="G1310" t="n">
-        <v>2.89632034301758</v>
+        <v>2.896320104599</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>3.43499994277954</v>
       </c>
       <c r="G1311" t="n">
-        <v>3.08491802215576</v>
+        <v>3.08491778373718</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34481,7 +34481,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1312" t="n">
-        <v>3.01756119728088</v>
+        <v>3.01756143569946</v>
       </c>
       <c r="H1312" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>3.375</v>
       </c>
       <c r="G1317" t="n">
-        <v>3.03103303909302</v>
+        <v>3.03103280067444</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34637,7 +34637,7 @@
         <v>3.375</v>
       </c>
       <c r="G1318" t="n">
-        <v>3.03103303909302</v>
+        <v>3.03103280067444</v>
       </c>
       <c r="H1318" t="s">
         <v>8</v>
@@ -34663,7 +34663,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1319" t="n">
-        <v>3.09838914871216</v>
+        <v>3.09838938713074</v>
       </c>
       <c r="H1319" t="s">
         <v>8</v>
@@ -34715,7 +34715,7 @@
         <v>3.39499998092651</v>
       </c>
       <c r="G1321" t="n">
-        <v>3.04899477958679</v>
+        <v>3.04899454116821</v>
       </c>
       <c r="H1321" t="s">
         <v>8</v>
@@ -34741,7 +34741,7 @@
         <v>3.28500008583069</v>
       </c>
       <c r="G1322" t="n">
-        <v>2.9502055644989</v>
+        <v>2.95020532608032</v>
       </c>
       <c r="H1322" t="s">
         <v>8</v>
@@ -34767,7 +34767,7 @@
         <v>3.375</v>
       </c>
       <c r="G1323" t="n">
-        <v>3.03103303909302</v>
+        <v>3.03103280067444</v>
       </c>
       <c r="H1323" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>3.375</v>
       </c>
       <c r="G1324" t="n">
-        <v>3.03103303909302</v>
+        <v>3.03103280067444</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>3.3050000667572</v>
       </c>
       <c r="G1327" t="n">
-        <v>2.96816730499268</v>
+        <v>2.9681670665741</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -34923,7 +34923,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1329" t="n">
-        <v>3.03552317619324</v>
+        <v>3.03552341461182</v>
       </c>
       <c r="H1329" t="s">
         <v>8</v>
@@ -34975,7 +34975,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1331" t="n">
-        <v>3.00858068466187</v>
+        <v>3.00858092308044</v>
       </c>
       <c r="H1331" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1332" t="n">
-        <v>3.01756119728088</v>
+        <v>3.01756143569946</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35027,7 +35027,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1333" t="n">
-        <v>3.03552317619324</v>
+        <v>3.03552341461182</v>
       </c>
       <c r="H1333" t="s">
         <v>8</v>
@@ -35131,7 +35131,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1337" t="n">
-        <v>2.79304051399231</v>
+        <v>2.79304075241089</v>
       </c>
       <c r="H1337" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1340" t="n">
-        <v>2.90081071853638</v>
+        <v>2.9008104801178</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35235,7 +35235,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1341" t="n">
-        <v>2.873868227005</v>
+        <v>2.87386846542358</v>
       </c>
       <c r="H1341" t="s">
         <v>8</v>
@@ -35261,7 +35261,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1342" t="n">
-        <v>2.873868227005</v>
+        <v>2.87386846542358</v>
       </c>
       <c r="H1342" t="s">
         <v>8</v>
@@ -35287,7 +35287,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1343" t="n">
-        <v>2.873868227005</v>
+        <v>2.87386846542358</v>
       </c>
       <c r="H1343" t="s">
         <v>8</v>
@@ -35365,7 +35365,7 @@
         <v>3.11500000953674</v>
       </c>
       <c r="G1346" t="n">
-        <v>2.79753088951111</v>
+        <v>2.79753112792969</v>
       </c>
       <c r="H1346" t="s">
         <v>8</v>
@@ -35495,7 +35495,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1351" t="n">
-        <v>3.08940815925598</v>
+        <v>3.08940839767456</v>
       </c>
       <c r="H1351" t="s">
         <v>8</v>
@@ -35521,7 +35521,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1352" t="n">
-        <v>3.08940815925598</v>
+        <v>3.08940839767456</v>
       </c>
       <c r="H1352" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1353" t="n">
-        <v>3.08940815925598</v>
+        <v>3.08940839767456</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35599,7 +35599,7 @@
         <v>3.4449999332428</v>
       </c>
       <c r="G1355" t="n">
-        <v>3.09389853477478</v>
+        <v>3.09389877319336</v>
       </c>
       <c r="H1355" t="s">
         <v>8</v>
@@ -35729,7 +35729,7 @@
         <v>3.60500001907349</v>
       </c>
       <c r="G1360" t="n">
-        <v>3.2375922203064</v>
+        <v>3.23759245872498</v>
       </c>
       <c r="H1360" t="s">
         <v>8</v>
@@ -36093,7 +36093,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1374" t="n">
-        <v>3.08940815925598</v>
+        <v>3.08940839767456</v>
       </c>
       <c r="H1374" t="s">
         <v>8</v>
@@ -36145,7 +36145,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1376" t="n">
-        <v>3.07144641876221</v>
+        <v>3.07144665718079</v>
       </c>
       <c r="H1376" t="s">
         <v>8</v>
@@ -36171,7 +36171,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1377" t="n">
-        <v>3.08940815925598</v>
+        <v>3.08940839767456</v>
       </c>
       <c r="H1377" t="s">
         <v>8</v>
@@ -36197,7 +36197,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1378" t="n">
-        <v>3.08940815925598</v>
+        <v>3.08940839767456</v>
       </c>
       <c r="H1378" t="s">
         <v>8</v>
@@ -36223,7 +36223,7 @@
         <v>3.4449999332428</v>
       </c>
       <c r="G1379" t="n">
-        <v>3.09389853477478</v>
+        <v>3.09389877319336</v>
       </c>
       <c r="H1379" t="s">
         <v>8</v>
@@ -36275,7 +36275,7 @@
         <v>3.39499998092651</v>
       </c>
       <c r="G1381" t="n">
-        <v>3.04899477958679</v>
+        <v>3.04899454116821</v>
       </c>
       <c r="H1381" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>3.43499994277954</v>
       </c>
       <c r="G1387" t="n">
-        <v>3.08491802215576</v>
+        <v>3.08491778373718</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36457,7 +36457,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1388" t="n">
-        <v>3.01756119728088</v>
+        <v>3.01756143569946</v>
       </c>
       <c r="H1388" t="s">
         <v>8</v>
@@ -36509,7 +36509,7 @@
         <v>3.33500003814697</v>
       </c>
       <c r="G1390" t="n">
-        <v>2.99510955810547</v>
+        <v>2.99510931968689</v>
       </c>
       <c r="H1390" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>3.28500008583069</v>
       </c>
       <c r="G1393" t="n">
-        <v>2.9502055644989</v>
+        <v>2.95020532608032</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36743,7 +36743,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1399" t="n">
-        <v>3.25106310844421</v>
+        <v>3.25106334686279</v>
       </c>
       <c r="H1399" t="s">
         <v>8</v>
@@ -36795,7 +36795,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1401" t="n">
-        <v>3.22412061691284</v>
+        <v>3.22412085533142</v>
       </c>
       <c r="H1401" t="s">
         <v>8</v>
@@ -36847,7 +36847,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1403" t="n">
-        <v>3.00858068466187</v>
+        <v>3.00858092308044</v>
       </c>
       <c r="H1403" t="s">
         <v>8</v>
@@ -36899,7 +36899,7 @@
         <v>3.39499998092651</v>
       </c>
       <c r="G1405" t="n">
-        <v>3.04899477958679</v>
+        <v>3.04899454116821</v>
       </c>
       <c r="H1405" t="s">
         <v>8</v>
@@ -36925,7 +36925,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1406" t="n">
-        <v>3.00858068466187</v>
+        <v>3.00858092308044</v>
       </c>
       <c r="H1406" t="s">
         <v>8</v>
@@ -36977,7 +36977,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1408" t="n">
-        <v>3.00858068466187</v>
+        <v>3.00858092308044</v>
       </c>
       <c r="H1408" t="s">
         <v>8</v>
@@ -37081,7 +37081,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1412" t="n">
-        <v>3.00858068466187</v>
+        <v>3.00858092308044</v>
       </c>
       <c r="H1412" t="s">
         <v>8</v>
@@ -37107,7 +37107,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1413" t="n">
-        <v>3.01756119728088</v>
+        <v>3.01756143569946</v>
       </c>
       <c r="H1413" t="s">
         <v>8</v>
@@ -37185,7 +37185,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1416" t="n">
-        <v>3.00858068466187</v>
+        <v>3.00858092308044</v>
       </c>
       <c r="H1416" t="s">
         <v>8</v>
@@ -37211,7 +37211,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1417" t="n">
-        <v>3.01756119728088</v>
+        <v>3.01756143569946</v>
       </c>
       <c r="H1417" t="s">
         <v>8</v>
@@ -37289,7 +37289,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1420" t="n">
-        <v>2.9726574420929</v>
+        <v>2.97265720367432</v>
       </c>
       <c r="H1420" t="s">
         <v>8</v>
@@ -37341,7 +37341,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1422" t="n">
-        <v>2.9726574420929</v>
+        <v>2.97265720367432</v>
       </c>
       <c r="H1422" t="s">
         <v>8</v>
@@ -37367,7 +37367,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1423" t="n">
-        <v>2.96367645263672</v>
+        <v>2.96367692947388</v>
       </c>
       <c r="H1423" t="s">
         <v>8</v>
@@ -37445,7 +37445,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1426" t="n">
-        <v>2.9726574420929</v>
+        <v>2.97265720367432</v>
       </c>
       <c r="H1426" t="s">
         <v>8</v>
@@ -37575,7 +37575,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1431" t="n">
-        <v>3.00858068466187</v>
+        <v>3.00858092308044</v>
       </c>
       <c r="H1431" t="s">
         <v>8</v>
@@ -37601,7 +37601,7 @@
         <v>3.33500003814697</v>
       </c>
       <c r="G1432" t="n">
-        <v>2.99510955810547</v>
+        <v>2.99510931968689</v>
       </c>
       <c r="H1432" t="s">
         <v>8</v>
@@ -37679,7 +37679,7 @@
         <v>3.3050000667572</v>
       </c>
       <c r="G1435" t="n">
-        <v>2.96816730499268</v>
+        <v>2.9681670665741</v>
       </c>
       <c r="H1435" t="s">
         <v>8</v>
@@ -37835,7 +37835,7 @@
         <v>3.28500008583069</v>
       </c>
       <c r="G1441" t="n">
-        <v>2.9502055644989</v>
+        <v>2.95020532608032</v>
       </c>
       <c r="H1441" t="s">
         <v>8</v>
@@ -38043,7 +38043,7 @@
         <v>3.22499990463257</v>
       </c>
       <c r="G1449" t="n">
-        <v>2.89632034301758</v>
+        <v>2.896320104599</v>
       </c>
       <c r="H1449" t="s">
         <v>8</v>
@@ -38069,7 +38069,7 @@
         <v>3.22499990463257</v>
       </c>
       <c r="G1450" t="n">
-        <v>2.89632034301758</v>
+        <v>2.896320104599</v>
       </c>
       <c r="H1450" t="s">
         <v>8</v>
@@ -38121,7 +38121,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1452" t="n">
-        <v>2.8828489780426</v>
+        <v>2.88284921646118</v>
       </c>
       <c r="H1452" t="s">
         <v>8</v>
@@ -38147,7 +38147,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1453" t="n">
-        <v>2.8828489780426</v>
+        <v>2.88284921646118</v>
       </c>
       <c r="H1453" t="s">
         <v>8</v>
@@ -38173,7 +38173,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1454" t="n">
-        <v>2.82896399497986</v>
+        <v>2.82896423339844</v>
       </c>
       <c r="H1454" t="s">
         <v>8</v>
@@ -38225,7 +38225,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G1456" t="n">
-        <v>2.91428208351135</v>
+        <v>2.91428160667419</v>
       </c>
       <c r="H1456" t="s">
         <v>8</v>
@@ -38251,7 +38251,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1457" t="n">
-        <v>2.8828489780426</v>
+        <v>2.88284921646118</v>
       </c>
       <c r="H1457" t="s">
         <v>8</v>
@@ -38303,7 +38303,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1459" t="n">
-        <v>3.08940815925598</v>
+        <v>3.08940839767456</v>
       </c>
       <c r="H1459" t="s">
         <v>8</v>
@@ -38355,7 +38355,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1461" t="n">
-        <v>3.09838914871216</v>
+        <v>3.09838938713074</v>
       </c>
       <c r="H1461" t="s">
         <v>8</v>
@@ -38433,7 +38433,7 @@
         <v>3.375</v>
       </c>
       <c r="G1464" t="n">
-        <v>3.03103303909302</v>
+        <v>3.03103280067444</v>
       </c>
       <c r="H1464" t="s">
         <v>8</v>
@@ -38485,7 +38485,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1466" t="n">
-        <v>2.96367645263672</v>
+        <v>2.96367692947388</v>
       </c>
       <c r="H1466" t="s">
         <v>8</v>
@@ -38693,7 +38693,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1474" t="n">
-        <v>3.08940815925598</v>
+        <v>3.08940839767456</v>
       </c>
       <c r="H1474" t="s">
         <v>8</v>
@@ -38719,7 +38719,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1475" t="n">
-        <v>3.09838914871216</v>
+        <v>3.09838938713074</v>
       </c>
       <c r="H1475" t="s">
         <v>8</v>
@@ -38927,7 +38927,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1483" t="n">
-        <v>3.22412061691284</v>
+        <v>3.22412085533142</v>
       </c>
       <c r="H1483" t="s">
         <v>8</v>
@@ -39187,7 +39187,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1493" t="n">
-        <v>3.24208235740662</v>
+        <v>3.2420825958252</v>
       </c>
       <c r="H1493" t="s">
         <v>8</v>
@@ -39239,7 +39239,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1495" t="n">
-        <v>3.24208235740662</v>
+        <v>3.2420825958252</v>
       </c>
       <c r="H1495" t="s">
         <v>8</v>
@@ -39265,7 +39265,7 @@
         <v>3.51500010490417</v>
       </c>
       <c r="G1496" t="n">
-        <v>3.15676498413086</v>
+        <v>3.15676474571228</v>
       </c>
       <c r="H1496" t="s">
         <v>8</v>
@@ -39291,7 +39291,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1497" t="n">
-        <v>3.10736989974976</v>
+        <v>3.10737013816833</v>
       </c>
       <c r="H1497" t="s">
         <v>8</v>
@@ -39343,7 +39343,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G1499" t="n">
-        <v>3.1477837562561</v>
+        <v>3.14778399467468</v>
       </c>
       <c r="H1499" t="s">
         <v>8</v>
@@ -39369,7 +39369,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1500" t="n">
-        <v>3.09838914871216</v>
+        <v>3.09838938713074</v>
       </c>
       <c r="H1500" t="s">
         <v>8</v>
@@ -39551,7 +39551,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1507" t="n">
-        <v>3.08940815925598</v>
+        <v>3.08940839767456</v>
       </c>
       <c r="H1507" t="s">
         <v>8</v>
@@ -39629,7 +39629,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1510" t="n">
-        <v>3.10736989974976</v>
+        <v>3.10737013816833</v>
       </c>
       <c r="H1510" t="s">
         <v>8</v>
@@ -39655,7 +39655,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1511" t="n">
-        <v>3.10736989974976</v>
+        <v>3.10737013816833</v>
       </c>
       <c r="H1511" t="s">
         <v>8</v>
@@ -39733,7 +39733,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G1514" t="n">
-        <v>3.1477837562561</v>
+        <v>3.14778399467468</v>
       </c>
       <c r="H1514" t="s">
         <v>8</v>
@@ -39759,7 +39759,7 @@
         <v>3.51500010490417</v>
       </c>
       <c r="G1515" t="n">
-        <v>3.15676498413086</v>
+        <v>3.15676474571228</v>
       </c>
       <c r="H1515" t="s">
         <v>8</v>
@@ -39811,7 +39811,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1517" t="n">
-        <v>3.27800583839417</v>
+        <v>3.27800607681274</v>
       </c>
       <c r="H1517" t="s">
         <v>8</v>
@@ -39837,7 +39837,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1518" t="n">
-        <v>3.27800583839417</v>
+        <v>3.27800607681274</v>
       </c>
       <c r="H1518" t="s">
         <v>8</v>
@@ -39889,7 +39889,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1520" t="n">
-        <v>3.25106310844421</v>
+        <v>3.25106334686279</v>
       </c>
       <c r="H1520" t="s">
         <v>8</v>
@@ -39915,7 +39915,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1521" t="n">
-        <v>3.27800583839417</v>
+        <v>3.27800607681274</v>
       </c>
       <c r="H1521" t="s">
         <v>8</v>
@@ -39941,7 +39941,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1522" t="n">
-        <v>3.27800583839417</v>
+        <v>3.27800607681274</v>
       </c>
       <c r="H1522" t="s">
         <v>8</v>
@@ -39967,7 +39967,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1523" t="n">
-        <v>3.25106310844421</v>
+        <v>3.25106334686279</v>
       </c>
       <c r="H1523" t="s">
         <v>8</v>
@@ -40045,7 +40045,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G1526" t="n">
-        <v>3.27351546287537</v>
+        <v>3.27351570129395</v>
       </c>
       <c r="H1526" t="s">
         <v>8</v>
@@ -40097,7 +40097,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1528" t="n">
-        <v>3.27800583839417</v>
+        <v>3.27800607681274</v>
       </c>
       <c r="H1528" t="s">
         <v>8</v>
@@ -40227,7 +40227,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G1533" t="n">
-        <v>3.1477837562561</v>
+        <v>3.14778399467468</v>
       </c>
       <c r="H1533" t="s">
         <v>8</v>
@@ -40253,7 +40253,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G1534" t="n">
-        <v>3.1477837562561</v>
+        <v>3.14778399467468</v>
       </c>
       <c r="H1534" t="s">
         <v>8</v>
@@ -40305,7 +40305,7 @@
         <v>3.42499995231628</v>
       </c>
       <c r="G1536" t="n">
-        <v>3.07593703269958</v>
+        <v>3.07593679428101</v>
       </c>
       <c r="H1536" t="s">
         <v>8</v>
@@ -40331,7 +40331,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1537" t="n">
-        <v>3.09838914871216</v>
+        <v>3.09838938713074</v>
       </c>
       <c r="H1537" t="s">
         <v>8</v>
@@ -40357,7 +40357,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1538" t="n">
-        <v>3.10736989974976</v>
+        <v>3.10737013816833</v>
       </c>
       <c r="H1538" t="s">
         <v>8</v>
@@ -40383,7 +40383,7 @@
         <v>3.4449999332428</v>
       </c>
       <c r="G1539" t="n">
-        <v>3.09389853477478</v>
+        <v>3.09389877319336</v>
       </c>
       <c r="H1539" t="s">
         <v>8</v>
@@ -40409,7 +40409,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1540" t="n">
-        <v>3.07144641876221</v>
+        <v>3.07144665718079</v>
       </c>
       <c r="H1540" t="s">
         <v>8</v>
@@ -40435,7 +40435,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1541" t="n">
-        <v>3.08940815925598</v>
+        <v>3.08940839767456</v>
       </c>
       <c r="H1541" t="s">
         <v>8</v>
@@ -40461,7 +40461,7 @@
         <v>3.375</v>
       </c>
       <c r="G1542" t="n">
-        <v>3.03103303909302</v>
+        <v>3.03103280067444</v>
       </c>
       <c r="H1542" t="s">
         <v>8</v>
@@ -40487,7 +40487,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1543" t="n">
-        <v>3.00858068466187</v>
+        <v>3.00858092308044</v>
       </c>
       <c r="H1543" t="s">
         <v>8</v>
@@ -40513,7 +40513,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1544" t="n">
-        <v>3.07144641876221</v>
+        <v>3.07144665718079</v>
       </c>
       <c r="H1544" t="s">
         <v>8</v>
@@ -40539,7 +40539,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1545" t="n">
-        <v>3.07144641876221</v>
+        <v>3.07144665718079</v>
       </c>
       <c r="H1545" t="s">
         <v>8</v>
@@ -40565,7 +40565,7 @@
         <v>3.39499998092651</v>
       </c>
       <c r="G1546" t="n">
-        <v>3.04899477958679</v>
+        <v>3.04899454116821</v>
       </c>
       <c r="H1546" t="s">
         <v>8</v>
@@ -40799,7 +40799,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1555" t="n">
-        <v>3.01756119728088</v>
+        <v>3.01756143569946</v>
       </c>
       <c r="H1555" t="s">
         <v>8</v>
@@ -40825,7 +40825,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1556" t="n">
-        <v>3.00858068466187</v>
+        <v>3.00858092308044</v>
       </c>
       <c r="H1556" t="s">
         <v>8</v>
@@ -40903,7 +40903,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1559" t="n">
-        <v>3.03552317619324</v>
+        <v>3.03552341461182</v>
       </c>
       <c r="H1559" t="s">
         <v>8</v>
@@ -41059,7 +41059,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1565" t="n">
-        <v>2.74813652038574</v>
+        <v>2.74813675880432</v>
       </c>
       <c r="H1565" t="s">
         <v>8</v>
@@ -41085,7 +41085,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1566" t="n">
-        <v>2.76609802246094</v>
+        <v>2.76609778404236</v>
       </c>
       <c r="H1566" t="s">
         <v>8</v>
@@ -41111,7 +41111,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G1567" t="n">
-        <v>2.72568416595459</v>
+        <v>2.72568440437317</v>
       </c>
       <c r="H1567" t="s">
         <v>8</v>
@@ -41189,7 +41189,7 @@
         <v>2.95499992370605</v>
       </c>
       <c r="G1570" t="n">
-        <v>2.65383768081665</v>
+        <v>2.65383791923523</v>
       </c>
       <c r="H1570" t="s">
         <v>8</v>
@@ -41215,7 +41215,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1571" t="n">
-        <v>2.54157733917236</v>
+        <v>2.54157710075378</v>
       </c>
       <c r="H1571" t="s">
         <v>8</v>
@@ -41241,7 +41241,7 @@
         <v>2.88499999046326</v>
       </c>
       <c r="G1572" t="n">
-        <v>2.59097146987915</v>
+        <v>2.59097170829773</v>
       </c>
       <c r="H1572" t="s">
         <v>8</v>
@@ -41345,7 +41345,7 @@
         <v>2.9449999332428</v>
       </c>
       <c r="G1576" t="n">
-        <v>2.64485645294189</v>
+        <v>2.64485669136047</v>
       </c>
       <c r="H1576" t="s">
         <v>8</v>
@@ -41449,7 +41449,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1580" t="n">
-        <v>2.76609802246094</v>
+        <v>2.76609778404236</v>
       </c>
       <c r="H1580" t="s">
         <v>8</v>
@@ -41527,7 +41527,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1583" t="n">
-        <v>2.82896399497986</v>
+        <v>2.82896423339844</v>
       </c>
       <c r="H1583" t="s">
         <v>8</v>
@@ -41735,7 +41735,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1591" t="n">
-        <v>2.8828489780426</v>
+        <v>2.88284921646118</v>
       </c>
       <c r="H1591" t="s">
         <v>8</v>
@@ -41787,7 +41787,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1593" t="n">
-        <v>2.82896399497986</v>
+        <v>2.82896423339844</v>
       </c>
       <c r="H1593" t="s">
         <v>8</v>
@@ -41839,7 +41839,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1595" t="n">
-        <v>2.80202126502991</v>
+        <v>2.80202150344849</v>
       </c>
       <c r="H1595" t="s">
         <v>8</v>
@@ -41865,7 +41865,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1596" t="n">
-        <v>2.873868227005</v>
+        <v>2.87386846542358</v>
       </c>
       <c r="H1596" t="s">
         <v>8</v>
@@ -41969,7 +41969,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1600" t="n">
-        <v>2.96367645263672</v>
+        <v>2.96367692947388</v>
       </c>
       <c r="H1600" t="s">
         <v>8</v>
@@ -42021,7 +42021,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1602" t="n">
-        <v>3.01756119728088</v>
+        <v>3.01756143569946</v>
       </c>
       <c r="H1602" t="s">
         <v>8</v>
@@ -42099,7 +42099,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1605" t="n">
-        <v>3.03552317619324</v>
+        <v>3.03552341461182</v>
       </c>
       <c r="H1605" t="s">
         <v>8</v>
@@ -42125,7 +42125,7 @@
         <v>3.39499998092651</v>
       </c>
       <c r="G1606" t="n">
-        <v>3.04899477958679</v>
+        <v>3.04899454116821</v>
       </c>
       <c r="H1606" t="s">
         <v>8</v>
@@ -42151,7 +42151,7 @@
         <v>3.39499998092651</v>
       </c>
       <c r="G1607" t="n">
-        <v>3.04899477958679</v>
+        <v>3.04899454116821</v>
       </c>
       <c r="H1607" t="s">
         <v>8</v>
@@ -42229,7 +42229,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1610" t="n">
-        <v>3.01756119728088</v>
+        <v>3.01756143569946</v>
       </c>
       <c r="H1610" t="s">
         <v>8</v>
@@ -42333,7 +42333,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1614" t="n">
-        <v>2.74813652038574</v>
+        <v>2.74813675880432</v>
       </c>
       <c r="H1614" t="s">
         <v>8</v>
@@ -42359,7 +42359,7 @@
         <v>2.95499992370605</v>
       </c>
       <c r="G1615" t="n">
-        <v>2.65383768081665</v>
+        <v>2.65383791923523</v>
       </c>
       <c r="H1615" t="s">
         <v>8</v>
@@ -42541,7 +42541,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G1622" t="n">
-        <v>2.91428208351135</v>
+        <v>2.91428160667419</v>
       </c>
       <c r="H1622" t="s">
         <v>8</v>
@@ -42593,7 +42593,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1624" t="n">
-        <v>2.873868227005</v>
+        <v>2.87386846542358</v>
       </c>
       <c r="H1624" t="s">
         <v>8</v>
@@ -42619,7 +42619,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1625" t="n">
-        <v>2.8828489780426</v>
+        <v>2.88284921646118</v>
       </c>
       <c r="H1625" t="s">
         <v>8</v>
@@ -42645,7 +42645,7 @@
         <v>3.11500000953674</v>
       </c>
       <c r="G1626" t="n">
-        <v>2.79753088951111</v>
+        <v>2.79753112792969</v>
       </c>
       <c r="H1626" t="s">
         <v>8</v>
@@ -42775,7 +42775,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1631" t="n">
-        <v>2.74813652038574</v>
+        <v>2.74813675880432</v>
       </c>
       <c r="H1631" t="s">
         <v>8</v>
@@ -42801,7 +42801,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G1632" t="n">
-        <v>2.72568416595459</v>
+        <v>2.72568440437317</v>
       </c>
       <c r="H1632" t="s">
         <v>8</v>
@@ -42827,7 +42827,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G1633" t="n">
-        <v>2.74364590644836</v>
+        <v>2.74364614486694</v>
       </c>
       <c r="H1633" t="s">
         <v>8</v>
@@ -42853,7 +42853,7 @@
         <v>3.02500009536743</v>
       </c>
       <c r="G1634" t="n">
-        <v>2.71670341491699</v>
+        <v>2.71670365333557</v>
       </c>
       <c r="H1634" t="s">
         <v>8</v>
@@ -42879,7 +42879,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1635" t="n">
-        <v>2.79304051399231</v>
+        <v>2.79304075241089</v>
       </c>
       <c r="H1635" t="s">
         <v>8</v>
@@ -42931,7 +42931,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1637" t="n">
-        <v>2.873868227005</v>
+        <v>2.87386846542358</v>
       </c>
       <c r="H1637" t="s">
         <v>8</v>
@@ -42983,7 +42983,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1639" t="n">
-        <v>2.68527054786682</v>
+        <v>2.68527030944824</v>
       </c>
       <c r="H1639" t="s">
         <v>8</v>
@@ -43009,7 +43009,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1640" t="n">
-        <v>2.64036655426025</v>
+        <v>2.64036631584167</v>
       </c>
       <c r="H1640" t="s">
         <v>8</v>
@@ -43061,7 +43061,7 @@
         <v>2.98499989509583</v>
       </c>
       <c r="G1642" t="n">
-        <v>2.68077993392944</v>
+        <v>2.68078017234802</v>
       </c>
       <c r="H1642" t="s">
         <v>8</v>
@@ -43087,7 +43087,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1643" t="n">
-        <v>2.59546256065369</v>
+        <v>2.59546232223511</v>
       </c>
       <c r="H1643" t="s">
         <v>8</v>
@@ -43165,7 +43165,7 @@
         <v>2.98499989509583</v>
       </c>
       <c r="G1646" t="n">
-        <v>2.68077993392944</v>
+        <v>2.68078017234802</v>
       </c>
       <c r="H1646" t="s">
         <v>8</v>
@@ -43217,7 +43217,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1648" t="n">
-        <v>2.55953884124756</v>
+        <v>2.55953860282898</v>
       </c>
       <c r="H1648" t="s">
         <v>8</v>
@@ -43295,7 +43295,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G1651" t="n">
-        <v>2.52810597419739</v>
+        <v>2.52810621261597</v>
       </c>
       <c r="H1651" t="s">
         <v>8</v>
@@ -43347,7 +43347,7 @@
         <v>2.75</v>
       </c>
       <c r="G1653" t="n">
-        <v>2.46973061561584</v>
+        <v>2.46973037719727</v>
       </c>
       <c r="H1653" t="s">
         <v>8</v>
@@ -43451,7 +43451,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1657" t="n">
-        <v>2.43380737304688</v>
+        <v>2.4338071346283</v>
       </c>
       <c r="H1657" t="s">
         <v>8</v>
@@ -43477,7 +43477,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G1658" t="n">
-        <v>2.52810597419739</v>
+        <v>2.52810621261597</v>
       </c>
       <c r="H1658" t="s">
         <v>8</v>
@@ -43555,7 +43555,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1661" t="n">
-        <v>2.56851983070374</v>
+        <v>2.56851959228516</v>
       </c>
       <c r="H1661" t="s">
         <v>8</v>
@@ -43581,7 +43581,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1662" t="n">
-        <v>2.53259611129761</v>
+        <v>2.53259634971619</v>
       </c>
       <c r="H1662" t="s">
         <v>8</v>
@@ -43607,7 +43607,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1663" t="n">
-        <v>2.53259611129761</v>
+        <v>2.53259634971619</v>
       </c>
       <c r="H1663" t="s">
         <v>8</v>
@@ -43633,7 +43633,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1664" t="n">
-        <v>2.53259611129761</v>
+        <v>2.53259634971619</v>
       </c>
       <c r="H1664" t="s">
         <v>8</v>
@@ -43685,7 +43685,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1666" t="n">
-        <v>2.59546256065369</v>
+        <v>2.59546232223511</v>
       </c>
       <c r="H1666" t="s">
         <v>8</v>
@@ -43815,7 +43815,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1671" t="n">
-        <v>2.53259611129761</v>
+        <v>2.53259634971619</v>
       </c>
       <c r="H1671" t="s">
         <v>8</v>
@@ -43867,7 +43867,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1673" t="n">
-        <v>2.51463484764099</v>
+        <v>2.51463460922241</v>
       </c>
       <c r="H1673" t="s">
         <v>8</v>
@@ -43919,7 +43919,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G1675" t="n">
-        <v>2.54606771469116</v>
+        <v>2.54606747627258</v>
       </c>
       <c r="H1675" t="s">
         <v>8</v>
@@ -43945,7 +43945,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1676" t="n">
-        <v>2.60444331169128</v>
+        <v>2.60444307327271</v>
       </c>
       <c r="H1676" t="s">
         <v>8</v>
@@ -43971,7 +43971,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1677" t="n">
-        <v>2.60444331169128</v>
+        <v>2.60444307327271</v>
       </c>
       <c r="H1677" t="s">
         <v>8</v>
@@ -44023,7 +44023,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1679" t="n">
-        <v>2.60444331169128</v>
+        <v>2.60444307327271</v>
       </c>
       <c r="H1679" t="s">
         <v>8</v>
@@ -44049,7 +44049,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1680" t="n">
-        <v>2.55953884124756</v>
+        <v>2.55953860282898</v>
       </c>
       <c r="H1680" t="s">
         <v>8</v>
@@ -44075,7 +44075,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1681" t="n">
-        <v>2.55953884124756</v>
+        <v>2.55953860282898</v>
       </c>
       <c r="H1681" t="s">
         <v>8</v>
@@ -44101,7 +44101,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1682" t="n">
-        <v>2.56851983070374</v>
+        <v>2.56851959228516</v>
       </c>
       <c r="H1682" t="s">
         <v>8</v>
@@ -44153,7 +44153,7 @@
         <v>2.88499999046326</v>
       </c>
       <c r="G1684" t="n">
-        <v>2.59097146987915</v>
+        <v>2.59097170829773</v>
       </c>
       <c r="H1684" t="s">
         <v>8</v>
@@ -44179,7 +44179,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1685" t="n">
-        <v>2.60444331169128</v>
+        <v>2.60444307327271</v>
       </c>
       <c r="H1685" t="s">
         <v>8</v>
@@ -44205,7 +44205,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1686" t="n">
-        <v>2.64934730529785</v>
+        <v>2.64934706687927</v>
       </c>
       <c r="H1686" t="s">
         <v>8</v>
@@ -44231,7 +44231,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1687" t="n">
-        <v>2.76609802246094</v>
+        <v>2.76609778404236</v>
       </c>
       <c r="H1687" t="s">
         <v>8</v>
@@ -44335,7 +44335,7 @@
         <v>3</v>
       </c>
       <c r="G1691" t="n">
-        <v>2.694251537323</v>
+        <v>2.69425129890442</v>
       </c>
       <c r="H1691" t="s">
         <v>8</v>
@@ -44361,7 +44361,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1692" t="n">
-        <v>2.66730880737305</v>
+        <v>2.66730904579163</v>
       </c>
       <c r="H1692" t="s">
         <v>8</v>
@@ -44387,7 +44387,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G1693" t="n">
-        <v>2.74364590644836</v>
+        <v>2.74364614486694</v>
       </c>
       <c r="H1693" t="s">
         <v>8</v>
@@ -44413,7 +44413,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1694" t="n">
-        <v>2.73017501831055</v>
+        <v>2.73017477989197</v>
       </c>
       <c r="H1694" t="s">
         <v>8</v>
@@ -44439,7 +44439,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G1695" t="n">
-        <v>2.74364590644836</v>
+        <v>2.74364614486694</v>
       </c>
       <c r="H1695" t="s">
         <v>8</v>
@@ -44465,7 +44465,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1696" t="n">
-        <v>2.68527054786682</v>
+        <v>2.68527030944824</v>
       </c>
       <c r="H1696" t="s">
         <v>8</v>
@@ -44491,7 +44491,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1697" t="n">
-        <v>2.60444331169128</v>
+        <v>2.60444307327271</v>
       </c>
       <c r="H1697" t="s">
         <v>8</v>
@@ -44569,7 +44569,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1700" t="n">
-        <v>2.59546256065369</v>
+        <v>2.59546232223511</v>
       </c>
       <c r="H1700" t="s">
         <v>8</v>
@@ -44673,7 +44673,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1704" t="n">
-        <v>2.55953884124756</v>
+        <v>2.55953860282898</v>
       </c>
       <c r="H1704" t="s">
         <v>8</v>
@@ -44751,7 +44751,7 @@
         <v>2.75</v>
       </c>
       <c r="G1707" t="n">
-        <v>2.46973061561584</v>
+        <v>2.46973037719727</v>
       </c>
       <c r="H1707" t="s">
         <v>8</v>
@@ -44829,7 +44829,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1710" t="n">
-        <v>2.37992215156555</v>
+        <v>2.37992238998413</v>
       </c>
       <c r="H1710" t="s">
         <v>8</v>
@@ -44855,7 +44855,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1711" t="n">
-        <v>2.37094116210938</v>
+        <v>2.37094140052795</v>
       </c>
       <c r="H1711" t="s">
         <v>8</v>
@@ -45037,7 +45037,7 @@
         <v>2.40499997138977</v>
       </c>
       <c r="G1718" t="n">
-        <v>2.1598916053772</v>
+        <v>2.15989136695862</v>
       </c>
       <c r="H1718" t="s">
         <v>8</v>
@@ -71664,6 +71664,32 @@
         <v>1.11500000953674</v>
       </c>
       <c r="H2742" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2743">
+      <c r="A2743" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B2743" t="n">
+        <v>7400</v>
+      </c>
+      <c r="C2743" t="n">
+        <v>1.10500001907349</v>
+      </c>
+      <c r="D2743" t="n">
+        <v>1.09500002861023</v>
+      </c>
+      <c r="E2743" t="n">
+        <v>1.10000002384186</v>
+      </c>
+      <c r="F2743" t="n">
+        <v>1.10500001907349</v>
+      </c>
+      <c r="G2743" t="n">
+        <v>1.10500001907349</v>
+      </c>
+      <c r="H2743" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/ELC.MI.xlsx
+++ b/data/ELC.MI.xlsx
@@ -421,7 +421,7 @@
         <v>1.93700003623962</v>
       </c>
       <c r="G2" t="n">
-        <v>1.73070454597473</v>
+        <v>1.73070466518402</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G3" t="n">
-        <v>1.73338508605957</v>
+        <v>1.73338520526886</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G4" t="n">
-        <v>1.72445023059845</v>
+        <v>1.72445011138916</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G6" t="n">
-        <v>1.69764518737793</v>
+        <v>1.69764530658722</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G9" t="n">
-        <v>1.69764518737793</v>
+        <v>1.69764530658722</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>1.81900000572205</v>
       </c>
       <c r="G10" t="n">
-        <v>1.62527191638947</v>
+        <v>1.62527179718018</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G11" t="n">
-        <v>1.59936034679413</v>
+        <v>1.59936046600342</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>1.65199995040894</v>
       </c>
       <c r="G12" t="n">
-        <v>1.47605776786804</v>
+        <v>1.47605764865875</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>1.71800005435944</v>
       </c>
       <c r="G15" t="n">
-        <v>1.53502881526947</v>
+        <v>1.53502869606018</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>1.625</v>
       </c>
       <c r="G18" t="n">
-        <v>1.45193326473236</v>
+        <v>1.45193350315094</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G19" t="n">
-        <v>1.46533596515656</v>
+        <v>1.46533572673798</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>1.65100002288818</v>
       </c>
       <c r="G21" t="n">
-        <v>1.47516429424286</v>
+        <v>1.47516441345215</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G23" t="n">
-        <v>1.39832377433777</v>
+        <v>1.39832353591919</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>1.54499995708466</v>
       </c>
       <c r="G24" t="n">
-        <v>1.38045358657837</v>
+        <v>1.38045346736908</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>1.51699995994568</v>
       </c>
       <c r="G25" t="n">
-        <v>1.35543572902679</v>
+        <v>1.3554356098175</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>1.40199995040894</v>
       </c>
       <c r="G27" t="n">
-        <v>1.25268340110779</v>
+        <v>1.25268352031708</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>1.63199996948242</v>
       </c>
       <c r="G32" t="n">
-        <v>1.45818781852722</v>
+        <v>1.45818793773651</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>1.6710000038147</v>
       </c>
       <c r="G33" t="n">
-        <v>1.49303436279297</v>
+        <v>1.49303424358368</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>1.65900003910065</v>
       </c>
       <c r="G34" t="n">
-        <v>1.48231244087219</v>
+        <v>1.4823123216629</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G35" t="n">
-        <v>1.51001071929932</v>
+        <v>1.51001060009003</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>1.75399994850159</v>
       </c>
       <c r="G36" t="n">
-        <v>1.56719470024109</v>
+        <v>1.56719446182251</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G37" t="n">
-        <v>1.57255566120148</v>
+        <v>1.57255554199219</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>1.74699997901917</v>
       </c>
       <c r="G39" t="n">
-        <v>1.56094014644623</v>
+        <v>1.56094026565552</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G42" t="n">
-        <v>1.58149063587189</v>
+        <v>1.5814905166626</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G43" t="n">
-        <v>1.57255566120148</v>
+        <v>1.57255554199219</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G44" t="n">
-        <v>1.51894569396973</v>
+        <v>1.51894581317902</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G45" t="n">
-        <v>1.58149063587189</v>
+        <v>1.5814905166626</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>1.77300000190735</v>
       </c>
       <c r="G46" t="n">
-        <v>1.58417105674744</v>
+        <v>1.58417093753815</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G50" t="n">
-        <v>1.58149063587189</v>
+        <v>1.5814905166626</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>1.89300000667572</v>
       </c>
       <c r="G53" t="n">
-        <v>1.69139087200165</v>
+        <v>1.69139075279236</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G55" t="n">
-        <v>1.6797753572464</v>
+        <v>1.67977523803711</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>1.90799999237061</v>
       </c>
       <c r="G56" t="n">
-        <v>1.70479309558868</v>
+        <v>1.70479321479797</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G57" t="n">
-        <v>1.72445023059845</v>
+        <v>1.72445011138916</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G58" t="n">
-        <v>1.76912486553192</v>
+        <v>1.76912498474121</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>1.95200002193451</v>
       </c>
       <c r="G59" t="n">
-        <v>1.74410712718964</v>
+        <v>1.74410700798035</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>1.93599998950958</v>
       </c>
       <c r="G60" t="n">
-        <v>1.72981119155884</v>
+        <v>1.72981107234955</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>1.94599997997284</v>
       </c>
       <c r="G61" t="n">
-        <v>1.73874616622925</v>
+        <v>1.73874604701996</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G63" t="n">
-        <v>1.75125515460968</v>
+        <v>1.75125503540039</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>1.96399998664856</v>
       </c>
       <c r="G64" t="n">
-        <v>1.75482904911041</v>
+        <v>1.75482892990112</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G65" t="n">
-        <v>1.72445023059845</v>
+        <v>1.72445011138916</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G66" t="n">
-        <v>1.68871021270752</v>
+        <v>1.68871033191681</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>1.87899994850159</v>
       </c>
       <c r="G67" t="n">
-        <v>1.67888152599335</v>
+        <v>1.67888176441193</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G68" t="n">
-        <v>1.69317770004272</v>
+        <v>1.69317758083344</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G69" t="n">
-        <v>1.69764518737793</v>
+        <v>1.69764530658722</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G70" t="n">
-        <v>1.69764518737793</v>
+        <v>1.69764530658722</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>1.88100004196167</v>
       </c>
       <c r="G72" t="n">
-        <v>1.68066883087158</v>
+        <v>1.68066871166229</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G73" t="n">
-        <v>1.69764518737793</v>
+        <v>1.69764530658722</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G75" t="n">
-        <v>1.71998274326324</v>
+        <v>1.71998262405396</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G78" t="n">
-        <v>1.71998274326324</v>
+        <v>1.71998262405396</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G80" t="n">
-        <v>1.71998274326324</v>
+        <v>1.71998262405396</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>1.89900004863739</v>
       </c>
       <c r="G81" t="n">
-        <v>1.69675183296204</v>
+        <v>1.69675159454346</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>1.92700004577637</v>
       </c>
       <c r="G82" t="n">
-        <v>1.72176957130432</v>
+        <v>1.72176969051361</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G84" t="n">
-        <v>1.74231994152069</v>
+        <v>1.74232006072998</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G88" t="n">
-        <v>1.69764518737793</v>
+        <v>1.69764530658722</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>1.84800004959106</v>
       </c>
       <c r="G90" t="n">
-        <v>1.6511834859848</v>
+        <v>1.65118336677551</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>1.85199999809265</v>
       </c>
       <c r="G93" t="n">
-        <v>1.65475726127625</v>
+        <v>1.65475738048553</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>1.88699996471405</v>
       </c>
       <c r="G94" t="n">
-        <v>1.68602967262268</v>
+        <v>1.68602979183197</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G95" t="n">
-        <v>1.68871021270752</v>
+        <v>1.68871033191681</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G96" t="n">
-        <v>1.68871021270752</v>
+        <v>1.68871033191681</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>1.91799998283386</v>
       </c>
       <c r="G98" t="n">
-        <v>1.71372807025909</v>
+        <v>1.71372818946838</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>1.9190000295639</v>
       </c>
       <c r="G99" t="n">
-        <v>1.71462166309357</v>
+        <v>1.71462178230286</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>1.9190000295639</v>
       </c>
       <c r="G101" t="n">
-        <v>1.72342276573181</v>
+        <v>1.7234228849411</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>1.93799996376038</v>
       </c>
       <c r="G104" t="n">
-        <v>1.7404865026474</v>
+        <v>1.74048638343811</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>1.9210000038147</v>
       </c>
       <c r="G105" t="n">
-        <v>1.72521901130676</v>
+        <v>1.72521889209747</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G107" t="n">
-        <v>1.72432100772858</v>
+        <v>1.72432088851929</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>1.92900002002716</v>
       </c>
       <c r="G108" t="n">
-        <v>1.73240375518799</v>
+        <v>1.7324036359787</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G110" t="n">
-        <v>1.72432100772858</v>
+        <v>1.72432088851929</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G111" t="n">
-        <v>1.72432100772858</v>
+        <v>1.72432088851929</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>1.85199999809265</v>
       </c>
       <c r="G115" t="n">
-        <v>1.66325116157532</v>
+        <v>1.66325128078461</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G119" t="n">
-        <v>1.60757005214691</v>
+        <v>1.60756993293762</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>1.82400000095367</v>
       </c>
       <c r="G122" t="n">
-        <v>1.6381049156189</v>
+        <v>1.63810479640961</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G124" t="n">
-        <v>1.6165509223938</v>
+        <v>1.61655080318451</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G126" t="n">
-        <v>1.6165509223938</v>
+        <v>1.61655080318451</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>1.79799997806549</v>
       </c>
       <c r="G128" t="n">
-        <v>1.61475467681885</v>
+        <v>1.61475455760956</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G130" t="n">
-        <v>1.6300220489502</v>
+        <v>1.63002228736877</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G131" t="n">
-        <v>1.59409868717194</v>
+        <v>1.59409880638123</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>1.69700002670288</v>
       </c>
       <c r="G132" t="n">
-        <v>1.52404820919037</v>
+        <v>1.52404832839966</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G133" t="n">
-        <v>1.46836698055267</v>
+        <v>1.46836709976196</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>1.64300000667572</v>
       </c>
       <c r="G134" t="n">
-        <v>1.4755517244339</v>
+        <v>1.47555184364319</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>1.62100005149841</v>
       </c>
       <c r="G135" t="n">
-        <v>1.45579409599304</v>
+        <v>1.45579397678375</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>1.66400003433228</v>
       </c>
       <c r="G138" t="n">
-        <v>1.49441146850586</v>
+        <v>1.49441158771515</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>1.6690000295639</v>
       </c>
       <c r="G140" t="n">
-        <v>1.49890196323395</v>
+        <v>1.49890184402466</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>1.67900002002716</v>
       </c>
       <c r="G142" t="n">
-        <v>1.50788283348083</v>
+        <v>1.50788271427155</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G144" t="n">
-        <v>1.49979984760284</v>
+        <v>1.49979996681213</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>1.66100001335144</v>
       </c>
       <c r="G145" t="n">
-        <v>1.49171721935272</v>
+        <v>1.49171733856201</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>1.66100001335144</v>
       </c>
       <c r="G146" t="n">
-        <v>1.49171721935272</v>
+        <v>1.49171733856201</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G147" t="n">
-        <v>1.50429046154022</v>
+        <v>1.50429034233093</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G150" t="n">
-        <v>1.50429046154022</v>
+        <v>1.50429034233093</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>1.65100002288818</v>
       </c>
       <c r="G151" t="n">
-        <v>1.48273634910583</v>
+        <v>1.48273646831512</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G155" t="n">
-        <v>1.52674245834351</v>
+        <v>1.52674269676208</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G157" t="n">
-        <v>1.52674245834351</v>
+        <v>1.52674269676208</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G159" t="n">
-        <v>1.51776170730591</v>
+        <v>1.51776158809662</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>1.68599998950958</v>
       </c>
       <c r="G160" t="n">
-        <v>1.5141693353653</v>
+        <v>1.51416945457458</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G163" t="n">
-        <v>1.49979984760284</v>
+        <v>1.49979996681213</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G164" t="n">
-        <v>1.49979984760284</v>
+        <v>1.49979996681213</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>1.71399998664856</v>
       </c>
       <c r="G166" t="n">
-        <v>1.53931570053101</v>
+        <v>1.53931558132172</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>1.93400001525879</v>
       </c>
       <c r="G168" t="n">
-        <v>1.73689413070679</v>
+        <v>1.7368940114975</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>1.93299996852875</v>
       </c>
       <c r="G170" t="n">
-        <v>1.7359961271286</v>
+        <v>1.73599600791931</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>1.89300000667572</v>
       </c>
       <c r="G172" t="n">
-        <v>1.70007264614105</v>
+        <v>1.70007276535034</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>1.87800002098083</v>
       </c>
       <c r="G174" t="n">
-        <v>1.68660151958466</v>
+        <v>1.68660128116608</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>1.85899996757507</v>
       </c>
       <c r="G176" t="n">
-        <v>1.66953778266907</v>
+        <v>1.66953766345978</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>1.85099995136261</v>
       </c>
       <c r="G178" t="n">
-        <v>1.66235315799713</v>
+        <v>1.66235303878784</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>1.88399994373322</v>
       </c>
       <c r="G179" t="n">
-        <v>1.69198989868164</v>
+        <v>1.69198977947235</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G181" t="n">
-        <v>1.68839764595032</v>
+        <v>1.68839752674103</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>1.85199999809265</v>
       </c>
       <c r="G182" t="n">
-        <v>1.66325116157532</v>
+        <v>1.66325128078461</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>1.80400002002716</v>
       </c>
       <c r="G185" t="n">
-        <v>1.62014317512512</v>
+        <v>1.62014329433441</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G186" t="n">
-        <v>1.6165509223938</v>
+        <v>1.61655080318451</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>1.80099999904633</v>
       </c>
       <c r="G187" t="n">
-        <v>1.61744892597198</v>
+        <v>1.61744904518127</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G188" t="n">
-        <v>1.6165509223938</v>
+        <v>1.61655080318451</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G189" t="n">
-        <v>1.6165509223938</v>
+        <v>1.61655080318451</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G190" t="n">
-        <v>1.6165509223938</v>
+        <v>1.61655080318451</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G191" t="n">
-        <v>1.6165509223938</v>
+        <v>1.61655080318451</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>1.80200004577637</v>
       </c>
       <c r="G192" t="n">
-        <v>1.61834716796875</v>
+        <v>1.61834704875946</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>1.80200004577637</v>
       </c>
       <c r="G193" t="n">
-        <v>1.61834716796875</v>
+        <v>1.61834704875946</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G200" t="n">
-        <v>1.68839764595032</v>
+        <v>1.68839752674103</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G203" t="n">
-        <v>1.66594552993774</v>
+        <v>1.66594541072845</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>1.85199999809265</v>
       </c>
       <c r="G205" t="n">
-        <v>1.66325116157532</v>
+        <v>1.66325128078461</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G211" t="n">
-        <v>1.65247416496277</v>
+        <v>1.65247428417206</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>1.86899995803833</v>
       </c>
       <c r="G212" t="n">
-        <v>1.67851853370667</v>
+        <v>1.67851865291595</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>1.86899995803833</v>
       </c>
       <c r="G213" t="n">
-        <v>1.67851853370667</v>
+        <v>1.67851865291595</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G214" t="n">
-        <v>1.65247416496277</v>
+        <v>1.65247428417206</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>1.8289999961853</v>
       </c>
       <c r="G216" t="n">
-        <v>1.64259541034698</v>
+        <v>1.6425952911377</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>1.83700001239777</v>
       </c>
       <c r="G219" t="n">
-        <v>1.64978003501892</v>
+        <v>1.64977991580963</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>1.80200004577637</v>
       </c>
       <c r="G221" t="n">
-        <v>1.61834716796875</v>
+        <v>1.61834704875946</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>1.83700001239777</v>
       </c>
       <c r="G222" t="n">
-        <v>1.64978003501892</v>
+        <v>1.64977991580963</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>1.74600005149841</v>
       </c>
       <c r="G224" t="n">
-        <v>1.56805443763733</v>
+        <v>1.56805431842804</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G226" t="n">
-        <v>1.52674245834351</v>
+        <v>1.52674269676208</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>1.65799999237061</v>
       </c>
       <c r="G228" t="n">
-        <v>1.48902308940887</v>
+        <v>1.4890228509903</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G230" t="n">
-        <v>1.42795324325562</v>
+        <v>1.4279533624649</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>1.49699997901917</v>
       </c>
       <c r="G233" t="n">
-        <v>1.34443151950836</v>
+        <v>1.34443140029907</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>1.4650000333786</v>
       </c>
       <c r="G235" t="n">
-        <v>1.31569290161133</v>
+        <v>1.31569278240204</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>1.4650000333786</v>
       </c>
       <c r="G236" t="n">
-        <v>1.31569290161133</v>
+        <v>1.31569278240204</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>1.52199995517731</v>
       </c>
       <c r="G237" t="n">
-        <v>1.36688363552094</v>
+        <v>1.36688351631165</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>1.5</v>
       </c>
       <c r="G238" t="n">
-        <v>1.34712564945221</v>
+        <v>1.3471257686615</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>1.58200001716614</v>
       </c>
       <c r="G240" t="n">
-        <v>1.42076861858368</v>
+        <v>1.42076873779297</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>1.61300003528595</v>
       </c>
       <c r="G244" t="n">
-        <v>1.44860935211182</v>
+        <v>1.44860923290253</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>1.67900002002716</v>
       </c>
       <c r="G246" t="n">
-        <v>1.50788283348083</v>
+        <v>1.50788271427155</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>1.71899998188019</v>
       </c>
       <c r="G247" t="n">
-        <v>1.54380595684052</v>
+        <v>1.5438060760498</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G249" t="n">
-        <v>1.54470419883728</v>
+        <v>1.54470407962799</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G250" t="n">
-        <v>1.54470419883728</v>
+        <v>1.54470407962799</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G257" t="n">
-        <v>1.66594552993774</v>
+        <v>1.66594541072845</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G258" t="n">
-        <v>1.66594552993774</v>
+        <v>1.66594541072845</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G259" t="n">
-        <v>1.66594552993774</v>
+        <v>1.66594541072845</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G263" t="n">
-        <v>1.65247416496277</v>
+        <v>1.65247428417206</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G265" t="n">
-        <v>1.64798390865326</v>
+        <v>1.64798378944397</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G267" t="n">
-        <v>1.65247416496277</v>
+        <v>1.65247428417206</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>1.81099998950958</v>
       </c>
       <c r="G268" t="n">
-        <v>1.62642967700958</v>
+        <v>1.62642979621887</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>1.80099999904633</v>
       </c>
       <c r="G270" t="n">
-        <v>1.61744892597198</v>
+        <v>1.61744904518127</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>1.71899998188019</v>
       </c>
       <c r="G274" t="n">
-        <v>1.54380595684052</v>
+        <v>1.5438060760498</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>1.69599997997284</v>
       </c>
       <c r="G276" t="n">
-        <v>1.52315008640289</v>
+        <v>1.52315020561218</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G280" t="n">
-        <v>1.54470419883728</v>
+        <v>1.54470407962799</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G282" t="n">
-        <v>1.54470419883728</v>
+        <v>1.54470407962799</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>1.65100002288818</v>
       </c>
       <c r="G283" t="n">
-        <v>1.48273634910583</v>
+        <v>1.48273646831512</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G284" t="n">
-        <v>1.48183846473694</v>
+        <v>1.48183822631836</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>1.62100005149841</v>
       </c>
       <c r="G285" t="n">
-        <v>1.45579409599304</v>
+        <v>1.45579397678375</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G286" t="n">
-        <v>1.47285747528076</v>
+        <v>1.47285735607147</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>1.63100004196167</v>
       </c>
       <c r="G287" t="n">
-        <v>1.46477460861206</v>
+        <v>1.46477472782135</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>1.56200003623962</v>
       </c>
       <c r="G289" t="n">
-        <v>1.40280699729919</v>
+        <v>1.4028068780899</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G290" t="n">
-        <v>1.38304889202118</v>
+        <v>1.38304901123047</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>1.48599994182587</v>
       </c>
       <c r="G292" t="n">
-        <v>1.334552526474</v>
+        <v>1.33455240726471</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>1.48399996757507</v>
       </c>
       <c r="G295" t="n">
-        <v>1.33275640010834</v>
+        <v>1.33275628089905</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G298" t="n">
-        <v>1.3381450176239</v>
+        <v>1.33814489841461</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>1.55299997329712</v>
       </c>
       <c r="G299" t="n">
-        <v>1.3947240114212</v>
+        <v>1.39472413063049</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G300" t="n">
-        <v>1.42795324325562</v>
+        <v>1.4279533624649</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>1.5789999961853</v>
       </c>
       <c r="G301" t="n">
-        <v>1.41807425022125</v>
+        <v>1.41807436943054</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>1.58599996566772</v>
       </c>
       <c r="G302" t="n">
-        <v>1.424360871315</v>
+        <v>1.42436099052429</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>1.58200001716614</v>
       </c>
       <c r="G305" t="n">
-        <v>1.42076861858368</v>
+        <v>1.42076873779297</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>1.57700002193451</v>
       </c>
       <c r="G307" t="n">
-        <v>1.41627812385559</v>
+        <v>1.41627824306488</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G308" t="n">
-        <v>1.39202988147736</v>
+        <v>1.39202976226807</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G309" t="n">
-        <v>1.37406837940216</v>
+        <v>1.37406826019287</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G313" t="n">
-        <v>1.38304889202118</v>
+        <v>1.38304901123047</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G315" t="n">
-        <v>1.39202988147736</v>
+        <v>1.39202976226807</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G317" t="n">
-        <v>1.41897249221802</v>
+        <v>1.41897237300873</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>1.6139999628067</v>
       </c>
       <c r="G319" t="n">
-        <v>1.44950723648071</v>
+        <v>1.44950735569</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>1.62600004673004</v>
       </c>
       <c r="G320" t="n">
-        <v>1.46028435230255</v>
+        <v>1.46028423309326</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>1.65100002288818</v>
       </c>
       <c r="G324" t="n">
-        <v>1.48273634910583</v>
+        <v>1.48273646831512</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>1.63399994373322</v>
       </c>
       <c r="G327" t="n">
-        <v>1.46746897697449</v>
+        <v>1.4674688577652</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>1.62399995326996</v>
       </c>
       <c r="G328" t="n">
-        <v>1.4584881067276</v>
+        <v>1.45848798751831</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>1.62199997901917</v>
       </c>
       <c r="G329" t="n">
-        <v>1.45669186115265</v>
+        <v>1.45669198036194</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>1.625</v>
       </c>
       <c r="G330" t="n">
-        <v>1.45938622951508</v>
+        <v>1.45938634872437</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G333" t="n">
-        <v>1.42346286773682</v>
+        <v>1.42346274852753</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>1.60300004482269</v>
       </c>
       <c r="G334" t="n">
-        <v>1.43962836265564</v>
+        <v>1.43962848186493</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>1.63399994373322</v>
       </c>
       <c r="G336" t="n">
-        <v>1.46746897697449</v>
+        <v>1.4674688577652</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G341" t="n">
-        <v>1.48183846473694</v>
+        <v>1.48183822631836</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>1.67900002002716</v>
       </c>
       <c r="G343" t="n">
-        <v>1.50788283348083</v>
+        <v>1.50788271427155</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>1.67900002002716</v>
       </c>
       <c r="G345" t="n">
-        <v>1.50788283348083</v>
+        <v>1.50788271427155</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>1.70099997520447</v>
       </c>
       <c r="G346" t="n">
-        <v>1.52764058113098</v>
+        <v>1.52764046192169</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G347" t="n">
-        <v>1.51327121257782</v>
+        <v>1.51327109336853</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G348" t="n">
-        <v>1.51776170730591</v>
+        <v>1.51776158809662</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>1.81099998950958</v>
       </c>
       <c r="G349" t="n">
-        <v>1.62642967700958</v>
+        <v>1.62642979621887</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>1.80099999904633</v>
       </c>
       <c r="G353" t="n">
-        <v>1.61744892597198</v>
+        <v>1.61744904518127</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>1.78699994087219</v>
       </c>
       <c r="G354" t="n">
-        <v>1.60487580299377</v>
+        <v>1.60487568378448</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G355" t="n">
-        <v>1.65247416496277</v>
+        <v>1.65247428417206</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G356" t="n">
-        <v>1.7108496427536</v>
+        <v>1.71084976196289</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G357" t="n">
-        <v>1.74228250980377</v>
+        <v>1.74228274822235</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G359" t="n">
-        <v>1.72432100772858</v>
+        <v>1.72432088851929</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G360" t="n">
-        <v>1.72432100772858</v>
+        <v>1.72432088851929</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>1.85899996757507</v>
       </c>
       <c r="G366" t="n">
-        <v>1.66953778266907</v>
+        <v>1.66953766345978</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>1.81700003147125</v>
       </c>
       <c r="G368" t="n">
-        <v>1.63181829452515</v>
+        <v>1.63181841373444</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G370" t="n">
-        <v>1.6165509223938</v>
+        <v>1.61655080318451</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G372" t="n">
-        <v>1.65247416496277</v>
+        <v>1.65247428417206</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>1.83700001239777</v>
       </c>
       <c r="G373" t="n">
-        <v>1.64978003501892</v>
+        <v>1.64977991580963</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>1.84200000762939</v>
       </c>
       <c r="G376" t="n">
-        <v>1.65427052974701</v>
+        <v>1.65427041053772</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>1.81200003623962</v>
       </c>
       <c r="G378" t="n">
-        <v>1.62732791900635</v>
+        <v>1.62732779979706</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G379" t="n">
-        <v>1.6165509223938</v>
+        <v>1.61655080318451</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>1.80400002002716</v>
       </c>
       <c r="G380" t="n">
-        <v>1.62014317512512</v>
+        <v>1.62014329433441</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>1.7610000371933</v>
       </c>
       <c r="G381" t="n">
-        <v>1.58152556419373</v>
+        <v>1.58152568340302</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>1.74800002574921</v>
       </c>
       <c r="G384" t="n">
-        <v>1.5698504447937</v>
+        <v>1.56985056400299</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>1.72099995613098</v>
       </c>
       <c r="G385" t="n">
-        <v>1.54560220241547</v>
+        <v>1.54560232162476</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>1.72099995613098</v>
       </c>
       <c r="G386" t="n">
-        <v>1.54560220241547</v>
+        <v>1.54560232162476</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G388" t="n">
-        <v>1.49979984760284</v>
+        <v>1.49979996681213</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>1.69700002670288</v>
       </c>
       <c r="G389" t="n">
-        <v>1.52404820919037</v>
+        <v>1.52404832839966</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G391" t="n">
-        <v>1.55368506908417</v>
+        <v>1.55368494987488</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G394" t="n">
-        <v>1.60757005214691</v>
+        <v>1.60756993293762</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G395" t="n">
-        <v>1.6165509223938</v>
+        <v>1.61655080318451</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>1.7610000371933</v>
       </c>
       <c r="G399" t="n">
-        <v>1.58152556419373</v>
+        <v>1.58152568340302</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>1.77799999713898</v>
       </c>
       <c r="G403" t="n">
-        <v>1.59679293632507</v>
+        <v>1.59679317474365</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>1.78299999237061</v>
       </c>
       <c r="G404" t="n">
-        <v>1.60128343105316</v>
+        <v>1.60128355026245</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>1.78900003433228</v>
       </c>
       <c r="G405" t="n">
-        <v>1.60667204856873</v>
+        <v>1.60667192935944</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G406" t="n">
-        <v>1.60757005214691</v>
+        <v>1.60756993293762</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>1.80400002002716</v>
       </c>
       <c r="G409" t="n">
-        <v>1.62014317512512</v>
+        <v>1.62014329433441</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>1.81700003147125</v>
       </c>
       <c r="G411" t="n">
-        <v>1.63181829452515</v>
+        <v>1.63181841373444</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>1.80099999904633</v>
       </c>
       <c r="G412" t="n">
-        <v>1.61744892597198</v>
+        <v>1.61744904518127</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>1.79799997806549</v>
       </c>
       <c r="G413" t="n">
-        <v>1.61475467681885</v>
+        <v>1.61475455760956</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>1.75399994850159</v>
       </c>
       <c r="G415" t="n">
-        <v>1.57523906230927</v>
+        <v>1.57523894309998</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G420" t="n">
-        <v>1.6165509223938</v>
+        <v>1.61655080318451</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G422" t="n">
-        <v>1.60757005214691</v>
+        <v>1.60756993293762</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>1.85199999809265</v>
       </c>
       <c r="G424" t="n">
-        <v>1.66325116157532</v>
+        <v>1.66325128078461</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G425" t="n">
-        <v>1.72432100772858</v>
+        <v>1.72432088851929</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>1.87899994850159</v>
       </c>
       <c r="G427" t="n">
-        <v>1.68749940395355</v>
+        <v>1.68749952316284</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>1.88199996948242</v>
       </c>
       <c r="G428" t="n">
-        <v>1.69019377231598</v>
+        <v>1.69019365310669</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>1.85199999809265</v>
       </c>
       <c r="G430" t="n">
-        <v>1.66325116157532</v>
+        <v>1.66325128078461</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G433" t="n">
-        <v>1.81412935256958</v>
+        <v>1.81412923336029</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G434" t="n">
-        <v>1.88597583770752</v>
+        <v>1.88597595691681</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>2.19600009918213</v>
       </c>
       <c r="G435" t="n">
-        <v>1.97219216823578</v>
+        <v>1.97219228744507</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G437" t="n">
-        <v>2.02966952323914</v>
+        <v>2.02966928482056</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>2.5239999294281</v>
       </c>
       <c r="G440" t="n">
-        <v>2.26676344871521</v>
+        <v>2.26676368713379</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>2.53800010681152</v>
       </c>
       <c r="G442" t="n">
-        <v>2.27933692932129</v>
+        <v>2.27933669090271</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G445" t="n">
-        <v>2.3529794216156</v>
+        <v>2.35297966003418</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G451" t="n">
-        <v>2.30807542800903</v>
+        <v>2.30807518959045</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>2.56399989128113</v>
       </c>
       <c r="G452" t="n">
-        <v>2.30268692970276</v>
+        <v>2.30268669128418</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G455" t="n">
-        <v>2.20030522346497</v>
+        <v>2.20030546188354</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>2.50600004196167</v>
       </c>
       <c r="G458" t="n">
-        <v>2.25059819221497</v>
+        <v>2.25059795379639</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>2.83800005912781</v>
       </c>
       <c r="G462" t="n">
-        <v>2.54876208305359</v>
+        <v>2.54876184463501</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G466" t="n">
-        <v>2.45176887512207</v>
+        <v>2.45176863670349</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>2.84400010108948</v>
       </c>
       <c r="G469" t="n">
-        <v>2.55415058135986</v>
+        <v>2.55415034294128</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G472" t="n">
-        <v>2.55055785179138</v>
+        <v>2.55055809020996</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>2.7739999294281</v>
       </c>
       <c r="G473" t="n">
-        <v>2.49128460884094</v>
+        <v>2.49128437042236</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>2.79200005531311</v>
       </c>
       <c r="G474" t="n">
-        <v>2.50744986534119</v>
+        <v>2.50745010375977</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>2.3659999370575</v>
       </c>
       <c r="G477" t="n">
-        <v>2.12486600875854</v>
+        <v>2.12486624717712</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G479" t="n">
-        <v>2.164381980896</v>
+        <v>2.16438221931458</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>2.25600004196167</v>
       </c>
       <c r="G481" t="n">
-        <v>2.02607727050781</v>
+        <v>2.02607703208923</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G483" t="n">
-        <v>2.164381980896</v>
+        <v>2.16438221931458</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>2.5</v>
       </c>
       <c r="G485" t="n">
-        <v>2.24520969390869</v>
+        <v>2.24520945549011</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>2.48799991607666</v>
       </c>
       <c r="G486" t="n">
-        <v>2.23443222045898</v>
+        <v>2.23443245887756</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>2.62199997901917</v>
       </c>
       <c r="G490" t="n">
-        <v>2.35477566719055</v>
+        <v>2.35477590560913</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>2.55800008773804</v>
       </c>
       <c r="G491" t="n">
-        <v>2.29729843139648</v>
+        <v>2.29729819297791</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>2.48399996757507</v>
       </c>
       <c r="G493" t="n">
-        <v>2.23084020614624</v>
+        <v>2.23083996772766</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G496" t="n">
-        <v>2.23622870445251</v>
+        <v>2.23622894287109</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G501" t="n">
-        <v>2.23622870445251</v>
+        <v>2.23622894287109</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>2.5</v>
       </c>
       <c r="G502" t="n">
-        <v>2.24520969390869</v>
+        <v>2.24520945549011</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>2.5239999294281</v>
       </c>
       <c r="G505" t="n">
-        <v>2.26676344871521</v>
+        <v>2.26676368713379</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>2.5220000743866</v>
       </c>
       <c r="G506" t="n">
-        <v>2.26496744155884</v>
+        <v>2.26496720314026</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>2.45199990272522</v>
       </c>
       <c r="G508" t="n">
-        <v>2.20210146903992</v>
+        <v>2.20210123062134</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>2.43799996376038</v>
       </c>
       <c r="G509" t="n">
-        <v>2.18952822685242</v>
+        <v>2.189528465271</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G513" t="n">
-        <v>2.18234348297119</v>
+        <v>2.18234372138977</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G518" t="n">
-        <v>2.21826720237732</v>
+        <v>2.21826696395874</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>2.43499994277954</v>
       </c>
       <c r="G519" t="n">
-        <v>2.18683409690857</v>
+        <v>2.18683385848999</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G521" t="n">
-        <v>2.164381980896</v>
+        <v>2.16438221931458</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>2.42499995231628</v>
       </c>
       <c r="G522" t="n">
-        <v>2.17785334587097</v>
+        <v>2.17785310745239</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G523" t="n">
-        <v>2.12845873832703</v>
+        <v>2.12845826148987</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G526" t="n">
-        <v>2.06559252738953</v>
+        <v>2.06559276580811</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G527" t="n">
-        <v>2.09253549575806</v>
+        <v>2.09253525733948</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G528" t="n">
-        <v>2.08355450630188</v>
+        <v>2.0835542678833</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G529" t="n">
-        <v>2.0745735168457</v>
+        <v>2.07457375526428</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G530" t="n">
-        <v>2.10151600837708</v>
+        <v>2.10151624679565</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G532" t="n">
-        <v>2.12845873832703</v>
+        <v>2.12845826148987</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G535" t="n">
-        <v>2.11947751045227</v>
+        <v>2.11947774887085</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G539" t="n">
-        <v>2.06559252738953</v>
+        <v>2.06559276580811</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>2.26500010490417</v>
       </c>
       <c r="G540" t="n">
-        <v>2.03415989875793</v>
+        <v>2.03416013717651</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>2.36500000953674</v>
       </c>
       <c r="G541" t="n">
-        <v>2.12396788597107</v>
+        <v>2.12396812438965</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>2.34500002861023</v>
       </c>
       <c r="G543" t="n">
-        <v>2.10600662231445</v>
+        <v>2.10600638389587</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G544" t="n">
-        <v>2.06559252738953</v>
+        <v>2.06559276580811</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G545" t="n">
-        <v>2.06559252738953</v>
+        <v>2.06559276580811</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G546" t="n">
-        <v>2.10151600837708</v>
+        <v>2.10151624679565</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G547" t="n">
-        <v>2.06559252738953</v>
+        <v>2.06559276580811</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G550" t="n">
-        <v>2.0745735168457</v>
+        <v>2.07457375526428</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G554" t="n">
-        <v>1.87699520587921</v>
+        <v>1.87699496746063</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G556" t="n">
-        <v>1.85005247592926</v>
+        <v>1.85005259513855</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G559" t="n">
-        <v>1.94884192943573</v>
+        <v>1.94884181022644</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G560" t="n">
-        <v>1.9847651720047</v>
+        <v>1.98476529121399</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G564" t="n">
-        <v>2.06110239028931</v>
+        <v>2.06110215187073</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G566" t="n">
-        <v>1.99374616146088</v>
+        <v>1.9937459230423</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G570" t="n">
-        <v>1.94884192943573</v>
+        <v>1.94884181022644</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>2.15499997138977</v>
       </c>
       <c r="G571" t="n">
-        <v>1.93537068367004</v>
+        <v>1.93537056446075</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>2.15499997138977</v>
       </c>
       <c r="G573" t="n">
-        <v>1.93537068367004</v>
+        <v>1.93537056446075</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G575" t="n">
-        <v>1.9847651720047</v>
+        <v>1.98476529121399</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G576" t="n">
-        <v>1.9847651720047</v>
+        <v>1.98476529121399</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>2.26500010490417</v>
       </c>
       <c r="G579" t="n">
-        <v>2.03415989875793</v>
+        <v>2.03416013717651</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>2.26500010490417</v>
       </c>
       <c r="G580" t="n">
-        <v>2.03415989875793</v>
+        <v>2.03416013717651</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>2.23499989509583</v>
       </c>
       <c r="G581" t="n">
-        <v>2.00721716880798</v>
+        <v>2.00721740722656</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G582" t="n">
-        <v>2.05661177635193</v>
+        <v>2.05661201477051</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G586" t="n">
-        <v>2.08355450630188</v>
+        <v>2.0835542678833</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G587" t="n">
-        <v>2.06110239028931</v>
+        <v>2.06110215187073</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>2.32500004768372</v>
       </c>
       <c r="G589" t="n">
-        <v>2.08804512023926</v>
+        <v>2.08804488182068</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G590" t="n">
-        <v>2.06559252738953</v>
+        <v>2.06559276580811</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G591" t="n">
-        <v>2.0745735168457</v>
+        <v>2.07457375526428</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G592" t="n">
-        <v>2.06110239028931</v>
+        <v>2.06110215187073</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G595" t="n">
-        <v>2.0745735168457</v>
+        <v>2.07457375526428</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G596" t="n">
-        <v>2.08355450630188</v>
+        <v>2.0835542678833</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G597" t="n">
-        <v>2.0745735168457</v>
+        <v>2.07457375526428</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G598" t="n">
-        <v>2.23622870445251</v>
+        <v>2.23622894287109</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G599" t="n">
-        <v>2.23622870445251</v>
+        <v>2.23622894287109</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>2.5</v>
       </c>
       <c r="G601" t="n">
-        <v>2.24520969390869</v>
+        <v>2.24520945549011</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G603" t="n">
-        <v>2.21826720237732</v>
+        <v>2.21826696395874</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G604" t="n">
-        <v>2.20030522346497</v>
+        <v>2.20030546188354</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G605" t="n">
-        <v>2.11947751045227</v>
+        <v>2.11947774887085</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>2.26500010490417</v>
       </c>
       <c r="G609" t="n">
-        <v>2.03415989875793</v>
+        <v>2.03416013717651</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>2.22499990463257</v>
       </c>
       <c r="G613" t="n">
-        <v>1.9982362985611</v>
+        <v>1.99823641777039</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>2.15499997138977</v>
       </c>
       <c r="G615" t="n">
-        <v>1.93537068367004</v>
+        <v>1.93537056446075</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G616" t="n">
-        <v>2.02966952323914</v>
+        <v>2.02966928482056</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G619" t="n">
-        <v>2.06559252738953</v>
+        <v>2.06559276580811</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G620" t="n">
-        <v>2.02966952323914</v>
+        <v>2.02966928482056</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G623" t="n">
-        <v>2.06110239028931</v>
+        <v>2.06110215187073</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G624" t="n">
-        <v>2.02966952323914</v>
+        <v>2.02966928482056</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G628" t="n">
-        <v>2.06559252738953</v>
+        <v>2.06559276580811</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>2.26500010490417</v>
       </c>
       <c r="G630" t="n">
-        <v>2.03415989875793</v>
+        <v>2.03416013717651</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G631" t="n">
-        <v>1.99374616146088</v>
+        <v>1.9937459230423</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G632" t="n">
-        <v>2.05661177635193</v>
+        <v>2.05661201477051</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G636" t="n">
-        <v>1.95782291889191</v>
+        <v>1.95782279968262</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G639" t="n">
-        <v>1.99374616146088</v>
+        <v>1.9937459230423</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>2.22499990463257</v>
       </c>
       <c r="G640" t="n">
-        <v>1.9982362985611</v>
+        <v>1.99823641777039</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G641" t="n">
-        <v>1.99374616146088</v>
+        <v>1.9937459230423</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G643" t="n">
-        <v>1.99374616146088</v>
+        <v>1.9937459230423</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G644" t="n">
-        <v>1.96680355072021</v>
+        <v>1.96680343151093</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G645" t="n">
-        <v>1.95782291889191</v>
+        <v>1.95782279968262</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G646" t="n">
-        <v>1.96680355072021</v>
+        <v>1.96680343151093</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>2.1949999332428</v>
       </c>
       <c r="G647" t="n">
-        <v>1.97129392623901</v>
+        <v>1.97129380702972</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G648" t="n">
-        <v>1.96680355072021</v>
+        <v>1.96680343151093</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G649" t="n">
-        <v>1.95782291889191</v>
+        <v>1.95782279968262</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G653" t="n">
-        <v>1.95782291889191</v>
+        <v>1.95782279968262</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>2.15499997138977</v>
       </c>
       <c r="G654" t="n">
-        <v>1.93537068367004</v>
+        <v>1.93537056446075</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G655" t="n">
-        <v>1.94884192943573</v>
+        <v>1.94884181022644</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G656" t="n">
-        <v>1.8949568271637</v>
+        <v>1.89495694637299</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G658" t="n">
-        <v>1.8949568271637</v>
+        <v>1.89495694637299</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G659" t="n">
-        <v>1.93088018894196</v>
+        <v>1.93088030815125</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>2.125</v>
       </c>
       <c r="G663" t="n">
-        <v>1.90842795372009</v>
+        <v>1.90842807292938</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G664" t="n">
-        <v>1.93088018894196</v>
+        <v>1.93088030815125</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G665" t="n">
-        <v>1.93088018894196</v>
+        <v>1.93088030815125</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>2.09500002861023</v>
       </c>
       <c r="G668" t="n">
-        <v>1.88148558139801</v>
+        <v>1.88148546218872</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G670" t="n">
-        <v>1.93088018894196</v>
+        <v>1.93088030815125</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G671" t="n">
-        <v>1.93088018894196</v>
+        <v>1.93088030815125</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G672" t="n">
-        <v>1.95782291889191</v>
+        <v>1.95782279968262</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G673" t="n">
-        <v>1.97578430175781</v>
+        <v>1.97578454017639</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G674" t="n">
-        <v>1.96680355072021</v>
+        <v>1.96680343151093</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G679" t="n">
-        <v>2.06559252738953</v>
+        <v>2.06559276580811</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G681" t="n">
-        <v>1.99374616146088</v>
+        <v>1.9937459230423</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G682" t="n">
-        <v>1.94884192943573</v>
+        <v>1.94884181022644</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G684" t="n">
-        <v>1.96680355072021</v>
+        <v>1.96680343151093</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G686" t="n">
-        <v>2.05661177635193</v>
+        <v>2.05661201477051</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G687" t="n">
-        <v>2.05661177635193</v>
+        <v>2.05661201477051</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G688" t="n">
-        <v>2.0745735168457</v>
+        <v>2.07457375526428</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>2.26500010490417</v>
       </c>
       <c r="G690" t="n">
-        <v>2.03415989875793</v>
+        <v>2.03416013717651</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>2.23499989509583</v>
       </c>
       <c r="G693" t="n">
-        <v>2.00721716880798</v>
+        <v>2.00721740722656</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G694" t="n">
-        <v>2.0745735168457</v>
+        <v>2.07457375526428</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G695" t="n">
-        <v>2.05661177635193</v>
+        <v>2.05661201477051</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G698" t="n">
-        <v>2.06110239028931</v>
+        <v>2.06110215187073</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G700" t="n">
-        <v>2.02966952323914</v>
+        <v>2.02966928482056</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G706" t="n">
-        <v>1.97578430175781</v>
+        <v>1.97578454017639</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G709" t="n">
-        <v>1.85005247592926</v>
+        <v>1.85005259513855</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G710" t="n">
-        <v>1.77820587158203</v>
+        <v>1.77820599079132</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G711" t="n">
-        <v>1.82311010360718</v>
+        <v>1.82311022281647</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G712" t="n">
-        <v>1.85903346538544</v>
+        <v>1.85903334617615</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>2.07500004768372</v>
       </c>
       <c r="G714" t="n">
-        <v>1.86352396011353</v>
+        <v>1.86352407932281</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G715" t="n">
-        <v>1.8051483631134</v>
+        <v>1.80514848232269</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>1.99199998378754</v>
       </c>
       <c r="G716" t="n">
-        <v>1.78898286819458</v>
+        <v>1.78898298740387</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G721" t="n">
-        <v>1.65247416496277</v>
+        <v>1.65247428417206</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G722" t="n">
-        <v>1.65247416496277</v>
+        <v>1.65247428417206</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>1.85599994659424</v>
       </c>
       <c r="G723" t="n">
-        <v>1.66684353351593</v>
+        <v>1.66684341430664</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>1.81599998474121</v>
       </c>
       <c r="G727" t="n">
-        <v>1.63092029094696</v>
+        <v>1.63092005252838</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>1.83399999141693</v>
       </c>
       <c r="G728" t="n">
-        <v>1.64708578586578</v>
+        <v>1.64708566665649</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>1.81599998474121</v>
       </c>
       <c r="G730" t="n">
-        <v>1.63092029094696</v>
+        <v>1.63092005252838</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G738" t="n">
-        <v>1.41897249221802</v>
+        <v>1.41897237300873</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G739" t="n">
-        <v>1.42795324325562</v>
+        <v>1.4279533624649</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>1.57400000095367</v>
       </c>
       <c r="G742" t="n">
-        <v>1.41358387470245</v>
+        <v>1.41358399391174</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>1.57200002670288</v>
       </c>
       <c r="G743" t="n">
-        <v>1.41178786754608</v>
+        <v>1.41178774833679</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>1.50800001621246</v>
       </c>
       <c r="G744" t="n">
-        <v>1.35431027412415</v>
+        <v>1.35431039333344</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>1.48399996757507</v>
       </c>
       <c r="G745" t="n">
-        <v>1.33275640010834</v>
+        <v>1.33275628089905</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>1.49600005149841</v>
       </c>
       <c r="G746" t="n">
-        <v>1.34353339672089</v>
+        <v>1.34353351593018</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G747" t="n">
-        <v>1.39202988147736</v>
+        <v>1.39202976226807</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G752" t="n">
-        <v>1.30222153663635</v>
+        <v>1.30222165584564</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>1.41600000858307</v>
       </c>
       <c r="G755" t="n">
-        <v>1.27168679237366</v>
+        <v>1.27168667316437</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>1.25</v>
       </c>
       <c r="G759" t="n">
-        <v>1.12260484695435</v>
+        <v>1.12260472774506</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>1.25399994850159</v>
       </c>
       <c r="G760" t="n">
-        <v>1.12619698047638</v>
+        <v>1.12619709968567</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G762" t="n">
-        <v>1.14954721927643</v>
+        <v>1.14954733848572</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>1.30400002002716</v>
       </c>
       <c r="G763" t="n">
-        <v>1.17110133171082</v>
+        <v>1.17110121250153</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>1.41400003433228</v>
       </c>
       <c r="G765" t="n">
-        <v>1.26989054679871</v>
+        <v>1.26989042758942</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>1.52799999713898</v>
       </c>
       <c r="G766" t="n">
-        <v>1.37227201461792</v>
+        <v>1.37227213382721</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G769" t="n">
-        <v>1.36508738994598</v>
+        <v>1.36508750915527</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G770" t="n">
-        <v>1.35610663890839</v>
+        <v>1.3561065196991</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>1.51800000667572</v>
       </c>
       <c r="G771" t="n">
-        <v>1.36329126358032</v>
+        <v>1.36329114437103</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G774" t="n">
-        <v>1.3381450176239</v>
+        <v>1.33814489841461</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>1.49600005149841</v>
       </c>
       <c r="G775" t="n">
-        <v>1.34353339672089</v>
+        <v>1.34353351593018</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>1.5</v>
       </c>
       <c r="G776" t="n">
-        <v>1.34712564945221</v>
+        <v>1.3471257686615</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>1.48399996757507</v>
       </c>
       <c r="G777" t="n">
-        <v>1.33275640010834</v>
+        <v>1.33275628089905</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>1.49600005149841</v>
       </c>
       <c r="G781" t="n">
-        <v>1.34353339672089</v>
+        <v>1.34353351593018</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>1.44200003147125</v>
       </c>
       <c r="G787" t="n">
-        <v>1.29503691196442</v>
+        <v>1.29503703117371</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>1.42799997329712</v>
       </c>
       <c r="G788" t="n">
-        <v>1.28246366977692</v>
+        <v>1.28246378898621</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G790" t="n">
-        <v>1.24833655357361</v>
+        <v>1.24833643436432</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>1.38800001144409</v>
       </c>
       <c r="G792" t="n">
-        <v>1.24654018878937</v>
+        <v>1.24654030799866</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>1.41799998283386</v>
       </c>
       <c r="G793" t="n">
-        <v>1.27348291873932</v>
+        <v>1.27348279953003</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G794" t="n">
-        <v>1.45309960842133</v>
+        <v>1.45309972763062</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G798" t="n">
-        <v>1.65247416496277</v>
+        <v>1.65247428417206</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>1.78199994564056</v>
       </c>
       <c r="G799" t="n">
-        <v>1.60038530826569</v>
+        <v>1.60038542747498</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G800" t="n">
-        <v>1.65247416496277</v>
+        <v>1.65247428417206</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>2.09500002861023</v>
       </c>
       <c r="G802" t="n">
-        <v>1.88148558139801</v>
+        <v>1.88148546218872</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G803" t="n">
-        <v>1.88597583770752</v>
+        <v>1.88597595691681</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G804" t="n">
-        <v>1.85005247592926</v>
+        <v>1.85005259513855</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G805" t="n">
-        <v>1.82311010360718</v>
+        <v>1.82311022281647</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G807" t="n">
-        <v>1.85903346538544</v>
+        <v>1.85903334617615</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>2.07500004768372</v>
       </c>
       <c r="G808" t="n">
-        <v>1.86352396011353</v>
+        <v>1.86352407932281</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G809" t="n">
-        <v>1.85005247592926</v>
+        <v>1.85005259513855</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>1.98199999332428</v>
       </c>
       <c r="G810" t="n">
-        <v>1.78000223636627</v>
+        <v>1.78000211715698</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G811" t="n">
-        <v>1.81412935256958</v>
+        <v>1.81412923336029</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>2.04500007629395</v>
       </c>
       <c r="G812" t="n">
-        <v>1.83658158779144</v>
+        <v>1.83658146858215</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G813" t="n">
-        <v>1.81412935256958</v>
+        <v>1.81412923336029</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G814" t="n">
-        <v>1.8051483631134</v>
+        <v>1.80514848232269</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>1.98599994182587</v>
       </c>
       <c r="G815" t="n">
-        <v>1.7835944890976</v>
+        <v>1.78359436988831</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>1.95799994468689</v>
       </c>
       <c r="G816" t="n">
-        <v>1.75844812393188</v>
+        <v>1.7584480047226</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G818" t="n">
-        <v>1.68839764595032</v>
+        <v>1.68839752674103</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>1.8639999628067</v>
       </c>
       <c r="G819" t="n">
-        <v>1.67402827739716</v>
+        <v>1.67402815818787</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>1.90600001811981</v>
       </c>
       <c r="G820" t="n">
-        <v>1.71174764633179</v>
+        <v>1.71174776554108</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>1.88399994373322</v>
       </c>
       <c r="G822" t="n">
-        <v>1.69198989868164</v>
+        <v>1.69198977947235</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>1.90600001811981</v>
       </c>
       <c r="G825" t="n">
-        <v>1.71174764633179</v>
+        <v>1.71174776554108</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>2.07500004768372</v>
       </c>
       <c r="G826" t="n">
-        <v>1.86352396011353</v>
+        <v>1.86352407932281</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G828" t="n">
-        <v>1.99374616146088</v>
+        <v>1.9937459230423</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G829" t="n">
-        <v>2.06559252738953</v>
+        <v>2.06559276580811</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>2.31500005722046</v>
       </c>
       <c r="G830" t="n">
-        <v>2.0790638923645</v>
+        <v>2.07906436920166</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>2.34500002861023</v>
       </c>
       <c r="G831" t="n">
-        <v>2.10600662231445</v>
+        <v>2.10600638389587</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G834" t="n">
-        <v>1.99374616146088</v>
+        <v>1.9937459230423</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G835" t="n">
-        <v>1.97578430175781</v>
+        <v>1.97578454017639</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G836" t="n">
-        <v>1.97578430175781</v>
+        <v>1.97578454017639</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G837" t="n">
-        <v>1.99374616146088</v>
+        <v>1.9937459230423</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>2.38499999046326</v>
       </c>
       <c r="G839" t="n">
-        <v>2.14192986488342</v>
+        <v>2.141930103302</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G840" t="n">
-        <v>2.17336320877075</v>
+        <v>2.17336273193359</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>2.42499995231628</v>
       </c>
       <c r="G841" t="n">
-        <v>2.17785334587097</v>
+        <v>2.17785310745239</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>2.39499998092651</v>
       </c>
       <c r="G845" t="n">
-        <v>2.1509108543396</v>
+        <v>2.15091061592102</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G846" t="n">
-        <v>2.09253549575806</v>
+        <v>2.09253525733948</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G847" t="n">
-        <v>2.0745735168457</v>
+        <v>2.07457375526428</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>2.38499999046326</v>
       </c>
       <c r="G848" t="n">
-        <v>2.14192986488342</v>
+        <v>2.141930103302</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>2.36500000953674</v>
       </c>
       <c r="G850" t="n">
-        <v>2.12396788597107</v>
+        <v>2.12396812438965</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G852" t="n">
-        <v>1.96680355072021</v>
+        <v>1.96680343151093</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G853" t="n">
-        <v>1.97578430175781</v>
+        <v>1.97578454017639</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G854" t="n">
-        <v>1.96680355072021</v>
+        <v>1.96680343151093</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G855" t="n">
-        <v>1.95782291889191</v>
+        <v>1.95782279968262</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G856" t="n">
-        <v>1.95782291889191</v>
+        <v>1.95782279968262</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G858" t="n">
-        <v>2.06110239028931</v>
+        <v>2.06110215187073</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G864" t="n">
-        <v>2.06559252738953</v>
+        <v>2.06559276580811</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G867" t="n">
-        <v>2.05661177635193</v>
+        <v>2.05661201477051</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G869" t="n">
-        <v>2.06559252738953</v>
+        <v>2.06559276580811</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G870" t="n">
-        <v>2.06110239028931</v>
+        <v>2.06110215187073</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G871" t="n">
-        <v>2.05661177635193</v>
+        <v>2.05661201477051</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G872" t="n">
-        <v>2.05661177635193</v>
+        <v>2.05661201477051</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G873" t="n">
-        <v>2.02966952323914</v>
+        <v>2.02966928482056</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>2.22499990463257</v>
       </c>
       <c r="G875" t="n">
-        <v>1.9982362985611</v>
+        <v>1.99823641777039</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G877" t="n">
-        <v>1.85903346538544</v>
+        <v>1.85903334617615</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G878" t="n">
-        <v>1.86801421642303</v>
+        <v>1.86801433563232</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G881" t="n">
-        <v>1.81412935256958</v>
+        <v>1.81412923336029</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>1.88399994373322</v>
       </c>
       <c r="G884" t="n">
-        <v>1.69198989868164</v>
+        <v>1.69198977947235</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G886" t="n">
-        <v>1.82311010360718</v>
+        <v>1.82311022281647</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G887" t="n">
-        <v>1.82311010360718</v>
+        <v>1.82311022281647</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G891" t="n">
-        <v>1.81412935256958</v>
+        <v>1.81412923336029</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G892" t="n">
-        <v>1.82311010360718</v>
+        <v>1.82311022281647</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G893" t="n">
-        <v>1.82311010360718</v>
+        <v>1.82311022281647</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G894" t="n">
-        <v>1.8051483631134</v>
+        <v>1.80514848232269</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G898" t="n">
-        <v>1.81412935256958</v>
+        <v>1.81412923336029</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G899" t="n">
-        <v>1.8051483631134</v>
+        <v>1.80514848232269</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>1.97800004482269</v>
       </c>
       <c r="G902" t="n">
-        <v>1.77640986442566</v>
+        <v>1.77640974521637</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G904" t="n">
-        <v>1.72432100772858</v>
+        <v>1.72432088851929</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>1.92200005054474</v>
       </c>
       <c r="G905" t="n">
-        <v>1.72611701488495</v>
+        <v>1.72611725330353</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>2.1949999332428</v>
       </c>
       <c r="G906" t="n">
-        <v>1.97129392623901</v>
+        <v>1.97129380702972</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G907" t="n">
-        <v>1.95782291889191</v>
+        <v>1.95782279968262</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G909" t="n">
-        <v>1.99374616146088</v>
+        <v>1.9937459230423</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G911" t="n">
-        <v>1.93088018894196</v>
+        <v>1.93088030815125</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G913" t="n">
-        <v>1.94884192943573</v>
+        <v>1.94884181022644</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>2.125</v>
       </c>
       <c r="G914" t="n">
-        <v>1.90842795372009</v>
+        <v>1.90842807292938</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>2.04500007629395</v>
       </c>
       <c r="G919" t="n">
-        <v>1.83658158779144</v>
+        <v>1.83658146858215</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G920" t="n">
-        <v>1.85005247592926</v>
+        <v>1.85005259513855</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>1.99199998378754</v>
       </c>
       <c r="G921" t="n">
-        <v>1.78898286819458</v>
+        <v>1.78898298740387</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>1.96599996089935</v>
       </c>
       <c r="G924" t="n">
-        <v>1.76563274860382</v>
+        <v>1.76563262939453</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G925" t="n">
-        <v>1.81412935256958</v>
+        <v>1.81412923336029</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>1.94799995422363</v>
       </c>
       <c r="G928" t="n">
-        <v>1.74946713447571</v>
+        <v>1.749467253685</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>1.93400001525879</v>
       </c>
       <c r="G931" t="n">
-        <v>1.73689413070679</v>
+        <v>1.7368940114975</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>1.94799995422363</v>
       </c>
       <c r="G932" t="n">
-        <v>1.74946713447571</v>
+        <v>1.749467253685</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>1.98199999332428</v>
       </c>
       <c r="G933" t="n">
-        <v>1.78000223636627</v>
+        <v>1.78000211715698</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G935" t="n">
-        <v>1.81412935256958</v>
+        <v>1.81412923336029</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G936" t="n">
-        <v>1.85903346538544</v>
+        <v>1.85903334617615</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G937" t="n">
-        <v>1.84556221961975</v>
+        <v>1.84556233882904</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G939" t="n">
-        <v>1.83209109306335</v>
+        <v>1.83209097385406</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>2.26500010490417</v>
       </c>
       <c r="G940" t="n">
-        <v>2.03415989875793</v>
+        <v>2.03416013717651</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G943" t="n">
-        <v>2.164381980896</v>
+        <v>2.16438221931458</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G944" t="n">
-        <v>2.09253549575806</v>
+        <v>2.09253525733948</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>2.31500005722046</v>
       </c>
       <c r="G945" t="n">
-        <v>2.0790638923645</v>
+        <v>2.07906436920166</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G947" t="n">
-        <v>1.9847651720047</v>
+        <v>1.98476529121399</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G948" t="n">
-        <v>1.97578430175781</v>
+        <v>1.97578454017639</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G953" t="n">
-        <v>2.05661177635193</v>
+        <v>2.05661201477051</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G956" t="n">
-        <v>1.96680355072021</v>
+        <v>1.96680343151093</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G957" t="n">
-        <v>1.99374616146088</v>
+        <v>1.9937459230423</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G958" t="n">
-        <v>1.97578430175781</v>
+        <v>1.97578454017639</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G960" t="n">
-        <v>1.95782291889191</v>
+        <v>1.95782279968262</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G961" t="n">
-        <v>1.9847651720047</v>
+        <v>1.98476529121399</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G962" t="n">
-        <v>1.99374616146088</v>
+        <v>1.9937459230423</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G963" t="n">
-        <v>2.09253549575806</v>
+        <v>2.09253525733948</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G964" t="n">
-        <v>2.08355450630188</v>
+        <v>2.0835542678833</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>2.40499997138977</v>
       </c>
       <c r="G965" t="n">
-        <v>2.15989136695862</v>
+        <v>2.1598916053772</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G966" t="n">
-        <v>2.164381980896</v>
+        <v>2.16438221931458</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G967" t="n">
-        <v>2.09253549575806</v>
+        <v>2.09253525733948</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>2.40499997138977</v>
       </c>
       <c r="G968" t="n">
-        <v>2.15989136695862</v>
+        <v>2.1598916053772</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>2.36500000953674</v>
       </c>
       <c r="G969" t="n">
-        <v>2.12396788597107</v>
+        <v>2.12396812438965</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G971" t="n">
-        <v>2.05661177635193</v>
+        <v>2.05661201477051</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G972" t="n">
-        <v>2.06559252738953</v>
+        <v>2.06559276580811</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>2.51500010490417</v>
       </c>
       <c r="G977" t="n">
-        <v>2.25868082046509</v>
+        <v>2.25868105888367</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G978" t="n">
-        <v>2.29909443855286</v>
+        <v>2.29909467697144</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G980" t="n">
-        <v>2.49667310714722</v>
+        <v>2.49667286872864</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>2.75500011444092</v>
       </c>
       <c r="G981" t="n">
-        <v>2.47422075271606</v>
+        <v>2.47422099113464</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G983" t="n">
-        <v>2.55055785179138</v>
+        <v>2.55055809020996</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>2.875</v>
       </c>
       <c r="G984" t="n">
-        <v>2.58199095726013</v>
+        <v>2.58199071884155</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G987" t="n">
-        <v>2.73017477989197</v>
+        <v>2.73017501831055</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G988" t="n">
-        <v>2.68527030944824</v>
+        <v>2.6852707862854</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G990" t="n">
-        <v>2.68527030944824</v>
+        <v>2.6852707862854</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G993" t="n">
-        <v>2.76609778404236</v>
+        <v>2.76609802246094</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G994" t="n">
-        <v>2.91428160667419</v>
+        <v>2.91428184509277</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G995" t="n">
-        <v>3.05348491668701</v>
+        <v>3.05348539352417</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G998" t="n">
-        <v>2.74364614486694</v>
+        <v>2.74364590644836</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1001" t="n">
-        <v>2.73915553092957</v>
+        <v>2.73915576934814</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1005" t="n">
-        <v>2.68527030944824</v>
+        <v>2.6852707862854</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>3.01500010490417</v>
       </c>
       <c r="G1006" t="n">
-        <v>2.70772266387939</v>
+        <v>2.70772290229797</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>3</v>
       </c>
       <c r="G1008" t="n">
-        <v>2.69425129890442</v>
+        <v>2.694251537323</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1009" t="n">
-        <v>2.66730904579163</v>
+        <v>2.66730928421021</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1012" t="n">
-        <v>2.78405976295471</v>
+        <v>2.78405952453613</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1015" t="n">
-        <v>2.74813675880432</v>
+        <v>2.74813652038574</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>2.88499999046326</v>
       </c>
       <c r="G1020" t="n">
-        <v>2.59097170829773</v>
+        <v>2.59097194671631</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1021" t="n">
-        <v>2.66730904579163</v>
+        <v>2.66730928421021</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>3.1949999332428</v>
       </c>
       <c r="G1022" t="n">
-        <v>2.86937761306763</v>
+        <v>2.86937785148621</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1023" t="n">
-        <v>3.12533164024353</v>
+        <v>3.12533187866211</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1026" t="n">
-        <v>2.96367692947388</v>
+        <v>2.96367645263672</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>3.3050000667572</v>
       </c>
       <c r="G1027" t="n">
-        <v>2.9681670665741</v>
+        <v>2.96816682815552</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1028" t="n">
-        <v>3.10737013816833</v>
+        <v>3.10736989974976</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G1030" t="n">
-        <v>3.28249621391296</v>
+        <v>3.28249645233154</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1033" t="n">
-        <v>2.96367692947388</v>
+        <v>2.96367645263672</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1034" t="n">
-        <v>3.12533164024353</v>
+        <v>3.12533187866211</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>3.57500004768372</v>
       </c>
       <c r="G1035" t="n">
-        <v>3.21064949035645</v>
+        <v>3.21064972877502</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1036" t="n">
-        <v>3.10737013816833</v>
+        <v>3.10736989974976</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1037" t="n">
-        <v>2.99959969520569</v>
+        <v>2.99959993362427</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1039" t="n">
-        <v>3.13431239128113</v>
+        <v>3.13431262969971</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1042" t="n">
-        <v>3.2420825958252</v>
+        <v>3.24208235740662</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G1043" t="n">
-        <v>3.29147720336914</v>
+        <v>3.29147696495056</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>3.74499988555908</v>
       </c>
       <c r="G1044" t="n">
-        <v>3.36332392692566</v>
+        <v>3.36332368850708</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>3.85500001907349</v>
       </c>
       <c r="G1045" t="n">
-        <v>3.46211314201355</v>
+        <v>3.46211338043213</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G1046" t="n">
-        <v>3.34536194801331</v>
+        <v>3.34536218643188</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1048" t="n">
-        <v>3.30494832992554</v>
+        <v>3.30494856834412</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>3.625</v>
       </c>
       <c r="G1049" t="n">
-        <v>3.25555372238159</v>
+        <v>3.25555396080017</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>3.57500004768372</v>
       </c>
       <c r="G1050" t="n">
-        <v>3.21064949035645</v>
+        <v>3.21064972877502</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1051" t="n">
-        <v>3.09838938713074</v>
+        <v>3.09838914871216</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1054" t="n">
-        <v>2.85590648651123</v>
+        <v>2.85590672492981</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1057" t="n">
-        <v>2.78405976295471</v>
+        <v>2.78405952453613</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1059" t="n">
-        <v>2.7032322883606</v>
+        <v>2.70323204994202</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G1060" t="n">
-        <v>2.57750058174133</v>
+        <v>2.57750034332275</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G1063" t="n">
-        <v>2.30807542800903</v>
+        <v>2.30807518959045</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>2.45499992370605</v>
       </c>
       <c r="G1064" t="n">
-        <v>2.20479559898376</v>
+        <v>2.20479583740234</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>2.39499998092651</v>
       </c>
       <c r="G1065" t="n">
-        <v>2.1509108543396</v>
+        <v>2.15091061592102</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1069" t="n">
-        <v>1.81412935256958</v>
+        <v>1.81412923336029</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1070" t="n">
-        <v>1.86801421642303</v>
+        <v>1.86801433563232</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>2.16499996185303</v>
       </c>
       <c r="G1074" t="n">
-        <v>1.94435143470764</v>
+        <v>1.94435131549835</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G1078" t="n">
-        <v>1.9847651720047</v>
+        <v>1.98476529121399</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G1083" t="n">
-        <v>2.30807542800903</v>
+        <v>2.30807518959045</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1084" t="n">
-        <v>2.45176887512207</v>
+        <v>2.45176863670349</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1085" t="n">
-        <v>2.45176887512207</v>
+        <v>2.45176863670349</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>2.68499994277954</v>
       </c>
       <c r="G1089" t="n">
-        <v>2.41135478019714</v>
+        <v>2.41135501861572</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>2.9449999332428</v>
       </c>
       <c r="G1091" t="n">
-        <v>2.64485669136047</v>
+        <v>2.64485692977905</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>2.86500000953674</v>
       </c>
       <c r="G1093" t="n">
-        <v>2.57301044464111</v>
+        <v>2.57301020622253</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1094" t="n">
-        <v>2.51463460922241</v>
+        <v>2.51463437080383</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>2.86500000953674</v>
       </c>
       <c r="G1095" t="n">
-        <v>2.57301044464111</v>
+        <v>2.57301020622253</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1096" t="n">
-        <v>2.68527030944824</v>
+        <v>2.6852707862854</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>2.97499990463257</v>
       </c>
       <c r="G1097" t="n">
-        <v>2.67179942131042</v>
+        <v>2.67179918289185</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1098" t="n">
-        <v>2.65832829475403</v>
+        <v>2.65832805633545</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1100" t="n">
-        <v>2.6762900352478</v>
+        <v>2.67628979682922</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1106" t="n">
-        <v>2.73017477989197</v>
+        <v>2.73017501831055</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>2.86500000953674</v>
       </c>
       <c r="G1108" t="n">
-        <v>2.57301044464111</v>
+        <v>2.57301020622253</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1114" t="n">
-        <v>2.48769211769104</v>
+        <v>2.48769235610962</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>2.86500000953674</v>
       </c>
       <c r="G1117" t="n">
-        <v>2.57301044464111</v>
+        <v>2.57301020622253</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>2.9449999332428</v>
       </c>
       <c r="G1118" t="n">
-        <v>2.64485669136047</v>
+        <v>2.64485692977905</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1123" t="n">
-        <v>2.60444307327271</v>
+        <v>2.60444331169128</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1124" t="n">
-        <v>2.60444307327271</v>
+        <v>2.60444331169128</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1126" t="n">
-        <v>2.74813675880432</v>
+        <v>2.74813652038574</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G1131" t="n">
-        <v>2.57750058174133</v>
+        <v>2.57750034332275</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1133" t="n">
-        <v>2.48769211769104</v>
+        <v>2.48769235610962</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G1134" t="n">
-        <v>2.57750058174133</v>
+        <v>2.57750034332275</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29879,7 +29879,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1135" t="n">
-        <v>2.51463460922241</v>
+        <v>2.51463437080383</v>
       </c>
       <c r="H1135" t="s">
         <v>8</v>
@@ -29983,7 +29983,7 @@
         <v>2.72499990463257</v>
       </c>
       <c r="G1139" t="n">
-        <v>2.44727849960327</v>
+        <v>2.44727826118469</v>
       </c>
       <c r="H1139" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>2.6949999332428</v>
       </c>
       <c r="G1141" t="n">
-        <v>2.42033576965332</v>
+        <v>2.4203360080719</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1143" t="n">
-        <v>2.48769211769104</v>
+        <v>2.48769235610962</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1146" t="n">
-        <v>2.45176887512207</v>
+        <v>2.45176863670349</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1152" t="n">
-        <v>2.41584539413452</v>
+        <v>2.4158456325531</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30425,7 +30425,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1156" t="n">
-        <v>2.48769211769104</v>
+        <v>2.48769235610962</v>
       </c>
       <c r="H1156" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1157" t="n">
-        <v>2.45176887512207</v>
+        <v>2.45176863670349</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1159" t="n">
-        <v>2.41584539413452</v>
+        <v>2.4158456325531</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1160" t="n">
-        <v>2.41584539413452</v>
+        <v>2.4158456325531</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G1162" t="n">
-        <v>2.39788365364075</v>
+        <v>2.39788389205933</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>2.57500004768372</v>
       </c>
       <c r="G1168" t="n">
-        <v>2.31256604194641</v>
+        <v>2.31256556510925</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>2.74499988555908</v>
       </c>
       <c r="G1171" t="n">
-        <v>2.46524000167847</v>
+        <v>2.46524024009705</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30945,7 +30945,7 @@
         <v>2.74499988555908</v>
       </c>
       <c r="G1176" t="n">
-        <v>2.46524000167847</v>
+        <v>2.46524024009705</v>
       </c>
       <c r="H1176" t="s">
         <v>8</v>
@@ -30971,7 +30971,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1177" t="n">
-        <v>2.48769211769104</v>
+        <v>2.48769235610962</v>
       </c>
       <c r="H1177" t="s">
         <v>8</v>
@@ -31023,7 +31023,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1179" t="n">
-        <v>2.41584539413452</v>
+        <v>2.4158456325531</v>
       </c>
       <c r="H1179" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G1180" t="n">
-        <v>2.39788365364075</v>
+        <v>2.39788389205933</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1181" t="n">
-        <v>2.37992238998413</v>
+        <v>2.37992215156555</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>2.60500001907349</v>
       </c>
       <c r="G1183" t="n">
-        <v>2.33950805664062</v>
+        <v>2.33950853347778</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>2.625</v>
       </c>
       <c r="G1184" t="n">
-        <v>2.35747003555298</v>
+        <v>2.3574697971344</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31231,7 +31231,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G1187" t="n">
-        <v>2.39788365364075</v>
+        <v>2.39788389205933</v>
       </c>
       <c r="H1187" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1190" t="n">
-        <v>2.37992238998413</v>
+        <v>2.37992215156555</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>2.625</v>
       </c>
       <c r="G1192" t="n">
-        <v>2.35747003555298</v>
+        <v>2.3574697971344</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G1195" t="n">
-        <v>2.49667310714722</v>
+        <v>2.49667286872864</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G1199" t="n">
-        <v>2.29909443855286</v>
+        <v>2.29909467697144</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>2.57500004768372</v>
       </c>
       <c r="G1201" t="n">
-        <v>2.31256604194641</v>
+        <v>2.31256556510925</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G1202" t="n">
-        <v>2.29909443855286</v>
+        <v>2.29909467697144</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G1203" t="n">
-        <v>2.28113269805908</v>
+        <v>2.28113293647766</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31725,7 +31725,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1206" t="n">
-        <v>2.23622870445251</v>
+        <v>2.23622894287109</v>
       </c>
       <c r="H1206" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>2.6949999332428</v>
       </c>
       <c r="G1208" t="n">
-        <v>2.42033576965332</v>
+        <v>2.4203360080719</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31829,7 +31829,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G1210" t="n">
-        <v>2.29909443855286</v>
+        <v>2.29909467697144</v>
       </c>
       <c r="H1210" t="s">
         <v>8</v>
@@ -31881,7 +31881,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1212" t="n">
-        <v>2.37992238998413</v>
+        <v>2.37992215156555</v>
       </c>
       <c r="H1212" t="s">
         <v>8</v>
@@ -31907,7 +31907,7 @@
         <v>2.6949999332428</v>
       </c>
       <c r="G1213" t="n">
-        <v>2.42033576965332</v>
+        <v>2.4203360080719</v>
       </c>
       <c r="H1213" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1215" t="n">
-        <v>2.37992238998413</v>
+        <v>2.37992215156555</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -32011,7 +32011,7 @@
         <v>2.74499988555908</v>
       </c>
       <c r="G1217" t="n">
-        <v>2.46524000167847</v>
+        <v>2.46524024009705</v>
       </c>
       <c r="H1217" t="s">
         <v>8</v>
@@ -32037,7 +32037,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G1218" t="n">
-        <v>2.49667310714722</v>
+        <v>2.49667286872864</v>
       </c>
       <c r="H1218" t="s">
         <v>8</v>
@@ -32063,7 +32063,7 @@
         <v>2.79500007629395</v>
       </c>
       <c r="G1219" t="n">
-        <v>2.51014423370361</v>
+        <v>2.51014447212219</v>
       </c>
       <c r="H1219" t="s">
         <v>8</v>
@@ -32115,7 +32115,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1221" t="n">
-        <v>2.60444307327271</v>
+        <v>2.60444331169128</v>
       </c>
       <c r="H1221" t="s">
         <v>8</v>
@@ -32141,7 +32141,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G1222" t="n">
-        <v>2.57750058174133</v>
+        <v>2.57750034332275</v>
       </c>
       <c r="H1222" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>2.86500000953674</v>
       </c>
       <c r="G1223" t="n">
-        <v>2.57301044464111</v>
+        <v>2.57301020622253</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>2.75500011444092</v>
       </c>
       <c r="G1226" t="n">
-        <v>2.47422075271606</v>
+        <v>2.47422099113464</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32297,7 +32297,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G1228" t="n">
-        <v>2.3529794216156</v>
+        <v>2.35297966003418</v>
       </c>
       <c r="H1228" t="s">
         <v>8</v>
@@ -32349,7 +32349,7 @@
         <v>2.59500002861023</v>
       </c>
       <c r="G1230" t="n">
-        <v>2.33052730560303</v>
+        <v>2.33052754402161</v>
       </c>
       <c r="H1230" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>2.59500002861023</v>
       </c>
       <c r="G1231" t="n">
-        <v>2.33052730560303</v>
+        <v>2.33052754402161</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32479,7 +32479,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1235" t="n">
-        <v>2.37992238998413</v>
+        <v>2.37992215156555</v>
       </c>
       <c r="H1235" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1237" t="n">
-        <v>2.41584539413452</v>
+        <v>2.4158456325531</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -32557,7 +32557,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1238" t="n">
-        <v>2.37992238998413</v>
+        <v>2.37992215156555</v>
       </c>
       <c r="H1238" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1240" t="n">
-        <v>2.45176887512207</v>
+        <v>2.45176863670349</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1250" t="n">
-        <v>2.58648157119751</v>
+        <v>2.58648133277893</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1251" t="n">
-        <v>2.65832829475403</v>
+        <v>2.65832805633545</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1252" t="n">
-        <v>2.68527030944824</v>
+        <v>2.6852707862854</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1253" t="n">
-        <v>2.6762900352478</v>
+        <v>2.67628979682922</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>3</v>
       </c>
       <c r="G1254" t="n">
-        <v>2.69425129890442</v>
+        <v>2.694251537323</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -32999,7 +32999,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1255" t="n">
-        <v>2.74813675880432</v>
+        <v>2.74813652038574</v>
       </c>
       <c r="H1255" t="s">
         <v>8</v>
@@ -33025,7 +33025,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G1256" t="n">
-        <v>2.76160764694214</v>
+        <v>2.76160788536072</v>
       </c>
       <c r="H1256" t="s">
         <v>8</v>
@@ -33051,7 +33051,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1257" t="n">
-        <v>2.73915553092957</v>
+        <v>2.73915576934814</v>
       </c>
       <c r="H1257" t="s">
         <v>8</v>
@@ -33077,7 +33077,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1258" t="n">
-        <v>2.73017477989197</v>
+        <v>2.73017501831055</v>
       </c>
       <c r="H1258" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1261" t="n">
-        <v>2.78405976295471</v>
+        <v>2.78405952453613</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1263" t="n">
-        <v>2.84692573547363</v>
+        <v>2.84692549705505</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33233,7 +33233,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1264" t="n">
-        <v>2.83794498443604</v>
+        <v>2.83794474601746</v>
       </c>
       <c r="H1264" t="s">
         <v>8</v>
@@ -33363,7 +33363,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1269" t="n">
-        <v>2.78405976295471</v>
+        <v>2.78405952453613</v>
       </c>
       <c r="H1269" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1272" t="n">
-        <v>2.78405976295471</v>
+        <v>2.78405952453613</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33649,7 +33649,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1280" t="n">
-        <v>2.73017477989197</v>
+        <v>2.73017501831055</v>
       </c>
       <c r="H1280" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>2.9449999332428</v>
       </c>
       <c r="G1283" t="n">
-        <v>2.64485669136047</v>
+        <v>2.64485692977905</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33753,7 +33753,7 @@
         <v>3</v>
       </c>
       <c r="G1284" t="n">
-        <v>2.69425129890442</v>
+        <v>2.694251537323</v>
       </c>
       <c r="H1284" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G1286" t="n">
-        <v>2.54606747627258</v>
+        <v>2.54606771469116</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1287" t="n">
-        <v>2.65832829475403</v>
+        <v>2.65832805633545</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1288" t="n">
-        <v>2.60444307327271</v>
+        <v>2.60444331169128</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33883,7 +33883,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G1289" t="n">
-        <v>2.63138580322266</v>
+        <v>2.63138556480408</v>
       </c>
       <c r="H1289" t="s">
         <v>8</v>
@@ -33909,7 +33909,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1290" t="n">
-        <v>2.60444307327271</v>
+        <v>2.60444331169128</v>
       </c>
       <c r="H1290" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>3</v>
       </c>
       <c r="G1291" t="n">
-        <v>2.69425129890442</v>
+        <v>2.694251537323</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -34013,7 +34013,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G1294" t="n">
-        <v>2.76160764694214</v>
+        <v>2.76160788536072</v>
       </c>
       <c r="H1294" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1299" t="n">
-        <v>3.08940839767456</v>
+        <v>3.08940815925598</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34169,7 +34169,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G1300" t="n">
-        <v>3.12982177734375</v>
+        <v>3.12982201576233</v>
       </c>
       <c r="H1300" t="s">
         <v>8</v>
@@ -34273,7 +34273,7 @@
         <v>3.36500000953674</v>
       </c>
       <c r="G1304" t="n">
-        <v>3.02205228805542</v>
+        <v>3.02205204963684</v>
       </c>
       <c r="H1304" t="s">
         <v>8</v>
@@ -34299,7 +34299,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G1305" t="n">
-        <v>3.12982177734375</v>
+        <v>3.12982201576233</v>
       </c>
       <c r="H1305" t="s">
         <v>8</v>
@@ -34351,7 +34351,7 @@
         <v>3.42499995231628</v>
       </c>
       <c r="G1307" t="n">
-        <v>3.07593679428101</v>
+        <v>3.07593727111816</v>
       </c>
       <c r="H1307" t="s">
         <v>8</v>
@@ -34377,7 +34377,7 @@
         <v>3.42499995231628</v>
       </c>
       <c r="G1308" t="n">
-        <v>3.07593679428101</v>
+        <v>3.07593727111816</v>
       </c>
       <c r="H1308" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>3.33500003814697</v>
       </c>
       <c r="G1309" t="n">
-        <v>2.99510931968689</v>
+        <v>2.99510955810547</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>3.22499990463257</v>
       </c>
       <c r="G1310" t="n">
-        <v>2.896320104599</v>
+        <v>2.89632034301758</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34507,7 +34507,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1313" t="n">
-        <v>3.02654242515564</v>
+        <v>3.02654218673706</v>
       </c>
       <c r="H1313" t="s">
         <v>8</v>
@@ -34533,7 +34533,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1314" t="n">
-        <v>3.02654242515564</v>
+        <v>3.02654218673706</v>
       </c>
       <c r="H1314" t="s">
         <v>8</v>
@@ -34585,7 +34585,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1316" t="n">
-        <v>3.05348491668701</v>
+        <v>3.05348539352417</v>
       </c>
       <c r="H1316" t="s">
         <v>8</v>
@@ -34663,7 +34663,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1319" t="n">
-        <v>3.09838938713074</v>
+        <v>3.09838914871216</v>
       </c>
       <c r="H1319" t="s">
         <v>8</v>
@@ -34689,7 +34689,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1320" t="n">
-        <v>3.02654242515564</v>
+        <v>3.02654218673706</v>
       </c>
       <c r="H1320" t="s">
         <v>8</v>
@@ -34819,7 +34819,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1325" t="n">
-        <v>3.02654242515564</v>
+        <v>3.02654218673706</v>
       </c>
       <c r="H1325" t="s">
         <v>8</v>
@@ -34845,7 +34845,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1326" t="n">
-        <v>2.99959969520569</v>
+        <v>2.99959993362427</v>
       </c>
       <c r="H1326" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>3.3050000667572</v>
       </c>
       <c r="G1327" t="n">
-        <v>2.9681670665741</v>
+        <v>2.96816682815552</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -34923,7 +34923,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1329" t="n">
-        <v>3.03552341461182</v>
+        <v>3.03552317619324</v>
       </c>
       <c r="H1329" t="s">
         <v>8</v>
@@ -34975,7 +34975,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1331" t="n">
-        <v>3.00858092308044</v>
+        <v>3.00858068466187</v>
       </c>
       <c r="H1331" t="s">
         <v>8</v>
@@ -35027,7 +35027,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1333" t="n">
-        <v>3.03552341461182</v>
+        <v>3.03552317619324</v>
       </c>
       <c r="H1333" t="s">
         <v>8</v>
@@ -35053,7 +35053,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1334" t="n">
-        <v>3.02654242515564</v>
+        <v>3.02654218673706</v>
       </c>
       <c r="H1334" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1336" t="n">
-        <v>2.85590648651123</v>
+        <v>2.85590672492981</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35313,7 +35313,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1344" t="n">
-        <v>2.85590648651123</v>
+        <v>2.85590672492981</v>
       </c>
       <c r="H1344" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>3.14499998092651</v>
       </c>
       <c r="G1345" t="n">
-        <v>2.82447338104248</v>
+        <v>2.82447361946106</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35391,7 +35391,7 @@
         <v>3.25</v>
       </c>
       <c r="G1347" t="n">
-        <v>2.91877245903015</v>
+        <v>2.91877269744873</v>
       </c>
       <c r="H1347" t="s">
         <v>8</v>
@@ -35417,7 +35417,7 @@
         <v>3.34500002861023</v>
       </c>
       <c r="G1348" t="n">
-        <v>3.00409054756165</v>
+        <v>3.00409030914307</v>
       </c>
       <c r="H1348" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1349" t="n">
-        <v>3.05348491668701</v>
+        <v>3.05348539352417</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35495,7 +35495,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1351" t="n">
-        <v>3.08940839767456</v>
+        <v>3.08940815925598</v>
       </c>
       <c r="H1351" t="s">
         <v>8</v>
@@ -35521,7 +35521,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1352" t="n">
-        <v>3.08940839767456</v>
+        <v>3.08940815925598</v>
       </c>
       <c r="H1352" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1353" t="n">
-        <v>3.08940839767456</v>
+        <v>3.08940815925598</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35573,7 +35573,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1354" t="n">
-        <v>3.05348491668701</v>
+        <v>3.05348539352417</v>
       </c>
       <c r="H1354" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1356" t="n">
-        <v>3.21514010429382</v>
+        <v>3.21513986587524</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35651,7 +35651,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G1357" t="n">
-        <v>3.28249621391296</v>
+        <v>3.28249645233154</v>
       </c>
       <c r="H1357" t="s">
         <v>8</v>
@@ -35677,7 +35677,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1358" t="n">
-        <v>3.30494832992554</v>
+        <v>3.30494856834412</v>
       </c>
       <c r="H1358" t="s">
         <v>8</v>
@@ -35729,7 +35729,7 @@
         <v>3.60500001907349</v>
       </c>
       <c r="G1360" t="n">
-        <v>3.23759245872498</v>
+        <v>3.2375922203064</v>
       </c>
       <c r="H1360" t="s">
         <v>8</v>
@@ -35755,7 +35755,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G1361" t="n">
-        <v>3.29147720336914</v>
+        <v>3.29147696495056</v>
       </c>
       <c r="H1361" t="s">
         <v>8</v>
@@ -35807,7 +35807,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1363" t="n">
-        <v>3.18819737434387</v>
+        <v>3.18819761276245</v>
       </c>
       <c r="H1363" t="s">
         <v>8</v>
@@ -35911,7 +35911,7 @@
         <v>3.46499991416931</v>
       </c>
       <c r="G1367" t="n">
-        <v>3.11186027526855</v>
+        <v>3.11186003684998</v>
       </c>
       <c r="H1367" t="s">
         <v>8</v>
@@ -35937,7 +35937,7 @@
         <v>3.46499991416931</v>
       </c>
       <c r="G1368" t="n">
-        <v>3.11186027526855</v>
+        <v>3.11186003684998</v>
       </c>
       <c r="H1368" t="s">
         <v>8</v>
@@ -35963,7 +35963,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1369" t="n">
-        <v>3.11635065078735</v>
+        <v>3.11635112762451</v>
       </c>
       <c r="H1369" t="s">
         <v>8</v>
@@ -35989,7 +35989,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1370" t="n">
-        <v>3.12533164024353</v>
+        <v>3.12533187866211</v>
       </c>
       <c r="H1370" t="s">
         <v>8</v>
@@ -36041,7 +36041,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1372" t="n">
-        <v>3.05348491668701</v>
+        <v>3.05348539352417</v>
       </c>
       <c r="H1372" t="s">
         <v>8</v>
@@ -36093,7 +36093,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1374" t="n">
-        <v>3.08940839767456</v>
+        <v>3.08940815925598</v>
       </c>
       <c r="H1374" t="s">
         <v>8</v>
@@ -36171,7 +36171,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1377" t="n">
-        <v>3.08940839767456</v>
+        <v>3.08940815925598</v>
       </c>
       <c r="H1377" t="s">
         <v>8</v>
@@ -36197,7 +36197,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1378" t="n">
-        <v>3.08940839767456</v>
+        <v>3.08940815925598</v>
       </c>
       <c r="H1378" t="s">
         <v>8</v>
@@ -36249,7 +36249,7 @@
         <v>3.40499997138977</v>
       </c>
       <c r="G1380" t="n">
-        <v>3.05797529220581</v>
+        <v>3.05797553062439</v>
       </c>
       <c r="H1380" t="s">
         <v>8</v>
@@ -36405,7 +36405,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1386" t="n">
-        <v>3.13431239128113</v>
+        <v>3.13431262969971</v>
       </c>
       <c r="H1386" t="s">
         <v>8</v>
@@ -36509,7 +36509,7 @@
         <v>3.33500003814697</v>
       </c>
       <c r="G1390" t="n">
-        <v>2.99510931968689</v>
+        <v>2.99510955810547</v>
       </c>
       <c r="H1390" t="s">
         <v>8</v>
@@ -36691,7 +36691,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1397" t="n">
-        <v>3.21514010429382</v>
+        <v>3.21513986587524</v>
       </c>
       <c r="H1397" t="s">
         <v>8</v>
@@ -36717,7 +36717,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1398" t="n">
-        <v>3.2331018447876</v>
+        <v>3.23310160636902</v>
       </c>
       <c r="H1398" t="s">
         <v>8</v>
@@ -36821,7 +36821,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1402" t="n">
-        <v>3.13431239128113</v>
+        <v>3.13431262969971</v>
       </c>
       <c r="H1402" t="s">
         <v>8</v>
@@ -36847,7 +36847,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1403" t="n">
-        <v>3.00858092308044</v>
+        <v>3.00858068466187</v>
       </c>
       <c r="H1403" t="s">
         <v>8</v>
@@ -36925,7 +36925,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1406" t="n">
-        <v>3.00858092308044</v>
+        <v>3.00858068466187</v>
       </c>
       <c r="H1406" t="s">
         <v>8</v>
@@ -36977,7 +36977,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1408" t="n">
-        <v>3.00858092308044</v>
+        <v>3.00858068466187</v>
       </c>
       <c r="H1408" t="s">
         <v>8</v>
@@ -37003,7 +37003,7 @@
         <v>3.23499989509583</v>
       </c>
       <c r="G1409" t="n">
-        <v>2.90530109405518</v>
+        <v>2.9053008556366</v>
       </c>
       <c r="H1409" t="s">
         <v>8</v>
@@ -37029,7 +37029,7 @@
         <v>3.23499989509583</v>
       </c>
       <c r="G1410" t="n">
-        <v>2.90530109405518</v>
+        <v>2.9053008556366</v>
       </c>
       <c r="H1410" t="s">
         <v>8</v>
@@ -37055,7 +37055,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1411" t="n">
-        <v>3.02654242515564</v>
+        <v>3.02654218673706</v>
       </c>
       <c r="H1411" t="s">
         <v>8</v>
@@ -37081,7 +37081,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1412" t="n">
-        <v>3.00858092308044</v>
+        <v>3.00858068466187</v>
       </c>
       <c r="H1412" t="s">
         <v>8</v>
@@ -37185,7 +37185,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1416" t="n">
-        <v>3.00858092308044</v>
+        <v>3.00858068466187</v>
       </c>
       <c r="H1416" t="s">
         <v>8</v>
@@ -37237,7 +37237,7 @@
         <v>3.34500002861023</v>
       </c>
       <c r="G1418" t="n">
-        <v>3.00409054756165</v>
+        <v>3.00409030914307</v>
       </c>
       <c r="H1418" t="s">
         <v>8</v>
@@ -37289,7 +37289,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1420" t="n">
-        <v>2.97265720367432</v>
+        <v>2.9726574420929</v>
       </c>
       <c r="H1420" t="s">
         <v>8</v>
@@ -37315,7 +37315,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1421" t="n">
-        <v>2.94571495056152</v>
+        <v>2.94571471214294</v>
       </c>
       <c r="H1421" t="s">
         <v>8</v>
@@ -37341,7 +37341,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1422" t="n">
-        <v>2.97265720367432</v>
+        <v>2.9726574420929</v>
       </c>
       <c r="H1422" t="s">
         <v>8</v>
@@ -37367,7 +37367,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1423" t="n">
-        <v>2.96367692947388</v>
+        <v>2.96367645263672</v>
       </c>
       <c r="H1423" t="s">
         <v>8</v>
@@ -37419,7 +37419,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1425" t="n">
-        <v>2.94571495056152</v>
+        <v>2.94571471214294</v>
       </c>
       <c r="H1425" t="s">
         <v>8</v>
@@ -37445,7 +37445,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1426" t="n">
-        <v>2.97265720367432</v>
+        <v>2.9726574420929</v>
       </c>
       <c r="H1426" t="s">
         <v>8</v>
@@ -37575,7 +37575,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1431" t="n">
-        <v>3.00858092308044</v>
+        <v>3.00858068466187</v>
       </c>
       <c r="H1431" t="s">
         <v>8</v>
@@ -37601,7 +37601,7 @@
         <v>3.33500003814697</v>
       </c>
       <c r="G1432" t="n">
-        <v>2.99510931968689</v>
+        <v>2.99510955810547</v>
       </c>
       <c r="H1432" t="s">
         <v>8</v>
@@ -37653,7 +37653,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G1434" t="n">
-        <v>2.95918607711792</v>
+        <v>2.9591863155365</v>
       </c>
       <c r="H1434" t="s">
         <v>8</v>
@@ -37679,7 +37679,7 @@
         <v>3.3050000667572</v>
       </c>
       <c r="G1435" t="n">
-        <v>2.9681670665741</v>
+        <v>2.96816682815552</v>
       </c>
       <c r="H1435" t="s">
         <v>8</v>
@@ -37705,7 +37705,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1436" t="n">
-        <v>2.93673396110535</v>
+        <v>2.93673419952393</v>
       </c>
       <c r="H1436" t="s">
         <v>8</v>
@@ -37731,7 +37731,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1437" t="n">
-        <v>2.93673396110535</v>
+        <v>2.93673419952393</v>
       </c>
       <c r="H1437" t="s">
         <v>8</v>
@@ -37757,7 +37757,7 @@
         <v>3.25</v>
       </c>
       <c r="G1438" t="n">
-        <v>2.91877245903015</v>
+        <v>2.91877269744873</v>
       </c>
       <c r="H1438" t="s">
         <v>8</v>
@@ -37783,7 +37783,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1439" t="n">
-        <v>2.93673396110535</v>
+        <v>2.93673419952393</v>
       </c>
       <c r="H1439" t="s">
         <v>8</v>
@@ -37913,7 +37913,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1444" t="n">
-        <v>2.94571495056152</v>
+        <v>2.94571471214294</v>
       </c>
       <c r="H1444" t="s">
         <v>8</v>
@@ -37939,7 +37939,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1445" t="n">
-        <v>2.93673396110535</v>
+        <v>2.93673419952393</v>
       </c>
       <c r="H1445" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>3.25500011444092</v>
       </c>
       <c r="G1447" t="n">
-        <v>2.92326307296753</v>
+        <v>2.92326283454895</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38017,7 +38017,7 @@
         <v>3.25</v>
       </c>
       <c r="G1448" t="n">
-        <v>2.91877245903015</v>
+        <v>2.91877269744873</v>
       </c>
       <c r="H1448" t="s">
         <v>8</v>
@@ -38043,7 +38043,7 @@
         <v>3.22499990463257</v>
       </c>
       <c r="G1449" t="n">
-        <v>2.896320104599</v>
+        <v>2.89632034301758</v>
       </c>
       <c r="H1449" t="s">
         <v>8</v>
@@ -38069,7 +38069,7 @@
         <v>3.22499990463257</v>
       </c>
       <c r="G1450" t="n">
-        <v>2.896320104599</v>
+        <v>2.89632034301758</v>
       </c>
       <c r="H1450" t="s">
         <v>8</v>
@@ -38121,7 +38121,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1452" t="n">
-        <v>2.88284921646118</v>
+        <v>2.8828489780426</v>
       </c>
       <c r="H1452" t="s">
         <v>8</v>
@@ -38147,7 +38147,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1453" t="n">
-        <v>2.88284921646118</v>
+        <v>2.8828489780426</v>
       </c>
       <c r="H1453" t="s">
         <v>8</v>
@@ -38225,7 +38225,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G1456" t="n">
-        <v>2.91428160667419</v>
+        <v>2.91428184509277</v>
       </c>
       <c r="H1456" t="s">
         <v>8</v>
@@ -38251,7 +38251,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1457" t="n">
-        <v>2.88284921646118</v>
+        <v>2.8828489780426</v>
       </c>
       <c r="H1457" t="s">
         <v>8</v>
@@ -38277,7 +38277,7 @@
         <v>3.25</v>
       </c>
       <c r="G1458" t="n">
-        <v>2.91877245903015</v>
+        <v>2.91877269744873</v>
       </c>
       <c r="H1458" t="s">
         <v>8</v>
@@ -38303,7 +38303,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1459" t="n">
-        <v>3.08940839767456</v>
+        <v>3.08940815925598</v>
       </c>
       <c r="H1459" t="s">
         <v>8</v>
@@ -38329,7 +38329,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1460" t="n">
-        <v>3.05348491668701</v>
+        <v>3.05348539352417</v>
       </c>
       <c r="H1460" t="s">
         <v>8</v>
@@ -38355,7 +38355,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1461" t="n">
-        <v>3.09838938713074</v>
+        <v>3.09838914871216</v>
       </c>
       <c r="H1461" t="s">
         <v>8</v>
@@ -38407,7 +38407,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1463" t="n">
-        <v>3.05348491668701</v>
+        <v>3.05348539352417</v>
       </c>
       <c r="H1463" t="s">
         <v>8</v>
@@ -38459,7 +38459,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1465" t="n">
-        <v>3.02654242515564</v>
+        <v>3.02654218673706</v>
       </c>
       <c r="H1465" t="s">
         <v>8</v>
@@ -38485,7 +38485,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1466" t="n">
-        <v>2.96367692947388</v>
+        <v>2.96367645263672</v>
       </c>
       <c r="H1466" t="s">
         <v>8</v>
@@ -38511,7 +38511,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1467" t="n">
-        <v>3.02654242515564</v>
+        <v>3.02654218673706</v>
       </c>
       <c r="H1467" t="s">
         <v>8</v>
@@ -38537,7 +38537,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1468" t="n">
-        <v>2.99959969520569</v>
+        <v>2.99959993362427</v>
       </c>
       <c r="H1468" t="s">
         <v>8</v>
@@ -38615,7 +38615,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1471" t="n">
-        <v>2.94571495056152</v>
+        <v>2.94571471214294</v>
       </c>
       <c r="H1471" t="s">
         <v>8</v>
@@ -38693,7 +38693,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1474" t="n">
-        <v>3.08940839767456</v>
+        <v>3.08940815925598</v>
       </c>
       <c r="H1474" t="s">
         <v>8</v>
@@ -38719,7 +38719,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1475" t="n">
-        <v>3.09838938713074</v>
+        <v>3.09838914871216</v>
       </c>
       <c r="H1475" t="s">
         <v>8</v>
@@ -38745,7 +38745,7 @@
         <v>3.45499992370605</v>
       </c>
       <c r="G1476" t="n">
-        <v>3.10287976264954</v>
+        <v>3.10287952423096</v>
       </c>
       <c r="H1476" t="s">
         <v>8</v>
@@ -38797,7 +38797,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1478" t="n">
-        <v>3.12533164024353</v>
+        <v>3.12533187866211</v>
       </c>
       <c r="H1478" t="s">
         <v>8</v>
@@ -38823,7 +38823,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1479" t="n">
-        <v>3.12533164024353</v>
+        <v>3.12533187866211</v>
       </c>
       <c r="H1479" t="s">
         <v>8</v>
@@ -38901,7 +38901,7 @@
         <v>3.625</v>
       </c>
       <c r="G1482" t="n">
-        <v>3.25555372238159</v>
+        <v>3.25555396080017</v>
       </c>
       <c r="H1482" t="s">
         <v>8</v>
@@ -38953,7 +38953,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1484" t="n">
-        <v>3.2331018447876</v>
+        <v>3.23310160636902</v>
       </c>
       <c r="H1484" t="s">
         <v>8</v>
@@ -38979,7 +38979,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1485" t="n">
-        <v>3.1522741317749</v>
+        <v>3.15227389335632</v>
       </c>
       <c r="H1485" t="s">
         <v>8</v>
@@ -39057,7 +39057,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1488" t="n">
-        <v>3.21514010429382</v>
+        <v>3.21513986587524</v>
       </c>
       <c r="H1488" t="s">
         <v>8</v>
@@ -39083,7 +39083,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1489" t="n">
-        <v>3.2331018447876</v>
+        <v>3.23310160636902</v>
       </c>
       <c r="H1489" t="s">
         <v>8</v>
@@ -39109,7 +39109,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1490" t="n">
-        <v>3.2331018447876</v>
+        <v>3.23310160636902</v>
       </c>
       <c r="H1490" t="s">
         <v>8</v>
@@ -39135,7 +39135,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1491" t="n">
-        <v>3.2331018447876</v>
+        <v>3.23310160636902</v>
       </c>
       <c r="H1491" t="s">
         <v>8</v>
@@ -39187,7 +39187,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1493" t="n">
-        <v>3.2420825958252</v>
+        <v>3.24208235740662</v>
       </c>
       <c r="H1493" t="s">
         <v>8</v>
@@ -39239,7 +39239,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1495" t="n">
-        <v>3.2420825958252</v>
+        <v>3.24208235740662</v>
       </c>
       <c r="H1495" t="s">
         <v>8</v>
@@ -39291,7 +39291,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1497" t="n">
-        <v>3.10737013816833</v>
+        <v>3.10736989974976</v>
       </c>
       <c r="H1497" t="s">
         <v>8</v>
@@ -39369,7 +39369,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1500" t="n">
-        <v>3.09838938713074</v>
+        <v>3.09838914871216</v>
       </c>
       <c r="H1500" t="s">
         <v>8</v>
@@ -39447,7 +39447,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1503" t="n">
-        <v>3.13431239128113</v>
+        <v>3.13431262969971</v>
       </c>
       <c r="H1503" t="s">
         <v>8</v>
@@ -39473,7 +39473,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1504" t="n">
-        <v>3.11635065078735</v>
+        <v>3.11635112762451</v>
       </c>
       <c r="H1504" t="s">
         <v>8</v>
@@ -39525,7 +39525,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1506" t="n">
-        <v>3.13431239128113</v>
+        <v>3.13431262969971</v>
       </c>
       <c r="H1506" t="s">
         <v>8</v>
@@ -39551,7 +39551,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1507" t="n">
-        <v>3.08940839767456</v>
+        <v>3.08940815925598</v>
       </c>
       <c r="H1507" t="s">
         <v>8</v>
@@ -39577,7 +39577,7 @@
         <v>3.46499991416931</v>
       </c>
       <c r="G1508" t="n">
-        <v>3.11186027526855</v>
+        <v>3.11186003684998</v>
       </c>
       <c r="H1508" t="s">
         <v>8</v>
@@ -39629,7 +39629,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1510" t="n">
-        <v>3.10737013816833</v>
+        <v>3.10736989974976</v>
       </c>
       <c r="H1510" t="s">
         <v>8</v>
@@ -39655,7 +39655,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1511" t="n">
-        <v>3.10737013816833</v>
+        <v>3.10736989974976</v>
       </c>
       <c r="H1511" t="s">
         <v>8</v>
@@ -39863,7 +39863,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1519" t="n">
-        <v>3.30494832992554</v>
+        <v>3.30494856834412</v>
       </c>
       <c r="H1519" t="s">
         <v>8</v>
@@ -40019,7 +40019,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1525" t="n">
-        <v>3.30494832992554</v>
+        <v>3.30494856834412</v>
       </c>
       <c r="H1525" t="s">
         <v>8</v>
@@ -40045,7 +40045,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G1526" t="n">
-        <v>3.27351570129395</v>
+        <v>3.27351546287537</v>
       </c>
       <c r="H1526" t="s">
         <v>8</v>
@@ -40149,7 +40149,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1530" t="n">
-        <v>3.2331018447876</v>
+        <v>3.23310160636902</v>
       </c>
       <c r="H1530" t="s">
         <v>8</v>
@@ -40305,7 +40305,7 @@
         <v>3.42499995231628</v>
       </c>
       <c r="G1536" t="n">
-        <v>3.07593679428101</v>
+        <v>3.07593727111816</v>
       </c>
       <c r="H1536" t="s">
         <v>8</v>
@@ -40331,7 +40331,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1537" t="n">
-        <v>3.09838938713074</v>
+        <v>3.09838914871216</v>
       </c>
       <c r="H1537" t="s">
         <v>8</v>
@@ -40357,7 +40357,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1538" t="n">
-        <v>3.10737013816833</v>
+        <v>3.10736989974976</v>
       </c>
       <c r="H1538" t="s">
         <v>8</v>
@@ -40435,7 +40435,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1541" t="n">
-        <v>3.08940839767456</v>
+        <v>3.08940815925598</v>
       </c>
       <c r="H1541" t="s">
         <v>8</v>
@@ -40487,7 +40487,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1543" t="n">
-        <v>3.00858092308044</v>
+        <v>3.00858068466187</v>
       </c>
       <c r="H1543" t="s">
         <v>8</v>
@@ -40591,7 +40591,7 @@
         <v>3.40499997138977</v>
       </c>
       <c r="G1547" t="n">
-        <v>3.05797529220581</v>
+        <v>3.05797553062439</v>
       </c>
       <c r="H1547" t="s">
         <v>8</v>
@@ -40617,7 +40617,7 @@
         <v>3.46499991416931</v>
       </c>
       <c r="G1548" t="n">
-        <v>3.11186027526855</v>
+        <v>3.11186003684998</v>
       </c>
       <c r="H1548" t="s">
         <v>8</v>
@@ -40669,7 +40669,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1550" t="n">
-        <v>3.11635065078735</v>
+        <v>3.11635112762451</v>
       </c>
       <c r="H1550" t="s">
         <v>8</v>
@@ -40695,7 +40695,7 @@
         <v>3.40499997138977</v>
       </c>
       <c r="G1551" t="n">
-        <v>3.05797529220581</v>
+        <v>3.05797553062439</v>
       </c>
       <c r="H1551" t="s">
         <v>8</v>
@@ -40747,7 +40747,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G1553" t="n">
-        <v>2.95918607711792</v>
+        <v>2.9591863155365</v>
       </c>
       <c r="H1553" t="s">
         <v>8</v>
@@ -40773,7 +40773,7 @@
         <v>3.36500000953674</v>
       </c>
       <c r="G1554" t="n">
-        <v>3.02205228805542</v>
+        <v>3.02205204963684</v>
       </c>
       <c r="H1554" t="s">
         <v>8</v>
@@ -40825,7 +40825,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1556" t="n">
-        <v>3.00858092308044</v>
+        <v>3.00858068466187</v>
       </c>
       <c r="H1556" t="s">
         <v>8</v>
@@ -40851,7 +40851,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1557" t="n">
-        <v>2.93673396110535</v>
+        <v>2.93673419952393</v>
       </c>
       <c r="H1557" t="s">
         <v>8</v>
@@ -40877,7 +40877,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1558" t="n">
-        <v>3.05348491668701</v>
+        <v>3.05348539352417</v>
       </c>
       <c r="H1558" t="s">
         <v>8</v>
@@ -40903,7 +40903,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1559" t="n">
-        <v>3.03552341461182</v>
+        <v>3.03552317619324</v>
       </c>
       <c r="H1559" t="s">
         <v>8</v>
@@ -40929,7 +40929,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1560" t="n">
-        <v>2.99959969520569</v>
+        <v>2.99959993362427</v>
       </c>
       <c r="H1560" t="s">
         <v>8</v>
@@ -40955,7 +40955,7 @@
         <v>3.34500002861023</v>
       </c>
       <c r="G1561" t="n">
-        <v>3.00409054756165</v>
+        <v>3.00409030914307</v>
       </c>
       <c r="H1561" t="s">
         <v>8</v>
@@ -40981,7 +40981,7 @@
         <v>3.25500011444092</v>
       </c>
       <c r="G1562" t="n">
-        <v>2.92326307296753</v>
+        <v>2.92326283454895</v>
       </c>
       <c r="H1562" t="s">
         <v>8</v>
@@ -41007,7 +41007,7 @@
         <v>3.25</v>
       </c>
       <c r="G1563" t="n">
-        <v>2.91877245903015</v>
+        <v>2.91877269744873</v>
       </c>
       <c r="H1563" t="s">
         <v>8</v>
@@ -41059,7 +41059,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1565" t="n">
-        <v>2.74813675880432</v>
+        <v>2.74813652038574</v>
       </c>
       <c r="H1565" t="s">
         <v>8</v>
@@ -41085,7 +41085,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1566" t="n">
-        <v>2.76609778404236</v>
+        <v>2.76609802246094</v>
       </c>
       <c r="H1566" t="s">
         <v>8</v>
@@ -41137,7 +41137,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1568" t="n">
-        <v>2.7032322883606</v>
+        <v>2.70323204994202</v>
       </c>
       <c r="H1568" t="s">
         <v>8</v>
@@ -41163,7 +41163,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G1569" t="n">
-        <v>2.63138580322266</v>
+        <v>2.63138556480408</v>
       </c>
       <c r="H1569" t="s">
         <v>8</v>
@@ -41189,7 +41189,7 @@
         <v>2.95499992370605</v>
       </c>
       <c r="G1570" t="n">
-        <v>2.65383791923523</v>
+        <v>2.65383768081665</v>
       </c>
       <c r="H1570" t="s">
         <v>8</v>
@@ -41241,7 +41241,7 @@
         <v>2.88499999046326</v>
       </c>
       <c r="G1572" t="n">
-        <v>2.59097170829773</v>
+        <v>2.59097194671631</v>
       </c>
       <c r="H1572" t="s">
         <v>8</v>
@@ -41293,7 +41293,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G1574" t="n">
-        <v>2.57750058174133</v>
+        <v>2.57750034332275</v>
       </c>
       <c r="H1574" t="s">
         <v>8</v>
@@ -41319,7 +41319,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1575" t="n">
-        <v>2.55055785179138</v>
+        <v>2.55055809020996</v>
       </c>
       <c r="H1575" t="s">
         <v>8</v>
@@ -41345,7 +41345,7 @@
         <v>2.9449999332428</v>
       </c>
       <c r="G1576" t="n">
-        <v>2.64485669136047</v>
+        <v>2.64485692977905</v>
       </c>
       <c r="H1576" t="s">
         <v>8</v>
@@ -41371,7 +41371,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1577" t="n">
-        <v>2.6762900352478</v>
+        <v>2.67628979682922</v>
       </c>
       <c r="H1577" t="s">
         <v>8</v>
@@ -41449,7 +41449,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1580" t="n">
-        <v>2.76609778404236</v>
+        <v>2.76609802246094</v>
       </c>
       <c r="H1580" t="s">
         <v>8</v>
@@ -41501,7 +41501,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1582" t="n">
-        <v>2.78405976295471</v>
+        <v>2.78405952453613</v>
       </c>
       <c r="H1582" t="s">
         <v>8</v>
@@ -41683,7 +41683,7 @@
         <v>3.14499998092651</v>
       </c>
       <c r="G1589" t="n">
-        <v>2.82447338104248</v>
+        <v>2.82447361946106</v>
       </c>
       <c r="H1589" t="s">
         <v>8</v>
@@ -41709,7 +41709,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1590" t="n">
-        <v>2.85590648651123</v>
+        <v>2.85590672492981</v>
       </c>
       <c r="H1590" t="s">
         <v>8</v>
@@ -41735,7 +41735,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1591" t="n">
-        <v>2.88284921646118</v>
+        <v>2.8828489780426</v>
       </c>
       <c r="H1591" t="s">
         <v>8</v>
@@ -41813,7 +41813,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G1594" t="n">
-        <v>2.76160764694214</v>
+        <v>2.76160788536072</v>
       </c>
       <c r="H1594" t="s">
         <v>8</v>
@@ -41943,7 +41943,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1599" t="n">
-        <v>2.78405976295471</v>
+        <v>2.78405952453613</v>
       </c>
       <c r="H1599" t="s">
         <v>8</v>
@@ -41969,7 +41969,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1600" t="n">
-        <v>2.96367692947388</v>
+        <v>2.96367645263672</v>
       </c>
       <c r="H1600" t="s">
         <v>8</v>
@@ -42047,7 +42047,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1603" t="n">
-        <v>2.99959969520569</v>
+        <v>2.99959993362427</v>
       </c>
       <c r="H1603" t="s">
         <v>8</v>
@@ -42073,7 +42073,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1604" t="n">
-        <v>2.99959969520569</v>
+        <v>2.99959993362427</v>
       </c>
       <c r="H1604" t="s">
         <v>8</v>
@@ -42099,7 +42099,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1605" t="n">
-        <v>3.03552341461182</v>
+        <v>3.03552317619324</v>
       </c>
       <c r="H1605" t="s">
         <v>8</v>
@@ -42177,7 +42177,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1608" t="n">
-        <v>3.05348491668701</v>
+        <v>3.05348539352417</v>
       </c>
       <c r="H1608" t="s">
         <v>8</v>
@@ -42203,7 +42203,7 @@
         <v>3.36500000953674</v>
       </c>
       <c r="G1609" t="n">
-        <v>3.02205228805542</v>
+        <v>3.02205204963684</v>
       </c>
       <c r="H1609" t="s">
         <v>8</v>
@@ -42333,7 +42333,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1614" t="n">
-        <v>2.74813675880432</v>
+        <v>2.74813652038574</v>
       </c>
       <c r="H1614" t="s">
         <v>8</v>
@@ -42359,7 +42359,7 @@
         <v>2.95499992370605</v>
       </c>
       <c r="G1615" t="n">
-        <v>2.65383791923523</v>
+        <v>2.65383768081665</v>
       </c>
       <c r="H1615" t="s">
         <v>8</v>
@@ -42385,7 +42385,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1616" t="n">
-        <v>2.71221327781677</v>
+        <v>2.71221303939819</v>
       </c>
       <c r="H1616" t="s">
         <v>8</v>
@@ -42437,7 +42437,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1618" t="n">
-        <v>2.84692573547363</v>
+        <v>2.84692549705505</v>
       </c>
       <c r="H1618" t="s">
         <v>8</v>
@@ -42515,7 +42515,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1621" t="n">
-        <v>2.84692573547363</v>
+        <v>2.84692549705505</v>
       </c>
       <c r="H1621" t="s">
         <v>8</v>
@@ -42541,7 +42541,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G1622" t="n">
-        <v>2.91428160667419</v>
+        <v>2.91428184509277</v>
       </c>
       <c r="H1622" t="s">
         <v>8</v>
@@ -42619,7 +42619,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1625" t="n">
-        <v>2.88284921646118</v>
+        <v>2.8828489780426</v>
       </c>
       <c r="H1625" t="s">
         <v>8</v>
@@ -42749,7 +42749,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1630" t="n">
-        <v>2.73915553092957</v>
+        <v>2.73915576934814</v>
       </c>
       <c r="H1630" t="s">
         <v>8</v>
@@ -42775,7 +42775,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1631" t="n">
-        <v>2.74813675880432</v>
+        <v>2.74813652038574</v>
       </c>
       <c r="H1631" t="s">
         <v>8</v>
@@ -42827,7 +42827,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G1633" t="n">
-        <v>2.74364614486694</v>
+        <v>2.74364590644836</v>
       </c>
       <c r="H1633" t="s">
         <v>8</v>
@@ -42983,7 +42983,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1639" t="n">
-        <v>2.68527030944824</v>
+        <v>2.6852707862854</v>
       </c>
       <c r="H1639" t="s">
         <v>8</v>
@@ -43061,7 +43061,7 @@
         <v>2.98499989509583</v>
       </c>
       <c r="G1642" t="n">
-        <v>2.68078017234802</v>
+        <v>2.68077993392944</v>
       </c>
       <c r="H1642" t="s">
         <v>8</v>
@@ -43113,7 +43113,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1644" t="n">
-        <v>2.6762900352478</v>
+        <v>2.67628979682922</v>
       </c>
       <c r="H1644" t="s">
         <v>8</v>
@@ -43165,7 +43165,7 @@
         <v>2.98499989509583</v>
       </c>
       <c r="G1646" t="n">
-        <v>2.68078017234802</v>
+        <v>2.68077993392944</v>
       </c>
       <c r="H1646" t="s">
         <v>8</v>
@@ -43243,7 +43243,7 @@
         <v>2.79500007629395</v>
       </c>
       <c r="G1649" t="n">
-        <v>2.51014423370361</v>
+        <v>2.51014447212219</v>
       </c>
       <c r="H1649" t="s">
         <v>8</v>
@@ -43373,7 +43373,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1654" t="n">
-        <v>2.45176887512207</v>
+        <v>2.45176863670349</v>
       </c>
       <c r="H1654" t="s">
         <v>8</v>
@@ -43425,7 +43425,7 @@
         <v>2.71499991416931</v>
       </c>
       <c r="G1656" t="n">
-        <v>2.43829774856567</v>
+        <v>2.43829727172852</v>
       </c>
       <c r="H1656" t="s">
         <v>8</v>
@@ -43529,7 +43529,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G1660" t="n">
-        <v>2.57750058174133</v>
+        <v>2.57750034332275</v>
       </c>
       <c r="H1660" t="s">
         <v>8</v>
@@ -43659,7 +43659,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1665" t="n">
-        <v>2.55055785179138</v>
+        <v>2.55055809020996</v>
       </c>
       <c r="H1665" t="s">
         <v>8</v>
@@ -43763,7 +43763,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G1669" t="n">
-        <v>2.57750058174133</v>
+        <v>2.57750034332275</v>
       </c>
       <c r="H1669" t="s">
         <v>8</v>
@@ -43789,7 +43789,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1670" t="n">
-        <v>2.55055785179138</v>
+        <v>2.55055809020996</v>
       </c>
       <c r="H1670" t="s">
         <v>8</v>
@@ -43867,7 +43867,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1673" t="n">
-        <v>2.51463460922241</v>
+        <v>2.51463437080383</v>
       </c>
       <c r="H1673" t="s">
         <v>8</v>
@@ -43893,7 +43893,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1674" t="n">
-        <v>2.55055785179138</v>
+        <v>2.55055809020996</v>
       </c>
       <c r="H1674" t="s">
         <v>8</v>
@@ -43919,7 +43919,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G1675" t="n">
-        <v>2.54606747627258</v>
+        <v>2.54606771469116</v>
       </c>
       <c r="H1675" t="s">
         <v>8</v>
@@ -43945,7 +43945,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1676" t="n">
-        <v>2.60444307327271</v>
+        <v>2.60444331169128</v>
       </c>
       <c r="H1676" t="s">
         <v>8</v>
@@ -43971,7 +43971,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1677" t="n">
-        <v>2.60444307327271</v>
+        <v>2.60444331169128</v>
       </c>
       <c r="H1677" t="s">
         <v>8</v>
@@ -44023,7 +44023,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1679" t="n">
-        <v>2.60444307327271</v>
+        <v>2.60444331169128</v>
       </c>
       <c r="H1679" t="s">
         <v>8</v>
@@ -44127,7 +44127,7 @@
         <v>2.875</v>
       </c>
       <c r="G1683" t="n">
-        <v>2.58199095726013</v>
+        <v>2.58199071884155</v>
       </c>
       <c r="H1683" t="s">
         <v>8</v>
@@ -44153,7 +44153,7 @@
         <v>2.88499999046326</v>
       </c>
       <c r="G1684" t="n">
-        <v>2.59097170829773</v>
+        <v>2.59097194671631</v>
       </c>
       <c r="H1684" t="s">
         <v>8</v>
@@ -44179,7 +44179,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1685" t="n">
-        <v>2.60444307327271</v>
+        <v>2.60444331169128</v>
       </c>
       <c r="H1685" t="s">
         <v>8</v>
@@ -44231,7 +44231,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1687" t="n">
-        <v>2.76609778404236</v>
+        <v>2.76609802246094</v>
       </c>
       <c r="H1687" t="s">
         <v>8</v>
@@ -44257,7 +44257,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1688" t="n">
-        <v>2.78405976295471</v>
+        <v>2.78405952453613</v>
       </c>
       <c r="H1688" t="s">
         <v>8</v>
@@ -44309,7 +44309,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1690" t="n">
-        <v>2.71221327781677</v>
+        <v>2.71221303939819</v>
       </c>
       <c r="H1690" t="s">
         <v>8</v>
@@ -44335,7 +44335,7 @@
         <v>3</v>
       </c>
       <c r="G1691" t="n">
-        <v>2.69425129890442</v>
+        <v>2.694251537323</v>
       </c>
       <c r="H1691" t="s">
         <v>8</v>
@@ -44361,7 +44361,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1692" t="n">
-        <v>2.66730904579163</v>
+        <v>2.66730928421021</v>
       </c>
       <c r="H1692" t="s">
         <v>8</v>
@@ -44387,7 +44387,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G1693" t="n">
-        <v>2.74364614486694</v>
+        <v>2.74364590644836</v>
       </c>
       <c r="H1693" t="s">
         <v>8</v>
@@ -44413,7 +44413,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1694" t="n">
-        <v>2.73017477989197</v>
+        <v>2.73017501831055</v>
       </c>
       <c r="H1694" t="s">
         <v>8</v>
@@ -44439,7 +44439,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G1695" t="n">
-        <v>2.74364614486694</v>
+        <v>2.74364590644836</v>
       </c>
       <c r="H1695" t="s">
         <v>8</v>
@@ -44465,7 +44465,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1696" t="n">
-        <v>2.68527030944824</v>
+        <v>2.6852707862854</v>
       </c>
       <c r="H1696" t="s">
         <v>8</v>
@@ -44491,7 +44491,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1697" t="n">
-        <v>2.60444307327271</v>
+        <v>2.60444331169128</v>
       </c>
       <c r="H1697" t="s">
         <v>8</v>
@@ -44543,7 +44543,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G1699" t="n">
-        <v>2.57750058174133</v>
+        <v>2.57750034332275</v>
       </c>
       <c r="H1699" t="s">
         <v>8</v>
@@ -44595,7 +44595,7 @@
         <v>2.8050000667572</v>
       </c>
       <c r="G1701" t="n">
-        <v>2.51912522315979</v>
+        <v>2.51912498474121</v>
       </c>
       <c r="H1701" t="s">
         <v>8</v>
@@ -44699,7 +44699,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1705" t="n">
-        <v>2.55055785179138</v>
+        <v>2.55055809020996</v>
       </c>
       <c r="H1705" t="s">
         <v>8</v>
@@ -44725,7 +44725,7 @@
         <v>2.73499989509583</v>
       </c>
       <c r="G1706" t="n">
-        <v>2.45625925064087</v>
+        <v>2.45625901222229</v>
       </c>
       <c r="H1706" t="s">
         <v>8</v>
@@ -44829,7 +44829,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1710" t="n">
-        <v>2.37992238998413</v>
+        <v>2.37992215156555</v>
       </c>
       <c r="H1710" t="s">
         <v>8</v>
@@ -44907,7 +44907,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1713" t="n">
-        <v>2.18234348297119</v>
+        <v>2.18234372138977</v>
       </c>
       <c r="H1713" t="s">
         <v>8</v>
@@ -44933,7 +44933,7 @@
         <v>2.43499994277954</v>
       </c>
       <c r="G1714" t="n">
-        <v>2.18683409690857</v>
+        <v>2.18683385848999</v>
       </c>
       <c r="H1714" t="s">
         <v>8</v>
@@ -44959,7 +44959,7 @@
         <v>2.42499995231628</v>
       </c>
       <c r="G1715" t="n">
-        <v>2.17785334587097</v>
+        <v>2.17785310745239</v>
       </c>
       <c r="H1715" t="s">
         <v>8</v>
@@ -45037,7 +45037,7 @@
         <v>2.40499997138977</v>
       </c>
       <c r="G1718" t="n">
-        <v>2.15989136695862</v>
+        <v>2.1598916053772</v>
       </c>
       <c r="H1718" t="s">
         <v>8</v>
@@ -45167,7 +45167,7 @@
         <v>2.28500008583069</v>
       </c>
       <c r="G1723" t="n">
-        <v>2.10462784767151</v>
+        <v>2.10462808609009</v>
       </c>
       <c r="H1723" t="s">
         <v>8</v>
@@ -45219,7 +45219,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G1725" t="n">
-        <v>2.07699608802795</v>
+        <v>2.07699584960938</v>
       </c>
       <c r="H1725" t="s">
         <v>8</v>
@@ -45245,7 +45245,7 @@
         <v>2.28500008583069</v>
       </c>
       <c r="G1726" t="n">
-        <v>2.10462784767151</v>
+        <v>2.10462808609009</v>
       </c>
       <c r="H1726" t="s">
         <v>8</v>
@@ -45271,7 +45271,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1727" t="n">
-        <v>2.09081172943115</v>
+        <v>2.09081196784973</v>
       </c>
       <c r="H1727" t="s">
         <v>8</v>
@@ -45323,7 +45323,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1729" t="n">
-        <v>2.09081172943115</v>
+        <v>2.09081196784973</v>
       </c>
       <c r="H1729" t="s">
         <v>8</v>
@@ -45427,7 +45427,7 @@
         <v>2.58500003814697</v>
       </c>
       <c r="G1733" t="n">
-        <v>2.38094687461853</v>
+        <v>2.38094639778137</v>
       </c>
       <c r="H1733" t="s">
         <v>8</v>
@@ -45479,7 +45479,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G1735" t="n">
-        <v>2.33949851989746</v>
+        <v>2.33949875831604</v>
       </c>
       <c r="H1735" t="s">
         <v>8</v>
@@ -45505,7 +45505,7 @@
         <v>2.58500003814697</v>
       </c>
       <c r="G1736" t="n">
-        <v>2.38094687461853</v>
+        <v>2.38094639778137</v>
       </c>
       <c r="H1736" t="s">
         <v>8</v>
@@ -45609,7 +45609,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G1740" t="n">
-        <v>2.40397310256958</v>
+        <v>2.403972864151</v>
       </c>
       <c r="H1740" t="s">
         <v>8</v>
@@ -45713,7 +45713,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1744" t="n">
-        <v>2.43160510063171</v>
+        <v>2.43160486221313</v>
       </c>
       <c r="H1744" t="s">
         <v>8</v>
@@ -45765,7 +45765,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G1746" t="n">
-        <v>2.45923662185669</v>
+        <v>2.45923709869385</v>
       </c>
       <c r="H1746" t="s">
         <v>8</v>
@@ -45843,7 +45843,7 @@
         <v>2.76500010490417</v>
       </c>
       <c r="G1749" t="n">
-        <v>2.54673790931702</v>
+        <v>2.54673767089844</v>
       </c>
       <c r="H1749" t="s">
         <v>8</v>
@@ -45869,7 +45869,7 @@
         <v>2.76500010490417</v>
       </c>
       <c r="G1750" t="n">
-        <v>2.54673790931702</v>
+        <v>2.54673767089844</v>
       </c>
       <c r="H1750" t="s">
         <v>8</v>
@@ -45999,7 +45999,7 @@
         <v>2.66499996185303</v>
       </c>
       <c r="G1755" t="n">
-        <v>2.45463156700134</v>
+        <v>2.45463132858276</v>
       </c>
       <c r="H1755" t="s">
         <v>8</v>
@@ -46025,7 +46025,7 @@
         <v>2.66499996185303</v>
       </c>
       <c r="G1756" t="n">
-        <v>2.45463156700134</v>
+        <v>2.45463132858276</v>
       </c>
       <c r="H1756" t="s">
         <v>8</v>
@@ -46051,7 +46051,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1757" t="n">
-        <v>2.4868688583374</v>
+        <v>2.48686861991882</v>
       </c>
       <c r="H1757" t="s">
         <v>8</v>
@@ -46077,7 +46077,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1758" t="n">
-        <v>2.4868688583374</v>
+        <v>2.48686861991882</v>
       </c>
       <c r="H1758" t="s">
         <v>8</v>
@@ -46103,7 +46103,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1759" t="n">
-        <v>2.4868688583374</v>
+        <v>2.48686861991882</v>
       </c>
       <c r="H1759" t="s">
         <v>8</v>
@@ -46207,7 +46207,7 @@
         <v>2.75500011444092</v>
       </c>
       <c r="G1763" t="n">
-        <v>2.53752708435059</v>
+        <v>2.53752732276917</v>
       </c>
       <c r="H1763" t="s">
         <v>8</v>
@@ -46233,7 +46233,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1764" t="n">
-        <v>2.55134296417236</v>
+        <v>2.55134320259094</v>
       </c>
       <c r="H1764" t="s">
         <v>8</v>
@@ -46259,7 +46259,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1765" t="n">
-        <v>2.52371144294739</v>
+        <v>2.52371120452881</v>
       </c>
       <c r="H1765" t="s">
         <v>8</v>
@@ -46285,7 +46285,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1766" t="n">
-        <v>2.52371144294739</v>
+        <v>2.52371120452881</v>
       </c>
       <c r="H1766" t="s">
         <v>8</v>
@@ -46337,7 +46337,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1768" t="n">
-        <v>2.49607920646667</v>
+        <v>2.49607944488525</v>
       </c>
       <c r="H1768" t="s">
         <v>8</v>
@@ -46363,7 +46363,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1769" t="n">
-        <v>2.52371144294739</v>
+        <v>2.52371120452881</v>
       </c>
       <c r="H1769" t="s">
         <v>8</v>
@@ -46415,7 +46415,7 @@
         <v>2.72499990463257</v>
       </c>
       <c r="G1771" t="n">
-        <v>2.50989532470703</v>
+        <v>2.50989508628845</v>
       </c>
       <c r="H1771" t="s">
         <v>8</v>
@@ -46493,7 +46493,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1774" t="n">
-        <v>2.52371144294739</v>
+        <v>2.52371120452881</v>
       </c>
       <c r="H1774" t="s">
         <v>8</v>
@@ -46519,7 +46519,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1775" t="n">
-        <v>2.52371144294739</v>
+        <v>2.52371120452881</v>
       </c>
       <c r="H1775" t="s">
         <v>8</v>
@@ -46545,7 +46545,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1776" t="n">
-        <v>2.5973961353302</v>
+        <v>2.59739589691162</v>
       </c>
       <c r="H1776" t="s">
         <v>8</v>
@@ -46597,7 +46597,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G1778" t="n">
-        <v>2.59279108047485</v>
+        <v>2.59279084205627</v>
       </c>
       <c r="H1778" t="s">
         <v>8</v>
@@ -46675,7 +46675,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1781" t="n">
-        <v>2.73555564880371</v>
+        <v>2.73555541038513</v>
       </c>
       <c r="H1781" t="s">
         <v>8</v>
@@ -46701,7 +46701,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1782" t="n">
-        <v>2.73555564880371</v>
+        <v>2.73555541038513</v>
       </c>
       <c r="H1782" t="s">
         <v>8</v>
@@ -46727,7 +46727,7 @@
         <v>3</v>
       </c>
       <c r="G1783" t="n">
-        <v>2.76318740844727</v>
+        <v>2.76318764686584</v>
       </c>
       <c r="H1783" t="s">
         <v>8</v>
@@ -46805,7 +46805,7 @@
         <v>3</v>
       </c>
       <c r="G1786" t="n">
-        <v>2.76318740844727</v>
+        <v>2.76318764686584</v>
       </c>
       <c r="H1786" t="s">
         <v>8</v>
@@ -46831,7 +46831,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1787" t="n">
-        <v>2.74476647377014</v>
+        <v>2.74476623535156</v>
       </c>
       <c r="H1787" t="s">
         <v>8</v>
@@ -46961,7 +46961,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1792" t="n">
-        <v>2.82766175270081</v>
+        <v>2.82766199111938</v>
       </c>
       <c r="H1792" t="s">
         <v>8</v>
@@ -47039,7 +47039,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1795" t="n">
-        <v>2.83687210083008</v>
+        <v>2.83687233924866</v>
       </c>
       <c r="H1795" t="s">
         <v>8</v>
@@ -47143,7 +47143,7 @@
         <v>3</v>
       </c>
       <c r="G1799" t="n">
-        <v>2.76318740844727</v>
+        <v>2.76318764686584</v>
       </c>
       <c r="H1799" t="s">
         <v>8</v>
@@ -47195,7 +47195,7 @@
         <v>3</v>
       </c>
       <c r="G1801" t="n">
-        <v>2.76318740844727</v>
+        <v>2.76318764686584</v>
       </c>
       <c r="H1801" t="s">
         <v>8</v>
@@ -47221,7 +47221,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1802" t="n">
-        <v>2.74476647377014</v>
+        <v>2.74476623535156</v>
       </c>
       <c r="H1802" t="s">
         <v>8</v>
@@ -47247,7 +47247,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1803" t="n">
-        <v>2.73555564880371</v>
+        <v>2.73555541038513</v>
       </c>
       <c r="H1803" t="s">
         <v>8</v>
@@ -47299,7 +47299,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1805" t="n">
-        <v>2.70792365074158</v>
+        <v>2.70792388916016</v>
       </c>
       <c r="H1805" t="s">
         <v>8</v>
@@ -47325,7 +47325,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1806" t="n">
-        <v>2.71713423728943</v>
+        <v>2.71713447570801</v>
       </c>
       <c r="H1806" t="s">
         <v>8</v>
@@ -47351,7 +47351,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G1807" t="n">
-        <v>2.6987133026123</v>
+        <v>2.69871306419373</v>
       </c>
       <c r="H1807" t="s">
         <v>8</v>
@@ -47429,7 +47429,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1810" t="n">
-        <v>2.66187071800232</v>
+        <v>2.6618709564209</v>
       </c>
       <c r="H1810" t="s">
         <v>8</v>
@@ -47481,7 +47481,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G1812" t="n">
-        <v>2.64344930648804</v>
+        <v>2.64344906806946</v>
       </c>
       <c r="H1812" t="s">
         <v>8</v>
@@ -47507,7 +47507,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1813" t="n">
-        <v>2.62502789497375</v>
+        <v>2.62502813339233</v>
       </c>
       <c r="H1813" t="s">
         <v>8</v>
@@ -47533,7 +47533,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1814" t="n">
-        <v>2.6158173084259</v>
+        <v>2.61581754684448</v>
       </c>
       <c r="H1814" t="s">
         <v>8</v>
@@ -47559,7 +47559,7 @@
         <v>2.90499997138977</v>
       </c>
       <c r="G1815" t="n">
-        <v>2.6756865978241</v>
+        <v>2.67568635940552</v>
       </c>
       <c r="H1815" t="s">
         <v>8</v>
@@ -47585,7 +47585,7 @@
         <v>2.95499992370605</v>
       </c>
       <c r="G1816" t="n">
-        <v>2.72173976898193</v>
+        <v>2.72173953056335</v>
       </c>
       <c r="H1816" t="s">
         <v>8</v>
@@ -47611,7 +47611,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1817" t="n">
-        <v>2.79081916809082</v>
+        <v>2.7908194065094</v>
       </c>
       <c r="H1817" t="s">
         <v>8</v>
@@ -47637,7 +47637,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1818" t="n">
-        <v>2.80002999305725</v>
+        <v>2.80002975463867</v>
       </c>
       <c r="H1818" t="s">
         <v>8</v>
@@ -47689,7 +47689,7 @@
         <v>3</v>
       </c>
       <c r="G1820" t="n">
-        <v>2.76318740844727</v>
+        <v>2.76318764686584</v>
       </c>
       <c r="H1820" t="s">
         <v>8</v>
@@ -47741,7 +47741,7 @@
         <v>3</v>
       </c>
       <c r="G1822" t="n">
-        <v>2.76318740844727</v>
+        <v>2.76318764686584</v>
       </c>
       <c r="H1822" t="s">
         <v>8</v>
@@ -47819,7 +47819,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1825" t="n">
-        <v>2.70792365074158</v>
+        <v>2.70792388916016</v>
       </c>
       <c r="H1825" t="s">
         <v>8</v>
@@ -47923,7 +47923,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1829" t="n">
-        <v>2.70792365074158</v>
+        <v>2.70792388916016</v>
       </c>
       <c r="H1829" t="s">
         <v>8</v>
@@ -48001,7 +48001,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G1832" t="n">
-        <v>2.6987133026123</v>
+        <v>2.69871306419373</v>
       </c>
       <c r="H1832" t="s">
         <v>8</v>
@@ -48053,7 +48053,7 @@
         <v>2.90499997138977</v>
       </c>
       <c r="G1834" t="n">
-        <v>2.6756865978241</v>
+        <v>2.67568635940552</v>
       </c>
       <c r="H1834" t="s">
         <v>8</v>
@@ -48079,7 +48079,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1835" t="n">
-        <v>2.6158173084259</v>
+        <v>2.61581754684448</v>
       </c>
       <c r="H1835" t="s">
         <v>8</v>
@@ -48157,7 +48157,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1838" t="n">
-        <v>2.66187071800232</v>
+        <v>2.6618709564209</v>
       </c>
       <c r="H1838" t="s">
         <v>8</v>
@@ -48183,7 +48183,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G1839" t="n">
-        <v>2.6987133026123</v>
+        <v>2.69871306419373</v>
       </c>
       <c r="H1839" t="s">
         <v>8</v>
@@ -48209,7 +48209,7 @@
         <v>2.91499996185303</v>
       </c>
       <c r="G1840" t="n">
-        <v>2.68489694595337</v>
+        <v>2.68489718437195</v>
       </c>
       <c r="H1840" t="s">
         <v>8</v>
@@ -48235,7 +48235,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1841" t="n">
-        <v>2.71713423728943</v>
+        <v>2.71713447570801</v>
       </c>
       <c r="H1841" t="s">
         <v>8</v>
@@ -48261,7 +48261,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1842" t="n">
-        <v>2.66187071800232</v>
+        <v>2.6618709564209</v>
       </c>
       <c r="H1842" t="s">
         <v>8</v>
@@ -48287,7 +48287,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1843" t="n">
-        <v>2.65266013145447</v>
+        <v>2.65265989303589</v>
       </c>
       <c r="H1843" t="s">
         <v>8</v>
@@ -48365,7 +48365,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1846" t="n">
-        <v>2.5973961353302</v>
+        <v>2.59739589691162</v>
       </c>
       <c r="H1846" t="s">
         <v>8</v>
@@ -48391,7 +48391,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1847" t="n">
-        <v>2.6158173084259</v>
+        <v>2.61581754684448</v>
       </c>
       <c r="H1847" t="s">
         <v>8</v>
@@ -48417,7 +48417,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1848" t="n">
-        <v>2.6158173084259</v>
+        <v>2.61581754684448</v>
       </c>
       <c r="H1848" t="s">
         <v>8</v>
@@ -48443,7 +48443,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1849" t="n">
-        <v>2.5973961353302</v>
+        <v>2.59739589691162</v>
       </c>
       <c r="H1849" t="s">
         <v>8</v>
@@ -48469,7 +48469,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1850" t="n">
-        <v>2.6158173084259</v>
+        <v>2.61581754684448</v>
       </c>
       <c r="H1850" t="s">
         <v>8</v>
@@ -48521,7 +48521,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1852" t="n">
-        <v>2.6158173084259</v>
+        <v>2.61581754684448</v>
       </c>
       <c r="H1852" t="s">
         <v>8</v>
@@ -48547,7 +48547,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1853" t="n">
-        <v>2.5973961353302</v>
+        <v>2.59739589691162</v>
       </c>
       <c r="H1853" t="s">
         <v>8</v>
@@ -48625,7 +48625,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.5973961353302</v>
+        <v>2.59739589691162</v>
       </c>
       <c r="H1856" t="s">
         <v>8</v>
@@ -48651,7 +48651,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.64344930648804</v>
+        <v>2.64344906806946</v>
       </c>
       <c r="H1857" t="s">
         <v>8</v>
@@ -48677,7 +48677,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.64344930648804</v>
+        <v>2.64344906806946</v>
       </c>
       <c r="H1858" t="s">
         <v>8</v>
@@ -48729,7 +48729,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.6158173084259</v>
+        <v>2.61581754684448</v>
       </c>
       <c r="H1860" t="s">
         <v>8</v>
@@ -48781,7 +48781,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.5973961353302</v>
+        <v>2.59739589691162</v>
       </c>
       <c r="H1862" t="s">
         <v>8</v>
@@ -48885,7 +48885,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.55134296417236</v>
+        <v>2.55134320259094</v>
       </c>
       <c r="H1866" t="s">
         <v>8</v>
@@ -48937,7 +48937,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.41318345069885</v>
+        <v>2.41318368911743</v>
       </c>
       <c r="H1868" t="s">
         <v>8</v>
@@ -48963,7 +48963,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.45923662185669</v>
+        <v>2.45923709869385</v>
       </c>
       <c r="H1869" t="s">
         <v>8</v>
@@ -49119,7 +49119,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.52371144294739</v>
+        <v>2.52371120452881</v>
       </c>
       <c r="H1875" t="s">
         <v>8</v>
@@ -49145,7 +49145,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.49607920646667</v>
+        <v>2.49607944488525</v>
       </c>
       <c r="H1876" t="s">
         <v>8</v>
@@ -49249,7 +49249,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.45923662185669</v>
+        <v>2.45923709869385</v>
       </c>
       <c r="H1880" t="s">
         <v>8</v>
@@ -49275,7 +49275,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.45923662185669</v>
+        <v>2.45923709869385</v>
       </c>
       <c r="H1881" t="s">
         <v>8</v>
@@ -49301,7 +49301,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.45923662185669</v>
+        <v>2.45923709869385</v>
       </c>
       <c r="H1882" t="s">
         <v>8</v>
@@ -49327,7 +49327,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.45923662185669</v>
+        <v>2.45923709869385</v>
       </c>
       <c r="H1883" t="s">
         <v>8</v>
@@ -49353,7 +49353,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.44081592559814</v>
+        <v>2.44081568717957</v>
       </c>
       <c r="H1884" t="s">
         <v>8</v>
@@ -49509,7 +49509,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.44081592559814</v>
+        <v>2.44081568717957</v>
       </c>
       <c r="H1890" t="s">
         <v>8</v>
@@ -49535,7 +49535,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.44081592559814</v>
+        <v>2.44081568717957</v>
       </c>
       <c r="H1891" t="s">
         <v>8</v>
@@ -49587,7 +49587,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.44081592559814</v>
+        <v>2.44081568717957</v>
       </c>
       <c r="H1893" t="s">
         <v>8</v>
@@ -49639,7 +49639,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.44081592559814</v>
+        <v>2.44081568717957</v>
       </c>
       <c r="H1895" t="s">
         <v>8</v>
@@ -49665,7 +49665,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.45923662185669</v>
+        <v>2.45923709869385</v>
       </c>
       <c r="H1896" t="s">
         <v>8</v>
@@ -49691,7 +49691,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.45923662185669</v>
+        <v>2.45923709869385</v>
       </c>
       <c r="H1897" t="s">
         <v>8</v>
@@ -49743,7 +49743,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.49607920646667</v>
+        <v>2.49607944488525</v>
       </c>
       <c r="H1899" t="s">
         <v>8</v>
@@ -49847,7 +49847,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.49607920646667</v>
+        <v>2.49607944488525</v>
       </c>
       <c r="H1903" t="s">
         <v>8</v>
@@ -49873,7 +49873,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.4868688583374</v>
+        <v>2.48686861991882</v>
       </c>
       <c r="H1904" t="s">
         <v>8</v>
@@ -49899,7 +49899,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.4868688583374</v>
+        <v>2.48686861991882</v>
       </c>
       <c r="H1905" t="s">
         <v>8</v>
@@ -50003,7 +50003,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.52371144294739</v>
+        <v>2.52371120452881</v>
       </c>
       <c r="H1909" t="s">
         <v>8</v>
@@ -71690,6 +71690,32 @@
         <v>1.10500001907349</v>
       </c>
       <c r="H2743" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2744">
+      <c r="A2744" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B2744" t="n">
+        <v>200</v>
+      </c>
+      <c r="C2744" t="n">
+        <v>1.11500000953674</v>
+      </c>
+      <c r="D2744" t="n">
+        <v>1.10500001907349</v>
+      </c>
+      <c r="E2744" t="n">
+        <v>1.11500000953674</v>
+      </c>
+      <c r="F2744" t="n">
+        <v>1.10500001907349</v>
+      </c>
+      <c r="G2744" t="n">
+        <v>1.10500001907349</v>
+      </c>
+      <c r="H2744" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/ELC.MI.xlsx
+++ b/data/ELC.MI.xlsx
@@ -427,7 +427,7 @@
         <v>1.93700003623962</v>
       </c>
       <c r="G2" t="n">
-        <v>1.73070454597473</v>
+        <v>1.73070466518402</v>
       </c>
       <c r="H2" t="n">
         <v>52100</v>
@@ -456,7 +456,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G3" t="n">
-        <v>1.73338508605957</v>
+        <v>1.73338520526886</v>
       </c>
       <c r="H3" t="n">
         <v>15024</v>
@@ -485,7 +485,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G4" t="n">
-        <v>1.72445023059845</v>
+        <v>1.72445011138916</v>
       </c>
       <c r="H4" t="n">
         <v>5059</v>
@@ -659,7 +659,7 @@
         <v>1.81900000572205</v>
       </c>
       <c r="G10" t="n">
-        <v>1.62527191638947</v>
+        <v>1.62527203559875</v>
       </c>
       <c r="H10" t="n">
         <v>37372</v>
@@ -688,7 +688,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G11" t="n">
-        <v>1.59936034679413</v>
+        <v>1.59936046600342</v>
       </c>
       <c r="H11" t="n">
         <v>30082</v>
@@ -775,7 +775,7 @@
         <v>1.61099994182587</v>
       </c>
       <c r="G14" t="n">
-        <v>1.43942439556122</v>
+        <v>1.43942427635193</v>
       </c>
       <c r="H14" t="n">
         <v>54905</v>
@@ -920,7 +920,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G19" t="n">
-        <v>1.46533596515656</v>
+        <v>1.46533584594727</v>
       </c>
       <c r="H19" t="n">
         <v>19803</v>
@@ -978,7 +978,7 @@
         <v>1.65100002288818</v>
       </c>
       <c r="G21" t="n">
-        <v>1.47516429424286</v>
+        <v>1.47516453266144</v>
       </c>
       <c r="H21" t="n">
         <v>7561</v>
@@ -1007,7 +1007,7 @@
         <v>1.59099996089935</v>
       </c>
       <c r="G22" t="n">
-        <v>1.4215544462204</v>
+        <v>1.42155456542969</v>
       </c>
       <c r="H22" t="n">
         <v>81953</v>
@@ -1036,7 +1036,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G23" t="n">
-        <v>1.39832377433777</v>
+        <v>1.39832365512848</v>
       </c>
       <c r="H23" t="n">
         <v>23089</v>
@@ -1065,7 +1065,7 @@
         <v>1.54499995708466</v>
       </c>
       <c r="G24" t="n">
-        <v>1.38045358657837</v>
+        <v>1.38045370578766</v>
       </c>
       <c r="H24" t="n">
         <v>20826</v>
@@ -1094,7 +1094,7 @@
         <v>1.51699995994568</v>
       </c>
       <c r="G25" t="n">
-        <v>1.35543572902679</v>
+        <v>1.35543549060822</v>
       </c>
       <c r="H25" t="n">
         <v>27464</v>
@@ -1123,7 +1123,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G26" t="n">
-        <v>1.38492107391357</v>
+        <v>1.38492119312286</v>
       </c>
       <c r="H26" t="n">
         <v>35283</v>
@@ -1181,7 +1181,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G28" t="n">
-        <v>1.28216874599457</v>
+        <v>1.28216886520386</v>
       </c>
       <c r="H28" t="n">
         <v>58422</v>
@@ -1268,7 +1268,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G31" t="n">
-        <v>1.42959606647491</v>
+        <v>1.42959594726562</v>
       </c>
       <c r="H31" t="n">
         <v>187635</v>
@@ -1326,7 +1326,7 @@
         <v>1.6710000038147</v>
       </c>
       <c r="G33" t="n">
-        <v>1.49303436279297</v>
+        <v>1.49303424358368</v>
       </c>
       <c r="H33" t="n">
         <v>16075</v>
@@ -1355,7 +1355,7 @@
         <v>1.65900003910065</v>
       </c>
       <c r="G34" t="n">
-        <v>1.48231244087219</v>
+        <v>1.48231220245361</v>
       </c>
       <c r="H34" t="n">
         <v>55221</v>
@@ -1384,7 +1384,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G35" t="n">
-        <v>1.51001071929932</v>
+        <v>1.51001083850861</v>
       </c>
       <c r="H35" t="n">
         <v>48925</v>
@@ -1413,7 +1413,7 @@
         <v>1.75399994850159</v>
       </c>
       <c r="G36" t="n">
-        <v>1.56719446182251</v>
+        <v>1.5671945810318</v>
       </c>
       <c r="H36" t="n">
         <v>41971</v>
@@ -1442,7 +1442,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G37" t="n">
-        <v>1.57255566120148</v>
+        <v>1.5725554227829</v>
       </c>
       <c r="H37" t="n">
         <v>29281</v>
@@ -1500,7 +1500,7 @@
         <v>1.74699997901917</v>
       </c>
       <c r="G39" t="n">
-        <v>1.56094014644623</v>
+        <v>1.56094002723694</v>
       </c>
       <c r="H39" t="n">
         <v>2902</v>
@@ -1529,7 +1529,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G40" t="n">
-        <v>1.57702302932739</v>
+        <v>1.5770229101181</v>
       </c>
       <c r="H40" t="n">
         <v>4812</v>
@@ -1558,7 +1558,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G41" t="n">
-        <v>1.59042549133301</v>
+        <v>1.5904256105423</v>
       </c>
       <c r="H41" t="n">
         <v>5892</v>
@@ -1587,7 +1587,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G42" t="n">
-        <v>1.5814905166626</v>
+        <v>1.58149063587189</v>
       </c>
       <c r="H42" t="n">
         <v>5093</v>
@@ -1616,7 +1616,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G43" t="n">
-        <v>1.57255566120148</v>
+        <v>1.5725554227829</v>
       </c>
       <c r="H43" t="n">
         <v>24781</v>
@@ -1645,7 +1645,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G44" t="n">
-        <v>1.51894581317902</v>
+        <v>1.51894593238831</v>
       </c>
       <c r="H44" t="n">
         <v>29575</v>
@@ -1674,7 +1674,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G45" t="n">
-        <v>1.5814905166626</v>
+        <v>1.58149063587189</v>
       </c>
       <c r="H45" t="n">
         <v>28487</v>
@@ -1819,7 +1819,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G50" t="n">
-        <v>1.5814905166626</v>
+        <v>1.58149063587189</v>
       </c>
       <c r="H50" t="n">
         <v>3356</v>
@@ -1848,7 +1848,7 @@
         <v>1.76600003242493</v>
       </c>
       <c r="G51" t="n">
-        <v>1.57791650295258</v>
+        <v>1.57791662216187</v>
       </c>
       <c r="H51" t="n">
         <v>27532</v>
@@ -1906,7 +1906,7 @@
         <v>1.89300000667572</v>
       </c>
       <c r="G53" t="n">
-        <v>1.69139087200165</v>
+        <v>1.69139075279236</v>
       </c>
       <c r="H53" t="n">
         <v>24502</v>
@@ -1935,7 +1935,7 @@
         <v>1.90900003910065</v>
       </c>
       <c r="G54" t="n">
-        <v>1.70568656921387</v>
+        <v>1.70568668842316</v>
       </c>
       <c r="H54" t="n">
         <v>85054</v>
@@ -1993,7 +1993,7 @@
         <v>1.90799999237061</v>
       </c>
       <c r="G56" t="n">
-        <v>1.70479309558868</v>
+        <v>1.70479321479797</v>
       </c>
       <c r="H56" t="n">
         <v>30447</v>
@@ -2022,7 +2022,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G57" t="n">
-        <v>1.72445023059845</v>
+        <v>1.72445011138916</v>
       </c>
       <c r="H57" t="n">
         <v>46823</v>
@@ -2051,7 +2051,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G58" t="n">
-        <v>1.76912498474121</v>
+        <v>1.7691251039505</v>
       </c>
       <c r="H58" t="n">
         <v>198777</v>
@@ -2138,7 +2138,7 @@
         <v>1.94599997997284</v>
       </c>
       <c r="G61" t="n">
-        <v>1.73874604701996</v>
+        <v>1.73874592781067</v>
       </c>
       <c r="H61" t="n">
         <v>32577</v>
@@ -2225,7 +2225,7 @@
         <v>1.96399998664856</v>
       </c>
       <c r="G64" t="n">
-        <v>1.7548291683197</v>
+        <v>1.75482904911041</v>
       </c>
       <c r="H64" t="n">
         <v>34653</v>
@@ -2254,7 +2254,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G65" t="n">
-        <v>1.72445023059845</v>
+        <v>1.72445011138916</v>
       </c>
       <c r="H65" t="n">
         <v>30447</v>
@@ -2283,7 +2283,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G66" t="n">
-        <v>1.68871009349823</v>
+        <v>1.68871021270752</v>
       </c>
       <c r="H66" t="n">
         <v>26185</v>
@@ -2457,7 +2457,7 @@
         <v>1.88100004196167</v>
       </c>
       <c r="G72" t="n">
-        <v>1.68066883087158</v>
+        <v>1.68066895008087</v>
       </c>
       <c r="H72" t="n">
         <v>6676</v>
@@ -2544,7 +2544,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G75" t="n">
-        <v>1.71998274326324</v>
+        <v>1.71998262405396</v>
       </c>
       <c r="H75" t="n">
         <v>16399</v>
@@ -2573,7 +2573,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G76" t="n">
-        <v>1.71104764938354</v>
+        <v>1.71104753017426</v>
       </c>
       <c r="H76" t="n">
         <v>11969</v>
@@ -2602,7 +2602,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G77" t="n">
-        <v>1.70658016204834</v>
+        <v>1.70658004283905</v>
       </c>
       <c r="H77" t="n">
         <v>6179</v>
@@ -2631,7 +2631,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G78" t="n">
-        <v>1.71998274326324</v>
+        <v>1.71998262405396</v>
       </c>
       <c r="H78" t="n">
         <v>32038</v>
@@ -2660,7 +2660,7 @@
         <v>1.89800000190735</v>
       </c>
       <c r="G79" t="n">
-        <v>1.69585835933685</v>
+        <v>1.69585824012756</v>
       </c>
       <c r="H79" t="n">
         <v>17651</v>
@@ -2689,7 +2689,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G80" t="n">
-        <v>1.71998274326324</v>
+        <v>1.71998262405396</v>
       </c>
       <c r="H80" t="n">
         <v>6935</v>
@@ -2718,7 +2718,7 @@
         <v>1.89900004863739</v>
       </c>
       <c r="G81" t="n">
-        <v>1.69675171375275</v>
+        <v>1.69675183296204</v>
       </c>
       <c r="H81" t="n">
         <v>12593</v>
@@ -2747,7 +2747,7 @@
         <v>1.92700004577637</v>
       </c>
       <c r="G82" t="n">
-        <v>1.72176957130432</v>
+        <v>1.72176969051361</v>
       </c>
       <c r="H82" t="n">
         <v>23360</v>
@@ -2776,7 +2776,7 @@
         <v>1.93900001049042</v>
       </c>
       <c r="G83" t="n">
-        <v>1.73249161243439</v>
+        <v>1.7324914932251</v>
       </c>
       <c r="H83" t="n">
         <v>20416</v>
@@ -2805,7 +2805,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G84" t="n">
-        <v>1.74231994152069</v>
+        <v>1.74232017993927</v>
       </c>
       <c r="H84" t="n">
         <v>30024</v>
@@ -2892,7 +2892,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G87" t="n">
-        <v>1.70658016204834</v>
+        <v>1.70658004283905</v>
       </c>
       <c r="H87" t="n">
         <v>14162</v>
@@ -2979,7 +2979,7 @@
         <v>1.84800004959106</v>
       </c>
       <c r="G90" t="n">
-        <v>1.65118336677551</v>
+        <v>1.65118324756622</v>
       </c>
       <c r="H90" t="n">
         <v>73958</v>
@@ -3037,7 +3037,7 @@
         <v>1.84700000286102</v>
       </c>
       <c r="G92" t="n">
-        <v>1.65028977394104</v>
+        <v>1.65028989315033</v>
       </c>
       <c r="H92" t="n">
         <v>15659</v>
@@ -3066,7 +3066,7 @@
         <v>1.85199999809265</v>
       </c>
       <c r="G93" t="n">
-        <v>1.65475726127625</v>
+        <v>1.65475738048553</v>
       </c>
       <c r="H93" t="n">
         <v>17094</v>
@@ -3095,7 +3095,7 @@
         <v>1.88699996471405</v>
       </c>
       <c r="G94" t="n">
-        <v>1.68602967262268</v>
+        <v>1.68602955341339</v>
       </c>
       <c r="H94" t="n">
         <v>23988</v>
@@ -3124,7 +3124,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G95" t="n">
-        <v>1.68871009349823</v>
+        <v>1.68871021270752</v>
       </c>
       <c r="H95" t="n">
         <v>3721</v>
@@ -3153,7 +3153,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G96" t="n">
-        <v>1.68871009349823</v>
+        <v>1.68871021270752</v>
       </c>
       <c r="H96" t="n">
         <v>2436</v>
@@ -3298,7 +3298,7 @@
         <v>1.9190000295639</v>
       </c>
       <c r="G101" t="n">
-        <v>1.72342276573181</v>
+        <v>1.7234228849411</v>
       </c>
       <c r="H101" t="n">
         <v>15489</v>
@@ -3356,7 +3356,7 @@
         <v>1.95700001716614</v>
       </c>
       <c r="G103" t="n">
-        <v>1.7575501203537</v>
+        <v>1.75755000114441</v>
       </c>
       <c r="H103" t="n">
         <v>198761</v>
@@ -3385,7 +3385,7 @@
         <v>1.93799996376038</v>
       </c>
       <c r="G104" t="n">
-        <v>1.7404865026474</v>
+        <v>1.74048626422882</v>
       </c>
       <c r="H104" t="n">
         <v>7025</v>
@@ -3443,7 +3443,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G106" t="n">
-        <v>1.73330175876617</v>
+        <v>1.73330187797546</v>
       </c>
       <c r="H106" t="n">
         <v>52731</v>
@@ -3472,7 +3472,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G107" t="n">
-        <v>1.72432100772858</v>
+        <v>1.72432076931</v>
       </c>
       <c r="H107" t="n">
         <v>8971</v>
@@ -3501,7 +3501,7 @@
         <v>1.92900002002716</v>
       </c>
       <c r="G108" t="n">
-        <v>1.73240375518799</v>
+        <v>1.7324036359787</v>
       </c>
       <c r="H108" t="n">
         <v>14291</v>
@@ -3559,7 +3559,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G110" t="n">
-        <v>1.72432100772858</v>
+        <v>1.72432076931</v>
       </c>
       <c r="H110" t="n">
         <v>25811</v>
@@ -3588,7 +3588,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G111" t="n">
-        <v>1.72432100772858</v>
+        <v>1.72432076931</v>
       </c>
       <c r="H111" t="n">
         <v>52856</v>
@@ -3733,7 +3733,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G116" t="n">
-        <v>1.63900303840637</v>
+        <v>1.63900291919708</v>
       </c>
       <c r="H116" t="n">
         <v>14527</v>
@@ -3791,7 +3791,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G118" t="n">
-        <v>1.58960843086243</v>
+        <v>1.58960831165314</v>
       </c>
       <c r="H118" t="n">
         <v>20333</v>
@@ -3849,7 +3849,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G120" t="n">
-        <v>1.63451254367828</v>
+        <v>1.63451242446899</v>
       </c>
       <c r="H120" t="n">
         <v>16192</v>
@@ -3878,7 +3878,7 @@
         <v>1.875</v>
       </c>
       <c r="G121" t="n">
-        <v>1.68390715122223</v>
+        <v>1.68390727043152</v>
       </c>
       <c r="H121" t="n">
         <v>30628</v>
@@ -3936,7 +3936,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G123" t="n">
-        <v>1.66145515441895</v>
+        <v>1.66145503520966</v>
       </c>
       <c r="H123" t="n">
         <v>13342</v>
@@ -3965,7 +3965,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G124" t="n">
-        <v>1.6165509223938</v>
+        <v>1.61655080318451</v>
       </c>
       <c r="H124" t="n">
         <v>30870</v>
@@ -3994,7 +3994,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G125" t="n">
-        <v>1.58960843086243</v>
+        <v>1.58960831165314</v>
       </c>
       <c r="H125" t="n">
         <v>22469</v>
@@ -4023,7 +4023,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G126" t="n">
-        <v>1.6165509223938</v>
+        <v>1.61655080318451</v>
       </c>
       <c r="H126" t="n">
         <v>25208</v>
@@ -4052,7 +4052,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G127" t="n">
-        <v>1.63900303840637</v>
+        <v>1.63900291919708</v>
       </c>
       <c r="H127" t="n">
         <v>3233</v>
@@ -4110,7 +4110,7 @@
         <v>1.80900001525879</v>
       </c>
       <c r="G129" t="n">
-        <v>1.62463366985321</v>
+        <v>1.62463355064392</v>
       </c>
       <c r="H129" t="n">
         <v>7722</v>
@@ -4139,7 +4139,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G130" t="n">
-        <v>1.6300220489502</v>
+        <v>1.63002228736877</v>
       </c>
       <c r="H130" t="n">
         <v>11486</v>
@@ -4168,7 +4168,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G131" t="n">
-        <v>1.59409868717194</v>
+        <v>1.59409880638123</v>
       </c>
       <c r="H131" t="n">
         <v>16611</v>
@@ -4197,7 +4197,7 @@
         <v>1.69700002670288</v>
       </c>
       <c r="G132" t="n">
-        <v>1.52404820919037</v>
+        <v>1.52404832839966</v>
       </c>
       <c r="H132" t="n">
         <v>59729</v>
@@ -4226,7 +4226,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G133" t="n">
-        <v>1.46836698055267</v>
+        <v>1.46836709976196</v>
       </c>
       <c r="H133" t="n">
         <v>25558</v>
@@ -4284,7 +4284,7 @@
         <v>1.62100005149841</v>
       </c>
       <c r="G135" t="n">
-        <v>1.45579409599304</v>
+        <v>1.45579397678375</v>
       </c>
       <c r="H135" t="n">
         <v>55410</v>
@@ -4313,7 +4313,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G136" t="n">
-        <v>1.45489573478699</v>
+        <v>1.45489585399628</v>
       </c>
       <c r="H136" t="n">
         <v>62701</v>
@@ -4371,7 +4371,7 @@
         <v>1.66400003433228</v>
       </c>
       <c r="G138" t="n">
-        <v>1.49441146850586</v>
+        <v>1.49441158771515</v>
       </c>
       <c r="H138" t="n">
         <v>38824</v>
@@ -4458,7 +4458,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G141" t="n">
-        <v>1.49081909656525</v>
+        <v>1.49081921577454</v>
       </c>
       <c r="H141" t="n">
         <v>4203</v>
@@ -4487,7 +4487,7 @@
         <v>1.67900002002716</v>
       </c>
       <c r="G142" t="n">
-        <v>1.50788283348083</v>
+        <v>1.50788271427155</v>
       </c>
       <c r="H142" t="n">
         <v>35224</v>
@@ -4516,7 +4516,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G143" t="n">
-        <v>1.49081909656525</v>
+        <v>1.49081921577454</v>
       </c>
       <c r="H143" t="n">
         <v>26883</v>
@@ -4632,7 +4632,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G147" t="n">
-        <v>1.50429046154022</v>
+        <v>1.50429034233093</v>
       </c>
       <c r="H147" t="n">
         <v>12727</v>
@@ -4719,7 +4719,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G150" t="n">
-        <v>1.50429046154022</v>
+        <v>1.50429034233093</v>
       </c>
       <c r="H150" t="n">
         <v>9385</v>
@@ -4864,7 +4864,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G155" t="n">
-        <v>1.52674245834351</v>
+        <v>1.5267425775528</v>
       </c>
       <c r="H155" t="n">
         <v>8511</v>
@@ -4922,7 +4922,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G157" t="n">
-        <v>1.52674245834351</v>
+        <v>1.5267425775528</v>
       </c>
       <c r="H157" t="n">
         <v>12054</v>
@@ -5183,7 +5183,7 @@
         <v>1.71399998664856</v>
       </c>
       <c r="G166" t="n">
-        <v>1.53931570053101</v>
+        <v>1.5393158197403</v>
       </c>
       <c r="H166" t="n">
         <v>50193</v>
@@ -5299,7 +5299,7 @@
         <v>1.93299996852875</v>
       </c>
       <c r="G170" t="n">
-        <v>1.7359961271286</v>
+        <v>1.73599600791931</v>
       </c>
       <c r="H170" t="n">
         <v>60291</v>
@@ -5357,7 +5357,7 @@
         <v>1.89300000667572</v>
       </c>
       <c r="G172" t="n">
-        <v>1.70007264614105</v>
+        <v>1.70007252693176</v>
       </c>
       <c r="H172" t="n">
         <v>29197</v>
@@ -5386,7 +5386,7 @@
         <v>1.84800004959106</v>
       </c>
       <c r="G173" t="n">
-        <v>1.65965890884399</v>
+        <v>1.65965902805328</v>
       </c>
       <c r="H173" t="n">
         <v>102738</v>
@@ -5473,7 +5473,7 @@
         <v>1.85899996757507</v>
       </c>
       <c r="G176" t="n">
-        <v>1.66953778266907</v>
+        <v>1.66953766345978</v>
       </c>
       <c r="H176" t="n">
         <v>24532</v>
@@ -5502,7 +5502,7 @@
         <v>1.86800003051758</v>
       </c>
       <c r="G177" t="n">
-        <v>1.67762064933777</v>
+        <v>1.67762053012848</v>
       </c>
       <c r="H177" t="n">
         <v>59095</v>
@@ -5618,7 +5618,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G181" t="n">
-        <v>1.68839764595032</v>
+        <v>1.68839752674103</v>
       </c>
       <c r="H181" t="n">
         <v>27805</v>
@@ -5705,7 +5705,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G184" t="n">
-        <v>1.63451254367828</v>
+        <v>1.63451242446899</v>
       </c>
       <c r="H184" t="n">
         <v>8710</v>
@@ -5763,7 +5763,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G186" t="n">
-        <v>1.6165509223938</v>
+        <v>1.61655080318451</v>
       </c>
       <c r="H186" t="n">
         <v>28218</v>
@@ -5792,7 +5792,7 @@
         <v>1.80099999904633</v>
       </c>
       <c r="G187" t="n">
-        <v>1.61744892597198</v>
+        <v>1.61744904518127</v>
       </c>
       <c r="H187" t="n">
         <v>18817</v>
@@ -5821,7 +5821,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G188" t="n">
-        <v>1.6165509223938</v>
+        <v>1.61655080318451</v>
       </c>
       <c r="H188" t="n">
         <v>35451</v>
@@ -5850,7 +5850,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G189" t="n">
-        <v>1.6165509223938</v>
+        <v>1.61655080318451</v>
       </c>
       <c r="H189" t="n">
         <v>33190</v>
@@ -5879,7 +5879,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G190" t="n">
-        <v>1.6165509223938</v>
+        <v>1.61655080318451</v>
       </c>
       <c r="H190" t="n">
         <v>29161</v>
@@ -5908,7 +5908,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G191" t="n">
-        <v>1.6165509223938</v>
+        <v>1.61655080318451</v>
       </c>
       <c r="H191" t="n">
         <v>2263</v>
@@ -5937,7 +5937,7 @@
         <v>1.80200004577637</v>
       </c>
       <c r="G192" t="n">
-        <v>1.61834716796875</v>
+        <v>1.61834704875946</v>
       </c>
       <c r="H192" t="n">
         <v>4696</v>
@@ -5966,7 +5966,7 @@
         <v>1.80200004577637</v>
       </c>
       <c r="G193" t="n">
-        <v>1.61834716796875</v>
+        <v>1.61834704875946</v>
       </c>
       <c r="H193" t="n">
         <v>6904</v>
@@ -5995,7 +5995,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G194" t="n">
-        <v>1.63451254367828</v>
+        <v>1.63451242446899</v>
       </c>
       <c r="H194" t="n">
         <v>7919</v>
@@ -6024,7 +6024,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G195" t="n">
-        <v>1.63451254367828</v>
+        <v>1.63451242446899</v>
       </c>
       <c r="H195" t="n">
         <v>15652</v>
@@ -6053,7 +6053,7 @@
         <v>1.83299994468689</v>
       </c>
       <c r="G196" t="n">
-        <v>1.64618754386902</v>
+        <v>1.64618766307831</v>
       </c>
       <c r="H196" t="n">
         <v>9565</v>
@@ -6111,7 +6111,7 @@
         <v>1.875</v>
       </c>
       <c r="G198" t="n">
-        <v>1.68390715122223</v>
+        <v>1.68390727043152</v>
       </c>
       <c r="H198" t="n">
         <v>38123</v>
@@ -6169,7 +6169,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G200" t="n">
-        <v>1.68839764595032</v>
+        <v>1.68839752674103</v>
       </c>
       <c r="H200" t="n">
         <v>22315</v>
@@ -6227,7 +6227,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G202" t="n">
-        <v>1.66145515441895</v>
+        <v>1.66145503520966</v>
       </c>
       <c r="H202" t="n">
         <v>14854</v>
@@ -6285,7 +6285,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G204" t="n">
-        <v>1.66145515441895</v>
+        <v>1.66145503520966</v>
       </c>
       <c r="H204" t="n">
         <v>39083</v>
@@ -6401,7 +6401,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G208" t="n">
-        <v>1.63451254367828</v>
+        <v>1.63451242446899</v>
       </c>
       <c r="H208" t="n">
         <v>34872</v>
@@ -6459,7 +6459,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G210" t="n">
-        <v>1.66145515441895</v>
+        <v>1.66145503520966</v>
       </c>
       <c r="H210" t="n">
         <v>12976</v>
@@ -6488,7 +6488,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G211" t="n">
-        <v>1.65247416496277</v>
+        <v>1.65247428417206</v>
       </c>
       <c r="H211" t="n">
         <v>11706</v>
@@ -6517,7 +6517,7 @@
         <v>1.86899995803833</v>
       </c>
       <c r="G212" t="n">
-        <v>1.67851853370667</v>
+        <v>1.67851877212524</v>
       </c>
       <c r="H212" t="n">
         <v>8145</v>
@@ -6546,7 +6546,7 @@
         <v>1.86899995803833</v>
       </c>
       <c r="G213" t="n">
-        <v>1.67851853370667</v>
+        <v>1.67851877212524</v>
       </c>
       <c r="H213" t="n">
         <v>6757</v>
@@ -6575,7 +6575,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G214" t="n">
-        <v>1.65247416496277</v>
+        <v>1.65247428417206</v>
       </c>
       <c r="H214" t="n">
         <v>7430</v>
@@ -6604,7 +6604,7 @@
         <v>1.86800003051758</v>
       </c>
       <c r="G215" t="n">
-        <v>1.67762064933777</v>
+        <v>1.67762053012848</v>
       </c>
       <c r="H215" t="n">
         <v>3321</v>
@@ -6633,7 +6633,7 @@
         <v>1.8289999961853</v>
       </c>
       <c r="G216" t="n">
-        <v>1.64259541034698</v>
+        <v>1.6425952911377</v>
       </c>
       <c r="H216" t="n">
         <v>15402</v>
@@ -6662,7 +6662,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G217" t="n">
-        <v>1.63451254367828</v>
+        <v>1.63451242446899</v>
       </c>
       <c r="H217" t="n">
         <v>3906</v>
@@ -6720,7 +6720,7 @@
         <v>1.83700001239777</v>
       </c>
       <c r="G219" t="n">
-        <v>1.64978003501892</v>
+        <v>1.64977991580963</v>
       </c>
       <c r="H219" t="n">
         <v>23250</v>
@@ -6778,7 +6778,7 @@
         <v>1.80200004577637</v>
       </c>
       <c r="G221" t="n">
-        <v>1.61834716796875</v>
+        <v>1.61834704875946</v>
       </c>
       <c r="H221" t="n">
         <v>17670</v>
@@ -6807,7 +6807,7 @@
         <v>1.83700001239777</v>
       </c>
       <c r="G222" t="n">
-        <v>1.64978003501892</v>
+        <v>1.64977991580963</v>
       </c>
       <c r="H222" t="n">
         <v>16935</v>
@@ -6836,7 +6836,7 @@
         <v>1.84800004959106</v>
       </c>
       <c r="G223" t="n">
-        <v>1.65965890884399</v>
+        <v>1.65965902805328</v>
       </c>
       <c r="H223" t="n">
         <v>13665</v>
@@ -6894,7 +6894,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G225" t="n">
-        <v>1.58960843086243</v>
+        <v>1.58960831165314</v>
       </c>
       <c r="H225" t="n">
         <v>117138</v>
@@ -6923,7 +6923,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G226" t="n">
-        <v>1.52674245834351</v>
+        <v>1.5267425775528</v>
       </c>
       <c r="H226" t="n">
         <v>99175</v>
@@ -6952,7 +6952,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G227" t="n">
-        <v>1.49081909656525</v>
+        <v>1.49081921577454</v>
       </c>
       <c r="H227" t="n">
         <v>74656</v>
@@ -6981,7 +6981,7 @@
         <v>1.65799999237061</v>
       </c>
       <c r="G228" t="n">
-        <v>1.48902308940887</v>
+        <v>1.4890228509903</v>
       </c>
       <c r="H228" t="n">
         <v>27997</v>
@@ -7068,7 +7068,7 @@
         <v>1.49199998378754</v>
       </c>
       <c r="G231" t="n">
-        <v>1.33994102478027</v>
+        <v>1.33994114398956</v>
       </c>
       <c r="H231" t="n">
         <v>200414</v>
@@ -7097,7 +7097,7 @@
         <v>1.49199998378754</v>
       </c>
       <c r="G232" t="n">
-        <v>1.33994102478027</v>
+        <v>1.33994114398956</v>
       </c>
       <c r="H232" t="n">
         <v>104739</v>
@@ -7126,7 +7126,7 @@
         <v>1.49699997901917</v>
       </c>
       <c r="G233" t="n">
-        <v>1.34443151950836</v>
+        <v>1.34443140029907</v>
       </c>
       <c r="H233" t="n">
         <v>56235</v>
@@ -7242,7 +7242,7 @@
         <v>1.52199995517731</v>
       </c>
       <c r="G237" t="n">
-        <v>1.36688363552094</v>
+        <v>1.36688339710236</v>
       </c>
       <c r="H237" t="n">
         <v>139886</v>
@@ -7271,7 +7271,7 @@
         <v>1.5</v>
       </c>
       <c r="G238" t="n">
-        <v>1.34712564945221</v>
+        <v>1.3471257686615</v>
       </c>
       <c r="H238" t="n">
         <v>44687</v>
@@ -7416,7 +7416,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G243" t="n">
-        <v>1.4504052400589</v>
+        <v>1.45040535926819</v>
       </c>
       <c r="H243" t="n">
         <v>70934</v>
@@ -7445,7 +7445,7 @@
         <v>1.61300003528595</v>
       </c>
       <c r="G244" t="n">
-        <v>1.44860935211182</v>
+        <v>1.44860923290253</v>
       </c>
       <c r="H244" t="n">
         <v>29084</v>
@@ -7474,7 +7474,7 @@
         <v>1.65299999713898</v>
       </c>
       <c r="G245" t="n">
-        <v>1.48453259468079</v>
+        <v>1.48453271389008</v>
       </c>
       <c r="H245" t="n">
         <v>48017</v>
@@ -7503,7 +7503,7 @@
         <v>1.67900002002716</v>
       </c>
       <c r="G246" t="n">
-        <v>1.50788283348083</v>
+        <v>1.50788271427155</v>
       </c>
       <c r="H246" t="n">
         <v>43881</v>
@@ -7677,7 +7677,7 @@
         <v>1.78600001335144</v>
       </c>
       <c r="G252" t="n">
-        <v>1.60397779941559</v>
+        <v>1.6039776802063</v>
       </c>
       <c r="H252" t="n">
         <v>99793</v>
@@ -7996,7 +7996,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G263" t="n">
-        <v>1.65247416496277</v>
+        <v>1.65247428417206</v>
       </c>
       <c r="H263" t="n">
         <v>21549</v>
@@ -8054,7 +8054,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G265" t="n">
-        <v>1.64798390865326</v>
+        <v>1.64798378944397</v>
       </c>
       <c r="H265" t="n">
         <v>68170</v>
@@ -8112,7 +8112,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G267" t="n">
-        <v>1.65247416496277</v>
+        <v>1.65247428417206</v>
       </c>
       <c r="H267" t="n">
         <v>16547</v>
@@ -8170,7 +8170,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G269" t="n">
-        <v>1.63451254367828</v>
+        <v>1.63451242446899</v>
       </c>
       <c r="H269" t="n">
         <v>12835</v>
@@ -8199,7 +8199,7 @@
         <v>1.80099999904633</v>
       </c>
       <c r="G270" t="n">
-        <v>1.61744892597198</v>
+        <v>1.61744904518127</v>
       </c>
       <c r="H270" t="n">
         <v>18653</v>
@@ -8257,7 +8257,7 @@
         <v>1.78600001335144</v>
       </c>
       <c r="G272" t="n">
-        <v>1.60397779941559</v>
+        <v>1.6039776802063</v>
       </c>
       <c r="H272" t="n">
         <v>14300</v>
@@ -8373,7 +8373,7 @@
         <v>1.69599997997284</v>
       </c>
       <c r="G276" t="n">
-        <v>1.52315008640289</v>
+        <v>1.52315020561218</v>
       </c>
       <c r="H276" t="n">
         <v>43115</v>
@@ -8402,7 +8402,7 @@
         <v>1.68099999427795</v>
       </c>
       <c r="G277" t="n">
-        <v>1.50967884063721</v>
+        <v>1.5096789598465</v>
       </c>
       <c r="H277" t="n">
         <v>16296</v>
@@ -8605,7 +8605,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G284" t="n">
-        <v>1.48183846473694</v>
+        <v>1.48183834552765</v>
       </c>
       <c r="H284" t="n">
         <v>14957</v>
@@ -8634,7 +8634,7 @@
         <v>1.62100005149841</v>
       </c>
       <c r="G285" t="n">
-        <v>1.45579409599304</v>
+        <v>1.45579397678375</v>
       </c>
       <c r="H285" t="n">
         <v>60471</v>
@@ -8663,7 +8663,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G286" t="n">
-        <v>1.47285747528076</v>
+        <v>1.47285735607147</v>
       </c>
       <c r="H286" t="n">
         <v>15937</v>
@@ -8692,7 +8692,7 @@
         <v>1.63100004196167</v>
       </c>
       <c r="G287" t="n">
-        <v>1.46477460861206</v>
+        <v>1.46477472782135</v>
       </c>
       <c r="H287" t="n">
         <v>11720</v>
@@ -8721,7 +8721,7 @@
         <v>1.51900005340576</v>
       </c>
       <c r="G288" t="n">
-        <v>1.36418926715851</v>
+        <v>1.3641893863678</v>
       </c>
       <c r="H288" t="n">
         <v>409131</v>
@@ -8779,7 +8779,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G290" t="n">
-        <v>1.38304889202118</v>
+        <v>1.38304901123047</v>
       </c>
       <c r="H290" t="n">
         <v>83769</v>
@@ -8866,7 +8866,7 @@
         <v>1.46700000762939</v>
       </c>
       <c r="G293" t="n">
-        <v>1.3174889087677</v>
+        <v>1.31748902797699</v>
       </c>
       <c r="H293" t="n">
         <v>48300</v>
@@ -8924,7 +8924,7 @@
         <v>1.48399996757507</v>
       </c>
       <c r="G295" t="n">
-        <v>1.33275640010834</v>
+        <v>1.33275628089905</v>
       </c>
       <c r="H295" t="n">
         <v>240883</v>
@@ -8982,7 +8982,7 @@
         <v>1.47800004482269</v>
       </c>
       <c r="G297" t="n">
-        <v>1.32736790180206</v>
+        <v>1.32736802101135</v>
       </c>
       <c r="H297" t="n">
         <v>41633</v>
@@ -9011,7 +9011,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G298" t="n">
-        <v>1.3381450176239</v>
+        <v>1.33814489841461</v>
       </c>
       <c r="H298" t="n">
         <v>73910</v>
@@ -9040,7 +9040,7 @@
         <v>1.55299997329712</v>
       </c>
       <c r="G299" t="n">
-        <v>1.3947240114212</v>
+        <v>1.39472424983978</v>
       </c>
       <c r="H299" t="n">
         <v>111237</v>
@@ -9127,7 +9127,7 @@
         <v>1.58599996566772</v>
       </c>
       <c r="G302" t="n">
-        <v>1.424360871315</v>
+        <v>1.42436099052429</v>
       </c>
       <c r="H302" t="n">
         <v>52521</v>
@@ -9272,7 +9272,7 @@
         <v>1.57700002193451</v>
       </c>
       <c r="G307" t="n">
-        <v>1.41627812385559</v>
+        <v>1.41627824306488</v>
       </c>
       <c r="H307" t="n">
         <v>147605</v>
@@ -9330,7 +9330,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G309" t="n">
-        <v>1.37406837940216</v>
+        <v>1.37406814098358</v>
       </c>
       <c r="H309" t="n">
         <v>68905</v>
@@ -9359,7 +9359,7 @@
         <v>1.53900003433228</v>
       </c>
       <c r="G310" t="n">
-        <v>1.38215112686157</v>
+        <v>1.38215100765228</v>
       </c>
       <c r="H310" t="n">
         <v>82753</v>
@@ -9388,7 +9388,7 @@
         <v>1.53600001335144</v>
       </c>
       <c r="G311" t="n">
-        <v>1.37945675849915</v>
+        <v>1.37945663928986</v>
       </c>
       <c r="H311" t="n">
         <v>31074</v>
@@ -9417,7 +9417,7 @@
         <v>1.54499995708466</v>
       </c>
       <c r="G312" t="n">
-        <v>1.38753938674927</v>
+        <v>1.38753950595856</v>
       </c>
       <c r="H312" t="n">
         <v>76286</v>
@@ -9446,7 +9446,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G313" t="n">
-        <v>1.38304889202118</v>
+        <v>1.38304901123047</v>
       </c>
       <c r="H313" t="n">
         <v>62248</v>
@@ -9475,7 +9475,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G314" t="n">
-        <v>1.39652037620544</v>
+        <v>1.39652025699615</v>
       </c>
       <c r="H314" t="n">
         <v>147645</v>
@@ -9794,7 +9794,7 @@
         <v>1.65299999713898</v>
       </c>
       <c r="G325" t="n">
-        <v>1.48453259468079</v>
+        <v>1.48453271389008</v>
       </c>
       <c r="H325" t="n">
         <v>133633</v>
@@ -9852,7 +9852,7 @@
         <v>1.63399994373322</v>
       </c>
       <c r="G327" t="n">
-        <v>1.46746897697449</v>
+        <v>1.4674688577652</v>
       </c>
       <c r="H327" t="n">
         <v>29486</v>
@@ -9939,7 +9939,7 @@
         <v>1.625</v>
       </c>
       <c r="G330" t="n">
-        <v>1.45938622951508</v>
+        <v>1.45938611030579</v>
       </c>
       <c r="H330" t="n">
         <v>44118</v>
@@ -10055,7 +10055,7 @@
         <v>1.60300004482269</v>
       </c>
       <c r="G334" t="n">
-        <v>1.43962836265564</v>
+        <v>1.43962848186493</v>
       </c>
       <c r="H334" t="n">
         <v>19962</v>
@@ -10113,7 +10113,7 @@
         <v>1.63399994373322</v>
       </c>
       <c r="G336" t="n">
-        <v>1.46746897697449</v>
+        <v>1.4674688577652</v>
       </c>
       <c r="H336" t="n">
         <v>79269</v>
@@ -10142,7 +10142,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G337" t="n">
-        <v>1.49081909656525</v>
+        <v>1.49081921577454</v>
       </c>
       <c r="H337" t="n">
         <v>86087</v>
@@ -10171,7 +10171,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G338" t="n">
-        <v>1.49081909656525</v>
+        <v>1.49081921577454</v>
       </c>
       <c r="H338" t="n">
         <v>44874</v>
@@ -10200,7 +10200,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G339" t="n">
-        <v>1.49081909656525</v>
+        <v>1.49081921577454</v>
       </c>
       <c r="H339" t="n">
         <v>55785</v>
@@ -10229,7 +10229,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G340" t="n">
-        <v>1.49081909656525</v>
+        <v>1.49081921577454</v>
       </c>
       <c r="H340" t="n">
         <v>80637</v>
@@ -10258,7 +10258,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G341" t="n">
-        <v>1.48183846473694</v>
+        <v>1.48183834552765</v>
       </c>
       <c r="H341" t="n">
         <v>38360</v>
@@ -10316,7 +10316,7 @@
         <v>1.67900002002716</v>
       </c>
       <c r="G343" t="n">
-        <v>1.50788283348083</v>
+        <v>1.50788271427155</v>
       </c>
       <c r="H343" t="n">
         <v>109764</v>
@@ -10374,7 +10374,7 @@
         <v>1.67900002002716</v>
       </c>
       <c r="G345" t="n">
-        <v>1.50788283348083</v>
+        <v>1.50788271427155</v>
       </c>
       <c r="H345" t="n">
         <v>60237</v>
@@ -10403,7 +10403,7 @@
         <v>1.70099997520447</v>
       </c>
       <c r="G346" t="n">
-        <v>1.52764058113098</v>
+        <v>1.52764046192169</v>
       </c>
       <c r="H346" t="n">
         <v>51869</v>
@@ -10519,7 +10519,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G350" t="n">
-        <v>1.67941677570343</v>
+        <v>1.67941665649414</v>
       </c>
       <c r="H350" t="n">
         <v>566755</v>
@@ -10606,7 +10606,7 @@
         <v>1.80099999904633</v>
       </c>
       <c r="G353" t="n">
-        <v>1.61744892597198</v>
+        <v>1.61744904518127</v>
       </c>
       <c r="H353" t="n">
         <v>167327</v>
@@ -10664,7 +10664,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G355" t="n">
-        <v>1.65247416496277</v>
+        <v>1.65247428417206</v>
       </c>
       <c r="H355" t="n">
         <v>265133</v>
@@ -10722,7 +10722,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G357" t="n">
-        <v>1.74228250980377</v>
+        <v>1.74228262901306</v>
       </c>
       <c r="H357" t="n">
         <v>320048</v>
@@ -10751,7 +10751,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G358" t="n">
-        <v>1.73330175876617</v>
+        <v>1.73330187797546</v>
       </c>
       <c r="H358" t="n">
         <v>184861</v>
@@ -10780,7 +10780,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G359" t="n">
-        <v>1.72432100772858</v>
+        <v>1.72432076931</v>
       </c>
       <c r="H359" t="n">
         <v>120208</v>
@@ -10809,7 +10809,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G360" t="n">
-        <v>1.72432100772858</v>
+        <v>1.72432076931</v>
       </c>
       <c r="H360" t="n">
         <v>68025</v>
@@ -10838,7 +10838,7 @@
         <v>1.875</v>
       </c>
       <c r="G361" t="n">
-        <v>1.68390715122223</v>
+        <v>1.68390727043152</v>
       </c>
       <c r="H361" t="n">
         <v>243867</v>
@@ -10954,7 +10954,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G365" t="n">
-        <v>1.66145515441895</v>
+        <v>1.66145503520966</v>
       </c>
       <c r="H365" t="n">
         <v>59030</v>
@@ -10983,7 +10983,7 @@
         <v>1.85899996757507</v>
       </c>
       <c r="G366" t="n">
-        <v>1.66953778266907</v>
+        <v>1.66953766345978</v>
       </c>
       <c r="H366" t="n">
         <v>64186</v>
@@ -11070,7 +11070,7 @@
         <v>1.80900001525879</v>
       </c>
       <c r="G369" t="n">
-        <v>1.62463366985321</v>
+        <v>1.62463355064392</v>
       </c>
       <c r="H369" t="n">
         <v>77361</v>
@@ -11099,7 +11099,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G370" t="n">
-        <v>1.6165509223938</v>
+        <v>1.61655080318451</v>
       </c>
       <c r="H370" t="n">
         <v>66407</v>
@@ -11128,7 +11128,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G371" t="n">
-        <v>1.63900303840637</v>
+        <v>1.63900291919708</v>
       </c>
       <c r="H371" t="n">
         <v>52595</v>
@@ -11157,7 +11157,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G372" t="n">
-        <v>1.65247416496277</v>
+        <v>1.65247428417206</v>
       </c>
       <c r="H372" t="n">
         <v>72016</v>
@@ -11186,7 +11186,7 @@
         <v>1.83700001239777</v>
       </c>
       <c r="G373" t="n">
-        <v>1.64978003501892</v>
+        <v>1.64977991580963</v>
       </c>
       <c r="H373" t="n">
         <v>46666</v>
@@ -11273,7 +11273,7 @@
         <v>1.84200000762939</v>
       </c>
       <c r="G376" t="n">
-        <v>1.65427052974701</v>
+        <v>1.65427041053772</v>
       </c>
       <c r="H376" t="n">
         <v>35182</v>
@@ -11360,7 +11360,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G379" t="n">
-        <v>1.6165509223938</v>
+        <v>1.61655080318451</v>
       </c>
       <c r="H379" t="n">
         <v>26590</v>
@@ -11418,7 +11418,7 @@
         <v>1.7610000371933</v>
       </c>
       <c r="G381" t="n">
-        <v>1.58152556419373</v>
+        <v>1.58152568340302</v>
       </c>
       <c r="H381" t="n">
         <v>104816</v>
@@ -11447,7 +11447,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G382" t="n">
-        <v>1.58960843086243</v>
+        <v>1.58960831165314</v>
       </c>
       <c r="H382" t="n">
         <v>25737</v>
@@ -11476,7 +11476,7 @@
         <v>1.70299994945526</v>
       </c>
       <c r="G383" t="n">
-        <v>1.52943658828735</v>
+        <v>1.52943670749664</v>
       </c>
       <c r="H383" t="n">
         <v>66555</v>
@@ -11505,7 +11505,7 @@
         <v>1.74800002574921</v>
       </c>
       <c r="G384" t="n">
-        <v>1.5698504447937</v>
+        <v>1.56985056400299</v>
       </c>
       <c r="H384" t="n">
         <v>79551</v>
@@ -11534,7 +11534,7 @@
         <v>1.72099995613098</v>
       </c>
       <c r="G385" t="n">
-        <v>1.54560220241547</v>
+        <v>1.54560232162476</v>
       </c>
       <c r="H385" t="n">
         <v>48776</v>
@@ -11563,7 +11563,7 @@
         <v>1.72099995613098</v>
       </c>
       <c r="G386" t="n">
-        <v>1.54560220241547</v>
+        <v>1.54560232162476</v>
       </c>
       <c r="H386" t="n">
         <v>93328</v>
@@ -11650,7 +11650,7 @@
         <v>1.69700002670288</v>
       </c>
       <c r="G389" t="n">
-        <v>1.52404820919037</v>
+        <v>1.52404832839966</v>
       </c>
       <c r="H389" t="n">
         <v>22102</v>
@@ -11824,7 +11824,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G395" t="n">
-        <v>1.6165509223938</v>
+        <v>1.61655080318451</v>
       </c>
       <c r="H395" t="n">
         <v>19546</v>
@@ -11882,7 +11882,7 @@
         <v>1.80900001525879</v>
       </c>
       <c r="G397" t="n">
-        <v>1.62463366985321</v>
+        <v>1.62463355064392</v>
       </c>
       <c r="H397" t="n">
         <v>3288</v>
@@ -11911,7 +11911,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G398" t="n">
-        <v>1.58960843086243</v>
+        <v>1.58960831165314</v>
       </c>
       <c r="H398" t="n">
         <v>55429</v>
@@ -11940,7 +11940,7 @@
         <v>1.7610000371933</v>
       </c>
       <c r="G399" t="n">
-        <v>1.58152556419373</v>
+        <v>1.58152568340302</v>
       </c>
       <c r="H399" t="n">
         <v>10377</v>
@@ -12056,7 +12056,7 @@
         <v>1.77799999713898</v>
       </c>
       <c r="G403" t="n">
-        <v>1.59679293632507</v>
+        <v>1.59679305553436</v>
       </c>
       <c r="H403" t="n">
         <v>16299</v>
@@ -12172,7 +12172,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G407" t="n">
-        <v>1.63451254367828</v>
+        <v>1.63451242446899</v>
       </c>
       <c r="H407" t="n">
         <v>64582</v>
@@ -12259,7 +12259,7 @@
         <v>1.80900001525879</v>
       </c>
       <c r="G410" t="n">
-        <v>1.62463366985321</v>
+        <v>1.62463355064392</v>
       </c>
       <c r="H410" t="n">
         <v>43219</v>
@@ -12317,7 +12317,7 @@
         <v>1.80099999904633</v>
       </c>
       <c r="G412" t="n">
-        <v>1.61744892597198</v>
+        <v>1.61744904518127</v>
       </c>
       <c r="H412" t="n">
         <v>27092</v>
@@ -12433,7 +12433,7 @@
         <v>1.78600001335144</v>
       </c>
       <c r="G416" t="n">
-        <v>1.60397779941559</v>
+        <v>1.6039776802063</v>
       </c>
       <c r="H416" t="n">
         <v>17027</v>
@@ -12462,7 +12462,7 @@
         <v>1.75899994373322</v>
       </c>
       <c r="G417" t="n">
-        <v>1.57972931861877</v>
+        <v>1.57972919940948</v>
       </c>
       <c r="H417" t="n">
         <v>17456</v>
@@ -12520,7 +12520,7 @@
         <v>1.73099994659424</v>
       </c>
       <c r="G419" t="n">
-        <v>1.55458307266235</v>
+        <v>1.55458295345306</v>
       </c>
       <c r="H419" t="n">
         <v>8031</v>
@@ -12549,7 +12549,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G420" t="n">
-        <v>1.6165509223938</v>
+        <v>1.61655080318451</v>
       </c>
       <c r="H420" t="n">
         <v>103982</v>
@@ -12694,7 +12694,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G425" t="n">
-        <v>1.72432100772858</v>
+        <v>1.72432076931</v>
       </c>
       <c r="H425" t="n">
         <v>904742</v>
@@ -12810,7 +12810,7 @@
         <v>1.85300004482269</v>
       </c>
       <c r="G429" t="n">
-        <v>1.66414940357208</v>
+        <v>1.66414928436279</v>
       </c>
       <c r="H429" t="n">
         <v>158747</v>
@@ -12897,7 +12897,7 @@
         <v>1.89600002765656</v>
       </c>
       <c r="G432" t="n">
-        <v>1.70276701450348</v>
+        <v>1.70276689529419</v>
       </c>
       <c r="H432" t="n">
         <v>450452</v>
@@ -12926,7 +12926,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G433" t="n">
-        <v>1.81412935256958</v>
+        <v>1.814129114151</v>
       </c>
       <c r="H433" t="n">
         <v>617385</v>
@@ -12955,7 +12955,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G434" t="n">
-        <v>1.88597583770752</v>
+        <v>1.88597595691681</v>
       </c>
       <c r="H434" t="n">
         <v>616287</v>
@@ -12984,7 +12984,7 @@
         <v>2.19600009918213</v>
       </c>
       <c r="G435" t="n">
-        <v>1.97219216823578</v>
+        <v>1.97219228744507</v>
       </c>
       <c r="H435" t="n">
         <v>825548</v>
@@ -13013,7 +13013,7 @@
         <v>2.24600005149841</v>
       </c>
       <c r="G436" t="n">
-        <v>2.01709651947021</v>
+        <v>2.01709628105164</v>
       </c>
       <c r="H436" t="n">
         <v>460797</v>
@@ -13071,7 +13071,7 @@
         <v>2.41199994087219</v>
       </c>
       <c r="G438" t="n">
-        <v>2.16617822647095</v>
+        <v>2.16617846488953</v>
       </c>
       <c r="H438" t="n">
         <v>990773</v>
@@ -13100,7 +13100,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G439" t="n">
-        <v>2.32603693008423</v>
+        <v>2.32603716850281</v>
       </c>
       <c r="H439" t="n">
         <v>793101</v>
@@ -13158,7 +13158,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G441" t="n">
-        <v>2.25419020652771</v>
+        <v>2.25419044494629</v>
       </c>
       <c r="H441" t="n">
         <v>349635</v>
@@ -13187,7 +13187,7 @@
         <v>2.53800010681152</v>
       </c>
       <c r="G442" t="n">
-        <v>2.27933692932129</v>
+        <v>2.27933669090271</v>
       </c>
       <c r="H442" t="n">
         <v>344384</v>
@@ -13216,7 +13216,7 @@
         <v>2.57599997520447</v>
       </c>
       <c r="G443" t="n">
-        <v>2.31346392631531</v>
+        <v>2.31346416473389</v>
       </c>
       <c r="H443" t="n">
         <v>153036</v>
@@ -13245,7 +13245,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G444" t="n">
-        <v>2.36196064949036</v>
+        <v>2.36196041107178</v>
       </c>
       <c r="H444" t="n">
         <v>291112</v>
@@ -13274,7 +13274,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G445" t="n">
-        <v>2.3529794216156</v>
+        <v>2.35297966003418</v>
       </c>
       <c r="H445" t="n">
         <v>213302</v>
@@ -13361,7 +13361,7 @@
         <v>2.53600001335144</v>
       </c>
       <c r="G448" t="n">
-        <v>2.27754068374634</v>
+        <v>2.27754044532776</v>
       </c>
       <c r="H448" t="n">
         <v>182982</v>
@@ -13448,7 +13448,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G451" t="n">
-        <v>2.30807542800903</v>
+        <v>2.30807518959045</v>
       </c>
       <c r="H451" t="n">
         <v>214951</v>
@@ -13477,7 +13477,7 @@
         <v>2.56399989128113</v>
       </c>
       <c r="G452" t="n">
-        <v>2.30268692970276</v>
+        <v>2.30268669128418</v>
       </c>
       <c r="H452" t="n">
         <v>110046</v>
@@ -13535,7 +13535,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G454" t="n">
-        <v>2.26317119598389</v>
+        <v>2.26317095756531</v>
       </c>
       <c r="H454" t="n">
         <v>120776</v>
@@ -13564,7 +13564,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G455" t="n">
-        <v>2.20030522346497</v>
+        <v>2.20030546188354</v>
       </c>
       <c r="H455" t="n">
         <v>150509</v>
@@ -13651,7 +13651,7 @@
         <v>2.50600004196167</v>
       </c>
       <c r="G458" t="n">
-        <v>2.25059819221497</v>
+        <v>2.25059795379639</v>
       </c>
       <c r="H458" t="n">
         <v>401496</v>
@@ -13680,7 +13680,7 @@
         <v>2.54800009727478</v>
       </c>
       <c r="G459" t="n">
-        <v>2.28831768035889</v>
+        <v>2.28831791877747</v>
       </c>
       <c r="H459" t="n">
         <v>214035</v>
@@ -13709,7 +13709,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G460" t="n">
-        <v>2.32603693008423</v>
+        <v>2.32603716850281</v>
       </c>
       <c r="H460" t="n">
         <v>221159</v>
@@ -13738,7 +13738,7 @@
         <v>2.80200004577637</v>
       </c>
       <c r="G461" t="n">
-        <v>2.51643085479736</v>
+        <v>2.51643109321594</v>
       </c>
       <c r="H461" t="n">
         <v>904445</v>
@@ -13796,7 +13796,7 @@
         <v>2.86199998855591</v>
       </c>
       <c r="G463" t="n">
-        <v>2.57031583786011</v>
+        <v>2.57031607627869</v>
       </c>
       <c r="H463" t="n">
         <v>833255</v>
@@ -14057,7 +14057,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G472" t="n">
-        <v>2.55055785179138</v>
+        <v>2.55055809020996</v>
       </c>
       <c r="H472" t="n">
         <v>90536</v>
@@ -14086,7 +14086,7 @@
         <v>2.7739999294281</v>
       </c>
       <c r="G473" t="n">
-        <v>2.49128460884094</v>
+        <v>2.49128437042236</v>
       </c>
       <c r="H473" t="n">
         <v>164387</v>
@@ -14115,7 +14115,7 @@
         <v>2.79200005531311</v>
       </c>
       <c r="G474" t="n">
-        <v>2.50744986534119</v>
+        <v>2.50745010375977</v>
       </c>
       <c r="H474" t="n">
         <v>83459</v>
@@ -14202,7 +14202,7 @@
         <v>2.3659999370575</v>
       </c>
       <c r="G477" t="n">
-        <v>2.12486600875854</v>
+        <v>2.12486624717712</v>
       </c>
       <c r="H477" t="n">
         <v>1409761</v>
@@ -14231,7 +14231,7 @@
         <v>2.42400002479553</v>
       </c>
       <c r="G478" t="n">
-        <v>2.17695498466492</v>
+        <v>2.1769552230835</v>
       </c>
       <c r="H478" t="n">
         <v>603916</v>
@@ -14318,7 +14318,7 @@
         <v>2.25600004196167</v>
       </c>
       <c r="G481" t="n">
-        <v>2.02607727050781</v>
+        <v>2.02607703208923</v>
       </c>
       <c r="H481" t="n">
         <v>252490</v>
@@ -14434,7 +14434,7 @@
         <v>2.5</v>
       </c>
       <c r="G485" t="n">
-        <v>2.24520969390869</v>
+        <v>2.24520945549011</v>
       </c>
       <c r="H485" t="n">
         <v>157685</v>
@@ -14463,7 +14463,7 @@
         <v>2.48799991607666</v>
       </c>
       <c r="G486" t="n">
-        <v>2.23443222045898</v>
+        <v>2.23443245887756</v>
       </c>
       <c r="H486" t="n">
         <v>141038</v>
@@ -14521,7 +14521,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G488" t="n">
-        <v>2.25419020652771</v>
+        <v>2.25419044494629</v>
       </c>
       <c r="H488" t="n">
         <v>81174</v>
@@ -14608,7 +14608,7 @@
         <v>2.55800008773804</v>
       </c>
       <c r="G491" t="n">
-        <v>2.29729843139648</v>
+        <v>2.29729866981506</v>
       </c>
       <c r="H491" t="n">
         <v>201051</v>
@@ -14666,7 +14666,7 @@
         <v>2.48399996757507</v>
       </c>
       <c r="G493" t="n">
-        <v>2.23084020614624</v>
+        <v>2.23083996772766</v>
       </c>
       <c r="H493" t="n">
         <v>58887</v>
@@ -14869,7 +14869,7 @@
         <v>2.54800009727478</v>
       </c>
       <c r="G500" t="n">
-        <v>2.28831768035889</v>
+        <v>2.28831791877747</v>
       </c>
       <c r="H500" t="n">
         <v>105664</v>
@@ -14927,7 +14927,7 @@
         <v>2.5</v>
       </c>
       <c r="G502" t="n">
-        <v>2.24520969390869</v>
+        <v>2.24520945549011</v>
       </c>
       <c r="H502" t="n">
         <v>122381</v>
@@ -15101,7 +15101,7 @@
         <v>2.45199990272522</v>
       </c>
       <c r="G508" t="n">
-        <v>2.20210146903992</v>
+        <v>2.20210123062134</v>
       </c>
       <c r="H508" t="n">
         <v>123957</v>
@@ -15217,7 +15217,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G512" t="n">
-        <v>2.19132447242737</v>
+        <v>2.19132471084595</v>
       </c>
       <c r="H512" t="n">
         <v>101821</v>
@@ -15246,7 +15246,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G513" t="n">
-        <v>2.18234348297119</v>
+        <v>2.18234395980835</v>
       </c>
       <c r="H513" t="n">
         <v>98129</v>
@@ -15304,7 +15304,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G515" t="n">
-        <v>2.19132447242737</v>
+        <v>2.19132471084595</v>
       </c>
       <c r="H515" t="n">
         <v>50871</v>
@@ -15391,7 +15391,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G518" t="n">
-        <v>2.21826720237732</v>
+        <v>2.21826672554016</v>
       </c>
       <c r="H518" t="n">
         <v>107211</v>
@@ -15507,7 +15507,7 @@
         <v>2.42499995231628</v>
       </c>
       <c r="G522" t="n">
-        <v>2.17785334587097</v>
+        <v>2.17785310745239</v>
       </c>
       <c r="H522" t="n">
         <v>82741</v>
@@ -15536,7 +15536,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G523" t="n">
-        <v>2.12845873832703</v>
+        <v>2.12845849990845</v>
       </c>
       <c r="H523" t="n">
         <v>89038</v>
@@ -15565,7 +15565,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G524" t="n">
-        <v>2.04763102531433</v>
+        <v>2.04763126373291</v>
       </c>
       <c r="H524" t="n">
         <v>233885</v>
@@ -15623,7 +15623,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G526" t="n">
-        <v>2.06559252738953</v>
+        <v>2.06559276580811</v>
       </c>
       <c r="H526" t="n">
         <v>88709</v>
@@ -15652,7 +15652,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G527" t="n">
-        <v>2.09253549575806</v>
+        <v>2.09253525733948</v>
       </c>
       <c r="H527" t="n">
         <v>55735</v>
@@ -15681,7 +15681,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G528" t="n">
-        <v>2.08355450630188</v>
+        <v>2.08355402946472</v>
       </c>
       <c r="H528" t="n">
         <v>61089</v>
@@ -15739,7 +15739,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G530" t="n">
-        <v>2.10151600837708</v>
+        <v>2.10151624679565</v>
       </c>
       <c r="H530" t="n">
         <v>83765</v>
@@ -15768,7 +15768,7 @@
         <v>2.41499996185303</v>
       </c>
       <c r="G531" t="n">
-        <v>2.16887235641479</v>
+        <v>2.16887259483337</v>
       </c>
       <c r="H531" t="n">
         <v>279959</v>
@@ -15797,7 +15797,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G532" t="n">
-        <v>2.12845873832703</v>
+        <v>2.12845849990845</v>
       </c>
       <c r="H532" t="n">
         <v>155830</v>
@@ -15884,7 +15884,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G535" t="n">
-        <v>2.11947751045227</v>
+        <v>2.11947774887085</v>
       </c>
       <c r="H535" t="n">
         <v>99717</v>
@@ -15913,7 +15913,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G536" t="n">
-        <v>2.01170802116394</v>
+        <v>2.01170778274536</v>
       </c>
       <c r="H536" t="n">
         <v>202868</v>
@@ -16000,7 +16000,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G539" t="n">
-        <v>2.06559252738953</v>
+        <v>2.06559276580811</v>
       </c>
       <c r="H539" t="n">
         <v>88481</v>
@@ -16029,7 +16029,7 @@
         <v>2.26500010490417</v>
       </c>
       <c r="G540" t="n">
-        <v>2.03415989875793</v>
+        <v>2.03416013717651</v>
       </c>
       <c r="H540" t="n">
         <v>99980</v>
@@ -16058,7 +16058,7 @@
         <v>2.36500000953674</v>
       </c>
       <c r="G541" t="n">
-        <v>2.12396788597107</v>
+        <v>2.12396812438965</v>
       </c>
       <c r="H541" t="n">
         <v>172019</v>
@@ -16145,7 +16145,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G544" t="n">
-        <v>2.06559252738953</v>
+        <v>2.06559276580811</v>
       </c>
       <c r="H544" t="n">
         <v>94606</v>
@@ -16174,7 +16174,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G545" t="n">
-        <v>2.06559252738953</v>
+        <v>2.06559276580811</v>
       </c>
       <c r="H545" t="n">
         <v>90340</v>
@@ -16203,7 +16203,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G546" t="n">
-        <v>2.10151600837708</v>
+        <v>2.10151624679565</v>
       </c>
       <c r="H546" t="n">
         <v>81347</v>
@@ -16232,7 +16232,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G547" t="n">
-        <v>2.06559252738953</v>
+        <v>2.06559276580811</v>
       </c>
       <c r="H547" t="n">
         <v>66787</v>
@@ -16261,7 +16261,7 @@
         <v>2.3050000667572</v>
       </c>
       <c r="G548" t="n">
-        <v>2.07008337974548</v>
+        <v>2.0700831413269</v>
       </c>
       <c r="H548" t="n">
         <v>54720</v>
@@ -16290,7 +16290,7 @@
         <v>2.3050000667572</v>
       </c>
       <c r="G549" t="n">
-        <v>2.07008337974548</v>
+        <v>2.0700831413269</v>
       </c>
       <c r="H549" t="n">
         <v>66155</v>
@@ -16348,7 +16348,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G551" t="n">
-        <v>2.04763102531433</v>
+        <v>2.04763126373291</v>
       </c>
       <c r="H551" t="n">
         <v>51292</v>
@@ -16377,7 +16377,7 @@
         <v>2.21499991416931</v>
       </c>
       <c r="G552" t="n">
-        <v>1.9892555475235</v>
+        <v>1.98925566673279</v>
       </c>
       <c r="H552" t="n">
         <v>123803</v>
@@ -16435,7 +16435,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G554" t="n">
-        <v>1.87699520587921</v>
+        <v>1.87699496746063</v>
       </c>
       <c r="H554" t="n">
         <v>92111</v>
@@ -16464,7 +16464,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G555" t="n">
-        <v>1.903937458992</v>
+        <v>1.90393769741058</v>
       </c>
       <c r="H555" t="n">
         <v>98801</v>
@@ -16493,7 +16493,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G556" t="n">
-        <v>1.85005247592926</v>
+        <v>1.85005259513855</v>
       </c>
       <c r="H556" t="n">
         <v>37112</v>
@@ -16551,7 +16551,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G558" t="n">
-        <v>1.92189943790436</v>
+        <v>1.92189931869507</v>
       </c>
       <c r="H558" t="n">
         <v>89704</v>
@@ -16609,7 +16609,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G560" t="n">
-        <v>1.9847651720047</v>
+        <v>1.98476529121399</v>
       </c>
       <c r="H560" t="n">
         <v>45217</v>
@@ -16638,7 +16638,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G561" t="n">
-        <v>2.01170802116394</v>
+        <v>2.01170778274536</v>
       </c>
       <c r="H561" t="n">
         <v>40737</v>
@@ -16841,7 +16841,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G568" t="n">
-        <v>2.01170802116394</v>
+        <v>2.01170778274536</v>
       </c>
       <c r="H568" t="n">
         <v>188558</v>
@@ -17044,7 +17044,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G575" t="n">
-        <v>1.9847651720047</v>
+        <v>1.98476529121399</v>
       </c>
       <c r="H575" t="n">
         <v>39791</v>
@@ -17073,7 +17073,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G576" t="n">
-        <v>1.9847651720047</v>
+        <v>1.98476529121399</v>
       </c>
       <c r="H576" t="n">
         <v>50692</v>
@@ -17160,7 +17160,7 @@
         <v>2.26500010490417</v>
       </c>
       <c r="G579" t="n">
-        <v>2.03415989875793</v>
+        <v>2.03416013717651</v>
       </c>
       <c r="H579" t="n">
         <v>11681</v>
@@ -17189,7 +17189,7 @@
         <v>2.26500010490417</v>
       </c>
       <c r="G580" t="n">
-        <v>2.03415989875793</v>
+        <v>2.03416013717651</v>
       </c>
       <c r="H580" t="n">
         <v>33062</v>
@@ -17218,7 +17218,7 @@
         <v>2.23499989509583</v>
       </c>
       <c r="G581" t="n">
-        <v>2.00721716880798</v>
+        <v>2.00721740722656</v>
       </c>
       <c r="H581" t="n">
         <v>14930</v>
@@ -17247,7 +17247,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G582" t="n">
-        <v>2.05661177635193</v>
+        <v>2.05661201477051</v>
       </c>
       <c r="H582" t="n">
         <v>69994</v>
@@ -17276,7 +17276,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G583" t="n">
-        <v>2.03865027427673</v>
+        <v>2.03865003585815</v>
       </c>
       <c r="H583" t="n">
         <v>32623</v>
@@ -17334,7 +17334,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G585" t="n">
-        <v>2.04763102531433</v>
+        <v>2.04763126373291</v>
       </c>
       <c r="H585" t="n">
         <v>8638</v>
@@ -17363,7 +17363,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G586" t="n">
-        <v>2.08355450630188</v>
+        <v>2.08355402946472</v>
       </c>
       <c r="H586" t="n">
         <v>83509</v>
@@ -17450,7 +17450,7 @@
         <v>2.32500004768372</v>
       </c>
       <c r="G589" t="n">
-        <v>2.08804512023926</v>
+        <v>2.08804488182068</v>
       </c>
       <c r="H589" t="n">
         <v>37266</v>
@@ -17479,7 +17479,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G590" t="n">
-        <v>2.06559252738953</v>
+        <v>2.06559276580811</v>
       </c>
       <c r="H590" t="n">
         <v>18851</v>
@@ -17566,7 +17566,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G593" t="n">
-        <v>2.01170802116394</v>
+        <v>2.01170778274536</v>
       </c>
       <c r="H593" t="n">
         <v>123150</v>
@@ -17653,7 +17653,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G596" t="n">
-        <v>2.08355450630188</v>
+        <v>2.08355402946472</v>
       </c>
       <c r="H596" t="n">
         <v>23339</v>
@@ -17769,7 +17769,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G600" t="n">
-        <v>2.32603693008423</v>
+        <v>2.32603716850281</v>
       </c>
       <c r="H600" t="n">
         <v>234645</v>
@@ -17798,7 +17798,7 @@
         <v>2.5</v>
       </c>
       <c r="G601" t="n">
-        <v>2.24520969390869</v>
+        <v>2.24520945549011</v>
       </c>
       <c r="H601" t="n">
         <v>170492</v>
@@ -17856,7 +17856,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G603" t="n">
-        <v>2.21826720237732</v>
+        <v>2.21826672554016</v>
       </c>
       <c r="H603" t="n">
         <v>66824</v>
@@ -17885,7 +17885,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G604" t="n">
-        <v>2.20030522346497</v>
+        <v>2.20030546188354</v>
       </c>
       <c r="H604" t="n">
         <v>38475</v>
@@ -17914,7 +17914,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G605" t="n">
-        <v>2.11947751045227</v>
+        <v>2.11947774887085</v>
       </c>
       <c r="H605" t="n">
         <v>89012</v>
@@ -18030,7 +18030,7 @@
         <v>2.26500010490417</v>
       </c>
       <c r="G609" t="n">
-        <v>2.03415989875793</v>
+        <v>2.03416013717651</v>
       </c>
       <c r="H609" t="n">
         <v>53796</v>
@@ -18262,7 +18262,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G617" t="n">
-        <v>2.04763102531433</v>
+        <v>2.04763126373291</v>
       </c>
       <c r="H617" t="n">
         <v>74739</v>
@@ -18291,7 +18291,7 @@
         <v>2.3050000667572</v>
       </c>
       <c r="G618" t="n">
-        <v>2.07008337974548</v>
+        <v>2.0700831413269</v>
       </c>
       <c r="H618" t="n">
         <v>103627</v>
@@ -18320,7 +18320,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G619" t="n">
-        <v>2.06559252738953</v>
+        <v>2.06559276580811</v>
       </c>
       <c r="H619" t="n">
         <v>36072</v>
@@ -18378,7 +18378,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G621" t="n">
-        <v>2.04763102531433</v>
+        <v>2.04763126373291</v>
       </c>
       <c r="H621" t="n">
         <v>34438</v>
@@ -18552,7 +18552,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G627" t="n">
-        <v>2.04763102531433</v>
+        <v>2.04763126373291</v>
       </c>
       <c r="H627" t="n">
         <v>13812</v>
@@ -18581,7 +18581,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G628" t="n">
-        <v>2.06559252738953</v>
+        <v>2.06559276580811</v>
       </c>
       <c r="H628" t="n">
         <v>17736</v>
@@ -18639,7 +18639,7 @@
         <v>2.26500010490417</v>
       </c>
       <c r="G630" t="n">
-        <v>2.03415989875793</v>
+        <v>2.03416013717651</v>
       </c>
       <c r="H630" t="n">
         <v>6255</v>
@@ -18697,7 +18697,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G632" t="n">
-        <v>2.05661177635193</v>
+        <v>2.05661201477051</v>
       </c>
       <c r="H632" t="n">
         <v>16723</v>
@@ -18726,7 +18726,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G633" t="n">
-        <v>2.01170802116394</v>
+        <v>2.01170778274536</v>
       </c>
       <c r="H633" t="n">
         <v>29189</v>
@@ -18813,7 +18813,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G636" t="n">
-        <v>1.95782291889191</v>
+        <v>1.95782268047333</v>
       </c>
       <c r="H636" t="n">
         <v>18514</v>
@@ -19045,7 +19045,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G644" t="n">
-        <v>1.96680355072021</v>
+        <v>1.96680343151093</v>
       </c>
       <c r="H644" t="n">
         <v>55833</v>
@@ -19074,7 +19074,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G645" t="n">
-        <v>1.95782291889191</v>
+        <v>1.95782268047333</v>
       </c>
       <c r="H645" t="n">
         <v>5655</v>
@@ -19103,7 +19103,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G646" t="n">
-        <v>1.96680355072021</v>
+        <v>1.96680343151093</v>
       </c>
       <c r="H646" t="n">
         <v>2659</v>
@@ -19132,7 +19132,7 @@
         <v>2.1949999332428</v>
       </c>
       <c r="G647" t="n">
-        <v>1.97129392623901</v>
+        <v>1.97129368782043</v>
       </c>
       <c r="H647" t="n">
         <v>2598</v>
@@ -19161,7 +19161,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G648" t="n">
-        <v>1.96680355072021</v>
+        <v>1.96680343151093</v>
       </c>
       <c r="H648" t="n">
         <v>8566</v>
@@ -19190,7 +19190,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G649" t="n">
-        <v>1.95782291889191</v>
+        <v>1.95782268047333</v>
       </c>
       <c r="H649" t="n">
         <v>11364</v>
@@ -19219,7 +19219,7 @@
         <v>2.18499994277954</v>
       </c>
       <c r="G650" t="n">
-        <v>1.96231317520142</v>
+        <v>1.96231329441071</v>
       </c>
       <c r="H650" t="n">
         <v>4540</v>
@@ -19277,7 +19277,7 @@
         <v>2.13499999046326</v>
       </c>
       <c r="G652" t="n">
-        <v>1.91740894317627</v>
+        <v>1.91740906238556</v>
       </c>
       <c r="H652" t="n">
         <v>14340</v>
@@ -19306,7 +19306,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G653" t="n">
-        <v>1.95782291889191</v>
+        <v>1.95782268047333</v>
       </c>
       <c r="H653" t="n">
         <v>7716</v>
@@ -19422,7 +19422,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G657" t="n">
-        <v>1.92189943790436</v>
+        <v>1.92189931869507</v>
       </c>
       <c r="H657" t="n">
         <v>25122</v>
@@ -19509,7 +19509,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G660" t="n">
-        <v>1.92189943790436</v>
+        <v>1.92189931869507</v>
       </c>
       <c r="H660" t="n">
         <v>41945</v>
@@ -19538,7 +19538,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G661" t="n">
-        <v>1.903937458992</v>
+        <v>1.90393769741058</v>
       </c>
       <c r="H661" t="n">
         <v>119673</v>
@@ -19567,7 +19567,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G662" t="n">
-        <v>1.903937458992</v>
+        <v>1.90393769741058</v>
       </c>
       <c r="H662" t="n">
         <v>41999</v>
@@ -19596,7 +19596,7 @@
         <v>2.125</v>
       </c>
       <c r="G663" t="n">
-        <v>1.90842795372009</v>
+        <v>1.90842819213867</v>
       </c>
       <c r="H663" t="n">
         <v>16492</v>
@@ -19712,7 +19712,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G667" t="n">
-        <v>1.903937458992</v>
+        <v>1.90393769741058</v>
       </c>
       <c r="H667" t="n">
         <v>22750</v>
@@ -19857,7 +19857,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G672" t="n">
-        <v>1.95782291889191</v>
+        <v>1.95782268047333</v>
       </c>
       <c r="H672" t="n">
         <v>30719</v>
@@ -19886,7 +19886,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G673" t="n">
-        <v>1.97578430175781</v>
+        <v>1.97578454017639</v>
       </c>
       <c r="H673" t="n">
         <v>17555</v>
@@ -19915,7 +19915,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G674" t="n">
-        <v>1.96680355072021</v>
+        <v>1.96680343151093</v>
       </c>
       <c r="H674" t="n">
         <v>11038</v>
@@ -19944,7 +19944,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G675" t="n">
-        <v>2.01170802116394</v>
+        <v>2.01170778274536</v>
       </c>
       <c r="H675" t="n">
         <v>40300</v>
@@ -20002,7 +20002,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G677" t="n">
-        <v>2.03865027427673</v>
+        <v>2.03865003585815</v>
       </c>
       <c r="H677" t="n">
         <v>13543</v>
@@ -20031,7 +20031,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G678" t="n">
-        <v>2.03865027427673</v>
+        <v>2.03865003585815</v>
       </c>
       <c r="H678" t="n">
         <v>54963</v>
@@ -20060,7 +20060,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G679" t="n">
-        <v>2.06559252738953</v>
+        <v>2.06559276580811</v>
       </c>
       <c r="H679" t="n">
         <v>71912</v>
@@ -20205,7 +20205,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G684" t="n">
-        <v>1.96680355072021</v>
+        <v>1.96680343151093</v>
       </c>
       <c r="H684" t="n">
         <v>15966</v>
@@ -20234,7 +20234,7 @@
         <v>2.21499991416931</v>
       </c>
       <c r="G685" t="n">
-        <v>1.9892555475235</v>
+        <v>1.98925566673279</v>
       </c>
       <c r="H685" t="n">
         <v>49471</v>
@@ -20263,7 +20263,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G686" t="n">
-        <v>2.05661177635193</v>
+        <v>2.05661201477051</v>
       </c>
       <c r="H686" t="n">
         <v>71272</v>
@@ -20292,7 +20292,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G687" t="n">
-        <v>2.05661177635193</v>
+        <v>2.05661201477051</v>
       </c>
       <c r="H687" t="n">
         <v>59680</v>
@@ -20379,7 +20379,7 @@
         <v>2.26500010490417</v>
       </c>
       <c r="G690" t="n">
-        <v>2.03415989875793</v>
+        <v>2.03416013717651</v>
       </c>
       <c r="H690" t="n">
         <v>8390</v>
@@ -20408,7 +20408,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G691" t="n">
-        <v>2.03865027427673</v>
+        <v>2.03865003585815</v>
       </c>
       <c r="H691" t="n">
         <v>3909</v>
@@ -20466,7 +20466,7 @@
         <v>2.23499989509583</v>
       </c>
       <c r="G693" t="n">
-        <v>2.00721716880798</v>
+        <v>2.00721740722656</v>
       </c>
       <c r="H693" t="n">
         <v>9970</v>
@@ -20524,7 +20524,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G695" t="n">
-        <v>2.05661177635193</v>
+        <v>2.05661201477051</v>
       </c>
       <c r="H695" t="n">
         <v>8106</v>
@@ -20553,7 +20553,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G696" t="n">
-        <v>2.01170802116394</v>
+        <v>2.01170778274536</v>
       </c>
       <c r="H696" t="n">
         <v>21043</v>
@@ -20756,7 +20756,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G703" t="n">
-        <v>2.03865027427673</v>
+        <v>2.03865003585815</v>
       </c>
       <c r="H703" t="n">
         <v>2475</v>
@@ -20843,7 +20843,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G706" t="n">
-        <v>1.97578430175781</v>
+        <v>1.97578454017639</v>
       </c>
       <c r="H706" t="n">
         <v>54288</v>
@@ -20901,7 +20901,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G708" t="n">
-        <v>1.92189943790436</v>
+        <v>1.92189931869507</v>
       </c>
       <c r="H708" t="n">
         <v>59815</v>
@@ -20930,7 +20930,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G709" t="n">
-        <v>1.85005247592926</v>
+        <v>1.85005259513855</v>
       </c>
       <c r="H709" t="n">
         <v>57600</v>
@@ -20959,7 +20959,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G710" t="n">
-        <v>1.77820587158203</v>
+        <v>1.77820599079132</v>
       </c>
       <c r="H710" t="n">
         <v>41058</v>
@@ -20988,7 +20988,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G711" t="n">
-        <v>1.82311010360718</v>
+        <v>1.82311022281647</v>
       </c>
       <c r="H711" t="n">
         <v>25998</v>
@@ -21046,7 +21046,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G713" t="n">
-        <v>1.92189943790436</v>
+        <v>1.92189931869507</v>
       </c>
       <c r="H713" t="n">
         <v>14008</v>
@@ -21104,7 +21104,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G715" t="n">
-        <v>1.8051483631134</v>
+        <v>1.80514848232269</v>
       </c>
       <c r="H715" t="n">
         <v>29989</v>
@@ -21278,7 +21278,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G721" t="n">
-        <v>1.65247416496277</v>
+        <v>1.65247428417206</v>
       </c>
       <c r="H721" t="n">
         <v>47767</v>
@@ -21307,7 +21307,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G722" t="n">
-        <v>1.65247416496277</v>
+        <v>1.65247428417206</v>
       </c>
       <c r="H722" t="n">
         <v>49356</v>
@@ -21336,7 +21336,7 @@
         <v>1.85599994659424</v>
       </c>
       <c r="G723" t="n">
-        <v>1.66684353351593</v>
+        <v>1.66684341430664</v>
       </c>
       <c r="H723" t="n">
         <v>93598</v>
@@ -21365,7 +21365,7 @@
         <v>1.89400005340576</v>
       </c>
       <c r="G724" t="n">
-        <v>1.70097076892853</v>
+        <v>1.70097088813782</v>
       </c>
       <c r="H724" t="n">
         <v>126727</v>
@@ -21423,7 +21423,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G726" t="n">
-        <v>1.67941677570343</v>
+        <v>1.67941665649414</v>
       </c>
       <c r="H726" t="n">
         <v>135018</v>
@@ -21452,7 +21452,7 @@
         <v>1.81599998474121</v>
       </c>
       <c r="G727" t="n">
-        <v>1.63092029094696</v>
+        <v>1.63092017173767</v>
       </c>
       <c r="H727" t="n">
         <v>33529</v>
@@ -21481,7 +21481,7 @@
         <v>1.83399999141693</v>
       </c>
       <c r="G728" t="n">
-        <v>1.64708578586578</v>
+        <v>1.64708566665649</v>
       </c>
       <c r="H728" t="n">
         <v>5430</v>
@@ -21510,7 +21510,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G729" t="n">
-        <v>1.63451254367828</v>
+        <v>1.63451242446899</v>
       </c>
       <c r="H729" t="n">
         <v>10781</v>
@@ -21539,7 +21539,7 @@
         <v>1.81599998474121</v>
       </c>
       <c r="G730" t="n">
-        <v>1.63092029094696</v>
+        <v>1.63092017173767</v>
       </c>
       <c r="H730" t="n">
         <v>15018</v>
@@ -21568,7 +21568,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G731" t="n">
-        <v>1.63451254367828</v>
+        <v>1.63451242446899</v>
       </c>
       <c r="H731" t="n">
         <v>4539</v>
@@ -21597,7 +21597,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G732" t="n">
-        <v>1.63451254367828</v>
+        <v>1.63451242446899</v>
       </c>
       <c r="H732" t="n">
         <v>13877</v>
@@ -21626,7 +21626,7 @@
         <v>1.76199996471405</v>
       </c>
       <c r="G733" t="n">
-        <v>1.5824236869812</v>
+        <v>1.58242356777191</v>
       </c>
       <c r="H733" t="n">
         <v>6578</v>
@@ -21655,7 +21655,7 @@
         <v>1.75</v>
       </c>
       <c r="G734" t="n">
-        <v>1.57164669036865</v>
+        <v>1.57164657115936</v>
       </c>
       <c r="H734" t="n">
         <v>17623</v>
@@ -21829,7 +21829,7 @@
         <v>1.59800004959106</v>
       </c>
       <c r="G740" t="n">
-        <v>1.43513798713684</v>
+        <v>1.43513786792755</v>
       </c>
       <c r="H740" t="n">
         <v>10009</v>
@@ -21858,7 +21858,7 @@
         <v>1.55599999427795</v>
       </c>
       <c r="G741" t="n">
-        <v>1.39741837978363</v>
+        <v>1.39741849899292</v>
       </c>
       <c r="H741" t="n">
         <v>29346</v>
@@ -21887,7 +21887,7 @@
         <v>1.57400000095367</v>
       </c>
       <c r="G742" t="n">
-        <v>1.41358387470245</v>
+        <v>1.41358399391174</v>
       </c>
       <c r="H742" t="n">
         <v>18646</v>
@@ -21916,7 +21916,7 @@
         <v>1.57200002670288</v>
       </c>
       <c r="G743" t="n">
-        <v>1.41178786754608</v>
+        <v>1.41178774833679</v>
       </c>
       <c r="H743" t="n">
         <v>37379</v>
@@ -21945,7 +21945,7 @@
         <v>1.50800001621246</v>
       </c>
       <c r="G744" t="n">
-        <v>1.35431027412415</v>
+        <v>1.35431039333344</v>
       </c>
       <c r="H744" t="n">
         <v>54423</v>
@@ -21974,7 +21974,7 @@
         <v>1.48399996757507</v>
       </c>
       <c r="G745" t="n">
-        <v>1.33275640010834</v>
+        <v>1.33275628089905</v>
       </c>
       <c r="H745" t="n">
         <v>99385</v>
@@ -22119,7 +22119,7 @@
         <v>1.45200002193451</v>
       </c>
       <c r="G750" t="n">
-        <v>1.3040177822113</v>
+        <v>1.30401766300201</v>
       </c>
       <c r="H750" t="n">
         <v>31108</v>
@@ -22264,7 +22264,7 @@
         <v>1.41600000858307</v>
       </c>
       <c r="G755" t="n">
-        <v>1.27168679237366</v>
+        <v>1.27168667316437</v>
       </c>
       <c r="H755" t="n">
         <v>45386</v>
@@ -22322,7 +22322,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G757" t="n">
-        <v>1.21241319179535</v>
+        <v>1.21241307258606</v>
       </c>
       <c r="H757" t="n">
         <v>34835</v>
@@ -22351,7 +22351,7 @@
         <v>1.29200005531311</v>
       </c>
       <c r="G758" t="n">
-        <v>1.16032433509827</v>
+        <v>1.16032445430756</v>
       </c>
       <c r="H758" t="n">
         <v>115682</v>
@@ -22380,7 +22380,7 @@
         <v>1.25</v>
       </c>
       <c r="G759" t="n">
-        <v>1.12260484695435</v>
+        <v>1.12260472774506</v>
       </c>
       <c r="H759" t="n">
         <v>48125</v>
@@ -22554,7 +22554,7 @@
         <v>1.41400003433228</v>
       </c>
       <c r="G765" t="n">
-        <v>1.26989054679871</v>
+        <v>1.26989042758942</v>
       </c>
       <c r="H765" t="n">
         <v>91324</v>
@@ -22583,7 +22583,7 @@
         <v>1.52799999713898</v>
       </c>
       <c r="G766" t="n">
-        <v>1.37227201461792</v>
+        <v>1.37227213382721</v>
       </c>
       <c r="H766" t="n">
         <v>166018</v>
@@ -22728,7 +22728,7 @@
         <v>1.51800000667572</v>
       </c>
       <c r="G771" t="n">
-        <v>1.36329126358032</v>
+        <v>1.36329114437103</v>
       </c>
       <c r="H771" t="n">
         <v>13363</v>
@@ -22757,7 +22757,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G772" t="n">
-        <v>1.31120240688324</v>
+        <v>1.31120252609253</v>
       </c>
       <c r="H772" t="n">
         <v>71525</v>
@@ -22786,7 +22786,7 @@
         <v>1.47800004482269</v>
       </c>
       <c r="G773" t="n">
-        <v>1.32736790180206</v>
+        <v>1.32736802101135</v>
       </c>
       <c r="H773" t="n">
         <v>32846</v>
@@ -22815,7 +22815,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G774" t="n">
-        <v>1.3381450176239</v>
+        <v>1.33814489841461</v>
       </c>
       <c r="H774" t="n">
         <v>16878</v>
@@ -22873,7 +22873,7 @@
         <v>1.5</v>
       </c>
       <c r="G776" t="n">
-        <v>1.34712564945221</v>
+        <v>1.3471257686615</v>
       </c>
       <c r="H776" t="n">
         <v>38027</v>
@@ -22902,7 +22902,7 @@
         <v>1.48399996757507</v>
       </c>
       <c r="G777" t="n">
-        <v>1.33275640010834</v>
+        <v>1.33275628089905</v>
       </c>
       <c r="H777" t="n">
         <v>8595</v>
@@ -23047,7 +23047,7 @@
         <v>1.49800002574921</v>
       </c>
       <c r="G782" t="n">
-        <v>1.34532964229584</v>
+        <v>1.34532952308655</v>
       </c>
       <c r="H782" t="n">
         <v>53053</v>
@@ -23076,7 +23076,7 @@
         <v>1.49199998378754</v>
       </c>
       <c r="G783" t="n">
-        <v>1.33994102478027</v>
+        <v>1.33994114398956</v>
       </c>
       <c r="H783" t="n">
         <v>26343</v>
@@ -23163,7 +23163,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G786" t="n">
-        <v>1.31120240688324</v>
+        <v>1.31120252609253</v>
       </c>
       <c r="H786" t="n">
         <v>38062</v>
@@ -23250,7 +23250,7 @@
         <v>1.40199995040894</v>
       </c>
       <c r="G789" t="n">
-        <v>1.25911355018616</v>
+        <v>1.25911343097687</v>
       </c>
       <c r="H789" t="n">
         <v>38229</v>
@@ -23279,7 +23279,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G790" t="n">
-        <v>1.24833655357361</v>
+        <v>1.24833643436432</v>
       </c>
       <c r="H790" t="n">
         <v>20252</v>
@@ -23308,7 +23308,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G791" t="n">
-        <v>1.23037493228912</v>
+        <v>1.23037481307983</v>
       </c>
       <c r="H791" t="n">
         <v>9601</v>
@@ -23337,7 +23337,7 @@
         <v>1.38800001144409</v>
       </c>
       <c r="G792" t="n">
-        <v>1.24654018878937</v>
+        <v>1.24654030799866</v>
       </c>
       <c r="H792" t="n">
         <v>43409</v>
@@ -23366,7 +23366,7 @@
         <v>1.41799998283386</v>
       </c>
       <c r="G793" t="n">
-        <v>1.27348291873932</v>
+        <v>1.27348279953003</v>
       </c>
       <c r="H793" t="n">
         <v>147492</v>
@@ -23424,7 +23424,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G795" t="n">
-        <v>1.45489573478699</v>
+        <v>1.45489585399628</v>
       </c>
       <c r="H795" t="n">
         <v>291933</v>
@@ -23511,7 +23511,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G798" t="n">
-        <v>1.65247416496277</v>
+        <v>1.65247428417206</v>
       </c>
       <c r="H798" t="n">
         <v>461676</v>
@@ -23540,7 +23540,7 @@
         <v>1.78199994564056</v>
       </c>
       <c r="G799" t="n">
-        <v>1.60038530826569</v>
+        <v>1.60038542747498</v>
       </c>
       <c r="H799" t="n">
         <v>184959</v>
@@ -23569,7 +23569,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G800" t="n">
-        <v>1.65247416496277</v>
+        <v>1.65247428417206</v>
       </c>
       <c r="H800" t="n">
         <v>179707</v>
@@ -23598,7 +23598,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G801" t="n">
-        <v>1.84107172489166</v>
+        <v>1.84107184410095</v>
       </c>
       <c r="H801" t="n">
         <v>1306104</v>
@@ -23656,7 +23656,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G803" t="n">
-        <v>1.88597583770752</v>
+        <v>1.88597595691681</v>
       </c>
       <c r="H803" t="n">
         <v>354581</v>
@@ -23685,7 +23685,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G804" t="n">
-        <v>1.85005247592926</v>
+        <v>1.85005259513855</v>
       </c>
       <c r="H804" t="n">
         <v>291089</v>
@@ -23714,7 +23714,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G805" t="n">
-        <v>1.82311010360718</v>
+        <v>1.82311022281647</v>
       </c>
       <c r="H805" t="n">
         <v>293536</v>
@@ -23830,7 +23830,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G809" t="n">
-        <v>1.85005247592926</v>
+        <v>1.85005259513855</v>
       </c>
       <c r="H809" t="n">
         <v>165023</v>
@@ -23888,7 +23888,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G811" t="n">
-        <v>1.81412935256958</v>
+        <v>1.814129114151</v>
       </c>
       <c r="H811" t="n">
         <v>401742</v>
@@ -23917,7 +23917,7 @@
         <v>2.04500007629395</v>
       </c>
       <c r="G812" t="n">
-        <v>1.83658158779144</v>
+        <v>1.83658134937286</v>
       </c>
       <c r="H812" t="n">
         <v>184309</v>
@@ -23946,7 +23946,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G813" t="n">
-        <v>1.81412935256958</v>
+        <v>1.814129114151</v>
       </c>
       <c r="H813" t="n">
         <v>103549</v>
@@ -23975,7 +23975,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G814" t="n">
-        <v>1.8051483631134</v>
+        <v>1.80514848232269</v>
       </c>
       <c r="H814" t="n">
         <v>69071</v>
@@ -24004,7 +24004,7 @@
         <v>1.98599994182587</v>
       </c>
       <c r="G815" t="n">
-        <v>1.7835944890976</v>
+        <v>1.78359436988831</v>
       </c>
       <c r="H815" t="n">
         <v>82002</v>
@@ -24091,7 +24091,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G818" t="n">
-        <v>1.68839764595032</v>
+        <v>1.68839752674103</v>
       </c>
       <c r="H818" t="n">
         <v>195439</v>
@@ -24149,7 +24149,7 @@
         <v>1.90600001811981</v>
       </c>
       <c r="G820" t="n">
-        <v>1.71174764633179</v>
+        <v>1.71174776554108</v>
       </c>
       <c r="H820" t="n">
         <v>125176</v>
@@ -24178,7 +24178,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G821" t="n">
-        <v>1.73330175876617</v>
+        <v>1.73330187797546</v>
       </c>
       <c r="H821" t="n">
         <v>92821</v>
@@ -24236,7 +24236,7 @@
         <v>1.87600004673004</v>
       </c>
       <c r="G823" t="n">
-        <v>1.6848052740097</v>
+        <v>1.68480539321899</v>
       </c>
       <c r="H823" t="n">
         <v>43015</v>
@@ -24294,7 +24294,7 @@
         <v>1.90600001811981</v>
       </c>
       <c r="G825" t="n">
-        <v>1.71174764633179</v>
+        <v>1.71174776554108</v>
       </c>
       <c r="H825" t="n">
         <v>44756</v>
@@ -24352,7 +24352,7 @@
         <v>2.21499991416931</v>
       </c>
       <c r="G827" t="n">
-        <v>1.9892555475235</v>
+        <v>1.98925566673279</v>
       </c>
       <c r="H827" t="n">
         <v>1267819</v>
@@ -24410,7 +24410,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G829" t="n">
-        <v>2.06559252738953</v>
+        <v>2.06559276580811</v>
       </c>
       <c r="H829" t="n">
         <v>658018</v>
@@ -24439,7 +24439,7 @@
         <v>2.31500005722046</v>
       </c>
       <c r="G830" t="n">
-        <v>2.0790638923645</v>
+        <v>2.07906413078308</v>
       </c>
       <c r="H830" t="n">
         <v>590495</v>
@@ -24497,7 +24497,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G832" t="n">
-        <v>2.01170802116394</v>
+        <v>2.01170778274536</v>
       </c>
       <c r="H832" t="n">
         <v>579044</v>
@@ -24584,7 +24584,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G835" t="n">
-        <v>1.97578430175781</v>
+        <v>1.97578454017639</v>
       </c>
       <c r="H835" t="n">
         <v>122181</v>
@@ -24613,7 +24613,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G836" t="n">
-        <v>1.97578430175781</v>
+        <v>1.97578454017639</v>
       </c>
       <c r="H836" t="n">
         <v>98899</v>
@@ -24700,7 +24700,7 @@
         <v>2.38499999046326</v>
       </c>
       <c r="G839" t="n">
-        <v>2.14192986488342</v>
+        <v>2.141930103302</v>
       </c>
       <c r="H839" t="n">
         <v>449610</v>
@@ -24729,7 +24729,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G840" t="n">
-        <v>2.17336320877075</v>
+        <v>2.17336273193359</v>
       </c>
       <c r="H840" t="n">
         <v>188366</v>
@@ -24758,7 +24758,7 @@
         <v>2.42499995231628</v>
       </c>
       <c r="G841" t="n">
-        <v>2.17785334587097</v>
+        <v>2.17785310745239</v>
       </c>
       <c r="H841" t="n">
         <v>275446</v>
@@ -24845,7 +24845,7 @@
         <v>2.3050000667572</v>
       </c>
       <c r="G844" t="n">
-        <v>2.07008337974548</v>
+        <v>2.0700831413269</v>
       </c>
       <c r="H844" t="n">
         <v>50463</v>
@@ -24874,7 +24874,7 @@
         <v>2.39499998092651</v>
       </c>
       <c r="G845" t="n">
-        <v>2.1509108543396</v>
+        <v>2.15091061592102</v>
       </c>
       <c r="H845" t="n">
         <v>87043</v>
@@ -24903,7 +24903,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G846" t="n">
-        <v>2.09253549575806</v>
+        <v>2.09253525733948</v>
       </c>
       <c r="H846" t="n">
         <v>460633</v>
@@ -24961,7 +24961,7 @@
         <v>2.38499999046326</v>
       </c>
       <c r="G848" t="n">
-        <v>2.14192986488342</v>
+        <v>2.141930103302</v>
       </c>
       <c r="H848" t="n">
         <v>177569</v>
@@ -25019,7 +25019,7 @@
         <v>2.36500000953674</v>
       </c>
       <c r="G850" t="n">
-        <v>2.12396788597107</v>
+        <v>2.12396812438965</v>
       </c>
       <c r="H850" t="n">
         <v>527196</v>
@@ -25048,7 +25048,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G851" t="n">
-        <v>2.04763102531433</v>
+        <v>2.04763126373291</v>
       </c>
       <c r="H851" t="n">
         <v>566449</v>
@@ -25077,7 +25077,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G852" t="n">
-        <v>1.96680355072021</v>
+        <v>1.96680343151093</v>
       </c>
       <c r="H852" t="n">
         <v>290714</v>
@@ -25106,7 +25106,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G853" t="n">
-        <v>1.97578430175781</v>
+        <v>1.97578454017639</v>
       </c>
       <c r="H853" t="n">
         <v>113970</v>
@@ -25135,7 +25135,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G854" t="n">
-        <v>1.96680355072021</v>
+        <v>1.96680343151093</v>
       </c>
       <c r="H854" t="n">
         <v>179252</v>
@@ -25164,7 +25164,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G855" t="n">
-        <v>1.95782291889191</v>
+        <v>1.95782268047333</v>
       </c>
       <c r="H855" t="n">
         <v>159758</v>
@@ -25193,7 +25193,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G856" t="n">
-        <v>1.95782291889191</v>
+        <v>1.95782268047333</v>
       </c>
       <c r="H856" t="n">
         <v>76878</v>
@@ -25222,7 +25222,7 @@
         <v>2.3050000667572</v>
       </c>
       <c r="G857" t="n">
-        <v>2.07008337974548</v>
+        <v>2.0700831413269</v>
       </c>
       <c r="H857" t="n">
         <v>247321</v>
@@ -25367,7 +25367,7 @@
         <v>2.3050000667572</v>
       </c>
       <c r="G862" t="n">
-        <v>2.07008337974548</v>
+        <v>2.0700831413269</v>
       </c>
       <c r="H862" t="n">
         <v>272097</v>
@@ -25425,7 +25425,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G864" t="n">
-        <v>2.06559252738953</v>
+        <v>2.06559276580811</v>
       </c>
       <c r="H864" t="n">
         <v>60672</v>
@@ -25454,7 +25454,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G865" t="n">
-        <v>2.03865027427673</v>
+        <v>2.03865003585815</v>
       </c>
       <c r="H865" t="n">
         <v>76078</v>
@@ -25512,7 +25512,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G867" t="n">
-        <v>2.05661177635193</v>
+        <v>2.05661201477051</v>
       </c>
       <c r="H867" t="n">
         <v>50681</v>
@@ -25570,7 +25570,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G869" t="n">
-        <v>2.06559252738953</v>
+        <v>2.06559276580811</v>
       </c>
       <c r="H869" t="n">
         <v>39249</v>
@@ -25628,7 +25628,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G871" t="n">
-        <v>2.05661177635193</v>
+        <v>2.05661201477051</v>
       </c>
       <c r="H871" t="n">
         <v>101754</v>
@@ -25657,7 +25657,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G872" t="n">
-        <v>2.05661177635193</v>
+        <v>2.05661201477051</v>
       </c>
       <c r="H872" t="n">
         <v>99626</v>
@@ -25773,7 +25773,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G876" t="n">
-        <v>1.92189943790436</v>
+        <v>1.92189931869507</v>
       </c>
       <c r="H876" t="n">
         <v>75417</v>
@@ -25831,7 +25831,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G878" t="n">
-        <v>1.86801421642303</v>
+        <v>1.86801433563232</v>
       </c>
       <c r="H878" t="n">
         <v>169753</v>
@@ -25860,7 +25860,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G879" t="n">
-        <v>1.84107172489166</v>
+        <v>1.84107184410095</v>
       </c>
       <c r="H879" t="n">
         <v>119512</v>
@@ -25918,7 +25918,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G881" t="n">
-        <v>1.81412935256958</v>
+        <v>1.814129114151</v>
       </c>
       <c r="H881" t="n">
         <v>135440</v>
@@ -25947,7 +25947,7 @@
         <v>2.02500009536743</v>
       </c>
       <c r="G882" t="n">
-        <v>1.81861972808838</v>
+        <v>1.81861984729767</v>
       </c>
       <c r="H882" t="n">
         <v>71776</v>
@@ -26034,7 +26034,7 @@
         <v>1.96399998664856</v>
       </c>
       <c r="G885" t="n">
-        <v>1.76383650302887</v>
+        <v>1.76383662223816</v>
       </c>
       <c r="H885" t="n">
         <v>93689</v>
@@ -26063,7 +26063,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G886" t="n">
-        <v>1.82311010360718</v>
+        <v>1.82311022281647</v>
       </c>
       <c r="H886" t="n">
         <v>136269</v>
@@ -26092,7 +26092,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G887" t="n">
-        <v>1.82311010360718</v>
+        <v>1.82311022281647</v>
       </c>
       <c r="H887" t="n">
         <v>97372</v>
@@ -26150,7 +26150,7 @@
         <v>2.00500011444092</v>
       </c>
       <c r="G889" t="n">
-        <v>1.80065810680389</v>
+        <v>1.80065822601318</v>
       </c>
       <c r="H889" t="n">
         <v>16944</v>
@@ -26208,7 +26208,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G891" t="n">
-        <v>1.81412935256958</v>
+        <v>1.814129114151</v>
       </c>
       <c r="H891" t="n">
         <v>36502</v>
@@ -26237,7 +26237,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G892" t="n">
-        <v>1.82311010360718</v>
+        <v>1.82311022281647</v>
       </c>
       <c r="H892" t="n">
         <v>56257</v>
@@ -26266,7 +26266,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G893" t="n">
-        <v>1.82311010360718</v>
+        <v>1.82311022281647</v>
       </c>
       <c r="H893" t="n">
         <v>35376</v>
@@ -26295,7 +26295,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G894" t="n">
-        <v>1.8051483631134</v>
+        <v>1.80514848232269</v>
       </c>
       <c r="H894" t="n">
         <v>41837</v>
@@ -26353,7 +26353,7 @@
         <v>1.99600005149841</v>
       </c>
       <c r="G896" t="n">
-        <v>1.79257524013519</v>
+        <v>1.79257535934448</v>
       </c>
       <c r="H896" t="n">
         <v>38649</v>
@@ -26411,7 +26411,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G898" t="n">
-        <v>1.81412935256958</v>
+        <v>1.814129114151</v>
       </c>
       <c r="H898" t="n">
         <v>26690</v>
@@ -26440,7 +26440,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G899" t="n">
-        <v>1.8051483631134</v>
+        <v>1.80514848232269</v>
       </c>
       <c r="H899" t="n">
         <v>40340</v>
@@ -26469,7 +26469,7 @@
         <v>2</v>
       </c>
       <c r="G900" t="n">
-        <v>1.79616761207581</v>
+        <v>1.7961677312851</v>
       </c>
       <c r="H900" t="n">
         <v>26209</v>
@@ -26527,7 +26527,7 @@
         <v>1.97800004482269</v>
       </c>
       <c r="G902" t="n">
-        <v>1.77640986442566</v>
+        <v>1.77640974521637</v>
       </c>
       <c r="H902" t="n">
         <v>37186</v>
@@ -26585,7 +26585,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G904" t="n">
-        <v>1.72432100772858</v>
+        <v>1.72432076931</v>
       </c>
       <c r="H904" t="n">
         <v>19574</v>
@@ -26614,7 +26614,7 @@
         <v>1.92200005054474</v>
       </c>
       <c r="G905" t="n">
-        <v>1.72611701488495</v>
+        <v>1.72611713409424</v>
       </c>
       <c r="H905" t="n">
         <v>31014</v>
@@ -26643,7 +26643,7 @@
         <v>2.1949999332428</v>
       </c>
       <c r="G906" t="n">
-        <v>1.97129392623901</v>
+        <v>1.97129368782043</v>
       </c>
       <c r="H906" t="n">
         <v>1347426</v>
@@ -26672,7 +26672,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G907" t="n">
-        <v>1.95782291889191</v>
+        <v>1.95782268047333</v>
       </c>
       <c r="H907" t="n">
         <v>660531</v>
@@ -26875,7 +26875,7 @@
         <v>2.125</v>
       </c>
       <c r="G914" t="n">
-        <v>1.90842795372009</v>
+        <v>1.90842819213867</v>
       </c>
       <c r="H914" t="n">
         <v>82298</v>
@@ -26904,7 +26904,7 @@
         <v>2.13499999046326</v>
       </c>
       <c r="G915" t="n">
-        <v>1.91740894317627</v>
+        <v>1.91740906238556</v>
       </c>
       <c r="H915" t="n">
         <v>92598</v>
@@ -26933,7 +26933,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G916" t="n">
-        <v>1.92189943790436</v>
+        <v>1.92189931869507</v>
       </c>
       <c r="H916" t="n">
         <v>56683</v>
@@ -26991,7 +26991,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G918" t="n">
-        <v>1.903937458992</v>
+        <v>1.90393769741058</v>
       </c>
       <c r="H918" t="n">
         <v>61933</v>
@@ -27020,7 +27020,7 @@
         <v>2.04500007629395</v>
       </c>
       <c r="G919" t="n">
-        <v>1.83658158779144</v>
+        <v>1.83658134937286</v>
       </c>
       <c r="H919" t="n">
         <v>36850</v>
@@ -27049,7 +27049,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G920" t="n">
-        <v>1.85005247592926</v>
+        <v>1.85005259513855</v>
       </c>
       <c r="H920" t="n">
         <v>122831</v>
@@ -27136,7 +27136,7 @@
         <v>2.00500011444092</v>
       </c>
       <c r="G923" t="n">
-        <v>1.80065810680389</v>
+        <v>1.80065822601318</v>
       </c>
       <c r="H923" t="n">
         <v>30841</v>
@@ -27165,7 +27165,7 @@
         <v>1.96599996089935</v>
       </c>
       <c r="G924" t="n">
-        <v>1.76563274860382</v>
+        <v>1.76563262939453</v>
       </c>
       <c r="H924" t="n">
         <v>25634</v>
@@ -27194,7 +27194,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G925" t="n">
-        <v>1.81412935256958</v>
+        <v>1.814129114151</v>
       </c>
       <c r="H925" t="n">
         <v>65569</v>
@@ -27281,7 +27281,7 @@
         <v>1.94799995422363</v>
       </c>
       <c r="G928" t="n">
-        <v>1.74946713447571</v>
+        <v>1.74946737289429</v>
       </c>
       <c r="H928" t="n">
         <v>104975</v>
@@ -27339,7 +27339,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G930" t="n">
-        <v>1.73330175876617</v>
+        <v>1.73330187797546</v>
       </c>
       <c r="H930" t="n">
         <v>35986</v>
@@ -27397,7 +27397,7 @@
         <v>1.94799995422363</v>
       </c>
       <c r="G932" t="n">
-        <v>1.74946713447571</v>
+        <v>1.74946737289429</v>
       </c>
       <c r="H932" t="n">
         <v>35715</v>
@@ -27484,7 +27484,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G935" t="n">
-        <v>1.81412935256958</v>
+        <v>1.814129114151</v>
       </c>
       <c r="H935" t="n">
         <v>153827</v>
@@ -27542,7 +27542,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G937" t="n">
-        <v>1.84556221961975</v>
+        <v>1.84556233882904</v>
       </c>
       <c r="H937" t="n">
         <v>30239</v>
@@ -27600,7 +27600,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G939" t="n">
-        <v>1.83209109306335</v>
+        <v>1.83209097385406</v>
       </c>
       <c r="H939" t="n">
         <v>132643</v>
@@ -27629,7 +27629,7 @@
         <v>2.26500010490417</v>
       </c>
       <c r="G940" t="n">
-        <v>2.03415989875793</v>
+        <v>2.03416013717651</v>
       </c>
       <c r="H940" t="n">
         <v>543815</v>
@@ -27687,7 +27687,7 @@
         <v>2.41499996185303</v>
       </c>
       <c r="G942" t="n">
-        <v>2.16887235641479</v>
+        <v>2.16887259483337</v>
       </c>
       <c r="H942" t="n">
         <v>266605</v>
@@ -27745,7 +27745,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G944" t="n">
-        <v>2.09253549575806</v>
+        <v>2.09253525733948</v>
       </c>
       <c r="H944" t="n">
         <v>91545</v>
@@ -27774,7 +27774,7 @@
         <v>2.31500005722046</v>
       </c>
       <c r="G945" t="n">
-        <v>2.0790638923645</v>
+        <v>2.07906413078308</v>
       </c>
       <c r="H945" t="n">
         <v>29653</v>
@@ -27803,7 +27803,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G946" t="n">
-        <v>2.03865027427673</v>
+        <v>2.03865003585815</v>
       </c>
       <c r="H946" t="n">
         <v>69467</v>
@@ -27832,7 +27832,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G947" t="n">
-        <v>1.9847651720047</v>
+        <v>1.98476529121399</v>
       </c>
       <c r="H947" t="n">
         <v>29391</v>
@@ -27861,7 +27861,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G948" t="n">
-        <v>1.97578430175781</v>
+        <v>1.97578454017639</v>
       </c>
       <c r="H948" t="n">
         <v>133606</v>
@@ -27890,7 +27890,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G949" t="n">
-        <v>1.92189943790436</v>
+        <v>1.92189931869507</v>
       </c>
       <c r="H949" t="n">
         <v>109591</v>
@@ -27919,7 +27919,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G950" t="n">
-        <v>2.03865027427673</v>
+        <v>2.03865003585815</v>
       </c>
       <c r="H950" t="n">
         <v>225593</v>
@@ -28006,7 +28006,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G953" t="n">
-        <v>2.05661177635193</v>
+        <v>2.05661201477051</v>
       </c>
       <c r="H953" t="n">
         <v>222591</v>
@@ -28035,7 +28035,7 @@
         <v>2.3050000667572</v>
       </c>
       <c r="G954" t="n">
-        <v>2.07008337974548</v>
+        <v>2.0700831413269</v>
       </c>
       <c r="H954" t="n">
         <v>111608</v>
@@ -28093,7 +28093,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G956" t="n">
-        <v>1.96680355072021</v>
+        <v>1.96680343151093</v>
       </c>
       <c r="H956" t="n">
         <v>60366</v>
@@ -28151,7 +28151,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G958" t="n">
-        <v>1.97578430175781</v>
+        <v>1.97578454017639</v>
       </c>
       <c r="H958" t="n">
         <v>31996</v>
@@ -28209,7 +28209,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G960" t="n">
-        <v>1.95782291889191</v>
+        <v>1.95782268047333</v>
       </c>
       <c r="H960" t="n">
         <v>130224</v>
@@ -28238,7 +28238,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G961" t="n">
-        <v>1.9847651720047</v>
+        <v>1.98476529121399</v>
       </c>
       <c r="H961" t="n">
         <v>88832</v>
@@ -28296,7 +28296,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G963" t="n">
-        <v>2.09253549575806</v>
+        <v>2.09253525733948</v>
       </c>
       <c r="H963" t="n">
         <v>109545</v>
@@ -28325,7 +28325,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G964" t="n">
-        <v>2.08355450630188</v>
+        <v>2.08355402946472</v>
       </c>
       <c r="H964" t="n">
         <v>200150</v>
@@ -28354,7 +28354,7 @@
         <v>2.40499997138977</v>
       </c>
       <c r="G965" t="n">
-        <v>2.15989136695862</v>
+        <v>2.1598916053772</v>
       </c>
       <c r="H965" t="n">
         <v>192266</v>
@@ -28412,7 +28412,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G967" t="n">
-        <v>2.09253549575806</v>
+        <v>2.09253525733948</v>
       </c>
       <c r="H967" t="n">
         <v>55373</v>
@@ -28441,7 +28441,7 @@
         <v>2.40499997138977</v>
       </c>
       <c r="G968" t="n">
-        <v>2.15989136695862</v>
+        <v>2.1598916053772</v>
       </c>
       <c r="H968" t="n">
         <v>88063</v>
@@ -28470,7 +28470,7 @@
         <v>2.36500000953674</v>
       </c>
       <c r="G969" t="n">
-        <v>2.12396788597107</v>
+        <v>2.12396812438965</v>
       </c>
       <c r="H969" t="n">
         <v>135399</v>
@@ -28528,7 +28528,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G971" t="n">
-        <v>2.05661177635193</v>
+        <v>2.05661201477051</v>
       </c>
       <c r="H971" t="n">
         <v>150831</v>
@@ -28557,7 +28557,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G972" t="n">
-        <v>2.06559252738953</v>
+        <v>2.06559276580811</v>
       </c>
       <c r="H972" t="n">
         <v>79359</v>
@@ -28789,7 +28789,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G980" t="n">
-        <v>2.49667310714722</v>
+        <v>2.49667286872864</v>
       </c>
       <c r="H980" t="n">
         <v>824891</v>
@@ -28847,7 +28847,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G982" t="n">
-        <v>2.56851959228516</v>
+        <v>2.56851935386658</v>
       </c>
       <c r="H982" t="n">
         <v>560423</v>
@@ -28876,7 +28876,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G983" t="n">
-        <v>2.55055785179138</v>
+        <v>2.55055809020996</v>
       </c>
       <c r="H983" t="n">
         <v>341029</v>
@@ -28963,7 +28963,7 @@
         <v>2.96499991416931</v>
       </c>
       <c r="G986" t="n">
-        <v>2.66281843185425</v>
+        <v>2.66281867027283</v>
       </c>
       <c r="H986" t="n">
         <v>459551</v>
@@ -29021,7 +29021,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G988" t="n">
-        <v>2.68527030944824</v>
+        <v>2.6852707862854</v>
       </c>
       <c r="H988" t="n">
         <v>775698</v>
@@ -29050,7 +29050,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G989" t="n">
-        <v>2.79304075241089</v>
+        <v>2.79304051399231</v>
       </c>
       <c r="H989" t="n">
         <v>386037</v>
@@ -29079,7 +29079,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G990" t="n">
-        <v>2.68527030944824</v>
+        <v>2.6852707862854</v>
       </c>
       <c r="H990" t="n">
         <v>513049</v>
@@ -29108,7 +29108,7 @@
         <v>2.96499991416931</v>
       </c>
       <c r="G991" t="n">
-        <v>2.66281843185425</v>
+        <v>2.66281867027283</v>
       </c>
       <c r="H991" t="n">
         <v>279205</v>
@@ -29166,7 +29166,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G993" t="n">
-        <v>2.76609778404236</v>
+        <v>2.76609802246094</v>
       </c>
       <c r="H993" t="n">
         <v>83244</v>
@@ -29195,7 +29195,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G994" t="n">
-        <v>2.91428160667419</v>
+        <v>2.91428184509277</v>
       </c>
       <c r="H994" t="n">
         <v>1103056</v>
@@ -29224,7 +29224,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G995" t="n">
-        <v>3.05348491668701</v>
+        <v>3.05348515510559</v>
       </c>
       <c r="H995" t="n">
         <v>731740</v>
@@ -29311,7 +29311,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G998" t="n">
-        <v>2.74364614486694</v>
+        <v>2.74364590644836</v>
       </c>
       <c r="H998" t="n">
         <v>799529</v>
@@ -29369,7 +29369,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1000" t="n">
-        <v>2.75711727142334</v>
+        <v>2.75711750984192</v>
       </c>
       <c r="H1000" t="n">
         <v>197667</v>
@@ -29456,7 +29456,7 @@
         <v>2.96499991416931</v>
       </c>
       <c r="G1003" t="n">
-        <v>2.66281843185425</v>
+        <v>2.66281867027283</v>
       </c>
       <c r="H1003" t="n">
         <v>198697</v>
@@ -29485,7 +29485,7 @@
         <v>3.02500009536743</v>
       </c>
       <c r="G1004" t="n">
-        <v>2.71670365333557</v>
+        <v>2.71670389175415</v>
       </c>
       <c r="H1004" t="n">
         <v>326494</v>
@@ -29514,7 +29514,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1005" t="n">
-        <v>2.68527030944824</v>
+        <v>2.6852707862854</v>
       </c>
       <c r="H1005" t="n">
         <v>92346</v>
@@ -29543,7 +29543,7 @@
         <v>3.01500010490417</v>
       </c>
       <c r="G1006" t="n">
-        <v>2.70772266387939</v>
+        <v>2.70772290229797</v>
       </c>
       <c r="H1006" t="n">
         <v>95646</v>
@@ -29601,7 +29601,7 @@
         <v>3</v>
       </c>
       <c r="G1008" t="n">
-        <v>2.69425129890442</v>
+        <v>2.694251537323</v>
       </c>
       <c r="H1008" t="n">
         <v>106210</v>
@@ -29746,7 +29746,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G1013" t="n">
-        <v>2.78855037689209</v>
+        <v>2.78855013847351</v>
       </c>
       <c r="H1013" t="n">
         <v>56422</v>
@@ -29775,7 +29775,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1014" t="n">
-        <v>2.77507877349854</v>
+        <v>2.77507901191711</v>
       </c>
       <c r="H1014" t="n">
         <v>86689</v>
@@ -29804,7 +29804,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1015" t="n">
-        <v>2.74813675880432</v>
+        <v>2.74813628196716</v>
       </c>
       <c r="H1015" t="n">
         <v>56516</v>
@@ -29833,7 +29833,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1016" t="n">
-        <v>2.75711727142334</v>
+        <v>2.75711750984192</v>
       </c>
       <c r="H1016" t="n">
         <v>97347</v>
@@ -29920,7 +29920,7 @@
         <v>2.96499991416931</v>
       </c>
       <c r="G1019" t="n">
-        <v>2.66281843185425</v>
+        <v>2.66281867027283</v>
       </c>
       <c r="H1019" t="n">
         <v>79291</v>
@@ -29949,7 +29949,7 @@
         <v>2.88499999046326</v>
       </c>
       <c r="G1020" t="n">
-        <v>2.59097170829773</v>
+        <v>2.59097194671631</v>
       </c>
       <c r="H1020" t="n">
         <v>113704</v>
@@ -30007,7 +30007,7 @@
         <v>3.1949999332428</v>
       </c>
       <c r="G1022" t="n">
-        <v>2.86937761306763</v>
+        <v>2.86937785148621</v>
       </c>
       <c r="H1022" t="n">
         <v>420324</v>
@@ -30036,7 +30036,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1023" t="n">
-        <v>3.12533164024353</v>
+        <v>3.12533187866211</v>
       </c>
       <c r="H1023" t="n">
         <v>1427408</v>
@@ -30123,7 +30123,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1026" t="n">
-        <v>2.96367692947388</v>
+        <v>2.9636766910553</v>
       </c>
       <c r="H1026" t="n">
         <v>237803</v>
@@ -30152,7 +30152,7 @@
         <v>3.3050000667572</v>
       </c>
       <c r="G1027" t="n">
-        <v>2.9681670665741</v>
+        <v>2.96816682815552</v>
       </c>
       <c r="H1027" t="n">
         <v>222935</v>
@@ -30210,7 +30210,7 @@
         <v>3.6949999332428</v>
       </c>
       <c r="G1029" t="n">
-        <v>3.31841993331909</v>
+        <v>3.31841945648193</v>
       </c>
       <c r="H1029" t="n">
         <v>1089635</v>
@@ -30239,7 +30239,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G1030" t="n">
-        <v>3.28249621391296</v>
+        <v>3.28249645233154</v>
       </c>
       <c r="H1030" t="n">
         <v>790910</v>
@@ -30268,7 +30268,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1031" t="n">
-        <v>3.17921686172485</v>
+        <v>3.17921662330627</v>
       </c>
       <c r="H1031" t="n">
         <v>425318</v>
@@ -30326,7 +30326,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1033" t="n">
-        <v>2.96367692947388</v>
+        <v>2.9636766910553</v>
       </c>
       <c r="H1033" t="n">
         <v>303204</v>
@@ -30355,7 +30355,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1034" t="n">
-        <v>3.12533164024353</v>
+        <v>3.12533187866211</v>
       </c>
       <c r="H1034" t="n">
         <v>522065</v>
@@ -30384,7 +30384,7 @@
         <v>3.57500004768372</v>
       </c>
       <c r="G1035" t="n">
-        <v>3.21064949035645</v>
+        <v>3.21064972877502</v>
       </c>
       <c r="H1035" t="n">
         <v>814671</v>
@@ -30529,7 +30529,7 @@
         <v>3.5</v>
       </c>
       <c r="G1040" t="n">
-        <v>3.1432933807373</v>
+        <v>3.14329314231873</v>
       </c>
       <c r="H1040" t="n">
         <v>237219</v>
@@ -30558,7 +30558,7 @@
         <v>3.81500005722046</v>
       </c>
       <c r="G1041" t="n">
-        <v>3.426189661026</v>
+        <v>3.42618989944458</v>
       </c>
       <c r="H1041" t="n">
         <v>993473</v>
@@ -30645,7 +30645,7 @@
         <v>3.74499988555908</v>
       </c>
       <c r="G1044" t="n">
-        <v>3.36332392692566</v>
+        <v>3.36332368850708</v>
       </c>
       <c r="H1044" t="n">
         <v>319519</v>
@@ -30703,7 +30703,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G1046" t="n">
-        <v>3.34536194801331</v>
+        <v>3.34536218643188</v>
       </c>
       <c r="H1046" t="n">
         <v>682751</v>
@@ -30761,7 +30761,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1048" t="n">
-        <v>3.30494832992554</v>
+        <v>3.30494856834412</v>
       </c>
       <c r="H1048" t="n">
         <v>343273</v>
@@ -30819,7 +30819,7 @@
         <v>3.57500004768372</v>
       </c>
       <c r="G1050" t="n">
-        <v>3.21064949035645</v>
+        <v>3.21064972877502</v>
       </c>
       <c r="H1050" t="n">
         <v>228274</v>
@@ -30848,7 +30848,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1051" t="n">
-        <v>3.09838938713074</v>
+        <v>3.09838914871216</v>
       </c>
       <c r="H1051" t="n">
         <v>316345</v>
@@ -30906,7 +30906,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1053" t="n">
-        <v>2.87386846542358</v>
+        <v>2.873868227005</v>
       </c>
       <c r="H1053" t="n">
         <v>433328</v>
@@ -30993,7 +30993,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1056" t="n">
-        <v>2.79304075241089</v>
+        <v>2.79304051399231</v>
       </c>
       <c r="H1056" t="n">
         <v>285032</v>
@@ -31167,7 +31167,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1062" t="n">
-        <v>2.56851959228516</v>
+        <v>2.56851935386658</v>
       </c>
       <c r="H1062" t="n">
         <v>216400</v>
@@ -31196,7 +31196,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G1063" t="n">
-        <v>2.30807542800903</v>
+        <v>2.30807518959045</v>
       </c>
       <c r="H1063" t="n">
         <v>452760</v>
@@ -31254,7 +31254,7 @@
         <v>2.39499998092651</v>
       </c>
       <c r="G1065" t="n">
-        <v>2.1509108543396</v>
+        <v>2.15091061592102</v>
       </c>
       <c r="H1065" t="n">
         <v>184356</v>
@@ -31283,7 +31283,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1066" t="n">
-        <v>1.84107172489166</v>
+        <v>1.84107184410095</v>
       </c>
       <c r="H1066" t="n">
         <v>296349</v>
@@ -31312,7 +31312,7 @@
         <v>2</v>
       </c>
       <c r="G1067" t="n">
-        <v>1.79616761207581</v>
+        <v>1.7961677312851</v>
       </c>
       <c r="H1067" t="n">
         <v>283496</v>
@@ -31370,7 +31370,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1069" t="n">
-        <v>1.81412935256958</v>
+        <v>1.814129114151</v>
       </c>
       <c r="H1069" t="n">
         <v>164736</v>
@@ -31399,7 +31399,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1070" t="n">
-        <v>1.86801421642303</v>
+        <v>1.86801433563232</v>
       </c>
       <c r="H1070" t="n">
         <v>60442</v>
@@ -31486,7 +31486,7 @@
         <v>2</v>
       </c>
       <c r="G1073" t="n">
-        <v>1.79616761207581</v>
+        <v>1.7961677312851</v>
       </c>
       <c r="H1073" t="n">
         <v>79287</v>
@@ -31515,7 +31515,7 @@
         <v>2.16499996185303</v>
       </c>
       <c r="G1074" t="n">
-        <v>1.94435143470764</v>
+        <v>1.94435119628906</v>
       </c>
       <c r="H1074" t="n">
         <v>152523</v>
@@ -31544,7 +31544,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1075" t="n">
-        <v>2.04763102531433</v>
+        <v>2.04763126373291</v>
       </c>
       <c r="H1075" t="n">
         <v>195849</v>
@@ -31573,7 +31573,7 @@
         <v>2.375</v>
       </c>
       <c r="G1076" t="n">
-        <v>2.13294911384583</v>
+        <v>2.13294887542725</v>
       </c>
       <c r="H1076" t="n">
         <v>100585</v>
@@ -31602,7 +31602,7 @@
         <v>2.21499991416931</v>
       </c>
       <c r="G1077" t="n">
-        <v>1.9892555475235</v>
+        <v>1.98925566673279</v>
       </c>
       <c r="H1077" t="n">
         <v>113895</v>
@@ -31631,7 +31631,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G1078" t="n">
-        <v>1.9847651720047</v>
+        <v>1.98476529121399</v>
       </c>
       <c r="H1078" t="n">
         <v>61328</v>
@@ -31660,7 +31660,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1079" t="n">
-        <v>2.04763102531433</v>
+        <v>2.04763126373291</v>
       </c>
       <c r="H1079" t="n">
         <v>150042</v>
@@ -31718,7 +31718,7 @@
         <v>2.5550000667572</v>
       </c>
       <c r="G1081" t="n">
-        <v>2.29460406303406</v>
+        <v>2.29460430145264</v>
       </c>
       <c r="H1081" t="n">
         <v>212896</v>
@@ -31747,7 +31747,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1082" t="n">
-        <v>2.26317119598389</v>
+        <v>2.26317095756531</v>
       </c>
       <c r="H1082" t="n">
         <v>269717</v>
@@ -31776,7 +31776,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G1083" t="n">
-        <v>2.30807542800903</v>
+        <v>2.30807518959045</v>
       </c>
       <c r="H1083" t="n">
         <v>299039</v>
@@ -31892,7 +31892,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1087" t="n">
-        <v>2.53259634971619</v>
+        <v>2.53259658813477</v>
       </c>
       <c r="H1087" t="n">
         <v>56325</v>
@@ -31950,7 +31950,7 @@
         <v>2.68499994277954</v>
       </c>
       <c r="G1089" t="n">
-        <v>2.41135478019714</v>
+        <v>2.41135501861572</v>
       </c>
       <c r="H1089" t="n">
         <v>103564</v>
@@ -32008,7 +32008,7 @@
         <v>2.9449999332428</v>
       </c>
       <c r="G1091" t="n">
-        <v>2.64485669136047</v>
+        <v>2.64485692977905</v>
       </c>
       <c r="H1091" t="n">
         <v>136319</v>
@@ -32037,7 +32037,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1092" t="n">
-        <v>2.62240481376648</v>
+        <v>2.62240505218506</v>
       </c>
       <c r="H1092" t="n">
         <v>54205</v>
@@ -32066,7 +32066,7 @@
         <v>2.86500000953674</v>
       </c>
       <c r="G1093" t="n">
-        <v>2.57301044464111</v>
+        <v>2.57301020622253</v>
       </c>
       <c r="H1093" t="n">
         <v>131890</v>
@@ -32095,7 +32095,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1094" t="n">
-        <v>2.51463460922241</v>
+        <v>2.51463437080383</v>
       </c>
       <c r="H1094" t="n">
         <v>71132</v>
@@ -32124,7 +32124,7 @@
         <v>2.86500000953674</v>
       </c>
       <c r="G1095" t="n">
-        <v>2.57301044464111</v>
+        <v>2.57301020622253</v>
       </c>
       <c r="H1095" t="n">
         <v>62094</v>
@@ -32153,7 +32153,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1096" t="n">
-        <v>2.68527030944824</v>
+        <v>2.6852707862854</v>
       </c>
       <c r="H1096" t="n">
         <v>161123</v>
@@ -32182,7 +32182,7 @@
         <v>2.97499990463257</v>
       </c>
       <c r="G1097" t="n">
-        <v>2.67179942131042</v>
+        <v>2.67179918289185</v>
       </c>
       <c r="H1097" t="n">
         <v>188131</v>
@@ -32211,7 +32211,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1098" t="n">
-        <v>2.65832829475403</v>
+        <v>2.65832805633545</v>
       </c>
       <c r="H1098" t="n">
         <v>64040</v>
@@ -32269,7 +32269,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1100" t="n">
-        <v>2.6762900352478</v>
+        <v>2.67628979682922</v>
       </c>
       <c r="H1100" t="n">
         <v>62723</v>
@@ -32356,7 +32356,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1103" t="n">
-        <v>2.55953860282898</v>
+        <v>2.55953884124756</v>
       </c>
       <c r="H1103" t="n">
         <v>51092</v>
@@ -32385,7 +32385,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1104" t="n">
-        <v>2.56851959228516</v>
+        <v>2.56851935386658</v>
       </c>
       <c r="H1104" t="n">
         <v>16641</v>
@@ -32501,7 +32501,7 @@
         <v>2.86500000953674</v>
       </c>
       <c r="G1108" t="n">
-        <v>2.57301044464111</v>
+        <v>2.57301020622253</v>
       </c>
       <c r="H1108" t="n">
         <v>71160</v>
@@ -32559,7 +32559,7 @@
         <v>2.96499991416931</v>
       </c>
       <c r="G1110" t="n">
-        <v>2.66281843185425</v>
+        <v>2.66281867027283</v>
       </c>
       <c r="H1110" t="n">
         <v>44783</v>
@@ -32588,7 +32588,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1111" t="n">
-        <v>2.55953860282898</v>
+        <v>2.55953884124756</v>
       </c>
       <c r="H1111" t="n">
         <v>96279</v>
@@ -32646,7 +32646,7 @@
         <v>2.77500009536743</v>
       </c>
       <c r="G1113" t="n">
-        <v>2.49218249320984</v>
+        <v>2.49218273162842</v>
       </c>
       <c r="H1113" t="n">
         <v>56483</v>
@@ -32675,7 +32675,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1114" t="n">
-        <v>2.48769211769104</v>
+        <v>2.48769235610962</v>
       </c>
       <c r="H1114" t="n">
         <v>45709</v>
@@ -32704,7 +32704,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G1115" t="n">
-        <v>2.52810621261597</v>
+        <v>2.52810597419739</v>
       </c>
       <c r="H1115" t="n">
         <v>47937</v>
@@ -32762,7 +32762,7 @@
         <v>2.86500000953674</v>
       </c>
       <c r="G1117" t="n">
-        <v>2.57301044464111</v>
+        <v>2.57301020622253</v>
       </c>
       <c r="H1117" t="n">
         <v>76069</v>
@@ -32791,7 +32791,7 @@
         <v>2.9449999332428</v>
       </c>
       <c r="G1118" t="n">
-        <v>2.64485669136047</v>
+        <v>2.64485692977905</v>
       </c>
       <c r="H1118" t="n">
         <v>73129</v>
@@ -32878,7 +32878,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G1121" t="n">
-        <v>2.61342406272888</v>
+        <v>2.6134238243103</v>
       </c>
       <c r="H1121" t="n">
         <v>47119</v>
@@ -32907,7 +32907,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G1122" t="n">
-        <v>2.61342406272888</v>
+        <v>2.6134238243103</v>
       </c>
       <c r="H1122" t="n">
         <v>47055</v>
@@ -33023,7 +33023,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1126" t="n">
-        <v>2.74813675880432</v>
+        <v>2.74813628196716</v>
       </c>
       <c r="H1126" t="n">
         <v>132655</v>
@@ -33110,7 +33110,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1129" t="n">
-        <v>2.55953860282898</v>
+        <v>2.55953884124756</v>
       </c>
       <c r="H1129" t="n">
         <v>99449</v>
@@ -33139,7 +33139,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1130" t="n">
-        <v>2.53259634971619</v>
+        <v>2.53259658813477</v>
       </c>
       <c r="H1130" t="n">
         <v>64525</v>
@@ -33226,7 +33226,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1133" t="n">
-        <v>2.48769211769104</v>
+        <v>2.48769235610962</v>
       </c>
       <c r="H1133" t="n">
         <v>84105</v>
@@ -33284,7 +33284,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1135" t="n">
-        <v>2.51463460922241</v>
+        <v>2.51463437080383</v>
       </c>
       <c r="H1135" t="n">
         <v>55256</v>
@@ -33313,7 +33313,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G1136" t="n">
-        <v>2.52361559867859</v>
+        <v>2.52361536026001</v>
       </c>
       <c r="H1136" t="n">
         <v>35770</v>
@@ -33342,7 +33342,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1137" t="n">
-        <v>2.4248263835907</v>
+        <v>2.42482614517212</v>
       </c>
       <c r="H1137" t="n">
         <v>62263</v>
@@ -33458,7 +33458,7 @@
         <v>2.6949999332428</v>
       </c>
       <c r="G1141" t="n">
-        <v>2.42033576965332</v>
+        <v>2.4203360080719</v>
       </c>
       <c r="H1141" t="n">
         <v>19022</v>
@@ -33516,7 +33516,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1143" t="n">
-        <v>2.48769211769104</v>
+        <v>2.48769235610962</v>
       </c>
       <c r="H1143" t="n">
         <v>28703</v>
@@ -33545,7 +33545,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1144" t="n">
-        <v>2.46074986457825</v>
+        <v>2.46074962615967</v>
       </c>
       <c r="H1144" t="n">
         <v>31806</v>
@@ -33719,7 +33719,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1150" t="n">
-        <v>2.4248263835907</v>
+        <v>2.42482614517212</v>
       </c>
       <c r="H1150" t="n">
         <v>22719</v>
@@ -33748,7 +33748,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G1151" t="n">
-        <v>2.40686464309692</v>
+        <v>2.4068648815155</v>
       </c>
       <c r="H1151" t="n">
         <v>39407</v>
@@ -33777,7 +33777,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1152" t="n">
-        <v>2.41584539413452</v>
+        <v>2.4158456325531</v>
       </c>
       <c r="H1152" t="n">
         <v>39947</v>
@@ -33806,7 +33806,7 @@
         <v>2.76500010490417</v>
       </c>
       <c r="G1153" t="n">
-        <v>2.48320198059082</v>
+        <v>2.48320174217224</v>
       </c>
       <c r="H1153" t="n">
         <v>69598</v>
@@ -33835,7 +33835,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1154" t="n">
-        <v>2.46074986457825</v>
+        <v>2.46074962615967</v>
       </c>
       <c r="H1154" t="n">
         <v>17622</v>
@@ -33864,7 +33864,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1155" t="n">
-        <v>2.53259634971619</v>
+        <v>2.53259658813477</v>
       </c>
       <c r="H1155" t="n">
         <v>33920</v>
@@ -33893,7 +33893,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1156" t="n">
-        <v>2.48769211769104</v>
+        <v>2.48769235610962</v>
       </c>
       <c r="H1156" t="n">
         <v>55468</v>
@@ -33951,7 +33951,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1158" t="n">
-        <v>2.46074986457825</v>
+        <v>2.46074962615967</v>
       </c>
       <c r="H1158" t="n">
         <v>25390</v>
@@ -33980,7 +33980,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1159" t="n">
-        <v>2.41584539413452</v>
+        <v>2.4158456325531</v>
       </c>
       <c r="H1159" t="n">
         <v>15842</v>
@@ -34009,7 +34009,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1160" t="n">
-        <v>2.41584539413452</v>
+        <v>2.4158456325531</v>
       </c>
       <c r="H1160" t="n">
         <v>20217</v>
@@ -34067,7 +34067,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G1162" t="n">
-        <v>2.39788365364075</v>
+        <v>2.39788389205933</v>
       </c>
       <c r="H1162" t="n">
         <v>35142</v>
@@ -34096,7 +34096,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1163" t="n">
-        <v>2.27215194702148</v>
+        <v>2.27215218544006</v>
       </c>
       <c r="H1163" t="n">
         <v>64651</v>
@@ -34125,7 +34125,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1164" t="n">
-        <v>2.27215194702148</v>
+        <v>2.27215218544006</v>
       </c>
       <c r="H1164" t="n">
         <v>24125</v>
@@ -34154,7 +34154,7 @@
         <v>2.64499998092651</v>
       </c>
       <c r="G1165" t="n">
-        <v>2.37543153762817</v>
+        <v>2.37543177604675</v>
       </c>
       <c r="H1165" t="n">
         <v>40838</v>
@@ -34299,7 +34299,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1170" t="n">
-        <v>2.4248263835907</v>
+        <v>2.42482614517212</v>
       </c>
       <c r="H1170" t="n">
         <v>84430</v>
@@ -34386,7 +34386,7 @@
         <v>2.76500010490417</v>
       </c>
       <c r="G1173" t="n">
-        <v>2.48320198059082</v>
+        <v>2.48320174217224</v>
       </c>
       <c r="H1173" t="n">
         <v>95187</v>
@@ -34502,7 +34502,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1177" t="n">
-        <v>2.48769211769104</v>
+        <v>2.48769235610962</v>
       </c>
       <c r="H1177" t="n">
         <v>10565</v>
@@ -34560,7 +34560,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1179" t="n">
-        <v>2.41584539413452</v>
+        <v>2.4158456325531</v>
       </c>
       <c r="H1179" t="n">
         <v>24291</v>
@@ -34589,7 +34589,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G1180" t="n">
-        <v>2.39788365364075</v>
+        <v>2.39788389205933</v>
       </c>
       <c r="H1180" t="n">
         <v>19836</v>
@@ -34618,7 +34618,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1181" t="n">
-        <v>2.37992238998413</v>
+        <v>2.37992215156555</v>
       </c>
       <c r="H1181" t="n">
         <v>13841</v>
@@ -34676,7 +34676,7 @@
         <v>2.60500001907349</v>
       </c>
       <c r="G1183" t="n">
-        <v>2.33950805664062</v>
+        <v>2.3395082950592</v>
       </c>
       <c r="H1183" t="n">
         <v>21306</v>
@@ -34734,7 +34734,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G1185" t="n">
-        <v>2.36196064949036</v>
+        <v>2.36196041107178</v>
       </c>
       <c r="H1185" t="n">
         <v>9167</v>
@@ -34792,7 +34792,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G1187" t="n">
-        <v>2.39788365364075</v>
+        <v>2.39788389205933</v>
       </c>
       <c r="H1187" t="n">
         <v>18532</v>
@@ -34821,7 +34821,7 @@
         <v>2.67499995231628</v>
       </c>
       <c r="G1188" t="n">
-        <v>2.40237426757812</v>
+        <v>2.40237402915955</v>
       </c>
       <c r="H1188" t="n">
         <v>28755</v>
@@ -34879,7 +34879,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1190" t="n">
-        <v>2.37992238998413</v>
+        <v>2.37992215156555</v>
       </c>
       <c r="H1190" t="n">
         <v>13045</v>
@@ -34908,7 +34908,7 @@
         <v>2.67499995231628</v>
       </c>
       <c r="G1191" t="n">
-        <v>2.40237426757812</v>
+        <v>2.40237402915955</v>
       </c>
       <c r="H1191" t="n">
         <v>5984</v>
@@ -34995,7 +34995,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1194" t="n">
-        <v>2.46074986457825</v>
+        <v>2.46074962615967</v>
       </c>
       <c r="H1194" t="n">
         <v>27385</v>
@@ -35024,7 +35024,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G1195" t="n">
-        <v>2.49667310714722</v>
+        <v>2.49667286872864</v>
       </c>
       <c r="H1195" t="n">
         <v>52126</v>
@@ -35082,7 +35082,7 @@
         <v>2.76500010490417</v>
       </c>
       <c r="G1197" t="n">
-        <v>2.48320198059082</v>
+        <v>2.48320174217224</v>
       </c>
       <c r="H1197" t="n">
         <v>28433</v>
@@ -35111,7 +35111,7 @@
         <v>2.66499996185303</v>
       </c>
       <c r="G1198" t="n">
-        <v>2.39339351654053</v>
+        <v>2.39339327812195</v>
       </c>
       <c r="H1198" t="n">
         <v>30486</v>
@@ -35256,7 +35256,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G1203" t="n">
-        <v>2.28113269805908</v>
+        <v>2.28113317489624</v>
       </c>
       <c r="H1203" t="n">
         <v>9858</v>
@@ -35285,7 +35285,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1204" t="n">
-        <v>2.27215194702148</v>
+        <v>2.27215218544006</v>
       </c>
       <c r="H1204" t="n">
         <v>51893</v>
@@ -35372,7 +35372,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1207" t="n">
-        <v>2.27215194702148</v>
+        <v>2.27215218544006</v>
       </c>
       <c r="H1207" t="n">
         <v>24666</v>
@@ -35401,7 +35401,7 @@
         <v>2.6949999332428</v>
       </c>
       <c r="G1208" t="n">
-        <v>2.42033576965332</v>
+        <v>2.4203360080719</v>
       </c>
       <c r="H1208" t="n">
         <v>103202</v>
@@ -35488,7 +35488,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G1211" t="n">
-        <v>2.32603693008423</v>
+        <v>2.32603716850281</v>
       </c>
       <c r="H1211" t="n">
         <v>41706</v>
@@ -35517,7 +35517,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1212" t="n">
-        <v>2.37992238998413</v>
+        <v>2.37992215156555</v>
       </c>
       <c r="H1212" t="n">
         <v>82760</v>
@@ -35546,7 +35546,7 @@
         <v>2.6949999332428</v>
       </c>
       <c r="G1213" t="n">
-        <v>2.42033576965332</v>
+        <v>2.4203360080719</v>
       </c>
       <c r="H1213" t="n">
         <v>60898</v>
@@ -35604,7 +35604,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1215" t="n">
-        <v>2.37992238998413</v>
+        <v>2.37992215156555</v>
       </c>
       <c r="H1215" t="n">
         <v>41460</v>
@@ -35633,7 +35633,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G1216" t="n">
-        <v>2.32603693008423</v>
+        <v>2.32603716850281</v>
       </c>
       <c r="H1216" t="n">
         <v>32139</v>
@@ -35691,7 +35691,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G1218" t="n">
-        <v>2.49667310714722</v>
+        <v>2.49667286872864</v>
       </c>
       <c r="H1218" t="n">
         <v>177616</v>
@@ -35720,7 +35720,7 @@
         <v>2.79500007629395</v>
       </c>
       <c r="G1219" t="n">
-        <v>2.51014423370361</v>
+        <v>2.51014447212219</v>
       </c>
       <c r="H1219" t="n">
         <v>57702</v>
@@ -35749,7 +35749,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1220" t="n">
-        <v>2.53259634971619</v>
+        <v>2.53259658813477</v>
       </c>
       <c r="H1220" t="n">
         <v>103554</v>
@@ -35836,7 +35836,7 @@
         <v>2.86500000953674</v>
       </c>
       <c r="G1223" t="n">
-        <v>2.57301044464111</v>
+        <v>2.57301020622253</v>
       </c>
       <c r="H1223" t="n">
         <v>73060</v>
@@ -35865,7 +35865,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1224" t="n">
-        <v>2.53259634971619</v>
+        <v>2.53259658813477</v>
       </c>
       <c r="H1224" t="n">
         <v>27341</v>
@@ -35952,7 +35952,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1227" t="n">
-        <v>2.27215194702148</v>
+        <v>2.27215218544006</v>
       </c>
       <c r="H1227" t="n">
         <v>120681</v>
@@ -35981,7 +35981,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G1228" t="n">
-        <v>2.3529794216156</v>
+        <v>2.35297966003418</v>
       </c>
       <c r="H1228" t="n">
         <v>45826</v>
@@ -36010,7 +36010,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G1229" t="n">
-        <v>2.29011368751526</v>
+        <v>2.29011344909668</v>
       </c>
       <c r="H1229" t="n">
         <v>95134</v>
@@ -36097,7 +36097,7 @@
         <v>2.5550000667572</v>
       </c>
       <c r="G1232" t="n">
-        <v>2.29460406303406</v>
+        <v>2.29460430145264</v>
       </c>
       <c r="H1232" t="n">
         <v>28247</v>
@@ -36184,7 +36184,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1235" t="n">
-        <v>2.37992238998413</v>
+        <v>2.37992215156555</v>
       </c>
       <c r="H1235" t="n">
         <v>81552</v>
@@ -36242,7 +36242,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1237" t="n">
-        <v>2.41584539413452</v>
+        <v>2.4158456325531</v>
       </c>
       <c r="H1237" t="n">
         <v>31433</v>
@@ -36271,7 +36271,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1238" t="n">
-        <v>2.37992238998413</v>
+        <v>2.37992215156555</v>
       </c>
       <c r="H1238" t="n">
         <v>23292</v>
@@ -36358,7 +36358,7 @@
         <v>2.64499998092651</v>
       </c>
       <c r="G1241" t="n">
-        <v>2.37543153762817</v>
+        <v>2.37543177604675</v>
       </c>
       <c r="H1241" t="n">
         <v>101736</v>
@@ -36387,7 +36387,7 @@
         <v>2.77500009536743</v>
       </c>
       <c r="G1242" t="n">
-        <v>2.49218249320984</v>
+        <v>2.49218273162842</v>
       </c>
       <c r="H1242" t="n">
         <v>155703</v>
@@ -36503,7 +36503,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1246" t="n">
-        <v>2.53259634971619</v>
+        <v>2.53259658813477</v>
       </c>
       <c r="H1246" t="n">
         <v>129020</v>
@@ -36532,7 +36532,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1247" t="n">
-        <v>2.55953860282898</v>
+        <v>2.55953884124756</v>
       </c>
       <c r="H1247" t="n">
         <v>81202</v>
@@ -36561,7 +36561,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1248" t="n">
-        <v>2.56851959228516</v>
+        <v>2.56851935386658</v>
       </c>
       <c r="H1248" t="n">
         <v>42513</v>
@@ -36590,7 +36590,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1249" t="n">
-        <v>2.53259634971619</v>
+        <v>2.53259658813477</v>
       </c>
       <c r="H1249" t="n">
         <v>31429</v>
@@ -36619,7 +36619,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1250" t="n">
-        <v>2.58648157119751</v>
+        <v>2.58648133277893</v>
       </c>
       <c r="H1250" t="n">
         <v>67685</v>
@@ -36648,7 +36648,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1251" t="n">
-        <v>2.65832829475403</v>
+        <v>2.65832805633545</v>
       </c>
       <c r="H1251" t="n">
         <v>125447</v>
@@ -36677,7 +36677,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1252" t="n">
-        <v>2.68527030944824</v>
+        <v>2.6852707862854</v>
       </c>
       <c r="H1252" t="n">
         <v>149703</v>
@@ -36706,7 +36706,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1253" t="n">
-        <v>2.6762900352478</v>
+        <v>2.67628979682922</v>
       </c>
       <c r="H1253" t="n">
         <v>34882</v>
@@ -36735,7 +36735,7 @@
         <v>3</v>
       </c>
       <c r="G1254" t="n">
-        <v>2.69425129890442</v>
+        <v>2.694251537323</v>
       </c>
       <c r="H1254" t="n">
         <v>211926</v>
@@ -36764,7 +36764,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1255" t="n">
-        <v>2.74813675880432</v>
+        <v>2.74813628196716</v>
       </c>
       <c r="H1255" t="n">
         <v>102967</v>
@@ -36793,7 +36793,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G1256" t="n">
-        <v>2.76160764694214</v>
+        <v>2.76160788536072</v>
       </c>
       <c r="H1256" t="n">
         <v>52490</v>
@@ -36909,7 +36909,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1260" t="n">
-        <v>2.77507877349854</v>
+        <v>2.77507901191711</v>
       </c>
       <c r="H1260" t="n">
         <v>108963</v>
@@ -36967,7 +36967,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1262" t="n">
-        <v>2.77507877349854</v>
+        <v>2.77507901191711</v>
       </c>
       <c r="H1262" t="n">
         <v>59601</v>
@@ -37054,7 +37054,7 @@
         <v>3.02500009536743</v>
       </c>
       <c r="G1265" t="n">
-        <v>2.71670365333557</v>
+        <v>2.71670389175415</v>
       </c>
       <c r="H1265" t="n">
         <v>137009</v>
@@ -37112,7 +37112,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1267" t="n">
-        <v>2.75711727142334</v>
+        <v>2.75711750984192</v>
       </c>
       <c r="H1267" t="n">
         <v>21704</v>
@@ -37141,7 +37141,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G1268" t="n">
-        <v>2.78855037689209</v>
+        <v>2.78855013847351</v>
       </c>
       <c r="H1268" t="n">
         <v>40994</v>
@@ -37228,7 +37228,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1271" t="n">
-        <v>2.77507877349854</v>
+        <v>2.77507901191711</v>
       </c>
       <c r="H1271" t="n">
         <v>80673</v>
@@ -37286,7 +37286,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1273" t="n">
-        <v>2.79304075241089</v>
+        <v>2.79304051399231</v>
       </c>
       <c r="H1273" t="n">
         <v>30997</v>
@@ -37315,7 +37315,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1274" t="n">
-        <v>2.77507877349854</v>
+        <v>2.77507901191711</v>
       </c>
       <c r="H1274" t="n">
         <v>66369</v>
@@ -37373,7 +37373,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1276" t="n">
-        <v>2.79304075241089</v>
+        <v>2.79304051399231</v>
       </c>
       <c r="H1276" t="n">
         <v>24902</v>
@@ -37402,7 +37402,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1277" t="n">
-        <v>2.79304075241089</v>
+        <v>2.79304051399231</v>
       </c>
       <c r="H1277" t="n">
         <v>22540</v>
@@ -37431,7 +37431,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1278" t="n">
-        <v>2.75711727142334</v>
+        <v>2.75711750984192</v>
       </c>
       <c r="H1278" t="n">
         <v>35383</v>
@@ -37576,7 +37576,7 @@
         <v>2.9449999332428</v>
       </c>
       <c r="G1283" t="n">
-        <v>2.64485669136047</v>
+        <v>2.64485692977905</v>
       </c>
       <c r="H1283" t="n">
         <v>43761</v>
@@ -37605,7 +37605,7 @@
         <v>3</v>
       </c>
       <c r="G1284" t="n">
-        <v>2.69425129890442</v>
+        <v>2.694251537323</v>
       </c>
       <c r="H1284" t="n">
         <v>14176</v>
@@ -37663,7 +37663,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G1286" t="n">
-        <v>2.54606747627258</v>
+        <v>2.54606771469116</v>
       </c>
       <c r="H1286" t="n">
         <v>52596</v>
@@ -37692,7 +37692,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1287" t="n">
-        <v>2.65832829475403</v>
+        <v>2.65832805633545</v>
       </c>
       <c r="H1287" t="n">
         <v>57291</v>
@@ -37808,7 +37808,7 @@
         <v>3</v>
       </c>
       <c r="G1291" t="n">
-        <v>2.69425129890442</v>
+        <v>2.694251537323</v>
       </c>
       <c r="H1291" t="n">
         <v>235563</v>
@@ -37837,7 +37837,7 @@
         <v>3.02500009536743</v>
       </c>
       <c r="G1292" t="n">
-        <v>2.71670365333557</v>
+        <v>2.71670389175415</v>
       </c>
       <c r="H1292" t="n">
         <v>68100</v>
@@ -37895,7 +37895,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G1294" t="n">
-        <v>2.76160764694214</v>
+        <v>2.76160788536072</v>
       </c>
       <c r="H1294" t="n">
         <v>149188</v>
@@ -37924,7 +37924,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1295" t="n">
-        <v>2.79304075241089</v>
+        <v>2.79304051399231</v>
       </c>
       <c r="H1295" t="n">
         <v>80017</v>
@@ -38098,7 +38098,7 @@
         <v>3.5</v>
       </c>
       <c r="G1301" t="n">
-        <v>3.1432933807373</v>
+        <v>3.14329314231873</v>
       </c>
       <c r="H1301" t="n">
         <v>338914</v>
@@ -38127,7 +38127,7 @@
         <v>3.49499988555908</v>
       </c>
       <c r="G1302" t="n">
-        <v>3.13880300521851</v>
+        <v>3.13880276679993</v>
       </c>
       <c r="H1302" t="n">
         <v>86110</v>
@@ -38185,7 +38185,7 @@
         <v>3.36500000953674</v>
       </c>
       <c r="G1304" t="n">
-        <v>3.02205228805542</v>
+        <v>3.02205204963684</v>
       </c>
       <c r="H1304" t="n">
         <v>102351</v>
@@ -38272,7 +38272,7 @@
         <v>3.42499995231628</v>
       </c>
       <c r="G1307" t="n">
-        <v>3.07593679428101</v>
+        <v>3.07593727111816</v>
       </c>
       <c r="H1307" t="n">
         <v>174636</v>
@@ -38301,7 +38301,7 @@
         <v>3.42499995231628</v>
       </c>
       <c r="G1308" t="n">
-        <v>3.07593679428101</v>
+        <v>3.07593727111816</v>
       </c>
       <c r="H1308" t="n">
         <v>35023</v>
@@ -38330,7 +38330,7 @@
         <v>3.33500003814697</v>
       </c>
       <c r="G1309" t="n">
-        <v>2.99510931968689</v>
+        <v>2.99510955810547</v>
       </c>
       <c r="H1309" t="n">
         <v>53098</v>
@@ -38359,7 +38359,7 @@
         <v>3.22499990463257</v>
       </c>
       <c r="G1310" t="n">
-        <v>2.896320104599</v>
+        <v>2.89632034301758</v>
       </c>
       <c r="H1310" t="n">
         <v>141496</v>
@@ -38533,7 +38533,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1316" t="n">
-        <v>3.05348491668701</v>
+        <v>3.05348515510559</v>
       </c>
       <c r="H1316" t="n">
         <v>56200</v>
@@ -38620,7 +38620,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1319" t="n">
-        <v>3.09838938713074</v>
+        <v>3.09838914871216</v>
       </c>
       <c r="H1319" t="n">
         <v>106279</v>
@@ -38707,7 +38707,7 @@
         <v>3.28500008583069</v>
       </c>
       <c r="G1322" t="n">
-        <v>2.95020532608032</v>
+        <v>2.9502055644989</v>
       </c>
       <c r="H1322" t="n">
         <v>455525</v>
@@ -38852,7 +38852,7 @@
         <v>3.3050000667572</v>
       </c>
       <c r="G1327" t="n">
-        <v>2.9681670665741</v>
+        <v>2.96816682815552</v>
       </c>
       <c r="H1327" t="n">
         <v>45781</v>
@@ -38968,7 +38968,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1331" t="n">
-        <v>3.00858092308044</v>
+        <v>3.00858068466187</v>
       </c>
       <c r="H1331" t="n">
         <v>25683</v>
@@ -39084,7 +39084,7 @@
         <v>3.31500005722046</v>
       </c>
       <c r="G1335" t="n">
-        <v>2.97714781761169</v>
+        <v>2.97714805603027</v>
       </c>
       <c r="H1335" t="n">
         <v>132492</v>
@@ -39142,7 +39142,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1337" t="n">
-        <v>2.79304075241089</v>
+        <v>2.79304051399231</v>
       </c>
       <c r="H1337" t="n">
         <v>257422</v>
@@ -39200,7 +39200,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1339" t="n">
-        <v>2.86488747596741</v>
+        <v>2.86488723754883</v>
       </c>
       <c r="H1339" t="n">
         <v>59189</v>
@@ -39229,7 +39229,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1340" t="n">
-        <v>2.9008104801178</v>
+        <v>2.90081071853638</v>
       </c>
       <c r="H1340" t="n">
         <v>22176</v>
@@ -39258,7 +39258,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1341" t="n">
-        <v>2.87386846542358</v>
+        <v>2.873868227005</v>
       </c>
       <c r="H1341" t="n">
         <v>97613</v>
@@ -39287,7 +39287,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1342" t="n">
-        <v>2.87386846542358</v>
+        <v>2.873868227005</v>
       </c>
       <c r="H1342" t="n">
         <v>52668</v>
@@ -39316,7 +39316,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1343" t="n">
-        <v>2.87386846542358</v>
+        <v>2.873868227005</v>
       </c>
       <c r="H1343" t="n">
         <v>33996</v>
@@ -39374,7 +39374,7 @@
         <v>3.14499998092651</v>
       </c>
       <c r="G1345" t="n">
-        <v>2.82447338104248</v>
+        <v>2.82447361946106</v>
       </c>
       <c r="H1345" t="n">
         <v>74454</v>
@@ -39403,7 +39403,7 @@
         <v>3.11500000953674</v>
       </c>
       <c r="G1346" t="n">
-        <v>2.79753112792969</v>
+        <v>2.79753136634827</v>
       </c>
       <c r="H1346" t="n">
         <v>28457</v>
@@ -39432,7 +39432,7 @@
         <v>3.25</v>
       </c>
       <c r="G1347" t="n">
-        <v>2.91877245903015</v>
+        <v>2.91877222061157</v>
       </c>
       <c r="H1347" t="n">
         <v>190767</v>
@@ -39461,7 +39461,7 @@
         <v>3.34500002861023</v>
       </c>
       <c r="G1348" t="n">
-        <v>3.00409054756165</v>
+        <v>3.00409030914307</v>
       </c>
       <c r="H1348" t="n">
         <v>247027</v>
@@ -39490,7 +39490,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1349" t="n">
-        <v>3.05348491668701</v>
+        <v>3.05348515510559</v>
       </c>
       <c r="H1349" t="n">
         <v>145927</v>
@@ -39635,7 +39635,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1354" t="n">
-        <v>3.05348491668701</v>
+        <v>3.05348515510559</v>
       </c>
       <c r="H1354" t="n">
         <v>75529</v>
@@ -39664,7 +39664,7 @@
         <v>3.4449999332428</v>
       </c>
       <c r="G1355" t="n">
-        <v>3.09389877319336</v>
+        <v>3.09389853477478</v>
       </c>
       <c r="H1355" t="n">
         <v>111458</v>
@@ -39722,7 +39722,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G1357" t="n">
-        <v>3.28249621391296</v>
+        <v>3.28249645233154</v>
       </c>
       <c r="H1357" t="n">
         <v>306265</v>
@@ -39751,7 +39751,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1358" t="n">
-        <v>3.30494832992554</v>
+        <v>3.30494856834412</v>
       </c>
       <c r="H1358" t="n">
         <v>134090</v>
@@ -39780,7 +39780,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1359" t="n">
-        <v>3.35883355140686</v>
+        <v>3.35883331298828</v>
       </c>
       <c r="H1359" t="n">
         <v>166356</v>
@@ -39809,7 +39809,7 @@
         <v>3.60500001907349</v>
       </c>
       <c r="G1360" t="n">
-        <v>3.23759245872498</v>
+        <v>3.2375922203064</v>
       </c>
       <c r="H1360" t="n">
         <v>186639</v>
@@ -39867,7 +39867,7 @@
         <v>3.68499994277954</v>
       </c>
       <c r="G1362" t="n">
-        <v>3.30943870544434</v>
+        <v>3.30943846702576</v>
       </c>
       <c r="H1362" t="n">
         <v>101891</v>
@@ -39896,7 +39896,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1363" t="n">
-        <v>3.18819737434387</v>
+        <v>3.18819761276245</v>
       </c>
       <c r="H1363" t="n">
         <v>116758</v>
@@ -39983,7 +39983,7 @@
         <v>3.5</v>
       </c>
       <c r="G1366" t="n">
-        <v>3.1432933807373</v>
+        <v>3.14329314231873</v>
       </c>
       <c r="H1366" t="n">
         <v>60802</v>
@@ -40070,7 +40070,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1369" t="n">
-        <v>3.11635065078735</v>
+        <v>3.11635088920593</v>
       </c>
       <c r="H1369" t="n">
         <v>23574</v>
@@ -40099,7 +40099,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1370" t="n">
-        <v>3.12533164024353</v>
+        <v>3.12533187866211</v>
       </c>
       <c r="H1370" t="n">
         <v>24814</v>
@@ -40157,7 +40157,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1372" t="n">
-        <v>3.05348491668701</v>
+        <v>3.05348515510559</v>
       </c>
       <c r="H1372" t="n">
         <v>69751</v>
@@ -40360,7 +40360,7 @@
         <v>3.4449999332428</v>
       </c>
       <c r="G1379" t="n">
-        <v>3.09389877319336</v>
+        <v>3.09389853477478</v>
       </c>
       <c r="H1379" t="n">
         <v>56458</v>
@@ -40505,7 +40505,7 @@
         <v>3.5</v>
       </c>
       <c r="G1384" t="n">
-        <v>3.1432933807373</v>
+        <v>3.14329314231873</v>
       </c>
       <c r="H1384" t="n">
         <v>187009</v>
@@ -40534,7 +40534,7 @@
         <v>3.54500007629395</v>
       </c>
       <c r="G1385" t="n">
-        <v>3.18370723724365</v>
+        <v>3.18370699882507</v>
       </c>
       <c r="H1385" t="n">
         <v>69860</v>
@@ -40650,7 +40650,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1389" t="n">
-        <v>2.98163819313049</v>
+        <v>2.98163843154907</v>
       </c>
       <c r="H1389" t="n">
         <v>38754</v>
@@ -40679,7 +40679,7 @@
         <v>3.33500003814697</v>
       </c>
       <c r="G1390" t="n">
-        <v>2.99510931968689</v>
+        <v>2.99510955810547</v>
       </c>
       <c r="H1390" t="n">
         <v>26650</v>
@@ -40737,7 +40737,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1392" t="n">
-        <v>2.98163819313049</v>
+        <v>2.98163843154907</v>
       </c>
       <c r="H1392" t="n">
         <v>35004</v>
@@ -40766,7 +40766,7 @@
         <v>3.28500008583069</v>
       </c>
       <c r="G1393" t="n">
-        <v>2.95020532608032</v>
+        <v>2.9502055644989</v>
       </c>
       <c r="H1393" t="n">
         <v>27275</v>
@@ -40911,7 +40911,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1398" t="n">
-        <v>3.2331018447876</v>
+        <v>3.23310160636902</v>
       </c>
       <c r="H1398" t="n">
         <v>59128</v>
@@ -40969,7 +40969,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G1400" t="n">
-        <v>3.19268798828125</v>
+        <v>3.19268822669983</v>
       </c>
       <c r="H1400" t="n">
         <v>37108</v>
@@ -40998,7 +40998,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1401" t="n">
-        <v>3.22412085533142</v>
+        <v>3.22412061691284</v>
       </c>
       <c r="H1401" t="n">
         <v>21167</v>
@@ -41056,7 +41056,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1403" t="n">
-        <v>3.00858092308044</v>
+        <v>3.00858068466187</v>
       </c>
       <c r="H1403" t="n">
         <v>116710</v>
@@ -41143,7 +41143,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1406" t="n">
-        <v>3.00858092308044</v>
+        <v>3.00858068466187</v>
       </c>
       <c r="H1406" t="n">
         <v>24698</v>
@@ -41201,7 +41201,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1408" t="n">
-        <v>3.00858092308044</v>
+        <v>3.00858068466187</v>
       </c>
       <c r="H1408" t="n">
         <v>35786</v>
@@ -41230,7 +41230,7 @@
         <v>3.23499989509583</v>
       </c>
       <c r="G1409" t="n">
-        <v>2.90530109405518</v>
+        <v>2.9053008556366</v>
       </c>
       <c r="H1409" t="n">
         <v>88494</v>
@@ -41259,7 +41259,7 @@
         <v>3.23499989509583</v>
       </c>
       <c r="G1410" t="n">
-        <v>2.90530109405518</v>
+        <v>2.9053008556366</v>
       </c>
       <c r="H1410" t="n">
         <v>32229</v>
@@ -41317,7 +41317,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1412" t="n">
-        <v>3.00858092308044</v>
+        <v>3.00858068466187</v>
       </c>
       <c r="H1412" t="n">
         <v>26694</v>
@@ -41433,7 +41433,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1416" t="n">
-        <v>3.00858092308044</v>
+        <v>3.00858068466187</v>
       </c>
       <c r="H1416" t="n">
         <v>42279</v>
@@ -41491,7 +41491,7 @@
         <v>3.34500002861023</v>
       </c>
       <c r="G1418" t="n">
-        <v>3.00409054756165</v>
+        <v>3.00409030914307</v>
       </c>
       <c r="H1418" t="n">
         <v>187546</v>
@@ -41520,7 +41520,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1419" t="n">
-        <v>2.98163819313049</v>
+        <v>2.98163843154907</v>
       </c>
       <c r="H1419" t="n">
         <v>139874</v>
@@ -41549,7 +41549,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1420" t="n">
-        <v>2.97265720367432</v>
+        <v>2.9726574420929</v>
       </c>
       <c r="H1420" t="n">
         <v>59670</v>
@@ -41578,7 +41578,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1421" t="n">
-        <v>2.94571495056152</v>
+        <v>2.94571471214294</v>
       </c>
       <c r="H1421" t="n">
         <v>12821</v>
@@ -41607,7 +41607,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1422" t="n">
-        <v>2.97265720367432</v>
+        <v>2.9726574420929</v>
       </c>
       <c r="H1422" t="n">
         <v>46077</v>
@@ -41636,7 +41636,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1423" t="n">
-        <v>2.96367692947388</v>
+        <v>2.9636766910553</v>
       </c>
       <c r="H1423" t="n">
         <v>50113</v>
@@ -41665,7 +41665,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1424" t="n">
-        <v>2.98163819313049</v>
+        <v>2.98163843154907</v>
       </c>
       <c r="H1424" t="n">
         <v>17111</v>
@@ -41694,7 +41694,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1425" t="n">
-        <v>2.94571495056152</v>
+        <v>2.94571471214294</v>
       </c>
       <c r="H1425" t="n">
         <v>32445</v>
@@ -41723,7 +41723,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1426" t="n">
-        <v>2.97265720367432</v>
+        <v>2.9726574420929</v>
       </c>
       <c r="H1426" t="n">
         <v>49587</v>
@@ -41810,7 +41810,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1429" t="n">
-        <v>2.90979146957397</v>
+        <v>2.90979170799255</v>
       </c>
       <c r="H1429" t="n">
         <v>45679</v>
@@ -41868,7 +41868,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1431" t="n">
-        <v>3.00858092308044</v>
+        <v>3.00858068466187</v>
       </c>
       <c r="H1431" t="n">
         <v>51310</v>
@@ -41897,7 +41897,7 @@
         <v>3.33500003814697</v>
       </c>
       <c r="G1432" t="n">
-        <v>2.99510931968689</v>
+        <v>2.99510955810547</v>
       </c>
       <c r="H1432" t="n">
         <v>100309</v>
@@ -41984,7 +41984,7 @@
         <v>3.3050000667572</v>
       </c>
       <c r="G1435" t="n">
-        <v>2.9681670665741</v>
+        <v>2.96816682815552</v>
       </c>
       <c r="H1435" t="n">
         <v>9467</v>
@@ -42013,7 +42013,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1436" t="n">
-        <v>2.93673396110535</v>
+        <v>2.93673419952393</v>
       </c>
       <c r="H1436" t="n">
         <v>21907</v>
@@ -42042,7 +42042,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1437" t="n">
-        <v>2.93673396110535</v>
+        <v>2.93673419952393</v>
       </c>
       <c r="H1437" t="n">
         <v>22159</v>
@@ -42071,7 +42071,7 @@
         <v>3.25</v>
       </c>
       <c r="G1438" t="n">
-        <v>2.91877245903015</v>
+        <v>2.91877222061157</v>
       </c>
       <c r="H1438" t="n">
         <v>18524</v>
@@ -42100,7 +42100,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1439" t="n">
-        <v>2.93673396110535</v>
+        <v>2.93673419952393</v>
       </c>
       <c r="H1439" t="n">
         <v>17042</v>
@@ -42158,7 +42158,7 @@
         <v>3.28500008583069</v>
       </c>
       <c r="G1441" t="n">
-        <v>2.95020532608032</v>
+        <v>2.9502055644989</v>
       </c>
       <c r="H1441" t="n">
         <v>53182</v>
@@ -42187,7 +42187,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1442" t="n">
-        <v>2.98163819313049</v>
+        <v>2.98163843154907</v>
       </c>
       <c r="H1442" t="n">
         <v>42870</v>
@@ -42216,7 +42216,7 @@
         <v>3.31500005722046</v>
       </c>
       <c r="G1443" t="n">
-        <v>2.97714781761169</v>
+        <v>2.97714805603027</v>
       </c>
       <c r="H1443" t="n">
         <v>79496</v>
@@ -42245,7 +42245,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1444" t="n">
-        <v>2.94571495056152</v>
+        <v>2.94571471214294</v>
       </c>
       <c r="H1444" t="n">
         <v>26595</v>
@@ -42274,7 +42274,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1445" t="n">
-        <v>2.93673396110535</v>
+        <v>2.93673419952393</v>
       </c>
       <c r="H1445" t="n">
         <v>16752</v>
@@ -42332,7 +42332,7 @@
         <v>3.25500011444092</v>
       </c>
       <c r="G1447" t="n">
-        <v>2.92326307296753</v>
+        <v>2.92326283454895</v>
       </c>
       <c r="H1447" t="n">
         <v>26505</v>
@@ -42361,7 +42361,7 @@
         <v>3.25</v>
       </c>
       <c r="G1448" t="n">
-        <v>2.91877245903015</v>
+        <v>2.91877222061157</v>
       </c>
       <c r="H1448" t="n">
         <v>29830</v>
@@ -42390,7 +42390,7 @@
         <v>3.22499990463257</v>
       </c>
       <c r="G1449" t="n">
-        <v>2.896320104599</v>
+        <v>2.89632034301758</v>
       </c>
       <c r="H1449" t="n">
         <v>52738</v>
@@ -42419,7 +42419,7 @@
         <v>3.22499990463257</v>
       </c>
       <c r="G1450" t="n">
-        <v>2.896320104599</v>
+        <v>2.89632034301758</v>
       </c>
       <c r="H1450" t="n">
         <v>30176</v>
@@ -42564,7 +42564,7 @@
         <v>3.15499997138977</v>
       </c>
       <c r="G1455" t="n">
-        <v>2.83345437049866</v>
+        <v>2.83345413208008</v>
       </c>
       <c r="H1455" t="n">
         <v>72257</v>
@@ -42593,7 +42593,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G1456" t="n">
-        <v>2.91428160667419</v>
+        <v>2.91428184509277</v>
       </c>
       <c r="H1456" t="n">
         <v>38071</v>
@@ -42651,7 +42651,7 @@
         <v>3.25</v>
       </c>
       <c r="G1458" t="n">
-        <v>2.91877245903015</v>
+        <v>2.91877222061157</v>
       </c>
       <c r="H1458" t="n">
         <v>79827</v>
@@ -42709,7 +42709,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1460" t="n">
-        <v>3.05348491668701</v>
+        <v>3.05348515510559</v>
       </c>
       <c r="H1460" t="n">
         <v>198569</v>
@@ -42738,7 +42738,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1461" t="n">
-        <v>3.09838938713074</v>
+        <v>3.09838914871216</v>
       </c>
       <c r="H1461" t="n">
         <v>72230</v>
@@ -42796,7 +42796,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1463" t="n">
-        <v>3.05348491668701</v>
+        <v>3.05348515510559</v>
       </c>
       <c r="H1463" t="n">
         <v>39306</v>
@@ -42883,7 +42883,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1466" t="n">
-        <v>2.96367692947388</v>
+        <v>2.9636766910553</v>
       </c>
       <c r="H1466" t="n">
         <v>73228</v>
@@ -42999,7 +42999,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1470" t="n">
-        <v>2.90979146957397</v>
+        <v>2.90979170799255</v>
       </c>
       <c r="H1470" t="n">
         <v>20781</v>
@@ -43028,7 +43028,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1471" t="n">
-        <v>2.94571495056152</v>
+        <v>2.94571471214294</v>
       </c>
       <c r="H1471" t="n">
         <v>10322</v>
@@ -43086,7 +43086,7 @@
         <v>3.49499988555908</v>
       </c>
       <c r="G1473" t="n">
-        <v>3.13880300521851</v>
+        <v>3.13880276679993</v>
       </c>
       <c r="H1473" t="n">
         <v>142449</v>
@@ -43144,7 +43144,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1475" t="n">
-        <v>3.09838938713074</v>
+        <v>3.09838914871216</v>
       </c>
       <c r="H1475" t="n">
         <v>27407</v>
@@ -43202,7 +43202,7 @@
         <v>3.49499988555908</v>
       </c>
       <c r="G1477" t="n">
-        <v>3.13880300521851</v>
+        <v>3.13880276679993</v>
       </c>
       <c r="H1477" t="n">
         <v>55323</v>
@@ -43231,7 +43231,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1478" t="n">
-        <v>3.12533164024353</v>
+        <v>3.12533187866211</v>
       </c>
       <c r="H1478" t="n">
         <v>50093</v>
@@ -43260,7 +43260,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1479" t="n">
-        <v>3.12533164024353</v>
+        <v>3.12533187866211</v>
       </c>
       <c r="H1479" t="n">
         <v>17551</v>
@@ -43289,7 +43289,7 @@
         <v>3.5</v>
       </c>
       <c r="G1480" t="n">
-        <v>3.1432933807373</v>
+        <v>3.14329314231873</v>
       </c>
       <c r="H1480" t="n">
         <v>57682</v>
@@ -43318,7 +43318,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1481" t="n">
-        <v>3.26902508735657</v>
+        <v>3.26902484893799</v>
       </c>
       <c r="H1481" t="n">
         <v>454970</v>
@@ -43376,7 +43376,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1483" t="n">
-        <v>3.22412085533142</v>
+        <v>3.22412061691284</v>
       </c>
       <c r="H1483" t="n">
         <v>45767</v>
@@ -43405,7 +43405,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1484" t="n">
-        <v>3.2331018447876</v>
+        <v>3.23310160636902</v>
       </c>
       <c r="H1484" t="n">
         <v>33548</v>
@@ -43463,7 +43463,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G1486" t="n">
-        <v>3.19268798828125</v>
+        <v>3.19268822669983</v>
       </c>
       <c r="H1486" t="n">
         <v>31620</v>
@@ -43492,7 +43492,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G1487" t="n">
-        <v>3.19268798828125</v>
+        <v>3.19268822669983</v>
       </c>
       <c r="H1487" t="n">
         <v>58891</v>
@@ -43550,7 +43550,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1489" t="n">
-        <v>3.2331018447876</v>
+        <v>3.23310160636902</v>
       </c>
       <c r="H1489" t="n">
         <v>64124</v>
@@ -43579,7 +43579,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1490" t="n">
-        <v>3.2331018447876</v>
+        <v>3.23310160636902</v>
       </c>
       <c r="H1490" t="n">
         <v>118491</v>
@@ -43608,7 +43608,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1491" t="n">
-        <v>3.2331018447876</v>
+        <v>3.23310160636902</v>
       </c>
       <c r="H1491" t="n">
         <v>47687</v>
@@ -43811,7 +43811,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1498" t="n">
-        <v>3.17921686172485</v>
+        <v>3.17921662330627</v>
       </c>
       <c r="H1498" t="n">
         <v>135978</v>
@@ -43869,7 +43869,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1500" t="n">
-        <v>3.09838938713074</v>
+        <v>3.09838914871216</v>
       </c>
       <c r="H1500" t="n">
         <v>105061</v>
@@ -43927,7 +43927,7 @@
         <v>3.54500007629395</v>
       </c>
       <c r="G1502" t="n">
-        <v>3.18370723724365</v>
+        <v>3.18370699882507</v>
       </c>
       <c r="H1502" t="n">
         <v>40339</v>
@@ -43985,7 +43985,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1504" t="n">
-        <v>3.11635065078735</v>
+        <v>3.11635088920593</v>
       </c>
       <c r="H1504" t="n">
         <v>79385</v>
@@ -44014,7 +44014,7 @@
         <v>3.5</v>
       </c>
       <c r="G1505" t="n">
-        <v>3.1432933807373</v>
+        <v>3.14329314231873</v>
       </c>
       <c r="H1505" t="n">
         <v>31724</v>
@@ -44333,7 +44333,7 @@
         <v>3.54500007629395</v>
       </c>
       <c r="G1516" t="n">
-        <v>3.18370723724365</v>
+        <v>3.18370699882507</v>
       </c>
       <c r="H1516" t="n">
         <v>37589</v>
@@ -44362,7 +44362,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1517" t="n">
-        <v>3.27800607681274</v>
+        <v>3.27800583839417</v>
       </c>
       <c r="H1517" t="n">
         <v>254428</v>
@@ -44391,7 +44391,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1518" t="n">
-        <v>3.27800607681274</v>
+        <v>3.27800583839417</v>
       </c>
       <c r="H1518" t="n">
         <v>105676</v>
@@ -44420,7 +44420,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1519" t="n">
-        <v>3.30494832992554</v>
+        <v>3.30494856834412</v>
       </c>
       <c r="H1519" t="n">
         <v>139095</v>
@@ -44478,7 +44478,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1521" t="n">
-        <v>3.27800607681274</v>
+        <v>3.27800583839417</v>
       </c>
       <c r="H1521" t="n">
         <v>35490</v>
@@ -44507,7 +44507,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1522" t="n">
-        <v>3.27800607681274</v>
+        <v>3.27800583839417</v>
       </c>
       <c r="H1522" t="n">
         <v>26645</v>
@@ -44565,7 +44565,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1524" t="n">
-        <v>3.26902508735657</v>
+        <v>3.26902484893799</v>
       </c>
       <c r="H1524" t="n">
         <v>25489</v>
@@ -44594,7 +44594,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1525" t="n">
-        <v>3.30494832992554</v>
+        <v>3.30494856834412</v>
       </c>
       <c r="H1525" t="n">
         <v>61541</v>
@@ -44623,7 +44623,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G1526" t="n">
-        <v>3.27351570129395</v>
+        <v>3.27351546287537</v>
       </c>
       <c r="H1526" t="n">
         <v>105095</v>
@@ -44652,7 +44652,7 @@
         <v>3.68499994277954</v>
       </c>
       <c r="G1527" t="n">
-        <v>3.30943870544434</v>
+        <v>3.30943846702576</v>
       </c>
       <c r="H1527" t="n">
         <v>16814</v>
@@ -44681,7 +44681,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1528" t="n">
-        <v>3.27800607681274</v>
+        <v>3.27800583839417</v>
       </c>
       <c r="H1528" t="n">
         <v>27468</v>
@@ -44710,7 +44710,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1529" t="n">
-        <v>3.26902508735657</v>
+        <v>3.26902484893799</v>
       </c>
       <c r="H1529" t="n">
         <v>17180</v>
@@ -44739,7 +44739,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1530" t="n">
-        <v>3.2331018447876</v>
+        <v>3.23310160636902</v>
       </c>
       <c r="H1530" t="n">
         <v>21904</v>
@@ -44768,7 +44768,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1531" t="n">
-        <v>3.17921686172485</v>
+        <v>3.17921662330627</v>
       </c>
       <c r="H1531" t="n">
         <v>34503</v>
@@ -44913,7 +44913,7 @@
         <v>3.42499995231628</v>
       </c>
       <c r="G1536" t="n">
-        <v>3.07593679428101</v>
+        <v>3.07593727111816</v>
       </c>
       <c r="H1536" t="n">
         <v>35737</v>
@@ -44942,7 +44942,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1537" t="n">
-        <v>3.09838938713074</v>
+        <v>3.09838914871216</v>
       </c>
       <c r="H1537" t="n">
         <v>31991</v>
@@ -45000,7 +45000,7 @@
         <v>3.4449999332428</v>
       </c>
       <c r="G1539" t="n">
-        <v>3.09389877319336</v>
+        <v>3.09389853477478</v>
       </c>
       <c r="H1539" t="n">
         <v>34077</v>
@@ -45116,7 +45116,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1543" t="n">
-        <v>3.00858092308044</v>
+        <v>3.00858068466187</v>
       </c>
       <c r="H1543" t="n">
         <v>51524</v>
@@ -45290,7 +45290,7 @@
         <v>3.5</v>
       </c>
       <c r="G1549" t="n">
-        <v>3.1432933807373</v>
+        <v>3.14329314231873</v>
       </c>
       <c r="H1549" t="n">
         <v>14524</v>
@@ -45319,7 +45319,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1550" t="n">
-        <v>3.11635065078735</v>
+        <v>3.11635088920593</v>
       </c>
       <c r="H1550" t="n">
         <v>27307</v>
@@ -45377,7 +45377,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1552" t="n">
-        <v>2.98163819313049</v>
+        <v>2.98163843154907</v>
       </c>
       <c r="H1552" t="n">
         <v>39306</v>
@@ -45435,7 +45435,7 @@
         <v>3.36500000953674</v>
       </c>
       <c r="G1554" t="n">
-        <v>3.02205228805542</v>
+        <v>3.02205204963684</v>
       </c>
       <c r="H1554" t="n">
         <v>48732</v>
@@ -45493,7 +45493,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1556" t="n">
-        <v>3.00858092308044</v>
+        <v>3.00858068466187</v>
       </c>
       <c r="H1556" t="n">
         <v>100390</v>
@@ -45522,7 +45522,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1557" t="n">
-        <v>2.93673396110535</v>
+        <v>2.93673419952393</v>
       </c>
       <c r="H1557" t="n">
         <v>62187</v>
@@ -45551,7 +45551,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1558" t="n">
-        <v>3.05348491668701</v>
+        <v>3.05348515510559</v>
       </c>
       <c r="H1558" t="n">
         <v>32557</v>
@@ -45638,7 +45638,7 @@
         <v>3.34500002861023</v>
       </c>
       <c r="G1561" t="n">
-        <v>3.00409054756165</v>
+        <v>3.00409030914307</v>
       </c>
       <c r="H1561" t="n">
         <v>13868</v>
@@ -45667,7 +45667,7 @@
         <v>3.25500011444092</v>
       </c>
       <c r="G1562" t="n">
-        <v>2.92326307296753</v>
+        <v>2.92326283454895</v>
       </c>
       <c r="H1562" t="n">
         <v>56513</v>
@@ -45696,7 +45696,7 @@
         <v>3.25</v>
       </c>
       <c r="G1563" t="n">
-        <v>2.91877245903015</v>
+        <v>2.91877222061157</v>
       </c>
       <c r="H1563" t="n">
         <v>50830</v>
@@ -45754,7 +45754,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1565" t="n">
-        <v>2.74813675880432</v>
+        <v>2.74813628196716</v>
       </c>
       <c r="H1565" t="n">
         <v>89981</v>
@@ -45783,7 +45783,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1566" t="n">
-        <v>2.76609778404236</v>
+        <v>2.76609802246094</v>
       </c>
       <c r="H1566" t="n">
         <v>31311</v>
@@ -45899,7 +45899,7 @@
         <v>2.95499992370605</v>
       </c>
       <c r="G1570" t="n">
-        <v>2.65383791923523</v>
+        <v>2.65383744239807</v>
       </c>
       <c r="H1570" t="n">
         <v>22678</v>
@@ -45957,7 +45957,7 @@
         <v>2.88499999046326</v>
       </c>
       <c r="G1572" t="n">
-        <v>2.59097170829773</v>
+        <v>2.59097194671631</v>
       </c>
       <c r="H1572" t="n">
         <v>89659</v>
@@ -46044,7 +46044,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1575" t="n">
-        <v>2.55055785179138</v>
+        <v>2.55055809020996</v>
       </c>
       <c r="H1575" t="n">
         <v>38829</v>
@@ -46073,7 +46073,7 @@
         <v>2.9449999332428</v>
       </c>
       <c r="G1576" t="n">
-        <v>2.64485669136047</v>
+        <v>2.64485692977905</v>
       </c>
       <c r="H1576" t="n">
         <v>49985</v>
@@ -46102,7 +46102,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1577" t="n">
-        <v>2.6762900352478</v>
+        <v>2.67628979682922</v>
       </c>
       <c r="H1577" t="n">
         <v>16145</v>
@@ -46189,7 +46189,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1580" t="n">
-        <v>2.76609778404236</v>
+        <v>2.76609802246094</v>
       </c>
       <c r="H1580" t="n">
         <v>27781</v>
@@ -46218,7 +46218,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G1581" t="n">
-        <v>2.78855037689209</v>
+        <v>2.78855013847351</v>
       </c>
       <c r="H1581" t="n">
         <v>22786</v>
@@ -46305,7 +46305,7 @@
         <v>3.15499997138977</v>
       </c>
       <c r="G1584" t="n">
-        <v>2.83345437049866</v>
+        <v>2.83345413208008</v>
       </c>
       <c r="H1584" t="n">
         <v>15092</v>
@@ -46334,7 +46334,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1585" t="n">
-        <v>2.75711727142334</v>
+        <v>2.75711750984192</v>
       </c>
       <c r="H1585" t="n">
         <v>11617</v>
@@ -46421,7 +46421,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G1588" t="n">
-        <v>2.8783586025238</v>
+        <v>2.87835836410522</v>
       </c>
       <c r="H1588" t="n">
         <v>64619</v>
@@ -46450,7 +46450,7 @@
         <v>3.14499998092651</v>
       </c>
       <c r="G1589" t="n">
-        <v>2.82447338104248</v>
+        <v>2.82447361946106</v>
       </c>
       <c r="H1589" t="n">
         <v>13234</v>
@@ -46595,7 +46595,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G1594" t="n">
-        <v>2.76160764694214</v>
+        <v>2.76160788536072</v>
       </c>
       <c r="H1594" t="n">
         <v>27786</v>
@@ -46653,7 +46653,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1596" t="n">
-        <v>2.87386846542358</v>
+        <v>2.873868227005</v>
       </c>
       <c r="H1596" t="n">
         <v>37503</v>
@@ -46711,7 +46711,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1598" t="n">
-        <v>2.77507877349854</v>
+        <v>2.77507901191711</v>
       </c>
       <c r="H1598" t="n">
         <v>9189</v>
@@ -46769,7 +46769,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1600" t="n">
-        <v>2.96367692947388</v>
+        <v>2.9636766910553</v>
       </c>
       <c r="H1600" t="n">
         <v>47531</v>
@@ -47001,7 +47001,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1608" t="n">
-        <v>3.05348491668701</v>
+        <v>3.05348515510559</v>
       </c>
       <c r="H1608" t="n">
         <v>124969</v>
@@ -47030,7 +47030,7 @@
         <v>3.36500000953674</v>
       </c>
       <c r="G1609" t="n">
-        <v>3.02205228805542</v>
+        <v>3.02205204963684</v>
       </c>
       <c r="H1609" t="n">
         <v>74971</v>
@@ -47175,7 +47175,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1614" t="n">
-        <v>2.74813675880432</v>
+        <v>2.74813628196716</v>
       </c>
       <c r="H1614" t="n">
         <v>54704</v>
@@ -47204,7 +47204,7 @@
         <v>2.95499992370605</v>
       </c>
       <c r="G1615" t="n">
-        <v>2.65383791923523</v>
+        <v>2.65383744239807</v>
       </c>
       <c r="H1615" t="n">
         <v>23742</v>
@@ -47262,7 +47262,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1617" t="n">
-        <v>2.77507877349854</v>
+        <v>2.77507901191711</v>
       </c>
       <c r="H1617" t="n">
         <v>23946</v>
@@ -47320,7 +47320,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1619" t="n">
-        <v>2.86488747596741</v>
+        <v>2.86488723754883</v>
       </c>
       <c r="H1619" t="n">
         <v>25473</v>
@@ -47407,7 +47407,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G1622" t="n">
-        <v>2.91428160667419</v>
+        <v>2.91428184509277</v>
       </c>
       <c r="H1622" t="n">
         <v>9595</v>
@@ -47465,7 +47465,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1624" t="n">
-        <v>2.87386846542358</v>
+        <v>2.873868227005</v>
       </c>
       <c r="H1624" t="n">
         <v>15992</v>
@@ -47523,7 +47523,7 @@
         <v>3.11500000953674</v>
       </c>
       <c r="G1626" t="n">
-        <v>2.79753112792969</v>
+        <v>2.79753136634827</v>
       </c>
       <c r="H1626" t="n">
         <v>18880</v>
@@ -47581,7 +47581,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1628" t="n">
-        <v>2.77507877349854</v>
+        <v>2.77507901191711</v>
       </c>
       <c r="H1628" t="n">
         <v>37767</v>
@@ -47668,7 +47668,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1631" t="n">
-        <v>2.74813675880432</v>
+        <v>2.74813628196716</v>
       </c>
       <c r="H1631" t="n">
         <v>33470</v>
@@ -47726,7 +47726,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G1633" t="n">
-        <v>2.74364614486694</v>
+        <v>2.74364590644836</v>
       </c>
       <c r="H1633" t="n">
         <v>2304</v>
@@ -47755,7 +47755,7 @@
         <v>3.02500009536743</v>
       </c>
       <c r="G1634" t="n">
-        <v>2.71670365333557</v>
+        <v>2.71670389175415</v>
       </c>
       <c r="H1634" t="n">
         <v>25006</v>
@@ -47784,7 +47784,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1635" t="n">
-        <v>2.79304075241089</v>
+        <v>2.79304051399231</v>
       </c>
       <c r="H1635" t="n">
         <v>84860</v>
@@ -47842,7 +47842,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1637" t="n">
-        <v>2.87386846542358</v>
+        <v>2.873868227005</v>
       </c>
       <c r="H1637" t="n">
         <v>19834</v>
@@ -47900,7 +47900,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1639" t="n">
-        <v>2.68527030944824</v>
+        <v>2.6852707862854</v>
       </c>
       <c r="H1639" t="n">
         <v>47785</v>
@@ -47987,7 +47987,7 @@
         <v>2.98499989509583</v>
       </c>
       <c r="G1642" t="n">
-        <v>2.68078017234802</v>
+        <v>2.68077993392944</v>
       </c>
       <c r="H1642" t="n">
         <v>11386</v>
@@ -48045,7 +48045,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1644" t="n">
-        <v>2.6762900352478</v>
+        <v>2.67628979682922</v>
       </c>
       <c r="H1644" t="n">
         <v>17398</v>
@@ -48103,7 +48103,7 @@
         <v>2.98499989509583</v>
       </c>
       <c r="G1646" t="n">
-        <v>2.68078017234802</v>
+        <v>2.68077993392944</v>
       </c>
       <c r="H1646" t="n">
         <v>19530</v>
@@ -48161,7 +48161,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1648" t="n">
-        <v>2.55953860282898</v>
+        <v>2.55953884124756</v>
       </c>
       <c r="H1648" t="n">
         <v>10238</v>
@@ -48190,7 +48190,7 @@
         <v>2.79500007629395</v>
       </c>
       <c r="G1649" t="n">
-        <v>2.51014423370361</v>
+        <v>2.51014447212219</v>
       </c>
       <c r="H1649" t="n">
         <v>41770</v>
@@ -48248,7 +48248,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G1651" t="n">
-        <v>2.52810621261597</v>
+        <v>2.52810597419739</v>
       </c>
       <c r="H1651" t="n">
         <v>47327</v>
@@ -48277,7 +48277,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G1652" t="n">
-        <v>2.52361559867859</v>
+        <v>2.52361536026001</v>
       </c>
       <c r="H1652" t="n">
         <v>28358</v>
@@ -48393,7 +48393,7 @@
         <v>2.71499991416931</v>
       </c>
       <c r="G1656" t="n">
-        <v>2.43829774856567</v>
+        <v>2.43829751014709</v>
       </c>
       <c r="H1656" t="n">
         <v>18378</v>
@@ -48451,7 +48451,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G1658" t="n">
-        <v>2.52810621261597</v>
+        <v>2.52810597419739</v>
       </c>
       <c r="H1658" t="n">
         <v>9524</v>
@@ -48538,7 +48538,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1661" t="n">
-        <v>2.56851959228516</v>
+        <v>2.56851935386658</v>
       </c>
       <c r="H1661" t="n">
         <v>7518</v>
@@ -48567,7 +48567,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1662" t="n">
-        <v>2.53259634971619</v>
+        <v>2.53259658813477</v>
       </c>
       <c r="H1662" t="n">
         <v>19482</v>
@@ -48596,7 +48596,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1663" t="n">
-        <v>2.53259634971619</v>
+        <v>2.53259658813477</v>
       </c>
       <c r="H1663" t="n">
         <v>5616</v>
@@ -48625,7 +48625,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1664" t="n">
-        <v>2.53259634971619</v>
+        <v>2.53259658813477</v>
       </c>
       <c r="H1664" t="n">
         <v>6368</v>
@@ -48654,7 +48654,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1665" t="n">
-        <v>2.55055785179138</v>
+        <v>2.55055809020996</v>
       </c>
       <c r="H1665" t="n">
         <v>2435</v>
@@ -48799,7 +48799,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1670" t="n">
-        <v>2.55055785179138</v>
+        <v>2.55055809020996</v>
       </c>
       <c r="H1670" t="n">
         <v>21085</v>
@@ -48828,7 +48828,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1671" t="n">
-        <v>2.53259634971619</v>
+        <v>2.53259658813477</v>
       </c>
       <c r="H1671" t="n">
         <v>5662</v>
@@ -48857,7 +48857,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G1672" t="n">
-        <v>2.52361559867859</v>
+        <v>2.52361536026001</v>
       </c>
       <c r="H1672" t="n">
         <v>3846</v>
@@ -48886,7 +48886,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1673" t="n">
-        <v>2.51463460922241</v>
+        <v>2.51463437080383</v>
       </c>
       <c r="H1673" t="n">
         <v>23788</v>
@@ -48915,7 +48915,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1674" t="n">
-        <v>2.55055785179138</v>
+        <v>2.55055809020996</v>
       </c>
       <c r="H1674" t="n">
         <v>18776</v>
@@ -48944,7 +48944,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G1675" t="n">
-        <v>2.54606747627258</v>
+        <v>2.54606771469116</v>
       </c>
       <c r="H1675" t="n">
         <v>2024</v>
@@ -49031,7 +49031,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G1678" t="n">
-        <v>2.61342406272888</v>
+        <v>2.6134238243103</v>
       </c>
       <c r="H1678" t="n">
         <v>18804</v>
@@ -49089,7 +49089,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1680" t="n">
-        <v>2.55953860282898</v>
+        <v>2.55953884124756</v>
       </c>
       <c r="H1680" t="n">
         <v>4603</v>
@@ -49118,7 +49118,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1681" t="n">
-        <v>2.55953860282898</v>
+        <v>2.55953884124756</v>
       </c>
       <c r="H1681" t="n">
         <v>3829</v>
@@ -49147,7 +49147,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1682" t="n">
-        <v>2.56851959228516</v>
+        <v>2.56851935386658</v>
       </c>
       <c r="H1682" t="n">
         <v>2200</v>
@@ -49205,7 +49205,7 @@
         <v>2.88499999046326</v>
       </c>
       <c r="G1684" t="n">
-        <v>2.59097170829773</v>
+        <v>2.59097194671631</v>
       </c>
       <c r="H1684" t="n">
         <v>28688</v>
@@ -49292,7 +49292,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1687" t="n">
-        <v>2.76609778404236</v>
+        <v>2.76609802246094</v>
       </c>
       <c r="H1687" t="n">
         <v>73107</v>
@@ -49408,7 +49408,7 @@
         <v>3</v>
       </c>
       <c r="G1691" t="n">
-        <v>2.69425129890442</v>
+        <v>2.694251537323</v>
       </c>
       <c r="H1691" t="n">
         <v>2780</v>
@@ -49466,7 +49466,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G1693" t="n">
-        <v>2.74364614486694</v>
+        <v>2.74364590644836</v>
       </c>
       <c r="H1693" t="n">
         <v>28500</v>
@@ -49524,7 +49524,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G1695" t="n">
-        <v>2.74364614486694</v>
+        <v>2.74364590644836</v>
       </c>
       <c r="H1695" t="n">
         <v>10635</v>
@@ -49553,7 +49553,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1696" t="n">
-        <v>2.68527030944824</v>
+        <v>2.6852707862854</v>
       </c>
       <c r="H1696" t="n">
         <v>32745</v>
@@ -49785,7 +49785,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1704" t="n">
-        <v>2.55953860282898</v>
+        <v>2.55953884124756</v>
       </c>
       <c r="H1704" t="n">
         <v>6628</v>
@@ -49814,7 +49814,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1705" t="n">
-        <v>2.55055785179138</v>
+        <v>2.55055809020996</v>
       </c>
       <c r="H1705" t="n">
         <v>16246</v>
@@ -49930,7 +49930,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1709" t="n">
-        <v>2.4248263835907</v>
+        <v>2.42482614517212</v>
       </c>
       <c r="H1709" t="n">
         <v>31942</v>
@@ -49959,7 +49959,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1710" t="n">
-        <v>2.37992238998413</v>
+        <v>2.37992215156555</v>
       </c>
       <c r="H1710" t="n">
         <v>5169</v>
@@ -50017,7 +50017,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G1712" t="n">
-        <v>2.29011368751526</v>
+        <v>2.29011344909668</v>
       </c>
       <c r="H1712" t="n">
         <v>27274</v>
@@ -50046,7 +50046,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1713" t="n">
-        <v>2.18234348297119</v>
+        <v>2.18234395980835</v>
       </c>
       <c r="H1713" t="n">
         <v>27891</v>
@@ -50104,7 +50104,7 @@
         <v>2.42499995231628</v>
       </c>
       <c r="G1715" t="n">
-        <v>2.17785334587097</v>
+        <v>2.17785310745239</v>
       </c>
       <c r="H1715" t="n">
         <v>5758</v>
@@ -50191,7 +50191,7 @@
         <v>2.40499997138977</v>
       </c>
       <c r="G1718" t="n">
-        <v>2.15989136695862</v>
+        <v>2.1598916053772</v>
       </c>
       <c r="H1718" t="n">
         <v>9107</v>
@@ -50220,7 +50220,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1719" t="n">
-        <v>2.15528607368469</v>
+        <v>2.15528583526611</v>
       </c>
       <c r="H1719" t="n">
         <v>22889</v>
@@ -50365,7 +50365,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1724" t="n">
-        <v>2.10923290252686</v>
+        <v>2.10923314094543</v>
       </c>
       <c r="H1724" t="n">
         <v>5267</v>
@@ -50626,7 +50626,7 @@
         <v>2.58500003814697</v>
       </c>
       <c r="G1733" t="n">
-        <v>2.38094687461853</v>
+        <v>2.38094639778137</v>
       </c>
       <c r="H1733" t="n">
         <v>26643</v>
@@ -50655,7 +50655,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1734" t="n">
-        <v>2.37634110450745</v>
+        <v>2.37634134292603</v>
       </c>
       <c r="H1734" t="n">
         <v>31856</v>
@@ -50713,7 +50713,7 @@
         <v>2.58500003814697</v>
       </c>
       <c r="G1736" t="n">
-        <v>2.38094687461853</v>
+        <v>2.38094639778137</v>
       </c>
       <c r="H1736" t="n">
         <v>12717</v>
@@ -50742,7 +50742,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G1737" t="n">
-        <v>2.42239451408386</v>
+        <v>2.42239427566528</v>
       </c>
       <c r="H1737" t="n">
         <v>17895</v>
@@ -50800,7 +50800,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1739" t="n">
-        <v>2.47765803337097</v>
+        <v>2.47765827178955</v>
       </c>
       <c r="H1739" t="n">
         <v>10139</v>
@@ -50829,7 +50829,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G1740" t="n">
-        <v>2.40397310256958</v>
+        <v>2.403972864151</v>
       </c>
       <c r="H1740" t="n">
         <v>68059</v>
@@ -50887,7 +50887,7 @@
         <v>2.56500005722046</v>
       </c>
       <c r="G1742" t="n">
-        <v>2.36252546310425</v>
+        <v>2.36252522468567</v>
       </c>
       <c r="H1742" t="n">
         <v>15189</v>
@@ -51003,7 +51003,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G1746" t="n">
-        <v>2.45923662185669</v>
+        <v>2.45923686027527</v>
       </c>
       <c r="H1746" t="n">
         <v>11854</v>
@@ -51032,7 +51032,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1747" t="n">
-        <v>2.47765803337097</v>
+        <v>2.47765827178955</v>
       </c>
       <c r="H1747" t="n">
         <v>8688</v>
@@ -51496,7 +51496,7 @@
         <v>2.75500011444092</v>
       </c>
       <c r="G1763" t="n">
-        <v>2.53752708435059</v>
+        <v>2.53752732276917</v>
       </c>
       <c r="H1763" t="n">
         <v>33748</v>
@@ -51554,7 +51554,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1765" t="n">
-        <v>2.52371144294739</v>
+        <v>2.52371096611023</v>
       </c>
       <c r="H1765" t="n">
         <v>15304</v>
@@ -51583,7 +51583,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1766" t="n">
-        <v>2.52371144294739</v>
+        <v>2.52371096611023</v>
       </c>
       <c r="H1766" t="n">
         <v>1876</v>
@@ -51641,7 +51641,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1768" t="n">
-        <v>2.49607920646667</v>
+        <v>2.49607944488525</v>
       </c>
       <c r="H1768" t="n">
         <v>6930</v>
@@ -51670,7 +51670,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1769" t="n">
-        <v>2.52371144294739</v>
+        <v>2.52371096611023</v>
       </c>
       <c r="H1769" t="n">
         <v>28615</v>
@@ -51699,7 +51699,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1770" t="n">
-        <v>2.47765803337097</v>
+        <v>2.47765827178955</v>
       </c>
       <c r="H1770" t="n">
         <v>99660</v>
@@ -51728,7 +51728,7 @@
         <v>2.72499990463257</v>
       </c>
       <c r="G1771" t="n">
-        <v>2.50989532470703</v>
+        <v>2.50989508628845</v>
       </c>
       <c r="H1771" t="n">
         <v>29944</v>
@@ -51757,7 +51757,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1772" t="n">
-        <v>2.50529003143311</v>
+        <v>2.50529026985168</v>
       </c>
       <c r="H1772" t="n">
         <v>5533</v>
@@ -51786,7 +51786,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1773" t="n">
-        <v>2.50529003143311</v>
+        <v>2.50529026985168</v>
       </c>
       <c r="H1773" t="n">
         <v>20515</v>
@@ -51815,7 +51815,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1774" t="n">
-        <v>2.52371144294739</v>
+        <v>2.52371096611023</v>
       </c>
       <c r="H1774" t="n">
         <v>9413</v>
@@ -51844,7 +51844,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1775" t="n">
-        <v>2.52371144294739</v>
+        <v>2.52371096611023</v>
       </c>
       <c r="H1775" t="n">
         <v>54098</v>
@@ -51931,7 +51931,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G1778" t="n">
-        <v>2.59279108047485</v>
+        <v>2.59279084205627</v>
       </c>
       <c r="H1778" t="n">
         <v>8933</v>
@@ -52105,7 +52105,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1784" t="n">
-        <v>2.78160881996155</v>
+        <v>2.78160858154297</v>
       </c>
       <c r="H1784" t="n">
         <v>18714</v>
@@ -52221,7 +52221,7 @@
         <v>3.06500005722046</v>
       </c>
       <c r="G1788" t="n">
-        <v>2.82305645942688</v>
+        <v>2.82305669784546</v>
       </c>
       <c r="H1788" t="n">
         <v>88822</v>
@@ -52279,7 +52279,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1790" t="n">
-        <v>2.94740009307861</v>
+        <v>2.94739985466003</v>
       </c>
       <c r="H1790" t="n">
         <v>44078</v>
@@ -52366,7 +52366,7 @@
         <v>3.09500002861023</v>
       </c>
       <c r="G1793" t="n">
-        <v>2.85068845748901</v>
+        <v>2.85068821907043</v>
       </c>
       <c r="H1793" t="n">
         <v>28822</v>
@@ -52395,7 +52395,7 @@
         <v>3.09500002861023</v>
       </c>
       <c r="G1794" t="n">
-        <v>2.85068845748901</v>
+        <v>2.85068821907043</v>
       </c>
       <c r="H1794" t="n">
         <v>16747</v>
@@ -52424,7 +52424,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1795" t="n">
-        <v>2.83687210083008</v>
+        <v>2.83687233924866</v>
       </c>
       <c r="H1795" t="n">
         <v>83919</v>
@@ -52453,7 +52453,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1796" t="n">
-        <v>2.84608292579651</v>
+        <v>2.84608316421509</v>
       </c>
       <c r="H1796" t="n">
         <v>31735</v>
@@ -52482,7 +52482,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G1797" t="n">
-        <v>2.84147787094116</v>
+        <v>2.84147763252258</v>
       </c>
       <c r="H1797" t="n">
         <v>22313</v>
@@ -52569,7 +52569,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1800" t="n">
-        <v>2.78160881996155</v>
+        <v>2.78160858154297</v>
       </c>
       <c r="H1800" t="n">
         <v>39074</v>
@@ -52743,7 +52743,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1806" t="n">
-        <v>2.71713423728943</v>
+        <v>2.71713447570801</v>
       </c>
       <c r="H1806" t="n">
         <v>40305</v>
@@ -52772,7 +52772,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G1807" t="n">
-        <v>2.6987133026123</v>
+        <v>2.69871306419373</v>
       </c>
       <c r="H1807" t="n">
         <v>22906</v>
@@ -52801,7 +52801,7 @@
         <v>2.875</v>
       </c>
       <c r="G1808" t="n">
-        <v>2.64805459976196</v>
+        <v>2.64805483818054</v>
       </c>
       <c r="H1808" t="n">
         <v>74121</v>
@@ -52830,7 +52830,7 @@
         <v>2.875</v>
       </c>
       <c r="G1809" t="n">
-        <v>2.64805459976196</v>
+        <v>2.64805483818054</v>
       </c>
       <c r="H1809" t="n">
         <v>32625</v>
@@ -52888,7 +52888,7 @@
         <v>2.875</v>
       </c>
       <c r="G1811" t="n">
-        <v>2.64805459976196</v>
+        <v>2.64805483818054</v>
       </c>
       <c r="H1811" t="n">
         <v>9680</v>
@@ -52917,7 +52917,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G1812" t="n">
-        <v>2.64344930648804</v>
+        <v>2.64344906806946</v>
       </c>
       <c r="H1812" t="n">
         <v>58962</v>
@@ -52946,7 +52946,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1813" t="n">
-        <v>2.62502789497375</v>
+        <v>2.62502813339233</v>
       </c>
       <c r="H1813" t="n">
         <v>148155</v>
@@ -52975,7 +52975,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1814" t="n">
-        <v>2.6158173084259</v>
+        <v>2.61581754684448</v>
       </c>
       <c r="H1814" t="n">
         <v>115139</v>
@@ -53033,7 +53033,7 @@
         <v>2.95499992370605</v>
       </c>
       <c r="G1816" t="n">
-        <v>2.72173976898193</v>
+        <v>2.72173929214478</v>
       </c>
       <c r="H1816" t="n">
         <v>147185</v>
@@ -53120,7 +53120,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G1819" t="n">
-        <v>2.81384587287903</v>
+        <v>2.81384611129761</v>
       </c>
       <c r="H1819" t="n">
         <v>49528</v>
@@ -53178,7 +53178,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1821" t="n">
-        <v>2.78160881996155</v>
+        <v>2.78160858154297</v>
       </c>
       <c r="H1821" t="n">
         <v>13158</v>
@@ -53236,7 +53236,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1823" t="n">
-        <v>2.68950247764587</v>
+        <v>2.68950271606445</v>
       </c>
       <c r="H1823" t="n">
         <v>109020</v>
@@ -53323,7 +53323,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1826" t="n">
-        <v>2.68950247764587</v>
+        <v>2.68950271606445</v>
       </c>
       <c r="H1826" t="n">
         <v>6444</v>
@@ -53381,7 +53381,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1828" t="n">
-        <v>2.68950247764587</v>
+        <v>2.68950271606445</v>
       </c>
       <c r="H1828" t="n">
         <v>9659</v>
@@ -53497,7 +53497,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G1832" t="n">
-        <v>2.6987133026123</v>
+        <v>2.69871306419373</v>
       </c>
       <c r="H1832" t="n">
         <v>15793</v>
@@ -53584,7 +53584,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1835" t="n">
-        <v>2.6158173084259</v>
+        <v>2.61581754684448</v>
       </c>
       <c r="H1835" t="n">
         <v>21353</v>
@@ -53613,7 +53613,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1836" t="n">
-        <v>2.63423848152161</v>
+        <v>2.63423871994019</v>
       </c>
       <c r="H1836" t="n">
         <v>31119</v>
@@ -53700,7 +53700,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G1839" t="n">
-        <v>2.6987133026123</v>
+        <v>2.69871306419373</v>
       </c>
       <c r="H1839" t="n">
         <v>17212</v>
@@ -53729,7 +53729,7 @@
         <v>2.91499996185303</v>
       </c>
       <c r="G1840" t="n">
-        <v>2.68489694595337</v>
+        <v>2.68489718437195</v>
       </c>
       <c r="H1840" t="n">
         <v>5968</v>
@@ -53758,7 +53758,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1841" t="n">
-        <v>2.71713423728943</v>
+        <v>2.71713447570801</v>
       </c>
       <c r="H1841" t="n">
         <v>21076</v>
@@ -53816,7 +53816,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1843" t="n">
-        <v>2.65266013145447</v>
+        <v>2.65265989303589</v>
       </c>
       <c r="H1843" t="n">
         <v>13495</v>
@@ -53845,7 +53845,7 @@
         <v>2.875</v>
       </c>
       <c r="G1844" t="n">
-        <v>2.64805459976196</v>
+        <v>2.64805483818054</v>
       </c>
       <c r="H1844" t="n">
         <v>3567</v>
@@ -53874,7 +53874,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1845" t="n">
-        <v>2.63423848152161</v>
+        <v>2.63423871994019</v>
       </c>
       <c r="H1845" t="n">
         <v>12759</v>
@@ -53932,7 +53932,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1847" t="n">
-        <v>2.6158173084259</v>
+        <v>2.61581754684448</v>
       </c>
       <c r="H1847" t="n">
         <v>22287</v>
@@ -53961,7 +53961,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1848" t="n">
-        <v>2.6158173084259</v>
+        <v>2.61581754684448</v>
       </c>
       <c r="H1848" t="n">
         <v>19641</v>
@@ -54019,7 +54019,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1850" t="n">
-        <v>2.6158173084259</v>
+        <v>2.61581754684448</v>
       </c>
       <c r="H1850" t="n">
         <v>10036</v>
@@ -54048,7 +54048,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1851" t="n">
-        <v>2.63423848152161</v>
+        <v>2.63423871994019</v>
       </c>
       <c r="H1851" t="n">
         <v>9771</v>
@@ -54077,7 +54077,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1852" t="n">
-        <v>2.6158173084259</v>
+        <v>2.61581754684448</v>
       </c>
       <c r="H1852" t="n">
         <v>3037</v>
@@ -54135,7 +54135,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1854" t="n">
-        <v>2.5789749622345</v>
+        <v>2.57897472381592</v>
       </c>
       <c r="H1854" t="n">
         <v>2376</v>
@@ -54164,7 +54164,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1855" t="n">
-        <v>2.5789749622345</v>
+        <v>2.57897472381592</v>
       </c>
       <c r="H1855" t="n">
         <v>15183</v>
@@ -54222,7 +54222,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.64344930648804</v>
+        <v>2.64344906806946</v>
       </c>
       <c r="H1857" t="n">
         <v>25025</v>
@@ -54251,7 +54251,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.64344930648804</v>
+        <v>2.64344906806946</v>
       </c>
       <c r="H1858" t="n">
         <v>9031</v>
@@ -54309,7 +54309,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.6158173084259</v>
+        <v>2.61581754684448</v>
       </c>
       <c r="H1860" t="n">
         <v>22309</v>
@@ -54396,7 +54396,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.5789749622345</v>
+        <v>2.57897472381592</v>
       </c>
       <c r="H1863" t="n">
         <v>15836</v>
@@ -54570,7 +54570,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.45923662185669</v>
+        <v>2.45923686027527</v>
       </c>
       <c r="H1869" t="n">
         <v>281162</v>
@@ -54599,7 +54599,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.50529003143311</v>
+        <v>2.50529026985168</v>
       </c>
       <c r="H1870" t="n">
         <v>10792</v>
@@ -54744,7 +54744,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.52371144294739</v>
+        <v>2.52371096611023</v>
       </c>
       <c r="H1875" t="n">
         <v>18900</v>
@@ -54773,7 +54773,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.49607920646667</v>
+        <v>2.49607944488525</v>
       </c>
       <c r="H1876" t="n">
         <v>17893</v>
@@ -54802,7 +54802,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.50529003143311</v>
+        <v>2.50529026985168</v>
       </c>
       <c r="H1877" t="n">
         <v>4167</v>
@@ -54889,7 +54889,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.45923662185669</v>
+        <v>2.45923686027527</v>
       </c>
       <c r="H1880" t="n">
         <v>11534</v>
@@ -54918,7 +54918,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.45923662185669</v>
+        <v>2.45923686027527</v>
       </c>
       <c r="H1881" t="n">
         <v>12393</v>
@@ -54947,7 +54947,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.45923662185669</v>
+        <v>2.45923686027527</v>
       </c>
       <c r="H1882" t="n">
         <v>33920</v>
@@ -54976,7 +54976,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.45923662185669</v>
+        <v>2.45923686027527</v>
       </c>
       <c r="H1883" t="n">
         <v>12708</v>
@@ -55005,7 +55005,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.44081592559814</v>
+        <v>2.44081568717957</v>
       </c>
       <c r="H1884" t="n">
         <v>11047</v>
@@ -55063,7 +55063,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.47765803337097</v>
+        <v>2.47765827178955</v>
       </c>
       <c r="H1886" t="n">
         <v>18267</v>
@@ -55179,7 +55179,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.44081592559814</v>
+        <v>2.44081568717957</v>
       </c>
       <c r="H1890" t="n">
         <v>12913</v>
@@ -55208,7 +55208,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.44081592559814</v>
+        <v>2.44081568717957</v>
       </c>
       <c r="H1891" t="n">
         <v>5430</v>
@@ -55266,7 +55266,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.44081592559814</v>
+        <v>2.44081568717957</v>
       </c>
       <c r="H1893" t="n">
         <v>8789</v>
@@ -55324,7 +55324,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.44081592559814</v>
+        <v>2.44081568717957</v>
       </c>
       <c r="H1895" t="n">
         <v>10322</v>
@@ -55353,7 +55353,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.45923662185669</v>
+        <v>2.45923686027527</v>
       </c>
       <c r="H1896" t="n">
         <v>13700</v>
@@ -55382,7 +55382,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.45923662185669</v>
+        <v>2.45923686027527</v>
       </c>
       <c r="H1897" t="n">
         <v>20267</v>
@@ -55440,7 +55440,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.49607920646667</v>
+        <v>2.49607944488525</v>
       </c>
       <c r="H1899" t="n">
         <v>22741</v>
@@ -55469,7 +55469,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.50529003143311</v>
+        <v>2.50529026985168</v>
       </c>
       <c r="H1900" t="n">
         <v>4115</v>
@@ -55556,7 +55556,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.49607920646667</v>
+        <v>2.49607944488525</v>
       </c>
       <c r="H1903" t="n">
         <v>14919</v>
@@ -55643,7 +55643,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.50529003143311</v>
+        <v>2.50529026985168</v>
       </c>
       <c r="H1906" t="n">
         <v>3964</v>
@@ -55730,7 +55730,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.52371144294739</v>
+        <v>2.52371096611023</v>
       </c>
       <c r="H1909" t="n">
         <v>21034</v>
@@ -55817,7 +55817,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.48590302467346</v>
+        <v>2.48590278625488</v>
       </c>
       <c r="H1912" t="n">
         <v>7088</v>
@@ -55933,7 +55933,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.48590302467346</v>
+        <v>2.48590278625488</v>
       </c>
       <c r="H1916" t="n">
         <v>25062</v>
@@ -55962,7 +55962,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.4764506816864</v>
+        <v>2.47645044326782</v>
       </c>
       <c r="H1917" t="n">
         <v>35748</v>
@@ -56194,7 +56194,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.35357356071472</v>
+        <v>2.35357332229614</v>
       </c>
       <c r="H1925" t="n">
         <v>78350</v>
@@ -56397,7 +56397,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.4764506816864</v>
+        <v>2.47645044326782</v>
       </c>
       <c r="H1932" t="n">
         <v>13093</v>
@@ -56571,7 +56571,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.4764506816864</v>
+        <v>2.47645044326782</v>
       </c>
       <c r="H1938" t="n">
         <v>1120</v>
@@ -56600,7 +56600,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.48590302467346</v>
+        <v>2.48590278625488</v>
       </c>
       <c r="H1939" t="n">
         <v>9455</v>
@@ -56629,7 +56629,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.48590302467346</v>
+        <v>2.48590278625488</v>
       </c>
       <c r="H1940" t="n">
         <v>11704</v>
@@ -56919,7 +56919,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.48590302467346</v>
+        <v>2.48590278625488</v>
       </c>
       <c r="H1950" t="n">
         <v>5260</v>
@@ -57151,7 +57151,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.25905227661133</v>
+        <v>2.25905251502991</v>
       </c>
       <c r="H1958" t="n">
         <v>30664</v>
@@ -57238,7 +57238,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.25905227661133</v>
+        <v>2.25905251502991</v>
       </c>
       <c r="H1961" t="n">
         <v>20841</v>
@@ -57354,7 +57354,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.20233964920044</v>
+        <v>2.20233988761902</v>
       </c>
       <c r="H1965" t="n">
         <v>29544</v>
@@ -57441,7 +57441,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.09836673736572</v>
+        <v>2.09836649894714</v>
       </c>
       <c r="H1968" t="n">
         <v>74706</v>
@@ -57470,7 +57470,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.09836673736572</v>
+        <v>2.09836649894714</v>
       </c>
       <c r="H1969" t="n">
         <v>9302</v>
@@ -57673,7 +57673,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1976" t="n">
-        <v>1.95658504962921</v>
+        <v>1.95658493041992</v>
       </c>
       <c r="H1976" t="n">
         <v>36000</v>
@@ -57702,7 +57702,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G1977" t="n">
-        <v>1.89987242221832</v>
+        <v>1.89987254142761</v>
       </c>
       <c r="H1977" t="n">
         <v>41806</v>
@@ -57731,7 +57731,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1978" t="n">
-        <v>1.88096833229065</v>
+        <v>1.88096821308136</v>
       </c>
       <c r="H1978" t="n">
         <v>34542</v>
@@ -58021,7 +58021,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G1988" t="n">
-        <v>1.76281690597534</v>
+        <v>1.76281702518463</v>
       </c>
       <c r="H1988" t="n">
         <v>33607</v>
@@ -58050,7 +58050,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1989" t="n">
-        <v>1.72028255462646</v>
+        <v>1.72028267383575</v>
       </c>
       <c r="H1989" t="n">
         <v>29742</v>
@@ -58079,7 +58079,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1990" t="n">
-        <v>1.71083033084869</v>
+        <v>1.71083045005798</v>
       </c>
       <c r="H1990" t="n">
         <v>30368</v>
@@ -58108,7 +58108,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G1991" t="n">
-        <v>1.69665217399597</v>
+        <v>1.69665229320526</v>
       </c>
       <c r="H1991" t="n">
         <v>20639</v>
@@ -58340,7 +58340,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1999" t="n">
-        <v>1.71083033084869</v>
+        <v>1.71083045005798</v>
       </c>
       <c r="H1999" t="n">
         <v>74975</v>
@@ -58369,7 +58369,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G2000" t="n">
-        <v>1.72028255462646</v>
+        <v>1.72028267383575</v>
       </c>
       <c r="H2000" t="n">
         <v>22410</v>
@@ -58398,7 +58398,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G2001" t="n">
-        <v>1.71555650234222</v>
+        <v>1.71555662155151</v>
       </c>
       <c r="H2001" t="n">
         <v>9789</v>
@@ -58427,7 +58427,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G2002" t="n">
-        <v>1.71555650234222</v>
+        <v>1.71555662155151</v>
       </c>
       <c r="H2002" t="n">
         <v>22125</v>
@@ -58456,7 +58456,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G2003" t="n">
-        <v>1.72028255462646</v>
+        <v>1.72028267383575</v>
       </c>
       <c r="H2003" t="n">
         <v>13291</v>
@@ -58485,7 +58485,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G2004" t="n">
-        <v>1.67302203178406</v>
+        <v>1.67302191257477</v>
       </c>
       <c r="H2004" t="n">
         <v>67771</v>
@@ -58514,7 +58514,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G2005" t="n">
-        <v>1.69665217399597</v>
+        <v>1.69665229320526</v>
       </c>
       <c r="H2005" t="n">
         <v>35812</v>
@@ -58543,7 +58543,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G2006" t="n">
-        <v>1.71555650234222</v>
+        <v>1.71555662155151</v>
       </c>
       <c r="H2006" t="n">
         <v>45452</v>
@@ -58601,7 +58601,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G2008" t="n">
-        <v>1.88096833229065</v>
+        <v>1.88096821308136</v>
       </c>
       <c r="H2008" t="n">
         <v>138796</v>
@@ -58630,7 +58630,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G2009" t="n">
-        <v>1.9093245267868</v>
+        <v>1.90932464599609</v>
       </c>
       <c r="H2009" t="n">
         <v>104194</v>
@@ -58659,7 +58659,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2010" t="n">
-        <v>1.89987242221832</v>
+        <v>1.89987254142761</v>
       </c>
       <c r="H2010" t="n">
         <v>65630</v>
@@ -58891,7 +58891,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G2018" t="n">
-        <v>1.97548937797546</v>
+        <v>1.97548913955688</v>
       </c>
       <c r="H2018" t="n">
         <v>15452</v>
@@ -59355,7 +59355,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G2034" t="n">
-        <v>2.20233964920044</v>
+        <v>2.20233988761902</v>
       </c>
       <c r="H2034" t="n">
         <v>63054</v>
@@ -59413,7 +59413,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G2036" t="n">
-        <v>2.14562726020813</v>
+        <v>2.14562702178955</v>
       </c>
       <c r="H2036" t="n">
         <v>37183</v>
@@ -59616,7 +59616,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G2043" t="n">
-        <v>2.14562726020813</v>
+        <v>2.14562702178955</v>
       </c>
       <c r="H2043" t="n">
         <v>24001</v>
@@ -60167,7 +60167,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G2062" t="n">
-        <v>2.13617515563965</v>
+        <v>2.13617491722107</v>
       </c>
       <c r="H2062" t="n">
         <v>65314</v>
@@ -60196,7 +60196,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G2063" t="n">
-        <v>2.1078188419342</v>
+        <v>2.10781860351562</v>
       </c>
       <c r="H2063" t="n">
         <v>13109</v>
@@ -60225,7 +60225,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G2064" t="n">
-        <v>1.94713282585144</v>
+        <v>1.94713306427002</v>
       </c>
       <c r="H2064" t="n">
         <v>87023</v>
@@ -60254,7 +60254,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2065" t="n">
-        <v>1.87151622772217</v>
+        <v>1.87151610851288</v>
       </c>
       <c r="H2065" t="n">
         <v>174135</v>
@@ -60428,7 +60428,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G2071" t="n">
-        <v>1.72973465919495</v>
+        <v>1.72973477840424</v>
       </c>
       <c r="H2071" t="n">
         <v>62542</v>
@@ -60457,7 +60457,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G2072" t="n">
-        <v>1.81007754802704</v>
+        <v>1.81007742881775</v>
       </c>
       <c r="H2072" t="n">
         <v>129521</v>
@@ -60486,7 +60486,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2073" t="n">
-        <v>1.87151622772217</v>
+        <v>1.87151610851288</v>
       </c>
       <c r="H2073" t="n">
         <v>114688</v>
@@ -60515,7 +60515,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2074" t="n">
-        <v>1.87151622772217</v>
+        <v>1.87151610851288</v>
       </c>
       <c r="H2074" t="n">
         <v>54667</v>
@@ -60544,7 +60544,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G2075" t="n">
-        <v>1.86206412315369</v>
+        <v>1.8620640039444</v>
       </c>
       <c r="H2075" t="n">
         <v>42101</v>
@@ -60573,7 +60573,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2076" t="n">
-        <v>1.89987242221832</v>
+        <v>1.89987254142761</v>
       </c>
       <c r="H2076" t="n">
         <v>75534</v>
@@ -60602,7 +60602,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G2077" t="n">
-        <v>1.9093245267868</v>
+        <v>1.90932464599609</v>
       </c>
       <c r="H2077" t="n">
         <v>42646</v>
@@ -60631,7 +60631,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G2078" t="n">
-        <v>1.9093245267868</v>
+        <v>1.90932464599609</v>
       </c>
       <c r="H2078" t="n">
         <v>37922</v>
@@ -60660,7 +60660,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G2079" t="n">
-        <v>1.9093245267868</v>
+        <v>1.90932464599609</v>
       </c>
       <c r="H2079" t="n">
         <v>25910</v>
@@ -60689,7 +60689,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G2080" t="n">
-        <v>1.9093245267868</v>
+        <v>1.90932464599609</v>
       </c>
       <c r="H2080" t="n">
         <v>51175</v>
@@ -60718,7 +60718,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2081" t="n">
-        <v>1.89987242221832</v>
+        <v>1.89987254142761</v>
       </c>
       <c r="H2081" t="n">
         <v>40180</v>
@@ -60834,7 +60834,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2085" t="n">
-        <v>1.89987242221832</v>
+        <v>1.89987254142761</v>
       </c>
       <c r="H2085" t="n">
         <v>68375</v>
@@ -60950,7 +60950,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G2089" t="n">
-        <v>1.76281690597534</v>
+        <v>1.76281702518463</v>
       </c>
       <c r="H2089" t="n">
         <v>43797</v>
@@ -61037,7 +61037,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G2092" t="n">
-        <v>1.76281690597534</v>
+        <v>1.76281702518463</v>
       </c>
       <c r="H2092" t="n">
         <v>15031</v>
@@ -61153,7 +61153,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G2096" t="n">
-        <v>1.828981757164</v>
+        <v>1.82898163795471</v>
       </c>
       <c r="H2096" t="n">
         <v>110255</v>
@@ -61182,7 +61182,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G2097" t="n">
-        <v>1.828981757164</v>
+        <v>1.82898163795471</v>
       </c>
       <c r="H2097" t="n">
         <v>41092</v>
@@ -61356,7 +61356,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G2103" t="n">
-        <v>1.81007754802704</v>
+        <v>1.81007742881775</v>
       </c>
       <c r="H2103" t="n">
         <v>18410</v>
@@ -61385,7 +61385,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G2104" t="n">
-        <v>1.7817211151123</v>
+        <v>1.78172123432159</v>
       </c>
       <c r="H2104" t="n">
         <v>15864</v>
@@ -61559,7 +61559,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G2110" t="n">
-        <v>1.74391293525696</v>
+        <v>1.74391281604767</v>
       </c>
       <c r="H2110" t="n">
         <v>17198</v>
@@ -61646,7 +61646,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G2113" t="n">
-        <v>1.7817211151123</v>
+        <v>1.78172123432159</v>
       </c>
       <c r="H2113" t="n">
         <v>11979</v>
@@ -61733,7 +61733,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G2116" t="n">
-        <v>1.76281690597534</v>
+        <v>1.76281702518463</v>
       </c>
       <c r="H2116" t="n">
         <v>43153</v>
@@ -61994,7 +61994,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G2125" t="n">
-        <v>1.7817211151123</v>
+        <v>1.78172123432159</v>
       </c>
       <c r="H2125" t="n">
         <v>20190</v>
@@ -62052,7 +62052,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G2127" t="n">
-        <v>1.81007754802704</v>
+        <v>1.81007742881775</v>
       </c>
       <c r="H2127" t="n">
         <v>31095</v>
@@ -62110,7 +62110,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G2129" t="n">
-        <v>1.828981757164</v>
+        <v>1.82898163795471</v>
       </c>
       <c r="H2129" t="n">
         <v>59721</v>
@@ -62313,7 +62313,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G2136" t="n">
-        <v>1.7817211151123</v>
+        <v>1.78172123432159</v>
       </c>
       <c r="H2136" t="n">
         <v>35099</v>
@@ -62429,7 +62429,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G2140" t="n">
-        <v>1.74391293525696</v>
+        <v>1.74391281604767</v>
       </c>
       <c r="H2140" t="n">
         <v>38041</v>
@@ -62661,7 +62661,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G2148" t="n">
-        <v>1.74391293525696</v>
+        <v>1.74391281604767</v>
       </c>
       <c r="H2148" t="n">
         <v>17260</v>
@@ -62719,7 +62719,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G2150" t="n">
-        <v>1.72973465919495</v>
+        <v>1.72973477840424</v>
       </c>
       <c r="H2150" t="n">
         <v>29061</v>
@@ -62748,7 +62748,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G2151" t="n">
-        <v>1.68720018863678</v>
+        <v>1.68720006942749</v>
       </c>
       <c r="H2151" t="n">
         <v>22353</v>
@@ -62806,7 +62806,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G2153" t="n">
-        <v>1.71083033084869</v>
+        <v>1.71083045005798</v>
       </c>
       <c r="H2153" t="n">
         <v>22443</v>
@@ -62835,7 +62835,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G2154" t="n">
-        <v>1.68247413635254</v>
+        <v>1.68247401714325</v>
       </c>
       <c r="H2154" t="n">
         <v>63518</v>
@@ -62951,7 +62951,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G2158" t="n">
-        <v>1.69665217399597</v>
+        <v>1.69665229320526</v>
       </c>
       <c r="H2158" t="n">
         <v>13437</v>
@@ -62980,7 +62980,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G2159" t="n">
-        <v>1.67302203178406</v>
+        <v>1.67302191257477</v>
       </c>
       <c r="H2159" t="n">
         <v>16783</v>
@@ -79980,6 +79980,35 @@
         <v>450</v>
       </c>
       <c r="I2745" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2746">
+      <c r="A2746" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2746" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C2746" t="n">
+        <v>1.09500002861023</v>
+      </c>
+      <c r="D2746" t="n">
+        <v>1.13999998569489</v>
+      </c>
+      <c r="E2746" t="n">
+        <v>1.07500004768372</v>
+      </c>
+      <c r="F2746" t="n">
+        <v>1.09500002861023</v>
+      </c>
+      <c r="G2746" t="n">
+        <v>1.09500002861023</v>
+      </c>
+      <c r="H2746" t="n">
+        <v>23090</v>
+      </c>
+      <c r="I2746" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELC.MI.xlsx
+++ b/data/ELC.MI.xlsx
@@ -456,7 +456,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G3" t="n">
-        <v>1.73338496685028</v>
+        <v>1.73338508605957</v>
       </c>
       <c r="H3" t="n">
         <v>15024</v>
@@ -514,7 +514,7 @@
         <v>1.87399995326996</v>
       </c>
       <c r="G5" t="n">
-        <v>1.67441415786743</v>
+        <v>1.67441427707672</v>
       </c>
       <c r="H5" t="n">
         <v>56904</v>
@@ -572,7 +572,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G7" t="n">
-        <v>1.65297031402588</v>
+        <v>1.65297043323517</v>
       </c>
       <c r="H7" t="n">
         <v>22563</v>
@@ -659,7 +659,7 @@
         <v>1.81900000572205</v>
       </c>
       <c r="G10" t="n">
-        <v>1.62527179718018</v>
+        <v>1.62527203559875</v>
       </c>
       <c r="H10" t="n">
         <v>37372</v>
@@ -688,7 +688,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G11" t="n">
-        <v>1.59936046600342</v>
+        <v>1.59936034679413</v>
       </c>
       <c r="H11" t="n">
         <v>30082</v>
@@ -746,7 +746,7 @@
         <v>1.66700005531311</v>
       </c>
       <c r="G13" t="n">
-        <v>1.48946034908295</v>
+        <v>1.48946022987366</v>
       </c>
       <c r="H13" t="n">
         <v>45328</v>
@@ -862,7 +862,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G17" t="n">
-        <v>1.44746589660645</v>
+        <v>1.44746601581573</v>
       </c>
       <c r="H17" t="n">
         <v>53091</v>
@@ -891,7 +891,7 @@
         <v>1.625</v>
       </c>
       <c r="G18" t="n">
-        <v>1.45193338394165</v>
+        <v>1.45193350315094</v>
       </c>
       <c r="H18" t="n">
         <v>25640</v>
@@ -920,7 +920,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G19" t="n">
-        <v>1.46533572673798</v>
+        <v>1.46533584594727</v>
       </c>
       <c r="H19" t="n">
         <v>19803</v>
@@ -978,7 +978,7 @@
         <v>1.65100002288818</v>
       </c>
       <c r="G21" t="n">
-        <v>1.47516429424286</v>
+        <v>1.47516441345215</v>
       </c>
       <c r="H21" t="n">
         <v>7561</v>
@@ -1036,7 +1036,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G23" t="n">
-        <v>1.39832353591919</v>
+        <v>1.39832365512848</v>
       </c>
       <c r="H23" t="n">
         <v>23089</v>
@@ -1123,7 +1123,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G26" t="n">
-        <v>1.38492107391357</v>
+        <v>1.38492095470428</v>
       </c>
       <c r="H26" t="n">
         <v>35283</v>
@@ -1181,7 +1181,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G28" t="n">
-        <v>1.28216886520386</v>
+        <v>1.28216874599457</v>
       </c>
       <c r="H28" t="n">
         <v>58422</v>
@@ -1210,7 +1210,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G29" t="n">
-        <v>1.313441157341</v>
+        <v>1.31344127655029</v>
       </c>
       <c r="H29" t="n">
         <v>29625</v>
@@ -1268,7 +1268,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G31" t="n">
-        <v>1.42959594726562</v>
+        <v>1.42959606647491</v>
       </c>
       <c r="H31" t="n">
         <v>187635</v>
@@ -1297,7 +1297,7 @@
         <v>1.63199996948242</v>
       </c>
       <c r="G32" t="n">
-        <v>1.45818793773651</v>
+        <v>1.45818781852722</v>
       </c>
       <c r="H32" t="n">
         <v>53239</v>
@@ -1413,7 +1413,7 @@
         <v>1.75399994850159</v>
       </c>
       <c r="G36" t="n">
-        <v>1.5671945810318</v>
+        <v>1.56719434261322</v>
       </c>
       <c r="H36" t="n">
         <v>41971</v>
@@ -1500,7 +1500,7 @@
         <v>1.74699997901917</v>
       </c>
       <c r="G39" t="n">
-        <v>1.56094002723694</v>
+        <v>1.56094014644623</v>
       </c>
       <c r="H39" t="n">
         <v>2902</v>
@@ -1529,7 +1529,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G40" t="n">
-        <v>1.57702314853668</v>
+        <v>1.5770229101181</v>
       </c>
       <c r="H40" t="n">
         <v>4812</v>
@@ -1587,7 +1587,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G42" t="n">
-        <v>1.5814905166626</v>
+        <v>1.58149063587189</v>
       </c>
       <c r="H42" t="n">
         <v>5093</v>
@@ -1645,7 +1645,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G44" t="n">
-        <v>1.51894569396973</v>
+        <v>1.51894581317902</v>
       </c>
       <c r="H44" t="n">
         <v>29575</v>
@@ -1674,7 +1674,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G45" t="n">
-        <v>1.5814905166626</v>
+        <v>1.58149063587189</v>
       </c>
       <c r="H45" t="n">
         <v>28487</v>
@@ -1819,7 +1819,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G50" t="n">
-        <v>1.5814905166626</v>
+        <v>1.58149063587189</v>
       </c>
       <c r="H50" t="n">
         <v>3356</v>
@@ -1877,7 +1877,7 @@
         <v>1.8309999704361</v>
       </c>
       <c r="G52" t="n">
-        <v>1.63599395751953</v>
+        <v>1.63599383831024</v>
       </c>
       <c r="H52" t="n">
         <v>51060</v>
@@ -1906,7 +1906,7 @@
         <v>1.89300000667572</v>
       </c>
       <c r="G53" t="n">
-        <v>1.69139063358307</v>
+        <v>1.69139075279236</v>
       </c>
       <c r="H53" t="n">
         <v>24502</v>
@@ -1993,7 +1993,7 @@
         <v>1.90799999237061</v>
       </c>
       <c r="G56" t="n">
-        <v>1.70479321479797</v>
+        <v>1.70479309558868</v>
       </c>
       <c r="H56" t="n">
         <v>30447</v>
@@ -2051,7 +2051,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G58" t="n">
-        <v>1.76912498474121</v>
+        <v>1.76912486553192</v>
       </c>
       <c r="H58" t="n">
         <v>198777</v>
@@ -2080,7 +2080,7 @@
         <v>1.95200002193451</v>
       </c>
       <c r="G59" t="n">
-        <v>1.74410700798035</v>
+        <v>1.74410724639893</v>
       </c>
       <c r="H59" t="n">
         <v>77105</v>
@@ -2109,7 +2109,7 @@
         <v>1.93599998950958</v>
       </c>
       <c r="G60" t="n">
-        <v>1.72981107234955</v>
+        <v>1.72981119155884</v>
       </c>
       <c r="H60" t="n">
         <v>25733</v>
@@ -2138,7 +2138,7 @@
         <v>1.94599997997284</v>
       </c>
       <c r="G61" t="n">
-        <v>1.73874592781067</v>
+        <v>1.73874616622925</v>
       </c>
       <c r="H61" t="n">
         <v>32577</v>
@@ -2196,7 +2196,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G63" t="n">
-        <v>1.7512549161911</v>
+        <v>1.75125503540039</v>
       </c>
       <c r="H63" t="n">
         <v>20594</v>
@@ -2225,7 +2225,7 @@
         <v>1.96399998664856</v>
       </c>
       <c r="G64" t="n">
-        <v>1.75482904911041</v>
+        <v>1.75482892990112</v>
       </c>
       <c r="H64" t="n">
         <v>34653</v>
@@ -2312,7 +2312,7 @@
         <v>1.87899994850159</v>
       </c>
       <c r="G67" t="n">
-        <v>1.67888152599335</v>
+        <v>1.67888164520264</v>
       </c>
       <c r="H67" t="n">
         <v>36815</v>
@@ -2341,7 +2341,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G68" t="n">
-        <v>1.69317770004272</v>
+        <v>1.69317781925201</v>
       </c>
       <c r="H68" t="n">
         <v>6467</v>
@@ -2515,7 +2515,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G74" t="n">
-        <v>1.71551501750946</v>
+        <v>1.71551513671875</v>
       </c>
       <c r="H74" t="n">
         <v>16230</v>
@@ -2573,7 +2573,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G76" t="n">
-        <v>1.71104764938354</v>
+        <v>1.71104753017426</v>
       </c>
       <c r="H76" t="n">
         <v>11969</v>
@@ -2660,7 +2660,7 @@
         <v>1.89800000190735</v>
       </c>
       <c r="G79" t="n">
-        <v>1.69585824012756</v>
+        <v>1.69585812091827</v>
       </c>
       <c r="H79" t="n">
         <v>17651</v>
@@ -2805,7 +2805,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G84" t="n">
-        <v>1.74232006072998</v>
+        <v>1.74232017993927</v>
       </c>
       <c r="H84" t="n">
         <v>30024</v>
@@ -2834,7 +2834,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G85" t="n">
-        <v>1.7557225227356</v>
+        <v>1.75572264194489</v>
       </c>
       <c r="H85" t="n">
         <v>142111</v>
@@ -3066,7 +3066,7 @@
         <v>1.85199999809265</v>
       </c>
       <c r="G93" t="n">
-        <v>1.65475749969482</v>
+        <v>1.65475738048553</v>
       </c>
       <c r="H93" t="n">
         <v>17094</v>
@@ -3095,7 +3095,7 @@
         <v>1.88699996471405</v>
       </c>
       <c r="G94" t="n">
-        <v>1.68602979183197</v>
+        <v>1.68602967262268</v>
       </c>
       <c r="H94" t="n">
         <v>23988</v>
@@ -3182,7 +3182,7 @@
         <v>1.90600001811981</v>
       </c>
       <c r="G97" t="n">
-        <v>1.70300626754761</v>
+        <v>1.70300614833832</v>
       </c>
       <c r="H97" t="n">
         <v>8769</v>
@@ -3211,7 +3211,7 @@
         <v>1.91799998283386</v>
       </c>
       <c r="G98" t="n">
-        <v>1.71372818946838</v>
+        <v>1.71372807025909</v>
       </c>
       <c r="H98" t="n">
         <v>37783</v>
@@ -3240,7 +3240,7 @@
         <v>1.9190000295639</v>
       </c>
       <c r="G99" t="n">
-        <v>1.71462166309357</v>
+        <v>1.71462154388428</v>
       </c>
       <c r="H99" t="n">
         <v>116965</v>
@@ -3269,7 +3269,7 @@
         <v>1.90299999713898</v>
       </c>
       <c r="G100" t="n">
-        <v>1.70905363559723</v>
+        <v>1.70905351638794</v>
       </c>
       <c r="H100" t="n">
         <v>72354</v>
@@ -3298,7 +3298,7 @@
         <v>1.9190000295639</v>
       </c>
       <c r="G101" t="n">
-        <v>1.7234228849411</v>
+        <v>1.72342276573181</v>
       </c>
       <c r="H101" t="n">
         <v>15489</v>
@@ -3385,7 +3385,7 @@
         <v>1.93799996376038</v>
       </c>
       <c r="G104" t="n">
-        <v>1.74048638343811</v>
+        <v>1.7404865026474</v>
       </c>
       <c r="H104" t="n">
         <v>7025</v>
@@ -3762,7 +3762,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G117" t="n">
-        <v>1.62553155422211</v>
+        <v>1.6255316734314</v>
       </c>
       <c r="H117" t="n">
         <v>26360</v>
@@ -3849,7 +3849,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G120" t="n">
-        <v>1.63451254367828</v>
+        <v>1.63451266288757</v>
       </c>
       <c r="H120" t="n">
         <v>16192</v>
@@ -3965,7 +3965,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G124" t="n">
-        <v>1.61655080318451</v>
+        <v>1.61655068397522</v>
       </c>
       <c r="H124" t="n">
         <v>30870</v>
@@ -4023,7 +4023,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G126" t="n">
-        <v>1.61655080318451</v>
+        <v>1.61655068397522</v>
       </c>
       <c r="H126" t="n">
         <v>25208</v>
@@ -4139,7 +4139,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G130" t="n">
-        <v>1.63002216815948</v>
+        <v>1.63002228736877</v>
       </c>
       <c r="H130" t="n">
         <v>11486</v>
@@ -4197,7 +4197,7 @@
         <v>1.69700002670288</v>
       </c>
       <c r="G132" t="n">
-        <v>1.52404820919037</v>
+        <v>1.52404832839966</v>
       </c>
       <c r="H132" t="n">
         <v>59729</v>
@@ -4226,7 +4226,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G133" t="n">
-        <v>1.46836698055267</v>
+        <v>1.46836709976196</v>
       </c>
       <c r="H133" t="n">
         <v>25558</v>
@@ -4284,7 +4284,7 @@
         <v>1.62100005149841</v>
       </c>
       <c r="G135" t="n">
-        <v>1.45579397678375</v>
+        <v>1.45579385757446</v>
       </c>
       <c r="H135" t="n">
         <v>55410</v>
@@ -4400,7 +4400,7 @@
         <v>1.67299997806549</v>
       </c>
       <c r="G139" t="n">
-        <v>1.50249409675598</v>
+        <v>1.50249421596527</v>
       </c>
       <c r="H139" t="n">
         <v>13739</v>
@@ -4487,7 +4487,7 @@
         <v>1.67900002002716</v>
       </c>
       <c r="G142" t="n">
-        <v>1.50788271427155</v>
+        <v>1.50788259506226</v>
       </c>
       <c r="H142" t="n">
         <v>35224</v>
@@ -4661,7 +4661,7 @@
         <v>1.67400002479553</v>
       </c>
       <c r="G148" t="n">
-        <v>1.50339245796204</v>
+        <v>1.50339233875275</v>
       </c>
       <c r="H148" t="n">
         <v>8998</v>
@@ -4748,7 +4748,7 @@
         <v>1.65100002288818</v>
       </c>
       <c r="G151" t="n">
-        <v>1.48273634910583</v>
+        <v>1.48273646831512</v>
       </c>
       <c r="H151" t="n">
         <v>36497</v>
@@ -4777,7 +4777,7 @@
         <v>1.67400002479553</v>
       </c>
       <c r="G152" t="n">
-        <v>1.50339245796204</v>
+        <v>1.50339233875275</v>
       </c>
       <c r="H152" t="n">
         <v>17575</v>
@@ -4951,7 +4951,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G158" t="n">
-        <v>1.5312328338623</v>
+        <v>1.53123295307159</v>
       </c>
       <c r="H158" t="n">
         <v>2893</v>
@@ -4980,7 +4980,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G159" t="n">
-        <v>1.5177618265152</v>
+        <v>1.51776170730591</v>
       </c>
       <c r="H159" t="n">
         <v>13014</v>
@@ -5415,7 +5415,7 @@
         <v>1.87800002098083</v>
       </c>
       <c r="G174" t="n">
-        <v>1.68660140037537</v>
+        <v>1.68660128116608</v>
       </c>
       <c r="H174" t="n">
         <v>29492</v>
@@ -5444,7 +5444,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G175" t="n">
-        <v>1.67043590545654</v>
+        <v>1.67043602466583</v>
       </c>
       <c r="H175" t="n">
         <v>32520</v>
@@ -5589,7 +5589,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G180" t="n">
-        <v>1.67043590545654</v>
+        <v>1.67043602466583</v>
       </c>
       <c r="H180" t="n">
         <v>18502</v>
@@ -5618,7 +5618,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G181" t="n">
-        <v>1.68839752674103</v>
+        <v>1.68839764595032</v>
       </c>
       <c r="H181" t="n">
         <v>27805</v>
@@ -5705,7 +5705,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G184" t="n">
-        <v>1.63451254367828</v>
+        <v>1.63451266288757</v>
       </c>
       <c r="H184" t="n">
         <v>8710</v>
@@ -5734,7 +5734,7 @@
         <v>1.80400002002716</v>
       </c>
       <c r="G185" t="n">
-        <v>1.62014317512512</v>
+        <v>1.62014329433441</v>
       </c>
       <c r="H185" t="n">
         <v>11917</v>
@@ -5763,7 +5763,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G186" t="n">
-        <v>1.61655080318451</v>
+        <v>1.61655068397522</v>
       </c>
       <c r="H186" t="n">
         <v>28218</v>
@@ -5821,7 +5821,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G188" t="n">
-        <v>1.61655080318451</v>
+        <v>1.61655068397522</v>
       </c>
       <c r="H188" t="n">
         <v>35451</v>
@@ -5850,7 +5850,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G189" t="n">
-        <v>1.61655080318451</v>
+        <v>1.61655068397522</v>
       </c>
       <c r="H189" t="n">
         <v>33190</v>
@@ -5879,7 +5879,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G190" t="n">
-        <v>1.61655080318451</v>
+        <v>1.61655068397522</v>
       </c>
       <c r="H190" t="n">
         <v>29161</v>
@@ -5908,7 +5908,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G191" t="n">
-        <v>1.61655080318451</v>
+        <v>1.61655068397522</v>
       </c>
       <c r="H191" t="n">
         <v>2263</v>
@@ -5995,7 +5995,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G194" t="n">
-        <v>1.63451254367828</v>
+        <v>1.63451266288757</v>
       </c>
       <c r="H194" t="n">
         <v>7919</v>
@@ -6024,7 +6024,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G195" t="n">
-        <v>1.63451254367828</v>
+        <v>1.63451266288757</v>
       </c>
       <c r="H195" t="n">
         <v>15652</v>
@@ -6082,7 +6082,7 @@
         <v>1.89699995517731</v>
       </c>
       <c r="G197" t="n">
-        <v>1.70366489887238</v>
+        <v>1.70366501808167</v>
       </c>
       <c r="H197" t="n">
         <v>75519</v>
@@ -6169,7 +6169,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G200" t="n">
-        <v>1.68839752674103</v>
+        <v>1.68839764595032</v>
       </c>
       <c r="H200" t="n">
         <v>22315</v>
@@ -6198,7 +6198,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G201" t="n">
-        <v>1.67043590545654</v>
+        <v>1.67043602466583</v>
       </c>
       <c r="H201" t="n">
         <v>20696</v>
@@ -6343,7 +6343,7 @@
         <v>1.84599995613098</v>
       </c>
       <c r="G206" t="n">
-        <v>1.65786278247833</v>
+        <v>1.65786266326904</v>
       </c>
       <c r="H206" t="n">
         <v>30617</v>
@@ -6401,7 +6401,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G208" t="n">
-        <v>1.63451254367828</v>
+        <v>1.63451266288757</v>
       </c>
       <c r="H208" t="n">
         <v>34872</v>
@@ -6517,7 +6517,7 @@
         <v>1.86899995803833</v>
       </c>
       <c r="G212" t="n">
-        <v>1.67851853370667</v>
+        <v>1.67851865291595</v>
       </c>
       <c r="H212" t="n">
         <v>8145</v>
@@ -6546,7 +6546,7 @@
         <v>1.86899995803833</v>
       </c>
       <c r="G213" t="n">
-        <v>1.67851853370667</v>
+        <v>1.67851865291595</v>
       </c>
       <c r="H213" t="n">
         <v>6757</v>
@@ -6662,7 +6662,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G217" t="n">
-        <v>1.63451254367828</v>
+        <v>1.63451266288757</v>
       </c>
       <c r="H217" t="n">
         <v>3906</v>
@@ -6749,7 +6749,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G220" t="n">
-        <v>1.62553155422211</v>
+        <v>1.6255316734314</v>
       </c>
       <c r="H220" t="n">
         <v>9667</v>
@@ -6981,7 +6981,7 @@
         <v>1.65799999237061</v>
       </c>
       <c r="G228" t="n">
-        <v>1.48902297019958</v>
+        <v>1.4890228509903</v>
       </c>
       <c r="H228" t="n">
         <v>27997</v>
@@ -7126,7 +7126,7 @@
         <v>1.49699997901917</v>
       </c>
       <c r="G233" t="n">
-        <v>1.34443140029907</v>
+        <v>1.34443151950836</v>
       </c>
       <c r="H233" t="n">
         <v>56235</v>
@@ -7242,7 +7242,7 @@
         <v>1.52199995517731</v>
       </c>
       <c r="G237" t="n">
-        <v>1.36688351631165</v>
+        <v>1.36688363552094</v>
       </c>
       <c r="H237" t="n">
         <v>139886</v>
@@ -7329,7 +7329,7 @@
         <v>1.58200001716614</v>
       </c>
       <c r="G240" t="n">
-        <v>1.42076849937439</v>
+        <v>1.42076861858368</v>
       </c>
       <c r="H240" t="n">
         <v>44280</v>
@@ -7474,7 +7474,7 @@
         <v>1.65299999713898</v>
       </c>
       <c r="G245" t="n">
-        <v>1.48453271389008</v>
+        <v>1.48453259468079</v>
       </c>
       <c r="H245" t="n">
         <v>48017</v>
@@ -7503,7 +7503,7 @@
         <v>1.67900002002716</v>
       </c>
       <c r="G246" t="n">
-        <v>1.50788271427155</v>
+        <v>1.50788259506226</v>
       </c>
       <c r="H246" t="n">
         <v>43881</v>
@@ -7706,7 +7706,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G253" t="n">
-        <v>1.62553155422211</v>
+        <v>1.6255316734314</v>
       </c>
       <c r="H253" t="n">
         <v>37423</v>
@@ -7793,7 +7793,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G256" t="n">
-        <v>1.62553155422211</v>
+        <v>1.6255316734314</v>
       </c>
       <c r="H256" t="n">
         <v>64043</v>
@@ -7909,7 +7909,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G260" t="n">
-        <v>1.62553155422211</v>
+        <v>1.6255316734314</v>
       </c>
       <c r="H260" t="n">
         <v>44432</v>
@@ -8025,7 +8025,7 @@
         <v>1.84599995613098</v>
       </c>
       <c r="G264" t="n">
-        <v>1.65786278247833</v>
+        <v>1.65786266326904</v>
       </c>
       <c r="H264" t="n">
         <v>17679</v>
@@ -8083,7 +8083,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G266" t="n">
-        <v>1.62553155422211</v>
+        <v>1.6255316734314</v>
       </c>
       <c r="H266" t="n">
         <v>19396</v>
@@ -8170,7 +8170,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G269" t="n">
-        <v>1.63451254367828</v>
+        <v>1.63451266288757</v>
       </c>
       <c r="H269" t="n">
         <v>12835</v>
@@ -8228,7 +8228,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G271" t="n">
-        <v>1.62553155422211</v>
+        <v>1.6255316734314</v>
       </c>
       <c r="H271" t="n">
         <v>20092</v>
@@ -8402,7 +8402,7 @@
         <v>1.68099999427795</v>
       </c>
       <c r="G277" t="n">
-        <v>1.50967884063721</v>
+        <v>1.5096789598465</v>
       </c>
       <c r="H277" t="n">
         <v>16296</v>
@@ -8518,7 +8518,7 @@
         <v>1.72599995136261</v>
       </c>
       <c r="G281" t="n">
-        <v>1.55009245872498</v>
+        <v>1.55009257793427</v>
       </c>
       <c r="H281" t="n">
         <v>16160</v>
@@ -8576,7 +8576,7 @@
         <v>1.65100002288818</v>
       </c>
       <c r="G283" t="n">
-        <v>1.48273634910583</v>
+        <v>1.48273646831512</v>
       </c>
       <c r="H283" t="n">
         <v>69383</v>
@@ -8634,7 +8634,7 @@
         <v>1.62100005149841</v>
       </c>
       <c r="G285" t="n">
-        <v>1.45579397678375</v>
+        <v>1.45579385757446</v>
       </c>
       <c r="H285" t="n">
         <v>60471</v>
@@ -8663,7 +8663,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G286" t="n">
-        <v>1.47285735607147</v>
+        <v>1.47285747528076</v>
       </c>
       <c r="H286" t="n">
         <v>15937</v>
@@ -8692,7 +8692,7 @@
         <v>1.63100004196167</v>
       </c>
       <c r="G287" t="n">
-        <v>1.46477472782135</v>
+        <v>1.46477460861206</v>
       </c>
       <c r="H287" t="n">
         <v>11720</v>
@@ -8721,7 +8721,7 @@
         <v>1.51900005340576</v>
       </c>
       <c r="G288" t="n">
-        <v>1.3641893863678</v>
+        <v>1.36418926715851</v>
       </c>
       <c r="H288" t="n">
         <v>409131</v>
@@ -8866,7 +8866,7 @@
         <v>1.46700000762939</v>
       </c>
       <c r="G293" t="n">
-        <v>1.31748902797699</v>
+        <v>1.3174889087677</v>
       </c>
       <c r="H293" t="n">
         <v>48300</v>
@@ -8953,7 +8953,7 @@
         <v>1.48099994659424</v>
       </c>
       <c r="G296" t="n">
-        <v>1.33006203174591</v>
+        <v>1.3300621509552</v>
       </c>
       <c r="H296" t="n">
         <v>97619</v>
@@ -8982,7 +8982,7 @@
         <v>1.47800004482269</v>
       </c>
       <c r="G297" t="n">
-        <v>1.32736790180206</v>
+        <v>1.32736778259277</v>
       </c>
       <c r="H297" t="n">
         <v>41633</v>
@@ -9214,7 +9214,7 @@
         <v>1.58200001716614</v>
       </c>
       <c r="G305" t="n">
-        <v>1.42076849937439</v>
+        <v>1.42076861858368</v>
       </c>
       <c r="H305" t="n">
         <v>30008</v>
@@ -9562,7 +9562,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G317" t="n">
-        <v>1.41897249221802</v>
+        <v>1.41897237300873</v>
       </c>
       <c r="H317" t="n">
         <v>347122</v>
@@ -9591,7 +9591,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G318" t="n">
-        <v>1.46387648582458</v>
+        <v>1.46387660503387</v>
       </c>
       <c r="H318" t="n">
         <v>285320</v>
@@ -9620,7 +9620,7 @@
         <v>1.6139999628067</v>
       </c>
       <c r="G319" t="n">
-        <v>1.44950723648071</v>
+        <v>1.44950735569</v>
       </c>
       <c r="H319" t="n">
         <v>156991</v>
@@ -9649,7 +9649,7 @@
         <v>1.62600004673004</v>
       </c>
       <c r="G320" t="n">
-        <v>1.46028435230255</v>
+        <v>1.46028423309326</v>
       </c>
       <c r="H320" t="n">
         <v>280073</v>
@@ -9736,7 +9736,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G323" t="n">
-        <v>1.46387648582458</v>
+        <v>1.46387660503387</v>
       </c>
       <c r="H323" t="n">
         <v>95927</v>
@@ -9765,7 +9765,7 @@
         <v>1.65100002288818</v>
       </c>
       <c r="G324" t="n">
-        <v>1.48273634910583</v>
+        <v>1.48273646831512</v>
       </c>
       <c r="H324" t="n">
         <v>98154</v>
@@ -9794,7 +9794,7 @@
         <v>1.65299999713898</v>
       </c>
       <c r="G325" t="n">
-        <v>1.48453271389008</v>
+        <v>1.48453259468079</v>
       </c>
       <c r="H325" t="n">
         <v>133633</v>
@@ -9823,7 +9823,7 @@
         <v>1.65199995040894</v>
       </c>
       <c r="G326" t="n">
-        <v>1.48363447189331</v>
+        <v>1.48363435268402</v>
       </c>
       <c r="H326" t="n">
         <v>57085</v>
@@ -9939,7 +9939,7 @@
         <v>1.625</v>
       </c>
       <c r="G330" t="n">
-        <v>1.45938622951508</v>
+        <v>1.45938634872437</v>
       </c>
       <c r="H330" t="n">
         <v>44118</v>
@@ -10026,7 +10026,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G333" t="n">
-        <v>1.42346286773682</v>
+        <v>1.42346274852753</v>
       </c>
       <c r="H333" t="n">
         <v>10071</v>
@@ -10055,7 +10055,7 @@
         <v>1.60300004482269</v>
       </c>
       <c r="G334" t="n">
-        <v>1.43962824344635</v>
+        <v>1.43962836265564</v>
       </c>
       <c r="H334" t="n">
         <v>19962</v>
@@ -10316,7 +10316,7 @@
         <v>1.67900002002716</v>
       </c>
       <c r="G343" t="n">
-        <v>1.50788271427155</v>
+        <v>1.50788259506226</v>
       </c>
       <c r="H343" t="n">
         <v>109764</v>
@@ -10345,7 +10345,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G344" t="n">
-        <v>1.522252202034</v>
+        <v>1.52225208282471</v>
       </c>
       <c r="H344" t="n">
         <v>48246</v>
@@ -10374,7 +10374,7 @@
         <v>1.67900002002716</v>
       </c>
       <c r="G345" t="n">
-        <v>1.50788271427155</v>
+        <v>1.50788259506226</v>
       </c>
       <c r="H345" t="n">
         <v>60237</v>
@@ -10461,7 +10461,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G348" t="n">
-        <v>1.5177618265152</v>
+        <v>1.51776170730591</v>
       </c>
       <c r="H348" t="n">
         <v>54131</v>
@@ -11099,7 +11099,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G370" t="n">
-        <v>1.61655080318451</v>
+        <v>1.61655068397522</v>
       </c>
       <c r="H370" t="n">
         <v>66407</v>
@@ -11331,7 +11331,7 @@
         <v>1.81200003623962</v>
       </c>
       <c r="G378" t="n">
-        <v>1.62732779979706</v>
+        <v>1.62732791900635</v>
       </c>
       <c r="H378" t="n">
         <v>22032</v>
@@ -11360,7 +11360,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G379" t="n">
-        <v>1.61655080318451</v>
+        <v>1.61655068397522</v>
       </c>
       <c r="H379" t="n">
         <v>26590</v>
@@ -11389,7 +11389,7 @@
         <v>1.80400002002716</v>
       </c>
       <c r="G380" t="n">
-        <v>1.62014317512512</v>
+        <v>1.62014329433441</v>
       </c>
       <c r="H380" t="n">
         <v>37514</v>
@@ -11476,7 +11476,7 @@
         <v>1.70299994945526</v>
       </c>
       <c r="G383" t="n">
-        <v>1.52943670749664</v>
+        <v>1.52943658828735</v>
       </c>
       <c r="H383" t="n">
         <v>66555</v>
@@ -11534,7 +11534,7 @@
         <v>1.72099995613098</v>
       </c>
       <c r="G385" t="n">
-        <v>1.54560220241547</v>
+        <v>1.54560232162476</v>
       </c>
       <c r="H385" t="n">
         <v>48776</v>
@@ -11563,7 +11563,7 @@
         <v>1.72099995613098</v>
       </c>
       <c r="G386" t="n">
-        <v>1.54560220241547</v>
+        <v>1.54560232162476</v>
       </c>
       <c r="H386" t="n">
         <v>93328</v>
@@ -11650,7 +11650,7 @@
         <v>1.69700002670288</v>
       </c>
       <c r="G389" t="n">
-        <v>1.52404820919037</v>
+        <v>1.52404832839966</v>
       </c>
       <c r="H389" t="n">
         <v>22102</v>
@@ -11737,7 +11737,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G392" t="n">
-        <v>1.58511793613434</v>
+        <v>1.58511781692505</v>
       </c>
       <c r="H392" t="n">
         <v>48340</v>
@@ -11824,7 +11824,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G395" t="n">
-        <v>1.61655080318451</v>
+        <v>1.61655068397522</v>
       </c>
       <c r="H395" t="n">
         <v>19546</v>
@@ -12027,7 +12027,7 @@
         <v>1.75300002098083</v>
       </c>
       <c r="G402" t="n">
-        <v>1.5743408203125</v>
+        <v>1.57434093952179</v>
       </c>
       <c r="H402" t="n">
         <v>35483</v>
@@ -12056,7 +12056,7 @@
         <v>1.77799999713898</v>
       </c>
       <c r="G403" t="n">
-        <v>1.59679305553436</v>
+        <v>1.59679317474365</v>
       </c>
       <c r="H403" t="n">
         <v>16299</v>
@@ -12085,7 +12085,7 @@
         <v>1.78299999237061</v>
       </c>
       <c r="G404" t="n">
-        <v>1.60128343105316</v>
+        <v>1.60128355026245</v>
       </c>
       <c r="H404" t="n">
         <v>28416</v>
@@ -12172,7 +12172,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G407" t="n">
-        <v>1.63451254367828</v>
+        <v>1.63451266288757</v>
       </c>
       <c r="H407" t="n">
         <v>64582</v>
@@ -12230,7 +12230,7 @@
         <v>1.80400002002716</v>
       </c>
       <c r="G409" t="n">
-        <v>1.62014317512512</v>
+        <v>1.62014329433441</v>
       </c>
       <c r="H409" t="n">
         <v>53324</v>
@@ -12404,7 +12404,7 @@
         <v>1.75399994850159</v>
       </c>
       <c r="G415" t="n">
-        <v>1.57523894309998</v>
+        <v>1.57523882389069</v>
       </c>
       <c r="H415" t="n">
         <v>10057</v>
@@ -12462,7 +12462,7 @@
         <v>1.75899994373322</v>
       </c>
       <c r="G417" t="n">
-        <v>1.57972943782806</v>
+        <v>1.57972931861877</v>
       </c>
       <c r="H417" t="n">
         <v>17456</v>
@@ -12491,7 +12491,7 @@
         <v>1.73699998855591</v>
       </c>
       <c r="G418" t="n">
-        <v>1.55997157096863</v>
+        <v>1.55997169017792</v>
       </c>
       <c r="H418" t="n">
         <v>31219</v>
@@ -12549,7 +12549,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G420" t="n">
-        <v>1.61655080318451</v>
+        <v>1.61655068397522</v>
       </c>
       <c r="H420" t="n">
         <v>103982</v>
@@ -12781,7 +12781,7 @@
         <v>1.88199996948242</v>
       </c>
       <c r="G428" t="n">
-        <v>1.69019377231598</v>
+        <v>1.69019365310669</v>
       </c>
       <c r="H428" t="n">
         <v>222805</v>
@@ -12810,7 +12810,7 @@
         <v>1.85300004482269</v>
       </c>
       <c r="G429" t="n">
-        <v>1.66414928436279</v>
+        <v>1.66414940357208</v>
       </c>
       <c r="H429" t="n">
         <v>158747</v>
@@ -12897,7 +12897,7 @@
         <v>1.89600002765656</v>
       </c>
       <c r="G432" t="n">
-        <v>1.70276689529419</v>
+        <v>1.70276701450348</v>
       </c>
       <c r="H432" t="n">
         <v>450452</v>
@@ -12955,7 +12955,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G434" t="n">
-        <v>1.88597583770752</v>
+        <v>1.88597595691681</v>
       </c>
       <c r="H434" t="n">
         <v>616287</v>
@@ -13013,7 +13013,7 @@
         <v>2.24600005149841</v>
       </c>
       <c r="G436" t="n">
-        <v>2.01709628105164</v>
+        <v>2.01709651947021</v>
       </c>
       <c r="H436" t="n">
         <v>460797</v>
@@ -13042,7 +13042,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G437" t="n">
-        <v>2.02966952323914</v>
+        <v>2.02966928482056</v>
       </c>
       <c r="H437" t="n">
         <v>255675</v>
@@ -13100,7 +13100,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G439" t="n">
-        <v>2.32603716850281</v>
+        <v>2.32603693008423</v>
       </c>
       <c r="H439" t="n">
         <v>793101</v>
@@ -13129,7 +13129,7 @@
         <v>2.5239999294281</v>
       </c>
       <c r="G440" t="n">
-        <v>2.26676344871521</v>
+        <v>2.26676368713379</v>
       </c>
       <c r="H440" t="n">
         <v>814395</v>
@@ -13187,7 +13187,7 @@
         <v>2.53800010681152</v>
       </c>
       <c r="G442" t="n">
-        <v>2.27933692932129</v>
+        <v>2.27933669090271</v>
       </c>
       <c r="H442" t="n">
         <v>344384</v>
@@ -13448,7 +13448,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G451" t="n">
-        <v>2.30807542800903</v>
+        <v>2.30807518959045</v>
       </c>
       <c r="H451" t="n">
         <v>214951</v>
@@ -13535,7 +13535,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G454" t="n">
-        <v>2.26317119598389</v>
+        <v>2.26317143440247</v>
       </c>
       <c r="H454" t="n">
         <v>120776</v>
@@ -13564,7 +13564,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G455" t="n">
-        <v>2.20030546188354</v>
+        <v>2.20030570030212</v>
       </c>
       <c r="H455" t="n">
         <v>150509</v>
@@ -13622,7 +13622,7 @@
         <v>2.32200002670288</v>
       </c>
       <c r="G457" t="n">
-        <v>2.08535075187683</v>
+        <v>2.08535051345825</v>
       </c>
       <c r="H457" t="n">
         <v>355994</v>
@@ -13651,7 +13651,7 @@
         <v>2.50600004196167</v>
       </c>
       <c r="G458" t="n">
-        <v>2.25059819221497</v>
+        <v>2.25059795379639</v>
       </c>
       <c r="H458" t="n">
         <v>401496</v>
@@ -13680,7 +13680,7 @@
         <v>2.54800009727478</v>
       </c>
       <c r="G459" t="n">
-        <v>2.28831791877747</v>
+        <v>2.28831768035889</v>
       </c>
       <c r="H459" t="n">
         <v>214035</v>
@@ -13709,7 +13709,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G460" t="n">
-        <v>2.32603716850281</v>
+        <v>2.32603693008423</v>
       </c>
       <c r="H460" t="n">
         <v>221159</v>
@@ -13796,7 +13796,7 @@
         <v>2.86199998855591</v>
       </c>
       <c r="G463" t="n">
-        <v>2.57031559944153</v>
+        <v>2.57031583786011</v>
       </c>
       <c r="H463" t="n">
         <v>833255</v>
@@ -13883,7 +13883,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G466" t="n">
-        <v>2.45176887512207</v>
+        <v>2.45176863670349</v>
       </c>
       <c r="H466" t="n">
         <v>573169</v>
@@ -13912,7 +13912,7 @@
         <v>2.75</v>
       </c>
       <c r="G467" t="n">
-        <v>2.46973061561584</v>
+        <v>2.46973037719727</v>
       </c>
       <c r="H467" t="n">
         <v>391427</v>
@@ -13941,7 +13941,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G468" t="n">
-        <v>2.50565361976624</v>
+        <v>2.50565385818481</v>
       </c>
       <c r="H468" t="n">
         <v>122440</v>
@@ -14115,7 +14115,7 @@
         <v>2.79200005531311</v>
       </c>
       <c r="G474" t="n">
-        <v>2.50745010375977</v>
+        <v>2.50744986534119</v>
       </c>
       <c r="H474" t="n">
         <v>83459</v>
@@ -14202,7 +14202,7 @@
         <v>2.3659999370575</v>
       </c>
       <c r="G477" t="n">
-        <v>2.1248664855957</v>
+        <v>2.12486624717712</v>
       </c>
       <c r="H477" t="n">
         <v>1409761</v>
@@ -14231,7 +14231,7 @@
         <v>2.42400002479553</v>
       </c>
       <c r="G478" t="n">
-        <v>2.1769552230835</v>
+        <v>2.17695498466492</v>
       </c>
       <c r="H478" t="n">
         <v>603916</v>
@@ -14318,7 +14318,7 @@
         <v>2.25600004196167</v>
       </c>
       <c r="G481" t="n">
-        <v>2.02607703208923</v>
+        <v>2.02607727050781</v>
       </c>
       <c r="H481" t="n">
         <v>252490</v>
@@ -14405,7 +14405,7 @@
         <v>2.49399995803833</v>
       </c>
       <c r="G484" t="n">
-        <v>2.23982119560242</v>
+        <v>2.23982095718384</v>
       </c>
       <c r="H484" t="n">
         <v>493546</v>
@@ -14463,7 +14463,7 @@
         <v>2.48799991607666</v>
       </c>
       <c r="G486" t="n">
-        <v>2.23443222045898</v>
+        <v>2.23443245887756</v>
       </c>
       <c r="H486" t="n">
         <v>141038</v>
@@ -14492,7 +14492,7 @@
         <v>2.50200009346008</v>
       </c>
       <c r="G487" t="n">
-        <v>2.24700546264648</v>
+        <v>2.24700570106506</v>
       </c>
       <c r="H487" t="n">
         <v>156824</v>
@@ -14550,7 +14550,7 @@
         <v>2.54399991035461</v>
       </c>
       <c r="G489" t="n">
-        <v>2.28472495079041</v>
+        <v>2.28472518920898</v>
       </c>
       <c r="H489" t="n">
         <v>116310</v>
@@ -14608,7 +14608,7 @@
         <v>2.55800008773804</v>
       </c>
       <c r="G491" t="n">
-        <v>2.29729843139648</v>
+        <v>2.29729819297791</v>
       </c>
       <c r="H491" t="n">
         <v>201051</v>
@@ -14666,7 +14666,7 @@
         <v>2.48399996757507</v>
       </c>
       <c r="G493" t="n">
-        <v>2.23084020614624</v>
+        <v>2.23083996772766</v>
       </c>
       <c r="H493" t="n">
         <v>58887</v>
@@ -14695,7 +14695,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G494" t="n">
-        <v>2.20928597450256</v>
+        <v>2.20928621292114</v>
       </c>
       <c r="H494" t="n">
         <v>52081</v>
@@ -14782,7 +14782,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G497" t="n">
-        <v>2.20928597450256</v>
+        <v>2.20928621292114</v>
       </c>
       <c r="H497" t="n">
         <v>17558</v>
@@ -14840,7 +14840,7 @@
         <v>2.51200008392334</v>
       </c>
       <c r="G499" t="n">
-        <v>2.25598645210266</v>
+        <v>2.25598669052124</v>
       </c>
       <c r="H499" t="n">
         <v>57422</v>
@@ -14869,7 +14869,7 @@
         <v>2.54800009727478</v>
       </c>
       <c r="G500" t="n">
-        <v>2.28831791877747</v>
+        <v>2.28831768035889</v>
       </c>
       <c r="H500" t="n">
         <v>105664</v>
@@ -14956,7 +14956,7 @@
         <v>2.47399997711182</v>
       </c>
       <c r="G503" t="n">
-        <v>2.22185945510864</v>
+        <v>2.22185921669006</v>
       </c>
       <c r="H503" t="n">
         <v>90422</v>
@@ -14985,7 +14985,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G504" t="n">
-        <v>2.22724771499634</v>
+        <v>2.22724795341492</v>
       </c>
       <c r="H504" t="n">
         <v>89542</v>
@@ -15014,7 +15014,7 @@
         <v>2.5239999294281</v>
       </c>
       <c r="G505" t="n">
-        <v>2.26676344871521</v>
+        <v>2.26676368713379</v>
       </c>
       <c r="H505" t="n">
         <v>167428</v>
@@ -15072,7 +15072,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G507" t="n">
-        <v>2.22724771499634</v>
+        <v>2.22724795341492</v>
       </c>
       <c r="H507" t="n">
         <v>48876</v>
@@ -15130,7 +15130,7 @@
         <v>2.43799996376038</v>
       </c>
       <c r="G509" t="n">
-        <v>2.18952822685242</v>
+        <v>2.189528465271</v>
       </c>
       <c r="H509" t="n">
         <v>58859</v>
@@ -15217,7 +15217,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G512" t="n">
-        <v>2.19132471084595</v>
+        <v>2.19132447242737</v>
       </c>
       <c r="H512" t="n">
         <v>101821</v>
@@ -15304,7 +15304,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G515" t="n">
-        <v>2.19132471084595</v>
+        <v>2.19132447242737</v>
       </c>
       <c r="H515" t="n">
         <v>50871</v>
@@ -15333,7 +15333,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G516" t="n">
-        <v>2.22724771499634</v>
+        <v>2.22724795341492</v>
       </c>
       <c r="H516" t="n">
         <v>124471</v>
@@ -15362,7 +15362,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G517" t="n">
-        <v>2.22724771499634</v>
+        <v>2.22724795341492</v>
       </c>
       <c r="H517" t="n">
         <v>74248</v>
@@ -15391,7 +15391,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G518" t="n">
-        <v>2.21826696395874</v>
+        <v>2.21826720237732</v>
       </c>
       <c r="H518" t="n">
         <v>107211</v>
@@ -15565,7 +15565,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G524" t="n">
-        <v>2.04763102531433</v>
+        <v>2.04763078689575</v>
       </c>
       <c r="H524" t="n">
         <v>233885</v>
@@ -15623,7 +15623,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G526" t="n">
-        <v>2.06559252738953</v>
+        <v>2.06559276580811</v>
       </c>
       <c r="H526" t="n">
         <v>88709</v>
@@ -15855,7 +15855,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G534" t="n">
-        <v>2.1374397277832</v>
+        <v>2.13743996620178</v>
       </c>
       <c r="H534" t="n">
         <v>38703</v>
@@ -16000,7 +16000,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G539" t="n">
-        <v>2.06559252738953</v>
+        <v>2.06559276580811</v>
       </c>
       <c r="H539" t="n">
         <v>88481</v>
@@ -16145,7 +16145,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G544" t="n">
-        <v>2.06559252738953</v>
+        <v>2.06559276580811</v>
       </c>
       <c r="H544" t="n">
         <v>94606</v>
@@ -16174,7 +16174,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G545" t="n">
-        <v>2.06559252738953</v>
+        <v>2.06559276580811</v>
       </c>
       <c r="H545" t="n">
         <v>90340</v>
@@ -16232,7 +16232,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G547" t="n">
-        <v>2.06559252738953</v>
+        <v>2.06559276580811</v>
       </c>
       <c r="H547" t="n">
         <v>66787</v>
@@ -16348,7 +16348,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G551" t="n">
-        <v>2.04763102531433</v>
+        <v>2.04763078689575</v>
       </c>
       <c r="H551" t="n">
         <v>51292</v>
@@ -16406,7 +16406,7 @@
         <v>2.14499998092651</v>
       </c>
       <c r="G553" t="n">
-        <v>1.92638981342316</v>
+        <v>1.92638993263245</v>
       </c>
       <c r="H553" t="n">
         <v>175487</v>
@@ -16435,7 +16435,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G554" t="n">
-        <v>1.8769953250885</v>
+        <v>1.87699520587921</v>
       </c>
       <c r="H554" t="n">
         <v>92111</v>
@@ -16464,7 +16464,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G555" t="n">
-        <v>1.90393757820129</v>
+        <v>1.90393769741058</v>
       </c>
       <c r="H555" t="n">
         <v>98801</v>
@@ -16522,7 +16522,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G557" t="n">
-        <v>1.91291856765747</v>
+        <v>1.91291844844818</v>
       </c>
       <c r="H557" t="n">
         <v>103311</v>
@@ -16580,7 +16580,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G559" t="n">
-        <v>1.94884204864502</v>
+        <v>1.94884181022644</v>
       </c>
       <c r="H559" t="n">
         <v>132375</v>
@@ -16725,7 +16725,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G564" t="n">
-        <v>2.06110239028931</v>
+        <v>2.06110215187073</v>
       </c>
       <c r="H564" t="n">
         <v>80977</v>
@@ -16783,7 +16783,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G566" t="n">
-        <v>1.99374616146088</v>
+        <v>1.9937459230423</v>
       </c>
       <c r="H566" t="n">
         <v>30462</v>
@@ -16899,7 +16899,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G570" t="n">
-        <v>1.94884204864502</v>
+        <v>1.94884181022644</v>
       </c>
       <c r="H570" t="n">
         <v>32611</v>
@@ -16928,7 +16928,7 @@
         <v>2.15499997138977</v>
       </c>
       <c r="G571" t="n">
-        <v>1.93537068367004</v>
+        <v>1.93537056446075</v>
       </c>
       <c r="H571" t="n">
         <v>21921</v>
@@ -16957,7 +16957,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G572" t="n">
-        <v>1.91291856765747</v>
+        <v>1.91291844844818</v>
       </c>
       <c r="H572" t="n">
         <v>49060</v>
@@ -16986,7 +16986,7 @@
         <v>2.15499997138977</v>
       </c>
       <c r="G573" t="n">
-        <v>1.93537068367004</v>
+        <v>1.93537056446075</v>
       </c>
       <c r="H573" t="n">
         <v>29223</v>
@@ -17247,7 +17247,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G582" t="n">
-        <v>2.05661201477051</v>
+        <v>2.05661177635193</v>
       </c>
       <c r="H582" t="n">
         <v>69994</v>
@@ -17276,7 +17276,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G583" t="n">
-        <v>2.03865051269531</v>
+        <v>2.03865027427673</v>
       </c>
       <c r="H583" t="n">
         <v>32623</v>
@@ -17334,7 +17334,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G585" t="n">
-        <v>2.04763102531433</v>
+        <v>2.04763078689575</v>
       </c>
       <c r="H585" t="n">
         <v>8638</v>
@@ -17392,7 +17392,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G587" t="n">
-        <v>2.06110239028931</v>
+        <v>2.06110215187073</v>
       </c>
       <c r="H587" t="n">
         <v>59626</v>
@@ -17479,7 +17479,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G590" t="n">
-        <v>2.06559252738953</v>
+        <v>2.06559276580811</v>
       </c>
       <c r="H590" t="n">
         <v>18851</v>
@@ -17537,7 +17537,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G592" t="n">
-        <v>2.06110239028931</v>
+        <v>2.06110215187073</v>
       </c>
       <c r="H592" t="n">
         <v>23900</v>
@@ -17769,7 +17769,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G600" t="n">
-        <v>2.32603716850281</v>
+        <v>2.32603693008423</v>
       </c>
       <c r="H600" t="n">
         <v>234645</v>
@@ -17856,7 +17856,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G603" t="n">
-        <v>2.21826696395874</v>
+        <v>2.21826720237732</v>
       </c>
       <c r="H603" t="n">
         <v>66824</v>
@@ -17885,7 +17885,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G604" t="n">
-        <v>2.20030546188354</v>
+        <v>2.20030570030212</v>
       </c>
       <c r="H604" t="n">
         <v>38475</v>
@@ -18146,7 +18146,7 @@
         <v>2.22499990463257</v>
       </c>
       <c r="G613" t="n">
-        <v>1.99823617935181</v>
+        <v>1.99823641777039</v>
       </c>
       <c r="H613" t="n">
         <v>76914</v>
@@ -18204,7 +18204,7 @@
         <v>2.15499997138977</v>
       </c>
       <c r="G615" t="n">
-        <v>1.93537068367004</v>
+        <v>1.93537056446075</v>
       </c>
       <c r="H615" t="n">
         <v>55377</v>
@@ -18233,7 +18233,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G616" t="n">
-        <v>2.02966952323914</v>
+        <v>2.02966928482056</v>
       </c>
       <c r="H616" t="n">
         <v>49483</v>
@@ -18262,7 +18262,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G617" t="n">
-        <v>2.04763102531433</v>
+        <v>2.04763078689575</v>
       </c>
       <c r="H617" t="n">
         <v>74739</v>
@@ -18320,7 +18320,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G619" t="n">
-        <v>2.06559252738953</v>
+        <v>2.06559276580811</v>
       </c>
       <c r="H619" t="n">
         <v>36072</v>
@@ -18349,7 +18349,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G620" t="n">
-        <v>2.02966952323914</v>
+        <v>2.02966928482056</v>
       </c>
       <c r="H620" t="n">
         <v>58818</v>
@@ -18378,7 +18378,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G621" t="n">
-        <v>2.04763102531433</v>
+        <v>2.04763078689575</v>
       </c>
       <c r="H621" t="n">
         <v>34438</v>
@@ -18436,7 +18436,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G623" t="n">
-        <v>2.06110239028931</v>
+        <v>2.06110215187073</v>
       </c>
       <c r="H623" t="n">
         <v>21291</v>
@@ -18465,7 +18465,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G624" t="n">
-        <v>2.02966952323914</v>
+        <v>2.02966928482056</v>
       </c>
       <c r="H624" t="n">
         <v>22488</v>
@@ -18552,7 +18552,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G627" t="n">
-        <v>2.04763102531433</v>
+        <v>2.04763078689575</v>
       </c>
       <c r="H627" t="n">
         <v>13812</v>
@@ -18581,7 +18581,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G628" t="n">
-        <v>2.06559252738953</v>
+        <v>2.06559276580811</v>
       </c>
       <c r="H628" t="n">
         <v>17736</v>
@@ -18668,7 +18668,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G631" t="n">
-        <v>1.99374616146088</v>
+        <v>1.9937459230423</v>
       </c>
       <c r="H631" t="n">
         <v>31667</v>
@@ -18697,7 +18697,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G632" t="n">
-        <v>2.05661201477051</v>
+        <v>2.05661177635193</v>
       </c>
       <c r="H632" t="n">
         <v>16723</v>
@@ -18900,7 +18900,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G639" t="n">
-        <v>1.99374616146088</v>
+        <v>1.9937459230423</v>
       </c>
       <c r="H639" t="n">
         <v>29982</v>
@@ -18929,7 +18929,7 @@
         <v>2.22499990463257</v>
       </c>
       <c r="G640" t="n">
-        <v>1.99823617935181</v>
+        <v>1.99823641777039</v>
       </c>
       <c r="H640" t="n">
         <v>33589</v>
@@ -18958,7 +18958,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G641" t="n">
-        <v>1.99374616146088</v>
+        <v>1.9937459230423</v>
       </c>
       <c r="H641" t="n">
         <v>11189</v>
@@ -19016,7 +19016,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G643" t="n">
-        <v>1.99374616146088</v>
+        <v>1.9937459230423</v>
       </c>
       <c r="H643" t="n">
         <v>8111</v>
@@ -19132,7 +19132,7 @@
         <v>2.1949999332428</v>
       </c>
       <c r="G647" t="n">
-        <v>1.9712940454483</v>
+        <v>1.97129380702972</v>
       </c>
       <c r="H647" t="n">
         <v>2598</v>
@@ -19248,7 +19248,7 @@
         <v>2.20499992370605</v>
       </c>
       <c r="G651" t="n">
-        <v>1.98027491569519</v>
+        <v>1.98027467727661</v>
       </c>
       <c r="H651" t="n">
         <v>2266</v>
@@ -19335,7 +19335,7 @@
         <v>2.15499997138977</v>
       </c>
       <c r="G654" t="n">
-        <v>1.93537068367004</v>
+        <v>1.93537056446075</v>
       </c>
       <c r="H654" t="n">
         <v>15993</v>
@@ -19364,7 +19364,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G655" t="n">
-        <v>1.94884204864502</v>
+        <v>1.94884181022644</v>
       </c>
       <c r="H655" t="n">
         <v>8943</v>
@@ -19393,7 +19393,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G656" t="n">
-        <v>1.89495670795441</v>
+        <v>1.8949568271637</v>
       </c>
       <c r="H656" t="n">
         <v>71608</v>
@@ -19451,7 +19451,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G658" t="n">
-        <v>1.89495670795441</v>
+        <v>1.8949568271637</v>
       </c>
       <c r="H658" t="n">
         <v>29865</v>
@@ -19538,7 +19538,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G661" t="n">
-        <v>1.90393757820129</v>
+        <v>1.90393769741058</v>
       </c>
       <c r="H661" t="n">
         <v>119673</v>
@@ -19567,7 +19567,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G662" t="n">
-        <v>1.90393757820129</v>
+        <v>1.90393769741058</v>
       </c>
       <c r="H662" t="n">
         <v>41999</v>
@@ -19683,7 +19683,7 @@
         <v>2.14499998092651</v>
       </c>
       <c r="G666" t="n">
-        <v>1.92638981342316</v>
+        <v>1.92638993263245</v>
       </c>
       <c r="H666" t="n">
         <v>17689</v>
@@ -19712,7 +19712,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G667" t="n">
-        <v>1.90393757820129</v>
+        <v>1.90393769741058</v>
       </c>
       <c r="H667" t="n">
         <v>22750</v>
@@ -19770,7 +19770,7 @@
         <v>2.14499998092651</v>
       </c>
       <c r="G669" t="n">
-        <v>1.92638981342316</v>
+        <v>1.92638993263245</v>
       </c>
       <c r="H669" t="n">
         <v>28810</v>
@@ -20002,7 +20002,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G677" t="n">
-        <v>2.03865051269531</v>
+        <v>2.03865027427673</v>
       </c>
       <c r="H677" t="n">
         <v>13543</v>
@@ -20031,7 +20031,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G678" t="n">
-        <v>2.03865051269531</v>
+        <v>2.03865027427673</v>
       </c>
       <c r="H678" t="n">
         <v>54963</v>
@@ -20060,7 +20060,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G679" t="n">
-        <v>2.06559252738953</v>
+        <v>2.06559276580811</v>
       </c>
       <c r="H679" t="n">
         <v>71912</v>
@@ -20118,7 +20118,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G681" t="n">
-        <v>1.99374616146088</v>
+        <v>1.9937459230423</v>
       </c>
       <c r="H681" t="n">
         <v>78160</v>
@@ -20147,7 +20147,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G682" t="n">
-        <v>1.94884204864502</v>
+        <v>1.94884181022644</v>
       </c>
       <c r="H682" t="n">
         <v>39975</v>
@@ -20263,7 +20263,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G686" t="n">
-        <v>2.05661201477051</v>
+        <v>2.05661177635193</v>
       </c>
       <c r="H686" t="n">
         <v>71272</v>
@@ -20292,7 +20292,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G687" t="n">
-        <v>2.05661201477051</v>
+        <v>2.05661177635193</v>
       </c>
       <c r="H687" t="n">
         <v>59680</v>
@@ -20408,7 +20408,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G691" t="n">
-        <v>2.03865051269531</v>
+        <v>2.03865027427673</v>
       </c>
       <c r="H691" t="n">
         <v>3909</v>
@@ -20524,7 +20524,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G695" t="n">
-        <v>2.05661201477051</v>
+        <v>2.05661177635193</v>
       </c>
       <c r="H695" t="n">
         <v>8106</v>
@@ -20611,7 +20611,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G698" t="n">
-        <v>2.06110239028931</v>
+        <v>2.06110215187073</v>
       </c>
       <c r="H698" t="n">
         <v>7245</v>
@@ -20669,7 +20669,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G700" t="n">
-        <v>2.02966952323914</v>
+        <v>2.02966928482056</v>
       </c>
       <c r="H700" t="n">
         <v>5195</v>
@@ -20756,7 +20756,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G703" t="n">
-        <v>2.03865051269531</v>
+        <v>2.03865027427673</v>
       </c>
       <c r="H703" t="n">
         <v>2475</v>
@@ -20872,7 +20872,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G707" t="n">
-        <v>1.91291856765747</v>
+        <v>1.91291844844818</v>
       </c>
       <c r="H707" t="n">
         <v>21836</v>
@@ -20959,7 +20959,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G710" t="n">
-        <v>1.77820599079132</v>
+        <v>1.77820587158203</v>
       </c>
       <c r="H710" t="n">
         <v>41058</v>
@@ -20988,7 +20988,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G711" t="n">
-        <v>1.82311010360718</v>
+        <v>1.82311022281647</v>
       </c>
       <c r="H711" t="n">
         <v>25998</v>
@@ -21104,7 +21104,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G715" t="n">
-        <v>1.80514848232269</v>
+        <v>1.8051483631134</v>
       </c>
       <c r="H715" t="n">
         <v>29989</v>
@@ -21365,7 +21365,7 @@
         <v>1.89400005340576</v>
       </c>
       <c r="G724" t="n">
-        <v>1.70097088813782</v>
+        <v>1.70097076892853</v>
       </c>
       <c r="H724" t="n">
         <v>126727</v>
@@ -21510,7 +21510,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G729" t="n">
-        <v>1.63451254367828</v>
+        <v>1.63451266288757</v>
       </c>
       <c r="H729" t="n">
         <v>10781</v>
@@ -21568,7 +21568,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G731" t="n">
-        <v>1.63451254367828</v>
+        <v>1.63451266288757</v>
       </c>
       <c r="H731" t="n">
         <v>4539</v>
@@ -21597,7 +21597,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G732" t="n">
-        <v>1.63451254367828</v>
+        <v>1.63451266288757</v>
       </c>
       <c r="H732" t="n">
         <v>13877</v>
@@ -21626,7 +21626,7 @@
         <v>1.76199996471405</v>
       </c>
       <c r="G733" t="n">
-        <v>1.58242356777191</v>
+        <v>1.5824236869812</v>
       </c>
       <c r="H733" t="n">
         <v>6578</v>
@@ -21684,7 +21684,7 @@
         <v>1.72599995136261</v>
       </c>
       <c r="G735" t="n">
-        <v>1.55009245872498</v>
+        <v>1.55009257793427</v>
       </c>
       <c r="H735" t="n">
         <v>13578</v>
@@ -21742,7 +21742,7 @@
         <v>1.65199995040894</v>
       </c>
       <c r="G737" t="n">
-        <v>1.48363447189331</v>
+        <v>1.48363435268402</v>
       </c>
       <c r="H737" t="n">
         <v>8876</v>
@@ -21771,7 +21771,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G738" t="n">
-        <v>1.41897249221802</v>
+        <v>1.41897237300873</v>
       </c>
       <c r="H738" t="n">
         <v>69081</v>
@@ -21829,7 +21829,7 @@
         <v>1.59800004959106</v>
       </c>
       <c r="G740" t="n">
-        <v>1.43513798713684</v>
+        <v>1.43513810634613</v>
       </c>
       <c r="H740" t="n">
         <v>10009</v>
@@ -21858,7 +21858,7 @@
         <v>1.55599999427795</v>
       </c>
       <c r="G741" t="n">
-        <v>1.39741849899292</v>
+        <v>1.39741837978363</v>
       </c>
       <c r="H741" t="n">
         <v>29346</v>
@@ -21887,7 +21887,7 @@
         <v>1.57400000095367</v>
       </c>
       <c r="G742" t="n">
-        <v>1.41358387470245</v>
+        <v>1.41358399391174</v>
       </c>
       <c r="H742" t="n">
         <v>18646</v>
@@ -21916,7 +21916,7 @@
         <v>1.57200002670288</v>
       </c>
       <c r="G743" t="n">
-        <v>1.41178786754608</v>
+        <v>1.41178774833679</v>
       </c>
       <c r="H743" t="n">
         <v>37379</v>
@@ -21945,7 +21945,7 @@
         <v>1.50800001621246</v>
       </c>
       <c r="G744" t="n">
-        <v>1.35431051254272</v>
+        <v>1.35431039333344</v>
       </c>
       <c r="H744" t="n">
         <v>54423</v>
@@ -22003,7 +22003,7 @@
         <v>1.49600005149841</v>
       </c>
       <c r="G746" t="n">
-        <v>1.34353339672089</v>
+        <v>1.34353351593018</v>
       </c>
       <c r="H746" t="n">
         <v>50501</v>
@@ -22235,7 +22235,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G754" t="n">
-        <v>1.22139406204224</v>
+        <v>1.22139394283295</v>
       </c>
       <c r="H754" t="n">
         <v>44371</v>
@@ -22264,7 +22264,7 @@
         <v>1.41600000858307</v>
       </c>
       <c r="G755" t="n">
-        <v>1.27168667316437</v>
+        <v>1.27168655395508</v>
       </c>
       <c r="H755" t="n">
         <v>45386</v>
@@ -22293,7 +22293,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G756" t="n">
-        <v>1.23935568332672</v>
+        <v>1.23935556411743</v>
       </c>
       <c r="H756" t="n">
         <v>25908</v>
@@ -22351,7 +22351,7 @@
         <v>1.29200005531311</v>
       </c>
       <c r="G758" t="n">
-        <v>1.16032421588898</v>
+        <v>1.16032433509827</v>
       </c>
       <c r="H758" t="n">
         <v>115682</v>
@@ -22583,7 +22583,7 @@
         <v>1.52799999713898</v>
       </c>
       <c r="G766" t="n">
-        <v>1.37227213382721</v>
+        <v>1.3722722530365</v>
       </c>
       <c r="H766" t="n">
         <v>166018</v>
@@ -22699,7 +22699,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G770" t="n">
-        <v>1.35610663890839</v>
+        <v>1.3561065196991</v>
       </c>
       <c r="H770" t="n">
         <v>32416</v>
@@ -22786,7 +22786,7 @@
         <v>1.47800004482269</v>
       </c>
       <c r="G773" t="n">
-        <v>1.32736790180206</v>
+        <v>1.32736778259277</v>
       </c>
       <c r="H773" t="n">
         <v>32846</v>
@@ -22844,7 +22844,7 @@
         <v>1.49600005149841</v>
       </c>
       <c r="G775" t="n">
-        <v>1.34353339672089</v>
+        <v>1.34353351593018</v>
       </c>
       <c r="H775" t="n">
         <v>8974</v>
@@ -22989,7 +22989,7 @@
         <v>1.47200000286102</v>
       </c>
       <c r="G780" t="n">
-        <v>1.3219792842865</v>
+        <v>1.32197940349579</v>
       </c>
       <c r="H780" t="n">
         <v>10353</v>
@@ -23018,7 +23018,7 @@
         <v>1.49600005149841</v>
       </c>
       <c r="G781" t="n">
-        <v>1.34353339672089</v>
+        <v>1.34353351593018</v>
       </c>
       <c r="H781" t="n">
         <v>72453</v>
@@ -23047,7 +23047,7 @@
         <v>1.49800002574921</v>
       </c>
       <c r="G782" t="n">
-        <v>1.34532964229584</v>
+        <v>1.34532952308655</v>
       </c>
       <c r="H782" t="n">
         <v>53053</v>
@@ -23279,7 +23279,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G790" t="n">
-        <v>1.24833643436432</v>
+        <v>1.24833655357361</v>
       </c>
       <c r="H790" t="n">
         <v>20252</v>
@@ -23482,7 +23482,7 @@
         <v>1.89800000190735</v>
       </c>
       <c r="G797" t="n">
-        <v>1.70456314086914</v>
+        <v>1.70456302165985</v>
       </c>
       <c r="H797" t="n">
         <v>898372</v>
@@ -23656,7 +23656,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G803" t="n">
-        <v>1.88597583770752</v>
+        <v>1.88597595691681</v>
       </c>
       <c r="H803" t="n">
         <v>354581</v>
@@ -23714,7 +23714,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G805" t="n">
-        <v>1.82311010360718</v>
+        <v>1.82311022281647</v>
       </c>
       <c r="H805" t="n">
         <v>293536</v>
@@ -23743,7 +23743,7 @@
         <v>2.14499998092651</v>
       </c>
       <c r="G806" t="n">
-        <v>1.92638981342316</v>
+        <v>1.92638993263245</v>
       </c>
       <c r="H806" t="n">
         <v>684242</v>
@@ -23859,7 +23859,7 @@
         <v>1.98199999332428</v>
       </c>
       <c r="G810" t="n">
-        <v>1.78000199794769</v>
+        <v>1.78000211715698</v>
       </c>
       <c r="H810" t="n">
         <v>354171</v>
@@ -23917,7 +23917,7 @@
         <v>2.04500007629395</v>
       </c>
       <c r="G812" t="n">
-        <v>1.83658146858215</v>
+        <v>1.83658158779144</v>
       </c>
       <c r="H812" t="n">
         <v>184309</v>
@@ -23975,7 +23975,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G814" t="n">
-        <v>1.80514848232269</v>
+        <v>1.8051483631134</v>
       </c>
       <c r="H814" t="n">
         <v>69071</v>
@@ -24091,7 +24091,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G818" t="n">
-        <v>1.68839752674103</v>
+        <v>1.68839764595032</v>
       </c>
       <c r="H818" t="n">
         <v>195439</v>
@@ -24149,7 +24149,7 @@
         <v>1.90600001811981</v>
       </c>
       <c r="G820" t="n">
-        <v>1.71174764633179</v>
+        <v>1.71174776554108</v>
       </c>
       <c r="H820" t="n">
         <v>125176</v>
@@ -24236,7 +24236,7 @@
         <v>1.87600004673004</v>
       </c>
       <c r="G823" t="n">
-        <v>1.68480515480042</v>
+        <v>1.6848052740097</v>
       </c>
       <c r="H823" t="n">
         <v>43015</v>
@@ -24294,7 +24294,7 @@
         <v>1.90600001811981</v>
       </c>
       <c r="G825" t="n">
-        <v>1.71174764633179</v>
+        <v>1.71174776554108</v>
       </c>
       <c r="H825" t="n">
         <v>44756</v>
@@ -24381,7 +24381,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G828" t="n">
-        <v>1.99374616146088</v>
+        <v>1.9937459230423</v>
       </c>
       <c r="H828" t="n">
         <v>356856</v>
@@ -24410,7 +24410,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G829" t="n">
-        <v>2.06559252738953</v>
+        <v>2.06559276580811</v>
       </c>
       <c r="H829" t="n">
         <v>658018</v>
@@ -24526,7 +24526,7 @@
         <v>2.14499998092651</v>
       </c>
       <c r="G833" t="n">
-        <v>1.92638981342316</v>
+        <v>1.92638993263245</v>
       </c>
       <c r="H833" t="n">
         <v>353418</v>
@@ -24555,7 +24555,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G834" t="n">
-        <v>1.99374616146088</v>
+        <v>1.9937459230423</v>
       </c>
       <c r="H834" t="n">
         <v>275786</v>
@@ -24642,7 +24642,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G837" t="n">
-        <v>1.99374616146088</v>
+        <v>1.9937459230423</v>
       </c>
       <c r="H837" t="n">
         <v>72023</v>
@@ -24671,7 +24671,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G838" t="n">
-        <v>2.1374397277832</v>
+        <v>2.13743996620178</v>
       </c>
       <c r="H838" t="n">
         <v>430992</v>
@@ -24700,7 +24700,7 @@
         <v>2.38499999046326</v>
       </c>
       <c r="G839" t="n">
-        <v>2.14192986488342</v>
+        <v>2.141930103302</v>
       </c>
       <c r="H839" t="n">
         <v>449610</v>
@@ -24787,7 +24787,7 @@
         <v>2.33500003814697</v>
       </c>
       <c r="G842" t="n">
-        <v>2.09702587127686</v>
+        <v>2.09702563285828</v>
       </c>
       <c r="H842" t="n">
         <v>111988</v>
@@ -24816,7 +24816,7 @@
         <v>2.33500003814697</v>
       </c>
       <c r="G843" t="n">
-        <v>2.09702587127686</v>
+        <v>2.09702563285828</v>
       </c>
       <c r="H843" t="n">
         <v>46383</v>
@@ -24874,7 +24874,7 @@
         <v>2.39499998092651</v>
       </c>
       <c r="G845" t="n">
-        <v>2.15091061592102</v>
+        <v>2.1509108543396</v>
       </c>
       <c r="H845" t="n">
         <v>87043</v>
@@ -24961,7 +24961,7 @@
         <v>2.38499999046326</v>
       </c>
       <c r="G848" t="n">
-        <v>2.14192986488342</v>
+        <v>2.141930103302</v>
       </c>
       <c r="H848" t="n">
         <v>177569</v>
@@ -25048,7 +25048,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G851" t="n">
-        <v>2.04763102531433</v>
+        <v>2.04763078689575</v>
       </c>
       <c r="H851" t="n">
         <v>566449</v>
@@ -25251,7 +25251,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G858" t="n">
-        <v>2.06110239028931</v>
+        <v>2.06110215187073</v>
       </c>
       <c r="H858" t="n">
         <v>59723</v>
@@ -25425,7 +25425,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G864" t="n">
-        <v>2.06559252738953</v>
+        <v>2.06559276580811</v>
       </c>
       <c r="H864" t="n">
         <v>60672</v>
@@ -25454,7 +25454,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G865" t="n">
-        <v>2.03865051269531</v>
+        <v>2.03865027427673</v>
       </c>
       <c r="H865" t="n">
         <v>76078</v>
@@ -25512,7 +25512,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G867" t="n">
-        <v>2.05661201477051</v>
+        <v>2.05661177635193</v>
       </c>
       <c r="H867" t="n">
         <v>50681</v>
@@ -25570,7 +25570,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G869" t="n">
-        <v>2.06559252738953</v>
+        <v>2.06559276580811</v>
       </c>
       <c r="H869" t="n">
         <v>39249</v>
@@ -25599,7 +25599,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G870" t="n">
-        <v>2.06110239028931</v>
+        <v>2.06110215187073</v>
       </c>
       <c r="H870" t="n">
         <v>52434</v>
@@ -25628,7 +25628,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G871" t="n">
-        <v>2.05661201477051</v>
+        <v>2.05661177635193</v>
       </c>
       <c r="H871" t="n">
         <v>101754</v>
@@ -25657,7 +25657,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G872" t="n">
-        <v>2.05661201477051</v>
+        <v>2.05661177635193</v>
       </c>
       <c r="H872" t="n">
         <v>99626</v>
@@ -25686,7 +25686,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G873" t="n">
-        <v>2.02966952323914</v>
+        <v>2.02966928482056</v>
       </c>
       <c r="H873" t="n">
         <v>45140</v>
@@ -25744,7 +25744,7 @@
         <v>2.22499990463257</v>
       </c>
       <c r="G875" t="n">
-        <v>1.99823617935181</v>
+        <v>1.99823641777039</v>
       </c>
       <c r="H875" t="n">
         <v>31598</v>
@@ -25889,7 +25889,7 @@
         <v>2.01500010490417</v>
       </c>
       <c r="G880" t="n">
-        <v>1.80963897705078</v>
+        <v>1.80963885784149</v>
       </c>
       <c r="H880" t="n">
         <v>97091</v>
@@ -25947,7 +25947,7 @@
         <v>2.02500009536743</v>
       </c>
       <c r="G882" t="n">
-        <v>1.81861984729767</v>
+        <v>1.81861972808838</v>
       </c>
       <c r="H882" t="n">
         <v>71776</v>
@@ -26034,7 +26034,7 @@
         <v>1.96399998664856</v>
       </c>
       <c r="G885" t="n">
-        <v>1.76383662223816</v>
+        <v>1.76383650302887</v>
       </c>
       <c r="H885" t="n">
         <v>93689</v>
@@ -26063,7 +26063,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G886" t="n">
-        <v>1.82311010360718</v>
+        <v>1.82311022281647</v>
       </c>
       <c r="H886" t="n">
         <v>136269</v>
@@ -26092,7 +26092,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G887" t="n">
-        <v>1.82311010360718</v>
+        <v>1.82311022281647</v>
       </c>
       <c r="H887" t="n">
         <v>97372</v>
@@ -26121,7 +26121,7 @@
         <v>2.01500010490417</v>
       </c>
       <c r="G888" t="n">
-        <v>1.80963897705078</v>
+        <v>1.80963885784149</v>
       </c>
       <c r="H888" t="n">
         <v>23086</v>
@@ -26150,7 +26150,7 @@
         <v>2.00500011444092</v>
       </c>
       <c r="G889" t="n">
-        <v>1.80065822601318</v>
+        <v>1.80065810680389</v>
       </c>
       <c r="H889" t="n">
         <v>16944</v>
@@ -26237,7 +26237,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G892" t="n">
-        <v>1.82311010360718</v>
+        <v>1.82311022281647</v>
       </c>
       <c r="H892" t="n">
         <v>56257</v>
@@ -26266,7 +26266,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G893" t="n">
-        <v>1.82311010360718</v>
+        <v>1.82311022281647</v>
       </c>
       <c r="H893" t="n">
         <v>35376</v>
@@ -26295,7 +26295,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G894" t="n">
-        <v>1.80514848232269</v>
+        <v>1.8051483631134</v>
       </c>
       <c r="H894" t="n">
         <v>41837</v>
@@ -26324,7 +26324,7 @@
         <v>2.01500010490417</v>
       </c>
       <c r="G895" t="n">
-        <v>1.80963897705078</v>
+        <v>1.80963885784149</v>
       </c>
       <c r="H895" t="n">
         <v>49791</v>
@@ -26353,7 +26353,7 @@
         <v>1.99600005149841</v>
       </c>
       <c r="G896" t="n">
-        <v>1.79257535934448</v>
+        <v>1.79257524013519</v>
       </c>
       <c r="H896" t="n">
         <v>38649</v>
@@ -26440,7 +26440,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G899" t="n">
-        <v>1.80514848232269</v>
+        <v>1.8051483631134</v>
       </c>
       <c r="H899" t="n">
         <v>40340</v>
@@ -26556,7 +26556,7 @@
         <v>1.89800000190735</v>
       </c>
       <c r="G903" t="n">
-        <v>1.70456314086914</v>
+        <v>1.70456302165985</v>
       </c>
       <c r="H903" t="n">
         <v>82014</v>
@@ -26614,7 +26614,7 @@
         <v>1.92200005054474</v>
       </c>
       <c r="G905" t="n">
-        <v>1.72611713409424</v>
+        <v>1.72611725330353</v>
       </c>
       <c r="H905" t="n">
         <v>31014</v>
@@ -26643,7 +26643,7 @@
         <v>2.1949999332428</v>
       </c>
       <c r="G906" t="n">
-        <v>1.9712940454483</v>
+        <v>1.97129380702972</v>
       </c>
       <c r="H906" t="n">
         <v>1347426</v>
@@ -26730,7 +26730,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G909" t="n">
-        <v>1.99374616146088</v>
+        <v>1.9937459230423</v>
       </c>
       <c r="H909" t="n">
         <v>143618</v>
@@ -26817,7 +26817,7 @@
         <v>2.20499992370605</v>
       </c>
       <c r="G912" t="n">
-        <v>1.98027491569519</v>
+        <v>1.98027467727661</v>
       </c>
       <c r="H912" t="n">
         <v>129711</v>
@@ -26846,7 +26846,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G913" t="n">
-        <v>1.94884204864502</v>
+        <v>1.94884181022644</v>
       </c>
       <c r="H913" t="n">
         <v>69703</v>
@@ -26962,7 +26962,7 @@
         <v>2.14499998092651</v>
       </c>
       <c r="G917" t="n">
-        <v>1.92638981342316</v>
+        <v>1.92638993263245</v>
       </c>
       <c r="H917" t="n">
         <v>16397</v>
@@ -26991,7 +26991,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G918" t="n">
-        <v>1.90393757820129</v>
+        <v>1.90393769741058</v>
       </c>
       <c r="H918" t="n">
         <v>61933</v>
@@ -27020,7 +27020,7 @@
         <v>2.04500007629395</v>
       </c>
       <c r="G919" t="n">
-        <v>1.83658146858215</v>
+        <v>1.83658158779144</v>
       </c>
       <c r="H919" t="n">
         <v>36850</v>
@@ -27136,7 +27136,7 @@
         <v>2.00500011444092</v>
       </c>
       <c r="G923" t="n">
-        <v>1.80065822601318</v>
+        <v>1.80065810680389</v>
       </c>
       <c r="H923" t="n">
         <v>30841</v>
@@ -27426,7 +27426,7 @@
         <v>1.98199999332428</v>
       </c>
       <c r="G933" t="n">
-        <v>1.78000199794769</v>
+        <v>1.78000211715698</v>
       </c>
       <c r="H933" t="n">
         <v>40565</v>
@@ -27571,7 +27571,7 @@
         <v>2.03500008583069</v>
       </c>
       <c r="G938" t="n">
-        <v>1.82760059833527</v>
+        <v>1.82760071754456</v>
       </c>
       <c r="H938" t="n">
         <v>55955</v>
@@ -27600,7 +27600,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G939" t="n">
-        <v>1.83209085464478</v>
+        <v>1.83209097385406</v>
       </c>
       <c r="H939" t="n">
         <v>132643</v>
@@ -27658,7 +27658,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G941" t="n">
-        <v>2.14642024040222</v>
+        <v>2.1464204788208</v>
       </c>
       <c r="H941" t="n">
         <v>788278</v>
@@ -27803,7 +27803,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G946" t="n">
-        <v>2.03865051269531</v>
+        <v>2.03865027427673</v>
       </c>
       <c r="H946" t="n">
         <v>69467</v>
@@ -27919,7 +27919,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G950" t="n">
-        <v>2.03865051269531</v>
+        <v>2.03865027427673</v>
       </c>
       <c r="H950" t="n">
         <v>225593</v>
@@ -28006,7 +28006,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G953" t="n">
-        <v>2.05661201477051</v>
+        <v>2.05661177635193</v>
       </c>
       <c r="H953" t="n">
         <v>222591</v>
@@ -28122,7 +28122,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G957" t="n">
-        <v>1.99374616146088</v>
+        <v>1.9937459230423</v>
       </c>
       <c r="H957" t="n">
         <v>144899</v>
@@ -28267,7 +28267,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G962" t="n">
-        <v>1.99374616146088</v>
+        <v>1.9937459230423</v>
       </c>
       <c r="H962" t="n">
         <v>97941</v>
@@ -28354,7 +28354,7 @@
         <v>2.40499997138977</v>
       </c>
       <c r="G965" t="n">
-        <v>2.15989136695862</v>
+        <v>2.1598916053772</v>
       </c>
       <c r="H965" t="n">
         <v>192266</v>
@@ -28441,7 +28441,7 @@
         <v>2.40499997138977</v>
       </c>
       <c r="G968" t="n">
-        <v>2.15989136695862</v>
+        <v>2.1598916053772</v>
       </c>
       <c r="H968" t="n">
         <v>88063</v>
@@ -28528,7 +28528,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G971" t="n">
-        <v>2.05661201477051</v>
+        <v>2.05661177635193</v>
       </c>
       <c r="H971" t="n">
         <v>150831</v>
@@ -28557,7 +28557,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G972" t="n">
-        <v>2.06559252738953</v>
+        <v>2.06559276580811</v>
       </c>
       <c r="H972" t="n">
         <v>79359</v>
@@ -28644,7 +28644,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G975" t="n">
-        <v>2.14642024040222</v>
+        <v>2.1464204788208</v>
       </c>
       <c r="H975" t="n">
         <v>267078</v>
@@ -28702,7 +28702,7 @@
         <v>2.51500010490417</v>
       </c>
       <c r="G977" t="n">
-        <v>2.25868105888367</v>
+        <v>2.25868082046509</v>
       </c>
       <c r="H977" t="n">
         <v>224235</v>
@@ -28789,7 +28789,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G980" t="n">
-        <v>2.49667286872864</v>
+        <v>2.49667310714722</v>
       </c>
       <c r="H980" t="n">
         <v>824891</v>
@@ -29137,7 +29137,7 @@
         <v>2.99499988555908</v>
       </c>
       <c r="G992" t="n">
-        <v>2.6897611618042</v>
+        <v>2.68976092338562</v>
       </c>
       <c r="H992" t="n">
         <v>444636</v>
@@ -29340,7 +29340,7 @@
         <v>2.99499988555908</v>
       </c>
       <c r="G999" t="n">
-        <v>2.6897611618042</v>
+        <v>2.68976092338562</v>
       </c>
       <c r="H999" t="n">
         <v>433029</v>
@@ -29369,7 +29369,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1000" t="n">
-        <v>2.75711750984192</v>
+        <v>2.75711727142334</v>
       </c>
       <c r="H1000" t="n">
         <v>197667</v>
@@ -29630,7 +29630,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1009" t="n">
-        <v>2.66730880737305</v>
+        <v>2.66730904579163</v>
       </c>
       <c r="H1009" t="n">
         <v>156751</v>
@@ -29833,7 +29833,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1016" t="n">
-        <v>2.75711750984192</v>
+        <v>2.75711727142334</v>
       </c>
       <c r="H1016" t="n">
         <v>97347</v>
@@ -29862,7 +29862,7 @@
         <v>2.99499988555908</v>
       </c>
       <c r="G1017" t="n">
-        <v>2.6897611618042</v>
+        <v>2.68976092338562</v>
       </c>
       <c r="H1017" t="n">
         <v>117891</v>
@@ -29949,7 +29949,7 @@
         <v>2.88499999046326</v>
       </c>
       <c r="G1020" t="n">
-        <v>2.59097170829773</v>
+        <v>2.59097194671631</v>
       </c>
       <c r="H1020" t="n">
         <v>113704</v>
@@ -29978,7 +29978,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1021" t="n">
-        <v>2.66730880737305</v>
+        <v>2.66730904579163</v>
       </c>
       <c r="H1021" t="n">
         <v>104777</v>
@@ -30065,7 +30065,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1024" t="n">
-        <v>3.06246566772461</v>
+        <v>3.06246590614319</v>
       </c>
       <c r="H1024" t="n">
         <v>1270615</v>
@@ -30210,7 +30210,7 @@
         <v>3.6949999332428</v>
       </c>
       <c r="G1029" t="n">
-        <v>3.31841969490051</v>
+        <v>3.31841993331909</v>
       </c>
       <c r="H1029" t="n">
         <v>1089635</v>
@@ -30239,7 +30239,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G1030" t="n">
-        <v>3.28249621391296</v>
+        <v>3.28249645233154</v>
       </c>
       <c r="H1030" t="n">
         <v>790910</v>
@@ -30297,7 +30297,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1032" t="n">
-        <v>3.07144641876221</v>
+        <v>3.07144665718079</v>
       </c>
       <c r="H1032" t="n">
         <v>369627</v>
@@ -30471,7 +30471,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1038" t="n">
-        <v>3.07144641876221</v>
+        <v>3.07144665718079</v>
       </c>
       <c r="H1038" t="n">
         <v>182313</v>
@@ -30587,7 +30587,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1042" t="n">
-        <v>3.2420825958252</v>
+        <v>3.24208235740662</v>
       </c>
       <c r="H1042" t="n">
         <v>857496</v>
@@ -30616,7 +30616,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G1043" t="n">
-        <v>3.29147696495056</v>
+        <v>3.29147720336914</v>
       </c>
       <c r="H1043" t="n">
         <v>415306</v>
@@ -30732,7 +30732,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1047" t="n">
-        <v>3.25106310844421</v>
+        <v>3.25106334686279</v>
       </c>
       <c r="H1047" t="n">
         <v>355854</v>
@@ -31051,7 +31051,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G1058" t="n">
-        <v>2.77058887481689</v>
+        <v>2.77058863639832</v>
       </c>
       <c r="H1058" t="n">
         <v>520479</v>
@@ -31196,7 +31196,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G1063" t="n">
-        <v>2.30807542800903</v>
+        <v>2.30807518959045</v>
       </c>
       <c r="H1063" t="n">
         <v>452760</v>
@@ -31225,7 +31225,7 @@
         <v>2.45499992370605</v>
       </c>
       <c r="G1064" t="n">
-        <v>2.20479559898376</v>
+        <v>2.20479583740234</v>
       </c>
       <c r="H1064" t="n">
         <v>236307</v>
@@ -31254,7 +31254,7 @@
         <v>2.39499998092651</v>
       </c>
       <c r="G1065" t="n">
-        <v>2.15091061592102</v>
+        <v>2.1509108543396</v>
       </c>
       <c r="H1065" t="n">
         <v>184356</v>
@@ -31515,7 +31515,7 @@
         <v>2.16499996185303</v>
       </c>
       <c r="G1074" t="n">
-        <v>1.94435143470764</v>
+        <v>1.94435131549835</v>
       </c>
       <c r="H1074" t="n">
         <v>152523</v>
@@ -31544,7 +31544,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1075" t="n">
-        <v>2.04763102531433</v>
+        <v>2.04763078689575</v>
       </c>
       <c r="H1075" t="n">
         <v>195849</v>
@@ -31573,7 +31573,7 @@
         <v>2.375</v>
       </c>
       <c r="G1076" t="n">
-        <v>2.13294887542725</v>
+        <v>2.13294911384583</v>
       </c>
       <c r="H1076" t="n">
         <v>100585</v>
@@ -31660,7 +31660,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1079" t="n">
-        <v>2.04763102531433</v>
+        <v>2.04763078689575</v>
       </c>
       <c r="H1079" t="n">
         <v>150042</v>
@@ -31747,7 +31747,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1082" t="n">
-        <v>2.26317119598389</v>
+        <v>2.26317143440247</v>
       </c>
       <c r="H1082" t="n">
         <v>269717</v>
@@ -31776,7 +31776,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G1083" t="n">
-        <v>2.30807542800903</v>
+        <v>2.30807518959045</v>
       </c>
       <c r="H1083" t="n">
         <v>299039</v>
@@ -31805,7 +31805,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1084" t="n">
-        <v>2.45176887512207</v>
+        <v>2.45176863670349</v>
       </c>
       <c r="H1084" t="n">
         <v>180092</v>
@@ -31834,7 +31834,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1085" t="n">
-        <v>2.45176887512207</v>
+        <v>2.45176863670349</v>
       </c>
       <c r="H1085" t="n">
         <v>125425</v>
@@ -31863,7 +31863,7 @@
         <v>2.75</v>
       </c>
       <c r="G1086" t="n">
-        <v>2.46973061561584</v>
+        <v>2.46973037719727</v>
       </c>
       <c r="H1086" t="n">
         <v>195527</v>
@@ -31892,7 +31892,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1087" t="n">
-        <v>2.53259611129761</v>
+        <v>2.53259634971619</v>
       </c>
       <c r="H1087" t="n">
         <v>56325</v>
@@ -31921,7 +31921,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1088" t="n">
-        <v>2.44278812408447</v>
+        <v>2.44278788566589</v>
       </c>
       <c r="H1088" t="n">
         <v>121140</v>
@@ -31950,7 +31950,7 @@
         <v>2.68499994277954</v>
       </c>
       <c r="G1089" t="n">
-        <v>2.4113552570343</v>
+        <v>2.41135501861572</v>
       </c>
       <c r="H1089" t="n">
         <v>103564</v>
@@ -32211,7 +32211,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1098" t="n">
-        <v>2.65832805633545</v>
+        <v>2.65832829475403</v>
       </c>
       <c r="H1098" t="n">
         <v>64040</v>
@@ -32414,7 +32414,7 @@
         <v>2.85500001907349</v>
       </c>
       <c r="G1105" t="n">
-        <v>2.56402921676636</v>
+        <v>2.56402945518494</v>
       </c>
       <c r="H1105" t="n">
         <v>19825</v>
@@ -32704,7 +32704,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G1115" t="n">
-        <v>2.52810597419739</v>
+        <v>2.52810621261597</v>
       </c>
       <c r="H1115" t="n">
         <v>47937</v>
@@ -32820,7 +32820,7 @@
         <v>2.89499998092651</v>
       </c>
       <c r="G1119" t="n">
-        <v>2.59995245933533</v>
+        <v>2.59995269775391</v>
       </c>
       <c r="H1119" t="n">
         <v>36216</v>
@@ -32849,7 +32849,7 @@
         <v>2.89499998092651</v>
       </c>
       <c r="G1120" t="n">
-        <v>2.59995245933533</v>
+        <v>2.59995269775391</v>
       </c>
       <c r="H1120" t="n">
         <v>33908</v>
@@ -33052,7 +33052,7 @@
         <v>2.99499988555908</v>
       </c>
       <c r="G1127" t="n">
-        <v>2.6897611618042</v>
+        <v>2.68976092338562</v>
       </c>
       <c r="H1127" t="n">
         <v>113781</v>
@@ -33081,7 +33081,7 @@
         <v>2.85500001907349</v>
       </c>
       <c r="G1128" t="n">
-        <v>2.56402921676636</v>
+        <v>2.56402945518494</v>
       </c>
       <c r="H1128" t="n">
         <v>145315</v>
@@ -33139,7 +33139,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1130" t="n">
-        <v>2.53259611129761</v>
+        <v>2.53259634971619</v>
       </c>
       <c r="H1130" t="n">
         <v>64525</v>
@@ -33197,7 +33197,7 @@
         <v>2.85500001907349</v>
       </c>
       <c r="G1132" t="n">
-        <v>2.56402921676636</v>
+        <v>2.56402945518494</v>
       </c>
       <c r="H1132" t="n">
         <v>49511</v>
@@ -33371,7 +33371,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G1138" t="n">
-        <v>2.50565361976624</v>
+        <v>2.50565385818481</v>
       </c>
       <c r="H1138" t="n">
         <v>45132</v>
@@ -33429,7 +33429,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1140" t="n">
-        <v>2.44278812408447</v>
+        <v>2.44278788566589</v>
       </c>
       <c r="H1140" t="n">
         <v>27100</v>
@@ -33487,7 +33487,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1142" t="n">
-        <v>2.4338071346283</v>
+        <v>2.43380689620972</v>
       </c>
       <c r="H1142" t="n">
         <v>35299</v>
@@ -33574,7 +33574,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1145" t="n">
-        <v>2.47871136665344</v>
+        <v>2.47871112823486</v>
       </c>
       <c r="H1145" t="n">
         <v>106981</v>
@@ -33603,7 +33603,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1146" t="n">
-        <v>2.45176887512207</v>
+        <v>2.45176863670349</v>
       </c>
       <c r="H1146" t="n">
         <v>36667</v>
@@ -33632,7 +33632,7 @@
         <v>2.75</v>
       </c>
       <c r="G1147" t="n">
-        <v>2.46973061561584</v>
+        <v>2.46973037719727</v>
       </c>
       <c r="H1147" t="n">
         <v>26371</v>
@@ -33864,7 +33864,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1155" t="n">
-        <v>2.53259611129761</v>
+        <v>2.53259634971619</v>
       </c>
       <c r="H1155" t="n">
         <v>33920</v>
@@ -33922,7 +33922,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1157" t="n">
-        <v>2.45176887512207</v>
+        <v>2.45176863670349</v>
       </c>
       <c r="H1157" t="n">
         <v>21286</v>
@@ -34154,7 +34154,7 @@
         <v>2.64499998092651</v>
       </c>
       <c r="G1165" t="n">
-        <v>2.37543177604675</v>
+        <v>2.37543153762817</v>
       </c>
       <c r="H1165" t="n">
         <v>40838</v>
@@ -34270,7 +34270,7 @@
         <v>2.54500007629395</v>
       </c>
       <c r="G1169" t="n">
-        <v>2.28562331199646</v>
+        <v>2.28562355041504</v>
       </c>
       <c r="H1169" t="n">
         <v>18461</v>
@@ -34415,7 +34415,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1174" t="n">
-        <v>2.44278812408447</v>
+        <v>2.44278788566589</v>
       </c>
       <c r="H1174" t="n">
         <v>33942</v>
@@ -34444,7 +34444,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1175" t="n">
-        <v>2.47871136665344</v>
+        <v>2.47871112823486</v>
       </c>
       <c r="H1175" t="n">
         <v>9626</v>
@@ -34763,7 +34763,7 @@
         <v>2.65499997138977</v>
       </c>
       <c r="G1186" t="n">
-        <v>2.38441252708435</v>
+        <v>2.38441228866577</v>
       </c>
       <c r="H1186" t="n">
         <v>20906</v>
@@ -34966,7 +34966,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1193" t="n">
-        <v>2.4338071346283</v>
+        <v>2.43380689620972</v>
       </c>
       <c r="H1193" t="n">
         <v>34787</v>
@@ -35024,7 +35024,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G1195" t="n">
-        <v>2.49667286872864</v>
+        <v>2.49667310714722</v>
       </c>
       <c r="H1195" t="n">
         <v>52126</v>
@@ -35488,7 +35488,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G1211" t="n">
-        <v>2.32603716850281</v>
+        <v>2.32603693008423</v>
       </c>
       <c r="H1211" t="n">
         <v>41706</v>
@@ -35633,7 +35633,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G1216" t="n">
-        <v>2.32603716850281</v>
+        <v>2.32603693008423</v>
       </c>
       <c r="H1216" t="n">
         <v>32139</v>
@@ -35691,7 +35691,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G1218" t="n">
-        <v>2.49667286872864</v>
+        <v>2.49667310714722</v>
       </c>
       <c r="H1218" t="n">
         <v>177616</v>
@@ -35749,7 +35749,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1220" t="n">
-        <v>2.53259611129761</v>
+        <v>2.53259634971619</v>
       </c>
       <c r="H1220" t="n">
         <v>103554</v>
@@ -35865,7 +35865,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1224" t="n">
-        <v>2.53259611129761</v>
+        <v>2.53259634971619</v>
       </c>
       <c r="H1224" t="n">
         <v>27341</v>
@@ -35894,7 +35894,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1225" t="n">
-        <v>2.4338071346283</v>
+        <v>2.43380689620972</v>
       </c>
       <c r="H1225" t="n">
         <v>47298</v>
@@ -36213,7 +36213,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1236" t="n">
-        <v>2.4338071346283</v>
+        <v>2.43380689620972</v>
       </c>
       <c r="H1236" t="n">
         <v>55259</v>
@@ -36300,7 +36300,7 @@
         <v>2.75</v>
       </c>
       <c r="G1239" t="n">
-        <v>2.46973061561584</v>
+        <v>2.46973037719727</v>
       </c>
       <c r="H1239" t="n">
         <v>170299</v>
@@ -36329,7 +36329,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1240" t="n">
-        <v>2.45176887512207</v>
+        <v>2.45176863670349</v>
       </c>
       <c r="H1240" t="n">
         <v>59133</v>
@@ -36358,7 +36358,7 @@
         <v>2.64499998092651</v>
       </c>
       <c r="G1241" t="n">
-        <v>2.37543177604675</v>
+        <v>2.37543153762817</v>
       </c>
       <c r="H1241" t="n">
         <v>101736</v>
@@ -36416,7 +36416,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1243" t="n">
-        <v>2.47871136665344</v>
+        <v>2.47871112823486</v>
       </c>
       <c r="H1243" t="n">
         <v>123604</v>
@@ -36445,7 +36445,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1244" t="n">
-        <v>2.44278812408447</v>
+        <v>2.44278788566589</v>
       </c>
       <c r="H1244" t="n">
         <v>27951</v>
@@ -36474,7 +36474,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1245" t="n">
-        <v>2.44278812408447</v>
+        <v>2.44278788566589</v>
       </c>
       <c r="H1245" t="n">
         <v>153595</v>
@@ -36503,7 +36503,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1246" t="n">
-        <v>2.53259611129761</v>
+        <v>2.53259634971619</v>
       </c>
       <c r="H1246" t="n">
         <v>129020</v>
@@ -36590,7 +36590,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1249" t="n">
-        <v>2.53259611129761</v>
+        <v>2.53259634971619</v>
       </c>
       <c r="H1249" t="n">
         <v>31429</v>
@@ -36648,7 +36648,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1251" t="n">
-        <v>2.65832805633545</v>
+        <v>2.65832829475403</v>
       </c>
       <c r="H1251" t="n">
         <v>125447</v>
@@ -36996,7 +36996,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1263" t="n">
-        <v>2.84692573547363</v>
+        <v>2.84692549705505</v>
       </c>
       <c r="H1263" t="n">
         <v>142485</v>
@@ -37025,7 +37025,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1264" t="n">
-        <v>2.83794498443604</v>
+        <v>2.83794474601746</v>
       </c>
       <c r="H1264" t="n">
         <v>41471</v>
@@ -37083,7 +37083,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G1266" t="n">
-        <v>2.77058887481689</v>
+        <v>2.77058863639832</v>
       </c>
       <c r="H1266" t="n">
         <v>25826</v>
@@ -37112,7 +37112,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1267" t="n">
-        <v>2.75711750984192</v>
+        <v>2.75711727142334</v>
       </c>
       <c r="H1267" t="n">
         <v>21704</v>
@@ -37199,7 +37199,7 @@
         <v>3.09500002861023</v>
       </c>
       <c r="G1270" t="n">
-        <v>2.77956938743591</v>
+        <v>2.77956914901733</v>
       </c>
       <c r="H1270" t="n">
         <v>26814</v>
@@ -37344,7 +37344,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G1275" t="n">
-        <v>2.77058887481689</v>
+        <v>2.77058863639832</v>
       </c>
       <c r="H1275" t="n">
         <v>28281</v>
@@ -37431,7 +37431,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1278" t="n">
-        <v>2.75711750984192</v>
+        <v>2.75711727142334</v>
       </c>
       <c r="H1278" t="n">
         <v>35383</v>
@@ -37547,7 +37547,7 @@
         <v>2.99499988555908</v>
       </c>
       <c r="G1282" t="n">
-        <v>2.6897611618042</v>
+        <v>2.68976092338562</v>
       </c>
       <c r="H1282" t="n">
         <v>28506</v>
@@ -37692,7 +37692,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1287" t="n">
-        <v>2.65832805633545</v>
+        <v>2.65832829475403</v>
       </c>
       <c r="H1287" t="n">
         <v>57291</v>
@@ -38069,7 +38069,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G1300" t="n">
-        <v>3.12982177734375</v>
+        <v>3.12982201576233</v>
       </c>
       <c r="H1300" t="n">
         <v>478492</v>
@@ -38214,7 +38214,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G1305" t="n">
-        <v>3.12982177734375</v>
+        <v>3.12982201576233</v>
       </c>
       <c r="H1305" t="n">
         <v>68636</v>
@@ -38243,7 +38243,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1306" t="n">
-        <v>3.16125512123108</v>
+        <v>3.1612548828125</v>
       </c>
       <c r="H1306" t="n">
         <v>84232</v>
@@ -38330,7 +38330,7 @@
         <v>3.33500003814697</v>
       </c>
       <c r="G1309" t="n">
-        <v>2.99510955810547</v>
+        <v>2.99510979652405</v>
       </c>
       <c r="H1309" t="n">
         <v>53098</v>
@@ -38504,7 +38504,7 @@
         <v>3.32500004768372</v>
       </c>
       <c r="G1315" t="n">
-        <v>2.98612856864929</v>
+        <v>2.98612880706787</v>
       </c>
       <c r="H1315" t="n">
         <v>58543</v>
@@ -38678,7 +38678,7 @@
         <v>3.39499998092651</v>
       </c>
       <c r="G1321" t="n">
-        <v>3.04899430274963</v>
+        <v>3.04899454116821</v>
       </c>
       <c r="H1321" t="n">
         <v>39687</v>
@@ -38881,7 +38881,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1328" t="n">
-        <v>3.06246566772461</v>
+        <v>3.06246590614319</v>
       </c>
       <c r="H1328" t="n">
         <v>66262</v>
@@ -38910,7 +38910,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1329" t="n">
-        <v>3.0355236530304</v>
+        <v>3.03552341461182</v>
       </c>
       <c r="H1329" t="n">
         <v>26407</v>
@@ -38939,7 +38939,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1330" t="n">
-        <v>3.04450440406799</v>
+        <v>3.04450416564941</v>
       </c>
       <c r="H1330" t="n">
         <v>22740</v>
@@ -39026,7 +39026,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1333" t="n">
-        <v>3.0355236530304</v>
+        <v>3.03552341461182</v>
       </c>
       <c r="H1333" t="n">
         <v>51435</v>
@@ -39084,7 +39084,7 @@
         <v>3.31500005722046</v>
       </c>
       <c r="G1335" t="n">
-        <v>2.97714805603027</v>
+        <v>2.97714781761169</v>
       </c>
       <c r="H1335" t="n">
         <v>132492</v>
@@ -39374,7 +39374,7 @@
         <v>3.14499998092651</v>
       </c>
       <c r="G1345" t="n">
-        <v>2.82447361946106</v>
+        <v>2.82447338104248</v>
       </c>
       <c r="H1345" t="n">
         <v>74454</v>
@@ -39432,7 +39432,7 @@
         <v>3.25</v>
       </c>
       <c r="G1347" t="n">
-        <v>2.91877245903015</v>
+        <v>2.91877269744873</v>
       </c>
       <c r="H1347" t="n">
         <v>190767</v>
@@ -39461,7 +39461,7 @@
         <v>3.34500002861023</v>
       </c>
       <c r="G1348" t="n">
-        <v>3.00409030914307</v>
+        <v>3.00409054756165</v>
       </c>
       <c r="H1348" t="n">
         <v>247027</v>
@@ -39519,7 +39519,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1350" t="n">
-        <v>3.06246566772461</v>
+        <v>3.06246590614319</v>
       </c>
       <c r="H1350" t="n">
         <v>234892</v>
@@ -39664,7 +39664,7 @@
         <v>3.4449999332428</v>
       </c>
       <c r="G1355" t="n">
-        <v>3.09389901161194</v>
+        <v>3.09389877319336</v>
       </c>
       <c r="H1355" t="n">
         <v>111458</v>
@@ -39722,7 +39722,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G1357" t="n">
-        <v>3.28249621391296</v>
+        <v>3.28249645233154</v>
       </c>
       <c r="H1357" t="n">
         <v>306265</v>
@@ -39809,7 +39809,7 @@
         <v>3.60500001907349</v>
       </c>
       <c r="G1360" t="n">
-        <v>3.2375922203064</v>
+        <v>3.23759198188782</v>
       </c>
       <c r="H1360" t="n">
         <v>186639</v>
@@ -39838,7 +39838,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G1361" t="n">
-        <v>3.29147696495056</v>
+        <v>3.29147720336914</v>
       </c>
       <c r="H1361" t="n">
         <v>67450</v>
@@ -39954,7 +39954,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G1365" t="n">
-        <v>3.2196307182312</v>
+        <v>3.21963047981262</v>
       </c>
       <c r="H1365" t="n">
         <v>49179</v>
@@ -40012,7 +40012,7 @@
         <v>3.46499991416931</v>
       </c>
       <c r="G1367" t="n">
-        <v>3.11186027526855</v>
+        <v>3.11186003684998</v>
       </c>
       <c r="H1367" t="n">
         <v>44147</v>
@@ -40041,7 +40041,7 @@
         <v>3.46499991416931</v>
       </c>
       <c r="G1368" t="n">
-        <v>3.11186027526855</v>
+        <v>3.11186003684998</v>
       </c>
       <c r="H1368" t="n">
         <v>26420</v>
@@ -40186,7 +40186,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1373" t="n">
-        <v>3.04450440406799</v>
+        <v>3.04450416564941</v>
       </c>
       <c r="H1373" t="n">
         <v>45517</v>
@@ -40244,7 +40244,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1375" t="n">
-        <v>3.04450440406799</v>
+        <v>3.04450416564941</v>
       </c>
       <c r="H1375" t="n">
         <v>56229</v>
@@ -40273,7 +40273,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1376" t="n">
-        <v>3.07144641876221</v>
+        <v>3.07144665718079</v>
       </c>
       <c r="H1376" t="n">
         <v>20384</v>
@@ -40360,7 +40360,7 @@
         <v>3.4449999332428</v>
       </c>
       <c r="G1379" t="n">
-        <v>3.09389901161194</v>
+        <v>3.09389877319336</v>
       </c>
       <c r="H1379" t="n">
         <v>56458</v>
@@ -40418,7 +40418,7 @@
         <v>3.39499998092651</v>
       </c>
       <c r="G1381" t="n">
-        <v>3.04899430274963</v>
+        <v>3.04899454116821</v>
       </c>
       <c r="H1381" t="n">
         <v>19913</v>
@@ -40447,7 +40447,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1382" t="n">
-        <v>3.04450440406799</v>
+        <v>3.04450416564941</v>
       </c>
       <c r="H1382" t="n">
         <v>59524</v>
@@ -40679,7 +40679,7 @@
         <v>3.33500003814697</v>
       </c>
       <c r="G1390" t="n">
-        <v>2.99510955810547</v>
+        <v>2.99510979652405</v>
       </c>
       <c r="H1390" t="n">
         <v>26650</v>
@@ -40708,7 +40708,7 @@
         <v>3.32500004768372</v>
       </c>
       <c r="G1391" t="n">
-        <v>2.98612856864929</v>
+        <v>2.98612880706787</v>
       </c>
       <c r="H1391" t="n">
         <v>31786</v>
@@ -40795,7 +40795,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1394" t="n">
-        <v>2.92775297164917</v>
+        <v>2.92775321006775</v>
       </c>
       <c r="H1394" t="n">
         <v>42784</v>
@@ -40824,7 +40824,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G1395" t="n">
-        <v>3.2196307182312</v>
+        <v>3.21963047981262</v>
       </c>
       <c r="H1395" t="n">
         <v>629617</v>
@@ -40911,7 +40911,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1398" t="n">
-        <v>3.23310160636902</v>
+        <v>3.23310136795044</v>
       </c>
       <c r="H1398" t="n">
         <v>59128</v>
@@ -40940,7 +40940,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1399" t="n">
-        <v>3.25106310844421</v>
+        <v>3.25106334686279</v>
       </c>
       <c r="H1399" t="n">
         <v>41825</v>
@@ -41085,7 +41085,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1404" t="n">
-        <v>3.04450440406799</v>
+        <v>3.04450416564941</v>
       </c>
       <c r="H1404" t="n">
         <v>19864</v>
@@ -41114,7 +41114,7 @@
         <v>3.39499998092651</v>
       </c>
       <c r="G1405" t="n">
-        <v>3.04899430274963</v>
+        <v>3.04899454116821</v>
       </c>
       <c r="H1405" t="n">
         <v>24332</v>
@@ -41172,7 +41172,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1407" t="n">
-        <v>3.04450440406799</v>
+        <v>3.04450416564941</v>
       </c>
       <c r="H1407" t="n">
         <v>30149</v>
@@ -41375,7 +41375,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1414" t="n">
-        <v>3.04450440406799</v>
+        <v>3.04450416564941</v>
       </c>
       <c r="H1414" t="n">
         <v>68643</v>
@@ -41404,7 +41404,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1415" t="n">
-        <v>3.06246566772461</v>
+        <v>3.06246590614319</v>
       </c>
       <c r="H1415" t="n">
         <v>74893</v>
@@ -41491,7 +41491,7 @@
         <v>3.34500002861023</v>
       </c>
       <c r="G1418" t="n">
-        <v>3.00409030914307</v>
+        <v>3.00409054756165</v>
       </c>
       <c r="H1418" t="n">
         <v>187546</v>
@@ -41578,7 +41578,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1421" t="n">
-        <v>2.94571471214294</v>
+        <v>2.94571495056152</v>
       </c>
       <c r="H1421" t="n">
         <v>12821</v>
@@ -41694,7 +41694,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1425" t="n">
-        <v>2.94571471214294</v>
+        <v>2.94571495056152</v>
       </c>
       <c r="H1425" t="n">
         <v>32445</v>
@@ -41839,7 +41839,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1430" t="n">
-        <v>3.04450440406799</v>
+        <v>3.04450416564941</v>
       </c>
       <c r="H1430" t="n">
         <v>150925</v>
@@ -41897,7 +41897,7 @@
         <v>3.33500003814697</v>
       </c>
       <c r="G1432" t="n">
-        <v>2.99510955810547</v>
+        <v>2.99510979652405</v>
       </c>
       <c r="H1432" t="n">
         <v>100309</v>
@@ -42013,7 +42013,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1436" t="n">
-        <v>2.93673396110535</v>
+        <v>2.93673419952393</v>
       </c>
       <c r="H1436" t="n">
         <v>21907</v>
@@ -42042,7 +42042,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1437" t="n">
-        <v>2.93673396110535</v>
+        <v>2.93673419952393</v>
       </c>
       <c r="H1437" t="n">
         <v>22159</v>
@@ -42071,7 +42071,7 @@
         <v>3.25</v>
       </c>
       <c r="G1438" t="n">
-        <v>2.91877245903015</v>
+        <v>2.91877269744873</v>
       </c>
       <c r="H1438" t="n">
         <v>18524</v>
@@ -42100,7 +42100,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1439" t="n">
-        <v>2.93673396110535</v>
+        <v>2.93673419952393</v>
       </c>
       <c r="H1439" t="n">
         <v>17042</v>
@@ -42129,7 +42129,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1440" t="n">
-        <v>2.92775297164917</v>
+        <v>2.92775321006775</v>
       </c>
       <c r="H1440" t="n">
         <v>40694</v>
@@ -42216,7 +42216,7 @@
         <v>3.31500005722046</v>
       </c>
       <c r="G1443" t="n">
-        <v>2.97714805603027</v>
+        <v>2.97714781761169</v>
       </c>
       <c r="H1443" t="n">
         <v>79496</v>
@@ -42245,7 +42245,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1444" t="n">
-        <v>2.94571471214294</v>
+        <v>2.94571495056152</v>
       </c>
       <c r="H1444" t="n">
         <v>26595</v>
@@ -42274,7 +42274,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1445" t="n">
-        <v>2.93673396110535</v>
+        <v>2.93673419952393</v>
       </c>
       <c r="H1445" t="n">
         <v>16752</v>
@@ -42303,7 +42303,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1446" t="n">
-        <v>2.92775297164917</v>
+        <v>2.92775321006775</v>
       </c>
       <c r="H1446" t="n">
         <v>48629</v>
@@ -42332,7 +42332,7 @@
         <v>3.25500011444092</v>
       </c>
       <c r="G1447" t="n">
-        <v>2.92326283454895</v>
+        <v>2.92326307296753</v>
       </c>
       <c r="H1447" t="n">
         <v>26505</v>
@@ -42361,7 +42361,7 @@
         <v>3.25</v>
       </c>
       <c r="G1448" t="n">
-        <v>2.91877245903015</v>
+        <v>2.91877269744873</v>
       </c>
       <c r="H1448" t="n">
         <v>29830</v>
@@ -42564,7 +42564,7 @@
         <v>3.15499997138977</v>
       </c>
       <c r="G1455" t="n">
-        <v>2.83345460891724</v>
+        <v>2.83345437049866</v>
       </c>
       <c r="H1455" t="n">
         <v>72257</v>
@@ -42651,7 +42651,7 @@
         <v>3.25</v>
       </c>
       <c r="G1458" t="n">
-        <v>2.91877245903015</v>
+        <v>2.91877269744873</v>
       </c>
       <c r="H1458" t="n">
         <v>79827</v>
@@ -42767,7 +42767,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1462" t="n">
-        <v>3.06246566772461</v>
+        <v>3.06246590614319</v>
       </c>
       <c r="H1462" t="n">
         <v>37649</v>
@@ -42970,7 +42970,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1469" t="n">
-        <v>2.92775297164917</v>
+        <v>2.92775321006775</v>
       </c>
       <c r="H1469" t="n">
         <v>40905</v>
@@ -43028,7 +43028,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1471" t="n">
-        <v>2.94571471214294</v>
+        <v>2.94571495056152</v>
       </c>
       <c r="H1471" t="n">
         <v>10322</v>
@@ -43057,7 +43057,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1472" t="n">
-        <v>3.06246566772461</v>
+        <v>3.06246590614319</v>
       </c>
       <c r="H1472" t="n">
         <v>107887</v>
@@ -43173,7 +43173,7 @@
         <v>3.45499992370605</v>
       </c>
       <c r="G1476" t="n">
-        <v>3.10287952423096</v>
+        <v>3.10287928581238</v>
       </c>
       <c r="H1476" t="n">
         <v>37566</v>
@@ -43318,7 +43318,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1481" t="n">
-        <v>3.26902508735657</v>
+        <v>3.26902532577515</v>
       </c>
       <c r="H1481" t="n">
         <v>454970</v>
@@ -43405,7 +43405,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1484" t="n">
-        <v>3.23310160636902</v>
+        <v>3.23310136795044</v>
       </c>
       <c r="H1484" t="n">
         <v>33548</v>
@@ -43434,7 +43434,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1485" t="n">
-        <v>3.1522741317749</v>
+        <v>3.15227389335632</v>
       </c>
       <c r="H1485" t="n">
         <v>62833</v>
@@ -43550,7 +43550,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1489" t="n">
-        <v>3.23310160636902</v>
+        <v>3.23310136795044</v>
       </c>
       <c r="H1489" t="n">
         <v>64124</v>
@@ -43579,7 +43579,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1490" t="n">
-        <v>3.23310160636902</v>
+        <v>3.23310136795044</v>
       </c>
       <c r="H1490" t="n">
         <v>118491</v>
@@ -43608,7 +43608,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1491" t="n">
-        <v>3.23310160636902</v>
+        <v>3.23310136795044</v>
       </c>
       <c r="H1491" t="n">
         <v>47687</v>
@@ -43666,7 +43666,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1493" t="n">
-        <v>3.2420825958252</v>
+        <v>3.24208235740662</v>
       </c>
       <c r="H1493" t="n">
         <v>22719</v>
@@ -43724,7 +43724,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1495" t="n">
-        <v>3.2420825958252</v>
+        <v>3.24208235740662</v>
       </c>
       <c r="H1495" t="n">
         <v>73201</v>
@@ -44101,7 +44101,7 @@
         <v>3.46499991416931</v>
       </c>
       <c r="G1508" t="n">
-        <v>3.11186027526855</v>
+        <v>3.11186003684998</v>
       </c>
       <c r="H1508" t="n">
         <v>30944</v>
@@ -44130,7 +44130,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1509" t="n">
-        <v>3.06246566772461</v>
+        <v>3.06246590614319</v>
       </c>
       <c r="H1509" t="n">
         <v>24521</v>
@@ -44449,7 +44449,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1520" t="n">
-        <v>3.25106310844421</v>
+        <v>3.25106334686279</v>
       </c>
       <c r="H1520" t="n">
         <v>128848</v>
@@ -44536,7 +44536,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1523" t="n">
-        <v>3.25106310844421</v>
+        <v>3.25106334686279</v>
       </c>
       <c r="H1523" t="n">
         <v>18299</v>
@@ -44565,7 +44565,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1524" t="n">
-        <v>3.26902508735657</v>
+        <v>3.26902532577515</v>
       </c>
       <c r="H1524" t="n">
         <v>25489</v>
@@ -44623,7 +44623,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G1526" t="n">
-        <v>3.27351522445679</v>
+        <v>3.27351546287537</v>
       </c>
       <c r="H1526" t="n">
         <v>105095</v>
@@ -44710,7 +44710,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1529" t="n">
-        <v>3.26902508735657</v>
+        <v>3.26902532577515</v>
       </c>
       <c r="H1529" t="n">
         <v>17180</v>
@@ -44739,7 +44739,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1530" t="n">
-        <v>3.23310160636902</v>
+        <v>3.23310136795044</v>
       </c>
       <c r="H1530" t="n">
         <v>21904</v>
@@ -44884,7 +44884,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1535" t="n">
-        <v>3.16125512123108</v>
+        <v>3.1612548828125</v>
       </c>
       <c r="H1535" t="n">
         <v>18692</v>
@@ -45000,7 +45000,7 @@
         <v>3.4449999332428</v>
       </c>
       <c r="G1539" t="n">
-        <v>3.09389901161194</v>
+        <v>3.09389877319336</v>
       </c>
       <c r="H1539" t="n">
         <v>34077</v>
@@ -45029,7 +45029,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1540" t="n">
-        <v>3.07144641876221</v>
+        <v>3.07144665718079</v>
       </c>
       <c r="H1540" t="n">
         <v>11436</v>
@@ -45145,7 +45145,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1544" t="n">
-        <v>3.07144641876221</v>
+        <v>3.07144665718079</v>
       </c>
       <c r="H1544" t="n">
         <v>26061</v>
@@ -45174,7 +45174,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1545" t="n">
-        <v>3.07144641876221</v>
+        <v>3.07144665718079</v>
       </c>
       <c r="H1545" t="n">
         <v>17611</v>
@@ -45203,7 +45203,7 @@
         <v>3.39499998092651</v>
       </c>
       <c r="G1546" t="n">
-        <v>3.04899430274963</v>
+        <v>3.04899454116821</v>
       </c>
       <c r="H1546" t="n">
         <v>13259</v>
@@ -45261,7 +45261,7 @@
         <v>3.46499991416931</v>
       </c>
       <c r="G1548" t="n">
-        <v>3.11186027526855</v>
+        <v>3.11186003684998</v>
       </c>
       <c r="H1548" t="n">
         <v>19882</v>
@@ -45522,7 +45522,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1557" t="n">
-        <v>2.93673396110535</v>
+        <v>2.93673419952393</v>
       </c>
       <c r="H1557" t="n">
         <v>62187</v>
@@ -45580,7 +45580,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1559" t="n">
-        <v>3.0355236530304</v>
+        <v>3.03552341461182</v>
       </c>
       <c r="H1559" t="n">
         <v>68012</v>
@@ -45638,7 +45638,7 @@
         <v>3.34500002861023</v>
       </c>
       <c r="G1561" t="n">
-        <v>3.00409030914307</v>
+        <v>3.00409054756165</v>
       </c>
       <c r="H1561" t="n">
         <v>13868</v>
@@ -45667,7 +45667,7 @@
         <v>3.25500011444092</v>
       </c>
       <c r="G1562" t="n">
-        <v>2.92326283454895</v>
+        <v>2.92326307296753</v>
       </c>
       <c r="H1562" t="n">
         <v>56513</v>
@@ -45696,7 +45696,7 @@
         <v>3.25</v>
       </c>
       <c r="G1563" t="n">
-        <v>2.91877245903015</v>
+        <v>2.91877269744873</v>
       </c>
       <c r="H1563" t="n">
         <v>50830</v>
@@ -45725,7 +45725,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1564" t="n">
-        <v>2.92775297164917</v>
+        <v>2.92775321006775</v>
       </c>
       <c r="H1564" t="n">
         <v>30025</v>
@@ -45957,7 +45957,7 @@
         <v>2.88499999046326</v>
       </c>
       <c r="G1572" t="n">
-        <v>2.59097170829773</v>
+        <v>2.59097194671631</v>
       </c>
       <c r="H1572" t="n">
         <v>89659</v>
@@ -45986,7 +45986,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1573" t="n">
-        <v>2.47871136665344</v>
+        <v>2.47871112823486</v>
       </c>
       <c r="H1573" t="n">
         <v>75837</v>
@@ -46305,7 +46305,7 @@
         <v>3.15499997138977</v>
       </c>
       <c r="G1584" t="n">
-        <v>2.83345460891724</v>
+        <v>2.83345437049866</v>
       </c>
       <c r="H1584" t="n">
         <v>15092</v>
@@ -46334,7 +46334,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1585" t="n">
-        <v>2.75711750984192</v>
+        <v>2.75711727142334</v>
       </c>
       <c r="H1585" t="n">
         <v>11617</v>
@@ -46363,7 +46363,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G1586" t="n">
-        <v>2.77058887481689</v>
+        <v>2.77058863639832</v>
       </c>
       <c r="H1586" t="n">
         <v>15848</v>
@@ -46392,7 +46392,7 @@
         <v>3.09500002861023</v>
       </c>
       <c r="G1587" t="n">
-        <v>2.77956938743591</v>
+        <v>2.77956914901733</v>
       </c>
       <c r="H1587" t="n">
         <v>16457</v>
@@ -46421,7 +46421,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G1588" t="n">
-        <v>2.87835836410522</v>
+        <v>2.8783586025238</v>
       </c>
       <c r="H1588" t="n">
         <v>64619</v>
@@ -46450,7 +46450,7 @@
         <v>3.14499998092651</v>
       </c>
       <c r="G1589" t="n">
-        <v>2.82447361946106</v>
+        <v>2.82447338104248</v>
       </c>
       <c r="H1589" t="n">
         <v>13234</v>
@@ -46914,7 +46914,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1605" t="n">
-        <v>3.0355236530304</v>
+        <v>3.03552341461182</v>
       </c>
       <c r="H1605" t="n">
         <v>91599</v>
@@ -46943,7 +46943,7 @@
         <v>3.39499998092651</v>
       </c>
       <c r="G1606" t="n">
-        <v>3.04899430274963</v>
+        <v>3.04899454116821</v>
       </c>
       <c r="H1606" t="n">
         <v>202255</v>
@@ -46972,7 +46972,7 @@
         <v>3.39499998092651</v>
       </c>
       <c r="G1607" t="n">
-        <v>3.04899430274963</v>
+        <v>3.04899454116821</v>
       </c>
       <c r="H1607" t="n">
         <v>240406</v>
@@ -47233,7 +47233,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1616" t="n">
-        <v>2.71221327781677</v>
+        <v>2.71221303939819</v>
       </c>
       <c r="H1616" t="n">
         <v>19150</v>
@@ -47291,7 +47291,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1618" t="n">
-        <v>2.84692573547363</v>
+        <v>2.84692549705505</v>
       </c>
       <c r="H1618" t="n">
         <v>37103</v>
@@ -47378,7 +47378,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1621" t="n">
-        <v>2.84692573547363</v>
+        <v>2.84692549705505</v>
       </c>
       <c r="H1621" t="n">
         <v>21461</v>
@@ -47436,7 +47436,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1623" t="n">
-        <v>2.92775297164917</v>
+        <v>2.92775321006775</v>
       </c>
       <c r="H1623" t="n">
         <v>16046</v>
@@ -48074,7 +48074,7 @@
         <v>2.89499998092651</v>
       </c>
       <c r="G1645" t="n">
-        <v>2.59995245933533</v>
+        <v>2.59995269775391</v>
       </c>
       <c r="H1645" t="n">
         <v>23745</v>
@@ -48248,7 +48248,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G1651" t="n">
-        <v>2.52810597419739</v>
+        <v>2.52810621261597</v>
       </c>
       <c r="H1651" t="n">
         <v>47327</v>
@@ -48306,7 +48306,7 @@
         <v>2.75</v>
       </c>
       <c r="G1653" t="n">
-        <v>2.46973061561584</v>
+        <v>2.46973037719727</v>
       </c>
       <c r="H1653" t="n">
         <v>15071</v>
@@ -48335,7 +48335,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1654" t="n">
-        <v>2.45176887512207</v>
+        <v>2.45176863670349</v>
       </c>
       <c r="H1654" t="n">
         <v>17302</v>
@@ -48422,7 +48422,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1657" t="n">
-        <v>2.4338071346283</v>
+        <v>2.43380689620972</v>
       </c>
       <c r="H1657" t="n">
         <v>4394</v>
@@ -48451,7 +48451,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G1658" t="n">
-        <v>2.52810597419739</v>
+        <v>2.52810621261597</v>
       </c>
       <c r="H1658" t="n">
         <v>9524</v>
@@ -48567,7 +48567,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1662" t="n">
-        <v>2.53259611129761</v>
+        <v>2.53259634971619</v>
       </c>
       <c r="H1662" t="n">
         <v>19482</v>
@@ -48596,7 +48596,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1663" t="n">
-        <v>2.53259611129761</v>
+        <v>2.53259634971619</v>
       </c>
       <c r="H1663" t="n">
         <v>5616</v>
@@ -48625,7 +48625,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1664" t="n">
-        <v>2.53259611129761</v>
+        <v>2.53259634971619</v>
       </c>
       <c r="H1664" t="n">
         <v>6368</v>
@@ -48712,7 +48712,7 @@
         <v>2.85500001907349</v>
       </c>
       <c r="G1667" t="n">
-        <v>2.56402921676636</v>
+        <v>2.56402945518494</v>
       </c>
       <c r="H1667" t="n">
         <v>1483</v>
@@ -48828,7 +48828,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1671" t="n">
-        <v>2.53259611129761</v>
+        <v>2.53259634971619</v>
       </c>
       <c r="H1671" t="n">
         <v>5662</v>
@@ -49205,7 +49205,7 @@
         <v>2.88499999046326</v>
       </c>
       <c r="G1684" t="n">
-        <v>2.59097170829773</v>
+        <v>2.59097194671631</v>
       </c>
       <c r="H1684" t="n">
         <v>28688</v>
@@ -49350,7 +49350,7 @@
         <v>2.99499988555908</v>
       </c>
       <c r="G1689" t="n">
-        <v>2.6897611618042</v>
+        <v>2.68976092338562</v>
       </c>
       <c r="H1689" t="n">
         <v>71265</v>
@@ -49379,7 +49379,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1690" t="n">
-        <v>2.71221327781677</v>
+        <v>2.71221303939819</v>
       </c>
       <c r="H1690" t="n">
         <v>13300</v>
@@ -49437,7 +49437,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1692" t="n">
-        <v>2.66730880737305</v>
+        <v>2.66730904579163</v>
       </c>
       <c r="H1692" t="n">
         <v>5911</v>
@@ -49872,7 +49872,7 @@
         <v>2.75</v>
       </c>
       <c r="G1707" t="n">
-        <v>2.46973061561584</v>
+        <v>2.46973037719727</v>
       </c>
       <c r="H1707" t="n">
         <v>4942</v>
@@ -49901,7 +49901,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1708" t="n">
-        <v>2.47871136665344</v>
+        <v>2.47871112823486</v>
       </c>
       <c r="H1708" t="n">
         <v>7448</v>
@@ -50191,7 +50191,7 @@
         <v>2.40499997138977</v>
       </c>
       <c r="G1718" t="n">
-        <v>2.15989136695862</v>
+        <v>2.1598916053772</v>
       </c>
       <c r="H1718" t="n">
         <v>9107</v>
@@ -80038,6 +80038,35 @@
         <v>5213</v>
       </c>
       <c r="I2747" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2748">
+      <c r="A2748" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2748" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C2748" t="n">
+        <v>1.08500003814697</v>
+      </c>
+      <c r="D2748" t="n">
+        <v>1.11500000953674</v>
+      </c>
+      <c r="E2748" t="n">
+        <v>1.08000004291534</v>
+      </c>
+      <c r="F2748" t="n">
+        <v>1.08000004291534</v>
+      </c>
+      <c r="G2748" t="n">
+        <v>1.08000004291534</v>
+      </c>
+      <c r="H2748" t="n">
+        <v>26261</v>
+      </c>
+      <c r="I2748" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELC.MI.xlsx
+++ b/data/ELC.MI.xlsx
@@ -456,7 +456,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G3" t="n">
-        <v>1.73338508605957</v>
+        <v>1.73338520526886</v>
       </c>
       <c r="H3" t="n">
         <v>15024</v>
@@ -485,7 +485,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G4" t="n">
-        <v>1.72445011138916</v>
+        <v>1.72444999217987</v>
       </c>
       <c r="H4" t="n">
         <v>5059</v>
@@ -514,7 +514,7 @@
         <v>1.87399995326996</v>
       </c>
       <c r="G5" t="n">
-        <v>1.67441427707672</v>
+        <v>1.67441415786743</v>
       </c>
       <c r="H5" t="n">
         <v>56904</v>
@@ -572,7 +572,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G7" t="n">
-        <v>1.65297043323517</v>
+        <v>1.65297031402588</v>
       </c>
       <c r="H7" t="n">
         <v>22563</v>
@@ -601,7 +601,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G8" t="n">
-        <v>1.66190540790558</v>
+        <v>1.661905169487</v>
       </c>
       <c r="H8" t="n">
         <v>15254</v>
@@ -659,7 +659,7 @@
         <v>1.81900000572205</v>
       </c>
       <c r="G10" t="n">
-        <v>1.62527203559875</v>
+        <v>1.62527191638947</v>
       </c>
       <c r="H10" t="n">
         <v>37372</v>
@@ -688,7 +688,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G11" t="n">
-        <v>1.59936034679413</v>
+        <v>1.59936058521271</v>
       </c>
       <c r="H11" t="n">
         <v>30082</v>
@@ -717,7 +717,7 @@
         <v>1.65199995040894</v>
       </c>
       <c r="G12" t="n">
-        <v>1.47605776786804</v>
+        <v>1.47605788707733</v>
       </c>
       <c r="H12" t="n">
         <v>45741</v>
@@ -746,7 +746,7 @@
         <v>1.66700005531311</v>
       </c>
       <c r="G13" t="n">
-        <v>1.48946022987366</v>
+        <v>1.48946034908295</v>
       </c>
       <c r="H13" t="n">
         <v>45328</v>
@@ -775,7 +775,7 @@
         <v>1.61099994182587</v>
       </c>
       <c r="G14" t="n">
-        <v>1.43942439556122</v>
+        <v>1.43942451477051</v>
       </c>
       <c r="H14" t="n">
         <v>54905</v>
@@ -804,7 +804,7 @@
         <v>1.71800005435944</v>
       </c>
       <c r="G15" t="n">
-        <v>1.53502857685089</v>
+        <v>1.53502869606018</v>
       </c>
       <c r="H15" t="n">
         <v>48803</v>
@@ -833,7 +833,7 @@
         <v>1.70700001716614</v>
       </c>
       <c r="G16" t="n">
-        <v>1.52520036697388</v>
+        <v>1.5252001285553</v>
       </c>
       <c r="H16" t="n">
         <v>85068</v>
@@ -862,7 +862,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G17" t="n">
-        <v>1.44746601581573</v>
+        <v>1.44746589660645</v>
       </c>
       <c r="H17" t="n">
         <v>53091</v>
@@ -920,7 +920,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G19" t="n">
-        <v>1.46533584594727</v>
+        <v>1.46533572673798</v>
       </c>
       <c r="H19" t="n">
         <v>19803</v>
@@ -978,7 +978,7 @@
         <v>1.65100002288818</v>
       </c>
       <c r="G21" t="n">
-        <v>1.47516441345215</v>
+        <v>1.47516429424286</v>
       </c>
       <c r="H21" t="n">
         <v>7561</v>
@@ -1007,7 +1007,7 @@
         <v>1.59099996089935</v>
       </c>
       <c r="G22" t="n">
-        <v>1.42155432701111</v>
+        <v>1.4215544462204</v>
       </c>
       <c r="H22" t="n">
         <v>81953</v>
@@ -1036,7 +1036,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G23" t="n">
-        <v>1.39832365512848</v>
+        <v>1.39832377433777</v>
       </c>
       <c r="H23" t="n">
         <v>23089</v>
@@ -1065,7 +1065,7 @@
         <v>1.54499995708466</v>
       </c>
       <c r="G24" t="n">
-        <v>1.38045346736908</v>
+        <v>1.38045358657837</v>
       </c>
       <c r="H24" t="n">
         <v>20826</v>
@@ -1094,7 +1094,7 @@
         <v>1.51699995994568</v>
       </c>
       <c r="G25" t="n">
-        <v>1.3554356098175</v>
+        <v>1.35543572902679</v>
       </c>
       <c r="H25" t="n">
         <v>27464</v>
@@ -1123,7 +1123,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G26" t="n">
-        <v>1.38492095470428</v>
+        <v>1.38492119312286</v>
       </c>
       <c r="H26" t="n">
         <v>35283</v>
@@ -1152,7 +1152,7 @@
         <v>1.40199995040894</v>
       </c>
       <c r="G27" t="n">
-        <v>1.25268340110779</v>
+        <v>1.25268352031708</v>
       </c>
       <c r="H27" t="n">
         <v>60303</v>
@@ -1268,7 +1268,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G31" t="n">
-        <v>1.42959606647491</v>
+        <v>1.42959594726562</v>
       </c>
       <c r="H31" t="n">
         <v>187635</v>
@@ -1355,7 +1355,7 @@
         <v>1.65900003910065</v>
       </c>
       <c r="G34" t="n">
-        <v>1.48231244087219</v>
+        <v>1.4823123216629</v>
       </c>
       <c r="H34" t="n">
         <v>55221</v>
@@ -1413,7 +1413,7 @@
         <v>1.75399994850159</v>
       </c>
       <c r="G36" t="n">
-        <v>1.56719434261322</v>
+        <v>1.5671945810318</v>
       </c>
       <c r="H36" t="n">
         <v>41971</v>
@@ -1442,7 +1442,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G37" t="n">
-        <v>1.57255554199219</v>
+        <v>1.57255566120148</v>
       </c>
       <c r="H37" t="n">
         <v>29281</v>
@@ -1500,7 +1500,7 @@
         <v>1.74699997901917</v>
       </c>
       <c r="G39" t="n">
-        <v>1.56094014644623</v>
+        <v>1.56094002723694</v>
       </c>
       <c r="H39" t="n">
         <v>2902</v>
@@ -1529,7 +1529,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G40" t="n">
-        <v>1.5770229101181</v>
+        <v>1.57702314853668</v>
       </c>
       <c r="H40" t="n">
         <v>4812</v>
@@ -1587,7 +1587,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G42" t="n">
-        <v>1.58149063587189</v>
+        <v>1.5814905166626</v>
       </c>
       <c r="H42" t="n">
         <v>5093</v>
@@ -1616,7 +1616,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G43" t="n">
-        <v>1.57255554199219</v>
+        <v>1.57255566120148</v>
       </c>
       <c r="H43" t="n">
         <v>24781</v>
@@ -1645,7 +1645,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G44" t="n">
-        <v>1.51894581317902</v>
+        <v>1.51894569396973</v>
       </c>
       <c r="H44" t="n">
         <v>29575</v>
@@ -1674,7 +1674,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G45" t="n">
-        <v>1.58149063587189</v>
+        <v>1.5814905166626</v>
       </c>
       <c r="H45" t="n">
         <v>28487</v>
@@ -1819,7 +1819,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G50" t="n">
-        <v>1.58149063587189</v>
+        <v>1.5814905166626</v>
       </c>
       <c r="H50" t="n">
         <v>3356</v>
@@ -1848,7 +1848,7 @@
         <v>1.76600003242493</v>
       </c>
       <c r="G51" t="n">
-        <v>1.57791662216187</v>
+        <v>1.57791650295258</v>
       </c>
       <c r="H51" t="n">
         <v>27532</v>
@@ -1877,7 +1877,7 @@
         <v>1.8309999704361</v>
       </c>
       <c r="G52" t="n">
-        <v>1.63599383831024</v>
+        <v>1.63599371910095</v>
       </c>
       <c r="H52" t="n">
         <v>51060</v>
@@ -1906,7 +1906,7 @@
         <v>1.89300000667572</v>
       </c>
       <c r="G53" t="n">
-        <v>1.69139075279236</v>
+        <v>1.69139063358307</v>
       </c>
       <c r="H53" t="n">
         <v>24502</v>
@@ -1935,7 +1935,7 @@
         <v>1.90900003910065</v>
       </c>
       <c r="G54" t="n">
-        <v>1.70568680763245</v>
+        <v>1.70568668842316</v>
       </c>
       <c r="H54" t="n">
         <v>85054</v>
@@ -1964,7 +1964,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G55" t="n">
-        <v>1.6797753572464</v>
+        <v>1.67977523803711</v>
       </c>
       <c r="H55" t="n">
         <v>33252</v>
@@ -1993,7 +1993,7 @@
         <v>1.90799999237061</v>
       </c>
       <c r="G56" t="n">
-        <v>1.70479309558868</v>
+        <v>1.70479321479797</v>
       </c>
       <c r="H56" t="n">
         <v>30447</v>
@@ -2022,7 +2022,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G57" t="n">
-        <v>1.72445011138916</v>
+        <v>1.72444999217987</v>
       </c>
       <c r="H57" t="n">
         <v>46823</v>
@@ -2051,7 +2051,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G58" t="n">
-        <v>1.76912486553192</v>
+        <v>1.7691251039505</v>
       </c>
       <c r="H58" t="n">
         <v>198777</v>
@@ -2080,7 +2080,7 @@
         <v>1.95200002193451</v>
       </c>
       <c r="G59" t="n">
-        <v>1.74410724639893</v>
+        <v>1.74410700798035</v>
       </c>
       <c r="H59" t="n">
         <v>77105</v>
@@ -2109,7 +2109,7 @@
         <v>1.93599998950958</v>
       </c>
       <c r="G60" t="n">
-        <v>1.72981119155884</v>
+        <v>1.72981107234955</v>
       </c>
       <c r="H60" t="n">
         <v>25733</v>
@@ -2138,7 +2138,7 @@
         <v>1.94599997997284</v>
       </c>
       <c r="G61" t="n">
-        <v>1.73874616622925</v>
+        <v>1.73874604701996</v>
       </c>
       <c r="H61" t="n">
         <v>32577</v>
@@ -2196,7 +2196,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G63" t="n">
-        <v>1.75125503540039</v>
+        <v>1.75125515460968</v>
       </c>
       <c r="H63" t="n">
         <v>20594</v>
@@ -2225,7 +2225,7 @@
         <v>1.96399998664856</v>
       </c>
       <c r="G64" t="n">
-        <v>1.75482892990112</v>
+        <v>1.75482904911041</v>
       </c>
       <c r="H64" t="n">
         <v>34653</v>
@@ -2254,7 +2254,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G65" t="n">
-        <v>1.72445011138916</v>
+        <v>1.72444999217987</v>
       </c>
       <c r="H65" t="n">
         <v>30447</v>
@@ -2312,7 +2312,7 @@
         <v>1.87899994850159</v>
       </c>
       <c r="G67" t="n">
-        <v>1.67888164520264</v>
+        <v>1.67888176441193</v>
       </c>
       <c r="H67" t="n">
         <v>36815</v>
@@ -2341,7 +2341,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G68" t="n">
-        <v>1.69317781925201</v>
+        <v>1.69317770004272</v>
       </c>
       <c r="H68" t="n">
         <v>6467</v>
@@ -2428,7 +2428,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G71" t="n">
-        <v>1.6708402633667</v>
+        <v>1.67084014415741</v>
       </c>
       <c r="H71" t="n">
         <v>26244</v>
@@ -2660,7 +2660,7 @@
         <v>1.89800000190735</v>
       </c>
       <c r="G79" t="n">
-        <v>1.69585812091827</v>
+        <v>1.69585824012756</v>
       </c>
       <c r="H79" t="n">
         <v>17651</v>
@@ -2718,7 +2718,7 @@
         <v>1.89900004863739</v>
       </c>
       <c r="G81" t="n">
-        <v>1.69675171375275</v>
+        <v>1.69675183296204</v>
       </c>
       <c r="H81" t="n">
         <v>12593</v>
@@ -2950,7 +2950,7 @@
         <v>1.92599999904633</v>
       </c>
       <c r="G89" t="n">
-        <v>1.72087609767914</v>
+        <v>1.72087621688843</v>
       </c>
       <c r="H89" t="n">
         <v>11063</v>
@@ -2979,7 +2979,7 @@
         <v>1.84800004959106</v>
       </c>
       <c r="G90" t="n">
-        <v>1.65118336677551</v>
+        <v>1.6511834859848</v>
       </c>
       <c r="H90" t="n">
         <v>73958</v>
@@ -3008,7 +3008,7 @@
         <v>1.875</v>
       </c>
       <c r="G91" t="n">
-        <v>1.6753077507019</v>
+        <v>1.67530786991119</v>
       </c>
       <c r="H91" t="n">
         <v>20346</v>
@@ -3066,7 +3066,7 @@
         <v>1.85199999809265</v>
       </c>
       <c r="G93" t="n">
-        <v>1.65475738048553</v>
+        <v>1.65475749969482</v>
       </c>
       <c r="H93" t="n">
         <v>17094</v>
@@ -3182,7 +3182,7 @@
         <v>1.90600001811981</v>
       </c>
       <c r="G97" t="n">
-        <v>1.70300614833832</v>
+        <v>1.70300626754761</v>
       </c>
       <c r="H97" t="n">
         <v>8769</v>
@@ -3211,7 +3211,7 @@
         <v>1.91799998283386</v>
       </c>
       <c r="G98" t="n">
-        <v>1.71372807025909</v>
+        <v>1.71372818946838</v>
       </c>
       <c r="H98" t="n">
         <v>37783</v>
@@ -3240,7 +3240,7 @@
         <v>1.9190000295639</v>
       </c>
       <c r="G99" t="n">
-        <v>1.71462154388428</v>
+        <v>1.71462166309357</v>
       </c>
       <c r="H99" t="n">
         <v>116965</v>
@@ -3327,7 +3327,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G102" t="n">
-        <v>1.76922512054443</v>
+        <v>1.76922500133514</v>
       </c>
       <c r="H102" t="n">
         <v>207475</v>
@@ -3356,7 +3356,7 @@
         <v>1.95700001716614</v>
       </c>
       <c r="G103" t="n">
-        <v>1.7575501203537</v>
+        <v>1.75755000114441</v>
       </c>
       <c r="H103" t="n">
         <v>198761</v>
@@ -3385,7 +3385,7 @@
         <v>1.93799996376038</v>
       </c>
       <c r="G104" t="n">
-        <v>1.7404865026474</v>
+        <v>1.74048626422882</v>
       </c>
       <c r="H104" t="n">
         <v>7025</v>
@@ -3704,7 +3704,7 @@
         <v>1.85199999809265</v>
       </c>
       <c r="G115" t="n">
-        <v>1.66325128078461</v>
+        <v>1.66325116157532</v>
       </c>
       <c r="H115" t="n">
         <v>23967</v>
@@ -3733,7 +3733,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G116" t="n">
-        <v>1.63900315761566</v>
+        <v>1.63900291919708</v>
       </c>
       <c r="H116" t="n">
         <v>14527</v>
@@ -3791,7 +3791,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G118" t="n">
-        <v>1.58960843086243</v>
+        <v>1.58960819244385</v>
       </c>
       <c r="H118" t="n">
         <v>20333</v>
@@ -3878,7 +3878,7 @@
         <v>1.875</v>
       </c>
       <c r="G121" t="n">
-        <v>1.68390715122223</v>
+        <v>1.68390727043152</v>
       </c>
       <c r="H121" t="n">
         <v>30628</v>
@@ -3907,7 +3907,7 @@
         <v>1.82400000095367</v>
       </c>
       <c r="G122" t="n">
-        <v>1.63810479640961</v>
+        <v>1.6381049156189</v>
       </c>
       <c r="H122" t="n">
         <v>17618</v>
@@ -3936,7 +3936,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G123" t="n">
-        <v>1.66145515441895</v>
+        <v>1.66145503520966</v>
       </c>
       <c r="H123" t="n">
         <v>13342</v>
@@ -3965,7 +3965,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G124" t="n">
-        <v>1.61655068397522</v>
+        <v>1.61655080318451</v>
       </c>
       <c r="H124" t="n">
         <v>30870</v>
@@ -3994,7 +3994,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G125" t="n">
-        <v>1.58960843086243</v>
+        <v>1.58960819244385</v>
       </c>
       <c r="H125" t="n">
         <v>22469</v>
@@ -4023,7 +4023,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G126" t="n">
-        <v>1.61655068397522</v>
+        <v>1.61655080318451</v>
       </c>
       <c r="H126" t="n">
         <v>25208</v>
@@ -4052,7 +4052,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G127" t="n">
-        <v>1.63900315761566</v>
+        <v>1.63900291919708</v>
       </c>
       <c r="H127" t="n">
         <v>3233</v>
@@ -4110,7 +4110,7 @@
         <v>1.80900001525879</v>
       </c>
       <c r="G129" t="n">
-        <v>1.62463366985321</v>
+        <v>1.62463355064392</v>
       </c>
       <c r="H129" t="n">
         <v>7722</v>
@@ -4197,7 +4197,7 @@
         <v>1.69700002670288</v>
       </c>
       <c r="G132" t="n">
-        <v>1.52404832839966</v>
+        <v>1.52404820919037</v>
       </c>
       <c r="H132" t="n">
         <v>59729</v>
@@ -4226,7 +4226,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G133" t="n">
-        <v>1.46836709976196</v>
+        <v>1.46836698055267</v>
       </c>
       <c r="H133" t="n">
         <v>25558</v>
@@ -4371,7 +4371,7 @@
         <v>1.66400003433228</v>
       </c>
       <c r="G138" t="n">
-        <v>1.49441146850586</v>
+        <v>1.49441158771515</v>
       </c>
       <c r="H138" t="n">
         <v>38824</v>
@@ -4429,7 +4429,7 @@
         <v>1.6690000295639</v>
       </c>
       <c r="G140" t="n">
-        <v>1.49890184402466</v>
+        <v>1.49890196323395</v>
       </c>
       <c r="H140" t="n">
         <v>29756</v>
@@ -4487,7 +4487,7 @@
         <v>1.67900002002716</v>
       </c>
       <c r="G142" t="n">
-        <v>1.50788259506226</v>
+        <v>1.50788271427155</v>
       </c>
       <c r="H142" t="n">
         <v>35224</v>
@@ -4545,7 +4545,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G144" t="n">
-        <v>1.49979996681213</v>
+        <v>1.49979984760284</v>
       </c>
       <c r="H144" t="n">
         <v>4167</v>
@@ -4574,7 +4574,7 @@
         <v>1.66100001335144</v>
       </c>
       <c r="G145" t="n">
-        <v>1.49171733856201</v>
+        <v>1.49171721935272</v>
       </c>
       <c r="H145" t="n">
         <v>7428</v>
@@ -4603,7 +4603,7 @@
         <v>1.66100001335144</v>
       </c>
       <c r="G146" t="n">
-        <v>1.49171733856201</v>
+        <v>1.49171721935272</v>
       </c>
       <c r="H146" t="n">
         <v>6561</v>
@@ -4690,7 +4690,7 @@
         <v>1.65400004386902</v>
       </c>
       <c r="G149" t="n">
-        <v>1.48543071746826</v>
+        <v>1.48543059825897</v>
       </c>
       <c r="H149" t="n">
         <v>29881</v>
@@ -4864,7 +4864,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G155" t="n">
-        <v>1.5267425775528</v>
+        <v>1.52674245834351</v>
       </c>
       <c r="H155" t="n">
         <v>8511</v>
@@ -4922,7 +4922,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G157" t="n">
-        <v>1.5267425775528</v>
+        <v>1.52674245834351</v>
       </c>
       <c r="H157" t="n">
         <v>12054</v>
@@ -5096,7 +5096,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G163" t="n">
-        <v>1.49979996681213</v>
+        <v>1.49979984760284</v>
       </c>
       <c r="H163" t="n">
         <v>16224</v>
@@ -5125,7 +5125,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G164" t="n">
-        <v>1.49979996681213</v>
+        <v>1.49979984760284</v>
       </c>
       <c r="H164" t="n">
         <v>48801</v>
@@ -5154,7 +5154,7 @@
         <v>1.69900000095367</v>
       </c>
       <c r="G165" t="n">
-        <v>1.52584433555603</v>
+        <v>1.52584445476532</v>
       </c>
       <c r="H165" t="n">
         <v>23950</v>
@@ -5212,7 +5212,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G167" t="n">
-        <v>1.64349341392517</v>
+        <v>1.64349353313446</v>
       </c>
       <c r="H167" t="n">
         <v>181062</v>
@@ -5241,7 +5241,7 @@
         <v>1.93400001525879</v>
       </c>
       <c r="G168" t="n">
-        <v>1.7368940114975</v>
+        <v>1.73689413070679</v>
       </c>
       <c r="H168" t="n">
         <v>557364</v>
@@ -5270,7 +5270,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G169" t="n">
-        <v>1.75126349925995</v>
+        <v>1.75126361846924</v>
       </c>
       <c r="H169" t="n">
         <v>207435</v>
@@ -5386,7 +5386,7 @@
         <v>1.84800004959106</v>
       </c>
       <c r="G173" t="n">
-        <v>1.65965890884399</v>
+        <v>1.65965902805328</v>
       </c>
       <c r="H173" t="n">
         <v>102738</v>
@@ -5415,7 +5415,7 @@
         <v>1.87800002098083</v>
       </c>
       <c r="G174" t="n">
-        <v>1.68660128116608</v>
+        <v>1.68660140037537</v>
       </c>
       <c r="H174" t="n">
         <v>29492</v>
@@ -5444,7 +5444,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G175" t="n">
-        <v>1.67043602466583</v>
+        <v>1.67043590545654</v>
       </c>
       <c r="H175" t="n">
         <v>32520</v>
@@ -5473,7 +5473,7 @@
         <v>1.85899996757507</v>
       </c>
       <c r="G176" t="n">
-        <v>1.66953778266907</v>
+        <v>1.66953766345978</v>
       </c>
       <c r="H176" t="n">
         <v>24532</v>
@@ -5502,7 +5502,7 @@
         <v>1.86800003051758</v>
       </c>
       <c r="G177" t="n">
-        <v>1.67762064933777</v>
+        <v>1.67762041091919</v>
       </c>
       <c r="H177" t="n">
         <v>59095</v>
@@ -5560,7 +5560,7 @@
         <v>1.88399994373322</v>
       </c>
       <c r="G179" t="n">
-        <v>1.69198977947235</v>
+        <v>1.69198989868164</v>
       </c>
       <c r="H179" t="n">
         <v>65993</v>
@@ -5589,7 +5589,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G180" t="n">
-        <v>1.67043602466583</v>
+        <v>1.67043590545654</v>
       </c>
       <c r="H180" t="n">
         <v>18502</v>
@@ -5647,7 +5647,7 @@
         <v>1.85199999809265</v>
       </c>
       <c r="G182" t="n">
-        <v>1.66325128078461</v>
+        <v>1.66325116157532</v>
       </c>
       <c r="H182" t="n">
         <v>5317</v>
@@ -5734,7 +5734,7 @@
         <v>1.80400002002716</v>
       </c>
       <c r="G185" t="n">
-        <v>1.62014329433441</v>
+        <v>1.62014317512512</v>
       </c>
       <c r="H185" t="n">
         <v>11917</v>
@@ -5763,7 +5763,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G186" t="n">
-        <v>1.61655068397522</v>
+        <v>1.61655080318451</v>
       </c>
       <c r="H186" t="n">
         <v>28218</v>
@@ -5792,7 +5792,7 @@
         <v>1.80099999904633</v>
       </c>
       <c r="G187" t="n">
-        <v>1.61744892597198</v>
+        <v>1.61744904518127</v>
       </c>
       <c r="H187" t="n">
         <v>18817</v>
@@ -5821,7 +5821,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G188" t="n">
-        <v>1.61655068397522</v>
+        <v>1.61655080318451</v>
       </c>
       <c r="H188" t="n">
         <v>35451</v>
@@ -5850,7 +5850,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G189" t="n">
-        <v>1.61655068397522</v>
+        <v>1.61655080318451</v>
       </c>
       <c r="H189" t="n">
         <v>33190</v>
@@ -5879,7 +5879,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G190" t="n">
-        <v>1.61655068397522</v>
+        <v>1.61655080318451</v>
       </c>
       <c r="H190" t="n">
         <v>29161</v>
@@ -5908,7 +5908,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G191" t="n">
-        <v>1.61655068397522</v>
+        <v>1.61655080318451</v>
       </c>
       <c r="H191" t="n">
         <v>2263</v>
@@ -6082,7 +6082,7 @@
         <v>1.89699995517731</v>
       </c>
       <c r="G197" t="n">
-        <v>1.70366501808167</v>
+        <v>1.70366489887238</v>
       </c>
       <c r="H197" t="n">
         <v>75519</v>
@@ -6111,7 +6111,7 @@
         <v>1.875</v>
       </c>
       <c r="G198" t="n">
-        <v>1.68390715122223</v>
+        <v>1.68390727043152</v>
       </c>
       <c r="H198" t="n">
         <v>38123</v>
@@ -6198,7 +6198,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G201" t="n">
-        <v>1.67043602466583</v>
+        <v>1.67043590545654</v>
       </c>
       <c r="H201" t="n">
         <v>20696</v>
@@ -6227,7 +6227,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G202" t="n">
-        <v>1.66145515441895</v>
+        <v>1.66145503520966</v>
       </c>
       <c r="H202" t="n">
         <v>14854</v>
@@ -6256,7 +6256,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G203" t="n">
-        <v>1.66594552993774</v>
+        <v>1.66594541072845</v>
       </c>
       <c r="H203" t="n">
         <v>24191</v>
@@ -6285,7 +6285,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G204" t="n">
-        <v>1.66145515441895</v>
+        <v>1.66145503520966</v>
       </c>
       <c r="H204" t="n">
         <v>39083</v>
@@ -6314,7 +6314,7 @@
         <v>1.85199999809265</v>
       </c>
       <c r="G205" t="n">
-        <v>1.66325128078461</v>
+        <v>1.66325116157532</v>
       </c>
       <c r="H205" t="n">
         <v>4455</v>
@@ -6372,7 +6372,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G207" t="n">
-        <v>1.64349341392517</v>
+        <v>1.64349353313446</v>
       </c>
       <c r="H207" t="n">
         <v>28071</v>
@@ -6430,7 +6430,7 @@
         <v>1.86600005626678</v>
       </c>
       <c r="G209" t="n">
-        <v>1.6758246421814</v>
+        <v>1.67582452297211</v>
       </c>
       <c r="H209" t="n">
         <v>12992</v>
@@ -6459,7 +6459,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G210" t="n">
-        <v>1.66145515441895</v>
+        <v>1.66145503520966</v>
       </c>
       <c r="H210" t="n">
         <v>12976</v>
@@ -6488,7 +6488,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G211" t="n">
-        <v>1.65247428417206</v>
+        <v>1.65247416496277</v>
       </c>
       <c r="H211" t="n">
         <v>11706</v>
@@ -6575,7 +6575,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G214" t="n">
-        <v>1.65247428417206</v>
+        <v>1.65247416496277</v>
       </c>
       <c r="H214" t="n">
         <v>7430</v>
@@ -6604,7 +6604,7 @@
         <v>1.86800003051758</v>
       </c>
       <c r="G215" t="n">
-        <v>1.67762064933777</v>
+        <v>1.67762041091919</v>
       </c>
       <c r="H215" t="n">
         <v>3321</v>
@@ -6691,7 +6691,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G218" t="n">
-        <v>1.64349341392517</v>
+        <v>1.64349353313446</v>
       </c>
       <c r="H218" t="n">
         <v>1563</v>
@@ -6720,7 +6720,7 @@
         <v>1.83700001239777</v>
       </c>
       <c r="G219" t="n">
-        <v>1.64977991580963</v>
+        <v>1.64978003501892</v>
       </c>
       <c r="H219" t="n">
         <v>23250</v>
@@ -6807,7 +6807,7 @@
         <v>1.83700001239777</v>
       </c>
       <c r="G222" t="n">
-        <v>1.64977991580963</v>
+        <v>1.64978003501892</v>
       </c>
       <c r="H222" t="n">
         <v>16935</v>
@@ -6836,7 +6836,7 @@
         <v>1.84800004959106</v>
       </c>
       <c r="G223" t="n">
-        <v>1.65965890884399</v>
+        <v>1.65965902805328</v>
       </c>
       <c r="H223" t="n">
         <v>13665</v>
@@ -6865,7 +6865,7 @@
         <v>1.74600005149841</v>
       </c>
       <c r="G224" t="n">
-        <v>1.56805431842804</v>
+        <v>1.56805443763733</v>
       </c>
       <c r="H224" t="n">
         <v>127860</v>
@@ -6894,7 +6894,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G225" t="n">
-        <v>1.58960843086243</v>
+        <v>1.58960819244385</v>
       </c>
       <c r="H225" t="n">
         <v>117138</v>
@@ -6923,7 +6923,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G226" t="n">
-        <v>1.5267425775528</v>
+        <v>1.52674245834351</v>
       </c>
       <c r="H226" t="n">
         <v>99175</v>
@@ -6981,7 +6981,7 @@
         <v>1.65799999237061</v>
       </c>
       <c r="G228" t="n">
-        <v>1.4890228509903</v>
+        <v>1.48902308940887</v>
       </c>
       <c r="H228" t="n">
         <v>27997</v>
@@ -7126,7 +7126,7 @@
         <v>1.49699997901917</v>
       </c>
       <c r="G233" t="n">
-        <v>1.34443151950836</v>
+        <v>1.34443140029907</v>
       </c>
       <c r="H233" t="n">
         <v>56235</v>
@@ -7242,7 +7242,7 @@
         <v>1.52199995517731</v>
       </c>
       <c r="G237" t="n">
-        <v>1.36688363552094</v>
+        <v>1.36688351631165</v>
       </c>
       <c r="H237" t="n">
         <v>139886</v>
@@ -7300,7 +7300,7 @@
         <v>1.55900001525879</v>
       </c>
       <c r="G239" t="n">
-        <v>1.40011274814606</v>
+        <v>1.40011262893677</v>
       </c>
       <c r="H239" t="n">
         <v>29691</v>
@@ -7387,7 +7387,7 @@
         <v>1.60800004005432</v>
       </c>
       <c r="G242" t="n">
-        <v>1.44411885738373</v>
+        <v>1.44411873817444</v>
       </c>
       <c r="H242" t="n">
         <v>23993</v>
@@ -7416,7 +7416,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G243" t="n">
-        <v>1.45040535926819</v>
+        <v>1.45040547847748</v>
       </c>
       <c r="H243" t="n">
         <v>70934</v>
@@ -7503,7 +7503,7 @@
         <v>1.67900002002716</v>
       </c>
       <c r="G246" t="n">
-        <v>1.50788259506226</v>
+        <v>1.50788271427155</v>
       </c>
       <c r="H246" t="n">
         <v>43881</v>
@@ -7532,7 +7532,7 @@
         <v>1.71899998188019</v>
       </c>
       <c r="G247" t="n">
-        <v>1.5438060760498</v>
+        <v>1.54380595684052</v>
       </c>
       <c r="H247" t="n">
         <v>48426</v>
@@ -7561,7 +7561,7 @@
         <v>1.70200002193451</v>
       </c>
       <c r="G248" t="n">
-        <v>1.52853882312775</v>
+        <v>1.52853858470917</v>
       </c>
       <c r="H248" t="n">
         <v>48300</v>
@@ -7590,7 +7590,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G249" t="n">
-        <v>1.54470407962799</v>
+        <v>1.54470419883728</v>
       </c>
       <c r="H249" t="n">
         <v>10215</v>
@@ -7619,7 +7619,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G250" t="n">
-        <v>1.54470407962799</v>
+        <v>1.54470419883728</v>
       </c>
       <c r="H250" t="n">
         <v>19598</v>
@@ -7677,7 +7677,7 @@
         <v>1.78600001335144</v>
       </c>
       <c r="G252" t="n">
-        <v>1.60397779941559</v>
+        <v>1.6039776802063</v>
       </c>
       <c r="H252" t="n">
         <v>99793</v>
@@ -7822,7 +7822,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G257" t="n">
-        <v>1.66594552993774</v>
+        <v>1.66594541072845</v>
       </c>
       <c r="H257" t="n">
         <v>29025</v>
@@ -7851,7 +7851,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G258" t="n">
-        <v>1.66594552993774</v>
+        <v>1.66594541072845</v>
       </c>
       <c r="H258" t="n">
         <v>32848</v>
@@ -7880,7 +7880,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G259" t="n">
-        <v>1.66594552993774</v>
+        <v>1.66594541072845</v>
       </c>
       <c r="H259" t="n">
         <v>41152</v>
@@ -7967,7 +7967,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G262" t="n">
-        <v>1.64349341392517</v>
+        <v>1.64349353313446</v>
       </c>
       <c r="H262" t="n">
         <v>12760</v>
@@ -7996,7 +7996,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G263" t="n">
-        <v>1.65247428417206</v>
+        <v>1.65247416496277</v>
       </c>
       <c r="H263" t="n">
         <v>21549</v>
@@ -8112,7 +8112,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G267" t="n">
-        <v>1.65247428417206</v>
+        <v>1.65247416496277</v>
       </c>
       <c r="H267" t="n">
         <v>16547</v>
@@ -8199,7 +8199,7 @@
         <v>1.80099999904633</v>
       </c>
       <c r="G270" t="n">
-        <v>1.61744892597198</v>
+        <v>1.61744904518127</v>
       </c>
       <c r="H270" t="n">
         <v>18653</v>
@@ -8257,7 +8257,7 @@
         <v>1.78600001335144</v>
       </c>
       <c r="G272" t="n">
-        <v>1.60397779941559</v>
+        <v>1.6039776802063</v>
       </c>
       <c r="H272" t="n">
         <v>14300</v>
@@ -8315,7 +8315,7 @@
         <v>1.71899998188019</v>
       </c>
       <c r="G274" t="n">
-        <v>1.5438060760498</v>
+        <v>1.54380595684052</v>
       </c>
       <c r="H274" t="n">
         <v>45146</v>
@@ -8344,7 +8344,7 @@
         <v>1.70200002193451</v>
       </c>
       <c r="G275" t="n">
-        <v>1.52853882312775</v>
+        <v>1.52853858470917</v>
       </c>
       <c r="H275" t="n">
         <v>22633</v>
@@ -8489,7 +8489,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G280" t="n">
-        <v>1.54470407962799</v>
+        <v>1.54470419883728</v>
       </c>
       <c r="H280" t="n">
         <v>43319</v>
@@ -8518,7 +8518,7 @@
         <v>1.72599995136261</v>
       </c>
       <c r="G281" t="n">
-        <v>1.55009257793427</v>
+        <v>1.55009269714355</v>
       </c>
       <c r="H281" t="n">
         <v>16160</v>
@@ -8547,7 +8547,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G282" t="n">
-        <v>1.54470407962799</v>
+        <v>1.54470419883728</v>
       </c>
       <c r="H282" t="n">
         <v>8484</v>
@@ -8663,7 +8663,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G286" t="n">
-        <v>1.47285747528076</v>
+        <v>1.47285735607147</v>
       </c>
       <c r="H286" t="n">
         <v>15937</v>
@@ -8692,7 +8692,7 @@
         <v>1.63100004196167</v>
       </c>
       <c r="G287" t="n">
-        <v>1.46477460861206</v>
+        <v>1.46477472782135</v>
       </c>
       <c r="H287" t="n">
         <v>11720</v>
@@ -8721,7 +8721,7 @@
         <v>1.51900005340576</v>
       </c>
       <c r="G288" t="n">
-        <v>1.36418926715851</v>
+        <v>1.3641893863678</v>
       </c>
       <c r="H288" t="n">
         <v>409131</v>
@@ -8750,7 +8750,7 @@
         <v>1.56200003623962</v>
       </c>
       <c r="G289" t="n">
-        <v>1.4028068780899</v>
+        <v>1.40280699729919</v>
       </c>
       <c r="H289" t="n">
         <v>163207</v>
@@ -8837,7 +8837,7 @@
         <v>1.48599994182587</v>
       </c>
       <c r="G292" t="n">
-        <v>1.33455240726471</v>
+        <v>1.334552526474</v>
       </c>
       <c r="H292" t="n">
         <v>200422</v>
@@ -8866,7 +8866,7 @@
         <v>1.46700000762939</v>
       </c>
       <c r="G293" t="n">
-        <v>1.3174889087677</v>
+        <v>1.31748902797699</v>
       </c>
       <c r="H293" t="n">
         <v>48300</v>
@@ -8982,7 +8982,7 @@
         <v>1.47800004482269</v>
       </c>
       <c r="G297" t="n">
-        <v>1.32736778259277</v>
+        <v>1.32736790180206</v>
       </c>
       <c r="H297" t="n">
         <v>41633</v>
@@ -9011,7 +9011,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G298" t="n">
-        <v>1.33814489841461</v>
+        <v>1.3381450176239</v>
       </c>
       <c r="H298" t="n">
         <v>73910</v>
@@ -9040,7 +9040,7 @@
         <v>1.55299997329712</v>
       </c>
       <c r="G299" t="n">
-        <v>1.39472413063049</v>
+        <v>1.39472424983978</v>
       </c>
       <c r="H299" t="n">
         <v>111237</v>
@@ -9156,7 +9156,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G303" t="n">
-        <v>1.40999162197113</v>
+        <v>1.40999150276184</v>
       </c>
       <c r="H303" t="n">
         <v>82518</v>
@@ -9243,7 +9243,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G306" t="n">
-        <v>1.40999162197113</v>
+        <v>1.40999150276184</v>
       </c>
       <c r="H306" t="n">
         <v>99179</v>
@@ -9301,7 +9301,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G308" t="n">
-        <v>1.39202976226807</v>
+        <v>1.39202988147736</v>
       </c>
       <c r="H308" t="n">
         <v>41100</v>
@@ -9330,7 +9330,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G309" t="n">
-        <v>1.37406826019287</v>
+        <v>1.37406814098358</v>
       </c>
       <c r="H309" t="n">
         <v>68905</v>
@@ -9388,7 +9388,7 @@
         <v>1.53600001335144</v>
       </c>
       <c r="G311" t="n">
-        <v>1.37945687770844</v>
+        <v>1.37945675849915</v>
       </c>
       <c r="H311" t="n">
         <v>31074</v>
@@ -9417,7 +9417,7 @@
         <v>1.54499995708466</v>
       </c>
       <c r="G312" t="n">
-        <v>1.38753938674927</v>
+        <v>1.38753950595856</v>
       </c>
       <c r="H312" t="n">
         <v>76286</v>
@@ -9504,7 +9504,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G315" t="n">
-        <v>1.39202976226807</v>
+        <v>1.39202988147736</v>
       </c>
       <c r="H315" t="n">
         <v>220108</v>
@@ -9591,7 +9591,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G318" t="n">
-        <v>1.46387660503387</v>
+        <v>1.46387672424316</v>
       </c>
       <c r="H318" t="n">
         <v>285320</v>
@@ -9620,7 +9620,7 @@
         <v>1.6139999628067</v>
       </c>
       <c r="G319" t="n">
-        <v>1.44950735569</v>
+        <v>1.44950723648071</v>
       </c>
       <c r="H319" t="n">
         <v>156991</v>
@@ -9649,7 +9649,7 @@
         <v>1.62600004673004</v>
       </c>
       <c r="G320" t="n">
-        <v>1.46028423309326</v>
+        <v>1.46028435230255</v>
       </c>
       <c r="H320" t="n">
         <v>280073</v>
@@ -9736,7 +9736,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G323" t="n">
-        <v>1.46387660503387</v>
+        <v>1.46387672424316</v>
       </c>
       <c r="H323" t="n">
         <v>95927</v>
@@ -9852,7 +9852,7 @@
         <v>1.63399994373322</v>
       </c>
       <c r="G327" t="n">
-        <v>1.4674688577652</v>
+        <v>1.46746897697449</v>
       </c>
       <c r="H327" t="n">
         <v>29486</v>
@@ -9881,7 +9881,7 @@
         <v>1.62399995326996</v>
       </c>
       <c r="G328" t="n">
-        <v>1.45848798751831</v>
+        <v>1.4584881067276</v>
       </c>
       <c r="H328" t="n">
         <v>22720</v>
@@ -9910,7 +9910,7 @@
         <v>1.62199997901917</v>
       </c>
       <c r="G329" t="n">
-        <v>1.45669198036194</v>
+        <v>1.45669186115265</v>
       </c>
       <c r="H329" t="n">
         <v>24881</v>
@@ -9939,7 +9939,7 @@
         <v>1.625</v>
       </c>
       <c r="G330" t="n">
-        <v>1.45938634872437</v>
+        <v>1.45938611030579</v>
       </c>
       <c r="H330" t="n">
         <v>44118</v>
@@ -9968,7 +9968,7 @@
         <v>1.56299996376038</v>
       </c>
       <c r="G331" t="n">
-        <v>1.40370512008667</v>
+        <v>1.40370500087738</v>
       </c>
       <c r="H331" t="n">
         <v>128838</v>
@@ -9997,7 +9997,7 @@
         <v>1.56299996376038</v>
       </c>
       <c r="G332" t="n">
-        <v>1.40370512008667</v>
+        <v>1.40370500087738</v>
       </c>
       <c r="H332" t="n">
         <v>50386</v>
@@ -10026,7 +10026,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G333" t="n">
-        <v>1.42346274852753</v>
+        <v>1.42346298694611</v>
       </c>
       <c r="H333" t="n">
         <v>10071</v>
@@ -10113,7 +10113,7 @@
         <v>1.63399994373322</v>
       </c>
       <c r="G336" t="n">
-        <v>1.4674688577652</v>
+        <v>1.46746897697449</v>
       </c>
       <c r="H336" t="n">
         <v>79269</v>
@@ -10287,7 +10287,7 @@
         <v>1.63300001621246</v>
       </c>
       <c r="G342" t="n">
-        <v>1.4665709733963</v>
+        <v>1.46657085418701</v>
       </c>
       <c r="H342" t="n">
         <v>11845</v>
@@ -10316,7 +10316,7 @@
         <v>1.67900002002716</v>
       </c>
       <c r="G343" t="n">
-        <v>1.50788259506226</v>
+        <v>1.50788271427155</v>
       </c>
       <c r="H343" t="n">
         <v>109764</v>
@@ -10374,7 +10374,7 @@
         <v>1.67900002002716</v>
       </c>
       <c r="G345" t="n">
-        <v>1.50788259506226</v>
+        <v>1.50788271427155</v>
       </c>
       <c r="H345" t="n">
         <v>60237</v>
@@ -10432,7 +10432,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G347" t="n">
-        <v>1.51327109336853</v>
+        <v>1.51327121257782</v>
       </c>
       <c r="H347" t="n">
         <v>32612</v>
@@ -10519,7 +10519,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G350" t="n">
-        <v>1.67941677570343</v>
+        <v>1.67941665649414</v>
       </c>
       <c r="H350" t="n">
         <v>566755</v>
@@ -10548,7 +10548,7 @@
         <v>1.89199995994568</v>
       </c>
       <c r="G351" t="n">
-        <v>1.69917440414429</v>
+        <v>1.69917452335358</v>
       </c>
       <c r="H351" t="n">
         <v>399479</v>
@@ -10577,7 +10577,7 @@
         <v>1.85399997234344</v>
       </c>
       <c r="G352" t="n">
-        <v>1.66504740715027</v>
+        <v>1.66504728794098</v>
       </c>
       <c r="H352" t="n">
         <v>183961</v>
@@ -10606,7 +10606,7 @@
         <v>1.80099999904633</v>
       </c>
       <c r="G353" t="n">
-        <v>1.61744892597198</v>
+        <v>1.61744904518127</v>
       </c>
       <c r="H353" t="n">
         <v>167327</v>
@@ -10664,7 +10664,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G355" t="n">
-        <v>1.65247428417206</v>
+        <v>1.65247416496277</v>
       </c>
       <c r="H355" t="n">
         <v>265133</v>
@@ -10838,7 +10838,7 @@
         <v>1.875</v>
       </c>
       <c r="G361" t="n">
-        <v>1.68390715122223</v>
+        <v>1.68390727043152</v>
       </c>
       <c r="H361" t="n">
         <v>243867</v>
@@ -10867,7 +10867,7 @@
         <v>1.8860000371933</v>
       </c>
       <c r="G362" t="n">
-        <v>1.6937860250473</v>
+        <v>1.69378614425659</v>
       </c>
       <c r="H362" t="n">
         <v>175263</v>
@@ -10954,7 +10954,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G365" t="n">
-        <v>1.66145515441895</v>
+        <v>1.66145503520966</v>
       </c>
       <c r="H365" t="n">
         <v>59030</v>
@@ -10983,7 +10983,7 @@
         <v>1.85899996757507</v>
       </c>
       <c r="G366" t="n">
-        <v>1.66953778266907</v>
+        <v>1.66953766345978</v>
       </c>
       <c r="H366" t="n">
         <v>64186</v>
@@ -11070,7 +11070,7 @@
         <v>1.80900001525879</v>
       </c>
       <c r="G369" t="n">
-        <v>1.62463366985321</v>
+        <v>1.62463355064392</v>
       </c>
       <c r="H369" t="n">
         <v>77361</v>
@@ -11099,7 +11099,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G370" t="n">
-        <v>1.61655068397522</v>
+        <v>1.61655080318451</v>
       </c>
       <c r="H370" t="n">
         <v>66407</v>
@@ -11128,7 +11128,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G371" t="n">
-        <v>1.63900315761566</v>
+        <v>1.63900291919708</v>
       </c>
       <c r="H371" t="n">
         <v>52595</v>
@@ -11157,7 +11157,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G372" t="n">
-        <v>1.65247428417206</v>
+        <v>1.65247416496277</v>
       </c>
       <c r="H372" t="n">
         <v>72016</v>
@@ -11186,7 +11186,7 @@
         <v>1.83700001239777</v>
       </c>
       <c r="G373" t="n">
-        <v>1.64977991580963</v>
+        <v>1.64978003501892</v>
       </c>
       <c r="H373" t="n">
         <v>46666</v>
@@ -11244,7 +11244,7 @@
         <v>1.83899998664856</v>
       </c>
       <c r="G375" t="n">
-        <v>1.65157616138458</v>
+        <v>1.65157628059387</v>
       </c>
       <c r="H375" t="n">
         <v>36475</v>
@@ -11302,7 +11302,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G377" t="n">
-        <v>1.64349341392517</v>
+        <v>1.64349353313446</v>
       </c>
       <c r="H377" t="n">
         <v>31220</v>
@@ -11360,7 +11360,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G379" t="n">
-        <v>1.61655068397522</v>
+        <v>1.61655080318451</v>
       </c>
       <c r="H379" t="n">
         <v>26590</v>
@@ -11389,7 +11389,7 @@
         <v>1.80400002002716</v>
       </c>
       <c r="G380" t="n">
-        <v>1.62014329433441</v>
+        <v>1.62014317512512</v>
       </c>
       <c r="H380" t="n">
         <v>37514</v>
@@ -11447,7 +11447,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G382" t="n">
-        <v>1.58960843086243</v>
+        <v>1.58960819244385</v>
       </c>
       <c r="H382" t="n">
         <v>25737</v>
@@ -11476,7 +11476,7 @@
         <v>1.70299994945526</v>
       </c>
       <c r="G383" t="n">
-        <v>1.52943658828735</v>
+        <v>1.52943670749664</v>
       </c>
       <c r="H383" t="n">
         <v>66555</v>
@@ -11534,7 +11534,7 @@
         <v>1.72099995613098</v>
       </c>
       <c r="G385" t="n">
-        <v>1.54560232162476</v>
+        <v>1.54560220241547</v>
       </c>
       <c r="H385" t="n">
         <v>48776</v>
@@ -11563,7 +11563,7 @@
         <v>1.72099995613098</v>
       </c>
       <c r="G386" t="n">
-        <v>1.54560232162476</v>
+        <v>1.54560220241547</v>
       </c>
       <c r="H386" t="n">
         <v>93328</v>
@@ -11621,7 +11621,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G388" t="n">
-        <v>1.49979996681213</v>
+        <v>1.49979984760284</v>
       </c>
       <c r="H388" t="n">
         <v>107443</v>
@@ -11650,7 +11650,7 @@
         <v>1.69700002670288</v>
       </c>
       <c r="G389" t="n">
-        <v>1.52404832839966</v>
+        <v>1.52404820919037</v>
       </c>
       <c r="H389" t="n">
         <v>22102</v>
@@ -11679,7 +11679,7 @@
         <v>1.71800005435944</v>
       </c>
       <c r="G390" t="n">
-        <v>1.54290795326233</v>
+        <v>1.54290807247162</v>
       </c>
       <c r="H390" t="n">
         <v>36140</v>
@@ -11708,7 +11708,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G391" t="n">
-        <v>1.55368494987488</v>
+        <v>1.55368506908417</v>
       </c>
       <c r="H391" t="n">
         <v>67131</v>
@@ -11737,7 +11737,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G392" t="n">
-        <v>1.58511781692505</v>
+        <v>1.58511793613434</v>
       </c>
       <c r="H392" t="n">
         <v>48340</v>
@@ -11824,7 +11824,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G395" t="n">
-        <v>1.61655068397522</v>
+        <v>1.61655080318451</v>
       </c>
       <c r="H395" t="n">
         <v>19546</v>
@@ -11853,7 +11853,7 @@
         <v>1.78799998760223</v>
       </c>
       <c r="G396" t="n">
-        <v>1.60577380657196</v>
+        <v>1.60577392578125</v>
       </c>
       <c r="H396" t="n">
         <v>58873</v>
@@ -11882,7 +11882,7 @@
         <v>1.80900001525879</v>
       </c>
       <c r="G397" t="n">
-        <v>1.62463366985321</v>
+        <v>1.62463355064392</v>
       </c>
       <c r="H397" t="n">
         <v>3288</v>
@@ -11911,7 +11911,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G398" t="n">
-        <v>1.58960843086243</v>
+        <v>1.58960819244385</v>
       </c>
       <c r="H398" t="n">
         <v>55429</v>
@@ -11998,7 +11998,7 @@
         <v>1.78400003910065</v>
       </c>
       <c r="G401" t="n">
-        <v>1.60218167304993</v>
+        <v>1.60218143463135</v>
       </c>
       <c r="H401" t="n">
         <v>34154</v>
@@ -12056,7 +12056,7 @@
         <v>1.77799999713898</v>
       </c>
       <c r="G403" t="n">
-        <v>1.59679317474365</v>
+        <v>1.59679305553436</v>
       </c>
       <c r="H403" t="n">
         <v>16299</v>
@@ -12201,7 +12201,7 @@
         <v>1.78400003910065</v>
       </c>
       <c r="G408" t="n">
-        <v>1.60218167304993</v>
+        <v>1.60218143463135</v>
       </c>
       <c r="H408" t="n">
         <v>110613</v>
@@ -12230,7 +12230,7 @@
         <v>1.80400002002716</v>
       </c>
       <c r="G409" t="n">
-        <v>1.62014329433441</v>
+        <v>1.62014317512512</v>
       </c>
       <c r="H409" t="n">
         <v>53324</v>
@@ -12259,7 +12259,7 @@
         <v>1.80900001525879</v>
       </c>
       <c r="G410" t="n">
-        <v>1.62463366985321</v>
+        <v>1.62463355064392</v>
       </c>
       <c r="H410" t="n">
         <v>43219</v>
@@ -12317,7 +12317,7 @@
         <v>1.80099999904633</v>
       </c>
       <c r="G412" t="n">
-        <v>1.61744892597198</v>
+        <v>1.61744904518127</v>
       </c>
       <c r="H412" t="n">
         <v>27092</v>
@@ -12404,7 +12404,7 @@
         <v>1.75399994850159</v>
       </c>
       <c r="G415" t="n">
-        <v>1.57523882389069</v>
+        <v>1.57523894309998</v>
       </c>
       <c r="H415" t="n">
         <v>10057</v>
@@ -12433,7 +12433,7 @@
         <v>1.78600001335144</v>
       </c>
       <c r="G416" t="n">
-        <v>1.60397779941559</v>
+        <v>1.6039776802063</v>
       </c>
       <c r="H416" t="n">
         <v>17027</v>
@@ -12549,7 +12549,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G420" t="n">
-        <v>1.61655068397522</v>
+        <v>1.61655080318451</v>
       </c>
       <c r="H420" t="n">
         <v>103982</v>
@@ -12665,7 +12665,7 @@
         <v>1.85199999809265</v>
       </c>
       <c r="G424" t="n">
-        <v>1.66325128078461</v>
+        <v>1.66325116157532</v>
       </c>
       <c r="H424" t="n">
         <v>757598</v>
@@ -12839,7 +12839,7 @@
         <v>1.85199999809265</v>
       </c>
       <c r="G430" t="n">
-        <v>1.66325128078461</v>
+        <v>1.66325116157532</v>
       </c>
       <c r="H430" t="n">
         <v>107773</v>
@@ -12868,7 +12868,7 @@
         <v>1.86600005626678</v>
       </c>
       <c r="G431" t="n">
-        <v>1.6758246421814</v>
+        <v>1.67582452297211</v>
       </c>
       <c r="H431" t="n">
         <v>250835</v>
@@ -12955,7 +12955,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G434" t="n">
-        <v>1.88597595691681</v>
+        <v>1.88597583770752</v>
       </c>
       <c r="H434" t="n">
         <v>616287</v>
@@ -13013,7 +13013,7 @@
         <v>2.24600005149841</v>
       </c>
       <c r="G436" t="n">
-        <v>2.01709651947021</v>
+        <v>2.01709628105164</v>
       </c>
       <c r="H436" t="n">
         <v>460797</v>
@@ -13042,7 +13042,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G437" t="n">
-        <v>2.02966928482056</v>
+        <v>2.02966952323914</v>
       </c>
       <c r="H437" t="n">
         <v>255675</v>
@@ -13100,7 +13100,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G439" t="n">
-        <v>2.32603693008423</v>
+        <v>2.32603716850281</v>
       </c>
       <c r="H439" t="n">
         <v>793101</v>
@@ -13129,7 +13129,7 @@
         <v>2.5239999294281</v>
       </c>
       <c r="G440" t="n">
-        <v>2.26676368713379</v>
+        <v>2.26676344871521</v>
       </c>
       <c r="H440" t="n">
         <v>814395</v>
@@ -13158,7 +13158,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G441" t="n">
-        <v>2.25419020652771</v>
+        <v>2.25419044494629</v>
       </c>
       <c r="H441" t="n">
         <v>349635</v>
@@ -13303,7 +13303,7 @@
         <v>2.61800003051758</v>
       </c>
       <c r="G446" t="n">
-        <v>2.35118341445923</v>
+        <v>2.35118365287781</v>
       </c>
       <c r="H446" t="n">
         <v>133237</v>
@@ -13332,7 +13332,7 @@
         <v>2.61800003051758</v>
       </c>
       <c r="G447" t="n">
-        <v>2.35118341445923</v>
+        <v>2.35118365287781</v>
       </c>
       <c r="H447" t="n">
         <v>157247</v>
@@ -13390,7 +13390,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G449" t="n">
-        <v>2.343998670578</v>
+        <v>2.34399843215942</v>
       </c>
       <c r="H449" t="n">
         <v>156938</v>
@@ -13419,7 +13419,7 @@
         <v>2.61400008201599</v>
       </c>
       <c r="G450" t="n">
-        <v>2.34759140014648</v>
+        <v>2.34759116172791</v>
       </c>
       <c r="H450" t="n">
         <v>76654</v>
@@ -13448,7 +13448,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G451" t="n">
-        <v>2.30807518959045</v>
+        <v>2.30807542800903</v>
       </c>
       <c r="H451" t="n">
         <v>214951</v>
@@ -13477,7 +13477,7 @@
         <v>2.56399989128113</v>
       </c>
       <c r="G452" t="n">
-        <v>2.30268692970276</v>
+        <v>2.30268669128418</v>
       </c>
       <c r="H452" t="n">
         <v>110046</v>
@@ -13535,7 +13535,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G454" t="n">
-        <v>2.26317143440247</v>
+        <v>2.26317119598389</v>
       </c>
       <c r="H454" t="n">
         <v>120776</v>
@@ -13564,7 +13564,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G455" t="n">
-        <v>2.20030570030212</v>
+        <v>2.20030546188354</v>
       </c>
       <c r="H455" t="n">
         <v>150509</v>
@@ -13651,7 +13651,7 @@
         <v>2.50600004196167</v>
       </c>
       <c r="G458" t="n">
-        <v>2.25059795379639</v>
+        <v>2.25059819221497</v>
       </c>
       <c r="H458" t="n">
         <v>401496</v>
@@ -13709,7 +13709,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G460" t="n">
-        <v>2.32603693008423</v>
+        <v>2.32603716850281</v>
       </c>
       <c r="H460" t="n">
         <v>221159</v>
@@ -13738,7 +13738,7 @@
         <v>2.80200004577637</v>
       </c>
       <c r="G461" t="n">
-        <v>2.51643085479736</v>
+        <v>2.51643109321594</v>
       </c>
       <c r="H461" t="n">
         <v>904445</v>
@@ -13767,7 +13767,7 @@
         <v>2.83800005912781</v>
       </c>
       <c r="G462" t="n">
-        <v>2.54876184463501</v>
+        <v>2.54876208305359</v>
       </c>
       <c r="H462" t="n">
         <v>952565</v>
@@ -13854,7 +13854,7 @@
         <v>2.7279999256134</v>
       </c>
       <c r="G465" t="n">
-        <v>2.4499728679657</v>
+        <v>2.44997262954712</v>
       </c>
       <c r="H465" t="n">
         <v>731544</v>
@@ -13883,7 +13883,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G466" t="n">
-        <v>2.45176863670349</v>
+        <v>2.45176887512207</v>
       </c>
       <c r="H466" t="n">
         <v>573169</v>
@@ -13941,7 +13941,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G468" t="n">
-        <v>2.50565385818481</v>
+        <v>2.50565361976624</v>
       </c>
       <c r="H468" t="n">
         <v>122440</v>
@@ -13999,7 +13999,7 @@
         <v>2.87599992752075</v>
       </c>
       <c r="G470" t="n">
-        <v>2.58288908004761</v>
+        <v>2.58288884162903</v>
       </c>
       <c r="H470" t="n">
         <v>115197</v>
@@ -14028,7 +14028,7 @@
         <v>2.87599992752075</v>
       </c>
       <c r="G471" t="n">
-        <v>2.58288908004761</v>
+        <v>2.58288884162903</v>
       </c>
       <c r="H471" t="n">
         <v>65266</v>
@@ -14086,7 +14086,7 @@
         <v>2.7739999294281</v>
       </c>
       <c r="G473" t="n">
-        <v>2.49128437042236</v>
+        <v>2.49128460884094</v>
       </c>
       <c r="H473" t="n">
         <v>164387</v>
@@ -14115,7 +14115,7 @@
         <v>2.79200005531311</v>
       </c>
       <c r="G474" t="n">
-        <v>2.50744986534119</v>
+        <v>2.50745010375977</v>
       </c>
       <c r="H474" t="n">
         <v>83459</v>
@@ -14260,7 +14260,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G479" t="n">
-        <v>2.16438221931458</v>
+        <v>2.164381980896</v>
       </c>
       <c r="H479" t="n">
         <v>417186</v>
@@ -14318,7 +14318,7 @@
         <v>2.25600004196167</v>
       </c>
       <c r="G481" t="n">
-        <v>2.02607727050781</v>
+        <v>2.02607703208923</v>
       </c>
       <c r="H481" t="n">
         <v>252490</v>
@@ -14376,7 +14376,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G483" t="n">
-        <v>2.16438221931458</v>
+        <v>2.164381980896</v>
       </c>
       <c r="H483" t="n">
         <v>373105</v>
@@ -14405,7 +14405,7 @@
         <v>2.49399995803833</v>
       </c>
       <c r="G484" t="n">
-        <v>2.23982095718384</v>
+        <v>2.23982119560242</v>
       </c>
       <c r="H484" t="n">
         <v>493546</v>
@@ -14521,7 +14521,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G488" t="n">
-        <v>2.25419020652771</v>
+        <v>2.25419044494629</v>
       </c>
       <c r="H488" t="n">
         <v>81174</v>
@@ -14579,7 +14579,7 @@
         <v>2.62199997901917</v>
       </c>
       <c r="G490" t="n">
-        <v>2.35477590560913</v>
+        <v>2.35477566719055</v>
       </c>
       <c r="H490" t="n">
         <v>259369</v>
@@ -14608,7 +14608,7 @@
         <v>2.55800008773804</v>
       </c>
       <c r="G491" t="n">
-        <v>2.29729819297791</v>
+        <v>2.29729866981506</v>
       </c>
       <c r="H491" t="n">
         <v>201051</v>
@@ -14637,7 +14637,7 @@
         <v>2.51399993896484</v>
       </c>
       <c r="G492" t="n">
-        <v>2.25778269767761</v>
+        <v>2.25778245925903</v>
       </c>
       <c r="H492" t="n">
         <v>74824</v>
@@ -14666,7 +14666,7 @@
         <v>2.48399996757507</v>
       </c>
       <c r="G493" t="n">
-        <v>2.23083996772766</v>
+        <v>2.23084020614624</v>
       </c>
       <c r="H493" t="n">
         <v>58887</v>
@@ -14695,7 +14695,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G494" t="n">
-        <v>2.20928621292114</v>
+        <v>2.20928645133972</v>
       </c>
       <c r="H494" t="n">
         <v>52081</v>
@@ -14753,7 +14753,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G496" t="n">
-        <v>2.23622894287109</v>
+        <v>2.23622870445251</v>
       </c>
       <c r="H496" t="n">
         <v>95489</v>
@@ -14782,7 +14782,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G497" t="n">
-        <v>2.20928621292114</v>
+        <v>2.20928645133972</v>
       </c>
       <c r="H497" t="n">
         <v>17558</v>
@@ -14811,7 +14811,7 @@
         <v>2.51399993896484</v>
       </c>
       <c r="G498" t="n">
-        <v>2.25778269767761</v>
+        <v>2.25778245925903</v>
       </c>
       <c r="H498" t="n">
         <v>63229</v>
@@ -14898,7 +14898,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G501" t="n">
-        <v>2.23622894287109</v>
+        <v>2.23622870445251</v>
       </c>
       <c r="H501" t="n">
         <v>57670</v>
@@ -14985,7 +14985,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G504" t="n">
-        <v>2.22724795341492</v>
+        <v>2.22724771499634</v>
       </c>
       <c r="H504" t="n">
         <v>89542</v>
@@ -15014,7 +15014,7 @@
         <v>2.5239999294281</v>
       </c>
       <c r="G505" t="n">
-        <v>2.26676368713379</v>
+        <v>2.26676344871521</v>
       </c>
       <c r="H505" t="n">
         <v>167428</v>
@@ -15072,7 +15072,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G507" t="n">
-        <v>2.22724795341492</v>
+        <v>2.22724771499634</v>
       </c>
       <c r="H507" t="n">
         <v>48876</v>
@@ -15101,7 +15101,7 @@
         <v>2.45199990272522</v>
       </c>
       <c r="G508" t="n">
-        <v>2.20210146903992</v>
+        <v>2.20210123062134</v>
       </c>
       <c r="H508" t="n">
         <v>123957</v>
@@ -15130,7 +15130,7 @@
         <v>2.43799996376038</v>
       </c>
       <c r="G509" t="n">
-        <v>2.189528465271</v>
+        <v>2.18952822685242</v>
       </c>
       <c r="H509" t="n">
         <v>58859</v>
@@ -15159,7 +15159,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G510" t="n">
-        <v>2.19850897789001</v>
+        <v>2.19850921630859</v>
       </c>
       <c r="H510" t="n">
         <v>53234</v>
@@ -15217,7 +15217,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G512" t="n">
-        <v>2.19132447242737</v>
+        <v>2.19132471084595</v>
       </c>
       <c r="H512" t="n">
         <v>101821</v>
@@ -15246,7 +15246,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G513" t="n">
-        <v>2.18234372138977</v>
+        <v>2.18234395980835</v>
       </c>
       <c r="H513" t="n">
         <v>98129</v>
@@ -15275,7 +15275,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G514" t="n">
-        <v>2.15540146827698</v>
+        <v>2.1554012298584</v>
       </c>
       <c r="H514" t="n">
         <v>62182</v>
@@ -15304,7 +15304,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G515" t="n">
-        <v>2.19132447242737</v>
+        <v>2.19132471084595</v>
       </c>
       <c r="H515" t="n">
         <v>50871</v>
@@ -15333,7 +15333,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G516" t="n">
-        <v>2.22724795341492</v>
+        <v>2.22724771499634</v>
       </c>
       <c r="H516" t="n">
         <v>124471</v>
@@ -15362,7 +15362,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G517" t="n">
-        <v>2.22724795341492</v>
+        <v>2.22724771499634</v>
       </c>
       <c r="H517" t="n">
         <v>74248</v>
@@ -15391,7 +15391,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G518" t="n">
-        <v>2.21826720237732</v>
+        <v>2.21826672554016</v>
       </c>
       <c r="H518" t="n">
         <v>107211</v>
@@ -15420,7 +15420,7 @@
         <v>2.43499994277954</v>
       </c>
       <c r="G519" t="n">
-        <v>2.18683409690857</v>
+        <v>2.18683385848999</v>
       </c>
       <c r="H519" t="n">
         <v>50889</v>
@@ -15449,7 +15449,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G520" t="n">
-        <v>2.15540146827698</v>
+        <v>2.1554012298584</v>
       </c>
       <c r="H520" t="n">
         <v>47165</v>
@@ -15478,7 +15478,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G521" t="n">
-        <v>2.16438221931458</v>
+        <v>2.164381980896</v>
       </c>
       <c r="H521" t="n">
         <v>183144</v>
@@ -15507,7 +15507,7 @@
         <v>2.42499995231628</v>
       </c>
       <c r="G522" t="n">
-        <v>2.17785334587097</v>
+        <v>2.17785310745239</v>
       </c>
       <c r="H522" t="n">
         <v>82741</v>
@@ -15565,7 +15565,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G524" t="n">
-        <v>2.04763078689575</v>
+        <v>2.04763126373291</v>
       </c>
       <c r="H524" t="n">
         <v>233885</v>
@@ -15681,7 +15681,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G528" t="n">
-        <v>2.0835542678833</v>
+        <v>2.08355450630188</v>
       </c>
       <c r="H528" t="n">
         <v>61089</v>
@@ -15710,7 +15710,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G529" t="n">
-        <v>2.0745735168457</v>
+        <v>2.07457375526428</v>
       </c>
       <c r="H529" t="n">
         <v>27581</v>
@@ -15826,7 +15826,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G533" t="n">
-        <v>2.15540146827698</v>
+        <v>2.1554012298584</v>
       </c>
       <c r="H533" t="n">
         <v>68783</v>
@@ -15855,7 +15855,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G534" t="n">
-        <v>2.13743996620178</v>
+        <v>2.1374397277832</v>
       </c>
       <c r="H534" t="n">
         <v>38703</v>
@@ -15884,7 +15884,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G535" t="n">
-        <v>2.11947774887085</v>
+        <v>2.11947751045227</v>
       </c>
       <c r="H535" t="n">
         <v>99717</v>
@@ -15971,7 +15971,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G538" t="n">
-        <v>2.15540146827698</v>
+        <v>2.1554012298584</v>
       </c>
       <c r="H538" t="n">
         <v>281784</v>
@@ -16319,7 +16319,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G550" t="n">
-        <v>2.0745735168457</v>
+        <v>2.07457375526428</v>
       </c>
       <c r="H550" t="n">
         <v>109305</v>
@@ -16348,7 +16348,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G551" t="n">
-        <v>2.04763078689575</v>
+        <v>2.04763126373291</v>
       </c>
       <c r="H551" t="n">
         <v>51292</v>
@@ -16377,7 +16377,7 @@
         <v>2.21499991416931</v>
       </c>
       <c r="G552" t="n">
-        <v>1.9892555475235</v>
+        <v>1.98925566673279</v>
       </c>
       <c r="H552" t="n">
         <v>123803</v>
@@ -16406,7 +16406,7 @@
         <v>2.14499998092651</v>
       </c>
       <c r="G553" t="n">
-        <v>1.92638993263245</v>
+        <v>1.92638981342316</v>
       </c>
       <c r="H553" t="n">
         <v>175487</v>
@@ -16435,7 +16435,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G554" t="n">
-        <v>1.87699520587921</v>
+        <v>1.87699496746063</v>
       </c>
       <c r="H554" t="n">
         <v>92111</v>
@@ -16493,7 +16493,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G556" t="n">
-        <v>1.85005247592926</v>
+        <v>1.85005271434784</v>
       </c>
       <c r="H556" t="n">
         <v>37112</v>
@@ -16522,7 +16522,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G557" t="n">
-        <v>1.91291844844818</v>
+        <v>1.91291868686676</v>
       </c>
       <c r="H557" t="n">
         <v>103311</v>
@@ -16551,7 +16551,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G558" t="n">
-        <v>1.92189943790436</v>
+        <v>1.92189931869507</v>
       </c>
       <c r="H558" t="n">
         <v>89704</v>
@@ -16580,7 +16580,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G559" t="n">
-        <v>1.94884181022644</v>
+        <v>1.94884216785431</v>
       </c>
       <c r="H559" t="n">
         <v>132375</v>
@@ -16725,7 +16725,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G564" t="n">
-        <v>2.06110215187073</v>
+        <v>2.06110262870789</v>
       </c>
       <c r="H564" t="n">
         <v>80977</v>
@@ -16899,7 +16899,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G570" t="n">
-        <v>1.94884181022644</v>
+        <v>1.94884216785431</v>
       </c>
       <c r="H570" t="n">
         <v>32611</v>
@@ -16957,7 +16957,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G572" t="n">
-        <v>1.91291844844818</v>
+        <v>1.91291868686676</v>
       </c>
       <c r="H572" t="n">
         <v>49060</v>
@@ -17247,7 +17247,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G582" t="n">
-        <v>2.05661177635193</v>
+        <v>2.05661201477051</v>
       </c>
       <c r="H582" t="n">
         <v>69994</v>
@@ -17276,7 +17276,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G583" t="n">
-        <v>2.03865027427673</v>
+        <v>2.03865003585815</v>
       </c>
       <c r="H583" t="n">
         <v>32623</v>
@@ -17334,7 +17334,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G585" t="n">
-        <v>2.04763078689575</v>
+        <v>2.04763126373291</v>
       </c>
       <c r="H585" t="n">
         <v>8638</v>
@@ -17363,7 +17363,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G586" t="n">
-        <v>2.0835542678833</v>
+        <v>2.08355450630188</v>
       </c>
       <c r="H586" t="n">
         <v>83509</v>
@@ -17392,7 +17392,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G587" t="n">
-        <v>2.06110215187073</v>
+        <v>2.06110262870789</v>
       </c>
       <c r="H587" t="n">
         <v>59626</v>
@@ -17508,7 +17508,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G591" t="n">
-        <v>2.0745735168457</v>
+        <v>2.07457375526428</v>
       </c>
       <c r="H591" t="n">
         <v>30375</v>
@@ -17537,7 +17537,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G592" t="n">
-        <v>2.06110215187073</v>
+        <v>2.06110262870789</v>
       </c>
       <c r="H592" t="n">
         <v>23900</v>
@@ -17624,7 +17624,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G595" t="n">
-        <v>2.0745735168457</v>
+        <v>2.07457375526428</v>
       </c>
       <c r="H595" t="n">
         <v>36494</v>
@@ -17653,7 +17653,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G596" t="n">
-        <v>2.0835542678833</v>
+        <v>2.08355450630188</v>
       </c>
       <c r="H596" t="n">
         <v>23339</v>
@@ -17682,7 +17682,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G597" t="n">
-        <v>2.0745735168457</v>
+        <v>2.07457375526428</v>
       </c>
       <c r="H597" t="n">
         <v>30236</v>
@@ -17711,7 +17711,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G598" t="n">
-        <v>2.23622894287109</v>
+        <v>2.23622870445251</v>
       </c>
       <c r="H598" t="n">
         <v>587158</v>
@@ -17740,7 +17740,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G599" t="n">
-        <v>2.23622894287109</v>
+        <v>2.23622870445251</v>
       </c>
       <c r="H599" t="n">
         <v>694433</v>
@@ -17769,7 +17769,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G600" t="n">
-        <v>2.32603693008423</v>
+        <v>2.32603716850281</v>
       </c>
       <c r="H600" t="n">
         <v>234645</v>
@@ -17827,7 +17827,7 @@
         <v>2.47499990463257</v>
       </c>
       <c r="G602" t="n">
-        <v>2.22275733947754</v>
+        <v>2.22275757789612</v>
       </c>
       <c r="H602" t="n">
         <v>96271</v>
@@ -17856,7 +17856,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G603" t="n">
-        <v>2.21826720237732</v>
+        <v>2.21826672554016</v>
       </c>
       <c r="H603" t="n">
         <v>66824</v>
@@ -17885,7 +17885,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G604" t="n">
-        <v>2.20030570030212</v>
+        <v>2.20030546188354</v>
       </c>
       <c r="H604" t="n">
         <v>38475</v>
@@ -17914,7 +17914,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G605" t="n">
-        <v>2.11947774887085</v>
+        <v>2.11947751045227</v>
       </c>
       <c r="H605" t="n">
         <v>89012</v>
@@ -18146,7 +18146,7 @@
         <v>2.22499990463257</v>
       </c>
       <c r="G613" t="n">
-        <v>1.99823641777039</v>
+        <v>1.99823653697968</v>
       </c>
       <c r="H613" t="n">
         <v>76914</v>
@@ -18233,7 +18233,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G616" t="n">
-        <v>2.02966928482056</v>
+        <v>2.02966952323914</v>
       </c>
       <c r="H616" t="n">
         <v>49483</v>
@@ -18262,7 +18262,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G617" t="n">
-        <v>2.04763078689575</v>
+        <v>2.04763126373291</v>
       </c>
       <c r="H617" t="n">
         <v>74739</v>
@@ -18349,7 +18349,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G620" t="n">
-        <v>2.02966928482056</v>
+        <v>2.02966952323914</v>
       </c>
       <c r="H620" t="n">
         <v>58818</v>
@@ -18378,7 +18378,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G621" t="n">
-        <v>2.04763078689575</v>
+        <v>2.04763126373291</v>
       </c>
       <c r="H621" t="n">
         <v>34438</v>
@@ -18436,7 +18436,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G623" t="n">
-        <v>2.06110215187073</v>
+        <v>2.06110262870789</v>
       </c>
       <c r="H623" t="n">
         <v>21291</v>
@@ -18465,7 +18465,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G624" t="n">
-        <v>2.02966928482056</v>
+        <v>2.02966952323914</v>
       </c>
       <c r="H624" t="n">
         <v>22488</v>
@@ -18552,7 +18552,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G627" t="n">
-        <v>2.04763078689575</v>
+        <v>2.04763126373291</v>
       </c>
       <c r="H627" t="n">
         <v>13812</v>
@@ -18610,7 +18610,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G629" t="n">
-        <v>2.02517890930176</v>
+        <v>2.02517914772034</v>
       </c>
       <c r="H629" t="n">
         <v>20116</v>
@@ -18697,7 +18697,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G632" t="n">
-        <v>2.05661177635193</v>
+        <v>2.05661201477051</v>
       </c>
       <c r="H632" t="n">
         <v>16723</v>
@@ -18813,7 +18813,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G636" t="n">
-        <v>1.95782279968262</v>
+        <v>1.95782291889191</v>
       </c>
       <c r="H636" t="n">
         <v>18514</v>
@@ -18929,7 +18929,7 @@
         <v>2.22499990463257</v>
       </c>
       <c r="G640" t="n">
-        <v>1.99823641777039</v>
+        <v>1.99823653697968</v>
       </c>
       <c r="H640" t="n">
         <v>33589</v>
@@ -19074,7 +19074,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G645" t="n">
-        <v>1.95782279968262</v>
+        <v>1.95782291889191</v>
       </c>
       <c r="H645" t="n">
         <v>5655</v>
@@ -19132,7 +19132,7 @@
         <v>2.1949999332428</v>
       </c>
       <c r="G647" t="n">
-        <v>1.97129380702972</v>
+        <v>1.97129392623901</v>
       </c>
       <c r="H647" t="n">
         <v>2598</v>
@@ -19190,7 +19190,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G649" t="n">
-        <v>1.95782279968262</v>
+        <v>1.95782291889191</v>
       </c>
       <c r="H649" t="n">
         <v>11364</v>
@@ -19219,7 +19219,7 @@
         <v>2.18499994277954</v>
       </c>
       <c r="G650" t="n">
-        <v>1.96231293678284</v>
+        <v>1.96231305599213</v>
       </c>
       <c r="H650" t="n">
         <v>4540</v>
@@ -19277,7 +19277,7 @@
         <v>2.13499999046326</v>
       </c>
       <c r="G652" t="n">
-        <v>1.91740894317627</v>
+        <v>1.91740882396698</v>
       </c>
       <c r="H652" t="n">
         <v>14340</v>
@@ -19306,7 +19306,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G653" t="n">
-        <v>1.95782279968262</v>
+        <v>1.95782291889191</v>
       </c>
       <c r="H653" t="n">
         <v>7716</v>
@@ -19364,7 +19364,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G655" t="n">
-        <v>1.94884181022644</v>
+        <v>1.94884216785431</v>
       </c>
       <c r="H655" t="n">
         <v>8943</v>
@@ -19393,7 +19393,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G656" t="n">
-        <v>1.8949568271637</v>
+        <v>1.89495670795441</v>
       </c>
       <c r="H656" t="n">
         <v>71608</v>
@@ -19422,7 +19422,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G657" t="n">
-        <v>1.92189943790436</v>
+        <v>1.92189931869507</v>
       </c>
       <c r="H657" t="n">
         <v>25122</v>
@@ -19451,7 +19451,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G658" t="n">
-        <v>1.8949568271637</v>
+        <v>1.89495670795441</v>
       </c>
       <c r="H658" t="n">
         <v>29865</v>
@@ -19509,7 +19509,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G660" t="n">
-        <v>1.92189943790436</v>
+        <v>1.92189931869507</v>
       </c>
       <c r="H660" t="n">
         <v>41945</v>
@@ -19596,7 +19596,7 @@
         <v>2.125</v>
       </c>
       <c r="G663" t="n">
-        <v>1.90842807292938</v>
+        <v>1.90842819213867</v>
       </c>
       <c r="H663" t="n">
         <v>16492</v>
@@ -19683,7 +19683,7 @@
         <v>2.14499998092651</v>
       </c>
       <c r="G666" t="n">
-        <v>1.92638993263245</v>
+        <v>1.92638981342316</v>
       </c>
       <c r="H666" t="n">
         <v>17689</v>
@@ -19770,7 +19770,7 @@
         <v>2.14499998092651</v>
       </c>
       <c r="G669" t="n">
-        <v>1.92638993263245</v>
+        <v>1.92638981342316</v>
       </c>
       <c r="H669" t="n">
         <v>28810</v>
@@ -19857,7 +19857,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G672" t="n">
-        <v>1.95782279968262</v>
+        <v>1.95782291889191</v>
       </c>
       <c r="H672" t="n">
         <v>30719</v>
@@ -20002,7 +20002,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G677" t="n">
-        <v>2.03865027427673</v>
+        <v>2.03865003585815</v>
       </c>
       <c r="H677" t="n">
         <v>13543</v>
@@ -20031,7 +20031,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G678" t="n">
-        <v>2.03865027427673</v>
+        <v>2.03865003585815</v>
       </c>
       <c r="H678" t="n">
         <v>54963</v>
@@ -20147,7 +20147,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G682" t="n">
-        <v>1.94884181022644</v>
+        <v>1.94884216785431</v>
       </c>
       <c r="H682" t="n">
         <v>39975</v>
@@ -20176,7 +20176,7 @@
         <v>2.17499995231628</v>
       </c>
       <c r="G683" t="n">
-        <v>1.95333230495453</v>
+        <v>1.95333206653595</v>
       </c>
       <c r="H683" t="n">
         <v>6570</v>
@@ -20234,7 +20234,7 @@
         <v>2.21499991416931</v>
       </c>
       <c r="G685" t="n">
-        <v>1.9892555475235</v>
+        <v>1.98925566673279</v>
       </c>
       <c r="H685" t="n">
         <v>49471</v>
@@ -20263,7 +20263,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G686" t="n">
-        <v>2.05661177635193</v>
+        <v>2.05661201477051</v>
       </c>
       <c r="H686" t="n">
         <v>71272</v>
@@ -20292,7 +20292,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G687" t="n">
-        <v>2.05661177635193</v>
+        <v>2.05661201477051</v>
       </c>
       <c r="H687" t="n">
         <v>59680</v>
@@ -20321,7 +20321,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G688" t="n">
-        <v>2.0745735168457</v>
+        <v>2.07457375526428</v>
       </c>
       <c r="H688" t="n">
         <v>22893</v>
@@ -20408,7 +20408,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G691" t="n">
-        <v>2.03865027427673</v>
+        <v>2.03865003585815</v>
       </c>
       <c r="H691" t="n">
         <v>3909</v>
@@ -20437,7 +20437,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G692" t="n">
-        <v>2.02517890930176</v>
+        <v>2.02517914772034</v>
       </c>
       <c r="H692" t="n">
         <v>2595</v>
@@ -20495,7 +20495,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G694" t="n">
-        <v>2.0745735168457</v>
+        <v>2.07457375526428</v>
       </c>
       <c r="H694" t="n">
         <v>50527</v>
@@ -20524,7 +20524,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G695" t="n">
-        <v>2.05661177635193</v>
+        <v>2.05661201477051</v>
       </c>
       <c r="H695" t="n">
         <v>8106</v>
@@ -20611,7 +20611,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G698" t="n">
-        <v>2.06110215187073</v>
+        <v>2.06110262870789</v>
       </c>
       <c r="H698" t="n">
         <v>7245</v>
@@ -20669,7 +20669,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G700" t="n">
-        <v>2.02966928482056</v>
+        <v>2.02966952323914</v>
       </c>
       <c r="H700" t="n">
         <v>5195</v>
@@ -20727,7 +20727,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G702" t="n">
-        <v>2.02517890930176</v>
+        <v>2.02517914772034</v>
       </c>
       <c r="H702" t="n">
         <v>35459</v>
@@ -20756,7 +20756,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G703" t="n">
-        <v>2.03865027427673</v>
+        <v>2.03865003585815</v>
       </c>
       <c r="H703" t="n">
         <v>2475</v>
@@ -20814,7 +20814,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G705" t="n">
-        <v>2.02517890930176</v>
+        <v>2.02517914772034</v>
       </c>
       <c r="H705" t="n">
         <v>1661</v>
@@ -20872,7 +20872,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G707" t="n">
-        <v>1.91291844844818</v>
+        <v>1.91291868686676</v>
       </c>
       <c r="H707" t="n">
         <v>21836</v>
@@ -20901,7 +20901,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G708" t="n">
-        <v>1.92189943790436</v>
+        <v>1.92189931869507</v>
       </c>
       <c r="H708" t="n">
         <v>59815</v>
@@ -20930,7 +20930,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G709" t="n">
-        <v>1.85005247592926</v>
+        <v>1.85005271434784</v>
       </c>
       <c r="H709" t="n">
         <v>57600</v>
@@ -20959,7 +20959,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G710" t="n">
-        <v>1.77820587158203</v>
+        <v>1.77820599079132</v>
       </c>
       <c r="H710" t="n">
         <v>41058</v>
@@ -21017,7 +21017,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G712" t="n">
-        <v>1.85903346538544</v>
+        <v>1.85903334617615</v>
       </c>
       <c r="H712" t="n">
         <v>49612</v>
@@ -21046,7 +21046,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G713" t="n">
-        <v>1.92189943790436</v>
+        <v>1.92189931869507</v>
       </c>
       <c r="H713" t="n">
         <v>14008</v>
@@ -21075,7 +21075,7 @@
         <v>2.07500004768372</v>
       </c>
       <c r="G714" t="n">
-        <v>1.86352396011353</v>
+        <v>1.86352407932281</v>
       </c>
       <c r="H714" t="n">
         <v>30060</v>
@@ -21104,7 +21104,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G715" t="n">
-        <v>1.8051483631134</v>
+        <v>1.80514848232269</v>
       </c>
       <c r="H715" t="n">
         <v>29989</v>
@@ -21162,7 +21162,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G717" t="n">
-        <v>1.76024425029755</v>
+        <v>1.76024436950684</v>
       </c>
       <c r="H717" t="n">
         <v>10455</v>
@@ -21191,7 +21191,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G718" t="n">
-        <v>1.75126349925995</v>
+        <v>1.75126361846924</v>
       </c>
       <c r="H718" t="n">
         <v>13797</v>
@@ -21220,7 +21220,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G719" t="n">
-        <v>1.76922512054443</v>
+        <v>1.76922500133514</v>
       </c>
       <c r="H719" t="n">
         <v>20654</v>
@@ -21249,7 +21249,7 @@
         <v>1.92599999904633</v>
       </c>
       <c r="G720" t="n">
-        <v>1.72970938682556</v>
+        <v>1.72970950603485</v>
       </c>
       <c r="H720" t="n">
         <v>9061</v>
@@ -21278,7 +21278,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G721" t="n">
-        <v>1.65247428417206</v>
+        <v>1.65247416496277</v>
       </c>
       <c r="H721" t="n">
         <v>47767</v>
@@ -21307,7 +21307,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G722" t="n">
-        <v>1.65247428417206</v>
+        <v>1.65247416496277</v>
       </c>
       <c r="H722" t="n">
         <v>49356</v>
@@ -21365,7 +21365,7 @@
         <v>1.89400005340576</v>
       </c>
       <c r="G724" t="n">
-        <v>1.70097076892853</v>
+        <v>1.70097088813782</v>
       </c>
       <c r="H724" t="n">
         <v>126727</v>
@@ -21394,7 +21394,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G725" t="n">
-        <v>1.76024425029755</v>
+        <v>1.76024436950684</v>
       </c>
       <c r="H725" t="n">
         <v>31378</v>
@@ -21423,7 +21423,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G726" t="n">
-        <v>1.67941677570343</v>
+        <v>1.67941665649414</v>
       </c>
       <c r="H726" t="n">
         <v>135018</v>
@@ -21452,7 +21452,7 @@
         <v>1.81599998474121</v>
       </c>
       <c r="G727" t="n">
-        <v>1.63092005252838</v>
+        <v>1.63092029094696</v>
       </c>
       <c r="H727" t="n">
         <v>33529</v>
@@ -21481,7 +21481,7 @@
         <v>1.83399999141693</v>
       </c>
       <c r="G728" t="n">
-        <v>1.64708578586578</v>
+        <v>1.64708566665649</v>
       </c>
       <c r="H728" t="n">
         <v>5430</v>
@@ -21539,7 +21539,7 @@
         <v>1.81599998474121</v>
       </c>
       <c r="G730" t="n">
-        <v>1.63092005252838</v>
+        <v>1.63092029094696</v>
       </c>
       <c r="H730" t="n">
         <v>15018</v>
@@ -21684,7 +21684,7 @@
         <v>1.72599995136261</v>
       </c>
       <c r="G735" t="n">
-        <v>1.55009257793427</v>
+        <v>1.55009269714355</v>
       </c>
       <c r="H735" t="n">
         <v>13578</v>
@@ -21713,7 +21713,7 @@
         <v>1.65400004386902</v>
       </c>
       <c r="G736" t="n">
-        <v>1.48543071746826</v>
+        <v>1.48543059825897</v>
       </c>
       <c r="H736" t="n">
         <v>40424</v>
@@ -21829,7 +21829,7 @@
         <v>1.59800004959106</v>
       </c>
       <c r="G740" t="n">
-        <v>1.43513810634613</v>
+        <v>1.43513798713684</v>
       </c>
       <c r="H740" t="n">
         <v>10009</v>
@@ -22003,7 +22003,7 @@
         <v>1.49600005149841</v>
       </c>
       <c r="G746" t="n">
-        <v>1.34353351593018</v>
+        <v>1.34353339672089</v>
       </c>
       <c r="H746" t="n">
         <v>50501</v>
@@ -22032,7 +22032,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G747" t="n">
-        <v>1.39202976226807</v>
+        <v>1.39202988147736</v>
       </c>
       <c r="H747" t="n">
         <v>44278</v>
@@ -22061,7 +22061,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G748" t="n">
-        <v>1.40101063251495</v>
+        <v>1.40101075172424</v>
       </c>
       <c r="H748" t="n">
         <v>15572</v>
@@ -22177,7 +22177,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G752" t="n">
-        <v>1.30222165584564</v>
+        <v>1.30222153663635</v>
       </c>
       <c r="H752" t="n">
         <v>11882</v>
@@ -22206,7 +22206,7 @@
         <v>1.40600001811981</v>
       </c>
       <c r="G753" t="n">
-        <v>1.26270580291748</v>
+        <v>1.26270592212677</v>
       </c>
       <c r="H753" t="n">
         <v>68829</v>
@@ -22235,7 +22235,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G754" t="n">
-        <v>1.22139394283295</v>
+        <v>1.22139406204224</v>
       </c>
       <c r="H754" t="n">
         <v>44371</v>
@@ -22264,7 +22264,7 @@
         <v>1.41600000858307</v>
       </c>
       <c r="G755" t="n">
-        <v>1.27168655395508</v>
+        <v>1.27168667316437</v>
       </c>
       <c r="H755" t="n">
         <v>45386</v>
@@ -22409,7 +22409,7 @@
         <v>1.25399994850159</v>
       </c>
       <c r="G760" t="n">
-        <v>1.12619709968567</v>
+        <v>1.12619698047638</v>
       </c>
       <c r="H760" t="n">
         <v>78907</v>
@@ -22467,7 +22467,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G762" t="n">
-        <v>1.14954733848572</v>
+        <v>1.14954721927643</v>
       </c>
       <c r="H762" t="n">
         <v>30043</v>
@@ -22496,7 +22496,7 @@
         <v>1.30400002002716</v>
       </c>
       <c r="G763" t="n">
-        <v>1.17110121250153</v>
+        <v>1.1711014509201</v>
       </c>
       <c r="H763" t="n">
         <v>48686</v>
@@ -22525,7 +22525,7 @@
         <v>1.36800003051758</v>
       </c>
       <c r="G764" t="n">
-        <v>1.22857868671417</v>
+        <v>1.22857880592346</v>
       </c>
       <c r="H764" t="n">
         <v>113578</v>
@@ -22583,7 +22583,7 @@
         <v>1.52799999713898</v>
       </c>
       <c r="G766" t="n">
-        <v>1.3722722530365</v>
+        <v>1.37227213382721</v>
       </c>
       <c r="H766" t="n">
         <v>166018</v>
@@ -22612,7 +22612,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G767" t="n">
-        <v>1.40999162197113</v>
+        <v>1.40999150276184</v>
       </c>
       <c r="H767" t="n">
         <v>144581</v>
@@ -22641,7 +22641,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G768" t="n">
-        <v>1.40999162197113</v>
+        <v>1.40999150276184</v>
       </c>
       <c r="H768" t="n">
         <v>41592</v>
@@ -22757,7 +22757,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G772" t="n">
-        <v>1.31120240688324</v>
+        <v>1.31120252609253</v>
       </c>
       <c r="H772" t="n">
         <v>71525</v>
@@ -22786,7 +22786,7 @@
         <v>1.47800004482269</v>
       </c>
       <c r="G773" t="n">
-        <v>1.32736778259277</v>
+        <v>1.32736790180206</v>
       </c>
       <c r="H773" t="n">
         <v>32846</v>
@@ -22815,7 +22815,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G774" t="n">
-        <v>1.33814489841461</v>
+        <v>1.3381450176239</v>
       </c>
       <c r="H774" t="n">
         <v>16878</v>
@@ -22844,7 +22844,7 @@
         <v>1.49600005149841</v>
       </c>
       <c r="G775" t="n">
-        <v>1.34353351593018</v>
+        <v>1.34353339672089</v>
       </c>
       <c r="H775" t="n">
         <v>8974</v>
@@ -23018,7 +23018,7 @@
         <v>1.49600005149841</v>
       </c>
       <c r="G781" t="n">
-        <v>1.34353351593018</v>
+        <v>1.34353339672089</v>
       </c>
       <c r="H781" t="n">
         <v>72453</v>
@@ -23047,7 +23047,7 @@
         <v>1.49800002574921</v>
       </c>
       <c r="G782" t="n">
-        <v>1.34532952308655</v>
+        <v>1.34532964229584</v>
       </c>
       <c r="H782" t="n">
         <v>53053</v>
@@ -23163,7 +23163,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G786" t="n">
-        <v>1.31120240688324</v>
+        <v>1.31120252609253</v>
       </c>
       <c r="H786" t="n">
         <v>38062</v>
@@ -23250,7 +23250,7 @@
         <v>1.40199995040894</v>
       </c>
       <c r="G789" t="n">
-        <v>1.25911343097687</v>
+        <v>1.25911355018616</v>
       </c>
       <c r="H789" t="n">
         <v>38229</v>
@@ -23308,7 +23308,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G791" t="n">
-        <v>1.23037493228912</v>
+        <v>1.23037481307983</v>
       </c>
       <c r="H791" t="n">
         <v>9601</v>
@@ -23337,7 +23337,7 @@
         <v>1.38800001144409</v>
       </c>
       <c r="G792" t="n">
-        <v>1.24654030799866</v>
+        <v>1.24654042720795</v>
       </c>
       <c r="H792" t="n">
         <v>43409</v>
@@ -23366,7 +23366,7 @@
         <v>1.41799998283386</v>
       </c>
       <c r="G793" t="n">
-        <v>1.27348291873932</v>
+        <v>1.27348279953003</v>
       </c>
       <c r="H793" t="n">
         <v>147492</v>
@@ -23395,7 +23395,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G794" t="n">
-        <v>1.45309972763062</v>
+        <v>1.45309960842133</v>
       </c>
       <c r="H794" t="n">
         <v>697644</v>
@@ -23453,7 +23453,7 @@
         <v>1.71800005435944</v>
       </c>
       <c r="G796" t="n">
-        <v>1.54290795326233</v>
+        <v>1.54290807247162</v>
       </c>
       <c r="H796" t="n">
         <v>264844</v>
@@ -23482,7 +23482,7 @@
         <v>1.89800000190735</v>
       </c>
       <c r="G797" t="n">
-        <v>1.70456302165985</v>
+        <v>1.70456314086914</v>
       </c>
       <c r="H797" t="n">
         <v>898372</v>
@@ -23511,7 +23511,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G798" t="n">
-        <v>1.65247428417206</v>
+        <v>1.65247416496277</v>
       </c>
       <c r="H798" t="n">
         <v>461676</v>
@@ -23540,7 +23540,7 @@
         <v>1.78199994564056</v>
       </c>
       <c r="G799" t="n">
-        <v>1.60038530826569</v>
+        <v>1.60038542747498</v>
       </c>
       <c r="H799" t="n">
         <v>184959</v>
@@ -23569,7 +23569,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G800" t="n">
-        <v>1.65247428417206</v>
+        <v>1.65247416496277</v>
       </c>
       <c r="H800" t="n">
         <v>179707</v>
@@ -23598,7 +23598,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G801" t="n">
-        <v>1.84107172489166</v>
+        <v>1.84107184410095</v>
       </c>
       <c r="H801" t="n">
         <v>1306104</v>
@@ -23656,7 +23656,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G803" t="n">
-        <v>1.88597595691681</v>
+        <v>1.88597583770752</v>
       </c>
       <c r="H803" t="n">
         <v>354581</v>
@@ -23685,7 +23685,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G804" t="n">
-        <v>1.85005247592926</v>
+        <v>1.85005271434784</v>
       </c>
       <c r="H804" t="n">
         <v>291089</v>
@@ -23743,7 +23743,7 @@
         <v>2.14499998092651</v>
       </c>
       <c r="G806" t="n">
-        <v>1.92638993263245</v>
+        <v>1.92638981342316</v>
       </c>
       <c r="H806" t="n">
         <v>684242</v>
@@ -23772,7 +23772,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G807" t="n">
-        <v>1.85903346538544</v>
+        <v>1.85903334617615</v>
       </c>
       <c r="H807" t="n">
         <v>324394</v>
@@ -23801,7 +23801,7 @@
         <v>2.07500004768372</v>
       </c>
       <c r="G808" t="n">
-        <v>1.86352396011353</v>
+        <v>1.86352407932281</v>
       </c>
       <c r="H808" t="n">
         <v>387958</v>
@@ -23830,7 +23830,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G809" t="n">
-        <v>1.85005247592926</v>
+        <v>1.85005271434784</v>
       </c>
       <c r="H809" t="n">
         <v>165023</v>
@@ -23917,7 +23917,7 @@
         <v>2.04500007629395</v>
       </c>
       <c r="G812" t="n">
-        <v>1.83658158779144</v>
+        <v>1.83658146858215</v>
       </c>
       <c r="H812" t="n">
         <v>184309</v>
@@ -23975,7 +23975,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G814" t="n">
-        <v>1.8051483631134</v>
+        <v>1.80514848232269</v>
       </c>
       <c r="H814" t="n">
         <v>69071</v>
@@ -24033,7 +24033,7 @@
         <v>1.95799994468689</v>
       </c>
       <c r="G816" t="n">
-        <v>1.7584480047226</v>
+        <v>1.75844812393188</v>
       </c>
       <c r="H816" t="n">
         <v>228707</v>
@@ -24120,7 +24120,7 @@
         <v>1.8639999628067</v>
       </c>
       <c r="G819" t="n">
-        <v>1.67402815818787</v>
+        <v>1.67402827739716</v>
       </c>
       <c r="H819" t="n">
         <v>216465</v>
@@ -24149,7 +24149,7 @@
         <v>1.90600001811981</v>
       </c>
       <c r="G820" t="n">
-        <v>1.71174776554108</v>
+        <v>1.71174764633179</v>
       </c>
       <c r="H820" t="n">
         <v>125176</v>
@@ -24207,7 +24207,7 @@
         <v>1.88399994373322</v>
       </c>
       <c r="G822" t="n">
-        <v>1.69198977947235</v>
+        <v>1.69198989868164</v>
       </c>
       <c r="H822" t="n">
         <v>48768</v>
@@ -24294,7 +24294,7 @@
         <v>1.90600001811981</v>
       </c>
       <c r="G825" t="n">
-        <v>1.71174776554108</v>
+        <v>1.71174764633179</v>
       </c>
       <c r="H825" t="n">
         <v>44756</v>
@@ -24323,7 +24323,7 @@
         <v>2.07500004768372</v>
       </c>
       <c r="G826" t="n">
-        <v>1.86352396011353</v>
+        <v>1.86352407932281</v>
       </c>
       <c r="H826" t="n">
         <v>973336</v>
@@ -24352,7 +24352,7 @@
         <v>2.21499991416931</v>
       </c>
       <c r="G827" t="n">
-        <v>1.9892555475235</v>
+        <v>1.98925566673279</v>
       </c>
       <c r="H827" t="n">
         <v>1267819</v>
@@ -24439,7 +24439,7 @@
         <v>2.31500005722046</v>
       </c>
       <c r="G830" t="n">
-        <v>2.07906413078308</v>
+        <v>2.0790638923645</v>
       </c>
       <c r="H830" t="n">
         <v>590495</v>
@@ -24526,7 +24526,7 @@
         <v>2.14499998092651</v>
       </c>
       <c r="G833" t="n">
-        <v>1.92638993263245</v>
+        <v>1.92638981342316</v>
       </c>
       <c r="H833" t="n">
         <v>353418</v>
@@ -24671,7 +24671,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G838" t="n">
-        <v>2.13743996620178</v>
+        <v>2.1374397277832</v>
       </c>
       <c r="H838" t="n">
         <v>430992</v>
@@ -24758,7 +24758,7 @@
         <v>2.42499995231628</v>
       </c>
       <c r="G841" t="n">
-        <v>2.17785334587097</v>
+        <v>2.17785310745239</v>
       </c>
       <c r="H841" t="n">
         <v>275446</v>
@@ -24787,7 +24787,7 @@
         <v>2.33500003814697</v>
       </c>
       <c r="G842" t="n">
-        <v>2.09702563285828</v>
+        <v>2.09702587127686</v>
       </c>
       <c r="H842" t="n">
         <v>111988</v>
@@ -24816,7 +24816,7 @@
         <v>2.33500003814697</v>
       </c>
       <c r="G843" t="n">
-        <v>2.09702563285828</v>
+        <v>2.09702587127686</v>
       </c>
       <c r="H843" t="n">
         <v>46383</v>
@@ -24932,7 +24932,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G847" t="n">
-        <v>2.0745735168457</v>
+        <v>2.07457375526428</v>
       </c>
       <c r="H847" t="n">
         <v>92338</v>
@@ -24990,7 +24990,7 @@
         <v>2.46499991416931</v>
       </c>
       <c r="G849" t="n">
-        <v>2.21377658843994</v>
+        <v>2.21377635002136</v>
       </c>
       <c r="H849" t="n">
         <v>455520</v>
@@ -25048,7 +25048,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G851" t="n">
-        <v>2.04763078689575</v>
+        <v>2.04763126373291</v>
       </c>
       <c r="H851" t="n">
         <v>566449</v>
@@ -25164,7 +25164,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G855" t="n">
-        <v>1.95782279968262</v>
+        <v>1.95782291889191</v>
       </c>
       <c r="H855" t="n">
         <v>159758</v>
@@ -25193,7 +25193,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G856" t="n">
-        <v>1.95782279968262</v>
+        <v>1.95782291889191</v>
       </c>
       <c r="H856" t="n">
         <v>76878</v>
@@ -25251,7 +25251,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G858" t="n">
-        <v>2.06110215187073</v>
+        <v>2.06110262870789</v>
       </c>
       <c r="H858" t="n">
         <v>59723</v>
@@ -25454,7 +25454,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G865" t="n">
-        <v>2.03865027427673</v>
+        <v>2.03865003585815</v>
       </c>
       <c r="H865" t="n">
         <v>76078</v>
@@ -25512,7 +25512,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G867" t="n">
-        <v>2.05661177635193</v>
+        <v>2.05661201477051</v>
       </c>
       <c r="H867" t="n">
         <v>50681</v>
@@ -25599,7 +25599,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G870" t="n">
-        <v>2.06110215187073</v>
+        <v>2.06110262870789</v>
       </c>
       <c r="H870" t="n">
         <v>52434</v>
@@ -25628,7 +25628,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G871" t="n">
-        <v>2.05661177635193</v>
+        <v>2.05661201477051</v>
       </c>
       <c r="H871" t="n">
         <v>101754</v>
@@ -25657,7 +25657,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G872" t="n">
-        <v>2.05661177635193</v>
+        <v>2.05661201477051</v>
       </c>
       <c r="H872" t="n">
         <v>99626</v>
@@ -25686,7 +25686,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G873" t="n">
-        <v>2.02966928482056</v>
+        <v>2.02966952323914</v>
       </c>
       <c r="H873" t="n">
         <v>45140</v>
@@ -25744,7 +25744,7 @@
         <v>2.22499990463257</v>
       </c>
       <c r="G875" t="n">
-        <v>1.99823641777039</v>
+        <v>1.99823653697968</v>
       </c>
       <c r="H875" t="n">
         <v>31598</v>
@@ -25773,7 +25773,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G876" t="n">
-        <v>1.92189943790436</v>
+        <v>1.92189931869507</v>
       </c>
       <c r="H876" t="n">
         <v>75417</v>
@@ -25802,7 +25802,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G877" t="n">
-        <v>1.85903346538544</v>
+        <v>1.85903334617615</v>
       </c>
       <c r="H877" t="n">
         <v>177393</v>
@@ -25831,7 +25831,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G878" t="n">
-        <v>1.86801433563232</v>
+        <v>1.86801421642303</v>
       </c>
       <c r="H878" t="n">
         <v>169753</v>
@@ -25860,7 +25860,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G879" t="n">
-        <v>1.84107172489166</v>
+        <v>1.84107184410095</v>
       </c>
       <c r="H879" t="n">
         <v>119512</v>
@@ -25889,7 +25889,7 @@
         <v>2.01500010490417</v>
       </c>
       <c r="G880" t="n">
-        <v>1.80963885784149</v>
+        <v>1.80963897705078</v>
       </c>
       <c r="H880" t="n">
         <v>97091</v>
@@ -25947,7 +25947,7 @@
         <v>2.02500009536743</v>
       </c>
       <c r="G882" t="n">
-        <v>1.81861972808838</v>
+        <v>1.81861984729767</v>
       </c>
       <c r="H882" t="n">
         <v>71776</v>
@@ -25976,7 +25976,7 @@
         <v>1.98399996757507</v>
       </c>
       <c r="G883" t="n">
-        <v>1.78179836273193</v>
+        <v>1.78179824352264</v>
       </c>
       <c r="H883" t="n">
         <v>47832</v>
@@ -26005,7 +26005,7 @@
         <v>1.88399994373322</v>
       </c>
       <c r="G884" t="n">
-        <v>1.69198977947235</v>
+        <v>1.69198989868164</v>
       </c>
       <c r="H884" t="n">
         <v>204305</v>
@@ -26034,7 +26034,7 @@
         <v>1.96399998664856</v>
       </c>
       <c r="G885" t="n">
-        <v>1.76383650302887</v>
+        <v>1.76383674144745</v>
       </c>
       <c r="H885" t="n">
         <v>93689</v>
@@ -26121,7 +26121,7 @@
         <v>2.01500010490417</v>
       </c>
       <c r="G888" t="n">
-        <v>1.80963885784149</v>
+        <v>1.80963897705078</v>
       </c>
       <c r="H888" t="n">
         <v>23086</v>
@@ -26150,7 +26150,7 @@
         <v>2.00500011444092</v>
       </c>
       <c r="G889" t="n">
-        <v>1.80065810680389</v>
+        <v>1.80065822601318</v>
       </c>
       <c r="H889" t="n">
         <v>16944</v>
@@ -26179,7 +26179,7 @@
         <v>1.98800003528595</v>
       </c>
       <c r="G890" t="n">
-        <v>1.78539061546326</v>
+        <v>1.78539073467255</v>
       </c>
       <c r="H890" t="n">
         <v>22304</v>
@@ -26295,7 +26295,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G894" t="n">
-        <v>1.8051483631134</v>
+        <v>1.80514848232269</v>
       </c>
       <c r="H894" t="n">
         <v>41837</v>
@@ -26324,7 +26324,7 @@
         <v>2.01500010490417</v>
       </c>
       <c r="G895" t="n">
-        <v>1.80963885784149</v>
+        <v>1.80963897705078</v>
       </c>
       <c r="H895" t="n">
         <v>49791</v>
@@ -26353,7 +26353,7 @@
         <v>1.99600005149841</v>
       </c>
       <c r="G896" t="n">
-        <v>1.79257524013519</v>
+        <v>1.79257547855377</v>
       </c>
       <c r="H896" t="n">
         <v>38649</v>
@@ -26440,7 +26440,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G899" t="n">
-        <v>1.8051483631134</v>
+        <v>1.80514848232269</v>
       </c>
       <c r="H899" t="n">
         <v>40340</v>
@@ -26556,7 +26556,7 @@
         <v>1.89800000190735</v>
       </c>
       <c r="G903" t="n">
-        <v>1.70456302165985</v>
+        <v>1.70456314086914</v>
       </c>
       <c r="H903" t="n">
         <v>82014</v>
@@ -26614,7 +26614,7 @@
         <v>1.92200005054474</v>
       </c>
       <c r="G905" t="n">
-        <v>1.72611725330353</v>
+        <v>1.72611713409424</v>
       </c>
       <c r="H905" t="n">
         <v>31014</v>
@@ -26643,7 +26643,7 @@
         <v>2.1949999332428</v>
       </c>
       <c r="G906" t="n">
-        <v>1.97129380702972</v>
+        <v>1.97129392623901</v>
       </c>
       <c r="H906" t="n">
         <v>1347426</v>
@@ -26672,7 +26672,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G907" t="n">
-        <v>1.95782279968262</v>
+        <v>1.95782291889191</v>
       </c>
       <c r="H907" t="n">
         <v>660531</v>
@@ -26846,7 +26846,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G913" t="n">
-        <v>1.94884181022644</v>
+        <v>1.94884216785431</v>
       </c>
       <c r="H913" t="n">
         <v>69703</v>
@@ -26875,7 +26875,7 @@
         <v>2.125</v>
       </c>
       <c r="G914" t="n">
-        <v>1.90842807292938</v>
+        <v>1.90842819213867</v>
       </c>
       <c r="H914" t="n">
         <v>82298</v>
@@ -26904,7 +26904,7 @@
         <v>2.13499999046326</v>
       </c>
       <c r="G915" t="n">
-        <v>1.91740894317627</v>
+        <v>1.91740882396698</v>
       </c>
       <c r="H915" t="n">
         <v>92598</v>
@@ -26933,7 +26933,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G916" t="n">
-        <v>1.92189943790436</v>
+        <v>1.92189931869507</v>
       </c>
       <c r="H916" t="n">
         <v>56683</v>
@@ -26962,7 +26962,7 @@
         <v>2.14499998092651</v>
       </c>
       <c r="G917" t="n">
-        <v>1.92638993263245</v>
+        <v>1.92638981342316</v>
       </c>
       <c r="H917" t="n">
         <v>16397</v>
@@ -27020,7 +27020,7 @@
         <v>2.04500007629395</v>
       </c>
       <c r="G919" t="n">
-        <v>1.83658158779144</v>
+        <v>1.83658146858215</v>
       </c>
       <c r="H919" t="n">
         <v>36850</v>
@@ -27049,7 +27049,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G920" t="n">
-        <v>1.85005247592926</v>
+        <v>1.85005271434784</v>
       </c>
       <c r="H920" t="n">
         <v>122831</v>
@@ -27107,7 +27107,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G922" t="n">
-        <v>1.76922512054443</v>
+        <v>1.76922500133514</v>
       </c>
       <c r="H922" t="n">
         <v>82986</v>
@@ -27136,7 +27136,7 @@
         <v>2.00500011444092</v>
       </c>
       <c r="G923" t="n">
-        <v>1.80065810680389</v>
+        <v>1.80065822601318</v>
       </c>
       <c r="H923" t="n">
         <v>30841</v>
@@ -27165,7 +27165,7 @@
         <v>1.96599996089935</v>
       </c>
       <c r="G924" t="n">
-        <v>1.76563262939453</v>
+        <v>1.76563274860382</v>
       </c>
       <c r="H924" t="n">
         <v>25634</v>
@@ -27223,7 +27223,7 @@
         <v>1.98399996757507</v>
       </c>
       <c r="G926" t="n">
-        <v>1.78179836273193</v>
+        <v>1.78179824352264</v>
       </c>
       <c r="H926" t="n">
         <v>108704</v>
@@ -27252,7 +27252,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G927" t="n">
-        <v>1.76024425029755</v>
+        <v>1.76024436950684</v>
       </c>
       <c r="H927" t="n">
         <v>11740</v>
@@ -27310,7 +27310,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G929" t="n">
-        <v>1.76024425029755</v>
+        <v>1.76024436950684</v>
       </c>
       <c r="H929" t="n">
         <v>20505</v>
@@ -27368,7 +27368,7 @@
         <v>1.93400001525879</v>
       </c>
       <c r="G931" t="n">
-        <v>1.7368940114975</v>
+        <v>1.73689413070679</v>
       </c>
       <c r="H931" t="n">
         <v>16107</v>
@@ -27513,7 +27513,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G936" t="n">
-        <v>1.85903346538544</v>
+        <v>1.85903334617615</v>
       </c>
       <c r="H936" t="n">
         <v>90582</v>
@@ -27542,7 +27542,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G937" t="n">
-        <v>1.84556233882904</v>
+        <v>1.84556221961975</v>
       </c>
       <c r="H937" t="n">
         <v>30239</v>
@@ -27571,7 +27571,7 @@
         <v>2.03500008583069</v>
       </c>
       <c r="G938" t="n">
-        <v>1.82760071754456</v>
+        <v>1.82760059833527</v>
       </c>
       <c r="H938" t="n">
         <v>55955</v>
@@ -27600,7 +27600,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G939" t="n">
-        <v>1.83209097385406</v>
+        <v>1.83209085464478</v>
       </c>
       <c r="H939" t="n">
         <v>132643</v>
@@ -27716,7 +27716,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G943" t="n">
-        <v>2.16438221931458</v>
+        <v>2.164381980896</v>
       </c>
       <c r="H943" t="n">
         <v>376074</v>
@@ -27774,7 +27774,7 @@
         <v>2.31500005722046</v>
       </c>
       <c r="G945" t="n">
-        <v>2.07906413078308</v>
+        <v>2.0790638923645</v>
       </c>
       <c r="H945" t="n">
         <v>29653</v>
@@ -27803,7 +27803,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G946" t="n">
-        <v>2.03865027427673</v>
+        <v>2.03865003585815</v>
       </c>
       <c r="H946" t="n">
         <v>69467</v>
@@ -27890,7 +27890,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G949" t="n">
-        <v>1.92189943790436</v>
+        <v>1.92189931869507</v>
       </c>
       <c r="H949" t="n">
         <v>109591</v>
@@ -27919,7 +27919,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G950" t="n">
-        <v>2.03865027427673</v>
+        <v>2.03865003585815</v>
       </c>
       <c r="H950" t="n">
         <v>225593</v>
@@ -28006,7 +28006,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G953" t="n">
-        <v>2.05661177635193</v>
+        <v>2.05661201477051</v>
       </c>
       <c r="H953" t="n">
         <v>222591</v>
@@ -28209,7 +28209,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G960" t="n">
-        <v>1.95782279968262</v>
+        <v>1.95782291889191</v>
       </c>
       <c r="H960" t="n">
         <v>130224</v>
@@ -28325,7 +28325,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G964" t="n">
-        <v>2.0835542678833</v>
+        <v>2.08355450630188</v>
       </c>
       <c r="H964" t="n">
         <v>200150</v>
@@ -28354,7 +28354,7 @@
         <v>2.40499997138977</v>
       </c>
       <c r="G965" t="n">
-        <v>2.1598916053772</v>
+        <v>2.15989136695862</v>
       </c>
       <c r="H965" t="n">
         <v>192266</v>
@@ -28383,7 +28383,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G966" t="n">
-        <v>2.16438221931458</v>
+        <v>2.164381980896</v>
       </c>
       <c r="H966" t="n">
         <v>136751</v>
@@ -28441,7 +28441,7 @@
         <v>2.40499997138977</v>
       </c>
       <c r="G968" t="n">
-        <v>2.1598916053772</v>
+        <v>2.15989136695862</v>
       </c>
       <c r="H968" t="n">
         <v>88063</v>
@@ -28528,7 +28528,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G971" t="n">
-        <v>2.05661177635193</v>
+        <v>2.05661201477051</v>
       </c>
       <c r="H971" t="n">
         <v>150831</v>
@@ -28673,7 +28673,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G976" t="n">
-        <v>2.15540146827698</v>
+        <v>2.1554012298584</v>
       </c>
       <c r="H976" t="n">
         <v>257157</v>
@@ -28731,7 +28731,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G978" t="n">
-        <v>2.29909467697144</v>
+        <v>2.29909443855286</v>
       </c>
       <c r="H978" t="n">
         <v>414720</v>
@@ -28818,7 +28818,7 @@
         <v>2.75500011444092</v>
       </c>
       <c r="G981" t="n">
-        <v>2.47422099113464</v>
+        <v>2.47422122955322</v>
       </c>
       <c r="H981" t="n">
         <v>747567</v>
@@ -28905,7 +28905,7 @@
         <v>2.875</v>
       </c>
       <c r="G984" t="n">
-        <v>2.58199071884155</v>
+        <v>2.58199119567871</v>
       </c>
       <c r="H984" t="n">
         <v>376960</v>
@@ -29021,7 +29021,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G988" t="n">
-        <v>2.6852707862854</v>
+        <v>2.68527054786682</v>
       </c>
       <c r="H988" t="n">
         <v>775698</v>
@@ -29079,7 +29079,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G990" t="n">
-        <v>2.6852707862854</v>
+        <v>2.68527054786682</v>
       </c>
       <c r="H990" t="n">
         <v>513049</v>
@@ -29224,7 +29224,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G995" t="n">
-        <v>3.05348515510559</v>
+        <v>3.05348491668701</v>
       </c>
       <c r="H995" t="n">
         <v>731740</v>
@@ -29282,7 +29282,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G997" t="n">
-        <v>2.9546959400177</v>
+        <v>2.95469570159912</v>
       </c>
       <c r="H997" t="n">
         <v>433216</v>
@@ -29311,7 +29311,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G998" t="n">
-        <v>2.74364590644836</v>
+        <v>2.74364614486694</v>
       </c>
       <c r="H998" t="n">
         <v>799529</v>
@@ -29485,7 +29485,7 @@
         <v>3.02500009536743</v>
       </c>
       <c r="G1004" t="n">
-        <v>2.71670341491699</v>
+        <v>2.71670365333557</v>
       </c>
       <c r="H1004" t="n">
         <v>326494</v>
@@ -29514,7 +29514,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1005" t="n">
-        <v>2.6852707862854</v>
+        <v>2.68527054786682</v>
       </c>
       <c r="H1005" t="n">
         <v>92346</v>
@@ -29630,7 +29630,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1009" t="n">
-        <v>2.66730904579163</v>
+        <v>2.66730928421021</v>
       </c>
       <c r="H1009" t="n">
         <v>156751</v>
@@ -29717,7 +29717,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1012" t="n">
-        <v>2.78405952453613</v>
+        <v>2.78405976295471</v>
       </c>
       <c r="H1012" t="n">
         <v>296367</v>
@@ -29746,7 +29746,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G1013" t="n">
-        <v>2.78855037689209</v>
+        <v>2.78855013847351</v>
       </c>
       <c r="H1013" t="n">
         <v>56422</v>
@@ -29775,7 +29775,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1014" t="n">
-        <v>2.77507877349854</v>
+        <v>2.77507901191711</v>
       </c>
       <c r="H1014" t="n">
         <v>86689</v>
@@ -29804,7 +29804,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1015" t="n">
-        <v>2.74813652038574</v>
+        <v>2.74813628196716</v>
       </c>
       <c r="H1015" t="n">
         <v>56516</v>
@@ -29978,7 +29978,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1021" t="n">
-        <v>2.66730904579163</v>
+        <v>2.66730928421021</v>
       </c>
       <c r="H1021" t="n">
         <v>104777</v>
@@ -30094,7 +30094,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1025" t="n">
-        <v>2.9546959400177</v>
+        <v>2.95469570159912</v>
       </c>
       <c r="H1025" t="n">
         <v>333259</v>
@@ -30181,7 +30181,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1028" t="n">
-        <v>3.10736989974976</v>
+        <v>3.10737013816833</v>
       </c>
       <c r="H1028" t="n">
         <v>1116689</v>
@@ -30210,7 +30210,7 @@
         <v>3.6949999332428</v>
       </c>
       <c r="G1029" t="n">
-        <v>3.31841993331909</v>
+        <v>3.31841945648193</v>
       </c>
       <c r="H1029" t="n">
         <v>1089635</v>
@@ -30268,7 +30268,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1031" t="n">
-        <v>3.17921686172485</v>
+        <v>3.1792163848877</v>
       </c>
       <c r="H1031" t="n">
         <v>425318</v>
@@ -30384,7 +30384,7 @@
         <v>3.57500004768372</v>
       </c>
       <c r="G1035" t="n">
-        <v>3.21064949035645</v>
+        <v>3.21064972877502</v>
       </c>
       <c r="H1035" t="n">
         <v>814671</v>
@@ -30413,7 +30413,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1036" t="n">
-        <v>3.10736989974976</v>
+        <v>3.10737013816833</v>
       </c>
       <c r="H1036" t="n">
         <v>376345</v>
@@ -30442,7 +30442,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1037" t="n">
-        <v>2.99959993362427</v>
+        <v>2.99959969520569</v>
       </c>
       <c r="H1037" t="n">
         <v>297082</v>
@@ -30587,7 +30587,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1042" t="n">
-        <v>3.24208235740662</v>
+        <v>3.2420825958252</v>
       </c>
       <c r="H1042" t="n">
         <v>857496</v>
@@ -30645,7 +30645,7 @@
         <v>3.74499988555908</v>
       </c>
       <c r="G1044" t="n">
-        <v>3.36332392692566</v>
+        <v>3.3633234500885</v>
       </c>
       <c r="H1044" t="n">
         <v>319519</v>
@@ -30674,7 +30674,7 @@
         <v>3.85500001907349</v>
       </c>
       <c r="G1045" t="n">
-        <v>3.46211314201355</v>
+        <v>3.46211338043213</v>
       </c>
       <c r="H1045" t="n">
         <v>407985</v>
@@ -30761,7 +30761,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1048" t="n">
-        <v>3.30494856834412</v>
+        <v>3.30494832992554</v>
       </c>
       <c r="H1048" t="n">
         <v>343273</v>
@@ -30790,7 +30790,7 @@
         <v>3.625</v>
       </c>
       <c r="G1049" t="n">
-        <v>3.25555396080017</v>
+        <v>3.25555372238159</v>
       </c>
       <c r="H1049" t="n">
         <v>365092</v>
@@ -30819,7 +30819,7 @@
         <v>3.57500004768372</v>
       </c>
       <c r="G1050" t="n">
-        <v>3.21064949035645</v>
+        <v>3.21064972877502</v>
       </c>
       <c r="H1050" t="n">
         <v>228274</v>
@@ -30848,7 +30848,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1051" t="n">
-        <v>3.09838914871216</v>
+        <v>3.09838891029358</v>
       </c>
       <c r="H1051" t="n">
         <v>316345</v>
@@ -30906,7 +30906,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1053" t="n">
-        <v>2.87386846542358</v>
+        <v>2.873868227005</v>
       </c>
       <c r="H1053" t="n">
         <v>433328</v>
@@ -31022,7 +31022,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1057" t="n">
-        <v>2.78405952453613</v>
+        <v>2.78405976295471</v>
       </c>
       <c r="H1057" t="n">
         <v>264140</v>
@@ -31051,7 +31051,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G1058" t="n">
-        <v>2.77058863639832</v>
+        <v>2.77058839797974</v>
       </c>
       <c r="H1058" t="n">
         <v>520479</v>
@@ -31196,7 +31196,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G1063" t="n">
-        <v>2.30807518959045</v>
+        <v>2.30807542800903</v>
       </c>
       <c r="H1063" t="n">
         <v>452760</v>
@@ -31225,7 +31225,7 @@
         <v>2.45499992370605</v>
       </c>
       <c r="G1064" t="n">
-        <v>2.20479583740234</v>
+        <v>2.20479559898376</v>
       </c>
       <c r="H1064" t="n">
         <v>236307</v>
@@ -31283,7 +31283,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1066" t="n">
-        <v>1.84107172489166</v>
+        <v>1.84107184410095</v>
       </c>
       <c r="H1066" t="n">
         <v>296349</v>
@@ -31399,7 +31399,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1070" t="n">
-        <v>1.86801433563232</v>
+        <v>1.86801421642303</v>
       </c>
       <c r="H1070" t="n">
         <v>60442</v>
@@ -31515,7 +31515,7 @@
         <v>2.16499996185303</v>
       </c>
       <c r="G1074" t="n">
-        <v>1.94435131549835</v>
+        <v>1.94435143470764</v>
       </c>
       <c r="H1074" t="n">
         <v>152523</v>
@@ -31544,7 +31544,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1075" t="n">
-        <v>2.04763078689575</v>
+        <v>2.04763126373291</v>
       </c>
       <c r="H1075" t="n">
         <v>195849</v>
@@ -31573,7 +31573,7 @@
         <v>2.375</v>
       </c>
       <c r="G1076" t="n">
-        <v>2.13294911384583</v>
+        <v>2.13294887542725</v>
       </c>
       <c r="H1076" t="n">
         <v>100585</v>
@@ -31602,7 +31602,7 @@
         <v>2.21499991416931</v>
       </c>
       <c r="G1077" t="n">
-        <v>1.9892555475235</v>
+        <v>1.98925566673279</v>
       </c>
       <c r="H1077" t="n">
         <v>113895</v>
@@ -31660,7 +31660,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1079" t="n">
-        <v>2.04763078689575</v>
+        <v>2.04763126373291</v>
       </c>
       <c r="H1079" t="n">
         <v>150042</v>
@@ -31689,7 +31689,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1080" t="n">
-        <v>2.15540146827698</v>
+        <v>2.1554012298584</v>
       </c>
       <c r="H1080" t="n">
         <v>113945</v>
@@ -31718,7 +31718,7 @@
         <v>2.5550000667572</v>
       </c>
       <c r="G1081" t="n">
-        <v>2.29460406303406</v>
+        <v>2.29460430145264</v>
       </c>
       <c r="H1081" t="n">
         <v>212896</v>
@@ -31747,7 +31747,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1082" t="n">
-        <v>2.26317143440247</v>
+        <v>2.26317119598389</v>
       </c>
       <c r="H1082" t="n">
         <v>269717</v>
@@ -31776,7 +31776,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G1083" t="n">
-        <v>2.30807518959045</v>
+        <v>2.30807542800903</v>
       </c>
       <c r="H1083" t="n">
         <v>299039</v>
@@ -31805,7 +31805,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1084" t="n">
-        <v>2.45176863670349</v>
+        <v>2.45176887512207</v>
       </c>
       <c r="H1084" t="n">
         <v>180092</v>
@@ -31834,7 +31834,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1085" t="n">
-        <v>2.45176863670349</v>
+        <v>2.45176887512207</v>
       </c>
       <c r="H1085" t="n">
         <v>125425</v>
@@ -31921,7 +31921,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1088" t="n">
-        <v>2.44278788566589</v>
+        <v>2.44278812408447</v>
       </c>
       <c r="H1088" t="n">
         <v>121140</v>
@@ -31979,7 +31979,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1090" t="n">
-        <v>2.54157710075378</v>
+        <v>2.54157733917236</v>
       </c>
       <c r="H1090" t="n">
         <v>128072</v>
@@ -32008,7 +32008,7 @@
         <v>2.9449999332428</v>
       </c>
       <c r="G1091" t="n">
-        <v>2.64485692977905</v>
+        <v>2.64485669136047</v>
       </c>
       <c r="H1091" t="n">
         <v>136319</v>
@@ -32037,7 +32037,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1092" t="n">
-        <v>2.62240481376648</v>
+        <v>2.62240505218506</v>
       </c>
       <c r="H1092" t="n">
         <v>54205</v>
@@ -32066,7 +32066,7 @@
         <v>2.86500000953674</v>
       </c>
       <c r="G1093" t="n">
-        <v>2.57301020622253</v>
+        <v>2.57300996780396</v>
       </c>
       <c r="H1093" t="n">
         <v>131890</v>
@@ -32124,7 +32124,7 @@
         <v>2.86500000953674</v>
       </c>
       <c r="G1095" t="n">
-        <v>2.57301020622253</v>
+        <v>2.57300996780396</v>
       </c>
       <c r="H1095" t="n">
         <v>62094</v>
@@ -32153,7 +32153,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1096" t="n">
-        <v>2.6852707862854</v>
+        <v>2.68527054786682</v>
       </c>
       <c r="H1096" t="n">
         <v>161123</v>
@@ -32182,7 +32182,7 @@
         <v>2.97499990463257</v>
       </c>
       <c r="G1097" t="n">
-        <v>2.67179942131042</v>
+        <v>2.67179918289185</v>
       </c>
       <c r="H1097" t="n">
         <v>188131</v>
@@ -32211,7 +32211,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1098" t="n">
-        <v>2.65832829475403</v>
+        <v>2.65832805633545</v>
       </c>
       <c r="H1098" t="n">
         <v>64040</v>
@@ -32269,7 +32269,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1100" t="n">
-        <v>2.67628979682922</v>
+        <v>2.6762900352478</v>
       </c>
       <c r="H1100" t="n">
         <v>62723</v>
@@ -32414,7 +32414,7 @@
         <v>2.85500001907349</v>
       </c>
       <c r="G1105" t="n">
-        <v>2.56402945518494</v>
+        <v>2.56402921676636</v>
       </c>
       <c r="H1105" t="n">
         <v>19825</v>
@@ -32501,7 +32501,7 @@
         <v>2.86500000953674</v>
       </c>
       <c r="G1108" t="n">
-        <v>2.57301020622253</v>
+        <v>2.57300996780396</v>
       </c>
       <c r="H1108" t="n">
         <v>71160</v>
@@ -32530,7 +32530,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1109" t="n">
-        <v>2.64036631584167</v>
+        <v>2.64036655426025</v>
       </c>
       <c r="H1109" t="n">
         <v>23456</v>
@@ -32617,7 +32617,7 @@
         <v>2.78500008583069</v>
       </c>
       <c r="G1112" t="n">
-        <v>2.50116348266602</v>
+        <v>2.50116372108459</v>
       </c>
       <c r="H1112" t="n">
         <v>81161</v>
@@ -32675,7 +32675,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1114" t="n">
-        <v>2.48769211769104</v>
+        <v>2.48769235610962</v>
       </c>
       <c r="H1114" t="n">
         <v>45709</v>
@@ -32704,7 +32704,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G1115" t="n">
-        <v>2.52810621261597</v>
+        <v>2.52810597419739</v>
       </c>
       <c r="H1115" t="n">
         <v>47937</v>
@@ -32733,7 +32733,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1116" t="n">
-        <v>2.59546256065369</v>
+        <v>2.59546232223511</v>
       </c>
       <c r="H1116" t="n">
         <v>74805</v>
@@ -32762,7 +32762,7 @@
         <v>2.86500000953674</v>
       </c>
       <c r="G1117" t="n">
-        <v>2.57301020622253</v>
+        <v>2.57300996780396</v>
       </c>
       <c r="H1117" t="n">
         <v>76069</v>
@@ -32791,7 +32791,7 @@
         <v>2.9449999332428</v>
       </c>
       <c r="G1118" t="n">
-        <v>2.64485692977905</v>
+        <v>2.64485669136047</v>
       </c>
       <c r="H1118" t="n">
         <v>73129</v>
@@ -32820,7 +32820,7 @@
         <v>2.89499998092651</v>
       </c>
       <c r="G1119" t="n">
-        <v>2.59995269775391</v>
+        <v>2.59995245933533</v>
       </c>
       <c r="H1119" t="n">
         <v>36216</v>
@@ -32849,7 +32849,7 @@
         <v>2.89499998092651</v>
       </c>
       <c r="G1120" t="n">
-        <v>2.59995269775391</v>
+        <v>2.59995245933533</v>
       </c>
       <c r="H1120" t="n">
         <v>33908</v>
@@ -32878,7 +32878,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G1121" t="n">
-        <v>2.61342406272888</v>
+        <v>2.6134238243103</v>
       </c>
       <c r="H1121" t="n">
         <v>47119</v>
@@ -32907,7 +32907,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G1122" t="n">
-        <v>2.61342406272888</v>
+        <v>2.6134238243103</v>
       </c>
       <c r="H1122" t="n">
         <v>47055</v>
@@ -32936,7 +32936,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1123" t="n">
-        <v>2.60444331169128</v>
+        <v>2.60444307327271</v>
       </c>
       <c r="H1123" t="n">
         <v>97328</v>
@@ -32965,7 +32965,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1124" t="n">
-        <v>2.60444331169128</v>
+        <v>2.60444307327271</v>
       </c>
       <c r="H1124" t="n">
         <v>130456</v>
@@ -32994,7 +32994,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1125" t="n">
-        <v>2.81998324394226</v>
+        <v>2.81998300552368</v>
       </c>
       <c r="H1125" t="n">
         <v>389566</v>
@@ -33023,7 +33023,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1126" t="n">
-        <v>2.74813652038574</v>
+        <v>2.74813628196716</v>
       </c>
       <c r="H1126" t="n">
         <v>132655</v>
@@ -33081,7 +33081,7 @@
         <v>2.85500001907349</v>
       </c>
       <c r="G1128" t="n">
-        <v>2.56402945518494</v>
+        <v>2.56402921676636</v>
       </c>
       <c r="H1128" t="n">
         <v>145315</v>
@@ -33197,7 +33197,7 @@
         <v>2.85500001907349</v>
       </c>
       <c r="G1132" t="n">
-        <v>2.56402945518494</v>
+        <v>2.56402921676636</v>
       </c>
       <c r="H1132" t="n">
         <v>49511</v>
@@ -33226,7 +33226,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1133" t="n">
-        <v>2.48769211769104</v>
+        <v>2.48769235610962</v>
       </c>
       <c r="H1133" t="n">
         <v>84105</v>
@@ -33313,7 +33313,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G1136" t="n">
-        <v>2.52361559867859</v>
+        <v>2.52361536026001</v>
       </c>
       <c r="H1136" t="n">
         <v>35770</v>
@@ -33371,7 +33371,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G1138" t="n">
-        <v>2.50565385818481</v>
+        <v>2.50565361976624</v>
       </c>
       <c r="H1138" t="n">
         <v>45132</v>
@@ -33400,7 +33400,7 @@
         <v>2.72499990463257</v>
       </c>
       <c r="G1139" t="n">
-        <v>2.44727826118469</v>
+        <v>2.44727849960327</v>
       </c>
       <c r="H1139" t="n">
         <v>31730</v>
@@ -33429,7 +33429,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1140" t="n">
-        <v>2.44278788566589</v>
+        <v>2.44278812408447</v>
       </c>
       <c r="H1140" t="n">
         <v>27100</v>
@@ -33458,7 +33458,7 @@
         <v>2.6949999332428</v>
       </c>
       <c r="G1141" t="n">
-        <v>2.42033576965332</v>
+        <v>2.42033553123474</v>
       </c>
       <c r="H1141" t="n">
         <v>19022</v>
@@ -33487,7 +33487,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1142" t="n">
-        <v>2.43380689620972</v>
+        <v>2.4338071346283</v>
       </c>
       <c r="H1142" t="n">
         <v>35299</v>
@@ -33516,7 +33516,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1143" t="n">
-        <v>2.48769211769104</v>
+        <v>2.48769235610962</v>
       </c>
       <c r="H1143" t="n">
         <v>28703</v>
@@ -33545,7 +33545,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1144" t="n">
-        <v>2.46074986457825</v>
+        <v>2.46074962615967</v>
       </c>
       <c r="H1144" t="n">
         <v>31806</v>
@@ -33603,7 +33603,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1146" t="n">
-        <v>2.45176863670349</v>
+        <v>2.45176887512207</v>
       </c>
       <c r="H1146" t="n">
         <v>36667</v>
@@ -33777,7 +33777,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1152" t="n">
-        <v>2.41584539413452</v>
+        <v>2.4158456325531</v>
       </c>
       <c r="H1152" t="n">
         <v>39947</v>
@@ -33835,7 +33835,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1154" t="n">
-        <v>2.46074986457825</v>
+        <v>2.46074962615967</v>
       </c>
       <c r="H1154" t="n">
         <v>17622</v>
@@ -33893,7 +33893,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1156" t="n">
-        <v>2.48769211769104</v>
+        <v>2.48769235610962</v>
       </c>
       <c r="H1156" t="n">
         <v>55468</v>
@@ -33922,7 +33922,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1157" t="n">
-        <v>2.45176863670349</v>
+        <v>2.45176887512207</v>
       </c>
       <c r="H1157" t="n">
         <v>21286</v>
@@ -33951,7 +33951,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1158" t="n">
-        <v>2.46074986457825</v>
+        <v>2.46074962615967</v>
       </c>
       <c r="H1158" t="n">
         <v>25390</v>
@@ -33980,7 +33980,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1159" t="n">
-        <v>2.41584539413452</v>
+        <v>2.4158456325531</v>
       </c>
       <c r="H1159" t="n">
         <v>15842</v>
@@ -34009,7 +34009,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1160" t="n">
-        <v>2.41584539413452</v>
+        <v>2.4158456325531</v>
       </c>
       <c r="H1160" t="n">
         <v>20217</v>
@@ -34067,7 +34067,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G1162" t="n">
-        <v>2.39788389205933</v>
+        <v>2.39788365364075</v>
       </c>
       <c r="H1162" t="n">
         <v>35142</v>
@@ -34154,7 +34154,7 @@
         <v>2.64499998092651</v>
       </c>
       <c r="G1165" t="n">
-        <v>2.37543153762817</v>
+        <v>2.37543177604675</v>
       </c>
       <c r="H1165" t="n">
         <v>40838</v>
@@ -34270,7 +34270,7 @@
         <v>2.54500007629395</v>
       </c>
       <c r="G1169" t="n">
-        <v>2.28562355041504</v>
+        <v>2.28562331199646</v>
       </c>
       <c r="H1169" t="n">
         <v>18461</v>
@@ -34357,7 +34357,7 @@
         <v>2.82500004768372</v>
       </c>
       <c r="G1172" t="n">
-        <v>2.53708696365356</v>
+        <v>2.53708672523499</v>
       </c>
       <c r="H1172" t="n">
         <v>50652</v>
@@ -34415,7 +34415,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1174" t="n">
-        <v>2.44278788566589</v>
+        <v>2.44278812408447</v>
       </c>
       <c r="H1174" t="n">
         <v>33942</v>
@@ -34502,7 +34502,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1177" t="n">
-        <v>2.48769211769104</v>
+        <v>2.48769235610962</v>
       </c>
       <c r="H1177" t="n">
         <v>10565</v>
@@ -34560,7 +34560,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1179" t="n">
-        <v>2.41584539413452</v>
+        <v>2.4158456325531</v>
       </c>
       <c r="H1179" t="n">
         <v>24291</v>
@@ -34589,7 +34589,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G1180" t="n">
-        <v>2.39788389205933</v>
+        <v>2.39788365364075</v>
       </c>
       <c r="H1180" t="n">
         <v>19836</v>
@@ -34647,7 +34647,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1182" t="n">
-        <v>2.37094116210938</v>
+        <v>2.37094140052795</v>
       </c>
       <c r="H1182" t="n">
         <v>43338</v>
@@ -34676,7 +34676,7 @@
         <v>2.60500001907349</v>
       </c>
       <c r="G1183" t="n">
-        <v>2.33950853347778</v>
+        <v>2.3395082950592</v>
       </c>
       <c r="H1183" t="n">
         <v>21306</v>
@@ -34705,7 +34705,7 @@
         <v>2.625</v>
       </c>
       <c r="G1184" t="n">
-        <v>2.3574697971344</v>
+        <v>2.35747003555298</v>
       </c>
       <c r="H1184" t="n">
         <v>43410</v>
@@ -34763,7 +34763,7 @@
         <v>2.65499997138977</v>
       </c>
       <c r="G1186" t="n">
-        <v>2.38441228866577</v>
+        <v>2.38441252708435</v>
       </c>
       <c r="H1186" t="n">
         <v>20906</v>
@@ -34792,7 +34792,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G1187" t="n">
-        <v>2.39788389205933</v>
+        <v>2.39788365364075</v>
       </c>
       <c r="H1187" t="n">
         <v>18532</v>
@@ -34850,7 +34850,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1189" t="n">
-        <v>2.37094116210938</v>
+        <v>2.37094140052795</v>
       </c>
       <c r="H1189" t="n">
         <v>5400</v>
@@ -34937,7 +34937,7 @@
         <v>2.625</v>
       </c>
       <c r="G1192" t="n">
-        <v>2.3574697971344</v>
+        <v>2.35747003555298</v>
       </c>
       <c r="H1192" t="n">
         <v>21386</v>
@@ -34966,7 +34966,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1193" t="n">
-        <v>2.43380689620972</v>
+        <v>2.4338071346283</v>
       </c>
       <c r="H1193" t="n">
         <v>34787</v>
@@ -34995,7 +34995,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1194" t="n">
-        <v>2.46074986457825</v>
+        <v>2.46074962615967</v>
       </c>
       <c r="H1194" t="n">
         <v>27385</v>
@@ -35053,7 +35053,7 @@
         <v>2.78500008583069</v>
       </c>
       <c r="G1196" t="n">
-        <v>2.50116348266602</v>
+        <v>2.50116372108459</v>
       </c>
       <c r="H1196" t="n">
         <v>31231</v>
@@ -35140,7 +35140,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G1199" t="n">
-        <v>2.29909467697144</v>
+        <v>2.29909443855286</v>
       </c>
       <c r="H1199" t="n">
         <v>83217</v>
@@ -35227,7 +35227,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G1202" t="n">
-        <v>2.29909467697144</v>
+        <v>2.29909443855286</v>
       </c>
       <c r="H1202" t="n">
         <v>10167</v>
@@ -35343,7 +35343,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1206" t="n">
-        <v>2.23622894287109</v>
+        <v>2.23622870445251</v>
       </c>
       <c r="H1206" t="n">
         <v>34554</v>
@@ -35401,7 +35401,7 @@
         <v>2.6949999332428</v>
       </c>
       <c r="G1208" t="n">
-        <v>2.42033576965332</v>
+        <v>2.42033553123474</v>
       </c>
       <c r="H1208" t="n">
         <v>103202</v>
@@ -35430,7 +35430,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1209" t="n">
-        <v>2.31705617904663</v>
+        <v>2.31705641746521</v>
       </c>
       <c r="H1209" t="n">
         <v>154849</v>
@@ -35459,7 +35459,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G1210" t="n">
-        <v>2.29909467697144</v>
+        <v>2.29909443855286</v>
       </c>
       <c r="H1210" t="n">
         <v>81222</v>
@@ -35488,7 +35488,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G1211" t="n">
-        <v>2.32603693008423</v>
+        <v>2.32603716850281</v>
       </c>
       <c r="H1211" t="n">
         <v>41706</v>
@@ -35546,7 +35546,7 @@
         <v>2.6949999332428</v>
       </c>
       <c r="G1213" t="n">
-        <v>2.42033576965332</v>
+        <v>2.42033553123474</v>
       </c>
       <c r="H1213" t="n">
         <v>60898</v>
@@ -35575,7 +35575,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1214" t="n">
-        <v>2.37094116210938</v>
+        <v>2.37094140052795</v>
       </c>
       <c r="H1214" t="n">
         <v>30496</v>
@@ -35633,7 +35633,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G1216" t="n">
-        <v>2.32603693008423</v>
+        <v>2.32603716850281</v>
       </c>
       <c r="H1216" t="n">
         <v>32139</v>
@@ -35778,7 +35778,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1221" t="n">
-        <v>2.60444331169128</v>
+        <v>2.60444307327271</v>
       </c>
       <c r="H1221" t="n">
         <v>166120</v>
@@ -35836,7 +35836,7 @@
         <v>2.86500000953674</v>
       </c>
       <c r="G1223" t="n">
-        <v>2.57301020622253</v>
+        <v>2.57300996780396</v>
       </c>
       <c r="H1223" t="n">
         <v>73060</v>
@@ -35894,7 +35894,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1225" t="n">
-        <v>2.43380689620972</v>
+        <v>2.4338071346283</v>
       </c>
       <c r="H1225" t="n">
         <v>47298</v>
@@ -35923,7 +35923,7 @@
         <v>2.75500011444092</v>
       </c>
       <c r="G1226" t="n">
-        <v>2.47422099113464</v>
+        <v>2.47422122955322</v>
       </c>
       <c r="H1226" t="n">
         <v>56976</v>
@@ -36097,7 +36097,7 @@
         <v>2.5550000667572</v>
       </c>
       <c r="G1232" t="n">
-        <v>2.29460406303406</v>
+        <v>2.29460430145264</v>
       </c>
       <c r="H1232" t="n">
         <v>28247</v>
@@ -36126,7 +36126,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G1233" t="n">
-        <v>2.343998670578</v>
+        <v>2.34399843215942</v>
       </c>
       <c r="H1233" t="n">
         <v>106983</v>
@@ -36155,7 +36155,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1234" t="n">
-        <v>2.31705617904663</v>
+        <v>2.31705641746521</v>
       </c>
       <c r="H1234" t="n">
         <v>23887</v>
@@ -36213,7 +36213,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1236" t="n">
-        <v>2.43380689620972</v>
+        <v>2.4338071346283</v>
       </c>
       <c r="H1236" t="n">
         <v>55259</v>
@@ -36242,7 +36242,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1237" t="n">
-        <v>2.41584539413452</v>
+        <v>2.4158456325531</v>
       </c>
       <c r="H1237" t="n">
         <v>31433</v>
@@ -36329,7 +36329,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1240" t="n">
-        <v>2.45176863670349</v>
+        <v>2.45176887512207</v>
       </c>
       <c r="H1240" t="n">
         <v>59133</v>
@@ -36358,7 +36358,7 @@
         <v>2.64499998092651</v>
       </c>
       <c r="G1241" t="n">
-        <v>2.37543153762817</v>
+        <v>2.37543177604675</v>
       </c>
       <c r="H1241" t="n">
         <v>101736</v>
@@ -36445,7 +36445,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1244" t="n">
-        <v>2.44278788566589</v>
+        <v>2.44278812408447</v>
       </c>
       <c r="H1244" t="n">
         <v>27951</v>
@@ -36474,7 +36474,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1245" t="n">
-        <v>2.44278788566589</v>
+        <v>2.44278812408447</v>
       </c>
       <c r="H1245" t="n">
         <v>153595</v>
@@ -36619,7 +36619,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1250" t="n">
-        <v>2.58648157119751</v>
+        <v>2.58648133277893</v>
       </c>
       <c r="H1250" t="n">
         <v>67685</v>
@@ -36648,7 +36648,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1251" t="n">
-        <v>2.65832829475403</v>
+        <v>2.65832805633545</v>
       </c>
       <c r="H1251" t="n">
         <v>125447</v>
@@ -36677,7 +36677,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1252" t="n">
-        <v>2.6852707862854</v>
+        <v>2.68527054786682</v>
       </c>
       <c r="H1252" t="n">
         <v>149703</v>
@@ -36706,7 +36706,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1253" t="n">
-        <v>2.67628979682922</v>
+        <v>2.6762900352478</v>
       </c>
       <c r="H1253" t="n">
         <v>34882</v>
@@ -36764,7 +36764,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1255" t="n">
-        <v>2.74813652038574</v>
+        <v>2.74813628196716</v>
       </c>
       <c r="H1255" t="n">
         <v>102967</v>
@@ -36793,7 +36793,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G1256" t="n">
-        <v>2.76160764694214</v>
+        <v>2.76160788536072</v>
       </c>
       <c r="H1256" t="n">
         <v>52490</v>
@@ -36880,7 +36880,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1259" t="n">
-        <v>2.64036631584167</v>
+        <v>2.64036655426025</v>
       </c>
       <c r="H1259" t="n">
         <v>47497</v>
@@ -36909,7 +36909,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1260" t="n">
-        <v>2.77507877349854</v>
+        <v>2.77507901191711</v>
       </c>
       <c r="H1260" t="n">
         <v>108963</v>
@@ -36938,7 +36938,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1261" t="n">
-        <v>2.78405952453613</v>
+        <v>2.78405976295471</v>
       </c>
       <c r="H1261" t="n">
         <v>56426</v>
@@ -36967,7 +36967,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1262" t="n">
-        <v>2.77507877349854</v>
+        <v>2.77507901191711</v>
       </c>
       <c r="H1262" t="n">
         <v>59601</v>
@@ -36996,7 +36996,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1263" t="n">
-        <v>2.84692549705505</v>
+        <v>2.84692597389221</v>
       </c>
       <c r="H1263" t="n">
         <v>142485</v>
@@ -37054,7 +37054,7 @@
         <v>3.02500009536743</v>
       </c>
       <c r="G1265" t="n">
-        <v>2.71670341491699</v>
+        <v>2.71670365333557</v>
       </c>
       <c r="H1265" t="n">
         <v>137009</v>
@@ -37083,7 +37083,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G1266" t="n">
-        <v>2.77058863639832</v>
+        <v>2.77058839797974</v>
       </c>
       <c r="H1266" t="n">
         <v>25826</v>
@@ -37141,7 +37141,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G1268" t="n">
-        <v>2.78855037689209</v>
+        <v>2.78855013847351</v>
       </c>
       <c r="H1268" t="n">
         <v>40994</v>
@@ -37170,7 +37170,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1269" t="n">
-        <v>2.78405952453613</v>
+        <v>2.78405976295471</v>
       </c>
       <c r="H1269" t="n">
         <v>34275</v>
@@ -37228,7 +37228,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1271" t="n">
-        <v>2.77507877349854</v>
+        <v>2.77507901191711</v>
       </c>
       <c r="H1271" t="n">
         <v>80673</v>
@@ -37257,7 +37257,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1272" t="n">
-        <v>2.78405952453613</v>
+        <v>2.78405976295471</v>
       </c>
       <c r="H1272" t="n">
         <v>92143</v>
@@ -37315,7 +37315,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1274" t="n">
-        <v>2.77507877349854</v>
+        <v>2.77507901191711</v>
       </c>
       <c r="H1274" t="n">
         <v>66369</v>
@@ -37344,7 +37344,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G1275" t="n">
-        <v>2.77058863639832</v>
+        <v>2.77058839797974</v>
       </c>
       <c r="H1275" t="n">
         <v>28281</v>
@@ -37576,7 +37576,7 @@
         <v>2.9449999332428</v>
       </c>
       <c r="G1283" t="n">
-        <v>2.64485692977905</v>
+        <v>2.64485669136047</v>
       </c>
       <c r="H1283" t="n">
         <v>43761</v>
@@ -37663,7 +37663,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G1286" t="n">
-        <v>2.54606795310974</v>
+        <v>2.54606747627258</v>
       </c>
       <c r="H1286" t="n">
         <v>52596</v>
@@ -37692,7 +37692,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1287" t="n">
-        <v>2.65832829475403</v>
+        <v>2.65832805633545</v>
       </c>
       <c r="H1287" t="n">
         <v>57291</v>
@@ -37721,7 +37721,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1288" t="n">
-        <v>2.60444331169128</v>
+        <v>2.60444307327271</v>
       </c>
       <c r="H1288" t="n">
         <v>73099</v>
@@ -37779,7 +37779,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1290" t="n">
-        <v>2.60444331169128</v>
+        <v>2.60444307327271</v>
       </c>
       <c r="H1290" t="n">
         <v>32277</v>
@@ -37837,7 +37837,7 @@
         <v>3.02500009536743</v>
       </c>
       <c r="G1292" t="n">
-        <v>2.71670341491699</v>
+        <v>2.71670365333557</v>
       </c>
       <c r="H1292" t="n">
         <v>68100</v>
@@ -37895,7 +37895,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G1294" t="n">
-        <v>2.76160764694214</v>
+        <v>2.76160788536072</v>
       </c>
       <c r="H1294" t="n">
         <v>149188</v>
@@ -37953,7 +37953,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1296" t="n">
-        <v>2.81998324394226</v>
+        <v>2.81998300552368</v>
       </c>
       <c r="H1296" t="n">
         <v>78007</v>
@@ -37982,7 +37982,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1297" t="n">
-        <v>2.81998324394226</v>
+        <v>2.81998300552368</v>
       </c>
       <c r="H1297" t="n">
         <v>52494</v>
@@ -38040,7 +38040,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1299" t="n">
-        <v>3.08940815925598</v>
+        <v>3.08940839767456</v>
       </c>
       <c r="H1299" t="n">
         <v>368241</v>
@@ -38069,7 +38069,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G1300" t="n">
-        <v>3.12982201576233</v>
+        <v>3.12982177734375</v>
       </c>
       <c r="H1300" t="n">
         <v>478492</v>
@@ -38127,7 +38127,7 @@
         <v>3.49499988555908</v>
       </c>
       <c r="G1302" t="n">
-        <v>3.13880276679993</v>
+        <v>3.13880252838135</v>
       </c>
       <c r="H1302" t="n">
         <v>86110</v>
@@ -38214,7 +38214,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G1305" t="n">
-        <v>3.12982201576233</v>
+        <v>3.12982177734375</v>
       </c>
       <c r="H1305" t="n">
         <v>68636</v>
@@ -38243,7 +38243,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1306" t="n">
-        <v>3.1612548828125</v>
+        <v>3.16125512123108</v>
       </c>
       <c r="H1306" t="n">
         <v>84232</v>
@@ -38330,7 +38330,7 @@
         <v>3.33500003814697</v>
       </c>
       <c r="G1309" t="n">
-        <v>2.99510979652405</v>
+        <v>2.99510955810547</v>
       </c>
       <c r="H1309" t="n">
         <v>53098</v>
@@ -38359,7 +38359,7 @@
         <v>3.22499990463257</v>
       </c>
       <c r="G1310" t="n">
-        <v>2.89632034301758</v>
+        <v>2.896320104599</v>
       </c>
       <c r="H1310" t="n">
         <v>141496</v>
@@ -38446,7 +38446,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1313" t="n">
-        <v>3.02654218673706</v>
+        <v>3.02654242515564</v>
       </c>
       <c r="H1313" t="n">
         <v>30124</v>
@@ -38475,7 +38475,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1314" t="n">
-        <v>3.02654218673706</v>
+        <v>3.02654242515564</v>
       </c>
       <c r="H1314" t="n">
         <v>20963</v>
@@ -38533,7 +38533,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1316" t="n">
-        <v>3.05348515510559</v>
+        <v>3.05348491668701</v>
       </c>
       <c r="H1316" t="n">
         <v>56200</v>
@@ -38620,7 +38620,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1319" t="n">
-        <v>3.09838914871216</v>
+        <v>3.09838891029358</v>
       </c>
       <c r="H1319" t="n">
         <v>106279</v>
@@ -38649,7 +38649,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1320" t="n">
-        <v>3.02654218673706</v>
+        <v>3.02654242515564</v>
       </c>
       <c r="H1320" t="n">
         <v>54445</v>
@@ -38794,7 +38794,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1325" t="n">
-        <v>3.02654218673706</v>
+        <v>3.02654242515564</v>
       </c>
       <c r="H1325" t="n">
         <v>45299</v>
@@ -38823,7 +38823,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1326" t="n">
-        <v>2.99959993362427</v>
+        <v>2.99959969520569</v>
       </c>
       <c r="H1326" t="n">
         <v>26917</v>
@@ -39055,7 +39055,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1334" t="n">
-        <v>3.02654218673706</v>
+        <v>3.02654242515564</v>
       </c>
       <c r="H1334" t="n">
         <v>59668</v>
@@ -39084,7 +39084,7 @@
         <v>3.31500005722046</v>
       </c>
       <c r="G1335" t="n">
-        <v>2.97714781761169</v>
+        <v>2.97714805603027</v>
       </c>
       <c r="H1335" t="n">
         <v>132492</v>
@@ -39229,7 +39229,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1340" t="n">
-        <v>2.90081071853638</v>
+        <v>2.90081095695496</v>
       </c>
       <c r="H1340" t="n">
         <v>22176</v>
@@ -39258,7 +39258,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1341" t="n">
-        <v>2.87386846542358</v>
+        <v>2.873868227005</v>
       </c>
       <c r="H1341" t="n">
         <v>97613</v>
@@ -39287,7 +39287,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1342" t="n">
-        <v>2.87386846542358</v>
+        <v>2.873868227005</v>
       </c>
       <c r="H1342" t="n">
         <v>52668</v>
@@ -39316,7 +39316,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1343" t="n">
-        <v>2.87386846542358</v>
+        <v>2.873868227005</v>
       </c>
       <c r="H1343" t="n">
         <v>33996</v>
@@ -39374,7 +39374,7 @@
         <v>3.14499998092651</v>
       </c>
       <c r="G1345" t="n">
-        <v>2.82447338104248</v>
+        <v>2.82447361946106</v>
       </c>
       <c r="H1345" t="n">
         <v>74454</v>
@@ -39432,7 +39432,7 @@
         <v>3.25</v>
       </c>
       <c r="G1347" t="n">
-        <v>2.91877269744873</v>
+        <v>2.91877222061157</v>
       </c>
       <c r="H1347" t="n">
         <v>190767</v>
@@ -39461,7 +39461,7 @@
         <v>3.34500002861023</v>
       </c>
       <c r="G1348" t="n">
-        <v>3.00409054756165</v>
+        <v>3.00409030914307</v>
       </c>
       <c r="H1348" t="n">
         <v>247027</v>
@@ -39490,7 +39490,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1349" t="n">
-        <v>3.05348515510559</v>
+        <v>3.05348491668701</v>
       </c>
       <c r="H1349" t="n">
         <v>145927</v>
@@ -39548,7 +39548,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1351" t="n">
-        <v>3.08940815925598</v>
+        <v>3.08940839767456</v>
       </c>
       <c r="H1351" t="n">
         <v>78308</v>
@@ -39577,7 +39577,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1352" t="n">
-        <v>3.08940815925598</v>
+        <v>3.08940839767456</v>
       </c>
       <c r="H1352" t="n">
         <v>143262</v>
@@ -39606,7 +39606,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1353" t="n">
-        <v>3.08940815925598</v>
+        <v>3.08940839767456</v>
       </c>
       <c r="H1353" t="n">
         <v>20389</v>
@@ -39635,7 +39635,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1354" t="n">
-        <v>3.05348515510559</v>
+        <v>3.05348491668701</v>
       </c>
       <c r="H1354" t="n">
         <v>75529</v>
@@ -39751,7 +39751,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1358" t="n">
-        <v>3.30494856834412</v>
+        <v>3.30494832992554</v>
       </c>
       <c r="H1358" t="n">
         <v>134090</v>
@@ -39780,7 +39780,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1359" t="n">
-        <v>3.35883355140686</v>
+        <v>3.35883331298828</v>
       </c>
       <c r="H1359" t="n">
         <v>166356</v>
@@ -39809,7 +39809,7 @@
         <v>3.60500001907349</v>
       </c>
       <c r="G1360" t="n">
-        <v>3.23759198188782</v>
+        <v>3.2375922203064</v>
       </c>
       <c r="H1360" t="n">
         <v>186639</v>
@@ -39925,7 +39925,7 @@
         <v>3.53500008583069</v>
       </c>
       <c r="G1364" t="n">
-        <v>3.17472624778748</v>
+        <v>3.17472648620605</v>
       </c>
       <c r="H1364" t="n">
         <v>60666</v>
@@ -40012,7 +40012,7 @@
         <v>3.46499991416931</v>
       </c>
       <c r="G1367" t="n">
-        <v>3.11186003684998</v>
+        <v>3.11186051368713</v>
       </c>
       <c r="H1367" t="n">
         <v>44147</v>
@@ -40041,7 +40041,7 @@
         <v>3.46499991416931</v>
       </c>
       <c r="G1368" t="n">
-        <v>3.11186003684998</v>
+        <v>3.11186051368713</v>
       </c>
       <c r="H1368" t="n">
         <v>26420</v>
@@ -40070,7 +40070,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1369" t="n">
-        <v>3.11635112762451</v>
+        <v>3.11635088920593</v>
       </c>
       <c r="H1369" t="n">
         <v>23574</v>
@@ -40157,7 +40157,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1372" t="n">
-        <v>3.05348515510559</v>
+        <v>3.05348491668701</v>
       </c>
       <c r="H1372" t="n">
         <v>69751</v>
@@ -40215,7 +40215,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1374" t="n">
-        <v>3.08940815925598</v>
+        <v>3.08940839767456</v>
       </c>
       <c r="H1374" t="n">
         <v>39393</v>
@@ -40302,7 +40302,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1377" t="n">
-        <v>3.08940815925598</v>
+        <v>3.08940839767456</v>
       </c>
       <c r="H1377" t="n">
         <v>32677</v>
@@ -40331,7 +40331,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1378" t="n">
-        <v>3.08940815925598</v>
+        <v>3.08940839767456</v>
       </c>
       <c r="H1378" t="n">
         <v>86915</v>
@@ -40389,7 +40389,7 @@
         <v>3.40499997138977</v>
       </c>
       <c r="G1380" t="n">
-        <v>3.05797553062439</v>
+        <v>3.05797529220581</v>
       </c>
       <c r="H1380" t="n">
         <v>35440</v>
@@ -40534,7 +40534,7 @@
         <v>3.54500007629395</v>
       </c>
       <c r="G1385" t="n">
-        <v>3.18370723724365</v>
+        <v>3.18370699882507</v>
       </c>
       <c r="H1385" t="n">
         <v>69860</v>
@@ -40679,7 +40679,7 @@
         <v>3.33500003814697</v>
       </c>
       <c r="G1390" t="n">
-        <v>2.99510979652405</v>
+        <v>2.99510955810547</v>
       </c>
       <c r="H1390" t="n">
         <v>26650</v>
@@ -40795,7 +40795,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1394" t="n">
-        <v>2.92775321006775</v>
+        <v>2.92775344848633</v>
       </c>
       <c r="H1394" t="n">
         <v>42784</v>
@@ -40911,7 +40911,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1398" t="n">
-        <v>3.23310136795044</v>
+        <v>3.23310160636902</v>
       </c>
       <c r="H1398" t="n">
         <v>59128</v>
@@ -41230,7 +41230,7 @@
         <v>3.23499989509583</v>
       </c>
       <c r="G1409" t="n">
-        <v>2.90530109405518</v>
+        <v>2.9053008556366</v>
       </c>
       <c r="H1409" t="n">
         <v>88494</v>
@@ -41259,7 +41259,7 @@
         <v>3.23499989509583</v>
       </c>
       <c r="G1410" t="n">
-        <v>2.90530109405518</v>
+        <v>2.9053008556366</v>
       </c>
       <c r="H1410" t="n">
         <v>32229</v>
@@ -41288,7 +41288,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1411" t="n">
-        <v>3.02654218673706</v>
+        <v>3.02654242515564</v>
       </c>
       <c r="H1411" t="n">
         <v>49358</v>
@@ -41491,7 +41491,7 @@
         <v>3.34500002861023</v>
       </c>
       <c r="G1418" t="n">
-        <v>3.00409054756165</v>
+        <v>3.00409030914307</v>
       </c>
       <c r="H1418" t="n">
         <v>187546</v>
@@ -41578,7 +41578,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1421" t="n">
-        <v>2.94571495056152</v>
+        <v>2.94571471214294</v>
       </c>
       <c r="H1421" t="n">
         <v>12821</v>
@@ -41694,7 +41694,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1425" t="n">
-        <v>2.94571495056152</v>
+        <v>2.94571471214294</v>
       </c>
       <c r="H1425" t="n">
         <v>32445</v>
@@ -41752,7 +41752,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1427" t="n">
-        <v>2.9546959400177</v>
+        <v>2.95469570159912</v>
       </c>
       <c r="H1427" t="n">
         <v>37331</v>
@@ -41781,7 +41781,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1428" t="n">
-        <v>2.9546959400177</v>
+        <v>2.95469570159912</v>
       </c>
       <c r="H1428" t="n">
         <v>25793</v>
@@ -41897,7 +41897,7 @@
         <v>3.33500003814697</v>
       </c>
       <c r="G1432" t="n">
-        <v>2.99510979652405</v>
+        <v>2.99510955810547</v>
       </c>
       <c r="H1432" t="n">
         <v>100309</v>
@@ -41926,7 +41926,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1433" t="n">
-        <v>2.9546959400177</v>
+        <v>2.95469570159912</v>
       </c>
       <c r="H1433" t="n">
         <v>74718</v>
@@ -41955,7 +41955,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G1434" t="n">
-        <v>2.9591863155365</v>
+        <v>2.95918607711792</v>
       </c>
       <c r="H1434" t="n">
         <v>31202</v>
@@ -42013,7 +42013,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1436" t="n">
-        <v>2.93673419952393</v>
+        <v>2.93673396110535</v>
       </c>
       <c r="H1436" t="n">
         <v>21907</v>
@@ -42042,7 +42042,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1437" t="n">
-        <v>2.93673419952393</v>
+        <v>2.93673396110535</v>
       </c>
       <c r="H1437" t="n">
         <v>22159</v>
@@ -42071,7 +42071,7 @@
         <v>3.25</v>
       </c>
       <c r="G1438" t="n">
-        <v>2.91877269744873</v>
+        <v>2.91877222061157</v>
       </c>
       <c r="H1438" t="n">
         <v>18524</v>
@@ -42100,7 +42100,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1439" t="n">
-        <v>2.93673419952393</v>
+        <v>2.93673396110535</v>
       </c>
       <c r="H1439" t="n">
         <v>17042</v>
@@ -42129,7 +42129,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1440" t="n">
-        <v>2.92775321006775</v>
+        <v>2.92775344848633</v>
       </c>
       <c r="H1440" t="n">
         <v>40694</v>
@@ -42216,7 +42216,7 @@
         <v>3.31500005722046</v>
       </c>
       <c r="G1443" t="n">
-        <v>2.97714781761169</v>
+        <v>2.97714805603027</v>
       </c>
       <c r="H1443" t="n">
         <v>79496</v>
@@ -42245,7 +42245,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1444" t="n">
-        <v>2.94571495056152</v>
+        <v>2.94571471214294</v>
       </c>
       <c r="H1444" t="n">
         <v>26595</v>
@@ -42274,7 +42274,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1445" t="n">
-        <v>2.93673419952393</v>
+        <v>2.93673396110535</v>
       </c>
       <c r="H1445" t="n">
         <v>16752</v>
@@ -42303,7 +42303,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1446" t="n">
-        <v>2.92775321006775</v>
+        <v>2.92775344848633</v>
       </c>
       <c r="H1446" t="n">
         <v>48629</v>
@@ -42332,7 +42332,7 @@
         <v>3.25500011444092</v>
       </c>
       <c r="G1447" t="n">
-        <v>2.92326307296753</v>
+        <v>2.92326283454895</v>
       </c>
       <c r="H1447" t="n">
         <v>26505</v>
@@ -42361,7 +42361,7 @@
         <v>3.25</v>
       </c>
       <c r="G1448" t="n">
-        <v>2.91877269744873</v>
+        <v>2.91877222061157</v>
       </c>
       <c r="H1448" t="n">
         <v>29830</v>
@@ -42390,7 +42390,7 @@
         <v>3.22499990463257</v>
       </c>
       <c r="G1449" t="n">
-        <v>2.89632034301758</v>
+        <v>2.896320104599</v>
       </c>
       <c r="H1449" t="n">
         <v>52738</v>
@@ -42419,7 +42419,7 @@
         <v>3.22499990463257</v>
       </c>
       <c r="G1450" t="n">
-        <v>2.89632034301758</v>
+        <v>2.896320104599</v>
       </c>
       <c r="H1450" t="n">
         <v>30176</v>
@@ -42651,7 +42651,7 @@
         <v>3.25</v>
       </c>
       <c r="G1458" t="n">
-        <v>2.91877269744873</v>
+        <v>2.91877222061157</v>
       </c>
       <c r="H1458" t="n">
         <v>79827</v>
@@ -42680,7 +42680,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1459" t="n">
-        <v>3.08940815925598</v>
+        <v>3.08940839767456</v>
       </c>
       <c r="H1459" t="n">
         <v>365755</v>
@@ -42709,7 +42709,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1460" t="n">
-        <v>3.05348515510559</v>
+        <v>3.05348491668701</v>
       </c>
       <c r="H1460" t="n">
         <v>198569</v>
@@ -42738,7 +42738,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1461" t="n">
-        <v>3.09838914871216</v>
+        <v>3.09838891029358</v>
       </c>
       <c r="H1461" t="n">
         <v>72230</v>
@@ -42796,7 +42796,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1463" t="n">
-        <v>3.05348515510559</v>
+        <v>3.05348491668701</v>
       </c>
       <c r="H1463" t="n">
         <v>39306</v>
@@ -42854,7 +42854,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1465" t="n">
-        <v>3.02654218673706</v>
+        <v>3.02654242515564</v>
       </c>
       <c r="H1465" t="n">
         <v>48343</v>
@@ -42912,7 +42912,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1467" t="n">
-        <v>3.02654218673706</v>
+        <v>3.02654242515564</v>
       </c>
       <c r="H1467" t="n">
         <v>37024</v>
@@ -42941,7 +42941,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1468" t="n">
-        <v>2.99959993362427</v>
+        <v>2.99959969520569</v>
       </c>
       <c r="H1468" t="n">
         <v>40370</v>
@@ -42970,7 +42970,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1469" t="n">
-        <v>2.92775321006775</v>
+        <v>2.92775344848633</v>
       </c>
       <c r="H1469" t="n">
         <v>40905</v>
@@ -43028,7 +43028,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1471" t="n">
-        <v>2.94571495056152</v>
+        <v>2.94571471214294</v>
       </c>
       <c r="H1471" t="n">
         <v>10322</v>
@@ -43086,7 +43086,7 @@
         <v>3.49499988555908</v>
       </c>
       <c r="G1473" t="n">
-        <v>3.13880276679993</v>
+        <v>3.13880252838135</v>
       </c>
       <c r="H1473" t="n">
         <v>142449</v>
@@ -43115,7 +43115,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1474" t="n">
-        <v>3.08940815925598</v>
+        <v>3.08940839767456</v>
       </c>
       <c r="H1474" t="n">
         <v>124598</v>
@@ -43144,7 +43144,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1475" t="n">
-        <v>3.09838914871216</v>
+        <v>3.09838891029358</v>
       </c>
       <c r="H1475" t="n">
         <v>27407</v>
@@ -43173,7 +43173,7 @@
         <v>3.45499992370605</v>
       </c>
       <c r="G1476" t="n">
-        <v>3.10287928581238</v>
+        <v>3.10287976264954</v>
       </c>
       <c r="H1476" t="n">
         <v>37566</v>
@@ -43202,7 +43202,7 @@
         <v>3.49499988555908</v>
       </c>
       <c r="G1477" t="n">
-        <v>3.13880276679993</v>
+        <v>3.13880252838135</v>
       </c>
       <c r="H1477" t="n">
         <v>55323</v>
@@ -43347,7 +43347,7 @@
         <v>3.625</v>
       </c>
       <c r="G1482" t="n">
-        <v>3.25555396080017</v>
+        <v>3.25555372238159</v>
       </c>
       <c r="H1482" t="n">
         <v>170116</v>
@@ -43405,7 +43405,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1484" t="n">
-        <v>3.23310136795044</v>
+        <v>3.23310160636902</v>
       </c>
       <c r="H1484" t="n">
         <v>33548</v>
@@ -43434,7 +43434,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1485" t="n">
-        <v>3.15227389335632</v>
+        <v>3.15227437019348</v>
       </c>
       <c r="H1485" t="n">
         <v>62833</v>
@@ -43550,7 +43550,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1489" t="n">
-        <v>3.23310136795044</v>
+        <v>3.23310160636902</v>
       </c>
       <c r="H1489" t="n">
         <v>64124</v>
@@ -43579,7 +43579,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1490" t="n">
-        <v>3.23310136795044</v>
+        <v>3.23310160636902</v>
       </c>
       <c r="H1490" t="n">
         <v>118491</v>
@@ -43608,7 +43608,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1491" t="n">
-        <v>3.23310136795044</v>
+        <v>3.23310160636902</v>
       </c>
       <c r="H1491" t="n">
         <v>47687</v>
@@ -43666,7 +43666,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1493" t="n">
-        <v>3.24208235740662</v>
+        <v>3.2420825958252</v>
       </c>
       <c r="H1493" t="n">
         <v>22719</v>
@@ -43724,7 +43724,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1495" t="n">
-        <v>3.24208235740662</v>
+        <v>3.2420825958252</v>
       </c>
       <c r="H1495" t="n">
         <v>73201</v>
@@ -43782,7 +43782,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1497" t="n">
-        <v>3.10736989974976</v>
+        <v>3.10737013816833</v>
       </c>
       <c r="H1497" t="n">
         <v>47786</v>
@@ -43811,7 +43811,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1498" t="n">
-        <v>3.17921686172485</v>
+        <v>3.1792163848877</v>
       </c>
       <c r="H1498" t="n">
         <v>135978</v>
@@ -43840,7 +43840,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G1499" t="n">
-        <v>3.1477837562561</v>
+        <v>3.14778399467468</v>
       </c>
       <c r="H1499" t="n">
         <v>54289</v>
@@ -43869,7 +43869,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1500" t="n">
-        <v>3.09838914871216</v>
+        <v>3.09838891029358</v>
       </c>
       <c r="H1500" t="n">
         <v>105061</v>
@@ -43927,7 +43927,7 @@
         <v>3.54500007629395</v>
       </c>
       <c r="G1502" t="n">
-        <v>3.18370723724365</v>
+        <v>3.18370699882507</v>
       </c>
       <c r="H1502" t="n">
         <v>40339</v>
@@ -43985,7 +43985,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1504" t="n">
-        <v>3.11635112762451</v>
+        <v>3.11635088920593</v>
       </c>
       <c r="H1504" t="n">
         <v>79385</v>
@@ -44072,7 +44072,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1507" t="n">
-        <v>3.08940815925598</v>
+        <v>3.08940839767456</v>
       </c>
       <c r="H1507" t="n">
         <v>30064</v>
@@ -44101,7 +44101,7 @@
         <v>3.46499991416931</v>
       </c>
       <c r="G1508" t="n">
-        <v>3.11186003684998</v>
+        <v>3.11186051368713</v>
       </c>
       <c r="H1508" t="n">
         <v>30944</v>
@@ -44159,7 +44159,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1510" t="n">
-        <v>3.10736989974976</v>
+        <v>3.10737013816833</v>
       </c>
       <c r="H1510" t="n">
         <v>6161</v>
@@ -44188,7 +44188,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1511" t="n">
-        <v>3.10736989974976</v>
+        <v>3.10737013816833</v>
       </c>
       <c r="H1511" t="n">
         <v>10489</v>
@@ -44246,7 +44246,7 @@
         <v>3.53500008583069</v>
       </c>
       <c r="G1513" t="n">
-        <v>3.17472624778748</v>
+        <v>3.17472648620605</v>
       </c>
       <c r="H1513" t="n">
         <v>145561</v>
@@ -44275,7 +44275,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G1514" t="n">
-        <v>3.1477837562561</v>
+        <v>3.14778399467468</v>
       </c>
       <c r="H1514" t="n">
         <v>33586</v>
@@ -44333,7 +44333,7 @@
         <v>3.54500007629395</v>
       </c>
       <c r="G1516" t="n">
-        <v>3.18370723724365</v>
+        <v>3.18370699882507</v>
       </c>
       <c r="H1516" t="n">
         <v>37589</v>
@@ -44362,7 +44362,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1517" t="n">
-        <v>3.27800631523132</v>
+        <v>3.27800583839417</v>
       </c>
       <c r="H1517" t="n">
         <v>254428</v>
@@ -44391,7 +44391,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1518" t="n">
-        <v>3.27800631523132</v>
+        <v>3.27800583839417</v>
       </c>
       <c r="H1518" t="n">
         <v>105676</v>
@@ -44420,7 +44420,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1519" t="n">
-        <v>3.30494856834412</v>
+        <v>3.30494832992554</v>
       </c>
       <c r="H1519" t="n">
         <v>139095</v>
@@ -44478,7 +44478,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1521" t="n">
-        <v>3.27800631523132</v>
+        <v>3.27800583839417</v>
       </c>
       <c r="H1521" t="n">
         <v>35490</v>
@@ -44507,7 +44507,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1522" t="n">
-        <v>3.27800631523132</v>
+        <v>3.27800583839417</v>
       </c>
       <c r="H1522" t="n">
         <v>26645</v>
@@ -44594,7 +44594,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1525" t="n">
-        <v>3.30494856834412</v>
+        <v>3.30494832992554</v>
       </c>
       <c r="H1525" t="n">
         <v>61541</v>
@@ -44681,7 +44681,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1528" t="n">
-        <v>3.27800631523132</v>
+        <v>3.27800583839417</v>
       </c>
       <c r="H1528" t="n">
         <v>27468</v>
@@ -44739,7 +44739,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1530" t="n">
-        <v>3.23310136795044</v>
+        <v>3.23310160636902</v>
       </c>
       <c r="H1530" t="n">
         <v>21904</v>
@@ -44768,7 +44768,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1531" t="n">
-        <v>3.17921686172485</v>
+        <v>3.1792163848877</v>
       </c>
       <c r="H1531" t="n">
         <v>34503</v>
@@ -44797,7 +44797,7 @@
         <v>3.53500008583069</v>
       </c>
       <c r="G1532" t="n">
-        <v>3.17472624778748</v>
+        <v>3.17472648620605</v>
       </c>
       <c r="H1532" t="n">
         <v>24725</v>
@@ -44826,7 +44826,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G1533" t="n">
-        <v>3.1477837562561</v>
+        <v>3.14778399467468</v>
       </c>
       <c r="H1533" t="n">
         <v>25499</v>
@@ -44855,7 +44855,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G1534" t="n">
-        <v>3.1477837562561</v>
+        <v>3.14778399467468</v>
       </c>
       <c r="H1534" t="n">
         <v>15315</v>
@@ -44884,7 +44884,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1535" t="n">
-        <v>3.1612548828125</v>
+        <v>3.16125512123108</v>
       </c>
       <c r="H1535" t="n">
         <v>18692</v>
@@ -44942,7 +44942,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1537" t="n">
-        <v>3.09838914871216</v>
+        <v>3.09838891029358</v>
       </c>
       <c r="H1537" t="n">
         <v>31991</v>
@@ -44971,7 +44971,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1538" t="n">
-        <v>3.10736989974976</v>
+        <v>3.10737013816833</v>
       </c>
       <c r="H1538" t="n">
         <v>24847</v>
@@ -45058,7 +45058,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1541" t="n">
-        <v>3.08940815925598</v>
+        <v>3.08940839767456</v>
       </c>
       <c r="H1541" t="n">
         <v>98810</v>
@@ -45232,7 +45232,7 @@
         <v>3.40499997138977</v>
       </c>
       <c r="G1547" t="n">
-        <v>3.05797553062439</v>
+        <v>3.05797529220581</v>
       </c>
       <c r="H1547" t="n">
         <v>11326</v>
@@ -45261,7 +45261,7 @@
         <v>3.46499991416931</v>
       </c>
       <c r="G1548" t="n">
-        <v>3.11186003684998</v>
+        <v>3.11186051368713</v>
       </c>
       <c r="H1548" t="n">
         <v>19882</v>
@@ -45319,7 +45319,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1550" t="n">
-        <v>3.11635112762451</v>
+        <v>3.11635088920593</v>
       </c>
       <c r="H1550" t="n">
         <v>27307</v>
@@ -45348,7 +45348,7 @@
         <v>3.40499997138977</v>
       </c>
       <c r="G1551" t="n">
-        <v>3.05797553062439</v>
+        <v>3.05797529220581</v>
       </c>
       <c r="H1551" t="n">
         <v>25326</v>
@@ -45406,7 +45406,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G1553" t="n">
-        <v>2.9591863155365</v>
+        <v>2.95918607711792</v>
       </c>
       <c r="H1553" t="n">
         <v>40157</v>
@@ -45522,7 +45522,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1557" t="n">
-        <v>2.93673419952393</v>
+        <v>2.93673396110535</v>
       </c>
       <c r="H1557" t="n">
         <v>62187</v>
@@ -45551,7 +45551,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1558" t="n">
-        <v>3.05348515510559</v>
+        <v>3.05348491668701</v>
       </c>
       <c r="H1558" t="n">
         <v>32557</v>
@@ -45609,7 +45609,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1560" t="n">
-        <v>2.99959993362427</v>
+        <v>2.99959969520569</v>
       </c>
       <c r="H1560" t="n">
         <v>10434</v>
@@ -45638,7 +45638,7 @@
         <v>3.34500002861023</v>
       </c>
       <c r="G1561" t="n">
-        <v>3.00409054756165</v>
+        <v>3.00409030914307</v>
       </c>
       <c r="H1561" t="n">
         <v>13868</v>
@@ -45667,7 +45667,7 @@
         <v>3.25500011444092</v>
       </c>
       <c r="G1562" t="n">
-        <v>2.92326307296753</v>
+        <v>2.92326283454895</v>
       </c>
       <c r="H1562" t="n">
         <v>56513</v>
@@ -45696,7 +45696,7 @@
         <v>3.25</v>
       </c>
       <c r="G1563" t="n">
-        <v>2.91877269744873</v>
+        <v>2.91877222061157</v>
       </c>
       <c r="H1563" t="n">
         <v>50830</v>
@@ -45725,7 +45725,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1564" t="n">
-        <v>2.92775321006775</v>
+        <v>2.92775344848633</v>
       </c>
       <c r="H1564" t="n">
         <v>30025</v>
@@ -45754,7 +45754,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1565" t="n">
-        <v>2.74813652038574</v>
+        <v>2.74813628196716</v>
       </c>
       <c r="H1565" t="n">
         <v>89981</v>
@@ -45899,7 +45899,7 @@
         <v>2.95499992370605</v>
       </c>
       <c r="G1570" t="n">
-        <v>2.65383768081665</v>
+        <v>2.65383744239807</v>
       </c>
       <c r="H1570" t="n">
         <v>22678</v>
@@ -45928,7 +45928,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1571" t="n">
-        <v>2.54157710075378</v>
+        <v>2.54157733917236</v>
       </c>
       <c r="H1571" t="n">
         <v>80837</v>
@@ -46073,7 +46073,7 @@
         <v>2.9449999332428</v>
       </c>
       <c r="G1576" t="n">
-        <v>2.64485692977905</v>
+        <v>2.64485669136047</v>
       </c>
       <c r="H1576" t="n">
         <v>49985</v>
@@ -46102,7 +46102,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1577" t="n">
-        <v>2.67628979682922</v>
+        <v>2.6762900352478</v>
       </c>
       <c r="H1577" t="n">
         <v>16145</v>
@@ -46218,7 +46218,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G1581" t="n">
-        <v>2.78855037689209</v>
+        <v>2.78855013847351</v>
       </c>
       <c r="H1581" t="n">
         <v>22786</v>
@@ -46247,7 +46247,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1582" t="n">
-        <v>2.78405952453613</v>
+        <v>2.78405976295471</v>
       </c>
       <c r="H1582" t="n">
         <v>22833</v>
@@ -46363,7 +46363,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G1586" t="n">
-        <v>2.77058863639832</v>
+        <v>2.77058839797974</v>
       </c>
       <c r="H1586" t="n">
         <v>15848</v>
@@ -46421,7 +46421,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G1588" t="n">
-        <v>2.8783586025238</v>
+        <v>2.87835836410522</v>
       </c>
       <c r="H1588" t="n">
         <v>64619</v>
@@ -46450,7 +46450,7 @@
         <v>3.14499998092651</v>
       </c>
       <c r="G1589" t="n">
-        <v>2.82447338104248</v>
+        <v>2.82447361946106</v>
       </c>
       <c r="H1589" t="n">
         <v>13234</v>
@@ -46537,7 +46537,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1592" t="n">
-        <v>2.81998324394226</v>
+        <v>2.81998300552368</v>
       </c>
       <c r="H1592" t="n">
         <v>7430</v>
@@ -46595,7 +46595,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G1594" t="n">
-        <v>2.76160764694214</v>
+        <v>2.76160788536072</v>
       </c>
       <c r="H1594" t="n">
         <v>27786</v>
@@ -46624,7 +46624,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1595" t="n">
-        <v>2.80202126502991</v>
+        <v>2.80202150344849</v>
       </c>
       <c r="H1595" t="n">
         <v>5697</v>
@@ -46653,7 +46653,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1596" t="n">
-        <v>2.87386846542358</v>
+        <v>2.873868227005</v>
       </c>
       <c r="H1596" t="n">
         <v>37503</v>
@@ -46711,7 +46711,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1598" t="n">
-        <v>2.77507877349854</v>
+        <v>2.77507901191711</v>
       </c>
       <c r="H1598" t="n">
         <v>9189</v>
@@ -46740,7 +46740,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1599" t="n">
-        <v>2.78405952453613</v>
+        <v>2.78405976295471</v>
       </c>
       <c r="H1599" t="n">
         <v>6972</v>
@@ -46856,7 +46856,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1603" t="n">
-        <v>2.99959993362427</v>
+        <v>2.99959969520569</v>
       </c>
       <c r="H1603" t="n">
         <v>61025</v>
@@ -46885,7 +46885,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1604" t="n">
-        <v>2.99959993362427</v>
+        <v>2.99959969520569</v>
       </c>
       <c r="H1604" t="n">
         <v>85751</v>
@@ -47001,7 +47001,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1608" t="n">
-        <v>3.05348515510559</v>
+        <v>3.05348491668701</v>
       </c>
       <c r="H1608" t="n">
         <v>124969</v>
@@ -47088,7 +47088,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1611" t="n">
-        <v>2.9546959400177</v>
+        <v>2.95469570159912</v>
       </c>
       <c r="H1611" t="n">
         <v>16140</v>
@@ -47117,7 +47117,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1612" t="n">
-        <v>2.9546959400177</v>
+        <v>2.95469570159912</v>
       </c>
       <c r="H1612" t="n">
         <v>21435</v>
@@ -47146,7 +47146,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1613" t="n">
-        <v>2.81998324394226</v>
+        <v>2.81998300552368</v>
       </c>
       <c r="H1613" t="n">
         <v>43746</v>
@@ -47175,7 +47175,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1614" t="n">
-        <v>2.74813652038574</v>
+        <v>2.74813628196716</v>
       </c>
       <c r="H1614" t="n">
         <v>54704</v>
@@ -47204,7 +47204,7 @@
         <v>2.95499992370605</v>
       </c>
       <c r="G1615" t="n">
-        <v>2.65383768081665</v>
+        <v>2.65383744239807</v>
       </c>
       <c r="H1615" t="n">
         <v>23742</v>
@@ -47262,7 +47262,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1617" t="n">
-        <v>2.77507877349854</v>
+        <v>2.77507901191711</v>
       </c>
       <c r="H1617" t="n">
         <v>23946</v>
@@ -47291,7 +47291,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1618" t="n">
-        <v>2.84692549705505</v>
+        <v>2.84692597389221</v>
       </c>
       <c r="H1618" t="n">
         <v>37103</v>
@@ -47378,7 +47378,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1621" t="n">
-        <v>2.84692549705505</v>
+        <v>2.84692597389221</v>
       </c>
       <c r="H1621" t="n">
         <v>21461</v>
@@ -47436,7 +47436,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1623" t="n">
-        <v>2.92775321006775</v>
+        <v>2.92775344848633</v>
       </c>
       <c r="H1623" t="n">
         <v>16046</v>
@@ -47465,7 +47465,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1624" t="n">
-        <v>2.87386846542358</v>
+        <v>2.873868227005</v>
       </c>
       <c r="H1624" t="n">
         <v>15992</v>
@@ -47552,7 +47552,7 @@
         <v>3.06500005722046</v>
       </c>
       <c r="G1627" t="n">
-        <v>2.75262689590454</v>
+        <v>2.75262713432312</v>
       </c>
       <c r="H1627" t="n">
         <v>13115</v>
@@ -47581,7 +47581,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1628" t="n">
-        <v>2.77507877349854</v>
+        <v>2.77507901191711</v>
       </c>
       <c r="H1628" t="n">
         <v>37767</v>
@@ -47668,7 +47668,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1631" t="n">
-        <v>2.74813652038574</v>
+        <v>2.74813628196716</v>
       </c>
       <c r="H1631" t="n">
         <v>33470</v>
@@ -47726,7 +47726,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G1633" t="n">
-        <v>2.74364590644836</v>
+        <v>2.74364614486694</v>
       </c>
       <c r="H1633" t="n">
         <v>2304</v>
@@ -47755,7 +47755,7 @@
         <v>3.02500009536743</v>
       </c>
       <c r="G1634" t="n">
-        <v>2.71670341491699</v>
+        <v>2.71670365333557</v>
       </c>
       <c r="H1634" t="n">
         <v>25006</v>
@@ -47842,7 +47842,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1637" t="n">
-        <v>2.87386846542358</v>
+        <v>2.873868227005</v>
       </c>
       <c r="H1637" t="n">
         <v>19834</v>
@@ -47900,7 +47900,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1639" t="n">
-        <v>2.6852707862854</v>
+        <v>2.68527054786682</v>
       </c>
       <c r="H1639" t="n">
         <v>47785</v>
@@ -47929,7 +47929,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1640" t="n">
-        <v>2.64036631584167</v>
+        <v>2.64036655426025</v>
       </c>
       <c r="H1640" t="n">
         <v>53238</v>
@@ -47987,7 +47987,7 @@
         <v>2.98499989509583</v>
       </c>
       <c r="G1642" t="n">
-        <v>2.68077993392944</v>
+        <v>2.68078017234802</v>
       </c>
       <c r="H1642" t="n">
         <v>11386</v>
@@ -48016,7 +48016,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1643" t="n">
-        <v>2.59546256065369</v>
+        <v>2.59546232223511</v>
       </c>
       <c r="H1643" t="n">
         <v>12450</v>
@@ -48045,7 +48045,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1644" t="n">
-        <v>2.67628979682922</v>
+        <v>2.6762900352478</v>
       </c>
       <c r="H1644" t="n">
         <v>17398</v>
@@ -48074,7 +48074,7 @@
         <v>2.89499998092651</v>
       </c>
       <c r="G1645" t="n">
-        <v>2.59995269775391</v>
+        <v>2.59995245933533</v>
       </c>
       <c r="H1645" t="n">
         <v>23745</v>
@@ -48103,7 +48103,7 @@
         <v>2.98499989509583</v>
       </c>
       <c r="G1646" t="n">
-        <v>2.68077993392944</v>
+        <v>2.68078017234802</v>
       </c>
       <c r="H1646" t="n">
         <v>19530</v>
@@ -48219,7 +48219,7 @@
         <v>2.78500008583069</v>
       </c>
       <c r="G1650" t="n">
-        <v>2.50116348266602</v>
+        <v>2.50116372108459</v>
       </c>
       <c r="H1650" t="n">
         <v>40324</v>
@@ -48248,7 +48248,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G1651" t="n">
-        <v>2.52810621261597</v>
+        <v>2.52810597419739</v>
       </c>
       <c r="H1651" t="n">
         <v>47327</v>
@@ -48277,7 +48277,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G1652" t="n">
-        <v>2.52361559867859</v>
+        <v>2.52361536026001</v>
       </c>
       <c r="H1652" t="n">
         <v>28358</v>
@@ -48335,7 +48335,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1654" t="n">
-        <v>2.45176863670349</v>
+        <v>2.45176887512207</v>
       </c>
       <c r="H1654" t="n">
         <v>17302</v>
@@ -48364,7 +48364,7 @@
         <v>2.78500008583069</v>
       </c>
       <c r="G1655" t="n">
-        <v>2.50116348266602</v>
+        <v>2.50116372108459</v>
       </c>
       <c r="H1655" t="n">
         <v>9326</v>
@@ -48422,7 +48422,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1657" t="n">
-        <v>2.43380689620972</v>
+        <v>2.4338071346283</v>
       </c>
       <c r="H1657" t="n">
         <v>4394</v>
@@ -48451,7 +48451,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G1658" t="n">
-        <v>2.52810621261597</v>
+        <v>2.52810597419739</v>
       </c>
       <c r="H1658" t="n">
         <v>9524</v>
@@ -48683,7 +48683,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1666" t="n">
-        <v>2.59546256065369</v>
+        <v>2.59546232223511</v>
       </c>
       <c r="H1666" t="n">
         <v>4476</v>
@@ -48712,7 +48712,7 @@
         <v>2.85500001907349</v>
       </c>
       <c r="G1667" t="n">
-        <v>2.56402945518494</v>
+        <v>2.56402921676636</v>
       </c>
       <c r="H1667" t="n">
         <v>1483</v>
@@ -48741,7 +48741,7 @@
         <v>2.82500004768372</v>
       </c>
       <c r="G1668" t="n">
-        <v>2.53708696365356</v>
+        <v>2.53708672523499</v>
       </c>
       <c r="H1668" t="n">
         <v>3254</v>
@@ -48857,7 +48857,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G1672" t="n">
-        <v>2.52361559867859</v>
+        <v>2.52361536026001</v>
       </c>
       <c r="H1672" t="n">
         <v>3846</v>
@@ -48944,7 +48944,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G1675" t="n">
-        <v>2.54606795310974</v>
+        <v>2.54606747627258</v>
       </c>
       <c r="H1675" t="n">
         <v>2024</v>
@@ -48973,7 +48973,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1676" t="n">
-        <v>2.60444331169128</v>
+        <v>2.60444307327271</v>
       </c>
       <c r="H1676" t="n">
         <v>45016</v>
@@ -49002,7 +49002,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1677" t="n">
-        <v>2.60444331169128</v>
+        <v>2.60444307327271</v>
       </c>
       <c r="H1677" t="n">
         <v>5371</v>
@@ -49031,7 +49031,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G1678" t="n">
-        <v>2.61342406272888</v>
+        <v>2.6134238243103</v>
       </c>
       <c r="H1678" t="n">
         <v>18804</v>
@@ -49060,7 +49060,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1679" t="n">
-        <v>2.60444331169128</v>
+        <v>2.60444307327271</v>
       </c>
       <c r="H1679" t="n">
         <v>12257</v>
@@ -49176,7 +49176,7 @@
         <v>2.875</v>
       </c>
       <c r="G1683" t="n">
-        <v>2.58199071884155</v>
+        <v>2.58199119567871</v>
       </c>
       <c r="H1683" t="n">
         <v>9857</v>
@@ -49234,7 +49234,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1685" t="n">
-        <v>2.60444331169128</v>
+        <v>2.60444307327271</v>
       </c>
       <c r="H1685" t="n">
         <v>56100</v>
@@ -49321,7 +49321,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1688" t="n">
-        <v>2.78405952453613</v>
+        <v>2.78405976295471</v>
       </c>
       <c r="H1688" t="n">
         <v>112904</v>
@@ -49437,7 +49437,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1692" t="n">
-        <v>2.66730904579163</v>
+        <v>2.66730928421021</v>
       </c>
       <c r="H1692" t="n">
         <v>5911</v>
@@ -49466,7 +49466,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G1693" t="n">
-        <v>2.74364590644836</v>
+        <v>2.74364614486694</v>
       </c>
       <c r="H1693" t="n">
         <v>28500</v>
@@ -49524,7 +49524,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G1695" t="n">
-        <v>2.74364590644836</v>
+        <v>2.74364614486694</v>
       </c>
       <c r="H1695" t="n">
         <v>10635</v>
@@ -49553,7 +49553,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1696" t="n">
-        <v>2.6852707862854</v>
+        <v>2.68527054786682</v>
       </c>
       <c r="H1696" t="n">
         <v>32745</v>
@@ -49582,7 +49582,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1697" t="n">
-        <v>2.60444331169128</v>
+        <v>2.60444307327271</v>
       </c>
       <c r="H1697" t="n">
         <v>11075</v>
@@ -49669,7 +49669,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1700" t="n">
-        <v>2.59546256065369</v>
+        <v>2.59546232223511</v>
       </c>
       <c r="H1700" t="n">
         <v>16911</v>
@@ -49843,7 +49843,7 @@
         <v>2.73499989509583</v>
       </c>
       <c r="G1706" t="n">
-        <v>2.45625901222229</v>
+        <v>2.45625925064087</v>
       </c>
       <c r="H1706" t="n">
         <v>16788</v>
@@ -49988,7 +49988,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1711" t="n">
-        <v>2.37094116210938</v>
+        <v>2.37094140052795</v>
       </c>
       <c r="H1711" t="n">
         <v>17808</v>
@@ -50046,7 +50046,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1713" t="n">
-        <v>2.18234372138977</v>
+        <v>2.18234395980835</v>
       </c>
       <c r="H1713" t="n">
         <v>27891</v>
@@ -50075,7 +50075,7 @@
         <v>2.43499994277954</v>
       </c>
       <c r="G1714" t="n">
-        <v>2.18683409690857</v>
+        <v>2.18683385848999</v>
       </c>
       <c r="H1714" t="n">
         <v>14743</v>
@@ -50104,7 +50104,7 @@
         <v>2.42499995231628</v>
       </c>
       <c r="G1715" t="n">
-        <v>2.17785334587097</v>
+        <v>2.17785310745239</v>
       </c>
       <c r="H1715" t="n">
         <v>5758</v>
@@ -50133,7 +50133,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1716" t="n">
-        <v>2.15540146827698</v>
+        <v>2.1554012298584</v>
       </c>
       <c r="H1716" t="n">
         <v>11011</v>
@@ -50191,7 +50191,7 @@
         <v>2.40499997138977</v>
       </c>
       <c r="G1718" t="n">
-        <v>2.1598916053772</v>
+        <v>2.15989136695862</v>
       </c>
       <c r="H1718" t="n">
         <v>9107</v>
@@ -50220,7 +50220,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1719" t="n">
-        <v>2.15528607368469</v>
+        <v>2.15528583526611</v>
       </c>
       <c r="H1719" t="n">
         <v>22889</v>
@@ -50336,7 +50336,7 @@
         <v>2.28500008583069</v>
       </c>
       <c r="G1723" t="n">
-        <v>2.10462808609009</v>
+        <v>2.10462784767151</v>
       </c>
       <c r="H1723" t="n">
         <v>36798</v>
@@ -50365,7 +50365,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1724" t="n">
-        <v>2.10923290252686</v>
+        <v>2.10923314094543</v>
       </c>
       <c r="H1724" t="n">
         <v>5267</v>
@@ -50394,7 +50394,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G1725" t="n">
-        <v>2.07699584960938</v>
+        <v>2.07699608802795</v>
       </c>
       <c r="H1725" t="n">
         <v>2911</v>
@@ -50423,7 +50423,7 @@
         <v>2.28500008583069</v>
       </c>
       <c r="G1726" t="n">
-        <v>2.10462808609009</v>
+        <v>2.10462784767151</v>
       </c>
       <c r="H1726" t="n">
         <v>24153</v>
@@ -50452,7 +50452,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1727" t="n">
-        <v>2.09081196784973</v>
+        <v>2.09081172943115</v>
       </c>
       <c r="H1727" t="n">
         <v>2694</v>
@@ -50510,7 +50510,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1729" t="n">
-        <v>2.09081196784973</v>
+        <v>2.09081172943115</v>
       </c>
       <c r="H1729" t="n">
         <v>3751</v>
@@ -50655,7 +50655,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1734" t="n">
-        <v>2.37634110450745</v>
+        <v>2.37634134292603</v>
       </c>
       <c r="H1734" t="n">
         <v>31856</v>
@@ -50684,7 +50684,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G1735" t="n">
-        <v>2.33949875831604</v>
+        <v>2.33949851989746</v>
       </c>
       <c r="H1735" t="n">
         <v>20747</v>
@@ -50742,7 +50742,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G1737" t="n">
-        <v>2.42239451408386</v>
+        <v>2.42239427566528</v>
       </c>
       <c r="H1737" t="n">
         <v>17895</v>
@@ -50800,7 +50800,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1739" t="n">
-        <v>2.47765803337097</v>
+        <v>2.47765827178955</v>
       </c>
       <c r="H1739" t="n">
         <v>10139</v>
@@ -50887,7 +50887,7 @@
         <v>2.56500005722046</v>
       </c>
       <c r="G1742" t="n">
-        <v>2.36252546310425</v>
+        <v>2.36252522468567</v>
       </c>
       <c r="H1742" t="n">
         <v>15189</v>
@@ -50945,7 +50945,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1744" t="n">
-        <v>2.43160486221313</v>
+        <v>2.43160510063171</v>
       </c>
       <c r="H1744" t="n">
         <v>26540</v>
@@ -51003,7 +51003,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G1746" t="n">
-        <v>2.45923709869385</v>
+        <v>2.45923686027527</v>
       </c>
       <c r="H1746" t="n">
         <v>11854</v>
@@ -51032,7 +51032,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1747" t="n">
-        <v>2.47765803337097</v>
+        <v>2.47765827178955</v>
       </c>
       <c r="H1747" t="n">
         <v>8688</v>
@@ -51090,7 +51090,7 @@
         <v>2.76500010490417</v>
       </c>
       <c r="G1749" t="n">
-        <v>2.54673767089844</v>
+        <v>2.54673790931702</v>
       </c>
       <c r="H1749" t="n">
         <v>5238</v>
@@ -51119,7 +51119,7 @@
         <v>2.76500010490417</v>
       </c>
       <c r="G1750" t="n">
-        <v>2.54673767089844</v>
+        <v>2.54673790931702</v>
       </c>
       <c r="H1750" t="n">
         <v>7388</v>
@@ -51264,7 +51264,7 @@
         <v>2.66499996185303</v>
       </c>
       <c r="G1755" t="n">
-        <v>2.45463132858276</v>
+        <v>2.45463156700134</v>
       </c>
       <c r="H1755" t="n">
         <v>8132</v>
@@ -51293,7 +51293,7 @@
         <v>2.66499996185303</v>
       </c>
       <c r="G1756" t="n">
-        <v>2.45463132858276</v>
+        <v>2.45463156700134</v>
       </c>
       <c r="H1756" t="n">
         <v>19648</v>
@@ -51322,7 +51322,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1757" t="n">
-        <v>2.48686861991882</v>
+        <v>2.4868688583374</v>
       </c>
       <c r="H1757" t="n">
         <v>7960</v>
@@ -51351,7 +51351,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1758" t="n">
-        <v>2.48686861991882</v>
+        <v>2.4868688583374</v>
       </c>
       <c r="H1758" t="n">
         <v>9897</v>
@@ -51380,7 +51380,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1759" t="n">
-        <v>2.48686861991882</v>
+        <v>2.4868688583374</v>
       </c>
       <c r="H1759" t="n">
         <v>6583</v>
@@ -51525,7 +51525,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1764" t="n">
-        <v>2.55134320259094</v>
+        <v>2.55134296417236</v>
       </c>
       <c r="H1764" t="n">
         <v>8841</v>
@@ -51554,7 +51554,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1765" t="n">
-        <v>2.52371120452881</v>
+        <v>2.52371096611023</v>
       </c>
       <c r="H1765" t="n">
         <v>15304</v>
@@ -51583,7 +51583,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1766" t="n">
-        <v>2.52371120452881</v>
+        <v>2.52371096611023</v>
       </c>
       <c r="H1766" t="n">
         <v>1876</v>
@@ -51670,7 +51670,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1769" t="n">
-        <v>2.52371120452881</v>
+        <v>2.52371096611023</v>
       </c>
       <c r="H1769" t="n">
         <v>28615</v>
@@ -51699,7 +51699,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1770" t="n">
-        <v>2.47765803337097</v>
+        <v>2.47765827178955</v>
       </c>
       <c r="H1770" t="n">
         <v>99660</v>
@@ -51757,7 +51757,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1772" t="n">
-        <v>2.50529003143311</v>
+        <v>2.50529026985168</v>
       </c>
       <c r="H1772" t="n">
         <v>5533</v>
@@ -51786,7 +51786,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1773" t="n">
-        <v>2.50529003143311</v>
+        <v>2.50529026985168</v>
       </c>
       <c r="H1773" t="n">
         <v>20515</v>
@@ -51815,7 +51815,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1774" t="n">
-        <v>2.52371120452881</v>
+        <v>2.52371096611023</v>
       </c>
       <c r="H1774" t="n">
         <v>9413</v>
@@ -51844,7 +51844,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1775" t="n">
-        <v>2.52371120452881</v>
+        <v>2.52371096611023</v>
       </c>
       <c r="H1775" t="n">
         <v>54098</v>
@@ -51873,7 +51873,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1776" t="n">
-        <v>2.59739589691162</v>
+        <v>2.5973961353302</v>
       </c>
       <c r="H1776" t="n">
         <v>20295</v>
@@ -52018,7 +52018,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1781" t="n">
-        <v>2.73555541038513</v>
+        <v>2.73555564880371</v>
       </c>
       <c r="H1781" t="n">
         <v>24158</v>
@@ -52047,7 +52047,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1782" t="n">
-        <v>2.73555541038513</v>
+        <v>2.73555564880371</v>
       </c>
       <c r="H1782" t="n">
         <v>30414</v>
@@ -52076,7 +52076,7 @@
         <v>3</v>
       </c>
       <c r="G1783" t="n">
-        <v>2.76318764686584</v>
+        <v>2.76318740844727</v>
       </c>
       <c r="H1783" t="n">
         <v>9403</v>
@@ -52105,7 +52105,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1784" t="n">
-        <v>2.78160881996155</v>
+        <v>2.78160858154297</v>
       </c>
       <c r="H1784" t="n">
         <v>18714</v>
@@ -52163,7 +52163,7 @@
         <v>3</v>
       </c>
       <c r="G1786" t="n">
-        <v>2.76318764686584</v>
+        <v>2.76318740844727</v>
       </c>
       <c r="H1786" t="n">
         <v>18289</v>
@@ -52192,7 +52192,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1787" t="n">
-        <v>2.74476623535156</v>
+        <v>2.74476647377014</v>
       </c>
       <c r="H1787" t="n">
         <v>7438</v>
@@ -52221,7 +52221,7 @@
         <v>3.06500005722046</v>
       </c>
       <c r="G1788" t="n">
-        <v>2.82305645942688</v>
+        <v>2.82305669784546</v>
       </c>
       <c r="H1788" t="n">
         <v>88822</v>
@@ -52279,7 +52279,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1790" t="n">
-        <v>2.94740009307861</v>
+        <v>2.94739985466003</v>
       </c>
       <c r="H1790" t="n">
         <v>44078</v>
@@ -52337,7 +52337,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1792" t="n">
-        <v>2.82766199111938</v>
+        <v>2.82766175270081</v>
       </c>
       <c r="H1792" t="n">
         <v>80015</v>
@@ -52366,7 +52366,7 @@
         <v>3.09500002861023</v>
       </c>
       <c r="G1793" t="n">
-        <v>2.85068845748901</v>
+        <v>2.85068821907043</v>
       </c>
       <c r="H1793" t="n">
         <v>28822</v>
@@ -52395,7 +52395,7 @@
         <v>3.09500002861023</v>
       </c>
       <c r="G1794" t="n">
-        <v>2.85068845748901</v>
+        <v>2.85068821907043</v>
       </c>
       <c r="H1794" t="n">
         <v>16747</v>
@@ -52453,7 +52453,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1796" t="n">
-        <v>2.84608292579651</v>
+        <v>2.84608316421509</v>
       </c>
       <c r="H1796" t="n">
         <v>31735</v>
@@ -52482,7 +52482,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G1797" t="n">
-        <v>2.84147787094116</v>
+        <v>2.84147763252258</v>
       </c>
       <c r="H1797" t="n">
         <v>22313</v>
@@ -52540,7 +52540,7 @@
         <v>3</v>
       </c>
       <c r="G1799" t="n">
-        <v>2.76318764686584</v>
+        <v>2.76318740844727</v>
       </c>
       <c r="H1799" t="n">
         <v>67864</v>
@@ -52569,7 +52569,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1800" t="n">
-        <v>2.78160881996155</v>
+        <v>2.78160858154297</v>
       </c>
       <c r="H1800" t="n">
         <v>39074</v>
@@ -52598,7 +52598,7 @@
         <v>3</v>
       </c>
       <c r="G1801" t="n">
-        <v>2.76318764686584</v>
+        <v>2.76318740844727</v>
       </c>
       <c r="H1801" t="n">
         <v>47474</v>
@@ -52627,7 +52627,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1802" t="n">
-        <v>2.74476623535156</v>
+        <v>2.74476647377014</v>
       </c>
       <c r="H1802" t="n">
         <v>37524</v>
@@ -52656,7 +52656,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1803" t="n">
-        <v>2.73555541038513</v>
+        <v>2.73555564880371</v>
       </c>
       <c r="H1803" t="n">
         <v>19498</v>
@@ -52714,7 +52714,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1805" t="n">
-        <v>2.70792388916016</v>
+        <v>2.70792365074158</v>
       </c>
       <c r="H1805" t="n">
         <v>19541</v>
@@ -52801,7 +52801,7 @@
         <v>2.875</v>
       </c>
       <c r="G1808" t="n">
-        <v>2.64805459976196</v>
+        <v>2.64805483818054</v>
       </c>
       <c r="H1808" t="n">
         <v>74121</v>
@@ -52830,7 +52830,7 @@
         <v>2.875</v>
       </c>
       <c r="G1809" t="n">
-        <v>2.64805459976196</v>
+        <v>2.64805483818054</v>
       </c>
       <c r="H1809" t="n">
         <v>32625</v>
@@ -52859,7 +52859,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1810" t="n">
-        <v>2.6618709564209</v>
+        <v>2.66187071800232</v>
       </c>
       <c r="H1810" t="n">
         <v>38253</v>
@@ -52888,7 +52888,7 @@
         <v>2.875</v>
       </c>
       <c r="G1811" t="n">
-        <v>2.64805459976196</v>
+        <v>2.64805483818054</v>
       </c>
       <c r="H1811" t="n">
         <v>9680</v>
@@ -53004,7 +53004,7 @@
         <v>2.90499997138977</v>
       </c>
       <c r="G1815" t="n">
-        <v>2.67568635940552</v>
+        <v>2.6756865978241</v>
       </c>
       <c r="H1815" t="n">
         <v>67806</v>
@@ -53033,7 +53033,7 @@
         <v>2.95499992370605</v>
       </c>
       <c r="G1816" t="n">
-        <v>2.72173953056335</v>
+        <v>2.72173929214478</v>
       </c>
       <c r="H1816" t="n">
         <v>147185</v>
@@ -53062,7 +53062,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1817" t="n">
-        <v>2.7908194065094</v>
+        <v>2.79081916809082</v>
       </c>
       <c r="H1817" t="n">
         <v>94728</v>
@@ -53091,7 +53091,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1818" t="n">
-        <v>2.80002975463867</v>
+        <v>2.80002999305725</v>
       </c>
       <c r="H1818" t="n">
         <v>111859</v>
@@ -53120,7 +53120,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G1819" t="n">
-        <v>2.81384587287903</v>
+        <v>2.81384611129761</v>
       </c>
       <c r="H1819" t="n">
         <v>49528</v>
@@ -53149,7 +53149,7 @@
         <v>3</v>
       </c>
       <c r="G1820" t="n">
-        <v>2.76318764686584</v>
+        <v>2.76318740844727</v>
       </c>
       <c r="H1820" t="n">
         <v>54736</v>
@@ -53178,7 +53178,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1821" t="n">
-        <v>2.78160881996155</v>
+        <v>2.78160858154297</v>
       </c>
       <c r="H1821" t="n">
         <v>13158</v>
@@ -53207,7 +53207,7 @@
         <v>3</v>
       </c>
       <c r="G1822" t="n">
-        <v>2.76318764686584</v>
+        <v>2.76318740844727</v>
       </c>
       <c r="H1822" t="n">
         <v>16651</v>
@@ -53236,7 +53236,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1823" t="n">
-        <v>2.68950247764587</v>
+        <v>2.68950271606445</v>
       </c>
       <c r="H1823" t="n">
         <v>109020</v>
@@ -53294,7 +53294,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1825" t="n">
-        <v>2.70792388916016</v>
+        <v>2.70792365074158</v>
       </c>
       <c r="H1825" t="n">
         <v>6429</v>
@@ -53323,7 +53323,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1826" t="n">
-        <v>2.68950247764587</v>
+        <v>2.68950271606445</v>
       </c>
       <c r="H1826" t="n">
         <v>6444</v>
@@ -53381,7 +53381,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1828" t="n">
-        <v>2.68950247764587</v>
+        <v>2.68950271606445</v>
       </c>
       <c r="H1828" t="n">
         <v>9659</v>
@@ -53410,7 +53410,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1829" t="n">
-        <v>2.70792388916016</v>
+        <v>2.70792365074158</v>
       </c>
       <c r="H1829" t="n">
         <v>14150</v>
@@ -53555,7 +53555,7 @@
         <v>2.90499997138977</v>
       </c>
       <c r="G1834" t="n">
-        <v>2.67568635940552</v>
+        <v>2.6756865978241</v>
       </c>
       <c r="H1834" t="n">
         <v>10959</v>
@@ -53613,7 +53613,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1836" t="n">
-        <v>2.63423848152161</v>
+        <v>2.63423871994019</v>
       </c>
       <c r="H1836" t="n">
         <v>31119</v>
@@ -53671,7 +53671,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1838" t="n">
-        <v>2.6618709564209</v>
+        <v>2.66187071800232</v>
       </c>
       <c r="H1838" t="n">
         <v>13437</v>
@@ -53787,7 +53787,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1842" t="n">
-        <v>2.6618709564209</v>
+        <v>2.66187071800232</v>
       </c>
       <c r="H1842" t="n">
         <v>22070</v>
@@ -53845,7 +53845,7 @@
         <v>2.875</v>
       </c>
       <c r="G1844" t="n">
-        <v>2.64805459976196</v>
+        <v>2.64805483818054</v>
       </c>
       <c r="H1844" t="n">
         <v>3567</v>
@@ -53874,7 +53874,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1845" t="n">
-        <v>2.63423848152161</v>
+        <v>2.63423871994019</v>
       </c>
       <c r="H1845" t="n">
         <v>12759</v>
@@ -53903,7 +53903,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1846" t="n">
-        <v>2.59739589691162</v>
+        <v>2.5973961353302</v>
       </c>
       <c r="H1846" t="n">
         <v>69161</v>
@@ -53990,7 +53990,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1849" t="n">
-        <v>2.59739589691162</v>
+        <v>2.5973961353302</v>
       </c>
       <c r="H1849" t="n">
         <v>12419</v>
@@ -54048,7 +54048,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1851" t="n">
-        <v>2.63423848152161</v>
+        <v>2.63423871994019</v>
       </c>
       <c r="H1851" t="n">
         <v>9771</v>
@@ -54106,7 +54106,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1853" t="n">
-        <v>2.59739589691162</v>
+        <v>2.5973961353302</v>
       </c>
       <c r="H1853" t="n">
         <v>3518</v>
@@ -54135,7 +54135,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1854" t="n">
-        <v>2.5789749622345</v>
+        <v>2.57897472381592</v>
       </c>
       <c r="H1854" t="n">
         <v>2376</v>
@@ -54164,7 +54164,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1855" t="n">
-        <v>2.5789749622345</v>
+        <v>2.57897472381592</v>
       </c>
       <c r="H1855" t="n">
         <v>15183</v>
@@ -54193,7 +54193,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.59739589691162</v>
+        <v>2.5973961353302</v>
       </c>
       <c r="H1856" t="n">
         <v>11695</v>
@@ -54367,7 +54367,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.59739589691162</v>
+        <v>2.5973961353302</v>
       </c>
       <c r="H1862" t="n">
         <v>3050</v>
@@ -54396,7 +54396,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.5789749622345</v>
+        <v>2.57897472381592</v>
       </c>
       <c r="H1863" t="n">
         <v>15836</v>
@@ -54483,7 +54483,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.55134320259094</v>
+        <v>2.55134296417236</v>
       </c>
       <c r="H1866" t="n">
         <v>7646</v>
@@ -54541,7 +54541,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.41318368911743</v>
+        <v>2.41318345069885</v>
       </c>
       <c r="H1868" t="n">
         <v>30827</v>
@@ -54570,7 +54570,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.45923709869385</v>
+        <v>2.45923686027527</v>
       </c>
       <c r="H1869" t="n">
         <v>281162</v>
@@ -54599,7 +54599,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.50529003143311</v>
+        <v>2.50529026985168</v>
       </c>
       <c r="H1870" t="n">
         <v>10792</v>
@@ -54744,7 +54744,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.52371120452881</v>
+        <v>2.52371096611023</v>
       </c>
       <c r="H1875" t="n">
         <v>18900</v>
@@ -54802,7 +54802,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.50529003143311</v>
+        <v>2.50529026985168</v>
       </c>
       <c r="H1877" t="n">
         <v>4167</v>
@@ -54889,7 +54889,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.45923709869385</v>
+        <v>2.45923686027527</v>
       </c>
       <c r="H1880" t="n">
         <v>11534</v>
@@ -54918,7 +54918,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.45923709869385</v>
+        <v>2.45923686027527</v>
       </c>
       <c r="H1881" t="n">
         <v>12393</v>
@@ -54947,7 +54947,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.45923709869385</v>
+        <v>2.45923686027527</v>
       </c>
       <c r="H1882" t="n">
         <v>33920</v>
@@ -54976,7 +54976,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.45923709869385</v>
+        <v>2.45923686027527</v>
       </c>
       <c r="H1883" t="n">
         <v>12708</v>
@@ -55063,7 +55063,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.47765803337097</v>
+        <v>2.47765827178955</v>
       </c>
       <c r="H1886" t="n">
         <v>18267</v>
@@ -55353,7 +55353,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.45923709869385</v>
+        <v>2.45923686027527</v>
       </c>
       <c r="H1896" t="n">
         <v>13700</v>
@@ -55382,7 +55382,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.45923709869385</v>
+        <v>2.45923686027527</v>
       </c>
       <c r="H1897" t="n">
         <v>20267</v>
@@ -55469,7 +55469,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.50529003143311</v>
+        <v>2.50529026985168</v>
       </c>
       <c r="H1900" t="n">
         <v>4115</v>
@@ -55585,7 +55585,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.48686861991882</v>
+        <v>2.4868688583374</v>
       </c>
       <c r="H1904" t="n">
         <v>3513</v>
@@ -55614,7 +55614,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.48686861991882</v>
+        <v>2.4868688583374</v>
       </c>
       <c r="H1905" t="n">
         <v>2592</v>
@@ -55643,7 +55643,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.50529003143311</v>
+        <v>2.50529026985168</v>
       </c>
       <c r="H1906" t="n">
         <v>3964</v>
@@ -55730,7 +55730,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.52371120452881</v>
+        <v>2.52371096611023</v>
       </c>
       <c r="H1909" t="n">
         <v>21034</v>
@@ -55817,7 +55817,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.48590302467346</v>
+        <v>2.48590278625488</v>
       </c>
       <c r="H1912" t="n">
         <v>7088</v>
@@ -55933,7 +55933,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.48590302467346</v>
+        <v>2.48590278625488</v>
       </c>
       <c r="H1916" t="n">
         <v>25062</v>
@@ -55962,7 +55962,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.4764506816864</v>
+        <v>2.47645044326782</v>
       </c>
       <c r="H1917" t="n">
         <v>35748</v>
@@ -56194,7 +56194,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.35357356071472</v>
+        <v>2.35357332229614</v>
       </c>
       <c r="H1925" t="n">
         <v>78350</v>
@@ -56397,7 +56397,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.4764506816864</v>
+        <v>2.47645044326782</v>
       </c>
       <c r="H1932" t="n">
         <v>13093</v>
@@ -56571,7 +56571,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.4764506816864</v>
+        <v>2.47645044326782</v>
       </c>
       <c r="H1938" t="n">
         <v>1120</v>
@@ -56600,7 +56600,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.48590302467346</v>
+        <v>2.48590278625488</v>
       </c>
       <c r="H1939" t="n">
         <v>9455</v>
@@ -56629,7 +56629,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.48590302467346</v>
+        <v>2.48590278625488</v>
       </c>
       <c r="H1940" t="n">
         <v>11704</v>
@@ -56919,7 +56919,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.48590302467346</v>
+        <v>2.48590278625488</v>
       </c>
       <c r="H1950" t="n">
         <v>5260</v>
@@ -57151,7 +57151,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.25905227661133</v>
+        <v>2.25905251502991</v>
       </c>
       <c r="H1958" t="n">
         <v>30664</v>
@@ -57238,7 +57238,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.25905227661133</v>
+        <v>2.25905251502991</v>
       </c>
       <c r="H1961" t="n">
         <v>20841</v>
@@ -57354,7 +57354,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.20233964920044</v>
+        <v>2.20233988761902</v>
       </c>
       <c r="H1965" t="n">
         <v>29544</v>
@@ -57441,7 +57441,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.09836673736572</v>
+        <v>2.09836649894714</v>
       </c>
       <c r="H1968" t="n">
         <v>74706</v>
@@ -57470,7 +57470,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.09836673736572</v>
+        <v>2.09836649894714</v>
       </c>
       <c r="H1969" t="n">
         <v>9302</v>
@@ -57673,7 +57673,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1976" t="n">
-        <v>1.95658504962921</v>
+        <v>1.95658493041992</v>
       </c>
       <c r="H1976" t="n">
         <v>36000</v>
@@ -57702,7 +57702,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G1977" t="n">
-        <v>1.89987242221832</v>
+        <v>1.89987254142761</v>
       </c>
       <c r="H1977" t="n">
         <v>41806</v>
@@ -57731,7 +57731,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1978" t="n">
-        <v>1.88096833229065</v>
+        <v>1.88096821308136</v>
       </c>
       <c r="H1978" t="n">
         <v>34542</v>
@@ -58021,7 +58021,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G1988" t="n">
-        <v>1.76281690597534</v>
+        <v>1.76281702518463</v>
       </c>
       <c r="H1988" t="n">
         <v>33607</v>
@@ -58050,7 +58050,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1989" t="n">
-        <v>1.72028255462646</v>
+        <v>1.72028267383575</v>
       </c>
       <c r="H1989" t="n">
         <v>29742</v>
@@ -58079,7 +58079,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1990" t="n">
-        <v>1.71083033084869</v>
+        <v>1.71083045005798</v>
       </c>
       <c r="H1990" t="n">
         <v>30368</v>
@@ -58108,7 +58108,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G1991" t="n">
-        <v>1.69665217399597</v>
+        <v>1.69665229320526</v>
       </c>
       <c r="H1991" t="n">
         <v>20639</v>
@@ -58340,7 +58340,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1999" t="n">
-        <v>1.71083033084869</v>
+        <v>1.71083045005798</v>
       </c>
       <c r="H1999" t="n">
         <v>74975</v>
@@ -58369,7 +58369,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G2000" t="n">
-        <v>1.72028255462646</v>
+        <v>1.72028267383575</v>
       </c>
       <c r="H2000" t="n">
         <v>22410</v>
@@ -58398,7 +58398,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G2001" t="n">
-        <v>1.71555650234222</v>
+        <v>1.71555662155151</v>
       </c>
       <c r="H2001" t="n">
         <v>9789</v>
@@ -58427,7 +58427,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G2002" t="n">
-        <v>1.71555650234222</v>
+        <v>1.71555662155151</v>
       </c>
       <c r="H2002" t="n">
         <v>22125</v>
@@ -58456,7 +58456,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G2003" t="n">
-        <v>1.72028255462646</v>
+        <v>1.72028267383575</v>
       </c>
       <c r="H2003" t="n">
         <v>13291</v>
@@ -58485,7 +58485,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G2004" t="n">
-        <v>1.67302203178406</v>
+        <v>1.67302191257477</v>
       </c>
       <c r="H2004" t="n">
         <v>67771</v>
@@ -58514,7 +58514,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G2005" t="n">
-        <v>1.69665217399597</v>
+        <v>1.69665229320526</v>
       </c>
       <c r="H2005" t="n">
         <v>35812</v>
@@ -58543,7 +58543,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G2006" t="n">
-        <v>1.71555650234222</v>
+        <v>1.71555662155151</v>
       </c>
       <c r="H2006" t="n">
         <v>45452</v>
@@ -58601,7 +58601,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G2008" t="n">
-        <v>1.88096833229065</v>
+        <v>1.88096821308136</v>
       </c>
       <c r="H2008" t="n">
         <v>138796</v>
@@ -58630,7 +58630,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G2009" t="n">
-        <v>1.9093245267868</v>
+        <v>1.90932464599609</v>
       </c>
       <c r="H2009" t="n">
         <v>104194</v>
@@ -58659,7 +58659,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2010" t="n">
-        <v>1.89987242221832</v>
+        <v>1.89987254142761</v>
       </c>
       <c r="H2010" t="n">
         <v>65630</v>
@@ -58891,7 +58891,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G2018" t="n">
-        <v>1.97548937797546</v>
+        <v>1.97548913955688</v>
       </c>
       <c r="H2018" t="n">
         <v>15452</v>
@@ -59355,7 +59355,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G2034" t="n">
-        <v>2.20233964920044</v>
+        <v>2.20233988761902</v>
       </c>
       <c r="H2034" t="n">
         <v>63054</v>
@@ -59413,7 +59413,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G2036" t="n">
-        <v>2.14562726020813</v>
+        <v>2.14562702178955</v>
       </c>
       <c r="H2036" t="n">
         <v>37183</v>
@@ -59616,7 +59616,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G2043" t="n">
-        <v>2.14562726020813</v>
+        <v>2.14562702178955</v>
       </c>
       <c r="H2043" t="n">
         <v>24001</v>
@@ -60167,7 +60167,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G2062" t="n">
-        <v>2.13617515563965</v>
+        <v>2.13617491722107</v>
       </c>
       <c r="H2062" t="n">
         <v>65314</v>
@@ -60196,7 +60196,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G2063" t="n">
-        <v>2.1078188419342</v>
+        <v>2.10781860351562</v>
       </c>
       <c r="H2063" t="n">
         <v>13109</v>
@@ -60225,7 +60225,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G2064" t="n">
-        <v>1.94713282585144</v>
+        <v>1.94713306427002</v>
       </c>
       <c r="H2064" t="n">
         <v>87023</v>
@@ -60254,7 +60254,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2065" t="n">
-        <v>1.87151622772217</v>
+        <v>1.87151610851288</v>
       </c>
       <c r="H2065" t="n">
         <v>174135</v>
@@ -60428,7 +60428,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G2071" t="n">
-        <v>1.72973465919495</v>
+        <v>1.72973477840424</v>
       </c>
       <c r="H2071" t="n">
         <v>62542</v>
@@ -60457,7 +60457,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G2072" t="n">
-        <v>1.81007754802704</v>
+        <v>1.81007742881775</v>
       </c>
       <c r="H2072" t="n">
         <v>129521</v>
@@ -60486,7 +60486,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2073" t="n">
-        <v>1.87151622772217</v>
+        <v>1.87151610851288</v>
       </c>
       <c r="H2073" t="n">
         <v>114688</v>
@@ -60515,7 +60515,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G2074" t="n">
-        <v>1.87151622772217</v>
+        <v>1.87151610851288</v>
       </c>
       <c r="H2074" t="n">
         <v>54667</v>
@@ -60544,7 +60544,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G2075" t="n">
-        <v>1.86206412315369</v>
+        <v>1.8620640039444</v>
       </c>
       <c r="H2075" t="n">
         <v>42101</v>
@@ -60573,7 +60573,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2076" t="n">
-        <v>1.89987242221832</v>
+        <v>1.89987254142761</v>
       </c>
       <c r="H2076" t="n">
         <v>75534</v>
@@ -60602,7 +60602,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G2077" t="n">
-        <v>1.9093245267868</v>
+        <v>1.90932464599609</v>
       </c>
       <c r="H2077" t="n">
         <v>42646</v>
@@ -60631,7 +60631,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G2078" t="n">
-        <v>1.9093245267868</v>
+        <v>1.90932464599609</v>
       </c>
       <c r="H2078" t="n">
         <v>37922</v>
@@ -60660,7 +60660,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G2079" t="n">
-        <v>1.9093245267868</v>
+        <v>1.90932464599609</v>
       </c>
       <c r="H2079" t="n">
         <v>25910</v>
@@ -60689,7 +60689,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G2080" t="n">
-        <v>1.9093245267868</v>
+        <v>1.90932464599609</v>
       </c>
       <c r="H2080" t="n">
         <v>51175</v>
@@ -60718,7 +60718,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2081" t="n">
-        <v>1.89987242221832</v>
+        <v>1.89987254142761</v>
       </c>
       <c r="H2081" t="n">
         <v>40180</v>
@@ -60834,7 +60834,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2085" t="n">
-        <v>1.89987242221832</v>
+        <v>1.89987254142761</v>
       </c>
       <c r="H2085" t="n">
         <v>68375</v>
@@ -60950,7 +60950,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G2089" t="n">
-        <v>1.76281690597534</v>
+        <v>1.76281702518463</v>
       </c>
       <c r="H2089" t="n">
         <v>43797</v>
@@ -61037,7 +61037,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G2092" t="n">
-        <v>1.76281690597534</v>
+        <v>1.76281702518463</v>
       </c>
       <c r="H2092" t="n">
         <v>15031</v>
@@ -61153,7 +61153,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G2096" t="n">
-        <v>1.828981757164</v>
+        <v>1.82898163795471</v>
       </c>
       <c r="H2096" t="n">
         <v>110255</v>
@@ -61182,7 +61182,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G2097" t="n">
-        <v>1.828981757164</v>
+        <v>1.82898163795471</v>
       </c>
       <c r="H2097" t="n">
         <v>41092</v>
@@ -61356,7 +61356,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G2103" t="n">
-        <v>1.81007754802704</v>
+        <v>1.81007742881775</v>
       </c>
       <c r="H2103" t="n">
         <v>18410</v>
@@ -61385,7 +61385,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G2104" t="n">
-        <v>1.7817211151123</v>
+        <v>1.78172123432159</v>
       </c>
       <c r="H2104" t="n">
         <v>15864</v>
@@ -61559,7 +61559,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G2110" t="n">
-        <v>1.74391293525696</v>
+        <v>1.74391281604767</v>
       </c>
       <c r="H2110" t="n">
         <v>17198</v>
@@ -61646,7 +61646,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G2113" t="n">
-        <v>1.7817211151123</v>
+        <v>1.78172123432159</v>
       </c>
       <c r="H2113" t="n">
         <v>11979</v>
@@ -61733,7 +61733,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G2116" t="n">
-        <v>1.76281690597534</v>
+        <v>1.76281702518463</v>
       </c>
       <c r="H2116" t="n">
         <v>43153</v>
@@ -61994,7 +61994,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G2125" t="n">
-        <v>1.7817211151123</v>
+        <v>1.78172123432159</v>
       </c>
       <c r="H2125" t="n">
         <v>20190</v>
@@ -62052,7 +62052,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G2127" t="n">
-        <v>1.81007754802704</v>
+        <v>1.81007742881775</v>
       </c>
       <c r="H2127" t="n">
         <v>31095</v>
@@ -62110,7 +62110,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G2129" t="n">
-        <v>1.828981757164</v>
+        <v>1.82898163795471</v>
       </c>
       <c r="H2129" t="n">
         <v>59721</v>
@@ -62313,7 +62313,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G2136" t="n">
-        <v>1.7817211151123</v>
+        <v>1.78172123432159</v>
       </c>
       <c r="H2136" t="n">
         <v>35099</v>
@@ -62429,7 +62429,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G2140" t="n">
-        <v>1.74391293525696</v>
+        <v>1.74391281604767</v>
       </c>
       <c r="H2140" t="n">
         <v>38041</v>
@@ -62661,7 +62661,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G2148" t="n">
-        <v>1.74391293525696</v>
+        <v>1.74391281604767</v>
       </c>
       <c r="H2148" t="n">
         <v>17260</v>
@@ -62719,7 +62719,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G2150" t="n">
-        <v>1.72973465919495</v>
+        <v>1.72973477840424</v>
       </c>
       <c r="H2150" t="n">
         <v>29061</v>
@@ -62748,7 +62748,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G2151" t="n">
-        <v>1.68720018863678</v>
+        <v>1.68720006942749</v>
       </c>
       <c r="H2151" t="n">
         <v>22353</v>
@@ -62806,7 +62806,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G2153" t="n">
-        <v>1.71083033084869</v>
+        <v>1.71083045005798</v>
       </c>
       <c r="H2153" t="n">
         <v>22443</v>
@@ -62835,7 +62835,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G2154" t="n">
-        <v>1.68247413635254</v>
+        <v>1.68247401714325</v>
       </c>
       <c r="H2154" t="n">
         <v>63518</v>
@@ -62951,7 +62951,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G2158" t="n">
-        <v>1.69665217399597</v>
+        <v>1.69665229320526</v>
       </c>
       <c r="H2158" t="n">
         <v>13437</v>
@@ -62980,7 +62980,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G2159" t="n">
-        <v>1.67302203178406</v>
+        <v>1.67302191257477</v>
       </c>
       <c r="H2159" t="n">
         <v>16783</v>
@@ -80067,6 +80067,35 @@
         <v>26261</v>
       </c>
       <c r="I2748" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2749">
+      <c r="A2749" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2749" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C2749" t="n">
+        <v>1.08000004291534</v>
+      </c>
+      <c r="D2749" t="n">
+        <v>1.0900000333786</v>
+      </c>
+      <c r="E2749" t="n">
+        <v>1.07000005245209</v>
+      </c>
+      <c r="F2749" t="n">
+        <v>1.07000005245209</v>
+      </c>
+      <c r="G2749" t="n">
+        <v>1.07000005245209</v>
+      </c>
+      <c r="H2749" t="n">
+        <v>14810</v>
+      </c>
+      <c r="I2749" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELC.MI.xlsx
+++ b/data/ELC.MI.xlsx
@@ -485,7 +485,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G4" t="n">
-        <v>1.72444999217987</v>
+        <v>1.72445023059845</v>
       </c>
       <c r="H4" t="n">
         <v>5059</v>
@@ -601,7 +601,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G8" t="n">
-        <v>1.661905169487</v>
+        <v>1.66190540790558</v>
       </c>
       <c r="H8" t="n">
         <v>15254</v>
@@ -688,7 +688,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G11" t="n">
-        <v>1.59936058521271</v>
+        <v>1.59936046600342</v>
       </c>
       <c r="H11" t="n">
         <v>30082</v>
@@ -717,7 +717,7 @@
         <v>1.65199995040894</v>
       </c>
       <c r="G12" t="n">
-        <v>1.47605788707733</v>
+        <v>1.47605776786804</v>
       </c>
       <c r="H12" t="n">
         <v>45741</v>
@@ -746,7 +746,7 @@
         <v>1.66700005531311</v>
       </c>
       <c r="G13" t="n">
-        <v>1.48946034908295</v>
+        <v>1.48946022987366</v>
       </c>
       <c r="H13" t="n">
         <v>45328</v>
@@ -775,7 +775,7 @@
         <v>1.61099994182587</v>
       </c>
       <c r="G14" t="n">
-        <v>1.43942451477051</v>
+        <v>1.43942439556122</v>
       </c>
       <c r="H14" t="n">
         <v>54905</v>
@@ -833,7 +833,7 @@
         <v>1.70700001716614</v>
       </c>
       <c r="G16" t="n">
-        <v>1.5252001285553</v>
+        <v>1.52520024776459</v>
       </c>
       <c r="H16" t="n">
         <v>85068</v>
@@ -862,7 +862,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G17" t="n">
-        <v>1.44746589660645</v>
+        <v>1.44746601581573</v>
       </c>
       <c r="H17" t="n">
         <v>53091</v>
@@ -891,7 +891,7 @@
         <v>1.625</v>
       </c>
       <c r="G18" t="n">
-        <v>1.45193350315094</v>
+        <v>1.45193338394165</v>
       </c>
       <c r="H18" t="n">
         <v>25640</v>
@@ -949,7 +949,7 @@
         <v>1.63100004196167</v>
       </c>
       <c r="G20" t="n">
-        <v>1.45729434490204</v>
+        <v>1.45729446411133</v>
       </c>
       <c r="H20" t="n">
         <v>7885</v>
@@ -978,7 +978,7 @@
         <v>1.65100002288818</v>
       </c>
       <c r="G21" t="n">
-        <v>1.47516429424286</v>
+        <v>1.47516441345215</v>
       </c>
       <c r="H21" t="n">
         <v>7561</v>
@@ -1007,7 +1007,7 @@
         <v>1.59099996089935</v>
       </c>
       <c r="G22" t="n">
-        <v>1.4215544462204</v>
+        <v>1.42155432701111</v>
       </c>
       <c r="H22" t="n">
         <v>81953</v>
@@ -1036,7 +1036,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G23" t="n">
-        <v>1.39832377433777</v>
+        <v>1.39832365512848</v>
       </c>
       <c r="H23" t="n">
         <v>23089</v>
@@ -1094,7 +1094,7 @@
         <v>1.51699995994568</v>
       </c>
       <c r="G25" t="n">
-        <v>1.35543572902679</v>
+        <v>1.3554356098175</v>
       </c>
       <c r="H25" t="n">
         <v>27464</v>
@@ -1123,7 +1123,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G26" t="n">
-        <v>1.38492119312286</v>
+        <v>1.38492107391357</v>
       </c>
       <c r="H26" t="n">
         <v>35283</v>
@@ -1152,7 +1152,7 @@
         <v>1.40199995040894</v>
       </c>
       <c r="G27" t="n">
-        <v>1.25268352031708</v>
+        <v>1.25268340110779</v>
       </c>
       <c r="H27" t="n">
         <v>60303</v>
@@ -1181,7 +1181,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G28" t="n">
-        <v>1.28216874599457</v>
+        <v>1.28216886520386</v>
       </c>
       <c r="H28" t="n">
         <v>58422</v>
@@ -1268,7 +1268,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G31" t="n">
-        <v>1.42959594726562</v>
+        <v>1.42959606647491</v>
       </c>
       <c r="H31" t="n">
         <v>187635</v>
@@ -1297,7 +1297,7 @@
         <v>1.63199996948242</v>
       </c>
       <c r="G32" t="n">
-        <v>1.45818781852722</v>
+        <v>1.45818793773651</v>
       </c>
       <c r="H32" t="n">
         <v>53239</v>
@@ -1355,7 +1355,7 @@
         <v>1.65900003910065</v>
       </c>
       <c r="G34" t="n">
-        <v>1.4823123216629</v>
+        <v>1.48231244087219</v>
       </c>
       <c r="H34" t="n">
         <v>55221</v>
@@ -1442,7 +1442,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G37" t="n">
-        <v>1.57255566120148</v>
+        <v>1.57255554199219</v>
       </c>
       <c r="H37" t="n">
         <v>29281</v>
@@ -1500,7 +1500,7 @@
         <v>1.74699997901917</v>
       </c>
       <c r="G39" t="n">
-        <v>1.56094002723694</v>
+        <v>1.56094014644623</v>
       </c>
       <c r="H39" t="n">
         <v>2902</v>
@@ -1529,7 +1529,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G40" t="n">
-        <v>1.57702314853668</v>
+        <v>1.57702302932739</v>
       </c>
       <c r="H40" t="n">
         <v>4812</v>
@@ -1616,7 +1616,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G43" t="n">
-        <v>1.57255566120148</v>
+        <v>1.57255554199219</v>
       </c>
       <c r="H43" t="n">
         <v>24781</v>
@@ -1645,7 +1645,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G44" t="n">
-        <v>1.51894569396973</v>
+        <v>1.51894581317902</v>
       </c>
       <c r="H44" t="n">
         <v>29575</v>
@@ -1848,7 +1848,7 @@
         <v>1.76600003242493</v>
       </c>
       <c r="G51" t="n">
-        <v>1.57791650295258</v>
+        <v>1.57791662216187</v>
       </c>
       <c r="H51" t="n">
         <v>27532</v>
@@ -1877,7 +1877,7 @@
         <v>1.8309999704361</v>
       </c>
       <c r="G52" t="n">
-        <v>1.63599371910095</v>
+        <v>1.63599383831024</v>
       </c>
       <c r="H52" t="n">
         <v>51060</v>
@@ -1906,7 +1906,7 @@
         <v>1.89300000667572</v>
       </c>
       <c r="G53" t="n">
-        <v>1.69139063358307</v>
+        <v>1.69139075279236</v>
       </c>
       <c r="H53" t="n">
         <v>24502</v>
@@ -1935,7 +1935,7 @@
         <v>1.90900003910065</v>
       </c>
       <c r="G54" t="n">
-        <v>1.70568668842316</v>
+        <v>1.70568680763245</v>
       </c>
       <c r="H54" t="n">
         <v>85054</v>
@@ -1964,7 +1964,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G55" t="n">
-        <v>1.67977523803711</v>
+        <v>1.67977511882782</v>
       </c>
       <c r="H55" t="n">
         <v>33252</v>
@@ -1993,7 +1993,7 @@
         <v>1.90799999237061</v>
       </c>
       <c r="G56" t="n">
-        <v>1.70479321479797</v>
+        <v>1.70479309558868</v>
       </c>
       <c r="H56" t="n">
         <v>30447</v>
@@ -2022,7 +2022,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G57" t="n">
-        <v>1.72444999217987</v>
+        <v>1.72445023059845</v>
       </c>
       <c r="H57" t="n">
         <v>46823</v>
@@ -2051,7 +2051,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G58" t="n">
-        <v>1.7691251039505</v>
+        <v>1.76912498474121</v>
       </c>
       <c r="H58" t="n">
         <v>198777</v>
@@ -2080,7 +2080,7 @@
         <v>1.95200002193451</v>
       </c>
       <c r="G59" t="n">
-        <v>1.74410700798035</v>
+        <v>1.74410712718964</v>
       </c>
       <c r="H59" t="n">
         <v>77105</v>
@@ -2109,7 +2109,7 @@
         <v>1.93599998950958</v>
       </c>
       <c r="G60" t="n">
-        <v>1.72981107234955</v>
+        <v>1.72981119155884</v>
       </c>
       <c r="H60" t="n">
         <v>25733</v>
@@ -2138,7 +2138,7 @@
         <v>1.94599997997284</v>
       </c>
       <c r="G61" t="n">
-        <v>1.73874604701996</v>
+        <v>1.73874616622925</v>
       </c>
       <c r="H61" t="n">
         <v>32577</v>
@@ -2196,7 +2196,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G63" t="n">
-        <v>1.75125515460968</v>
+        <v>1.7512549161911</v>
       </c>
       <c r="H63" t="n">
         <v>20594</v>
@@ -2254,7 +2254,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G65" t="n">
-        <v>1.72444999217987</v>
+        <v>1.72445023059845</v>
       </c>
       <c r="H65" t="n">
         <v>30447</v>
@@ -2428,7 +2428,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G71" t="n">
-        <v>1.67084014415741</v>
+        <v>1.6708402633667</v>
       </c>
       <c r="H71" t="n">
         <v>26244</v>
@@ -2515,7 +2515,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G74" t="n">
-        <v>1.71551513671875</v>
+        <v>1.71551501750946</v>
       </c>
       <c r="H74" t="n">
         <v>16230</v>
@@ -2573,7 +2573,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G76" t="n">
-        <v>1.71104753017426</v>
+        <v>1.71104764938354</v>
       </c>
       <c r="H76" t="n">
         <v>11969</v>
@@ -2660,7 +2660,7 @@
         <v>1.89800000190735</v>
       </c>
       <c r="G79" t="n">
-        <v>1.69585824012756</v>
+        <v>1.69585812091827</v>
       </c>
       <c r="H79" t="n">
         <v>17651</v>
@@ -2718,7 +2718,7 @@
         <v>1.89900004863739</v>
       </c>
       <c r="G81" t="n">
-        <v>1.69675183296204</v>
+        <v>1.69675171375275</v>
       </c>
       <c r="H81" t="n">
         <v>12593</v>
@@ -2863,7 +2863,7 @@
         <v>1.91600000858307</v>
       </c>
       <c r="G86" t="n">
-        <v>1.71194124221802</v>
+        <v>1.71194112300873</v>
       </c>
       <c r="H86" t="n">
         <v>107351</v>
@@ -2979,7 +2979,7 @@
         <v>1.84800004959106</v>
       </c>
       <c r="G90" t="n">
-        <v>1.6511834859848</v>
+        <v>1.65118336677551</v>
       </c>
       <c r="H90" t="n">
         <v>73958</v>
@@ -3066,7 +3066,7 @@
         <v>1.85199999809265</v>
       </c>
       <c r="G93" t="n">
-        <v>1.65475749969482</v>
+        <v>1.65475738048553</v>
       </c>
       <c r="H93" t="n">
         <v>17094</v>
@@ -3182,7 +3182,7 @@
         <v>1.90600001811981</v>
       </c>
       <c r="G97" t="n">
-        <v>1.70300626754761</v>
+        <v>1.70300614833832</v>
       </c>
       <c r="H97" t="n">
         <v>8769</v>
@@ -3298,7 +3298,7 @@
         <v>1.9190000295639</v>
       </c>
       <c r="G101" t="n">
-        <v>1.72342276573181</v>
+        <v>1.7234228849411</v>
       </c>
       <c r="H101" t="n">
         <v>15489</v>
@@ -3327,7 +3327,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G102" t="n">
-        <v>1.76922500133514</v>
+        <v>1.76922512054443</v>
       </c>
       <c r="H102" t="n">
         <v>207475</v>
@@ -3385,7 +3385,7 @@
         <v>1.93799996376038</v>
       </c>
       <c r="G104" t="n">
-        <v>1.74048626422882</v>
+        <v>1.74048638343811</v>
       </c>
       <c r="H104" t="n">
         <v>7025</v>
@@ -3443,7 +3443,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G106" t="n">
-        <v>1.73330175876617</v>
+        <v>1.73330187797546</v>
       </c>
       <c r="H106" t="n">
         <v>52731</v>
@@ -3472,7 +3472,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G107" t="n">
-        <v>1.72432088851929</v>
+        <v>1.72432076931</v>
       </c>
       <c r="H107" t="n">
         <v>8971</v>
@@ -3559,7 +3559,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G110" t="n">
-        <v>1.72432088851929</v>
+        <v>1.72432076931</v>
       </c>
       <c r="H110" t="n">
         <v>25811</v>
@@ -3588,7 +3588,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G111" t="n">
-        <v>1.72432088851929</v>
+        <v>1.72432076931</v>
       </c>
       <c r="H111" t="n">
         <v>52856</v>
@@ -3704,7 +3704,7 @@
         <v>1.85199999809265</v>
       </c>
       <c r="G115" t="n">
-        <v>1.66325116157532</v>
+        <v>1.66325128078461</v>
       </c>
       <c r="H115" t="n">
         <v>23967</v>
@@ -3733,7 +3733,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G116" t="n">
-        <v>1.63900291919708</v>
+        <v>1.63900303840637</v>
       </c>
       <c r="H116" t="n">
         <v>14527</v>
@@ -3762,7 +3762,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G117" t="n">
-        <v>1.6255316734314</v>
+        <v>1.62553155422211</v>
       </c>
       <c r="H117" t="n">
         <v>26360</v>
@@ -3791,7 +3791,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G118" t="n">
-        <v>1.58960819244385</v>
+        <v>1.58960831165314</v>
       </c>
       <c r="H118" t="n">
         <v>20333</v>
@@ -3820,7 +3820,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G119" t="n">
-        <v>1.60756993293762</v>
+        <v>1.60757005214691</v>
       </c>
       <c r="H119" t="n">
         <v>29731</v>
@@ -3849,7 +3849,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G120" t="n">
-        <v>1.63451266288757</v>
+        <v>1.63451254367828</v>
       </c>
       <c r="H120" t="n">
         <v>16192</v>
@@ -3994,7 +3994,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G125" t="n">
-        <v>1.58960819244385</v>
+        <v>1.58960831165314</v>
       </c>
       <c r="H125" t="n">
         <v>22469</v>
@@ -4052,7 +4052,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G127" t="n">
-        <v>1.63900291919708</v>
+        <v>1.63900303840637</v>
       </c>
       <c r="H127" t="n">
         <v>3233</v>
@@ -4081,7 +4081,7 @@
         <v>1.79799997806549</v>
       </c>
       <c r="G128" t="n">
-        <v>1.61475467681885</v>
+        <v>1.61475455760956</v>
       </c>
       <c r="H128" t="n">
         <v>11186</v>
@@ -4110,7 +4110,7 @@
         <v>1.80900001525879</v>
       </c>
       <c r="G129" t="n">
-        <v>1.62463355064392</v>
+        <v>1.62463366985321</v>
       </c>
       <c r="H129" t="n">
         <v>7722</v>
@@ -4168,7 +4168,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G131" t="n">
-        <v>1.59409868717194</v>
+        <v>1.59409880638123</v>
       </c>
       <c r="H131" t="n">
         <v>16611</v>
@@ -4197,7 +4197,7 @@
         <v>1.69700002670288</v>
       </c>
       <c r="G132" t="n">
-        <v>1.52404820919037</v>
+        <v>1.52404832839966</v>
       </c>
       <c r="H132" t="n">
         <v>59729</v>
@@ -4226,7 +4226,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G133" t="n">
-        <v>1.46836698055267</v>
+        <v>1.46836709976196</v>
       </c>
       <c r="H133" t="n">
         <v>25558</v>
@@ -4284,7 +4284,7 @@
         <v>1.62100005149841</v>
       </c>
       <c r="G135" t="n">
-        <v>1.45579385757446</v>
+        <v>1.45579397678375</v>
       </c>
       <c r="H135" t="n">
         <v>55410</v>
@@ -4371,7 +4371,7 @@
         <v>1.66400003433228</v>
       </c>
       <c r="G138" t="n">
-        <v>1.49441158771515</v>
+        <v>1.49441146850586</v>
       </c>
       <c r="H138" t="n">
         <v>38824</v>
@@ -4400,7 +4400,7 @@
         <v>1.67299997806549</v>
       </c>
       <c r="G139" t="n">
-        <v>1.50249421596527</v>
+        <v>1.50249409675598</v>
       </c>
       <c r="H139" t="n">
         <v>13739</v>
@@ -4429,7 +4429,7 @@
         <v>1.6690000295639</v>
       </c>
       <c r="G140" t="n">
-        <v>1.49890196323395</v>
+        <v>1.49890184402466</v>
       </c>
       <c r="H140" t="n">
         <v>29756</v>
@@ -4545,7 +4545,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G144" t="n">
-        <v>1.49979984760284</v>
+        <v>1.49979996681213</v>
       </c>
       <c r="H144" t="n">
         <v>4167</v>
@@ -4574,7 +4574,7 @@
         <v>1.66100001335144</v>
       </c>
       <c r="G145" t="n">
-        <v>1.49171721935272</v>
+        <v>1.49171733856201</v>
       </c>
       <c r="H145" t="n">
         <v>7428</v>
@@ -4603,7 +4603,7 @@
         <v>1.66100001335144</v>
       </c>
       <c r="G146" t="n">
-        <v>1.49171721935272</v>
+        <v>1.49171733856201</v>
       </c>
       <c r="H146" t="n">
         <v>6561</v>
@@ -4690,7 +4690,7 @@
         <v>1.65400004386902</v>
       </c>
       <c r="G149" t="n">
-        <v>1.48543059825897</v>
+        <v>1.48543071746826</v>
       </c>
       <c r="H149" t="n">
         <v>29881</v>
@@ -4806,7 +4806,7 @@
         <v>1.69400000572205</v>
       </c>
       <c r="G153" t="n">
-        <v>1.52135407924652</v>
+        <v>1.52135396003723</v>
       </c>
       <c r="H153" t="n">
         <v>5121</v>
@@ -4835,7 +4835,7 @@
         <v>1.69400000572205</v>
       </c>
       <c r="G154" t="n">
-        <v>1.52135407924652</v>
+        <v>1.52135396003723</v>
       </c>
       <c r="H154" t="n">
         <v>20263</v>
@@ -4864,7 +4864,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G155" t="n">
-        <v>1.52674245834351</v>
+        <v>1.5267425775528</v>
       </c>
       <c r="H155" t="n">
         <v>8511</v>
@@ -4893,7 +4893,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G156" t="n">
-        <v>1.50878083705902</v>
+        <v>1.50878071784973</v>
       </c>
       <c r="H156" t="n">
         <v>8538</v>
@@ -4922,7 +4922,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G157" t="n">
-        <v>1.52674245834351</v>
+        <v>1.5267425775528</v>
       </c>
       <c r="H157" t="n">
         <v>12054</v>
@@ -5096,7 +5096,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G163" t="n">
-        <v>1.49979984760284</v>
+        <v>1.49979996681213</v>
       </c>
       <c r="H163" t="n">
         <v>16224</v>
@@ -5125,7 +5125,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G164" t="n">
-        <v>1.49979984760284</v>
+        <v>1.49979996681213</v>
       </c>
       <c r="H164" t="n">
         <v>48801</v>
@@ -5183,7 +5183,7 @@
         <v>1.71399998664856</v>
       </c>
       <c r="G166" t="n">
-        <v>1.53931558132172</v>
+        <v>1.53931570053101</v>
       </c>
       <c r="H166" t="n">
         <v>50193</v>
@@ -5212,7 +5212,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G167" t="n">
-        <v>1.64349353313446</v>
+        <v>1.64349341392517</v>
       </c>
       <c r="H167" t="n">
         <v>181062</v>
@@ -5270,7 +5270,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G169" t="n">
-        <v>1.75126361846924</v>
+        <v>1.75126349925995</v>
       </c>
       <c r="H169" t="n">
         <v>207435</v>
@@ -5299,7 +5299,7 @@
         <v>1.93299996852875</v>
       </c>
       <c r="G170" t="n">
-        <v>1.73599588871002</v>
+        <v>1.73599600791931</v>
       </c>
       <c r="H170" t="n">
         <v>60291</v>
@@ -5386,7 +5386,7 @@
         <v>1.84800004959106</v>
       </c>
       <c r="G173" t="n">
-        <v>1.65965902805328</v>
+        <v>1.65965890884399</v>
       </c>
       <c r="H173" t="n">
         <v>102738</v>
@@ -5444,7 +5444,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G175" t="n">
-        <v>1.67043590545654</v>
+        <v>1.67043602466583</v>
       </c>
       <c r="H175" t="n">
         <v>32520</v>
@@ -5502,7 +5502,7 @@
         <v>1.86800003051758</v>
       </c>
       <c r="G177" t="n">
-        <v>1.67762041091919</v>
+        <v>1.67762064933777</v>
       </c>
       <c r="H177" t="n">
         <v>59095</v>
@@ -5531,7 +5531,7 @@
         <v>1.85099995136261</v>
       </c>
       <c r="G178" t="n">
-        <v>1.66235303878784</v>
+        <v>1.66235315799713</v>
       </c>
       <c r="H178" t="n">
         <v>54287</v>
@@ -5560,7 +5560,7 @@
         <v>1.88399994373322</v>
       </c>
       <c r="G179" t="n">
-        <v>1.69198989868164</v>
+        <v>1.69198977947235</v>
       </c>
       <c r="H179" t="n">
         <v>65993</v>
@@ -5589,7 +5589,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G180" t="n">
-        <v>1.67043590545654</v>
+        <v>1.67043602466583</v>
       </c>
       <c r="H180" t="n">
         <v>18502</v>
@@ -5618,7 +5618,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G181" t="n">
-        <v>1.68839764595032</v>
+        <v>1.68839740753174</v>
       </c>
       <c r="H181" t="n">
         <v>27805</v>
@@ -5647,7 +5647,7 @@
         <v>1.85199999809265</v>
       </c>
       <c r="G182" t="n">
-        <v>1.66325116157532</v>
+        <v>1.66325128078461</v>
       </c>
       <c r="H182" t="n">
         <v>5317</v>
@@ -5676,7 +5676,7 @@
         <v>1.81400001049042</v>
       </c>
       <c r="G183" t="n">
-        <v>1.62912404537201</v>
+        <v>1.62912392616272</v>
       </c>
       <c r="H183" t="n">
         <v>26014</v>
@@ -5705,7 +5705,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G184" t="n">
-        <v>1.63451266288757</v>
+        <v>1.63451254367828</v>
       </c>
       <c r="H184" t="n">
         <v>8710</v>
@@ -5995,7 +5995,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G194" t="n">
-        <v>1.63451266288757</v>
+        <v>1.63451254367828</v>
       </c>
       <c r="H194" t="n">
         <v>7919</v>
@@ -6024,7 +6024,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G195" t="n">
-        <v>1.63451266288757</v>
+        <v>1.63451254367828</v>
       </c>
       <c r="H195" t="n">
         <v>15652</v>
@@ -6082,7 +6082,7 @@
         <v>1.89699995517731</v>
       </c>
       <c r="G197" t="n">
-        <v>1.70366489887238</v>
+        <v>1.70366501808167</v>
       </c>
       <c r="H197" t="n">
         <v>75519</v>
@@ -6169,7 +6169,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G200" t="n">
-        <v>1.68839764595032</v>
+        <v>1.68839740753174</v>
       </c>
       <c r="H200" t="n">
         <v>22315</v>
@@ -6198,7 +6198,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G201" t="n">
-        <v>1.67043590545654</v>
+        <v>1.67043602466583</v>
       </c>
       <c r="H201" t="n">
         <v>20696</v>
@@ -6314,7 +6314,7 @@
         <v>1.85199999809265</v>
       </c>
       <c r="G205" t="n">
-        <v>1.66325116157532</v>
+        <v>1.66325128078461</v>
       </c>
       <c r="H205" t="n">
         <v>4455</v>
@@ -6372,7 +6372,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G207" t="n">
-        <v>1.64349353313446</v>
+        <v>1.64349341392517</v>
       </c>
       <c r="H207" t="n">
         <v>28071</v>
@@ -6401,7 +6401,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G208" t="n">
-        <v>1.63451266288757</v>
+        <v>1.63451254367828</v>
       </c>
       <c r="H208" t="n">
         <v>34872</v>
@@ -6488,7 +6488,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G211" t="n">
-        <v>1.65247416496277</v>
+        <v>1.65247428417206</v>
       </c>
       <c r="H211" t="n">
         <v>11706</v>
@@ -6575,7 +6575,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G214" t="n">
-        <v>1.65247416496277</v>
+        <v>1.65247428417206</v>
       </c>
       <c r="H214" t="n">
         <v>7430</v>
@@ -6604,7 +6604,7 @@
         <v>1.86800003051758</v>
       </c>
       <c r="G215" t="n">
-        <v>1.67762041091919</v>
+        <v>1.67762064933777</v>
       </c>
       <c r="H215" t="n">
         <v>3321</v>
@@ -6662,7 +6662,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G217" t="n">
-        <v>1.63451266288757</v>
+        <v>1.63451254367828</v>
       </c>
       <c r="H217" t="n">
         <v>3906</v>
@@ -6691,7 +6691,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G218" t="n">
-        <v>1.64349353313446</v>
+        <v>1.64349341392517</v>
       </c>
       <c r="H218" t="n">
         <v>1563</v>
@@ -6720,7 +6720,7 @@
         <v>1.83700001239777</v>
       </c>
       <c r="G219" t="n">
-        <v>1.64978003501892</v>
+        <v>1.64977991580963</v>
       </c>
       <c r="H219" t="n">
         <v>23250</v>
@@ -6749,7 +6749,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G220" t="n">
-        <v>1.6255316734314</v>
+        <v>1.62553155422211</v>
       </c>
       <c r="H220" t="n">
         <v>9667</v>
@@ -6807,7 +6807,7 @@
         <v>1.83700001239777</v>
       </c>
       <c r="G222" t="n">
-        <v>1.64978003501892</v>
+        <v>1.64977991580963</v>
       </c>
       <c r="H222" t="n">
         <v>16935</v>
@@ -6836,7 +6836,7 @@
         <v>1.84800004959106</v>
       </c>
       <c r="G223" t="n">
-        <v>1.65965902805328</v>
+        <v>1.65965890884399</v>
       </c>
       <c r="H223" t="n">
         <v>13665</v>
@@ -6894,7 +6894,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G225" t="n">
-        <v>1.58960819244385</v>
+        <v>1.58960831165314</v>
       </c>
       <c r="H225" t="n">
         <v>117138</v>
@@ -6923,7 +6923,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G226" t="n">
-        <v>1.52674245834351</v>
+        <v>1.5267425775528</v>
       </c>
       <c r="H226" t="n">
         <v>99175</v>
@@ -6981,7 +6981,7 @@
         <v>1.65799999237061</v>
       </c>
       <c r="G228" t="n">
-        <v>1.48902308940887</v>
+        <v>1.4890228509903</v>
       </c>
       <c r="H228" t="n">
         <v>27997</v>
@@ -7010,7 +7010,7 @@
         <v>1.62899994850159</v>
       </c>
       <c r="G229" t="n">
-        <v>1.4629784822464</v>
+        <v>1.46297860145569</v>
       </c>
       <c r="H229" t="n">
         <v>31851</v>
@@ -7039,7 +7039,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G230" t="n">
-        <v>1.4279533624649</v>
+        <v>1.42795324325562</v>
       </c>
       <c r="H230" t="n">
         <v>59409</v>
@@ -7068,7 +7068,7 @@
         <v>1.49199998378754</v>
       </c>
       <c r="G231" t="n">
-        <v>1.33994102478027</v>
+        <v>1.33994114398956</v>
       </c>
       <c r="H231" t="n">
         <v>200414</v>
@@ -7097,7 +7097,7 @@
         <v>1.49199998378754</v>
       </c>
       <c r="G232" t="n">
-        <v>1.33994102478027</v>
+        <v>1.33994114398956</v>
       </c>
       <c r="H232" t="n">
         <v>104739</v>
@@ -7300,7 +7300,7 @@
         <v>1.55900001525879</v>
       </c>
       <c r="G239" t="n">
-        <v>1.40011262893677</v>
+        <v>1.40011274814606</v>
       </c>
       <c r="H239" t="n">
         <v>29691</v>
@@ -7358,7 +7358,7 @@
         <v>1.59399998188019</v>
       </c>
       <c r="G241" t="n">
-        <v>1.43154561519623</v>
+        <v>1.43154549598694</v>
       </c>
       <c r="H241" t="n">
         <v>112147</v>
@@ -7387,7 +7387,7 @@
         <v>1.60800004005432</v>
       </c>
       <c r="G242" t="n">
-        <v>1.44411873817444</v>
+        <v>1.44411885738373</v>
       </c>
       <c r="H242" t="n">
         <v>23993</v>
@@ -7416,7 +7416,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G243" t="n">
-        <v>1.45040547847748</v>
+        <v>1.45040535926819</v>
       </c>
       <c r="H243" t="n">
         <v>70934</v>
@@ -7474,7 +7474,7 @@
         <v>1.65299999713898</v>
       </c>
       <c r="G245" t="n">
-        <v>1.48453259468079</v>
+        <v>1.48453271389008</v>
       </c>
       <c r="H245" t="n">
         <v>48017</v>
@@ -7561,7 +7561,7 @@
         <v>1.70200002193451</v>
       </c>
       <c r="G248" t="n">
-        <v>1.52853858470917</v>
+        <v>1.52853870391846</v>
       </c>
       <c r="H248" t="n">
         <v>48300</v>
@@ -7677,7 +7677,7 @@
         <v>1.78600001335144</v>
       </c>
       <c r="G252" t="n">
-        <v>1.6039776802063</v>
+        <v>1.60397779941559</v>
       </c>
       <c r="H252" t="n">
         <v>99793</v>
@@ -7706,7 +7706,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G253" t="n">
-        <v>1.6255316734314</v>
+        <v>1.62553155422211</v>
       </c>
       <c r="H253" t="n">
         <v>37423</v>
@@ -7735,7 +7735,7 @@
         <v>1.81400001049042</v>
       </c>
       <c r="G254" t="n">
-        <v>1.62912404537201</v>
+        <v>1.62912392616272</v>
       </c>
       <c r="H254" t="n">
         <v>9303</v>
@@ -7793,7 +7793,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G256" t="n">
-        <v>1.6255316734314</v>
+        <v>1.62553155422211</v>
       </c>
       <c r="H256" t="n">
         <v>64043</v>
@@ -7909,7 +7909,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G260" t="n">
-        <v>1.6255316734314</v>
+        <v>1.62553155422211</v>
       </c>
       <c r="H260" t="n">
         <v>44432</v>
@@ -7938,7 +7938,7 @@
         <v>1.81400001049042</v>
       </c>
       <c r="G261" t="n">
-        <v>1.62912404537201</v>
+        <v>1.62912392616272</v>
       </c>
       <c r="H261" t="n">
         <v>24558</v>
@@ -7967,7 +7967,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G262" t="n">
-        <v>1.64349353313446</v>
+        <v>1.64349341392517</v>
       </c>
       <c r="H262" t="n">
         <v>12760</v>
@@ -7996,7 +7996,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G263" t="n">
-        <v>1.65247416496277</v>
+        <v>1.65247428417206</v>
       </c>
       <c r="H263" t="n">
         <v>21549</v>
@@ -8083,7 +8083,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G266" t="n">
-        <v>1.6255316734314</v>
+        <v>1.62553155422211</v>
       </c>
       <c r="H266" t="n">
         <v>19396</v>
@@ -8112,7 +8112,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G267" t="n">
-        <v>1.65247416496277</v>
+        <v>1.65247428417206</v>
       </c>
       <c r="H267" t="n">
         <v>16547</v>
@@ -8170,7 +8170,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G269" t="n">
-        <v>1.63451266288757</v>
+        <v>1.63451254367828</v>
       </c>
       <c r="H269" t="n">
         <v>12835</v>
@@ -8228,7 +8228,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G271" t="n">
-        <v>1.6255316734314</v>
+        <v>1.62553155422211</v>
       </c>
       <c r="H271" t="n">
         <v>20092</v>
@@ -8257,7 +8257,7 @@
         <v>1.78600001335144</v>
       </c>
       <c r="G272" t="n">
-        <v>1.6039776802063</v>
+        <v>1.60397779941559</v>
       </c>
       <c r="H272" t="n">
         <v>14300</v>
@@ -8344,7 +8344,7 @@
         <v>1.70200002193451</v>
       </c>
       <c r="G275" t="n">
-        <v>1.52853858470917</v>
+        <v>1.52853870391846</v>
       </c>
       <c r="H275" t="n">
         <v>22633</v>
@@ -8402,7 +8402,7 @@
         <v>1.68099999427795</v>
       </c>
       <c r="G277" t="n">
-        <v>1.5096789598465</v>
+        <v>1.50967884063721</v>
       </c>
       <c r="H277" t="n">
         <v>16296</v>
@@ -8431,7 +8431,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G278" t="n">
-        <v>1.50878083705902</v>
+        <v>1.50878071784973</v>
       </c>
       <c r="H278" t="n">
         <v>28951</v>
@@ -8460,7 +8460,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G279" t="n">
-        <v>1.50878083705902</v>
+        <v>1.50878071784973</v>
       </c>
       <c r="H279" t="n">
         <v>7031</v>
@@ -8518,7 +8518,7 @@
         <v>1.72599995136261</v>
       </c>
       <c r="G281" t="n">
-        <v>1.55009269714355</v>
+        <v>1.55009257793427</v>
       </c>
       <c r="H281" t="n">
         <v>16160</v>
@@ -8605,7 +8605,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G284" t="n">
-        <v>1.48183822631836</v>
+        <v>1.48183834552765</v>
       </c>
       <c r="H284" t="n">
         <v>14957</v>
@@ -8634,7 +8634,7 @@
         <v>1.62100005149841</v>
       </c>
       <c r="G285" t="n">
-        <v>1.45579385757446</v>
+        <v>1.45579397678375</v>
       </c>
       <c r="H285" t="n">
         <v>60471</v>
@@ -8721,7 +8721,7 @@
         <v>1.51900005340576</v>
       </c>
       <c r="G288" t="n">
-        <v>1.3641893863678</v>
+        <v>1.36418926715851</v>
       </c>
       <c r="H288" t="n">
         <v>409131</v>
@@ -9011,7 +9011,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G298" t="n">
-        <v>1.3381450176239</v>
+        <v>1.33814489841461</v>
       </c>
       <c r="H298" t="n">
         <v>73910</v>
@@ -9069,7 +9069,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G300" t="n">
-        <v>1.4279533624649</v>
+        <v>1.42795324325562</v>
       </c>
       <c r="H300" t="n">
         <v>175966</v>
@@ -9127,7 +9127,7 @@
         <v>1.58599996566772</v>
       </c>
       <c r="G302" t="n">
-        <v>1.424360871315</v>
+        <v>1.42436099052429</v>
       </c>
       <c r="H302" t="n">
         <v>52521</v>
@@ -9156,7 +9156,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G303" t="n">
-        <v>1.40999150276184</v>
+        <v>1.40999162197113</v>
       </c>
       <c r="H303" t="n">
         <v>82518</v>
@@ -9243,7 +9243,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G306" t="n">
-        <v>1.40999150276184</v>
+        <v>1.40999162197113</v>
       </c>
       <c r="H306" t="n">
         <v>99179</v>
@@ -9272,7 +9272,7 @@
         <v>1.57700002193451</v>
       </c>
       <c r="G307" t="n">
-        <v>1.41627824306488</v>
+        <v>1.41627836227417</v>
       </c>
       <c r="H307" t="n">
         <v>147605</v>
@@ -9330,7 +9330,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G309" t="n">
-        <v>1.37406814098358</v>
+        <v>1.37406826019287</v>
       </c>
       <c r="H309" t="n">
         <v>68905</v>
@@ -9533,7 +9533,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G316" t="n">
-        <v>1.41448199748993</v>
+        <v>1.41448211669922</v>
       </c>
       <c r="H316" t="n">
         <v>135167</v>
@@ -9562,7 +9562,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G317" t="n">
-        <v>1.41897237300873</v>
+        <v>1.41897249221802</v>
       </c>
       <c r="H317" t="n">
         <v>347122</v>
@@ -9591,7 +9591,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G318" t="n">
-        <v>1.46387672424316</v>
+        <v>1.46387648582458</v>
       </c>
       <c r="H318" t="n">
         <v>285320</v>
@@ -9620,7 +9620,7 @@
         <v>1.6139999628067</v>
       </c>
       <c r="G319" t="n">
-        <v>1.44950723648071</v>
+        <v>1.44950735569</v>
       </c>
       <c r="H319" t="n">
         <v>156991</v>
@@ -9649,7 +9649,7 @@
         <v>1.62600004673004</v>
       </c>
       <c r="G320" t="n">
-        <v>1.46028435230255</v>
+        <v>1.46028423309326</v>
       </c>
       <c r="H320" t="n">
         <v>280073</v>
@@ -9678,7 +9678,7 @@
         <v>1.62300002574921</v>
       </c>
       <c r="G321" t="n">
-        <v>1.45758998394012</v>
+        <v>1.45759010314941</v>
       </c>
       <c r="H321" t="n">
         <v>85627</v>
@@ -9707,7 +9707,7 @@
         <v>1.62899994850159</v>
       </c>
       <c r="G322" t="n">
-        <v>1.4629784822464</v>
+        <v>1.46297860145569</v>
       </c>
       <c r="H322" t="n">
         <v>36193</v>
@@ -9736,7 +9736,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G323" t="n">
-        <v>1.46387672424316</v>
+        <v>1.46387648582458</v>
       </c>
       <c r="H323" t="n">
         <v>95927</v>
@@ -9794,7 +9794,7 @@
         <v>1.65299999713898</v>
       </c>
       <c r="G325" t="n">
-        <v>1.48453259468079</v>
+        <v>1.48453271389008</v>
       </c>
       <c r="H325" t="n">
         <v>133633</v>
@@ -9852,7 +9852,7 @@
         <v>1.63399994373322</v>
       </c>
       <c r="G327" t="n">
-        <v>1.46746897697449</v>
+        <v>1.4674688577652</v>
       </c>
       <c r="H327" t="n">
         <v>29486</v>
@@ -9881,7 +9881,7 @@
         <v>1.62399995326996</v>
       </c>
       <c r="G328" t="n">
-        <v>1.4584881067276</v>
+        <v>1.45848798751831</v>
       </c>
       <c r="H328" t="n">
         <v>22720</v>
@@ -9939,7 +9939,7 @@
         <v>1.625</v>
       </c>
       <c r="G330" t="n">
-        <v>1.45938611030579</v>
+        <v>1.45938622951508</v>
       </c>
       <c r="H330" t="n">
         <v>44118</v>
@@ -10026,7 +10026,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G333" t="n">
-        <v>1.42346298694611</v>
+        <v>1.42346286773682</v>
       </c>
       <c r="H333" t="n">
         <v>10071</v>
@@ -10113,7 +10113,7 @@
         <v>1.63399994373322</v>
       </c>
       <c r="G336" t="n">
-        <v>1.46746897697449</v>
+        <v>1.4674688577652</v>
       </c>
       <c r="H336" t="n">
         <v>79269</v>
@@ -10258,7 +10258,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G341" t="n">
-        <v>1.48183822631836</v>
+        <v>1.48183834552765</v>
       </c>
       <c r="H341" t="n">
         <v>38360</v>
@@ -10403,7 +10403,7 @@
         <v>1.70099997520447</v>
       </c>
       <c r="G346" t="n">
-        <v>1.52764058113098</v>
+        <v>1.52764046192169</v>
       </c>
       <c r="H346" t="n">
         <v>51869</v>
@@ -10432,7 +10432,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G347" t="n">
-        <v>1.51327121257782</v>
+        <v>1.51327109336853</v>
       </c>
       <c r="H347" t="n">
         <v>32612</v>
@@ -10519,7 +10519,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G350" t="n">
-        <v>1.67941665649414</v>
+        <v>1.67941677570343</v>
       </c>
       <c r="H350" t="n">
         <v>566755</v>
@@ -10577,7 +10577,7 @@
         <v>1.85399997234344</v>
       </c>
       <c r="G352" t="n">
-        <v>1.66504728794098</v>
+        <v>1.66504752635956</v>
       </c>
       <c r="H352" t="n">
         <v>183961</v>
@@ -10664,7 +10664,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G355" t="n">
-        <v>1.65247416496277</v>
+        <v>1.65247428417206</v>
       </c>
       <c r="H355" t="n">
         <v>265133</v>
@@ -10722,7 +10722,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G357" t="n">
-        <v>1.74228262901306</v>
+        <v>1.74228274822235</v>
       </c>
       <c r="H357" t="n">
         <v>320048</v>
@@ -10751,7 +10751,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G358" t="n">
-        <v>1.73330175876617</v>
+        <v>1.73330187797546</v>
       </c>
       <c r="H358" t="n">
         <v>184861</v>
@@ -10780,7 +10780,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G359" t="n">
-        <v>1.72432088851929</v>
+        <v>1.72432076931</v>
       </c>
       <c r="H359" t="n">
         <v>120208</v>
@@ -10809,7 +10809,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G360" t="n">
-        <v>1.72432088851929</v>
+        <v>1.72432076931</v>
       </c>
       <c r="H360" t="n">
         <v>68025</v>
@@ -10867,7 +10867,7 @@
         <v>1.8860000371933</v>
       </c>
       <c r="G362" t="n">
-        <v>1.69378614425659</v>
+        <v>1.6937860250473</v>
       </c>
       <c r="H362" t="n">
         <v>175263</v>
@@ -11012,7 +11012,7 @@
         <v>1.82200002670288</v>
       </c>
       <c r="G367" t="n">
-        <v>1.63630867004395</v>
+        <v>1.63630878925323</v>
       </c>
       <c r="H367" t="n">
         <v>150910</v>
@@ -11070,7 +11070,7 @@
         <v>1.80900001525879</v>
       </c>
       <c r="G369" t="n">
-        <v>1.62463355064392</v>
+        <v>1.62463366985321</v>
       </c>
       <c r="H369" t="n">
         <v>77361</v>
@@ -11128,7 +11128,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G371" t="n">
-        <v>1.63900291919708</v>
+        <v>1.63900303840637</v>
       </c>
       <c r="H371" t="n">
         <v>52595</v>
@@ -11157,7 +11157,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G372" t="n">
-        <v>1.65247416496277</v>
+        <v>1.65247428417206</v>
       </c>
       <c r="H372" t="n">
         <v>72016</v>
@@ -11186,7 +11186,7 @@
         <v>1.83700001239777</v>
       </c>
       <c r="G373" t="n">
-        <v>1.64978003501892</v>
+        <v>1.64977991580963</v>
       </c>
       <c r="H373" t="n">
         <v>46666</v>
@@ -11215,7 +11215,7 @@
         <v>1.82200002670288</v>
       </c>
       <c r="G374" t="n">
-        <v>1.63630867004395</v>
+        <v>1.63630878925323</v>
       </c>
       <c r="H374" t="n">
         <v>44811</v>
@@ -11244,7 +11244,7 @@
         <v>1.83899998664856</v>
       </c>
       <c r="G375" t="n">
-        <v>1.65157628059387</v>
+        <v>1.65157616138458</v>
       </c>
       <c r="H375" t="n">
         <v>36475</v>
@@ -11302,7 +11302,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G377" t="n">
-        <v>1.64349353313446</v>
+        <v>1.64349341392517</v>
       </c>
       <c r="H377" t="n">
         <v>31220</v>
@@ -11331,7 +11331,7 @@
         <v>1.81200003623962</v>
       </c>
       <c r="G378" t="n">
-        <v>1.62732791900635</v>
+        <v>1.62732779979706</v>
       </c>
       <c r="H378" t="n">
         <v>22032</v>
@@ -11418,7 +11418,7 @@
         <v>1.7610000371933</v>
       </c>
       <c r="G381" t="n">
-        <v>1.58152556419373</v>
+        <v>1.58152568340302</v>
       </c>
       <c r="H381" t="n">
         <v>104816</v>
@@ -11447,7 +11447,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G382" t="n">
-        <v>1.58960819244385</v>
+        <v>1.58960831165314</v>
       </c>
       <c r="H382" t="n">
         <v>25737</v>
@@ -11621,7 +11621,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G388" t="n">
-        <v>1.49979984760284</v>
+        <v>1.49979996681213</v>
       </c>
       <c r="H388" t="n">
         <v>107443</v>
@@ -11650,7 +11650,7 @@
         <v>1.69700002670288</v>
       </c>
       <c r="G389" t="n">
-        <v>1.52404820919037</v>
+        <v>1.52404832839966</v>
       </c>
       <c r="H389" t="n">
         <v>22102</v>
@@ -11708,7 +11708,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G391" t="n">
-        <v>1.55368506908417</v>
+        <v>1.55368494987488</v>
       </c>
       <c r="H391" t="n">
         <v>67131</v>
@@ -11795,7 +11795,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G394" t="n">
-        <v>1.60756993293762</v>
+        <v>1.60757005214691</v>
       </c>
       <c r="H394" t="n">
         <v>18440</v>
@@ -11853,7 +11853,7 @@
         <v>1.78799998760223</v>
       </c>
       <c r="G396" t="n">
-        <v>1.60577392578125</v>
+        <v>1.60577380657196</v>
       </c>
       <c r="H396" t="n">
         <v>58873</v>
@@ -11882,7 +11882,7 @@
         <v>1.80900001525879</v>
       </c>
       <c r="G397" t="n">
-        <v>1.62463355064392</v>
+        <v>1.62463366985321</v>
       </c>
       <c r="H397" t="n">
         <v>3288</v>
@@ -11911,7 +11911,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G398" t="n">
-        <v>1.58960819244385</v>
+        <v>1.58960831165314</v>
       </c>
       <c r="H398" t="n">
         <v>55429</v>
@@ -11940,7 +11940,7 @@
         <v>1.7610000371933</v>
       </c>
       <c r="G399" t="n">
-        <v>1.58152556419373</v>
+        <v>1.58152568340302</v>
       </c>
       <c r="H399" t="n">
         <v>10377</v>
@@ -11998,7 +11998,7 @@
         <v>1.78400003910065</v>
       </c>
       <c r="G401" t="n">
-        <v>1.60218143463135</v>
+        <v>1.60218167304993</v>
       </c>
       <c r="H401" t="n">
         <v>34154</v>
@@ -12027,7 +12027,7 @@
         <v>1.75300002098083</v>
       </c>
       <c r="G402" t="n">
-        <v>1.57434093952179</v>
+        <v>1.5743408203125</v>
       </c>
       <c r="H402" t="n">
         <v>35483</v>
@@ -12085,7 +12085,7 @@
         <v>1.78299999237061</v>
       </c>
       <c r="G404" t="n">
-        <v>1.60128355026245</v>
+        <v>1.60128343105316</v>
       </c>
       <c r="H404" t="n">
         <v>28416</v>
@@ -12143,7 +12143,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G406" t="n">
-        <v>1.60756993293762</v>
+        <v>1.60757005214691</v>
       </c>
       <c r="H406" t="n">
         <v>6875</v>
@@ -12172,7 +12172,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G407" t="n">
-        <v>1.63451266288757</v>
+        <v>1.63451254367828</v>
       </c>
       <c r="H407" t="n">
         <v>64582</v>
@@ -12201,7 +12201,7 @@
         <v>1.78400003910065</v>
       </c>
       <c r="G408" t="n">
-        <v>1.60218143463135</v>
+        <v>1.60218167304993</v>
       </c>
       <c r="H408" t="n">
         <v>110613</v>
@@ -12259,7 +12259,7 @@
         <v>1.80900001525879</v>
       </c>
       <c r="G410" t="n">
-        <v>1.62463355064392</v>
+        <v>1.62463366985321</v>
       </c>
       <c r="H410" t="n">
         <v>43219</v>
@@ -12346,7 +12346,7 @@
         <v>1.79799997806549</v>
       </c>
       <c r="G413" t="n">
-        <v>1.61475467681885</v>
+        <v>1.61475455760956</v>
       </c>
       <c r="H413" t="n">
         <v>21152</v>
@@ -12404,7 +12404,7 @@
         <v>1.75399994850159</v>
       </c>
       <c r="G415" t="n">
-        <v>1.57523894309998</v>
+        <v>1.57523906230927</v>
       </c>
       <c r="H415" t="n">
         <v>10057</v>
@@ -12433,7 +12433,7 @@
         <v>1.78600001335144</v>
       </c>
       <c r="G416" t="n">
-        <v>1.6039776802063</v>
+        <v>1.60397779941559</v>
       </c>
       <c r="H416" t="n">
         <v>17027</v>
@@ -12491,7 +12491,7 @@
         <v>1.73699998855591</v>
       </c>
       <c r="G418" t="n">
-        <v>1.55997169017792</v>
+        <v>1.55997157096863</v>
       </c>
       <c r="H418" t="n">
         <v>31219</v>
@@ -12607,7 +12607,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G422" t="n">
-        <v>1.60756993293762</v>
+        <v>1.60757005214691</v>
       </c>
       <c r="H422" t="n">
         <v>28229</v>
@@ -12665,7 +12665,7 @@
         <v>1.85199999809265</v>
       </c>
       <c r="G424" t="n">
-        <v>1.66325116157532</v>
+        <v>1.66325128078461</v>
       </c>
       <c r="H424" t="n">
         <v>757598</v>
@@ -12694,7 +12694,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G425" t="n">
-        <v>1.72432088851929</v>
+        <v>1.72432076931</v>
       </c>
       <c r="H425" t="n">
         <v>904742</v>
@@ -12752,7 +12752,7 @@
         <v>1.87899994850159</v>
       </c>
       <c r="G427" t="n">
-        <v>1.68749940395355</v>
+        <v>1.68749952316284</v>
       </c>
       <c r="H427" t="n">
         <v>160276</v>
@@ -12810,7 +12810,7 @@
         <v>1.85300004482269</v>
       </c>
       <c r="G429" t="n">
-        <v>1.66414940357208</v>
+        <v>1.66414928436279</v>
       </c>
       <c r="H429" t="n">
         <v>158747</v>
@@ -12839,7 +12839,7 @@
         <v>1.85199999809265</v>
       </c>
       <c r="G430" t="n">
-        <v>1.66325116157532</v>
+        <v>1.66325128078461</v>
       </c>
       <c r="H430" t="n">
         <v>107773</v>
@@ -12897,7 +12897,7 @@
         <v>1.89600002765656</v>
       </c>
       <c r="G432" t="n">
-        <v>1.70276701450348</v>
+        <v>1.70276689529419</v>
       </c>
       <c r="H432" t="n">
         <v>450452</v>
@@ -12955,7 +12955,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G434" t="n">
-        <v>1.88597583770752</v>
+        <v>1.88597595691681</v>
       </c>
       <c r="H434" t="n">
         <v>616287</v>
@@ -13245,7 +13245,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G444" t="n">
-        <v>2.36196064949036</v>
+        <v>2.36196041107178</v>
       </c>
       <c r="H444" t="n">
         <v>291112</v>
@@ -13274,7 +13274,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G445" t="n">
-        <v>2.3529794216156</v>
+        <v>2.35297966003418</v>
       </c>
       <c r="H445" t="n">
         <v>213302</v>
@@ -13303,7 +13303,7 @@
         <v>2.61800003051758</v>
       </c>
       <c r="G446" t="n">
-        <v>2.35118365287781</v>
+        <v>2.35118341445923</v>
       </c>
       <c r="H446" t="n">
         <v>133237</v>
@@ -13332,7 +13332,7 @@
         <v>2.61800003051758</v>
       </c>
       <c r="G447" t="n">
-        <v>2.35118365287781</v>
+        <v>2.35118341445923</v>
       </c>
       <c r="H447" t="n">
         <v>157247</v>
@@ -13390,7 +13390,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G449" t="n">
-        <v>2.34399843215942</v>
+        <v>2.343998670578</v>
       </c>
       <c r="H449" t="n">
         <v>156938</v>
@@ -13477,7 +13477,7 @@
         <v>2.56399989128113</v>
       </c>
       <c r="G452" t="n">
-        <v>2.30268669128418</v>
+        <v>2.30268692970276</v>
       </c>
       <c r="H452" t="n">
         <v>110046</v>
@@ -13535,7 +13535,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G454" t="n">
-        <v>2.26317119598389</v>
+        <v>2.26317095756531</v>
       </c>
       <c r="H454" t="n">
         <v>120776</v>
@@ -13593,7 +13593,7 @@
         <v>2.43600010871887</v>
       </c>
       <c r="G456" t="n">
-        <v>2.18773221969604</v>
+        <v>2.18773198127747</v>
       </c>
       <c r="H456" t="n">
         <v>225310</v>
@@ -13622,7 +13622,7 @@
         <v>2.32200002670288</v>
       </c>
       <c r="G457" t="n">
-        <v>2.08535051345825</v>
+        <v>2.08535075187683</v>
       </c>
       <c r="H457" t="n">
         <v>355994</v>
@@ -13651,7 +13651,7 @@
         <v>2.50600004196167</v>
       </c>
       <c r="G458" t="n">
-        <v>2.25059819221497</v>
+        <v>2.25059795379639</v>
       </c>
       <c r="H458" t="n">
         <v>401496</v>
@@ -13680,7 +13680,7 @@
         <v>2.54800009727478</v>
       </c>
       <c r="G459" t="n">
-        <v>2.28831768035889</v>
+        <v>2.28831791877747</v>
       </c>
       <c r="H459" t="n">
         <v>214035</v>
@@ -13767,7 +13767,7 @@
         <v>2.83800005912781</v>
       </c>
       <c r="G462" t="n">
-        <v>2.54876208305359</v>
+        <v>2.54876184463501</v>
       </c>
       <c r="H462" t="n">
         <v>952565</v>
@@ -13796,7 +13796,7 @@
         <v>2.86199998855591</v>
       </c>
       <c r="G463" t="n">
-        <v>2.57031583786011</v>
+        <v>2.57031607627869</v>
       </c>
       <c r="H463" t="n">
         <v>833255</v>
@@ -13941,7 +13941,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G468" t="n">
-        <v>2.50565361976624</v>
+        <v>2.50565409660339</v>
       </c>
       <c r="H468" t="n">
         <v>122440</v>
@@ -13970,7 +13970,7 @@
         <v>2.84400010108948</v>
       </c>
       <c r="G469" t="n">
-        <v>2.55415034294128</v>
+        <v>2.55415058135986</v>
       </c>
       <c r="H469" t="n">
         <v>200297</v>
@@ -13999,7 +13999,7 @@
         <v>2.87599992752075</v>
       </c>
       <c r="G470" t="n">
-        <v>2.58288884162903</v>
+        <v>2.58288908004761</v>
       </c>
       <c r="H470" t="n">
         <v>115197</v>
@@ -14028,7 +14028,7 @@
         <v>2.87599992752075</v>
       </c>
       <c r="G471" t="n">
-        <v>2.58288884162903</v>
+        <v>2.58288908004761</v>
       </c>
       <c r="H471" t="n">
         <v>65266</v>
@@ -14086,7 +14086,7 @@
         <v>2.7739999294281</v>
       </c>
       <c r="G473" t="n">
-        <v>2.49128460884094</v>
+        <v>2.49128437042236</v>
       </c>
       <c r="H473" t="n">
         <v>164387</v>
@@ -14231,7 +14231,7 @@
         <v>2.42400002479553</v>
       </c>
       <c r="G478" t="n">
-        <v>2.17695498466492</v>
+        <v>2.1769552230835</v>
       </c>
       <c r="H478" t="n">
         <v>603916</v>
@@ -14608,7 +14608,7 @@
         <v>2.55800008773804</v>
       </c>
       <c r="G491" t="n">
-        <v>2.29729866981506</v>
+        <v>2.29729843139648</v>
       </c>
       <c r="H491" t="n">
         <v>201051</v>
@@ -14666,7 +14666,7 @@
         <v>2.48399996757507</v>
       </c>
       <c r="G493" t="n">
-        <v>2.23084020614624</v>
+        <v>2.23083996772766</v>
       </c>
       <c r="H493" t="n">
         <v>58887</v>
@@ -14695,7 +14695,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G494" t="n">
-        <v>2.20928645133972</v>
+        <v>2.20928621292114</v>
       </c>
       <c r="H494" t="n">
         <v>52081</v>
@@ -14782,7 +14782,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G497" t="n">
-        <v>2.20928645133972</v>
+        <v>2.20928621292114</v>
       </c>
       <c r="H497" t="n">
         <v>17558</v>
@@ -14869,7 +14869,7 @@
         <v>2.54800009727478</v>
       </c>
       <c r="G500" t="n">
-        <v>2.28831768035889</v>
+        <v>2.28831791877747</v>
       </c>
       <c r="H500" t="n">
         <v>105664</v>
@@ -14956,7 +14956,7 @@
         <v>2.47399997711182</v>
       </c>
       <c r="G503" t="n">
-        <v>2.22185921669006</v>
+        <v>2.22185945510864</v>
       </c>
       <c r="H503" t="n">
         <v>90422</v>
@@ -14985,7 +14985,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G504" t="n">
-        <v>2.22724771499634</v>
+        <v>2.22724795341492</v>
       </c>
       <c r="H504" t="n">
         <v>89542</v>
@@ -15072,7 +15072,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G507" t="n">
-        <v>2.22724771499634</v>
+        <v>2.22724795341492</v>
       </c>
       <c r="H507" t="n">
         <v>48876</v>
@@ -15130,7 +15130,7 @@
         <v>2.43799996376038</v>
       </c>
       <c r="G509" t="n">
-        <v>2.18952822685242</v>
+        <v>2.189528465271</v>
       </c>
       <c r="H509" t="n">
         <v>58859</v>
@@ -15159,7 +15159,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G510" t="n">
-        <v>2.19850921630859</v>
+        <v>2.19850897789001</v>
       </c>
       <c r="H510" t="n">
         <v>53234</v>
@@ -15217,7 +15217,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G512" t="n">
-        <v>2.19132471084595</v>
+        <v>2.19132447242737</v>
       </c>
       <c r="H512" t="n">
         <v>101821</v>
@@ -15275,7 +15275,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G514" t="n">
-        <v>2.1554012298584</v>
+        <v>2.15540146827698</v>
       </c>
       <c r="H514" t="n">
         <v>62182</v>
@@ -15304,7 +15304,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G515" t="n">
-        <v>2.19132471084595</v>
+        <v>2.19132447242737</v>
       </c>
       <c r="H515" t="n">
         <v>50871</v>
@@ -15333,7 +15333,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G516" t="n">
-        <v>2.22724771499634</v>
+        <v>2.22724795341492</v>
       </c>
       <c r="H516" t="n">
         <v>124471</v>
@@ -15362,7 +15362,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G517" t="n">
-        <v>2.22724771499634</v>
+        <v>2.22724795341492</v>
       </c>
       <c r="H517" t="n">
         <v>74248</v>
@@ -15391,7 +15391,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G518" t="n">
-        <v>2.21826672554016</v>
+        <v>2.21826696395874</v>
       </c>
       <c r="H518" t="n">
         <v>107211</v>
@@ -15420,7 +15420,7 @@
         <v>2.43499994277954</v>
       </c>
       <c r="G519" t="n">
-        <v>2.18683385848999</v>
+        <v>2.18683409690857</v>
       </c>
       <c r="H519" t="n">
         <v>50889</v>
@@ -15449,7 +15449,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G520" t="n">
-        <v>2.1554012298584</v>
+        <v>2.15540146827698</v>
       </c>
       <c r="H520" t="n">
         <v>47165</v>
@@ -15565,7 +15565,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G524" t="n">
-        <v>2.04763126373291</v>
+        <v>2.04763102531433</v>
       </c>
       <c r="H524" t="n">
         <v>233885</v>
@@ -15623,7 +15623,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G526" t="n">
-        <v>2.06559276580811</v>
+        <v>2.06559252738953</v>
       </c>
       <c r="H526" t="n">
         <v>88709</v>
@@ -15681,7 +15681,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G528" t="n">
-        <v>2.08355450630188</v>
+        <v>2.0835542678833</v>
       </c>
       <c r="H528" t="n">
         <v>61089</v>
@@ -15739,7 +15739,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G530" t="n">
-        <v>2.10151600837708</v>
+        <v>2.10151624679565</v>
       </c>
       <c r="H530" t="n">
         <v>83765</v>
@@ -15768,7 +15768,7 @@
         <v>2.41499996185303</v>
       </c>
       <c r="G531" t="n">
-        <v>2.16887235641479</v>
+        <v>2.16887259483337</v>
       </c>
       <c r="H531" t="n">
         <v>279959</v>
@@ -15826,7 +15826,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G533" t="n">
-        <v>2.1554012298584</v>
+        <v>2.15540146827698</v>
       </c>
       <c r="H533" t="n">
         <v>68783</v>
@@ -15855,7 +15855,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G534" t="n">
-        <v>2.1374397277832</v>
+        <v>2.13743948936462</v>
       </c>
       <c r="H534" t="n">
         <v>38703</v>
@@ -15884,7 +15884,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G535" t="n">
-        <v>2.11947751045227</v>
+        <v>2.11947774887085</v>
       </c>
       <c r="H535" t="n">
         <v>99717</v>
@@ -15913,7 +15913,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G536" t="n">
-        <v>2.01170778274536</v>
+        <v>2.01170802116394</v>
       </c>
       <c r="H536" t="n">
         <v>202868</v>
@@ -15942,7 +15942,7 @@
         <v>2.27500009536743</v>
       </c>
       <c r="G537" t="n">
-        <v>2.04314064979553</v>
+        <v>2.04314088821411</v>
       </c>
       <c r="H537" t="n">
         <v>191254</v>
@@ -15971,7 +15971,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G538" t="n">
-        <v>2.1554012298584</v>
+        <v>2.15540146827698</v>
       </c>
       <c r="H538" t="n">
         <v>281784</v>
@@ -16000,7 +16000,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G539" t="n">
-        <v>2.06559276580811</v>
+        <v>2.06559252738953</v>
       </c>
       <c r="H539" t="n">
         <v>88481</v>
@@ -16029,7 +16029,7 @@
         <v>2.26500010490417</v>
       </c>
       <c r="G540" t="n">
-        <v>2.03415989875793</v>
+        <v>2.03416013717651</v>
       </c>
       <c r="H540" t="n">
         <v>99980</v>
@@ -16058,7 +16058,7 @@
         <v>2.36500000953674</v>
       </c>
       <c r="G541" t="n">
-        <v>2.12396812438965</v>
+        <v>2.12396836280823</v>
       </c>
       <c r="H541" t="n">
         <v>172019</v>
@@ -16116,7 +16116,7 @@
         <v>2.34500002861023</v>
       </c>
       <c r="G543" t="n">
-        <v>2.10600662231445</v>
+        <v>2.10600638389587</v>
       </c>
       <c r="H543" t="n">
         <v>72504</v>
@@ -16145,7 +16145,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G544" t="n">
-        <v>2.06559276580811</v>
+        <v>2.06559252738953</v>
       </c>
       <c r="H544" t="n">
         <v>94606</v>
@@ -16174,7 +16174,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G545" t="n">
-        <v>2.06559276580811</v>
+        <v>2.06559252738953</v>
       </c>
       <c r="H545" t="n">
         <v>90340</v>
@@ -16203,7 +16203,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G546" t="n">
-        <v>2.10151600837708</v>
+        <v>2.10151624679565</v>
       </c>
       <c r="H546" t="n">
         <v>81347</v>
@@ -16232,7 +16232,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G547" t="n">
-        <v>2.06559276580811</v>
+        <v>2.06559252738953</v>
       </c>
       <c r="H547" t="n">
         <v>66787</v>
@@ -16348,7 +16348,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G551" t="n">
-        <v>2.04763126373291</v>
+        <v>2.04763102531433</v>
       </c>
       <c r="H551" t="n">
         <v>51292</v>
@@ -16377,7 +16377,7 @@
         <v>2.21499991416931</v>
       </c>
       <c r="G552" t="n">
-        <v>1.98925566673279</v>
+        <v>1.98925578594208</v>
       </c>
       <c r="H552" t="n">
         <v>123803</v>
@@ -16406,7 +16406,7 @@
         <v>2.14499998092651</v>
       </c>
       <c r="G553" t="n">
-        <v>1.92638981342316</v>
+        <v>1.92638969421387</v>
       </c>
       <c r="H553" t="n">
         <v>175487</v>
@@ -16493,7 +16493,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G556" t="n">
-        <v>1.85005271434784</v>
+        <v>1.85005259513855</v>
       </c>
       <c r="H556" t="n">
         <v>37112</v>
@@ -16522,7 +16522,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G557" t="n">
-        <v>1.91291868686676</v>
+        <v>1.91291856765747</v>
       </c>
       <c r="H557" t="n">
         <v>103311</v>
@@ -16580,7 +16580,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G559" t="n">
-        <v>1.94884216785431</v>
+        <v>1.94884192943573</v>
       </c>
       <c r="H559" t="n">
         <v>132375</v>
@@ -16609,7 +16609,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G560" t="n">
-        <v>1.98476505279541</v>
+        <v>1.98476529121399</v>
       </c>
       <c r="H560" t="n">
         <v>45217</v>
@@ -16638,7 +16638,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G561" t="n">
-        <v>2.01170778274536</v>
+        <v>2.01170802116394</v>
       </c>
       <c r="H561" t="n">
         <v>40737</v>
@@ -16725,7 +16725,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G564" t="n">
-        <v>2.06110262870789</v>
+        <v>2.06110239028931</v>
       </c>
       <c r="H564" t="n">
         <v>80977</v>
@@ -16754,7 +16754,7 @@
         <v>2.27500009536743</v>
       </c>
       <c r="G565" t="n">
-        <v>2.04314064979553</v>
+        <v>2.04314088821411</v>
       </c>
       <c r="H565" t="n">
         <v>23262</v>
@@ -16841,7 +16841,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G568" t="n">
-        <v>2.01170778274536</v>
+        <v>2.01170802116394</v>
       </c>
       <c r="H568" t="n">
         <v>188558</v>
@@ -16899,7 +16899,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G570" t="n">
-        <v>1.94884216785431</v>
+        <v>1.94884192943573</v>
       </c>
       <c r="H570" t="n">
         <v>32611</v>
@@ -16928,7 +16928,7 @@
         <v>2.15499997138977</v>
       </c>
       <c r="G571" t="n">
-        <v>1.93537056446075</v>
+        <v>1.93537068367004</v>
       </c>
       <c r="H571" t="n">
         <v>21921</v>
@@ -16957,7 +16957,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G572" t="n">
-        <v>1.91291868686676</v>
+        <v>1.91291856765747</v>
       </c>
       <c r="H572" t="n">
         <v>49060</v>
@@ -16986,7 +16986,7 @@
         <v>2.15499997138977</v>
       </c>
       <c r="G573" t="n">
-        <v>1.93537056446075</v>
+        <v>1.93537068367004</v>
       </c>
       <c r="H573" t="n">
         <v>29223</v>
@@ -17044,7 +17044,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G575" t="n">
-        <v>1.98476505279541</v>
+        <v>1.98476529121399</v>
       </c>
       <c r="H575" t="n">
         <v>39791</v>
@@ -17073,7 +17073,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G576" t="n">
-        <v>1.98476505279541</v>
+        <v>1.98476529121399</v>
       </c>
       <c r="H576" t="n">
         <v>50692</v>
@@ -17160,7 +17160,7 @@
         <v>2.26500010490417</v>
       </c>
       <c r="G579" t="n">
-        <v>2.03415989875793</v>
+        <v>2.03416013717651</v>
       </c>
       <c r="H579" t="n">
         <v>11681</v>
@@ -17189,7 +17189,7 @@
         <v>2.26500010490417</v>
       </c>
       <c r="G580" t="n">
-        <v>2.03415989875793</v>
+        <v>2.03416013717651</v>
       </c>
       <c r="H580" t="n">
         <v>33062</v>
@@ -17334,7 +17334,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G585" t="n">
-        <v>2.04763126373291</v>
+        <v>2.04763102531433</v>
       </c>
       <c r="H585" t="n">
         <v>8638</v>
@@ -17363,7 +17363,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G586" t="n">
-        <v>2.08355450630188</v>
+        <v>2.0835542678833</v>
       </c>
       <c r="H586" t="n">
         <v>83509</v>
@@ -17392,7 +17392,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G587" t="n">
-        <v>2.06110262870789</v>
+        <v>2.06110239028931</v>
       </c>
       <c r="H587" t="n">
         <v>59626</v>
@@ -17479,7 +17479,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G590" t="n">
-        <v>2.06559276580811</v>
+        <v>2.06559252738953</v>
       </c>
       <c r="H590" t="n">
         <v>18851</v>
@@ -17537,7 +17537,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G592" t="n">
-        <v>2.06110262870789</v>
+        <v>2.06110239028931</v>
       </c>
       <c r="H592" t="n">
         <v>23900</v>
@@ -17566,7 +17566,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G593" t="n">
-        <v>2.01170778274536</v>
+        <v>2.01170802116394</v>
       </c>
       <c r="H593" t="n">
         <v>123150</v>
@@ -17653,7 +17653,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G596" t="n">
-        <v>2.08355450630188</v>
+        <v>2.0835542678833</v>
       </c>
       <c r="H596" t="n">
         <v>23339</v>
@@ -17827,7 +17827,7 @@
         <v>2.47499990463257</v>
       </c>
       <c r="G602" t="n">
-        <v>2.22275757789612</v>
+        <v>2.22275733947754</v>
       </c>
       <c r="H602" t="n">
         <v>96271</v>
@@ -17856,7 +17856,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G603" t="n">
-        <v>2.21826672554016</v>
+        <v>2.21826696395874</v>
       </c>
       <c r="H603" t="n">
         <v>66824</v>
@@ -17914,7 +17914,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G605" t="n">
-        <v>2.11947751045227</v>
+        <v>2.11947774887085</v>
       </c>
       <c r="H605" t="n">
         <v>89012</v>
@@ -18030,7 +18030,7 @@
         <v>2.26500010490417</v>
       </c>
       <c r="G609" t="n">
-        <v>2.03415989875793</v>
+        <v>2.03416013717651</v>
       </c>
       <c r="H609" t="n">
         <v>53796</v>
@@ -18117,7 +18117,7 @@
         <v>2.27500009536743</v>
       </c>
       <c r="G612" t="n">
-        <v>2.04314064979553</v>
+        <v>2.04314088821411</v>
       </c>
       <c r="H612" t="n">
         <v>116656</v>
@@ -18146,7 +18146,7 @@
         <v>2.22499990463257</v>
       </c>
       <c r="G613" t="n">
-        <v>1.99823653697968</v>
+        <v>1.99823641777039</v>
       </c>
       <c r="H613" t="n">
         <v>76914</v>
@@ -18204,7 +18204,7 @@
         <v>2.15499997138977</v>
       </c>
       <c r="G615" t="n">
-        <v>1.93537056446075</v>
+        <v>1.93537068367004</v>
       </c>
       <c r="H615" t="n">
         <v>55377</v>
@@ -18262,7 +18262,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G617" t="n">
-        <v>2.04763126373291</v>
+        <v>2.04763102531433</v>
       </c>
       <c r="H617" t="n">
         <v>74739</v>
@@ -18320,7 +18320,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G619" t="n">
-        <v>2.06559276580811</v>
+        <v>2.06559252738953</v>
       </c>
       <c r="H619" t="n">
         <v>36072</v>
@@ -18378,7 +18378,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G621" t="n">
-        <v>2.04763126373291</v>
+        <v>2.04763102531433</v>
       </c>
       <c r="H621" t="n">
         <v>34438</v>
@@ -18436,7 +18436,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G623" t="n">
-        <v>2.06110262870789</v>
+        <v>2.06110239028931</v>
       </c>
       <c r="H623" t="n">
         <v>21291</v>
@@ -18552,7 +18552,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G627" t="n">
-        <v>2.04763126373291</v>
+        <v>2.04763102531433</v>
       </c>
       <c r="H627" t="n">
         <v>13812</v>
@@ -18581,7 +18581,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G628" t="n">
-        <v>2.06559276580811</v>
+        <v>2.06559252738953</v>
       </c>
       <c r="H628" t="n">
         <v>17736</v>
@@ -18610,7 +18610,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G629" t="n">
-        <v>2.02517914772034</v>
+        <v>2.02517890930176</v>
       </c>
       <c r="H629" t="n">
         <v>20116</v>
@@ -18639,7 +18639,7 @@
         <v>2.26500010490417</v>
       </c>
       <c r="G630" t="n">
-        <v>2.03415989875793</v>
+        <v>2.03416013717651</v>
       </c>
       <c r="H630" t="n">
         <v>6255</v>
@@ -18726,7 +18726,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G633" t="n">
-        <v>2.01170778274536</v>
+        <v>2.01170802116394</v>
       </c>
       <c r="H633" t="n">
         <v>29189</v>
@@ -18813,7 +18813,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G636" t="n">
-        <v>1.95782291889191</v>
+        <v>1.95782279968262</v>
       </c>
       <c r="H636" t="n">
         <v>18514</v>
@@ -18929,7 +18929,7 @@
         <v>2.22499990463257</v>
       </c>
       <c r="G640" t="n">
-        <v>1.99823653697968</v>
+        <v>1.99823641777039</v>
       </c>
       <c r="H640" t="n">
         <v>33589</v>
@@ -19045,7 +19045,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G644" t="n">
-        <v>1.9668036699295</v>
+        <v>1.96680343151093</v>
       </c>
       <c r="H644" t="n">
         <v>55833</v>
@@ -19074,7 +19074,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G645" t="n">
-        <v>1.95782291889191</v>
+        <v>1.95782279968262</v>
       </c>
       <c r="H645" t="n">
         <v>5655</v>
@@ -19103,7 +19103,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G646" t="n">
-        <v>1.9668036699295</v>
+        <v>1.96680343151093</v>
       </c>
       <c r="H646" t="n">
         <v>2659</v>
@@ -19132,7 +19132,7 @@
         <v>2.1949999332428</v>
       </c>
       <c r="G647" t="n">
-        <v>1.97129392623901</v>
+        <v>1.97129380702972</v>
       </c>
       <c r="H647" t="n">
         <v>2598</v>
@@ -19161,7 +19161,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G648" t="n">
-        <v>1.9668036699295</v>
+        <v>1.96680343151093</v>
       </c>
       <c r="H648" t="n">
         <v>8566</v>
@@ -19190,7 +19190,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G649" t="n">
-        <v>1.95782291889191</v>
+        <v>1.95782279968262</v>
       </c>
       <c r="H649" t="n">
         <v>11364</v>
@@ -19219,7 +19219,7 @@
         <v>2.18499994277954</v>
       </c>
       <c r="G650" t="n">
-        <v>1.96231305599213</v>
+        <v>1.96231317520142</v>
       </c>
       <c r="H650" t="n">
         <v>4540</v>
@@ -19277,7 +19277,7 @@
         <v>2.13499999046326</v>
       </c>
       <c r="G652" t="n">
-        <v>1.91740882396698</v>
+        <v>1.91740918159485</v>
       </c>
       <c r="H652" t="n">
         <v>14340</v>
@@ -19306,7 +19306,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G653" t="n">
-        <v>1.95782291889191</v>
+        <v>1.95782279968262</v>
       </c>
       <c r="H653" t="n">
         <v>7716</v>
@@ -19335,7 +19335,7 @@
         <v>2.15499997138977</v>
       </c>
       <c r="G654" t="n">
-        <v>1.93537056446075</v>
+        <v>1.93537068367004</v>
       </c>
       <c r="H654" t="n">
         <v>15993</v>
@@ -19364,7 +19364,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G655" t="n">
-        <v>1.94884216785431</v>
+        <v>1.94884192943573</v>
       </c>
       <c r="H655" t="n">
         <v>8943</v>
@@ -19393,7 +19393,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G656" t="n">
-        <v>1.89495670795441</v>
+        <v>1.89495694637299</v>
       </c>
       <c r="H656" t="n">
         <v>71608</v>
@@ -19451,7 +19451,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G658" t="n">
-        <v>1.89495670795441</v>
+        <v>1.89495694637299</v>
       </c>
       <c r="H658" t="n">
         <v>29865</v>
@@ -19480,7 +19480,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G659" t="n">
-        <v>1.93088030815125</v>
+        <v>1.93088018894196</v>
       </c>
       <c r="H659" t="n">
         <v>49869</v>
@@ -19596,7 +19596,7 @@
         <v>2.125</v>
       </c>
       <c r="G663" t="n">
-        <v>1.90842819213867</v>
+        <v>1.90842807292938</v>
       </c>
       <c r="H663" t="n">
         <v>16492</v>
@@ -19625,7 +19625,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G664" t="n">
-        <v>1.93088030815125</v>
+        <v>1.93088018894196</v>
       </c>
       <c r="H664" t="n">
         <v>15652</v>
@@ -19654,7 +19654,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G665" t="n">
-        <v>1.93088030815125</v>
+        <v>1.93088018894196</v>
       </c>
       <c r="H665" t="n">
         <v>8935</v>
@@ -19683,7 +19683,7 @@
         <v>2.14499998092651</v>
       </c>
       <c r="G666" t="n">
-        <v>1.92638981342316</v>
+        <v>1.92638969421387</v>
       </c>
       <c r="H666" t="n">
         <v>17689</v>
@@ -19770,7 +19770,7 @@
         <v>2.14499998092651</v>
       </c>
       <c r="G669" t="n">
-        <v>1.92638981342316</v>
+        <v>1.92638969421387</v>
       </c>
       <c r="H669" t="n">
         <v>28810</v>
@@ -19799,7 +19799,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G670" t="n">
-        <v>1.93088030815125</v>
+        <v>1.93088018894196</v>
       </c>
       <c r="H670" t="n">
         <v>35306</v>
@@ -19828,7 +19828,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G671" t="n">
-        <v>1.93088030815125</v>
+        <v>1.93088018894196</v>
       </c>
       <c r="H671" t="n">
         <v>17930</v>
@@ -19857,7 +19857,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G672" t="n">
-        <v>1.95782291889191</v>
+        <v>1.95782279968262</v>
       </c>
       <c r="H672" t="n">
         <v>30719</v>
@@ -19886,7 +19886,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G673" t="n">
-        <v>1.97578430175781</v>
+        <v>1.97578454017639</v>
       </c>
       <c r="H673" t="n">
         <v>17555</v>
@@ -19915,7 +19915,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G674" t="n">
-        <v>1.9668036699295</v>
+        <v>1.96680343151093</v>
       </c>
       <c r="H674" t="n">
         <v>11038</v>
@@ -19944,7 +19944,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G675" t="n">
-        <v>2.01170778274536</v>
+        <v>2.01170802116394</v>
       </c>
       <c r="H675" t="n">
         <v>40300</v>
@@ -20060,7 +20060,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G679" t="n">
-        <v>2.06559276580811</v>
+        <v>2.06559252738953</v>
       </c>
       <c r="H679" t="n">
         <v>71912</v>
@@ -20147,7 +20147,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G682" t="n">
-        <v>1.94884216785431</v>
+        <v>1.94884192943573</v>
       </c>
       <c r="H682" t="n">
         <v>39975</v>
@@ -20205,7 +20205,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G684" t="n">
-        <v>1.9668036699295</v>
+        <v>1.96680343151093</v>
       </c>
       <c r="H684" t="n">
         <v>15966</v>
@@ -20234,7 +20234,7 @@
         <v>2.21499991416931</v>
       </c>
       <c r="G685" t="n">
-        <v>1.98925566673279</v>
+        <v>1.98925578594208</v>
       </c>
       <c r="H685" t="n">
         <v>49471</v>
@@ -20350,7 +20350,7 @@
         <v>2.27500009536743</v>
       </c>
       <c r="G689" t="n">
-        <v>2.04314064979553</v>
+        <v>2.04314088821411</v>
       </c>
       <c r="H689" t="n">
         <v>10005</v>
@@ -20379,7 +20379,7 @@
         <v>2.26500010490417</v>
       </c>
       <c r="G690" t="n">
-        <v>2.03415989875793</v>
+        <v>2.03416013717651</v>
       </c>
       <c r="H690" t="n">
         <v>8390</v>
@@ -20437,7 +20437,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G692" t="n">
-        <v>2.02517914772034</v>
+        <v>2.02517890930176</v>
       </c>
       <c r="H692" t="n">
         <v>2595</v>
@@ -20553,7 +20553,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G696" t="n">
-        <v>2.01170778274536</v>
+        <v>2.01170802116394</v>
       </c>
       <c r="H696" t="n">
         <v>21043</v>
@@ -20582,7 +20582,7 @@
         <v>2.27500009536743</v>
       </c>
       <c r="G697" t="n">
-        <v>2.04314064979553</v>
+        <v>2.04314088821411</v>
       </c>
       <c r="H697" t="n">
         <v>8913</v>
@@ -20611,7 +20611,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G698" t="n">
-        <v>2.06110262870789</v>
+        <v>2.06110239028931</v>
       </c>
       <c r="H698" t="n">
         <v>7245</v>
@@ -20640,7 +20640,7 @@
         <v>2.27500009536743</v>
       </c>
       <c r="G699" t="n">
-        <v>2.04314064979553</v>
+        <v>2.04314088821411</v>
       </c>
       <c r="H699" t="n">
         <v>36164</v>
@@ -20727,7 +20727,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G702" t="n">
-        <v>2.02517914772034</v>
+        <v>2.02517890930176</v>
       </c>
       <c r="H702" t="n">
         <v>35459</v>
@@ -20814,7 +20814,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G705" t="n">
-        <v>2.02517914772034</v>
+        <v>2.02517890930176</v>
       </c>
       <c r="H705" t="n">
         <v>1661</v>
@@ -20843,7 +20843,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G706" t="n">
-        <v>1.97578430175781</v>
+        <v>1.97578454017639</v>
       </c>
       <c r="H706" t="n">
         <v>54288</v>
@@ -20872,7 +20872,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G707" t="n">
-        <v>1.91291868686676</v>
+        <v>1.91291856765747</v>
       </c>
       <c r="H707" t="n">
         <v>21836</v>
@@ -20930,7 +20930,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G709" t="n">
-        <v>1.85005271434784</v>
+        <v>1.85005259513855</v>
       </c>
       <c r="H709" t="n">
         <v>57600</v>
@@ -21075,7 +21075,7 @@
         <v>2.07500004768372</v>
       </c>
       <c r="G714" t="n">
-        <v>1.86352407932281</v>
+        <v>1.86352396011353</v>
       </c>
       <c r="H714" t="n">
         <v>30060</v>
@@ -21133,7 +21133,7 @@
         <v>1.99199998378754</v>
       </c>
       <c r="G716" t="n">
-        <v>1.78898298740387</v>
+        <v>1.78898286819458</v>
       </c>
       <c r="H716" t="n">
         <v>16731</v>
@@ -21162,7 +21162,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G717" t="n">
-        <v>1.76024436950684</v>
+        <v>1.76024413108826</v>
       </c>
       <c r="H717" t="n">
         <v>10455</v>
@@ -21191,7 +21191,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G718" t="n">
-        <v>1.75126361846924</v>
+        <v>1.75126349925995</v>
       </c>
       <c r="H718" t="n">
         <v>13797</v>
@@ -21220,7 +21220,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G719" t="n">
-        <v>1.76922500133514</v>
+        <v>1.76922512054443</v>
       </c>
       <c r="H719" t="n">
         <v>20654</v>
@@ -21278,7 +21278,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G721" t="n">
-        <v>1.65247416496277</v>
+        <v>1.65247428417206</v>
       </c>
       <c r="H721" t="n">
         <v>47767</v>
@@ -21307,7 +21307,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G722" t="n">
-        <v>1.65247416496277</v>
+        <v>1.65247428417206</v>
       </c>
       <c r="H722" t="n">
         <v>49356</v>
@@ -21394,7 +21394,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G725" t="n">
-        <v>1.76024436950684</v>
+        <v>1.76024413108826</v>
       </c>
       <c r="H725" t="n">
         <v>31378</v>
@@ -21423,7 +21423,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G726" t="n">
-        <v>1.67941665649414</v>
+        <v>1.67941677570343</v>
       </c>
       <c r="H726" t="n">
         <v>135018</v>
@@ -21452,7 +21452,7 @@
         <v>1.81599998474121</v>
       </c>
       <c r="G727" t="n">
-        <v>1.63092029094696</v>
+        <v>1.63092017173767</v>
       </c>
       <c r="H727" t="n">
         <v>33529</v>
@@ -21510,7 +21510,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G729" t="n">
-        <v>1.63451266288757</v>
+        <v>1.63451254367828</v>
       </c>
       <c r="H729" t="n">
         <v>10781</v>
@@ -21539,7 +21539,7 @@
         <v>1.81599998474121</v>
       </c>
       <c r="G730" t="n">
-        <v>1.63092029094696</v>
+        <v>1.63092017173767</v>
       </c>
       <c r="H730" t="n">
         <v>15018</v>
@@ -21568,7 +21568,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G731" t="n">
-        <v>1.63451266288757</v>
+        <v>1.63451254367828</v>
       </c>
       <c r="H731" t="n">
         <v>4539</v>
@@ -21597,7 +21597,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G732" t="n">
-        <v>1.63451266288757</v>
+        <v>1.63451254367828</v>
       </c>
       <c r="H732" t="n">
         <v>13877</v>
@@ -21626,7 +21626,7 @@
         <v>1.76199996471405</v>
       </c>
       <c r="G733" t="n">
-        <v>1.5824236869812</v>
+        <v>1.58242356777191</v>
       </c>
       <c r="H733" t="n">
         <v>6578</v>
@@ -21684,7 +21684,7 @@
         <v>1.72599995136261</v>
       </c>
       <c r="G735" t="n">
-        <v>1.55009269714355</v>
+        <v>1.55009257793427</v>
       </c>
       <c r="H735" t="n">
         <v>13578</v>
@@ -21713,7 +21713,7 @@
         <v>1.65400004386902</v>
       </c>
       <c r="G736" t="n">
-        <v>1.48543059825897</v>
+        <v>1.48543071746826</v>
       </c>
       <c r="H736" t="n">
         <v>40424</v>
@@ -21771,7 +21771,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G738" t="n">
-        <v>1.41897237300873</v>
+        <v>1.41897249221802</v>
       </c>
       <c r="H738" t="n">
         <v>69081</v>
@@ -21800,7 +21800,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G739" t="n">
-        <v>1.4279533624649</v>
+        <v>1.42795324325562</v>
       </c>
       <c r="H739" t="n">
         <v>104679</v>
@@ -22003,7 +22003,7 @@
         <v>1.49600005149841</v>
       </c>
       <c r="G746" t="n">
-        <v>1.34353339672089</v>
+        <v>1.34353351593018</v>
       </c>
       <c r="H746" t="n">
         <v>50501</v>
@@ -22148,7 +22148,7 @@
         <v>1.46599996089935</v>
       </c>
       <c r="G751" t="n">
-        <v>1.31659090518951</v>
+        <v>1.31659078598022</v>
       </c>
       <c r="H751" t="n">
         <v>28992</v>
@@ -22177,7 +22177,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G752" t="n">
-        <v>1.30222153663635</v>
+        <v>1.30222165584564</v>
       </c>
       <c r="H752" t="n">
         <v>11882</v>
@@ -22206,7 +22206,7 @@
         <v>1.40600001811981</v>
       </c>
       <c r="G753" t="n">
-        <v>1.26270592212677</v>
+        <v>1.26270580291748</v>
       </c>
       <c r="H753" t="n">
         <v>68829</v>
@@ -22264,7 +22264,7 @@
         <v>1.41600000858307</v>
       </c>
       <c r="G755" t="n">
-        <v>1.27168667316437</v>
+        <v>1.27168679237366</v>
       </c>
       <c r="H755" t="n">
         <v>45386</v>
@@ -22293,7 +22293,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G756" t="n">
-        <v>1.23935556411743</v>
+        <v>1.23935568332672</v>
       </c>
       <c r="H756" t="n">
         <v>25908</v>
@@ -22438,7 +22438,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G761" t="n">
-        <v>1.1675089597702</v>
+        <v>1.16750872135162</v>
       </c>
       <c r="H761" t="n">
         <v>77898</v>
@@ -22467,7 +22467,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G762" t="n">
-        <v>1.14954721927643</v>
+        <v>1.14954733848572</v>
       </c>
       <c r="H762" t="n">
         <v>30043</v>
@@ -22496,7 +22496,7 @@
         <v>1.30400002002716</v>
       </c>
       <c r="G763" t="n">
-        <v>1.1711014509201</v>
+        <v>1.17110133171082</v>
       </c>
       <c r="H763" t="n">
         <v>48686</v>
@@ -22525,7 +22525,7 @@
         <v>1.36800003051758</v>
       </c>
       <c r="G764" t="n">
-        <v>1.22857880592346</v>
+        <v>1.22857868671417</v>
       </c>
       <c r="H764" t="n">
         <v>113578</v>
@@ -22612,7 +22612,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G767" t="n">
-        <v>1.40999150276184</v>
+        <v>1.40999162197113</v>
       </c>
       <c r="H767" t="n">
         <v>144581</v>
@@ -22641,7 +22641,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G768" t="n">
-        <v>1.40999150276184</v>
+        <v>1.40999162197113</v>
       </c>
       <c r="H768" t="n">
         <v>41592</v>
@@ -22699,7 +22699,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G770" t="n">
-        <v>1.3561065196991</v>
+        <v>1.35610663890839</v>
       </c>
       <c r="H770" t="n">
         <v>32416</v>
@@ -22728,7 +22728,7 @@
         <v>1.51800000667572</v>
       </c>
       <c r="G771" t="n">
-        <v>1.36329126358032</v>
+        <v>1.36329114437103</v>
       </c>
       <c r="H771" t="n">
         <v>13363</v>
@@ -22757,7 +22757,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G772" t="n">
-        <v>1.31120252609253</v>
+        <v>1.31120240688324</v>
       </c>
       <c r="H772" t="n">
         <v>71525</v>
@@ -22815,7 +22815,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G774" t="n">
-        <v>1.3381450176239</v>
+        <v>1.33814489841461</v>
       </c>
       <c r="H774" t="n">
         <v>16878</v>
@@ -22844,7 +22844,7 @@
         <v>1.49600005149841</v>
       </c>
       <c r="G775" t="n">
-        <v>1.34353339672089</v>
+        <v>1.34353351593018</v>
       </c>
       <c r="H775" t="n">
         <v>8974</v>
@@ -22931,7 +22931,7 @@
         <v>1.47599995136261</v>
       </c>
       <c r="G778" t="n">
-        <v>1.32557165622711</v>
+        <v>1.32557153701782</v>
       </c>
       <c r="H778" t="n">
         <v>4157</v>
@@ -22960,7 +22960,7 @@
         <v>1.46599996089935</v>
       </c>
       <c r="G779" t="n">
-        <v>1.31659090518951</v>
+        <v>1.31659078598022</v>
       </c>
       <c r="H779" t="n">
         <v>15448</v>
@@ -22989,7 +22989,7 @@
         <v>1.47200000286102</v>
       </c>
       <c r="G780" t="n">
-        <v>1.32197940349579</v>
+        <v>1.3219792842865</v>
       </c>
       <c r="H780" t="n">
         <v>10353</v>
@@ -23018,7 +23018,7 @@
         <v>1.49600005149841</v>
       </c>
       <c r="G781" t="n">
-        <v>1.34353339672089</v>
+        <v>1.34353351593018</v>
       </c>
       <c r="H781" t="n">
         <v>72453</v>
@@ -23076,7 +23076,7 @@
         <v>1.49199998378754</v>
       </c>
       <c r="G783" t="n">
-        <v>1.33994102478027</v>
+        <v>1.33994114398956</v>
       </c>
       <c r="H783" t="n">
         <v>26343</v>
@@ -23105,7 +23105,7 @@
         <v>1.47599995136261</v>
       </c>
       <c r="G784" t="n">
-        <v>1.32557165622711</v>
+        <v>1.32557153701782</v>
       </c>
       <c r="H784" t="n">
         <v>15747</v>
@@ -23134,7 +23134,7 @@
         <v>1.46599996089935</v>
       </c>
       <c r="G785" t="n">
-        <v>1.31659090518951</v>
+        <v>1.31659078598022</v>
       </c>
       <c r="H785" t="n">
         <v>24673</v>
@@ -23163,7 +23163,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G786" t="n">
-        <v>1.31120252609253</v>
+        <v>1.31120240688324</v>
       </c>
       <c r="H786" t="n">
         <v>38062</v>
@@ -23221,7 +23221,7 @@
         <v>1.42799997329712</v>
       </c>
       <c r="G788" t="n">
-        <v>1.28246366977692</v>
+        <v>1.28246378898621</v>
       </c>
       <c r="H788" t="n">
         <v>63444</v>
@@ -23250,7 +23250,7 @@
         <v>1.40199995040894</v>
       </c>
       <c r="G789" t="n">
-        <v>1.25911355018616</v>
+        <v>1.25911343097687</v>
       </c>
       <c r="H789" t="n">
         <v>38229</v>
@@ -23279,7 +23279,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G790" t="n">
-        <v>1.24833655357361</v>
+        <v>1.24833643436432</v>
       </c>
       <c r="H790" t="n">
         <v>20252</v>
@@ -23337,7 +23337,7 @@
         <v>1.38800001144409</v>
       </c>
       <c r="G792" t="n">
-        <v>1.24654042720795</v>
+        <v>1.24654030799866</v>
       </c>
       <c r="H792" t="n">
         <v>43409</v>
@@ -23395,7 +23395,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G794" t="n">
-        <v>1.45309960842133</v>
+        <v>1.45309972763062</v>
       </c>
       <c r="H794" t="n">
         <v>697644</v>
@@ -23482,7 +23482,7 @@
         <v>1.89800000190735</v>
       </c>
       <c r="G797" t="n">
-        <v>1.70456314086914</v>
+        <v>1.70456302165985</v>
       </c>
       <c r="H797" t="n">
         <v>898372</v>
@@ -23511,7 +23511,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G798" t="n">
-        <v>1.65247416496277</v>
+        <v>1.65247428417206</v>
       </c>
       <c r="H798" t="n">
         <v>461676</v>
@@ -23569,7 +23569,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G800" t="n">
-        <v>1.65247416496277</v>
+        <v>1.65247428417206</v>
       </c>
       <c r="H800" t="n">
         <v>179707</v>
@@ -23598,7 +23598,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G801" t="n">
-        <v>1.84107184410095</v>
+        <v>1.84107172489166</v>
       </c>
       <c r="H801" t="n">
         <v>1306104</v>
@@ -23656,7 +23656,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G803" t="n">
-        <v>1.88597583770752</v>
+        <v>1.88597595691681</v>
       </c>
       <c r="H803" t="n">
         <v>354581</v>
@@ -23685,7 +23685,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G804" t="n">
-        <v>1.85005271434784</v>
+        <v>1.85005259513855</v>
       </c>
       <c r="H804" t="n">
         <v>291089</v>
@@ -23743,7 +23743,7 @@
         <v>2.14499998092651</v>
       </c>
       <c r="G806" t="n">
-        <v>1.92638981342316</v>
+        <v>1.92638969421387</v>
       </c>
       <c r="H806" t="n">
         <v>684242</v>
@@ -23801,7 +23801,7 @@
         <v>2.07500004768372</v>
       </c>
       <c r="G808" t="n">
-        <v>1.86352407932281</v>
+        <v>1.86352396011353</v>
       </c>
       <c r="H808" t="n">
         <v>387958</v>
@@ -23830,7 +23830,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G809" t="n">
-        <v>1.85005271434784</v>
+        <v>1.85005259513855</v>
       </c>
       <c r="H809" t="n">
         <v>165023</v>
@@ -23917,7 +23917,7 @@
         <v>2.04500007629395</v>
       </c>
       <c r="G812" t="n">
-        <v>1.83658146858215</v>
+        <v>1.83658134937286</v>
       </c>
       <c r="H812" t="n">
         <v>184309</v>
@@ -24033,7 +24033,7 @@
         <v>1.95799994468689</v>
       </c>
       <c r="G816" t="n">
-        <v>1.75844812393188</v>
+        <v>1.7584480047226</v>
       </c>
       <c r="H816" t="n">
         <v>228707</v>
@@ -24091,7 +24091,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G818" t="n">
-        <v>1.68839764595032</v>
+        <v>1.68839740753174</v>
       </c>
       <c r="H818" t="n">
         <v>195439</v>
@@ -24149,7 +24149,7 @@
         <v>1.90600001811981</v>
       </c>
       <c r="G820" t="n">
-        <v>1.71174764633179</v>
+        <v>1.71174776554108</v>
       </c>
       <c r="H820" t="n">
         <v>125176</v>
@@ -24178,7 +24178,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G821" t="n">
-        <v>1.73330175876617</v>
+        <v>1.73330187797546</v>
       </c>
       <c r="H821" t="n">
         <v>92821</v>
@@ -24207,7 +24207,7 @@
         <v>1.88399994373322</v>
       </c>
       <c r="G822" t="n">
-        <v>1.69198989868164</v>
+        <v>1.69198977947235</v>
       </c>
       <c r="H822" t="n">
         <v>48768</v>
@@ -24294,7 +24294,7 @@
         <v>1.90600001811981</v>
       </c>
       <c r="G825" t="n">
-        <v>1.71174764633179</v>
+        <v>1.71174776554108</v>
       </c>
       <c r="H825" t="n">
         <v>44756</v>
@@ -24323,7 +24323,7 @@
         <v>2.07500004768372</v>
       </c>
       <c r="G826" t="n">
-        <v>1.86352407932281</v>
+        <v>1.86352396011353</v>
       </c>
       <c r="H826" t="n">
         <v>973336</v>
@@ -24352,7 +24352,7 @@
         <v>2.21499991416931</v>
       </c>
       <c r="G827" t="n">
-        <v>1.98925566673279</v>
+        <v>1.98925578594208</v>
       </c>
       <c r="H827" t="n">
         <v>1267819</v>
@@ -24410,7 +24410,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G829" t="n">
-        <v>2.06559276580811</v>
+        <v>2.06559252738953</v>
       </c>
       <c r="H829" t="n">
         <v>658018</v>
@@ -24439,7 +24439,7 @@
         <v>2.31500005722046</v>
       </c>
       <c r="G830" t="n">
-        <v>2.0790638923645</v>
+        <v>2.07906413078308</v>
       </c>
       <c r="H830" t="n">
         <v>590495</v>
@@ -24468,7 +24468,7 @@
         <v>2.34500002861023</v>
       </c>
       <c r="G831" t="n">
-        <v>2.10600662231445</v>
+        <v>2.10600638389587</v>
       </c>
       <c r="H831" t="n">
         <v>232693</v>
@@ -24497,7 +24497,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G832" t="n">
-        <v>2.01170778274536</v>
+        <v>2.01170802116394</v>
       </c>
       <c r="H832" t="n">
         <v>579044</v>
@@ -24526,7 +24526,7 @@
         <v>2.14499998092651</v>
       </c>
       <c r="G833" t="n">
-        <v>1.92638981342316</v>
+        <v>1.92638969421387</v>
       </c>
       <c r="H833" t="n">
         <v>353418</v>
@@ -24584,7 +24584,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G835" t="n">
-        <v>1.97578430175781</v>
+        <v>1.97578454017639</v>
       </c>
       <c r="H835" t="n">
         <v>122181</v>
@@ -24613,7 +24613,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G836" t="n">
-        <v>1.97578430175781</v>
+        <v>1.97578454017639</v>
       </c>
       <c r="H836" t="n">
         <v>98899</v>
@@ -24671,7 +24671,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G838" t="n">
-        <v>2.1374397277832</v>
+        <v>2.13743948936462</v>
       </c>
       <c r="H838" t="n">
         <v>430992</v>
@@ -24874,7 +24874,7 @@
         <v>2.39499998092651</v>
       </c>
       <c r="G845" t="n">
-        <v>2.1509108543396</v>
+        <v>2.15091037750244</v>
       </c>
       <c r="H845" t="n">
         <v>87043</v>
@@ -24990,7 +24990,7 @@
         <v>2.46499991416931</v>
       </c>
       <c r="G849" t="n">
-        <v>2.21377635002136</v>
+        <v>2.21377658843994</v>
       </c>
       <c r="H849" t="n">
         <v>455520</v>
@@ -25019,7 +25019,7 @@
         <v>2.36500000953674</v>
       </c>
       <c r="G850" t="n">
-        <v>2.12396812438965</v>
+        <v>2.12396836280823</v>
       </c>
       <c r="H850" t="n">
         <v>527196</v>
@@ -25048,7 +25048,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G851" t="n">
-        <v>2.04763126373291</v>
+        <v>2.04763102531433</v>
       </c>
       <c r="H851" t="n">
         <v>566449</v>
@@ -25077,7 +25077,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G852" t="n">
-        <v>1.9668036699295</v>
+        <v>1.96680343151093</v>
       </c>
       <c r="H852" t="n">
         <v>290714</v>
@@ -25106,7 +25106,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G853" t="n">
-        <v>1.97578430175781</v>
+        <v>1.97578454017639</v>
       </c>
       <c r="H853" t="n">
         <v>113970</v>
@@ -25135,7 +25135,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G854" t="n">
-        <v>1.9668036